--- a/04_结果/示例审批/两基金_m30新版式示例_公式说明版.xlsx
+++ b/04_结果/示例审批/两基金_m30新版式示例_公式说明版.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -470,35 +470,112 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>统计头公式：Hit Ratio=Up/(Up+Down)，Up/Down=COUNTIF(数据区,"&gt;0"或"&lt;0")，Average=AVERAGE(数据区) 等。</t>
+          <t>公式说明：</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>回报率公式：=(今日AdjClose/前一交易日AdjClose-1)*100；</t>
+          <t>1. 统计头公式（第2-10行）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ISNUMBER 用于判断两个 Adj Close 都是数字才计算，避免空白导致 #DIV/0!。</t>
+          <t xml:space="preserve">   Hit Ratio = Up Count / (Up Count + Down Count)；</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>策略公式：=IF(条件, 基金次日回报, "")；条件引用回报率列，满足则显示次日实际回报，否则留空。</t>
+          <t xml:space="preserve">   Up Count = COUNTIF(该列数据区, "&gt;0")；Down Count = COUNTIF(该列数据区, "&lt;0")；</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>合并公式：同日多条策略触发时，按 |全历史Average| 最大者取值；未触发留空。</t>
+          <t xml:space="preserve">   Average = AVERAGE(该列数据区)；Max/Min/Count/Std/Sum 对应 MAX/MIN/COUNT/STDEV/SUM。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2. 回报率公式</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   =IF(COUNT(B14:B15)=2,(B14/B15-1)*100,"")</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   含义：B14 是今日 Adj Close，B15 是前一交易日 Adj Close；</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   COUNT 判断两天价格是否都存在（都是数字时=2），存在才计算当日回报率，否则留空，避免 #DIV/0!。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3. 策略公式</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   =IF(条件, 基金次日回报, "")</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   条件引用回报率列；满足条件时显示基金次日实际回报（日期降序，次日=上一行），否则留空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4. 合并公式</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   策略列按 |全历史Average| 从高到低排列，合并列取第一个非空策略：</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   =IF(策略1&lt;&gt;"",策略1,IF(策略2&lt;&gt;"",策略2,策略3))</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   含义：同一天多条策略触发时，历史 |Average| 最大的策略生效；全部未触发则留空。</t>
         </is>
       </c>
     </row>
@@ -1773,14 +1850,14 @@
       </c>
       <c r="X13" s="4" t="inlineStr">
         <is>
+          <t>HYG&lt;0 且 TIP&gt;0，买基金第二天</t>
+        </is>
+      </c>
+      <c r="Y13" s="4" t="inlineStr">
+        <is>
           <t>EEM&gt;0 且 GLD&lt;0 且 HYG&gt;0，买基金第二天</t>
         </is>
       </c>
-      <c r="Y13" s="4" t="inlineStr">
-        <is>
-          <t>HYG&lt;0 且 TIP&gt;0，买基金第二天</t>
-        </is>
-      </c>
       <c r="Z13" s="4" t="inlineStr">
         <is>
           <t>Ultra NASDAQ-100 ProFunds Investor Class（UOPIX）合并效果</t>
@@ -1788,17 +1865,17 @@
       </c>
       <c r="AA13" s="4" t="inlineStr">
         <is>
+          <t>GDX&gt;0 且 XLC&lt;0，买基金第二天</t>
+        </is>
+      </c>
+      <c r="AB13" s="4" t="inlineStr">
+        <is>
           <t>XLF&lt;=-1% 且 基金&lt;0，买基金第二天</t>
         </is>
       </c>
-      <c r="AB13" s="4" t="inlineStr">
+      <c r="AC13" s="4" t="inlineStr">
         <is>
           <t>FXY&gt;0 且 GDX&gt;0，买基金第二天</t>
-        </is>
-      </c>
-      <c r="AC13" s="4" t="inlineStr">
-        <is>
-          <t>GDX&gt;0 且 XLC&lt;0，买基金第二天</t>
         </is>
       </c>
       <c r="AD13" s="4" t="inlineStr">
@@ -1817,62 +1894,62 @@
         <v>164.02</v>
       </c>
       <c r="C14" s="5">
-        <f>IF(AND(ISNUMBER(B14),ISNUMBER(B15)),(B14/B15-1)*100,"")</f>
+        <f>IF(COUNT(B14:B15)=2,(B14/B15-1)*100,"")</f>
         <v/>
       </c>
       <c r="D14" s="5" t="n">
         <v>66</v>
       </c>
       <c r="E14" s="5">
-        <f>IF(AND(ISNUMBER(D14),ISNUMBER(D15)),(D14/D15-1)*100,"")</f>
+        <f>IF(COUNT(D14:D15)=2,(D14/D15-1)*100,"")</f>
         <v/>
       </c>
       <c r="F14" s="5" t="n">
         <v>79.55</v>
       </c>
       <c r="G14" s="5">
-        <f>IF(AND(ISNUMBER(F14),ISNUMBER(F15)),(F14/F15-1)*100,"")</f>
+        <f>IF(COUNT(F14:F15)=2,(F14/F15-1)*100,"")</f>
         <v/>
       </c>
       <c r="H14" s="5" t="n">
         <v>57.88</v>
       </c>
       <c r="I14" s="5">
-        <f>IF(AND(ISNUMBER(H14),ISNUMBER(H15)),(H14/H15-1)*100,"")</f>
+        <f>IF(COUNT(H14:H15)=2,(H14/H15-1)*100,"")</f>
         <v/>
       </c>
       <c r="J14" s="5" t="n">
         <v>77.92</v>
       </c>
       <c r="K14" s="5">
-        <f>IF(AND(ISNUMBER(J14),ISNUMBER(J15)),(J14/J15-1)*100,"")</f>
+        <f>IF(COUNT(J14:J15)=2,(J14/J15-1)*100,"")</f>
         <v/>
       </c>
       <c r="L14" s="5" t="n">
         <v/>
       </c>
       <c r="M14" s="5">
-        <f>IF(AND(ISNUMBER(L14),ISNUMBER(L15)),(L14/L15-1)*100,"")</f>
+        <f>IF(COUNT(L14:L15)=2,(L14/L15-1)*100,"")</f>
         <v/>
       </c>
       <c r="N14" s="5" t="n"/>
       <c r="O14" s="5">
-        <f>IF(AND(ISNUMBER(N14),ISNUMBER(N15)),(N14/N15-1)*100,"")</f>
+        <f>IF(COUNT(N14:N15)=2,(N14/N15-1)*100,"")</f>
         <v/>
       </c>
       <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5">
-        <f>IF(AND(ISNUMBER(P14),ISNUMBER(P15)),(P14/P15-1)*100,"")</f>
+        <f>IF(COUNT(P14:P15)=2,(P14/P15-1)*100,"")</f>
         <v/>
       </c>
       <c r="R14" s="5" t="n"/>
       <c r="S14" s="5">
-        <f>IF(AND(ISNUMBER(R14),ISNUMBER(R15)),(R14/R15-1)*100,"")</f>
+        <f>IF(COUNT(R14:R15)=2,(R14/R15-1)*100,"")</f>
         <v/>
       </c>
       <c r="T14" s="5" t="n"/>
       <c r="U14" s="5">
-        <f>IF(AND(ISNUMBER(T14),ISNUMBER(T15)),(T14/T15-1)*100,"")</f>
+        <f>IF(COUNT(T14:T15)=2,(T14/T15-1)*100,"")</f>
         <v/>
       </c>
       <c r="V14" s="5" t="n"/>
@@ -1880,14 +1957,14 @@
       <c r="X14" s="5" t="inlineStr"/>
       <c r="Y14" s="5" t="inlineStr"/>
       <c r="Z14" s="5">
-        <f>IF(AND(ISNUMBER(W14),0.549579&gt;=MAX(IF(ISNUMBER(X14),0.299732,-1),IF(ISNUMBER(Y14),0.323835,-1))),W14,IF(AND(ISNUMBER(X14),0.299732&gt;MAX(IF(ISNUMBER(W14),0.549579,-1),IF(ISNUMBER(Y14),0.323835,-1))),X14,IF(AND(ISNUMBER(Y14),0.323835&gt;MAX(IF(ISNUMBER(W14),0.549579,-1),IF(ISNUMBER(X14),0.299732,-1))),Y14,"")))</f>
+        <f>IF(W14&lt;&gt;"",W14,IF(X14&lt;&gt;"",X14,Y14))</f>
         <v/>
       </c>
       <c r="AA14" s="5" t="inlineStr"/>
       <c r="AB14" s="5" t="inlineStr"/>
       <c r="AC14" s="5" t="inlineStr"/>
       <c r="AD14" s="5">
-        <f>IF(AND(ISNUMBER(AA14),0.408167&gt;=MAX(IF(ISNUMBER(AB14),0.31868,-1),IF(ISNUMBER(AC14),0.510996,-1))),AA14,IF(AND(ISNUMBER(AB14),0.31868&gt;MAX(IF(ISNUMBER(AA14),0.408167,-1),IF(ISNUMBER(AC14),0.510996,-1))),AB14,IF(AND(ISNUMBER(AC14),0.510996&gt;MAX(IF(ISNUMBER(AA14),0.408167,-1),IF(ISNUMBER(AB14),0.31868,-1))),AC14,"")))</f>
+        <f>IF(AA14&lt;&gt;"",AA14,IF(AB14&lt;&gt;"",AB14,AC14))</f>
         <v/>
       </c>
     </row>
@@ -1901,62 +1978,62 @@
         <v>153.8</v>
       </c>
       <c r="C15" s="5">
-        <f>IF(AND(ISNUMBER(B15),ISNUMBER(B16)),(B15/B16-1)*100,"")</f>
+        <f>IF(COUNT(B15:B16)=2,(B15/B16-1)*100,"")</f>
         <v/>
       </c>
       <c r="D15" s="5" t="n">
         <v>64.31999999999999</v>
       </c>
       <c r="E15" s="5">
-        <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16)),(D15/D16-1)*100,"")</f>
+        <f>IF(COUNT(D15:D16)=2,(D15/D16-1)*100,"")</f>
         <v/>
       </c>
       <c r="F15" s="5" t="n">
         <v>79.31</v>
       </c>
       <c r="G15" s="5">
-        <f>IF(AND(ISNUMBER(F15),ISNUMBER(F16)),(F15/F16-1)*100,"")</f>
+        <f>IF(COUNT(F15:F16)=2,(F15/F16-1)*100,"")</f>
         <v/>
       </c>
       <c r="H15" s="5" t="n">
         <v>57.38</v>
       </c>
       <c r="I15" s="5">
-        <f>IF(AND(ISNUMBER(H15),ISNUMBER(H16)),(H15/H16-1)*100,"")</f>
+        <f>IF(COUNT(H15:H16)=2,(H15/H16-1)*100,"")</f>
         <v/>
       </c>
       <c r="J15" s="5" t="n">
         <v>76.05</v>
       </c>
       <c r="K15" s="5">
-        <f>IF(AND(ISNUMBER(J15),ISNUMBER(J16)),(J15/J16-1)*100,"")</f>
+        <f>IF(COUNT(J15:J16)=2,(J15/J16-1)*100,"")</f>
         <v/>
       </c>
       <c r="L15" s="5" t="n">
         <v/>
       </c>
       <c r="M15" s="5">
-        <f>IF(AND(ISNUMBER(L15),ISNUMBER(L16)),(L15/L16-1)*100,"")</f>
+        <f>IF(COUNT(L15:L16)=2,(L15/L16-1)*100,"")</f>
         <v/>
       </c>
       <c r="N15" s="5" t="n"/>
       <c r="O15" s="5">
-        <f>IF(AND(ISNUMBER(N15),ISNUMBER(N16)),(N15/N16-1)*100,"")</f>
+        <f>IF(COUNT(N15:N16)=2,(N15/N16-1)*100,"")</f>
         <v/>
       </c>
       <c r="P15" s="5" t="n"/>
       <c r="Q15" s="5">
-        <f>IF(AND(ISNUMBER(P15),ISNUMBER(P16)),(P15/P16-1)*100,"")</f>
+        <f>IF(COUNT(P15:P16)=2,(P15/P16-1)*100,"")</f>
         <v/>
       </c>
       <c r="R15" s="5" t="n"/>
       <c r="S15" s="5">
-        <f>IF(AND(ISNUMBER(R15),ISNUMBER(R16)),(R15/R16-1)*100,"")</f>
+        <f>IF(COUNT(R15:R16)=2,(R15/R16-1)*100,"")</f>
         <v/>
       </c>
       <c r="T15" s="5" t="n"/>
       <c r="U15" s="5">
-        <f>IF(AND(ISNUMBER(T15),ISNUMBER(T16)),(T15/T16-1)*100,"")</f>
+        <f>IF(COUNT(T15:T16)=2,(T15/T16-1)*100,"")</f>
         <v/>
       </c>
       <c r="V15" s="5" t="n"/>
@@ -1965,31 +2042,31 @@
         <v/>
       </c>
       <c r="X15" s="5">
+        <f>IF(AND(K15&lt;0,M15&gt;0),C14,"")</f>
+        <v/>
+      </c>
+      <c r="Y15" s="5">
         <f>IF(AND(G15&gt;0,I15&lt;0,K15&gt;0),C14,"")</f>
         <v/>
       </c>
-      <c r="Y15" s="5">
-        <f>IF(AND(K15&lt;0,M15&gt;0),C14,"")</f>
-        <v/>
-      </c>
       <c r="Z15" s="5">
-        <f>IF(AND(ISNUMBER(W15),0.549579&gt;=MAX(IF(ISNUMBER(X15),0.299732,-1),IF(ISNUMBER(Y15),0.323835,-1))),W15,IF(AND(ISNUMBER(X15),0.299732&gt;MAX(IF(ISNUMBER(W15),0.549579,-1),IF(ISNUMBER(Y15),0.323835,-1))),X15,IF(AND(ISNUMBER(Y15),0.323835&gt;MAX(IF(ISNUMBER(W15),0.549579,-1),IF(ISNUMBER(X15),0.299732,-1))),Y15,"")))</f>
+        <f>IF(W15&lt;&gt;"",W15,IF(X15&lt;&gt;"",X15,Y15))</f>
         <v/>
       </c>
       <c r="AA15" s="5">
+        <f>IF(AND(S15&gt;0,U15&lt;0),E14,"")</f>
+        <v/>
+      </c>
+      <c r="AB15" s="5">
         <f>IF(AND(O15&lt;=-1,E15&lt;0),E14,"")</f>
         <v/>
       </c>
-      <c r="AB15" s="5">
+      <c r="AC15" s="5">
         <f>IF(AND(Q15&gt;0,S15&gt;0),E14,"")</f>
         <v/>
       </c>
-      <c r="AC15" s="5">
-        <f>IF(AND(S15&gt;0,U15&lt;0),E14,"")</f>
-        <v/>
-      </c>
       <c r="AD15" s="5">
-        <f>IF(AND(ISNUMBER(AA15),0.408167&gt;=MAX(IF(ISNUMBER(AB15),0.31868,-1),IF(ISNUMBER(AC15),0.510996,-1))),AA15,IF(AND(ISNUMBER(AB15),0.31868&gt;MAX(IF(ISNUMBER(AA15),0.408167,-1),IF(ISNUMBER(AC15),0.510996,-1))),AB15,IF(AND(ISNUMBER(AC15),0.510996&gt;MAX(IF(ISNUMBER(AA15),0.408167,-1),IF(ISNUMBER(AB15),0.31868,-1))),AC15,"")))</f>
+        <f>IF(AA15&lt;&gt;"",AA15,IF(AB15&lt;&gt;"",AB15,AC15))</f>
         <v/>
       </c>
     </row>
@@ -2003,62 +2080,62 @@
         <v>148.6</v>
       </c>
       <c r="C16" s="5">
-        <f>IF(AND(ISNUMBER(B16),ISNUMBER(B17)),(B16/B17-1)*100,"")</f>
+        <f>IF(COUNT(B16:B17)=2,(B16/B17-1)*100,"")</f>
         <v/>
       </c>
       <c r="D16" s="5" t="n">
         <v>64.09</v>
       </c>
       <c r="E16" s="5">
-        <f>IF(AND(ISNUMBER(D16),ISNUMBER(D17)),(D16/D17-1)*100,"")</f>
+        <f>IF(COUNT(D16:D17)=2,(D16/D17-1)*100,"")</f>
         <v/>
       </c>
       <c r="F16" s="5" t="n">
         <v>79.096</v>
       </c>
       <c r="G16" s="5">
-        <f>IF(AND(ISNUMBER(F16),ISNUMBER(F17)),(F16/F17-1)*100,"")</f>
+        <f>IF(COUNT(F16:F17)=2,(F16/F17-1)*100,"")</f>
         <v/>
       </c>
       <c r="H16" s="5" t="n">
         <v>56.94</v>
       </c>
       <c r="I16" s="5">
-        <f>IF(AND(ISNUMBER(H16),ISNUMBER(H17)),(H16/H17-1)*100,"")</f>
+        <f>IF(COUNT(H16:H17)=2,(H16/H17-1)*100,"")</f>
         <v/>
       </c>
       <c r="J16" s="5" t="n">
         <v>74.09999999999999</v>
       </c>
       <c r="K16" s="5">
-        <f>IF(AND(ISNUMBER(J16),ISNUMBER(J17)),(J16/J17-1)*100,"")</f>
+        <f>IF(COUNT(J16:J17)=2,(J16/J17-1)*100,"")</f>
         <v/>
       </c>
       <c r="L16" s="5" t="n">
         <v/>
       </c>
       <c r="M16" s="5">
-        <f>IF(AND(ISNUMBER(L16),ISNUMBER(L17)),(L16/L17-1)*100,"")</f>
+        <f>IF(COUNT(L16:L17)=2,(L16/L17-1)*100,"")</f>
         <v/>
       </c>
       <c r="N16" s="5" t="n"/>
       <c r="O16" s="5">
-        <f>IF(AND(ISNUMBER(N16),ISNUMBER(N17)),(N16/N17-1)*100,"")</f>
+        <f>IF(COUNT(N16:N17)=2,(N16/N17-1)*100,"")</f>
         <v/>
       </c>
       <c r="P16" s="5" t="n"/>
       <c r="Q16" s="5">
-        <f>IF(AND(ISNUMBER(P16),ISNUMBER(P17)),(P16/P17-1)*100,"")</f>
+        <f>IF(COUNT(P16:P17)=2,(P16/P17-1)*100,"")</f>
         <v/>
       </c>
       <c r="R16" s="5" t="n"/>
       <c r="S16" s="5">
-        <f>IF(AND(ISNUMBER(R16),ISNUMBER(R17)),(R16/R17-1)*100,"")</f>
+        <f>IF(COUNT(R16:R17)=2,(R16/R17-1)*100,"")</f>
         <v/>
       </c>
       <c r="T16" s="5" t="n"/>
       <c r="U16" s="5">
-        <f>IF(AND(ISNUMBER(T16),ISNUMBER(T17)),(T16/T17-1)*100,"")</f>
+        <f>IF(COUNT(T16:T17)=2,(T16/T17-1)*100,"")</f>
         <v/>
       </c>
       <c r="V16" s="5" t="n"/>
@@ -2067,31 +2144,31 @@
         <v/>
       </c>
       <c r="X16" s="5">
+        <f>IF(AND(K16&lt;0,M16&gt;0),C15,"")</f>
+        <v/>
+      </c>
+      <c r="Y16" s="5">
         <f>IF(AND(G16&gt;0,I16&lt;0,K16&gt;0),C15,"")</f>
         <v/>
       </c>
-      <c r="Y16" s="5">
-        <f>IF(AND(K16&lt;0,M16&gt;0),C15,"")</f>
-        <v/>
-      </c>
       <c r="Z16" s="5">
-        <f>IF(AND(ISNUMBER(W16),0.549579&gt;=MAX(IF(ISNUMBER(X16),0.299732,-1),IF(ISNUMBER(Y16),0.323835,-1))),W16,IF(AND(ISNUMBER(X16),0.299732&gt;MAX(IF(ISNUMBER(W16),0.549579,-1),IF(ISNUMBER(Y16),0.323835,-1))),X16,IF(AND(ISNUMBER(Y16),0.323835&gt;MAX(IF(ISNUMBER(W16),0.549579,-1),IF(ISNUMBER(X16),0.299732,-1))),Y16,"")))</f>
+        <f>IF(W16&lt;&gt;"",W16,IF(X16&lt;&gt;"",X16,Y16))</f>
         <v/>
       </c>
       <c r="AA16" s="5">
+        <f>IF(AND(S16&gt;0,U16&lt;0),E15,"")</f>
+        <v/>
+      </c>
+      <c r="AB16" s="5">
         <f>IF(AND(O16&lt;=-1,E16&lt;0),E15,"")</f>
         <v/>
       </c>
-      <c r="AB16" s="5">
+      <c r="AC16" s="5">
         <f>IF(AND(Q16&gt;0,S16&gt;0),E15,"")</f>
         <v/>
       </c>
-      <c r="AC16" s="5">
-        <f>IF(AND(S16&gt;0,U16&lt;0),E15,"")</f>
-        <v/>
-      </c>
       <c r="AD16" s="5">
-        <f>IF(AND(ISNUMBER(AA16),0.408167&gt;=MAX(IF(ISNUMBER(AB16),0.31868,-1),IF(ISNUMBER(AC16),0.510996,-1))),AA16,IF(AND(ISNUMBER(AB16),0.31868&gt;MAX(IF(ISNUMBER(AA16),0.408167,-1),IF(ISNUMBER(AC16),0.510996,-1))),AB16,IF(AND(ISNUMBER(AC16),0.510996&gt;MAX(IF(ISNUMBER(AA16),0.408167,-1),IF(ISNUMBER(AB16),0.31868,-1))),AC16,"")))</f>
+        <f>IF(AA16&lt;&gt;"",AA16,IF(AB16&lt;&gt;"",AB16,AC16))</f>
         <v/>
       </c>
     </row>
@@ -2105,62 +2182,62 @@
         <v>146.84</v>
       </c>
       <c r="C17" s="5">
-        <f>IF(AND(ISNUMBER(B17),ISNUMBER(B18)),(B17/B18-1)*100,"")</f>
+        <f>IF(COUNT(B17:B18)=2,(B17/B18-1)*100,"")</f>
         <v/>
       </c>
       <c r="D17" s="5" t="n">
         <v>63.59</v>
       </c>
       <c r="E17" s="5">
-        <f>IF(AND(ISNUMBER(D17),ISNUMBER(D18)),(D17/D18-1)*100,"")</f>
+        <f>IF(COUNT(D17:D18)=2,(D17/D18-1)*100,"")</f>
         <v/>
       </c>
       <c r="F17" s="5" t="n">
         <v>79.086</v>
       </c>
       <c r="G17" s="5">
-        <f>IF(AND(ISNUMBER(F17),ISNUMBER(F18)),(F17/F18-1)*100,"")</f>
+        <f>IF(COUNT(F17:F18)=2,(F17/F18-1)*100,"")</f>
         <v/>
       </c>
       <c r="H17" s="5" t="n">
         <v>57</v>
       </c>
       <c r="I17" s="5">
-        <f>IF(AND(ISNUMBER(H17),ISNUMBER(H18)),(H17/H18-1)*100,"")</f>
+        <f>IF(COUNT(H17:H18)=2,(H17/H18-1)*100,"")</f>
         <v/>
       </c>
       <c r="J17" s="5" t="n">
         <v>76.78</v>
       </c>
       <c r="K17" s="5">
-        <f>IF(AND(ISNUMBER(J17),ISNUMBER(J18)),(J17/J18-1)*100,"")</f>
+        <f>IF(COUNT(J17:J18)=2,(J17/J18-1)*100,"")</f>
         <v/>
       </c>
       <c r="L17" s="5" t="n">
         <v/>
       </c>
       <c r="M17" s="5">
-        <f>IF(AND(ISNUMBER(L17),ISNUMBER(L18)),(L17/L18-1)*100,"")</f>
+        <f>IF(COUNT(L17:L18)=2,(L17/L18-1)*100,"")</f>
         <v/>
       </c>
       <c r="N17" s="5" t="n"/>
       <c r="O17" s="5">
-        <f>IF(AND(ISNUMBER(N17),ISNUMBER(N18)),(N17/N18-1)*100,"")</f>
+        <f>IF(COUNT(N17:N18)=2,(N17/N18-1)*100,"")</f>
         <v/>
       </c>
       <c r="P17" s="5" t="n"/>
       <c r="Q17" s="5">
-        <f>IF(AND(ISNUMBER(P17),ISNUMBER(P18)),(P17/P18-1)*100,"")</f>
+        <f>IF(COUNT(P17:P18)=2,(P17/P18-1)*100,"")</f>
         <v/>
       </c>
       <c r="R17" s="5" t="n"/>
       <c r="S17" s="5">
-        <f>IF(AND(ISNUMBER(R17),ISNUMBER(R18)),(R17/R18-1)*100,"")</f>
+        <f>IF(COUNT(R17:R18)=2,(R17/R18-1)*100,"")</f>
         <v/>
       </c>
       <c r="T17" s="5" t="n"/>
       <c r="U17" s="5">
-        <f>IF(AND(ISNUMBER(T17),ISNUMBER(T18)),(T17/T18-1)*100,"")</f>
+        <f>IF(COUNT(T17:T18)=2,(T17/T18-1)*100,"")</f>
         <v/>
       </c>
       <c r="V17" s="5" t="n"/>
@@ -2169,31 +2246,31 @@
         <v/>
       </c>
       <c r="X17" s="5">
+        <f>IF(AND(K17&lt;0,M17&gt;0),C16,"")</f>
+        <v/>
+      </c>
+      <c r="Y17" s="5">
         <f>IF(AND(G17&gt;0,I17&lt;0,K17&gt;0),C16,"")</f>
         <v/>
       </c>
-      <c r="Y17" s="5">
-        <f>IF(AND(K17&lt;0,M17&gt;0),C16,"")</f>
-        <v/>
-      </c>
       <c r="Z17" s="5">
-        <f>IF(AND(ISNUMBER(W17),0.549579&gt;=MAX(IF(ISNUMBER(X17),0.299732,-1),IF(ISNUMBER(Y17),0.323835,-1))),W17,IF(AND(ISNUMBER(X17),0.299732&gt;MAX(IF(ISNUMBER(W17),0.549579,-1),IF(ISNUMBER(Y17),0.323835,-1))),X17,IF(AND(ISNUMBER(Y17),0.323835&gt;MAX(IF(ISNUMBER(W17),0.549579,-1),IF(ISNUMBER(X17),0.299732,-1))),Y17,"")))</f>
+        <f>IF(W17&lt;&gt;"",W17,IF(X17&lt;&gt;"",X17,Y17))</f>
         <v/>
       </c>
       <c r="AA17" s="5">
+        <f>IF(AND(S17&gt;0,U17&lt;0),E16,"")</f>
+        <v/>
+      </c>
+      <c r="AB17" s="5">
         <f>IF(AND(O17&lt;=-1,E17&lt;0),E16,"")</f>
         <v/>
       </c>
-      <c r="AB17" s="5">
+      <c r="AC17" s="5">
         <f>IF(AND(Q17&gt;0,S17&gt;0),E16,"")</f>
         <v/>
       </c>
-      <c r="AC17" s="5">
-        <f>IF(AND(S17&gt;0,U17&lt;0),E16,"")</f>
-        <v/>
-      </c>
       <c r="AD17" s="5">
-        <f>IF(AND(ISNUMBER(AA17),0.408167&gt;=MAX(IF(ISNUMBER(AB17),0.31868,-1),IF(ISNUMBER(AC17),0.510996,-1))),AA17,IF(AND(ISNUMBER(AB17),0.31868&gt;MAX(IF(ISNUMBER(AA17),0.408167,-1),IF(ISNUMBER(AC17),0.510996,-1))),AB17,IF(AND(ISNUMBER(AC17),0.510996&gt;MAX(IF(ISNUMBER(AA17),0.408167,-1),IF(ISNUMBER(AB17),0.31868,-1))),AC17,"")))</f>
+        <f>IF(AA17&lt;&gt;"",AA17,IF(AB17&lt;&gt;"",AB17,AC17))</f>
         <v/>
       </c>
     </row>
@@ -2207,62 +2284,62 @@
         <v>137.65</v>
       </c>
       <c r="C18" s="5">
-        <f>IF(AND(ISNUMBER(B18),ISNUMBER(B19)),(B18/B19-1)*100,"")</f>
+        <f>IF(COUNT(B18:B19)=2,(B18/B19-1)*100,"")</f>
         <v/>
       </c>
       <c r="D18" s="5" t="n">
         <v>61.07</v>
       </c>
       <c r="E18" s="5">
-        <f>IF(AND(ISNUMBER(D18),ISNUMBER(D19)),(D18/D19-1)*100,"")</f>
+        <f>IF(COUNT(D18:D19)=2,(D18/D19-1)*100,"")</f>
         <v/>
       </c>
       <c r="F18" s="5" t="n">
         <v>78.85720000000001</v>
       </c>
       <c r="G18" s="5">
-        <f>IF(AND(ISNUMBER(F18),ISNUMBER(F19)),(F18/F19-1)*100,"")</f>
+        <f>IF(COUNT(F18:F19)=2,(F18/F19-1)*100,"")</f>
         <v/>
       </c>
       <c r="H18" s="5" t="n">
         <v>56.68</v>
       </c>
       <c r="I18" s="5">
-        <f>IF(AND(ISNUMBER(H18),ISNUMBER(H19)),(H18/H19-1)*100,"")</f>
+        <f>IF(COUNT(H18:H19)=2,(H18/H19-1)*100,"")</f>
         <v/>
       </c>
       <c r="J18" s="5" t="n">
         <v>73.56999999999999</v>
       </c>
       <c r="K18" s="5">
-        <f>IF(AND(ISNUMBER(J18),ISNUMBER(J19)),(J18/J19-1)*100,"")</f>
+        <f>IF(COUNT(J18:J19)=2,(J18/J19-1)*100,"")</f>
         <v/>
       </c>
       <c r="L18" s="5" t="n">
         <v/>
       </c>
       <c r="M18" s="5">
-        <f>IF(AND(ISNUMBER(L18),ISNUMBER(L19)),(L18/L19-1)*100,"")</f>
+        <f>IF(COUNT(L18:L19)=2,(L18/L19-1)*100,"")</f>
         <v/>
       </c>
       <c r="N18" s="5" t="n"/>
       <c r="O18" s="5">
-        <f>IF(AND(ISNUMBER(N18),ISNUMBER(N19)),(N18/N19-1)*100,"")</f>
+        <f>IF(COUNT(N18:N19)=2,(N18/N19-1)*100,"")</f>
         <v/>
       </c>
       <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5">
-        <f>IF(AND(ISNUMBER(P18),ISNUMBER(P19)),(P18/P19-1)*100,"")</f>
+        <f>IF(COUNT(P18:P19)=2,(P18/P19-1)*100,"")</f>
         <v/>
       </c>
       <c r="R18" s="5" t="n"/>
       <c r="S18" s="5">
-        <f>IF(AND(ISNUMBER(R18),ISNUMBER(R19)),(R18/R19-1)*100,"")</f>
+        <f>IF(COUNT(R18:R19)=2,(R18/R19-1)*100,"")</f>
         <v/>
       </c>
       <c r="T18" s="5" t="n"/>
       <c r="U18" s="5">
-        <f>IF(AND(ISNUMBER(T18),ISNUMBER(T19)),(T18/T19-1)*100,"")</f>
+        <f>IF(COUNT(T18:T19)=2,(T18/T19-1)*100,"")</f>
         <v/>
       </c>
       <c r="V18" s="5" t="n"/>
@@ -2271,31 +2348,31 @@
         <v/>
       </c>
       <c r="X18" s="5">
+        <f>IF(AND(K18&lt;0,M18&gt;0),C17,"")</f>
+        <v/>
+      </c>
+      <c r="Y18" s="5">
         <f>IF(AND(G18&gt;0,I18&lt;0,K18&gt;0),C17,"")</f>
         <v/>
       </c>
-      <c r="Y18" s="5">
-        <f>IF(AND(K18&lt;0,M18&gt;0),C17,"")</f>
-        <v/>
-      </c>
       <c r="Z18" s="5">
-        <f>IF(AND(ISNUMBER(W18),0.549579&gt;=MAX(IF(ISNUMBER(X18),0.299732,-1),IF(ISNUMBER(Y18),0.323835,-1))),W18,IF(AND(ISNUMBER(X18),0.299732&gt;MAX(IF(ISNUMBER(W18),0.549579,-1),IF(ISNUMBER(Y18),0.323835,-1))),X18,IF(AND(ISNUMBER(Y18),0.323835&gt;MAX(IF(ISNUMBER(W18),0.549579,-1),IF(ISNUMBER(X18),0.299732,-1))),Y18,"")))</f>
+        <f>IF(W18&lt;&gt;"",W18,IF(X18&lt;&gt;"",X18,Y18))</f>
         <v/>
       </c>
       <c r="AA18" s="5">
+        <f>IF(AND(S18&gt;0,U18&lt;0),E17,"")</f>
+        <v/>
+      </c>
+      <c r="AB18" s="5">
         <f>IF(AND(O18&lt;=-1,E18&lt;0),E17,"")</f>
         <v/>
       </c>
-      <c r="AB18" s="5">
+      <c r="AC18" s="5">
         <f>IF(AND(Q18&gt;0,S18&gt;0),E17,"")</f>
         <v/>
       </c>
-      <c r="AC18" s="5">
-        <f>IF(AND(S18&gt;0,U18&lt;0),E17,"")</f>
-        <v/>
-      </c>
       <c r="AD18" s="5">
-        <f>IF(AND(ISNUMBER(AA18),0.408167&gt;=MAX(IF(ISNUMBER(AB18),0.31868,-1),IF(ISNUMBER(AC18),0.510996,-1))),AA18,IF(AND(ISNUMBER(AB18),0.31868&gt;MAX(IF(ISNUMBER(AA18),0.408167,-1),IF(ISNUMBER(AC18),0.510996,-1))),AB18,IF(AND(ISNUMBER(AC18),0.510996&gt;MAX(IF(ISNUMBER(AA18),0.408167,-1),IF(ISNUMBER(AB18),0.31868,-1))),AC18,"")))</f>
+        <f>IF(AA18&lt;&gt;"",AA18,IF(AB18&lt;&gt;"",AB18,AC18))</f>
         <v/>
       </c>
     </row>
@@ -2309,62 +2386,62 @@
         <v>143.57</v>
       </c>
       <c r="C19" s="5">
-        <f>IF(AND(ISNUMBER(B19),ISNUMBER(B20)),(B19/B20-1)*100,"")</f>
+        <f>IF(COUNT(B19:B20)=2,(B19/B20-1)*100,"")</f>
         <v/>
       </c>
       <c r="D19" s="5" t="n">
         <v>62.36</v>
       </c>
       <c r="E19" s="5">
-        <f>IF(AND(ISNUMBER(D19),ISNUMBER(D20)),(D19/D20-1)*100,"")</f>
+        <f>IF(COUNT(D19:D20)=2,(D19/D20-1)*100,"")</f>
         <v/>
       </c>
       <c r="F19" s="5" t="n">
         <v>79.0363</v>
       </c>
       <c r="G19" s="5">
-        <f>IF(AND(ISNUMBER(F19),ISNUMBER(F20)),(F19/F20-1)*100,"")</f>
+        <f>IF(COUNT(F19:F20)=2,(F19/F20-1)*100,"")</f>
         <v/>
       </c>
       <c r="H19" s="5" t="n">
         <v>57.6</v>
       </c>
       <c r="I19" s="5">
-        <f>IF(AND(ISNUMBER(H19),ISNUMBER(H20)),(H19/H20-1)*100,"")</f>
+        <f>IF(COUNT(H19:H20)=2,(H19/H20-1)*100,"")</f>
         <v/>
       </c>
       <c r="J19" s="5" t="n">
         <v>74.20999999999999</v>
       </c>
       <c r="K19" s="5">
-        <f>IF(AND(ISNUMBER(J19),ISNUMBER(J20)),(J19/J20-1)*100,"")</f>
+        <f>IF(COUNT(J19:J20)=2,(J19/J20-1)*100,"")</f>
         <v/>
       </c>
       <c r="L19" s="5" t="n">
         <v/>
       </c>
       <c r="M19" s="5">
-        <f>IF(AND(ISNUMBER(L19),ISNUMBER(L20)),(L19/L20-1)*100,"")</f>
+        <f>IF(COUNT(L19:L20)=2,(L19/L20-1)*100,"")</f>
         <v/>
       </c>
       <c r="N19" s="5" t="n"/>
       <c r="O19" s="5">
-        <f>IF(AND(ISNUMBER(N19),ISNUMBER(N20)),(N19/N20-1)*100,"")</f>
+        <f>IF(COUNT(N19:N20)=2,(N19/N20-1)*100,"")</f>
         <v/>
       </c>
       <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5">
-        <f>IF(AND(ISNUMBER(P19),ISNUMBER(P20)),(P19/P20-1)*100,"")</f>
+        <f>IF(COUNT(P19:P20)=2,(P19/P20-1)*100,"")</f>
         <v/>
       </c>
       <c r="R19" s="5" t="n"/>
       <c r="S19" s="5">
-        <f>IF(AND(ISNUMBER(R19),ISNUMBER(R20)),(R19/R20-1)*100,"")</f>
+        <f>IF(COUNT(R19:R20)=2,(R19/R20-1)*100,"")</f>
         <v/>
       </c>
       <c r="T19" s="5" t="n"/>
       <c r="U19" s="5">
-        <f>IF(AND(ISNUMBER(T19),ISNUMBER(T20)),(T19/T20-1)*100,"")</f>
+        <f>IF(COUNT(T19:T20)=2,(T19/T20-1)*100,"")</f>
         <v/>
       </c>
       <c r="V19" s="5" t="n"/>
@@ -2373,31 +2450,31 @@
         <v/>
       </c>
       <c r="X19" s="5">
+        <f>IF(AND(K19&lt;0,M19&gt;0),C18,"")</f>
+        <v/>
+      </c>
+      <c r="Y19" s="5">
         <f>IF(AND(G19&gt;0,I19&lt;0,K19&gt;0),C18,"")</f>
         <v/>
       </c>
-      <c r="Y19" s="5">
-        <f>IF(AND(K19&lt;0,M19&gt;0),C18,"")</f>
-        <v/>
-      </c>
       <c r="Z19" s="5">
-        <f>IF(AND(ISNUMBER(W19),0.549579&gt;=MAX(IF(ISNUMBER(X19),0.299732,-1),IF(ISNUMBER(Y19),0.323835,-1))),W19,IF(AND(ISNUMBER(X19),0.299732&gt;MAX(IF(ISNUMBER(W19),0.549579,-1),IF(ISNUMBER(Y19),0.323835,-1))),X19,IF(AND(ISNUMBER(Y19),0.323835&gt;MAX(IF(ISNUMBER(W19),0.549579,-1),IF(ISNUMBER(X19),0.299732,-1))),Y19,"")))</f>
+        <f>IF(W19&lt;&gt;"",W19,IF(X19&lt;&gt;"",X19,Y19))</f>
         <v/>
       </c>
       <c r="AA19" s="5">
+        <f>IF(AND(S19&gt;0,U19&lt;0),E18,"")</f>
+        <v/>
+      </c>
+      <c r="AB19" s="5">
         <f>IF(AND(O19&lt;=-1,E19&lt;0),E18,"")</f>
         <v/>
       </c>
-      <c r="AB19" s="5">
+      <c r="AC19" s="5">
         <f>IF(AND(Q19&gt;0,S19&gt;0),E18,"")</f>
         <v/>
       </c>
-      <c r="AC19" s="5">
-        <f>IF(AND(S19&gt;0,U19&lt;0),E18,"")</f>
-        <v/>
-      </c>
       <c r="AD19" s="5">
-        <f>IF(AND(ISNUMBER(AA19),0.408167&gt;=MAX(IF(ISNUMBER(AB19),0.31868,-1),IF(ISNUMBER(AC19),0.510996,-1))),AA19,IF(AND(ISNUMBER(AB19),0.31868&gt;MAX(IF(ISNUMBER(AA19),0.408167,-1),IF(ISNUMBER(AC19),0.510996,-1))),AB19,IF(AND(ISNUMBER(AC19),0.510996&gt;MAX(IF(ISNUMBER(AA19),0.408167,-1),IF(ISNUMBER(AB19),0.31868,-1))),AC19,"")))</f>
+        <f>IF(AA19&lt;&gt;"",AA19,IF(AB19&lt;&gt;"",AB19,AC19))</f>
         <v/>
       </c>
     </row>
@@ -2411,62 +2488,62 @@
         <v>146.46</v>
       </c>
       <c r="C20" s="5">
-        <f>IF(AND(ISNUMBER(B20),ISNUMBER(B21)),(B20/B21-1)*100,"")</f>
+        <f>IF(COUNT(B20:B21)=2,(B20/B21-1)*100,"")</f>
         <v/>
       </c>
       <c r="D20" s="5" t="n">
         <v>63.62</v>
       </c>
       <c r="E20" s="5">
-        <f>IF(AND(ISNUMBER(D20),ISNUMBER(D21)),(D20/D21-1)*100,"")</f>
+        <f>IF(COUNT(D20:D21)=2,(D20/D21-1)*100,"")</f>
         <v/>
       </c>
       <c r="F20" s="5" t="n">
         <v>78.887</v>
       </c>
       <c r="G20" s="5">
-        <f>IF(AND(ISNUMBER(F20),ISNUMBER(F21)),(F20/F21-1)*100,"")</f>
+        <f>IF(COUNT(F20:F21)=2,(F20/F21-1)*100,"")</f>
         <v/>
       </c>
       <c r="H20" s="5" t="n">
         <v>56.88</v>
       </c>
       <c r="I20" s="5">
-        <f>IF(AND(ISNUMBER(H20),ISNUMBER(H21)),(H20/H21-1)*100,"")</f>
+        <f>IF(COUNT(H20:H21)=2,(H20/H21-1)*100,"")</f>
         <v/>
       </c>
       <c r="J20" s="5" t="n">
         <v>75.73</v>
       </c>
       <c r="K20" s="5">
-        <f>IF(AND(ISNUMBER(J20),ISNUMBER(J21)),(J20/J21-1)*100,"")</f>
+        <f>IF(COUNT(J20:J21)=2,(J20/J21-1)*100,"")</f>
         <v/>
       </c>
       <c r="L20" s="5" t="n">
         <v/>
       </c>
       <c r="M20" s="5">
-        <f>IF(AND(ISNUMBER(L20),ISNUMBER(L21)),(L20/L21-1)*100,"")</f>
+        <f>IF(COUNT(L20:L21)=2,(L20/L21-1)*100,"")</f>
         <v/>
       </c>
       <c r="N20" s="5" t="n"/>
       <c r="O20" s="5">
-        <f>IF(AND(ISNUMBER(N20),ISNUMBER(N21)),(N20/N21-1)*100,"")</f>
+        <f>IF(COUNT(N20:N21)=2,(N20/N21-1)*100,"")</f>
         <v/>
       </c>
       <c r="P20" s="5" t="n"/>
       <c r="Q20" s="5">
-        <f>IF(AND(ISNUMBER(P20),ISNUMBER(P21)),(P20/P21-1)*100,"")</f>
+        <f>IF(COUNT(P20:P21)=2,(P20/P21-1)*100,"")</f>
         <v/>
       </c>
       <c r="R20" s="5" t="n"/>
       <c r="S20" s="5">
-        <f>IF(AND(ISNUMBER(R20),ISNUMBER(R21)),(R20/R21-1)*100,"")</f>
+        <f>IF(COUNT(R20:R21)=2,(R20/R21-1)*100,"")</f>
         <v/>
       </c>
       <c r="T20" s="5" t="n"/>
       <c r="U20" s="5">
-        <f>IF(AND(ISNUMBER(T20),ISNUMBER(T21)),(T20/T21-1)*100,"")</f>
+        <f>IF(COUNT(T20:T21)=2,(T20/T21-1)*100,"")</f>
         <v/>
       </c>
       <c r="V20" s="5" t="n"/>
@@ -2475,31 +2552,31 @@
         <v/>
       </c>
       <c r="X20" s="5">
+        <f>IF(AND(K20&lt;0,M20&gt;0),C19,"")</f>
+        <v/>
+      </c>
+      <c r="Y20" s="5">
         <f>IF(AND(G20&gt;0,I20&lt;0,K20&gt;0),C19,"")</f>
         <v/>
       </c>
-      <c r="Y20" s="5">
-        <f>IF(AND(K20&lt;0,M20&gt;0),C19,"")</f>
-        <v/>
-      </c>
       <c r="Z20" s="5">
-        <f>IF(AND(ISNUMBER(W20),0.549579&gt;=MAX(IF(ISNUMBER(X20),0.299732,-1),IF(ISNUMBER(Y20),0.323835,-1))),W20,IF(AND(ISNUMBER(X20),0.299732&gt;MAX(IF(ISNUMBER(W20),0.549579,-1),IF(ISNUMBER(Y20),0.323835,-1))),X20,IF(AND(ISNUMBER(Y20),0.323835&gt;MAX(IF(ISNUMBER(W20),0.549579,-1),IF(ISNUMBER(X20),0.299732,-1))),Y20,"")))</f>
+        <f>IF(W20&lt;&gt;"",W20,IF(X20&lt;&gt;"",X20,Y20))</f>
         <v/>
       </c>
       <c r="AA20" s="5">
+        <f>IF(AND(S20&gt;0,U20&lt;0),E19,"")</f>
+        <v/>
+      </c>
+      <c r="AB20" s="5">
         <f>IF(AND(O20&lt;=-1,E20&lt;0),E19,"")</f>
         <v/>
       </c>
-      <c r="AB20" s="5">
+      <c r="AC20" s="5">
         <f>IF(AND(Q20&gt;0,S20&gt;0),E19,"")</f>
         <v/>
       </c>
-      <c r="AC20" s="5">
-        <f>IF(AND(S20&gt;0,U20&lt;0),E19,"")</f>
-        <v/>
-      </c>
       <c r="AD20" s="5">
-        <f>IF(AND(ISNUMBER(AA20),0.408167&gt;=MAX(IF(ISNUMBER(AB20),0.31868,-1),IF(ISNUMBER(AC20),0.510996,-1))),AA20,IF(AND(ISNUMBER(AB20),0.31868&gt;MAX(IF(ISNUMBER(AA20),0.408167,-1),IF(ISNUMBER(AC20),0.510996,-1))),AB20,IF(AND(ISNUMBER(AC20),0.510996&gt;MAX(IF(ISNUMBER(AA20),0.408167,-1),IF(ISNUMBER(AB20),0.31868,-1))),AC20,"")))</f>
+        <f>IF(AA20&lt;&gt;"",AA20,IF(AB20&lt;&gt;"",AB20,AC20))</f>
         <v/>
       </c>
     </row>
@@ -2513,62 +2590,62 @@
         <v>147.47</v>
       </c>
       <c r="C21" s="5">
-        <f>IF(AND(ISNUMBER(B21),ISNUMBER(B22)),(B21/B22-1)*100,"")</f>
+        <f>IF(COUNT(B21:B22)=2,(B21/B22-1)*100,"")</f>
         <v/>
       </c>
       <c r="D21" s="5" t="n">
         <v>63.33</v>
       </c>
       <c r="E21" s="5">
-        <f>IF(AND(ISNUMBER(D21),ISNUMBER(D22)),(D21/D22-1)*100,"")</f>
+        <f>IF(COUNT(D21:D22)=2,(D21/D22-1)*100,"")</f>
         <v/>
       </c>
       <c r="F21" s="5" t="n">
         <v>78.8472</v>
       </c>
       <c r="G21" s="5">
-        <f>IF(AND(ISNUMBER(F21),ISNUMBER(F22)),(F21/F22-1)*100,"")</f>
+        <f>IF(COUNT(F21:F22)=2,(F21/F22-1)*100,"")</f>
         <v/>
       </c>
       <c r="H21" s="5" t="n">
         <v>56.31</v>
       </c>
       <c r="I21" s="5">
-        <f>IF(AND(ISNUMBER(H21),ISNUMBER(H22)),(H21/H22-1)*100,"")</f>
+        <f>IF(COUNT(H21:H22)=2,(H21/H22-1)*100,"")</f>
         <v/>
       </c>
       <c r="J21" s="5" t="n">
         <v>75.23</v>
       </c>
       <c r="K21" s="5">
-        <f>IF(AND(ISNUMBER(J21),ISNUMBER(J22)),(J21/J22-1)*100,"")</f>
+        <f>IF(COUNT(J21:J22)=2,(J21/J22-1)*100,"")</f>
         <v/>
       </c>
       <c r="L21" s="5" t="n">
         <v>-0.6417</v>
       </c>
       <c r="M21" s="5">
-        <f>IF(AND(ISNUMBER(L21),ISNUMBER(L22)),(L21/L22-1)*100,"")</f>
+        <f>IF(COUNT(L21:L22)=2,(L21/L22-1)*100,"")</f>
         <v/>
       </c>
       <c r="N21" s="5" t="n"/>
       <c r="O21" s="5">
-        <f>IF(AND(ISNUMBER(N21),ISNUMBER(N22)),(N21/N22-1)*100,"")</f>
+        <f>IF(COUNT(N21:N22)=2,(N21/N22-1)*100,"")</f>
         <v/>
       </c>
       <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5">
-        <f>IF(AND(ISNUMBER(P21),ISNUMBER(P22)),(P21/P22-1)*100,"")</f>
+        <f>IF(COUNT(P21:P22)=2,(P21/P22-1)*100,"")</f>
         <v/>
       </c>
       <c r="R21" s="5" t="n"/>
       <c r="S21" s="5">
-        <f>IF(AND(ISNUMBER(R21),ISNUMBER(R22)),(R21/R22-1)*100,"")</f>
+        <f>IF(COUNT(R21:R22)=2,(R21/R22-1)*100,"")</f>
         <v/>
       </c>
       <c r="T21" s="5" t="n"/>
       <c r="U21" s="5">
-        <f>IF(AND(ISNUMBER(T21),ISNUMBER(T22)),(T21/T22-1)*100,"")</f>
+        <f>IF(COUNT(T21:T22)=2,(T21/T22-1)*100,"")</f>
         <v/>
       </c>
       <c r="V21" s="5" t="n"/>
@@ -2577,31 +2654,31 @@
         <v/>
       </c>
       <c r="X21" s="5">
+        <f>IF(AND(K21&lt;0,M21&gt;0),C20,"")</f>
+        <v/>
+      </c>
+      <c r="Y21" s="5">
         <f>IF(AND(G21&gt;0,I21&lt;0,K21&gt;0),C20,"")</f>
         <v/>
       </c>
-      <c r="Y21" s="5">
-        <f>IF(AND(K21&lt;0,M21&gt;0),C20,"")</f>
-        <v/>
-      </c>
       <c r="Z21" s="5">
-        <f>IF(AND(ISNUMBER(W21),0.549579&gt;=MAX(IF(ISNUMBER(X21),0.299732,-1),IF(ISNUMBER(Y21),0.323835,-1))),W21,IF(AND(ISNUMBER(X21),0.299732&gt;MAX(IF(ISNUMBER(W21),0.549579,-1),IF(ISNUMBER(Y21),0.323835,-1))),X21,IF(AND(ISNUMBER(Y21),0.323835&gt;MAX(IF(ISNUMBER(W21),0.549579,-1),IF(ISNUMBER(X21),0.299732,-1))),Y21,"")))</f>
+        <f>IF(W21&lt;&gt;"",W21,IF(X21&lt;&gt;"",X21,Y21))</f>
         <v/>
       </c>
       <c r="AA21" s="5">
+        <f>IF(AND(S21&gt;0,U21&lt;0),E20,"")</f>
+        <v/>
+      </c>
+      <c r="AB21" s="5">
         <f>IF(AND(O21&lt;=-1,E21&lt;0),E20,"")</f>
         <v/>
       </c>
-      <c r="AB21" s="5">
+      <c r="AC21" s="5">
         <f>IF(AND(Q21&gt;0,S21&gt;0),E20,"")</f>
         <v/>
       </c>
-      <c r="AC21" s="5">
-        <f>IF(AND(S21&gt;0,U21&lt;0),E20,"")</f>
-        <v/>
-      </c>
       <c r="AD21" s="5">
-        <f>IF(AND(ISNUMBER(AA21),0.408167&gt;=MAX(IF(ISNUMBER(AB21),0.31868,-1),IF(ISNUMBER(AC21),0.510996,-1))),AA21,IF(AND(ISNUMBER(AB21),0.31868&gt;MAX(IF(ISNUMBER(AA21),0.408167,-1),IF(ISNUMBER(AC21),0.510996,-1))),AB21,IF(AND(ISNUMBER(AC21),0.510996&gt;MAX(IF(ISNUMBER(AA21),0.408167,-1),IF(ISNUMBER(AB21),0.31868,-1))),AC21,"")))</f>
+        <f>IF(AA21&lt;&gt;"",AA21,IF(AB21&lt;&gt;"",AB21,AC21))</f>
         <v/>
       </c>
     </row>
@@ -2615,62 +2692,62 @@
         <v>150.94</v>
       </c>
       <c r="C22" s="5">
-        <f>IF(AND(ISNUMBER(B22),ISNUMBER(B23)),(B22/B23-1)*100,"")</f>
+        <f>IF(COUNT(B22:B23)=2,(B22/B23-1)*100,"")</f>
         <v/>
       </c>
       <c r="D22" s="5" t="n">
         <v>64.59999999999999</v>
       </c>
       <c r="E22" s="5">
-        <f>IF(AND(ISNUMBER(D22),ISNUMBER(D23)),(D22/D23-1)*100,"")</f>
+        <f>IF(COUNT(D22:D23)=2,(D22/D23-1)*100,"")</f>
         <v/>
       </c>
       <c r="F22" s="5" t="n">
         <v>78.8472</v>
       </c>
       <c r="G22" s="5">
-        <f>IF(AND(ISNUMBER(F22),ISNUMBER(F23)),(F22/F23-1)*100,"")</f>
+        <f>IF(COUNT(F22:F23)=2,(F22/F23-1)*100,"")</f>
         <v/>
       </c>
       <c r="H22" s="5" t="n">
         <v>55.83</v>
       </c>
       <c r="I22" s="5">
-        <f>IF(AND(ISNUMBER(H22),ISNUMBER(H23)),(H22/H23-1)*100,"")</f>
+        <f>IF(COUNT(H22:H23)=2,(H22/H23-1)*100,"")</f>
         <v/>
       </c>
       <c r="J22" s="5" t="n">
         <v>75.02</v>
       </c>
       <c r="K22" s="5">
-        <f>IF(AND(ISNUMBER(J22),ISNUMBER(J23)),(J22/J23-1)*100,"")</f>
+        <f>IF(COUNT(J22:J23)=2,(J22/J23-1)*100,"")</f>
         <v/>
       </c>
       <c r="L22" s="5" t="n">
         <v>12.3798</v>
       </c>
       <c r="M22" s="5">
-        <f>IF(AND(ISNUMBER(L22),ISNUMBER(L23)),(L22/L23-1)*100,"")</f>
+        <f>IF(COUNT(L22:L23)=2,(L22/L23-1)*100,"")</f>
         <v/>
       </c>
       <c r="N22" s="5" t="n"/>
       <c r="O22" s="5">
-        <f>IF(AND(ISNUMBER(N22),ISNUMBER(N23)),(N22/N23-1)*100,"")</f>
+        <f>IF(COUNT(N22:N23)=2,(N22/N23-1)*100,"")</f>
         <v/>
       </c>
       <c r="P22" s="5" t="n"/>
       <c r="Q22" s="5">
-        <f>IF(AND(ISNUMBER(P22),ISNUMBER(P23)),(P22/P23-1)*100,"")</f>
+        <f>IF(COUNT(P22:P23)=2,(P22/P23-1)*100,"")</f>
         <v/>
       </c>
       <c r="R22" s="5" t="n"/>
       <c r="S22" s="5">
-        <f>IF(AND(ISNUMBER(R22),ISNUMBER(R23)),(R22/R23-1)*100,"")</f>
+        <f>IF(COUNT(R22:R23)=2,(R22/R23-1)*100,"")</f>
         <v/>
       </c>
       <c r="T22" s="5" t="n"/>
       <c r="U22" s="5">
-        <f>IF(AND(ISNUMBER(T22),ISNUMBER(T23)),(T22/T23-1)*100,"")</f>
+        <f>IF(COUNT(T22:T23)=2,(T22/T23-1)*100,"")</f>
         <v/>
       </c>
       <c r="V22" s="5" t="n"/>
@@ -2679,31 +2756,31 @@
         <v/>
       </c>
       <c r="X22" s="5">
+        <f>IF(AND(K22&lt;0,M22&gt;0),C21,"")</f>
+        <v/>
+      </c>
+      <c r="Y22" s="5">
         <f>IF(AND(G22&gt;0,I22&lt;0,K22&gt;0),C21,"")</f>
         <v/>
       </c>
-      <c r="Y22" s="5">
-        <f>IF(AND(K22&lt;0,M22&gt;0),C21,"")</f>
-        <v/>
-      </c>
       <c r="Z22" s="5">
-        <f>IF(AND(ISNUMBER(W22),0.549579&gt;=MAX(IF(ISNUMBER(X22),0.299732,-1),IF(ISNUMBER(Y22),0.323835,-1))),W22,IF(AND(ISNUMBER(X22),0.299732&gt;MAX(IF(ISNUMBER(W22),0.549579,-1),IF(ISNUMBER(Y22),0.323835,-1))),X22,IF(AND(ISNUMBER(Y22),0.323835&gt;MAX(IF(ISNUMBER(W22),0.549579,-1),IF(ISNUMBER(X22),0.299732,-1))),Y22,"")))</f>
+        <f>IF(W22&lt;&gt;"",W22,IF(X22&lt;&gt;"",X22,Y22))</f>
         <v/>
       </c>
       <c r="AA22" s="5">
+        <f>IF(AND(S22&gt;0,U22&lt;0),E21,"")</f>
+        <v/>
+      </c>
+      <c r="AB22" s="5">
         <f>IF(AND(O22&lt;=-1,E22&lt;0),E21,"")</f>
         <v/>
       </c>
-      <c r="AB22" s="5">
+      <c r="AC22" s="5">
         <f>IF(AND(Q22&gt;0,S22&gt;0),E21,"")</f>
         <v/>
       </c>
-      <c r="AC22" s="5">
-        <f>IF(AND(S22&gt;0,U22&lt;0),E21,"")</f>
-        <v/>
-      </c>
       <c r="AD22" s="5">
-        <f>IF(AND(ISNUMBER(AA22),0.408167&gt;=MAX(IF(ISNUMBER(AB22),0.31868,-1),IF(ISNUMBER(AC22),0.510996,-1))),AA22,IF(AND(ISNUMBER(AB22),0.31868&gt;MAX(IF(ISNUMBER(AA22),0.408167,-1),IF(ISNUMBER(AC22),0.510996,-1))),AB22,IF(AND(ISNUMBER(AC22),0.510996&gt;MAX(IF(ISNUMBER(AA22),0.408167,-1),IF(ISNUMBER(AB22),0.31868,-1))),AC22,"")))</f>
+        <f>IF(AA22&lt;&gt;"",AA22,IF(AB22&lt;&gt;"",AB22,AC22))</f>
         <v/>
       </c>
     </row>
@@ -2717,62 +2794,62 @@
         <v>156.87</v>
       </c>
       <c r="C23" s="5">
-        <f>IF(AND(ISNUMBER(B23),ISNUMBER(B24)),(B23/B24-1)*100,"")</f>
+        <f>IF(COUNT(B23:B24)=2,(B23/B24-1)*100,"")</f>
         <v/>
       </c>
       <c r="D23" s="5" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="E23" s="5">
-        <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24)),(D23/D24-1)*100,"")</f>
+        <f>IF(COUNT(D23:D24)=2,(D23/D24-1)*100,"")</f>
         <v/>
       </c>
       <c r="F23" s="5" t="n">
         <v>79.1358</v>
       </c>
       <c r="G23" s="5">
-        <f>IF(AND(ISNUMBER(F23),ISNUMBER(F24)),(F23/F24-1)*100,"")</f>
+        <f>IF(COUNT(F23:F24)=2,(F23/F24-1)*100,"")</f>
         <v/>
       </c>
       <c r="H23" s="5" t="n">
         <v>56.05</v>
       </c>
       <c r="I23" s="5">
-        <f>IF(AND(ISNUMBER(H23),ISNUMBER(H24)),(H23/H24-1)*100,"")</f>
+        <f>IF(COUNT(H23:H24)=2,(H23/H24-1)*100,"")</f>
         <v/>
       </c>
       <c r="J23" s="5" t="n">
         <v>76.68000000000001</v>
       </c>
       <c r="K23" s="5">
-        <f>IF(AND(ISNUMBER(J23),ISNUMBER(J24)),(J23/J24-1)*100,"")</f>
+        <f>IF(COUNT(J23:J24)=2,(J23/J24-1)*100,"")</f>
         <v/>
       </c>
       <c r="L23" s="5" t="n">
         <v>-2.4047</v>
       </c>
       <c r="M23" s="5">
-        <f>IF(AND(ISNUMBER(L23),ISNUMBER(L24)),(L23/L24-1)*100,"")</f>
+        <f>IF(COUNT(L23:L24)=2,(L23/L24-1)*100,"")</f>
         <v/>
       </c>
       <c r="N23" s="5" t="n"/>
       <c r="O23" s="5">
-        <f>IF(AND(ISNUMBER(N23),ISNUMBER(N24)),(N23/N24-1)*100,"")</f>
+        <f>IF(COUNT(N23:N24)=2,(N23/N24-1)*100,"")</f>
         <v/>
       </c>
       <c r="P23" s="5" t="n"/>
       <c r="Q23" s="5">
-        <f>IF(AND(ISNUMBER(P23),ISNUMBER(P24)),(P23/P24-1)*100,"")</f>
+        <f>IF(COUNT(P23:P24)=2,(P23/P24-1)*100,"")</f>
         <v/>
       </c>
       <c r="R23" s="5" t="n"/>
       <c r="S23" s="5">
-        <f>IF(AND(ISNUMBER(R23),ISNUMBER(R24)),(R23/R24-1)*100,"")</f>
+        <f>IF(COUNT(R23:R24)=2,(R23/R24-1)*100,"")</f>
         <v/>
       </c>
       <c r="T23" s="5" t="n"/>
       <c r="U23" s="5">
-        <f>IF(AND(ISNUMBER(T23),ISNUMBER(T24)),(T23/T24-1)*100,"")</f>
+        <f>IF(COUNT(T23:T24)=2,(T23/T24-1)*100,"")</f>
         <v/>
       </c>
       <c r="V23" s="5" t="n"/>
@@ -2781,31 +2858,31 @@
         <v/>
       </c>
       <c r="X23" s="5">
+        <f>IF(AND(K23&lt;0,M23&gt;0),C22,"")</f>
+        <v/>
+      </c>
+      <c r="Y23" s="5">
         <f>IF(AND(G23&gt;0,I23&lt;0,K23&gt;0),C22,"")</f>
         <v/>
       </c>
-      <c r="Y23" s="5">
-        <f>IF(AND(K23&lt;0,M23&gt;0),C22,"")</f>
-        <v/>
-      </c>
       <c r="Z23" s="5">
-        <f>IF(AND(ISNUMBER(W23),0.549579&gt;=MAX(IF(ISNUMBER(X23),0.299732,-1),IF(ISNUMBER(Y23),0.323835,-1))),W23,IF(AND(ISNUMBER(X23),0.299732&gt;MAX(IF(ISNUMBER(W23),0.549579,-1),IF(ISNUMBER(Y23),0.323835,-1))),X23,IF(AND(ISNUMBER(Y23),0.323835&gt;MAX(IF(ISNUMBER(W23),0.549579,-1),IF(ISNUMBER(X23),0.299732,-1))),Y23,"")))</f>
+        <f>IF(W23&lt;&gt;"",W23,IF(X23&lt;&gt;"",X23,Y23))</f>
         <v/>
       </c>
       <c r="AA23" s="5">
+        <f>IF(AND(S23&gt;0,U23&lt;0),E22,"")</f>
+        <v/>
+      </c>
+      <c r="AB23" s="5">
         <f>IF(AND(O23&lt;=-1,E23&lt;0),E22,"")</f>
         <v/>
       </c>
-      <c r="AB23" s="5">
+      <c r="AC23" s="5">
         <f>IF(AND(Q23&gt;0,S23&gt;0),E22,"")</f>
         <v/>
       </c>
-      <c r="AC23" s="5">
-        <f>IF(AND(S23&gt;0,U23&lt;0),E22,"")</f>
-        <v/>
-      </c>
       <c r="AD23" s="5">
-        <f>IF(AND(ISNUMBER(AA23),0.408167&gt;=MAX(IF(ISNUMBER(AB23),0.31868,-1),IF(ISNUMBER(AC23),0.510996,-1))),AA23,IF(AND(ISNUMBER(AB23),0.31868&gt;MAX(IF(ISNUMBER(AA23),0.408167,-1),IF(ISNUMBER(AC23),0.510996,-1))),AB23,IF(AND(ISNUMBER(AC23),0.510996&gt;MAX(IF(ISNUMBER(AA23),0.408167,-1),IF(ISNUMBER(AB23),0.31868,-1))),AC23,"")))</f>
+        <f>IF(AA23&lt;&gt;"",AA23,IF(AB23&lt;&gt;"",AB23,AC23))</f>
         <v/>
       </c>
     </row>
@@ -2819,62 +2896,62 @@
         <v>158.58</v>
       </c>
       <c r="C24" s="5">
-        <f>IF(AND(ISNUMBER(B24),ISNUMBER(B25)),(B24/B25-1)*100,"")</f>
+        <f>IF(COUNT(B24:B25)=2,(B24/B25-1)*100,"")</f>
         <v/>
       </c>
       <c r="D24" s="5" t="n">
         <v>65.34</v>
       </c>
       <c r="E24" s="5">
-        <f>IF(AND(ISNUMBER(D24),ISNUMBER(D25)),(D24/D25-1)*100,"")</f>
+        <f>IF(COUNT(D24:D25)=2,(D24/D25-1)*100,"")</f>
         <v/>
       </c>
       <c r="F24" s="5" t="n">
         <v>79.26519999999999</v>
       </c>
       <c r="G24" s="5">
-        <f>IF(AND(ISNUMBER(F24),ISNUMBER(F25)),(F24/F25-1)*100,"")</f>
+        <f>IF(COUNT(F24:F25)=2,(F24/F25-1)*100,"")</f>
         <v/>
       </c>
       <c r="H24" s="5" t="n">
         <v>56.11</v>
       </c>
       <c r="I24" s="5">
-        <f>IF(AND(ISNUMBER(H24),ISNUMBER(H25)),(H24/H25-1)*100,"")</f>
+        <f>IF(COUNT(H24:H25)=2,(H24/H25-1)*100,"")</f>
         <v/>
       </c>
       <c r="J24" s="5" t="n">
         <v>74.19</v>
       </c>
       <c r="K24" s="5">
-        <f>IF(AND(ISNUMBER(J24),ISNUMBER(J25)),(J24/J25-1)*100,"")</f>
+        <f>IF(COUNT(J24:J25)=2,(J24/J25-1)*100,"")</f>
         <v/>
       </c>
       <c r="L24" s="5" t="n">
         <v>-8.5791</v>
       </c>
       <c r="M24" s="5">
-        <f>IF(AND(ISNUMBER(L24),ISNUMBER(L25)),(L24/L25-1)*100,"")</f>
+        <f>IF(COUNT(L24:L25)=2,(L24/L25-1)*100,"")</f>
         <v/>
       </c>
       <c r="N24" s="5" t="n"/>
       <c r="O24" s="5">
-        <f>IF(AND(ISNUMBER(N24),ISNUMBER(N25)),(N24/N25-1)*100,"")</f>
+        <f>IF(COUNT(N24:N25)=2,(N24/N25-1)*100,"")</f>
         <v/>
       </c>
       <c r="P24" s="5" t="n"/>
       <c r="Q24" s="5">
-        <f>IF(AND(ISNUMBER(P24),ISNUMBER(P25)),(P24/P25-1)*100,"")</f>
+        <f>IF(COUNT(P24:P25)=2,(P24/P25-1)*100,"")</f>
         <v/>
       </c>
       <c r="R24" s="5" t="n"/>
       <c r="S24" s="5">
-        <f>IF(AND(ISNUMBER(R24),ISNUMBER(R25)),(R24/R25-1)*100,"")</f>
+        <f>IF(COUNT(R24:R25)=2,(R24/R25-1)*100,"")</f>
         <v/>
       </c>
       <c r="T24" s="5" t="n"/>
       <c r="U24" s="5">
-        <f>IF(AND(ISNUMBER(T24),ISNUMBER(T25)),(T24/T25-1)*100,"")</f>
+        <f>IF(COUNT(T24:T25)=2,(T24/T25-1)*100,"")</f>
         <v/>
       </c>
       <c r="V24" s="5" t="n"/>
@@ -2883,31 +2960,31 @@
         <v/>
       </c>
       <c r="X24" s="5">
+        <f>IF(AND(K24&lt;0,M24&gt;0),C23,"")</f>
+        <v/>
+      </c>
+      <c r="Y24" s="5">
         <f>IF(AND(G24&gt;0,I24&lt;0,K24&gt;0),C23,"")</f>
         <v/>
       </c>
-      <c r="Y24" s="5">
-        <f>IF(AND(K24&lt;0,M24&gt;0),C23,"")</f>
-        <v/>
-      </c>
       <c r="Z24" s="5">
-        <f>IF(AND(ISNUMBER(W24),0.549579&gt;=MAX(IF(ISNUMBER(X24),0.299732,-1),IF(ISNUMBER(Y24),0.323835,-1))),W24,IF(AND(ISNUMBER(X24),0.299732&gt;MAX(IF(ISNUMBER(W24),0.549579,-1),IF(ISNUMBER(Y24),0.323835,-1))),X24,IF(AND(ISNUMBER(Y24),0.323835&gt;MAX(IF(ISNUMBER(W24),0.549579,-1),IF(ISNUMBER(X24),0.299732,-1))),Y24,"")))</f>
+        <f>IF(W24&lt;&gt;"",W24,IF(X24&lt;&gt;"",X24,Y24))</f>
         <v/>
       </c>
       <c r="AA24" s="5">
+        <f>IF(AND(S24&gt;0,U24&lt;0),E23,"")</f>
+        <v/>
+      </c>
+      <c r="AB24" s="5">
         <f>IF(AND(O24&lt;=-1,E24&lt;0),E23,"")</f>
         <v/>
       </c>
-      <c r="AB24" s="5">
+      <c r="AC24" s="5">
         <f>IF(AND(Q24&gt;0,S24&gt;0),E23,"")</f>
         <v/>
       </c>
-      <c r="AC24" s="5">
-        <f>IF(AND(S24&gt;0,U24&lt;0),E23,"")</f>
-        <v/>
-      </c>
       <c r="AD24" s="5">
-        <f>IF(AND(ISNUMBER(AA24),0.408167&gt;=MAX(IF(ISNUMBER(AB24),0.31868,-1),IF(ISNUMBER(AC24),0.510996,-1))),AA24,IF(AND(ISNUMBER(AB24),0.31868&gt;MAX(IF(ISNUMBER(AA24),0.408167,-1),IF(ISNUMBER(AC24),0.510996,-1))),AB24,IF(AND(ISNUMBER(AC24),0.510996&gt;MAX(IF(ISNUMBER(AA24),0.408167,-1),IF(ISNUMBER(AB24),0.31868,-1))),AC24,"")))</f>
+        <f>IF(AA24&lt;&gt;"",AA24,IF(AB24&lt;&gt;"",AB24,AC24))</f>
         <v/>
       </c>
     </row>
@@ -2921,62 +2998,62 @@
         <v>152.76</v>
       </c>
       <c r="C25" s="5">
-        <f>IF(AND(ISNUMBER(B25),ISNUMBER(B26)),(B25/B26-1)*100,"")</f>
+        <f>IF(COUNT(B25:B26)=2,(B25/B26-1)*100,"")</f>
         <v/>
       </c>
       <c r="D25" s="5" t="n">
         <v>63.56</v>
       </c>
       <c r="E25" s="5">
-        <f>IF(AND(ISNUMBER(D25),ISNUMBER(D26)),(D25/D26-1)*100,"")</f>
+        <f>IF(COUNT(D25:D26)=2,(D25/D26-1)*100,"")</f>
         <v/>
       </c>
       <c r="F25" s="5" t="n">
         <v>79.295</v>
       </c>
       <c r="G25" s="5">
-        <f>IF(AND(ISNUMBER(F25),ISNUMBER(F26)),(F25/F26-1)*100,"")</f>
+        <f>IF(COUNT(F25:F26)=2,(F25/F26-1)*100,"")</f>
         <v/>
       </c>
       <c r="H25" s="5" t="n">
         <v>56.04</v>
       </c>
       <c r="I25" s="5">
-        <f>IF(AND(ISNUMBER(H25),ISNUMBER(H26)),(H25/H26-1)*100,"")</f>
+        <f>IF(COUNT(H25:H26)=2,(H25/H26-1)*100,"")</f>
         <v/>
       </c>
       <c r="J25" s="5" t="n">
         <v>70.73999999999999</v>
       </c>
       <c r="K25" s="5">
-        <f>IF(AND(ISNUMBER(J25),ISNUMBER(J26)),(J25/J26-1)*100,"")</f>
+        <f>IF(COUNT(J25:J26)=2,(J25/J26-1)*100,"")</f>
         <v/>
       </c>
       <c r="L25" s="5" t="n">
         <v>-0.6393</v>
       </c>
       <c r="M25" s="5">
-        <f>IF(AND(ISNUMBER(L25),ISNUMBER(L26)),(L25/L26-1)*100,"")</f>
+        <f>IF(COUNT(L25:L26)=2,(L25/L26-1)*100,"")</f>
         <v/>
       </c>
       <c r="N25" s="5" t="n"/>
       <c r="O25" s="5">
-        <f>IF(AND(ISNUMBER(N25),ISNUMBER(N26)),(N25/N26-1)*100,"")</f>
+        <f>IF(COUNT(N25:N26)=2,(N25/N26-1)*100,"")</f>
         <v/>
       </c>
       <c r="P25" s="5" t="n"/>
       <c r="Q25" s="5">
-        <f>IF(AND(ISNUMBER(P25),ISNUMBER(P26)),(P25/P26-1)*100,"")</f>
+        <f>IF(COUNT(P25:P26)=2,(P25/P26-1)*100,"")</f>
         <v/>
       </c>
       <c r="R25" s="5" t="n"/>
       <c r="S25" s="5">
-        <f>IF(AND(ISNUMBER(R25),ISNUMBER(R26)),(R25/R26-1)*100,"")</f>
+        <f>IF(COUNT(R25:R26)=2,(R25/R26-1)*100,"")</f>
         <v/>
       </c>
       <c r="T25" s="5" t="n"/>
       <c r="U25" s="5">
-        <f>IF(AND(ISNUMBER(T25),ISNUMBER(T26)),(T25/T26-1)*100,"")</f>
+        <f>IF(COUNT(T25:T26)=2,(T25/T26-1)*100,"")</f>
         <v/>
       </c>
       <c r="V25" s="5" t="n"/>
@@ -2985,31 +3062,31 @@
         <v/>
       </c>
       <c r="X25" s="5">
+        <f>IF(AND(K25&lt;0,M25&gt;0),C24,"")</f>
+        <v/>
+      </c>
+      <c r="Y25" s="5">
         <f>IF(AND(G25&gt;0,I25&lt;0,K25&gt;0),C24,"")</f>
         <v/>
       </c>
-      <c r="Y25" s="5">
-        <f>IF(AND(K25&lt;0,M25&gt;0),C24,"")</f>
-        <v/>
-      </c>
       <c r="Z25" s="5">
-        <f>IF(AND(ISNUMBER(W25),0.549579&gt;=MAX(IF(ISNUMBER(X25),0.299732,-1),IF(ISNUMBER(Y25),0.323835,-1))),W25,IF(AND(ISNUMBER(X25),0.299732&gt;MAX(IF(ISNUMBER(W25),0.549579,-1),IF(ISNUMBER(Y25),0.323835,-1))),X25,IF(AND(ISNUMBER(Y25),0.323835&gt;MAX(IF(ISNUMBER(W25),0.549579,-1),IF(ISNUMBER(X25),0.299732,-1))),Y25,"")))</f>
+        <f>IF(W25&lt;&gt;"",W25,IF(X25&lt;&gt;"",X25,Y25))</f>
         <v/>
       </c>
       <c r="AA25" s="5">
+        <f>IF(AND(S25&gt;0,U25&lt;0),E24,"")</f>
+        <v/>
+      </c>
+      <c r="AB25" s="5">
         <f>IF(AND(O25&lt;=-1,E25&lt;0),E24,"")</f>
         <v/>
       </c>
-      <c r="AB25" s="5">
+      <c r="AC25" s="5">
         <f>IF(AND(Q25&gt;0,S25&gt;0),E24,"")</f>
         <v/>
       </c>
-      <c r="AC25" s="5">
-        <f>IF(AND(S25&gt;0,U25&lt;0),E24,"")</f>
-        <v/>
-      </c>
       <c r="AD25" s="5">
-        <f>IF(AND(ISNUMBER(AA25),0.408167&gt;=MAX(IF(ISNUMBER(AB25),0.31868,-1),IF(ISNUMBER(AC25),0.510996,-1))),AA25,IF(AND(ISNUMBER(AB25),0.31868&gt;MAX(IF(ISNUMBER(AA25),0.408167,-1),IF(ISNUMBER(AC25),0.510996,-1))),AB25,IF(AND(ISNUMBER(AC25),0.510996&gt;MAX(IF(ISNUMBER(AA25),0.408167,-1),IF(ISNUMBER(AB25),0.31868,-1))),AC25,"")))</f>
+        <f>IF(AA25&lt;&gt;"",AA25,IF(AB25&lt;&gt;"",AB25,AC25))</f>
         <v/>
       </c>
     </row>
@@ -3023,62 +3100,62 @@
         <v>152.68</v>
       </c>
       <c r="C26" s="5">
-        <f>IF(AND(ISNUMBER(B26),ISNUMBER(B27)),(B26/B27-1)*100,"")</f>
+        <f>IF(COUNT(B26:B27)=2,(B26/B27-1)*100,"")</f>
         <v/>
       </c>
       <c r="D26" s="5" t="n">
         <v>63.29</v>
       </c>
       <c r="E26" s="5">
-        <f>IF(AND(ISNUMBER(D26),ISNUMBER(D27)),(D26/D27-1)*100,"")</f>
+        <f>IF(COUNT(D26:D27)=2,(D26/D27-1)*100,"")</f>
         <v/>
       </c>
       <c r="F26" s="5" t="n">
         <v>79.26519999999999</v>
       </c>
       <c r="G26" s="5">
-        <f>IF(AND(ISNUMBER(F26),ISNUMBER(F27)),(F26/F27-1)*100,"")</f>
+        <f>IF(COUNT(F26:F27)=2,(F26/F27-1)*100,"")</f>
         <v/>
       </c>
       <c r="H26" s="5" t="n">
         <v>56.26</v>
       </c>
       <c r="I26" s="5">
-        <f>IF(AND(ISNUMBER(H26),ISNUMBER(H27)),(H26/H27-1)*100,"")</f>
+        <f>IF(COUNT(H26:H27)=2,(H26/H27-1)*100,"")</f>
         <v/>
       </c>
       <c r="J26" s="5" t="n">
         <v>71.31999999999999</v>
       </c>
       <c r="K26" s="5">
-        <f>IF(AND(ISNUMBER(J26),ISNUMBER(J27)),(J26/J27-1)*100,"")</f>
+        <f>IF(COUNT(J26:J27)=2,(J26/J27-1)*100,"")</f>
         <v/>
       </c>
       <c r="L26" s="5" t="n">
         <v>12.1937</v>
       </c>
       <c r="M26" s="5">
-        <f>IF(AND(ISNUMBER(L26),ISNUMBER(L27)),(L26/L27-1)*100,"")</f>
+        <f>IF(COUNT(L26:L27)=2,(L26/L27-1)*100,"")</f>
         <v/>
       </c>
       <c r="N26" s="5" t="n"/>
       <c r="O26" s="5">
-        <f>IF(AND(ISNUMBER(N26),ISNUMBER(N27)),(N26/N27-1)*100,"")</f>
+        <f>IF(COUNT(N26:N27)=2,(N26/N27-1)*100,"")</f>
         <v/>
       </c>
       <c r="P26" s="5" t="n"/>
       <c r="Q26" s="5">
-        <f>IF(AND(ISNUMBER(P26),ISNUMBER(P27)),(P26/P27-1)*100,"")</f>
+        <f>IF(COUNT(P26:P27)=2,(P26/P27-1)*100,"")</f>
         <v/>
       </c>
       <c r="R26" s="5" t="n"/>
       <c r="S26" s="5">
-        <f>IF(AND(ISNUMBER(R26),ISNUMBER(R27)),(R26/R27-1)*100,"")</f>
+        <f>IF(COUNT(R26:R27)=2,(R26/R27-1)*100,"")</f>
         <v/>
       </c>
       <c r="T26" s="5" t="n"/>
       <c r="U26" s="5">
-        <f>IF(AND(ISNUMBER(T26),ISNUMBER(T27)),(T26/T27-1)*100,"")</f>
+        <f>IF(COUNT(T26:T27)=2,(T26/T27-1)*100,"")</f>
         <v/>
       </c>
       <c r="V26" s="5" t="n"/>
@@ -3087,31 +3164,31 @@
         <v/>
       </c>
       <c r="X26" s="5">
+        <f>IF(AND(K26&lt;0,M26&gt;0),C25,"")</f>
+        <v/>
+      </c>
+      <c r="Y26" s="5">
         <f>IF(AND(G26&gt;0,I26&lt;0,K26&gt;0),C25,"")</f>
         <v/>
       </c>
-      <c r="Y26" s="5">
-        <f>IF(AND(K26&lt;0,M26&gt;0),C25,"")</f>
-        <v/>
-      </c>
       <c r="Z26" s="5">
-        <f>IF(AND(ISNUMBER(W26),0.549579&gt;=MAX(IF(ISNUMBER(X26),0.299732,-1),IF(ISNUMBER(Y26),0.323835,-1))),W26,IF(AND(ISNUMBER(X26),0.299732&gt;MAX(IF(ISNUMBER(W26),0.549579,-1),IF(ISNUMBER(Y26),0.323835,-1))),X26,IF(AND(ISNUMBER(Y26),0.323835&gt;MAX(IF(ISNUMBER(W26),0.549579,-1),IF(ISNUMBER(X26),0.299732,-1))),Y26,"")))</f>
+        <f>IF(W26&lt;&gt;"",W26,IF(X26&lt;&gt;"",X26,Y26))</f>
         <v/>
       </c>
       <c r="AA26" s="5">
+        <f>IF(AND(S26&gt;0,U26&lt;0),E25,"")</f>
+        <v/>
+      </c>
+      <c r="AB26" s="5">
         <f>IF(AND(O26&lt;=-1,E26&lt;0),E25,"")</f>
         <v/>
       </c>
-      <c r="AB26" s="5">
+      <c r="AC26" s="5">
         <f>IF(AND(Q26&gt;0,S26&gt;0),E25,"")</f>
         <v/>
       </c>
-      <c r="AC26" s="5">
-        <f>IF(AND(S26&gt;0,U26&lt;0),E25,"")</f>
-        <v/>
-      </c>
       <c r="AD26" s="5">
-        <f>IF(AND(ISNUMBER(AA26),0.408167&gt;=MAX(IF(ISNUMBER(AB26),0.31868,-1),IF(ISNUMBER(AC26),0.510996,-1))),AA26,IF(AND(ISNUMBER(AB26),0.31868&gt;MAX(IF(ISNUMBER(AA26),0.408167,-1),IF(ISNUMBER(AC26),0.510996,-1))),AB26,IF(AND(ISNUMBER(AC26),0.510996&gt;MAX(IF(ISNUMBER(AA26),0.408167,-1),IF(ISNUMBER(AB26),0.31868,-1))),AC26,"")))</f>
+        <f>IF(AA26&lt;&gt;"",AA26,IF(AB26&lt;&gt;"",AB26,AC26))</f>
         <v/>
       </c>
     </row>
@@ -3125,62 +3202,62 @@
         <v>157.41</v>
       </c>
       <c r="C27" s="5">
-        <f>IF(AND(ISNUMBER(B27),ISNUMBER(B28)),(B27/B28-1)*100,"")</f>
+        <f>IF(COUNT(B27:B28)=2,(B27/B28-1)*100,"")</f>
         <v/>
       </c>
       <c r="D27" s="5" t="n">
         <v>64.19</v>
       </c>
       <c r="E27" s="5">
-        <f>IF(AND(ISNUMBER(D27),ISNUMBER(D28)),(D27/D28-1)*100,"")</f>
+        <f>IF(COUNT(D27:D28)=2,(D27/D28-1)*100,"")</f>
         <v/>
       </c>
       <c r="F27" s="5" t="n">
         <v>79.4145</v>
       </c>
       <c r="G27" s="5">
-        <f>IF(AND(ISNUMBER(F27),ISNUMBER(F28)),(F27/F28-1)*100,"")</f>
+        <f>IF(COUNT(F27:F28)=2,(F27/F28-1)*100,"")</f>
         <v/>
       </c>
       <c r="H27" s="5" t="n">
         <v>56.75</v>
       </c>
       <c r="I27" s="5">
-        <f>IF(AND(ISNUMBER(H27),ISNUMBER(H28)),(H27/H28-1)*100,"")</f>
+        <f>IF(COUNT(H27:H28)=2,(H27/H28-1)*100,"")</f>
         <v/>
       </c>
       <c r="J27" s="5" t="n">
         <v>71.40000000000001</v>
       </c>
       <c r="K27" s="5">
-        <f>IF(AND(ISNUMBER(J27),ISNUMBER(J28)),(J27/J28-1)*100,"")</f>
+        <f>IF(COUNT(J27:J28)=2,(J27/J28-1)*100,"")</f>
         <v/>
       </c>
       <c r="L27" s="5" t="n">
         <v>6.7645</v>
       </c>
       <c r="M27" s="5">
-        <f>IF(AND(ISNUMBER(L27),ISNUMBER(L28)),(L27/L28-1)*100,"")</f>
+        <f>IF(COUNT(L27:L28)=2,(L27/L28-1)*100,"")</f>
         <v/>
       </c>
       <c r="N27" s="5" t="n"/>
       <c r="O27" s="5">
-        <f>IF(AND(ISNUMBER(N27),ISNUMBER(N28)),(N27/N28-1)*100,"")</f>
+        <f>IF(COUNT(N27:N28)=2,(N27/N28-1)*100,"")</f>
         <v/>
       </c>
       <c r="P27" s="5" t="n"/>
       <c r="Q27" s="5">
-        <f>IF(AND(ISNUMBER(P27),ISNUMBER(P28)),(P27/P28-1)*100,"")</f>
+        <f>IF(COUNT(P27:P28)=2,(P27/P28-1)*100,"")</f>
         <v/>
       </c>
       <c r="R27" s="5" t="n"/>
       <c r="S27" s="5">
-        <f>IF(AND(ISNUMBER(R27),ISNUMBER(R28)),(R27/R28-1)*100,"")</f>
+        <f>IF(COUNT(R27:R28)=2,(R27/R28-1)*100,"")</f>
         <v/>
       </c>
       <c r="T27" s="5" t="n"/>
       <c r="U27" s="5">
-        <f>IF(AND(ISNUMBER(T27),ISNUMBER(T28)),(T27/T28-1)*100,"")</f>
+        <f>IF(COUNT(T27:T28)=2,(T27/T28-1)*100,"")</f>
         <v/>
       </c>
       <c r="V27" s="5" t="n"/>
@@ -3189,31 +3266,31 @@
         <v/>
       </c>
       <c r="X27" s="5">
+        <f>IF(AND(K27&lt;0,M27&gt;0),C26,"")</f>
+        <v/>
+      </c>
+      <c r="Y27" s="5">
         <f>IF(AND(G27&gt;0,I27&lt;0,K27&gt;0),C26,"")</f>
         <v/>
       </c>
-      <c r="Y27" s="5">
-        <f>IF(AND(K27&lt;0,M27&gt;0),C26,"")</f>
-        <v/>
-      </c>
       <c r="Z27" s="5">
-        <f>IF(AND(ISNUMBER(W27),0.549579&gt;=MAX(IF(ISNUMBER(X27),0.299732,-1),IF(ISNUMBER(Y27),0.323835,-1))),W27,IF(AND(ISNUMBER(X27),0.299732&gt;MAX(IF(ISNUMBER(W27),0.549579,-1),IF(ISNUMBER(Y27),0.323835,-1))),X27,IF(AND(ISNUMBER(Y27),0.323835&gt;MAX(IF(ISNUMBER(W27),0.549579,-1),IF(ISNUMBER(X27),0.299732,-1))),Y27,"")))</f>
+        <f>IF(W27&lt;&gt;"",W27,IF(X27&lt;&gt;"",X27,Y27))</f>
         <v/>
       </c>
       <c r="AA27" s="5">
+        <f>IF(AND(S27&gt;0,U27&lt;0),E26,"")</f>
+        <v/>
+      </c>
+      <c r="AB27" s="5">
         <f>IF(AND(O27&lt;=-1,E27&lt;0),E26,"")</f>
         <v/>
       </c>
-      <c r="AB27" s="5">
+      <c r="AC27" s="5">
         <f>IF(AND(Q27&gt;0,S27&gt;0),E26,"")</f>
         <v/>
       </c>
-      <c r="AC27" s="5">
-        <f>IF(AND(S27&gt;0,U27&lt;0),E26,"")</f>
-        <v/>
-      </c>
       <c r="AD27" s="5">
-        <f>IF(AND(ISNUMBER(AA27),0.408167&gt;=MAX(IF(ISNUMBER(AB27),0.31868,-1),IF(ISNUMBER(AC27),0.510996,-1))),AA27,IF(AND(ISNUMBER(AB27),0.31868&gt;MAX(IF(ISNUMBER(AA27),0.408167,-1),IF(ISNUMBER(AC27),0.510996,-1))),AB27,IF(AND(ISNUMBER(AC27),0.510996&gt;MAX(IF(ISNUMBER(AA27),0.408167,-1),IF(ISNUMBER(AB27),0.31868,-1))),AC27,"")))</f>
+        <f>IF(AA27&lt;&gt;"",AA27,IF(AB27&lt;&gt;"",AB27,AC27))</f>
         <v/>
       </c>
     </row>
@@ -3227,62 +3304,62 @@
         <v>162.7</v>
       </c>
       <c r="C28" s="5">
-        <f>IF(AND(ISNUMBER(B28),ISNUMBER(B29)),(B28/B29-1)*100,"")</f>
+        <f>IF(COUNT(B28:B29)=2,(B28/B29-1)*100,"")</f>
         <v/>
       </c>
       <c r="D28" s="5" t="n">
         <v>65.56999999999999</v>
       </c>
       <c r="E28" s="5">
-        <f>IF(AND(ISNUMBER(D28),ISNUMBER(D29)),(D28/D29-1)*100,"")</f>
+        <f>IF(COUNT(D28:D29)=2,(D28/D29-1)*100,"")</f>
         <v/>
       </c>
       <c r="F28" s="5" t="n">
         <v>79.42440000000001</v>
       </c>
       <c r="G28" s="5">
-        <f>IF(AND(ISNUMBER(F28),ISNUMBER(F29)),(F28/F29-1)*100,"")</f>
+        <f>IF(COUNT(F28:F29)=2,(F28/F29-1)*100,"")</f>
         <v/>
       </c>
       <c r="H28" s="5" t="n">
         <v>56.56</v>
       </c>
       <c r="I28" s="5">
-        <f>IF(AND(ISNUMBER(H28),ISNUMBER(H29)),(H28/H29-1)*100,"")</f>
+        <f>IF(COUNT(H28:H29)=2,(H28/H29-1)*100,"")</f>
         <v/>
       </c>
       <c r="J28" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K28" s="5">
-        <f>IF(AND(ISNUMBER(J28),ISNUMBER(J29)),(J28/J29-1)*100,"")</f>
+        <f>IF(COUNT(J28:J29)=2,(J28/J29-1)*100,"")</f>
         <v/>
       </c>
       <c r="L28" s="5" t="n">
         <v>-5.0303</v>
       </c>
       <c r="M28" s="5">
-        <f>IF(AND(ISNUMBER(L28),ISNUMBER(L29)),(L28/L29-1)*100,"")</f>
+        <f>IF(COUNT(L28:L29)=2,(L28/L29-1)*100,"")</f>
         <v/>
       </c>
       <c r="N28" s="5" t="n"/>
       <c r="O28" s="5">
-        <f>IF(AND(ISNUMBER(N28),ISNUMBER(N29)),(N28/N29-1)*100,"")</f>
+        <f>IF(COUNT(N28:N29)=2,(N28/N29-1)*100,"")</f>
         <v/>
       </c>
       <c r="P28" s="5" t="n"/>
       <c r="Q28" s="5">
-        <f>IF(AND(ISNUMBER(P28),ISNUMBER(P29)),(P28/P29-1)*100,"")</f>
+        <f>IF(COUNT(P28:P29)=2,(P28/P29-1)*100,"")</f>
         <v/>
       </c>
       <c r="R28" s="5" t="n"/>
       <c r="S28" s="5">
-        <f>IF(AND(ISNUMBER(R28),ISNUMBER(R29)),(R28/R29-1)*100,"")</f>
+        <f>IF(COUNT(R28:R29)=2,(R28/R29-1)*100,"")</f>
         <v/>
       </c>
       <c r="T28" s="5" t="n"/>
       <c r="U28" s="5">
-        <f>IF(AND(ISNUMBER(T28),ISNUMBER(T29)),(T28/T29-1)*100,"")</f>
+        <f>IF(COUNT(T28:T29)=2,(T28/T29-1)*100,"")</f>
         <v/>
       </c>
       <c r="V28" s="5" t="n"/>
@@ -3291,31 +3368,31 @@
         <v/>
       </c>
       <c r="X28" s="5">
+        <f>IF(AND(K28&lt;0,M28&gt;0),C27,"")</f>
+        <v/>
+      </c>
+      <c r="Y28" s="5">
         <f>IF(AND(G28&gt;0,I28&lt;0,K28&gt;0),C27,"")</f>
         <v/>
       </c>
-      <c r="Y28" s="5">
-        <f>IF(AND(K28&lt;0,M28&gt;0),C27,"")</f>
-        <v/>
-      </c>
       <c r="Z28" s="5">
-        <f>IF(AND(ISNUMBER(W28),0.549579&gt;=MAX(IF(ISNUMBER(X28),0.299732,-1),IF(ISNUMBER(Y28),0.323835,-1))),W28,IF(AND(ISNUMBER(X28),0.299732&gt;MAX(IF(ISNUMBER(W28),0.549579,-1),IF(ISNUMBER(Y28),0.323835,-1))),X28,IF(AND(ISNUMBER(Y28),0.323835&gt;MAX(IF(ISNUMBER(W28),0.549579,-1),IF(ISNUMBER(X28),0.299732,-1))),Y28,"")))</f>
+        <f>IF(W28&lt;&gt;"",W28,IF(X28&lt;&gt;"",X28,Y28))</f>
         <v/>
       </c>
       <c r="AA28" s="5">
+        <f>IF(AND(S28&gt;0,U28&lt;0),E27,"")</f>
+        <v/>
+      </c>
+      <c r="AB28" s="5">
         <f>IF(AND(O28&lt;=-1,E28&lt;0),E27,"")</f>
         <v/>
       </c>
-      <c r="AB28" s="5">
+      <c r="AC28" s="5">
         <f>IF(AND(Q28&gt;0,S28&gt;0),E27,"")</f>
         <v/>
       </c>
-      <c r="AC28" s="5">
-        <f>IF(AND(S28&gt;0,U28&lt;0),E27,"")</f>
-        <v/>
-      </c>
       <c r="AD28" s="5">
-        <f>IF(AND(ISNUMBER(AA28),0.408167&gt;=MAX(IF(ISNUMBER(AB28),0.31868,-1),IF(ISNUMBER(AC28),0.510996,-1))),AA28,IF(AND(ISNUMBER(AB28),0.31868&gt;MAX(IF(ISNUMBER(AA28),0.408167,-1),IF(ISNUMBER(AC28),0.510996,-1))),AB28,IF(AND(ISNUMBER(AC28),0.510996&gt;MAX(IF(ISNUMBER(AA28),0.408167,-1),IF(ISNUMBER(AB28),0.31868,-1))),AC28,"")))</f>
+        <f>IF(AA28&lt;&gt;"",AA28,IF(AB28&lt;&gt;"",AB28,AC28))</f>
         <v/>
       </c>
     </row>
@@ -3329,62 +3406,62 @@
         <v>163.66</v>
       </c>
       <c r="C29" s="5">
-        <f>IF(AND(ISNUMBER(B29),ISNUMBER(B30)),(B29/B30-1)*100,"")</f>
+        <f>IF(COUNT(B29:B30)=2,(B29/B30-1)*100,"")</f>
         <v/>
       </c>
       <c r="D29" s="5" t="n">
         <v>65.67</v>
       </c>
       <c r="E29" s="5">
-        <f>IF(AND(ISNUMBER(D29),ISNUMBER(D30)),(D29/D30-1)*100,"")</f>
+        <f>IF(COUNT(D29:D30)=2,(D29/D30-1)*100,"")</f>
         <v/>
       </c>
       <c r="F29" s="5" t="n">
         <v>79.295</v>
       </c>
       <c r="G29" s="5">
-        <f>IF(AND(ISNUMBER(F29),ISNUMBER(F30)),(F29/F30-1)*100,"")</f>
+        <f>IF(COUNT(F29:F30)=2,(F29/F30-1)*100,"")</f>
         <v/>
       </c>
       <c r="H29" s="5" t="n">
         <v>56.18</v>
       </c>
       <c r="I29" s="5">
-        <f>IF(AND(ISNUMBER(H29),ISNUMBER(H30)),(H29/H30-1)*100,"")</f>
+        <f>IF(COUNT(H29:H30)=2,(H29/H30-1)*100,"")</f>
         <v/>
       </c>
       <c r="J29" s="5" t="n">
         <v>74.88</v>
       </c>
       <c r="K29" s="5">
-        <f>IF(AND(ISNUMBER(J29),ISNUMBER(J30)),(J29/J30-1)*100,"")</f>
+        <f>IF(COUNT(J29:J30)=2,(J29/J30-1)*100,"")</f>
         <v/>
       </c>
       <c r="L29" s="5" t="n">
         <v>-3.8462</v>
       </c>
       <c r="M29" s="5">
-        <f>IF(AND(ISNUMBER(L29),ISNUMBER(L30)),(L29/L30-1)*100,"")</f>
+        <f>IF(COUNT(L29:L30)=2,(L29/L30-1)*100,"")</f>
         <v/>
       </c>
       <c r="N29" s="5" t="n"/>
       <c r="O29" s="5">
-        <f>IF(AND(ISNUMBER(N29),ISNUMBER(N30)),(N29/N30-1)*100,"")</f>
+        <f>IF(COUNT(N29:N30)=2,(N29/N30-1)*100,"")</f>
         <v/>
       </c>
       <c r="P29" s="5" t="n"/>
       <c r="Q29" s="5">
-        <f>IF(AND(ISNUMBER(P29),ISNUMBER(P30)),(P29/P30-1)*100,"")</f>
+        <f>IF(COUNT(P29:P30)=2,(P29/P30-1)*100,"")</f>
         <v/>
       </c>
       <c r="R29" s="5" t="n"/>
       <c r="S29" s="5">
-        <f>IF(AND(ISNUMBER(R29),ISNUMBER(R30)),(R29/R30-1)*100,"")</f>
+        <f>IF(COUNT(R29:R30)=2,(R29/R30-1)*100,"")</f>
         <v/>
       </c>
       <c r="T29" s="5" t="n"/>
       <c r="U29" s="5">
-        <f>IF(AND(ISNUMBER(T29),ISNUMBER(T30)),(T29/T30-1)*100,"")</f>
+        <f>IF(COUNT(T29:T30)=2,(T29/T30-1)*100,"")</f>
         <v/>
       </c>
       <c r="V29" s="5" t="n"/>
@@ -3393,31 +3470,31 @@
         <v/>
       </c>
       <c r="X29" s="5">
+        <f>IF(AND(K29&lt;0,M29&gt;0),C28,"")</f>
+        <v/>
+      </c>
+      <c r="Y29" s="5">
         <f>IF(AND(G29&gt;0,I29&lt;0,K29&gt;0),C28,"")</f>
         <v/>
       </c>
-      <c r="Y29" s="5">
-        <f>IF(AND(K29&lt;0,M29&gt;0),C28,"")</f>
-        <v/>
-      </c>
       <c r="Z29" s="5">
-        <f>IF(AND(ISNUMBER(W29),0.549579&gt;=MAX(IF(ISNUMBER(X29),0.299732,-1),IF(ISNUMBER(Y29),0.323835,-1))),W29,IF(AND(ISNUMBER(X29),0.299732&gt;MAX(IF(ISNUMBER(W29),0.549579,-1),IF(ISNUMBER(Y29),0.323835,-1))),X29,IF(AND(ISNUMBER(Y29),0.323835&gt;MAX(IF(ISNUMBER(W29),0.549579,-1),IF(ISNUMBER(X29),0.299732,-1))),Y29,"")))</f>
+        <f>IF(W29&lt;&gt;"",W29,IF(X29&lt;&gt;"",X29,Y29))</f>
         <v/>
       </c>
       <c r="AA29" s="5">
+        <f>IF(AND(S29&gt;0,U29&lt;0),E28,"")</f>
+        <v/>
+      </c>
+      <c r="AB29" s="5">
         <f>IF(AND(O29&lt;=-1,E29&lt;0),E28,"")</f>
         <v/>
       </c>
-      <c r="AB29" s="5">
+      <c r="AC29" s="5">
         <f>IF(AND(Q29&gt;0,S29&gt;0),E28,"")</f>
         <v/>
       </c>
-      <c r="AC29" s="5">
-        <f>IF(AND(S29&gt;0,U29&lt;0),E28,"")</f>
-        <v/>
-      </c>
       <c r="AD29" s="5">
-        <f>IF(AND(ISNUMBER(AA29),0.408167&gt;=MAX(IF(ISNUMBER(AB29),0.31868,-1),IF(ISNUMBER(AC29),0.510996,-1))),AA29,IF(AND(ISNUMBER(AB29),0.31868&gt;MAX(IF(ISNUMBER(AA29),0.408167,-1),IF(ISNUMBER(AC29),0.510996,-1))),AB29,IF(AND(ISNUMBER(AC29),0.510996&gt;MAX(IF(ISNUMBER(AA29),0.408167,-1),IF(ISNUMBER(AB29),0.31868,-1))),AC29,"")))</f>
+        <f>IF(AA29&lt;&gt;"",AA29,IF(AB29&lt;&gt;"",AB29,AC29))</f>
         <v/>
       </c>
     </row>
@@ -3431,62 +3508,62 @@
         <v>160.15</v>
       </c>
       <c r="C30" s="5">
-        <f>IF(AND(ISNUMBER(B30),ISNUMBER(B31)),(B30/B31-1)*100,"")</f>
+        <f>IF(COUNT(B30:B31)=2,(B30/B31-1)*100,"")</f>
         <v/>
       </c>
       <c r="D30" s="5" t="n">
         <v>64.5</v>
       </c>
       <c r="E30" s="5">
-        <f>IF(AND(ISNUMBER(D30),ISNUMBER(D31)),(D30/D31-1)*100,"")</f>
+        <f>IF(COUNT(D30:D31)=2,(D30/D31-1)*100,"")</f>
         <v/>
       </c>
       <c r="F30" s="5" t="n">
         <v>79.1358</v>
       </c>
       <c r="G30" s="5">
-        <f>IF(AND(ISNUMBER(F30),ISNUMBER(F31)),(F30/F31-1)*100,"")</f>
+        <f>IF(COUNT(F30:F31)=2,(F30/F31-1)*100,"")</f>
         <v/>
       </c>
       <c r="H30" s="5" t="n">
         <v>56.07</v>
       </c>
       <c r="I30" s="5">
-        <f>IF(AND(ISNUMBER(H30),ISNUMBER(H31)),(H30/H31-1)*100,"")</f>
+        <f>IF(COUNT(H30:H31)=2,(H30/H31-1)*100,"")</f>
         <v/>
       </c>
       <c r="J30" s="5" t="n">
         <v>73.37</v>
       </c>
       <c r="K30" s="5">
-        <f>IF(AND(ISNUMBER(J30),ISNUMBER(J31)),(J30/J31-1)*100,"")</f>
+        <f>IF(COUNT(J30:J31)=2,(J30/J31-1)*100,"")</f>
         <v/>
       </c>
       <c r="L30" s="5" t="n">
         <v>14.1717</v>
       </c>
       <c r="M30" s="5">
-        <f>IF(AND(ISNUMBER(L30),ISNUMBER(L31)),(L30/L31-1)*100,"")</f>
+        <f>IF(COUNT(L30:L31)=2,(L30/L31-1)*100,"")</f>
         <v/>
       </c>
       <c r="N30" s="5" t="n"/>
       <c r="O30" s="5">
-        <f>IF(AND(ISNUMBER(N30),ISNUMBER(N31)),(N30/N31-1)*100,"")</f>
+        <f>IF(COUNT(N30:N31)=2,(N30/N31-1)*100,"")</f>
         <v/>
       </c>
       <c r="P30" s="5" t="n"/>
       <c r="Q30" s="5">
-        <f>IF(AND(ISNUMBER(P30),ISNUMBER(P31)),(P30/P31-1)*100,"")</f>
+        <f>IF(COUNT(P30:P31)=2,(P30/P31-1)*100,"")</f>
         <v/>
       </c>
       <c r="R30" s="5" t="n"/>
       <c r="S30" s="5">
-        <f>IF(AND(ISNUMBER(R30),ISNUMBER(R31)),(R30/R31-1)*100,"")</f>
+        <f>IF(COUNT(R30:R31)=2,(R30/R31-1)*100,"")</f>
         <v/>
       </c>
       <c r="T30" s="5" t="n"/>
       <c r="U30" s="5">
-        <f>IF(AND(ISNUMBER(T30),ISNUMBER(T31)),(T30/T31-1)*100,"")</f>
+        <f>IF(COUNT(T30:T31)=2,(T30/T31-1)*100,"")</f>
         <v/>
       </c>
       <c r="V30" s="5" t="n"/>
@@ -3495,31 +3572,31 @@
         <v/>
       </c>
       <c r="X30" s="5">
+        <f>IF(AND(K30&lt;0,M30&gt;0),C29,"")</f>
+        <v/>
+      </c>
+      <c r="Y30" s="5">
         <f>IF(AND(G30&gt;0,I30&lt;0,K30&gt;0),C29,"")</f>
         <v/>
       </c>
-      <c r="Y30" s="5">
-        <f>IF(AND(K30&lt;0,M30&gt;0),C29,"")</f>
-        <v/>
-      </c>
       <c r="Z30" s="5">
-        <f>IF(AND(ISNUMBER(W30),0.549579&gt;=MAX(IF(ISNUMBER(X30),0.299732,-1),IF(ISNUMBER(Y30),0.323835,-1))),W30,IF(AND(ISNUMBER(X30),0.299732&gt;MAX(IF(ISNUMBER(W30),0.549579,-1),IF(ISNUMBER(Y30),0.323835,-1))),X30,IF(AND(ISNUMBER(Y30),0.323835&gt;MAX(IF(ISNUMBER(W30),0.549579,-1),IF(ISNUMBER(X30),0.299732,-1))),Y30,"")))</f>
+        <f>IF(W30&lt;&gt;"",W30,IF(X30&lt;&gt;"",X30,Y30))</f>
         <v/>
       </c>
       <c r="AA30" s="5">
+        <f>IF(AND(S30&gt;0,U30&lt;0),E29,"")</f>
+        <v/>
+      </c>
+      <c r="AB30" s="5">
         <f>IF(AND(O30&lt;=-1,E30&lt;0),E29,"")</f>
         <v/>
       </c>
-      <c r="AB30" s="5">
+      <c r="AC30" s="5">
         <f>IF(AND(Q30&gt;0,S30&gt;0),E29,"")</f>
         <v/>
       </c>
-      <c r="AC30" s="5">
-        <f>IF(AND(S30&gt;0,U30&lt;0),E29,"")</f>
-        <v/>
-      </c>
       <c r="AD30" s="5">
-        <f>IF(AND(ISNUMBER(AA30),0.408167&gt;=MAX(IF(ISNUMBER(AB30),0.31868,-1),IF(ISNUMBER(AC30),0.510996,-1))),AA30,IF(AND(ISNUMBER(AB30),0.31868&gt;MAX(IF(ISNUMBER(AA30),0.408167,-1),IF(ISNUMBER(AC30),0.510996,-1))),AB30,IF(AND(ISNUMBER(AC30),0.510996&gt;MAX(IF(ISNUMBER(AA30),0.408167,-1),IF(ISNUMBER(AB30),0.31868,-1))),AC30,"")))</f>
+        <f>IF(AA30&lt;&gt;"",AA30,IF(AB30&lt;&gt;"",AB30,AC30))</f>
         <v/>
       </c>
     </row>
@@ -3533,62 +3610,62 @@
         <v>166.49</v>
       </c>
       <c r="C31" s="5">
-        <f>IF(AND(ISNUMBER(B31),ISNUMBER(B32)),(B31/B32-1)*100,"")</f>
+        <f>IF(COUNT(B31:B32)=2,(B31/B32-1)*100,"")</f>
         <v/>
       </c>
       <c r="D31" s="5" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="E31" s="5">
-        <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32)),(D31/D32-1)*100,"")</f>
+        <f>IF(COUNT(D31:D32)=2,(D31/D32-1)*100,"")</f>
         <v/>
       </c>
       <c r="F31" s="5" t="n">
         <v>79.3249</v>
       </c>
       <c r="G31" s="5">
-        <f>IF(AND(ISNUMBER(F31),ISNUMBER(F32)),(F31/F32-1)*100,"")</f>
+        <f>IF(COUNT(F31:F32)=2,(F31/F32-1)*100,"")</f>
         <v/>
       </c>
       <c r="H31" s="5" t="n">
         <v>55.71</v>
       </c>
       <c r="I31" s="5">
-        <f>IF(AND(ISNUMBER(H31),ISNUMBER(H32)),(H31/H32-1)*100,"")</f>
+        <f>IF(COUNT(H31:H32)=2,(H31/H32-1)*100,"")</f>
         <v/>
       </c>
       <c r="J31" s="5" t="n">
         <v>75.53</v>
       </c>
       <c r="K31" s="5">
-        <f>IF(AND(ISNUMBER(J31),ISNUMBER(J32)),(J31/J32-1)*100,"")</f>
+        <f>IF(COUNT(J31:J32)=2,(J31/J32-1)*100,"")</f>
         <v/>
       </c>
       <c r="L31" s="5" t="n">
         <v>-5.1136</v>
       </c>
       <c r="M31" s="5">
-        <f>IF(AND(ISNUMBER(L31),ISNUMBER(L32)),(L31/L32-1)*100,"")</f>
+        <f>IF(COUNT(L31:L32)=2,(L31/L32-1)*100,"")</f>
         <v/>
       </c>
       <c r="N31" s="5" t="n"/>
       <c r="O31" s="5">
-        <f>IF(AND(ISNUMBER(N31),ISNUMBER(N32)),(N31/N32-1)*100,"")</f>
+        <f>IF(COUNT(N31:N32)=2,(N31/N32-1)*100,"")</f>
         <v/>
       </c>
       <c r="P31" s="5" t="n"/>
       <c r="Q31" s="5">
-        <f>IF(AND(ISNUMBER(P31),ISNUMBER(P32)),(P31/P32-1)*100,"")</f>
+        <f>IF(COUNT(P31:P32)=2,(P31/P32-1)*100,"")</f>
         <v/>
       </c>
       <c r="R31" s="5" t="n"/>
       <c r="S31" s="5">
-        <f>IF(AND(ISNUMBER(R31),ISNUMBER(R32)),(R31/R32-1)*100,"")</f>
+        <f>IF(COUNT(R31:R32)=2,(R31/R32-1)*100,"")</f>
         <v/>
       </c>
       <c r="T31" s="5" t="n"/>
       <c r="U31" s="5">
-        <f>IF(AND(ISNUMBER(T31),ISNUMBER(T32)),(T31/T32-1)*100,"")</f>
+        <f>IF(COUNT(T31:T32)=2,(T31/T32-1)*100,"")</f>
         <v/>
       </c>
       <c r="V31" s="5" t="n"/>
@@ -3597,31 +3674,31 @@
         <v/>
       </c>
       <c r="X31" s="5">
+        <f>IF(AND(K31&lt;0,M31&gt;0),C30,"")</f>
+        <v/>
+      </c>
+      <c r="Y31" s="5">
         <f>IF(AND(G31&gt;0,I31&lt;0,K31&gt;0),C30,"")</f>
         <v/>
       </c>
-      <c r="Y31" s="5">
-        <f>IF(AND(K31&lt;0,M31&gt;0),C30,"")</f>
-        <v/>
-      </c>
       <c r="Z31" s="5">
-        <f>IF(AND(ISNUMBER(W31),0.549579&gt;=MAX(IF(ISNUMBER(X31),0.299732,-1),IF(ISNUMBER(Y31),0.323835,-1))),W31,IF(AND(ISNUMBER(X31),0.299732&gt;MAX(IF(ISNUMBER(W31),0.549579,-1),IF(ISNUMBER(Y31),0.323835,-1))),X31,IF(AND(ISNUMBER(Y31),0.323835&gt;MAX(IF(ISNUMBER(W31),0.549579,-1),IF(ISNUMBER(X31),0.299732,-1))),Y31,"")))</f>
+        <f>IF(W31&lt;&gt;"",W31,IF(X31&lt;&gt;"",X31,Y31))</f>
         <v/>
       </c>
       <c r="AA31" s="5">
+        <f>IF(AND(S31&gt;0,U31&lt;0),E30,"")</f>
+        <v/>
+      </c>
+      <c r="AB31" s="5">
         <f>IF(AND(O31&lt;=-1,E31&lt;0),E30,"")</f>
         <v/>
       </c>
-      <c r="AB31" s="5">
+      <c r="AC31" s="5">
         <f>IF(AND(Q31&gt;0,S31&gt;0),E30,"")</f>
         <v/>
       </c>
-      <c r="AC31" s="5">
-        <f>IF(AND(S31&gt;0,U31&lt;0),E30,"")</f>
-        <v/>
-      </c>
       <c r="AD31" s="5">
-        <f>IF(AND(ISNUMBER(AA31),0.408167&gt;=MAX(IF(ISNUMBER(AB31),0.31868,-1),IF(ISNUMBER(AC31),0.510996,-1))),AA31,IF(AND(ISNUMBER(AB31),0.31868&gt;MAX(IF(ISNUMBER(AA31),0.408167,-1),IF(ISNUMBER(AC31),0.510996,-1))),AB31,IF(AND(ISNUMBER(AC31),0.510996&gt;MAX(IF(ISNUMBER(AA31),0.408167,-1),IF(ISNUMBER(AB31),0.31868,-1))),AC31,"")))</f>
+        <f>IF(AA31&lt;&gt;"",AA31,IF(AB31&lt;&gt;"",AB31,AC31))</f>
         <v/>
       </c>
     </row>
@@ -3635,62 +3712,62 @@
         <v>165.43</v>
       </c>
       <c r="C32" s="5">
-        <f>IF(AND(ISNUMBER(B32),ISNUMBER(B33)),(B32/B33-1)*100,"")</f>
+        <f>IF(COUNT(B32:B33)=2,(B32/B33-1)*100,"")</f>
         <v/>
       </c>
       <c r="D32" s="5" t="n">
         <v>66.78</v>
       </c>
       <c r="E32" s="5">
-        <f>IF(AND(ISNUMBER(D32),ISNUMBER(D33)),(D32/D33-1)*100,"")</f>
+        <f>IF(COUNT(D32:D33)=2,(D32/D33-1)*100,"")</f>
         <v/>
       </c>
       <c r="F32" s="5" t="n">
         <v>79.3647</v>
       </c>
       <c r="G32" s="5">
-        <f>IF(AND(ISNUMBER(F32),ISNUMBER(F33)),(F32/F33-1)*100,"")</f>
+        <f>IF(COUNT(F32:F33)=2,(F32/F33-1)*100,"")</f>
         <v/>
       </c>
       <c r="H32" s="5" t="n">
         <v>55.54</v>
       </c>
       <c r="I32" s="5">
-        <f>IF(AND(ISNUMBER(H32),ISNUMBER(H33)),(H32/H33-1)*100,"")</f>
+        <f>IF(COUNT(H32:H33)=2,(H32/H33-1)*100,"")</f>
         <v/>
       </c>
       <c r="J32" s="5" t="n">
         <v>75.78</v>
       </c>
       <c r="K32" s="5">
-        <f>IF(AND(ISNUMBER(J32),ISNUMBER(J33)),(J32/J33-1)*100,"")</f>
+        <f>IF(COUNT(J32:J33)=2,(J32/J33-1)*100,"")</f>
         <v/>
       </c>
       <c r="L32" s="5" t="n">
         <v>-6.2722</v>
       </c>
       <c r="M32" s="5">
-        <f>IF(AND(ISNUMBER(L32),ISNUMBER(L33)),(L32/L33-1)*100,"")</f>
+        <f>IF(COUNT(L32:L33)=2,(L32/L33-1)*100,"")</f>
         <v/>
       </c>
       <c r="N32" s="5" t="n"/>
       <c r="O32" s="5">
-        <f>IF(AND(ISNUMBER(N32),ISNUMBER(N33)),(N32/N33-1)*100,"")</f>
+        <f>IF(COUNT(N32:N33)=2,(N32/N33-1)*100,"")</f>
         <v/>
       </c>
       <c r="P32" s="5" t="n"/>
       <c r="Q32" s="5">
-        <f>IF(AND(ISNUMBER(P32),ISNUMBER(P33)),(P32/P33-1)*100,"")</f>
+        <f>IF(COUNT(P32:P33)=2,(P32/P33-1)*100,"")</f>
         <v/>
       </c>
       <c r="R32" s="5" t="n"/>
       <c r="S32" s="5">
-        <f>IF(AND(ISNUMBER(R32),ISNUMBER(R33)),(R32/R33-1)*100,"")</f>
+        <f>IF(COUNT(R32:R33)=2,(R32/R33-1)*100,"")</f>
         <v/>
       </c>
       <c r="T32" s="5" t="n"/>
       <c r="U32" s="5">
-        <f>IF(AND(ISNUMBER(T32),ISNUMBER(T33)),(T32/T33-1)*100,"")</f>
+        <f>IF(COUNT(T32:T33)=2,(T32/T33-1)*100,"")</f>
         <v/>
       </c>
       <c r="V32" s="5" t="n"/>
@@ -3699,31 +3776,31 @@
         <v/>
       </c>
       <c r="X32" s="5">
+        <f>IF(AND(K32&lt;0,M32&gt;0),C31,"")</f>
+        <v/>
+      </c>
+      <c r="Y32" s="5">
         <f>IF(AND(G32&gt;0,I32&lt;0,K32&gt;0),C31,"")</f>
         <v/>
       </c>
-      <c r="Y32" s="5">
-        <f>IF(AND(K32&lt;0,M32&gt;0),C31,"")</f>
-        <v/>
-      </c>
       <c r="Z32" s="5">
-        <f>IF(AND(ISNUMBER(W32),0.549579&gt;=MAX(IF(ISNUMBER(X32),0.299732,-1),IF(ISNUMBER(Y32),0.323835,-1))),W32,IF(AND(ISNUMBER(X32),0.299732&gt;MAX(IF(ISNUMBER(W32),0.549579,-1),IF(ISNUMBER(Y32),0.323835,-1))),X32,IF(AND(ISNUMBER(Y32),0.323835&gt;MAX(IF(ISNUMBER(W32),0.549579,-1),IF(ISNUMBER(X32),0.299732,-1))),Y32,"")))</f>
+        <f>IF(W32&lt;&gt;"",W32,IF(X32&lt;&gt;"",X32,Y32))</f>
         <v/>
       </c>
       <c r="AA32" s="5">
+        <f>IF(AND(S32&gt;0,U32&lt;0),E31,"")</f>
+        <v/>
+      </c>
+      <c r="AB32" s="5">
         <f>IF(AND(O32&lt;=-1,E32&lt;0),E31,"")</f>
         <v/>
       </c>
-      <c r="AB32" s="5">
+      <c r="AC32" s="5">
         <f>IF(AND(Q32&gt;0,S32&gt;0),E31,"")</f>
         <v/>
       </c>
-      <c r="AC32" s="5">
-        <f>IF(AND(S32&gt;0,U32&lt;0),E31,"")</f>
-        <v/>
-      </c>
       <c r="AD32" s="5">
-        <f>IF(AND(ISNUMBER(AA32),0.408167&gt;=MAX(IF(ISNUMBER(AB32),0.31868,-1),IF(ISNUMBER(AC32),0.510996,-1))),AA32,IF(AND(ISNUMBER(AB32),0.31868&gt;MAX(IF(ISNUMBER(AA32),0.408167,-1),IF(ISNUMBER(AC32),0.510996,-1))),AB32,IF(AND(ISNUMBER(AC32),0.510996&gt;MAX(IF(ISNUMBER(AA32),0.408167,-1),IF(ISNUMBER(AB32),0.31868,-1))),AC32,"")))</f>
+        <f>IF(AA32&lt;&gt;"",AA32,IF(AB32&lt;&gt;"",AB32,AC32))</f>
         <v/>
       </c>
     </row>
@@ -3737,62 +3814,62 @@
         <v>160.25</v>
       </c>
       <c r="C33" s="5">
-        <f>IF(AND(ISNUMBER(B33),ISNUMBER(B34)),(B33/B34-1)*100,"")</f>
+        <f>IF(COUNT(B33:B34)=2,(B33/B34-1)*100,"")</f>
         <v/>
       </c>
       <c r="D33" s="5" t="n">
         <v>66.23</v>
       </c>
       <c r="E33" s="5">
-        <f>IF(AND(ISNUMBER(D33),ISNUMBER(D34)),(D33/D34-1)*100,"")</f>
+        <f>IF(COUNT(D33:D34)=2,(D33/D34-1)*100,"")</f>
         <v/>
       </c>
       <c r="F33" s="5" t="n">
         <v>79.27509999999999</v>
       </c>
       <c r="G33" s="5">
-        <f>IF(AND(ISNUMBER(F33),ISNUMBER(F34)),(F33/F34-1)*100,"")</f>
+        <f>IF(COUNT(F33:F34)=2,(F33/F34-1)*100,"")</f>
         <v/>
       </c>
       <c r="H33" s="5" t="n">
         <v>54.97</v>
       </c>
       <c r="I33" s="5">
-        <f>IF(AND(ISNUMBER(H33),ISNUMBER(H34)),(H33/H34-1)*100,"")</f>
+        <f>IF(COUNT(H33:H34)=2,(H33/H34-1)*100,"")</f>
         <v/>
       </c>
       <c r="J33" s="5" t="n">
         <v>73.53</v>
       </c>
       <c r="K33" s="5">
-        <f>IF(AND(ISNUMBER(J33),ISNUMBER(J34)),(J33/J34-1)*100,"")</f>
+        <f>IF(COUNT(J33:J34)=2,(J33/J34-1)*100,"")</f>
         <v/>
       </c>
       <c r="L33" s="5" t="n">
         <v>4.7737</v>
       </c>
       <c r="M33" s="5">
-        <f>IF(AND(ISNUMBER(L33),ISNUMBER(L34)),(L33/L34-1)*100,"")</f>
+        <f>IF(COUNT(L33:L34)=2,(L33/L34-1)*100,"")</f>
         <v/>
       </c>
       <c r="N33" s="5" t="n"/>
       <c r="O33" s="5">
-        <f>IF(AND(ISNUMBER(N33),ISNUMBER(N34)),(N33/N34-1)*100,"")</f>
+        <f>IF(COUNT(N33:N34)=2,(N33/N34-1)*100,"")</f>
         <v/>
       </c>
       <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5">
-        <f>IF(AND(ISNUMBER(P33),ISNUMBER(P34)),(P33/P34-1)*100,"")</f>
+        <f>IF(COUNT(P33:P34)=2,(P33/P34-1)*100,"")</f>
         <v/>
       </c>
       <c r="R33" s="5" t="n"/>
       <c r="S33" s="5">
-        <f>IF(AND(ISNUMBER(R33),ISNUMBER(R34)),(R33/R34-1)*100,"")</f>
+        <f>IF(COUNT(R33:R34)=2,(R33/R34-1)*100,"")</f>
         <v/>
       </c>
       <c r="T33" s="5" t="n"/>
       <c r="U33" s="5">
-        <f>IF(AND(ISNUMBER(T33),ISNUMBER(T34)),(T33/T34-1)*100,"")</f>
+        <f>IF(COUNT(T33:T34)=2,(T33/T34-1)*100,"")</f>
         <v/>
       </c>
       <c r="V33" s="5" t="n"/>
@@ -3801,31 +3878,31 @@
         <v/>
       </c>
       <c r="X33" s="5">
+        <f>IF(AND(K33&lt;0,M33&gt;0),C32,"")</f>
+        <v/>
+      </c>
+      <c r="Y33" s="5">
         <f>IF(AND(G33&gt;0,I33&lt;0,K33&gt;0),C32,"")</f>
         <v/>
       </c>
-      <c r="Y33" s="5">
-        <f>IF(AND(K33&lt;0,M33&gt;0),C32,"")</f>
-        <v/>
-      </c>
       <c r="Z33" s="5">
-        <f>IF(AND(ISNUMBER(W33),0.549579&gt;=MAX(IF(ISNUMBER(X33),0.299732,-1),IF(ISNUMBER(Y33),0.323835,-1))),W33,IF(AND(ISNUMBER(X33),0.299732&gt;MAX(IF(ISNUMBER(W33),0.549579,-1),IF(ISNUMBER(Y33),0.323835,-1))),X33,IF(AND(ISNUMBER(Y33),0.323835&gt;MAX(IF(ISNUMBER(W33),0.549579,-1),IF(ISNUMBER(X33),0.299732,-1))),Y33,"")))</f>
+        <f>IF(W33&lt;&gt;"",W33,IF(X33&lt;&gt;"",X33,Y33))</f>
         <v/>
       </c>
       <c r="AA33" s="5">
+        <f>IF(AND(S33&gt;0,U33&lt;0),E32,"")</f>
+        <v/>
+      </c>
+      <c r="AB33" s="5">
         <f>IF(AND(O33&lt;=-1,E33&lt;0),E32,"")</f>
         <v/>
       </c>
-      <c r="AB33" s="5">
+      <c r="AC33" s="5">
         <f>IF(AND(Q33&gt;0,S33&gt;0),E32,"")</f>
         <v/>
       </c>
-      <c r="AC33" s="5">
-        <f>IF(AND(S33&gt;0,U33&lt;0),E32,"")</f>
-        <v/>
-      </c>
       <c r="AD33" s="5">
-        <f>IF(AND(ISNUMBER(AA33),0.408167&gt;=MAX(IF(ISNUMBER(AB33),0.31868,-1),IF(ISNUMBER(AC33),0.510996,-1))),AA33,IF(AND(ISNUMBER(AB33),0.31868&gt;MAX(IF(ISNUMBER(AA33),0.408167,-1),IF(ISNUMBER(AC33),0.510996,-1))),AB33,IF(AND(ISNUMBER(AC33),0.510996&gt;MAX(IF(ISNUMBER(AA33),0.408167,-1),IF(ISNUMBER(AB33),0.31868,-1))),AC33,"")))</f>
+        <f>IF(AA33&lt;&gt;"",AA33,IF(AB33&lt;&gt;"",AB33,AC33))</f>
         <v/>
       </c>
     </row>
@@ -3839,62 +3916,62 @@
         <v>159.4</v>
       </c>
       <c r="C34" s="5">
-        <f>IF(AND(ISNUMBER(B34),ISNUMBER(B35)),(B34/B35-1)*100,"")</f>
+        <f>IF(COUNT(B34:B35)=2,(B34/B35-1)*100,"")</f>
         <v/>
       </c>
       <c r="D34" s="5" t="n">
         <v>65.72</v>
       </c>
       <c r="E34" s="5">
-        <f>IF(AND(ISNUMBER(D34),ISNUMBER(D35)),(D34/D35-1)*100,"")</f>
+        <f>IF(COUNT(D34:D35)=2,(D34/D35-1)*100,"")</f>
         <v/>
       </c>
       <c r="F34" s="5" t="n">
         <v>79.3746</v>
       </c>
       <c r="G34" s="5">
-        <f>IF(AND(ISNUMBER(F34),ISNUMBER(F35)),(F34/F35-1)*100,"")</f>
+        <f>IF(COUNT(F34:F35)=2,(F34/F35-1)*100,"")</f>
         <v/>
       </c>
       <c r="H34" s="5" t="n">
         <v>56.05</v>
       </c>
       <c r="I34" s="5">
-        <f>IF(AND(ISNUMBER(H34),ISNUMBER(H35)),(H34/H35-1)*100,"")</f>
+        <f>IF(COUNT(H34:H35)=2,(H34/H35-1)*100,"")</f>
         <v/>
       </c>
       <c r="J34" s="5" t="n">
         <v>75.76000000000001</v>
       </c>
       <c r="K34" s="5">
-        <f>IF(AND(ISNUMBER(J34),ISNUMBER(J35)),(J34/J35-1)*100,"")</f>
+        <f>IF(COUNT(J34:J35)=2,(J34/J35-1)*100,"")</f>
         <v/>
       </c>
       <c r="L34" s="5" t="n">
         <v>3.5967</v>
       </c>
       <c r="M34" s="5">
-        <f>IF(AND(ISNUMBER(L34),ISNUMBER(L35)),(L34/L35-1)*100,"")</f>
+        <f>IF(COUNT(L34:L35)=2,(L34/L35-1)*100,"")</f>
         <v/>
       </c>
       <c r="N34" s="5" t="n"/>
       <c r="O34" s="5">
-        <f>IF(AND(ISNUMBER(N34),ISNUMBER(N35)),(N34/N35-1)*100,"")</f>
+        <f>IF(COUNT(N34:N35)=2,(N34/N35-1)*100,"")</f>
         <v/>
       </c>
       <c r="P34" s="5" t="n"/>
       <c r="Q34" s="5">
-        <f>IF(AND(ISNUMBER(P34),ISNUMBER(P35)),(P34/P35-1)*100,"")</f>
+        <f>IF(COUNT(P34:P35)=2,(P34/P35-1)*100,"")</f>
         <v/>
       </c>
       <c r="R34" s="5" t="n"/>
       <c r="S34" s="5">
-        <f>IF(AND(ISNUMBER(R34),ISNUMBER(R35)),(R34/R35-1)*100,"")</f>
+        <f>IF(COUNT(R34:R35)=2,(R34/R35-1)*100,"")</f>
         <v/>
       </c>
       <c r="T34" s="5" t="n"/>
       <c r="U34" s="5">
-        <f>IF(AND(ISNUMBER(T34),ISNUMBER(T35)),(T34/T35-1)*100,"")</f>
+        <f>IF(COUNT(T34:T35)=2,(T34/T35-1)*100,"")</f>
         <v/>
       </c>
       <c r="V34" s="5" t="n"/>
@@ -3903,31 +3980,31 @@
         <v/>
       </c>
       <c r="X34" s="5">
+        <f>IF(AND(K34&lt;0,M34&gt;0),C33,"")</f>
+        <v/>
+      </c>
+      <c r="Y34" s="5">
         <f>IF(AND(G34&gt;0,I34&lt;0,K34&gt;0),C33,"")</f>
         <v/>
       </c>
-      <c r="Y34" s="5">
-        <f>IF(AND(K34&lt;0,M34&gt;0),C33,"")</f>
-        <v/>
-      </c>
       <c r="Z34" s="5">
-        <f>IF(AND(ISNUMBER(W34),0.549579&gt;=MAX(IF(ISNUMBER(X34),0.299732,-1),IF(ISNUMBER(Y34),0.323835,-1))),W34,IF(AND(ISNUMBER(X34),0.299732&gt;MAX(IF(ISNUMBER(W34),0.549579,-1),IF(ISNUMBER(Y34),0.323835,-1))),X34,IF(AND(ISNUMBER(Y34),0.323835&gt;MAX(IF(ISNUMBER(W34),0.549579,-1),IF(ISNUMBER(X34),0.299732,-1))),Y34,"")))</f>
+        <f>IF(W34&lt;&gt;"",W34,IF(X34&lt;&gt;"",X34,Y34))</f>
         <v/>
       </c>
       <c r="AA34" s="5">
+        <f>IF(AND(S34&gt;0,U34&lt;0),E33,"")</f>
+        <v/>
+      </c>
+      <c r="AB34" s="5">
         <f>IF(AND(O34&lt;=-1,E34&lt;0),E33,"")</f>
         <v/>
       </c>
-      <c r="AB34" s="5">
+      <c r="AC34" s="5">
         <f>IF(AND(Q34&gt;0,S34&gt;0),E33,"")</f>
         <v/>
       </c>
-      <c r="AC34" s="5">
-        <f>IF(AND(S34&gt;0,U34&lt;0),E33,"")</f>
-        <v/>
-      </c>
       <c r="AD34" s="5">
-        <f>IF(AND(ISNUMBER(AA34),0.408167&gt;=MAX(IF(ISNUMBER(AB34),0.31868,-1),IF(ISNUMBER(AC34),0.510996,-1))),AA34,IF(AND(ISNUMBER(AB34),0.31868&gt;MAX(IF(ISNUMBER(AA34),0.408167,-1),IF(ISNUMBER(AC34),0.510996,-1))),AB34,IF(AND(ISNUMBER(AC34),0.510996&gt;MAX(IF(ISNUMBER(AA34),0.408167,-1),IF(ISNUMBER(AB34),0.31868,-1))),AC34,"")))</f>
+        <f>IF(AA34&lt;&gt;"",AA34,IF(AB34&lt;&gt;"",AB34,AC34))</f>
         <v/>
       </c>
     </row>
@@ -3941,62 +4018,62 @@
         <v>165.32</v>
       </c>
       <c r="C35" s="5">
-        <f>IF(AND(ISNUMBER(B35),ISNUMBER(B36)),(B35/B36-1)*100,"")</f>
+        <f>IF(COUNT(B35:B36)=2,(B35/B36-1)*100,"")</f>
         <v/>
       </c>
       <c r="D35" s="5" t="n">
         <v>67.56999999999999</v>
       </c>
       <c r="E35" s="5">
-        <f>IF(AND(ISNUMBER(D35),ISNUMBER(D36)),(D35/D36-1)*100,"")</f>
+        <f>IF(COUNT(D35:D36)=2,(D35/D36-1)*100,"")</f>
         <v/>
       </c>
       <c r="F35" s="5" t="n">
         <v>79.4841</v>
       </c>
       <c r="G35" s="5">
-        <f>IF(AND(ISNUMBER(F35),ISNUMBER(F36)),(F35/F36-1)*100,"")</f>
+        <f>IF(COUNT(F35:F36)=2,(F35/F36-1)*100,"")</f>
         <v/>
       </c>
       <c r="H35" s="5" t="n">
         <v>56.14</v>
       </c>
       <c r="I35" s="5">
-        <f>IF(AND(ISNUMBER(H35),ISNUMBER(H36)),(H35/H36-1)*100,"")</f>
+        <f>IF(COUNT(H35:H36)=2,(H35/H36-1)*100,"")</f>
         <v/>
       </c>
       <c r="J35" s="5" t="n">
         <v>78.73999999999999</v>
       </c>
       <c r="K35" s="5">
-        <f>IF(AND(ISNUMBER(J35),ISNUMBER(J36)),(J35/J36-1)*100,"")</f>
+        <f>IF(COUNT(J35:J36)=2,(J35/J36-1)*100,"")</f>
         <v/>
       </c>
       <c r="L35" s="5" t="n">
         <v>-3.5913</v>
       </c>
       <c r="M35" s="5">
-        <f>IF(AND(ISNUMBER(L35),ISNUMBER(L36)),(L35/L36-1)*100,"")</f>
+        <f>IF(COUNT(L35:L36)=2,(L35/L36-1)*100,"")</f>
         <v/>
       </c>
       <c r="N35" s="5" t="n"/>
       <c r="O35" s="5">
-        <f>IF(AND(ISNUMBER(N35),ISNUMBER(N36)),(N35/N36-1)*100,"")</f>
+        <f>IF(COUNT(N35:N36)=2,(N35/N36-1)*100,"")</f>
         <v/>
       </c>
       <c r="P35" s="5" t="n"/>
       <c r="Q35" s="5">
-        <f>IF(AND(ISNUMBER(P35),ISNUMBER(P36)),(P35/P36-1)*100,"")</f>
+        <f>IF(COUNT(P35:P36)=2,(P35/P36-1)*100,"")</f>
         <v/>
       </c>
       <c r="R35" s="5" t="n"/>
       <c r="S35" s="5">
-        <f>IF(AND(ISNUMBER(R35),ISNUMBER(R36)),(R35/R36-1)*100,"")</f>
+        <f>IF(COUNT(R35:R36)=2,(R35/R36-1)*100,"")</f>
         <v/>
       </c>
       <c r="T35" s="5" t="n"/>
       <c r="U35" s="5">
-        <f>IF(AND(ISNUMBER(T35),ISNUMBER(T36)),(T35/T36-1)*100,"")</f>
+        <f>IF(COUNT(T35:T36)=2,(T35/T36-1)*100,"")</f>
         <v/>
       </c>
       <c r="V35" s="5" t="n"/>
@@ -4005,31 +4082,31 @@
         <v/>
       </c>
       <c r="X35" s="5">
+        <f>IF(AND(K35&lt;0,M35&gt;0),C34,"")</f>
+        <v/>
+      </c>
+      <c r="Y35" s="5">
         <f>IF(AND(G35&gt;0,I35&lt;0,K35&gt;0),C34,"")</f>
         <v/>
       </c>
-      <c r="Y35" s="5">
-        <f>IF(AND(K35&lt;0,M35&gt;0),C34,"")</f>
-        <v/>
-      </c>
       <c r="Z35" s="5">
-        <f>IF(AND(ISNUMBER(W35),0.549579&gt;=MAX(IF(ISNUMBER(X35),0.299732,-1),IF(ISNUMBER(Y35),0.323835,-1))),W35,IF(AND(ISNUMBER(X35),0.299732&gt;MAX(IF(ISNUMBER(W35),0.549579,-1),IF(ISNUMBER(Y35),0.323835,-1))),X35,IF(AND(ISNUMBER(Y35),0.323835&gt;MAX(IF(ISNUMBER(W35),0.549579,-1),IF(ISNUMBER(X35),0.299732,-1))),Y35,"")))</f>
+        <f>IF(W35&lt;&gt;"",W35,IF(X35&lt;&gt;"",X35,Y35))</f>
         <v/>
       </c>
       <c r="AA35" s="5">
+        <f>IF(AND(S35&gt;0,U35&lt;0),E34,"")</f>
+        <v/>
+      </c>
+      <c r="AB35" s="5">
         <f>IF(AND(O35&lt;=-1,E35&lt;0),E34,"")</f>
         <v/>
       </c>
-      <c r="AB35" s="5">
+      <c r="AC35" s="5">
         <f>IF(AND(Q35&gt;0,S35&gt;0),E34,"")</f>
         <v/>
       </c>
-      <c r="AC35" s="5">
-        <f>IF(AND(S35&gt;0,U35&lt;0),E34,"")</f>
-        <v/>
-      </c>
       <c r="AD35" s="5">
-        <f>IF(AND(ISNUMBER(AA35),0.408167&gt;=MAX(IF(ISNUMBER(AB35),0.31868,-1),IF(ISNUMBER(AC35),0.510996,-1))),AA35,IF(AND(ISNUMBER(AB35),0.31868&gt;MAX(IF(ISNUMBER(AA35),0.408167,-1),IF(ISNUMBER(AC35),0.510996,-1))),AB35,IF(AND(ISNUMBER(AC35),0.510996&gt;MAX(IF(ISNUMBER(AA35),0.408167,-1),IF(ISNUMBER(AB35),0.31868,-1))),AC35,"")))</f>
+        <f>IF(AA35&lt;&gt;"",AA35,IF(AB35&lt;&gt;"",AB35,AC35))</f>
         <v/>
       </c>
     </row>
@@ -4043,62 +4120,62 @@
         <v>161.26</v>
       </c>
       <c r="C36" s="5">
-        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37)),(B36/B37-1)*100,"")</f>
+        <f>IF(COUNT(B36:B37)=2,(B36/B37-1)*100,"")</f>
         <v/>
       </c>
       <c r="D36" s="5" t="n">
         <v>65.7</v>
       </c>
       <c r="E36" s="5">
-        <f>IF(AND(ISNUMBER(D36),ISNUMBER(D37)),(D36/D37-1)*100,"")</f>
+        <f>IF(COUNT(D36:D37)=2,(D36/D37-1)*100,"")</f>
         <v/>
       </c>
       <c r="F36" s="5" t="n">
         <v>79.3249</v>
       </c>
       <c r="G36" s="5">
-        <f>IF(AND(ISNUMBER(F36),ISNUMBER(F37)),(F36/F37-1)*100,"")</f>
+        <f>IF(COUNT(F36:F37)=2,(F36/F37-1)*100,"")</f>
         <v/>
       </c>
       <c r="H36" s="5" t="n">
         <v>55.62</v>
       </c>
       <c r="I36" s="5">
-        <f>IF(AND(ISNUMBER(H36),ISNUMBER(H37)),(H36/H37-1)*100,"")</f>
+        <f>IF(COUNT(H36:H37)=2,(H36/H37-1)*100,"")</f>
         <v/>
       </c>
       <c r="J36" s="5" t="n">
         <v>78.43000000000001</v>
       </c>
       <c r="K36" s="5">
-        <f>IF(AND(ISNUMBER(J36),ISNUMBER(J37)),(J36/J37-1)*100,"")</f>
+        <f>IF(COUNT(J36:J37)=2,(J36/J37-1)*100,"")</f>
         <v/>
       </c>
       <c r="L36" s="5" t="n">
         <v>-2.6522</v>
       </c>
       <c r="M36" s="5">
-        <f>IF(AND(ISNUMBER(L36),ISNUMBER(L37)),(L36/L37-1)*100,"")</f>
+        <f>IF(COUNT(L36:L37)=2,(L36/L37-1)*100,"")</f>
         <v/>
       </c>
       <c r="N36" s="5" t="n"/>
       <c r="O36" s="5">
-        <f>IF(AND(ISNUMBER(N36),ISNUMBER(N37)),(N36/N37-1)*100,"")</f>
+        <f>IF(COUNT(N36:N37)=2,(N36/N37-1)*100,"")</f>
         <v/>
       </c>
       <c r="P36" s="5" t="n"/>
       <c r="Q36" s="5">
-        <f>IF(AND(ISNUMBER(P36),ISNUMBER(P37)),(P36/P37-1)*100,"")</f>
+        <f>IF(COUNT(P36:P37)=2,(P36/P37-1)*100,"")</f>
         <v/>
       </c>
       <c r="R36" s="5" t="n"/>
       <c r="S36" s="5">
-        <f>IF(AND(ISNUMBER(R36),ISNUMBER(R37)),(R36/R37-1)*100,"")</f>
+        <f>IF(COUNT(R36:R37)=2,(R36/R37-1)*100,"")</f>
         <v/>
       </c>
       <c r="T36" s="5" t="n"/>
       <c r="U36" s="5">
-        <f>IF(AND(ISNUMBER(T36),ISNUMBER(T37)),(T36/T37-1)*100,"")</f>
+        <f>IF(COUNT(T36:T37)=2,(T36/T37-1)*100,"")</f>
         <v/>
       </c>
       <c r="V36" s="5" t="n"/>
@@ -4107,31 +4184,31 @@
         <v/>
       </c>
       <c r="X36" s="5">
+        <f>IF(AND(K36&lt;0,M36&gt;0),C35,"")</f>
+        <v/>
+      </c>
+      <c r="Y36" s="5">
         <f>IF(AND(G36&gt;0,I36&lt;0,K36&gt;0),C35,"")</f>
         <v/>
       </c>
-      <c r="Y36" s="5">
-        <f>IF(AND(K36&lt;0,M36&gt;0),C35,"")</f>
-        <v/>
-      </c>
       <c r="Z36" s="5">
-        <f>IF(AND(ISNUMBER(W36),0.549579&gt;=MAX(IF(ISNUMBER(X36),0.299732,-1),IF(ISNUMBER(Y36),0.323835,-1))),W36,IF(AND(ISNUMBER(X36),0.299732&gt;MAX(IF(ISNUMBER(W36),0.549579,-1),IF(ISNUMBER(Y36),0.323835,-1))),X36,IF(AND(ISNUMBER(Y36),0.323835&gt;MAX(IF(ISNUMBER(W36),0.549579,-1),IF(ISNUMBER(X36),0.299732,-1))),Y36,"")))</f>
+        <f>IF(W36&lt;&gt;"",W36,IF(X36&lt;&gt;"",X36,Y36))</f>
         <v/>
       </c>
       <c r="AA36" s="5">
+        <f>IF(AND(S36&gt;0,U36&lt;0),E35,"")</f>
+        <v/>
+      </c>
+      <c r="AB36" s="5">
         <f>IF(AND(O36&lt;=-1,E36&lt;0),E35,"")</f>
         <v/>
       </c>
-      <c r="AB36" s="5">
+      <c r="AC36" s="5">
         <f>IF(AND(Q36&gt;0,S36&gt;0),E35,"")</f>
         <v/>
       </c>
-      <c r="AC36" s="5">
-        <f>IF(AND(S36&gt;0,U36&lt;0),E35,"")</f>
-        <v/>
-      </c>
       <c r="AD36" s="5">
-        <f>IF(AND(ISNUMBER(AA36),0.408167&gt;=MAX(IF(ISNUMBER(AB36),0.31868,-1),IF(ISNUMBER(AC36),0.510996,-1))),AA36,IF(AND(ISNUMBER(AB36),0.31868&gt;MAX(IF(ISNUMBER(AA36),0.408167,-1),IF(ISNUMBER(AC36),0.510996,-1))),AB36,IF(AND(ISNUMBER(AC36),0.510996&gt;MAX(IF(ISNUMBER(AA36),0.408167,-1),IF(ISNUMBER(AB36),0.31868,-1))),AC36,"")))</f>
+        <f>IF(AA36&lt;&gt;"",AA36,IF(AB36&lt;&gt;"",AB36,AC36))</f>
         <v/>
       </c>
     </row>
@@ -4145,62 +4222,62 @@
         <v>166.74</v>
       </c>
       <c r="C37" s="5">
-        <f>IF(AND(ISNUMBER(B37),ISNUMBER(B38)),(B37/B38-1)*100,"")</f>
+        <f>IF(COUNT(B37:B38)=2,(B37/B38-1)*100,"")</f>
         <v/>
       </c>
       <c r="D37" s="5" t="n">
         <v>66.48</v>
       </c>
       <c r="E37" s="5">
-        <f>IF(AND(ISNUMBER(D37),ISNUMBER(D38)),(D37/D38-1)*100,"")</f>
+        <f>IF(COUNT(D37:D38)=2,(D37/D38-1)*100,"")</f>
         <v/>
       </c>
       <c r="F37" s="5" t="n">
         <v>79.2055</v>
       </c>
       <c r="G37" s="5">
-        <f>IF(AND(ISNUMBER(F37),ISNUMBER(F38)),(F37/F38-1)*100,"")</f>
+        <f>IF(COUNT(F37:F38)=2,(F37/F38-1)*100,"")</f>
         <v/>
       </c>
       <c r="H37" s="5" t="n">
         <v>54.78</v>
       </c>
       <c r="I37" s="5">
-        <f>IF(AND(ISNUMBER(H37),ISNUMBER(H38)),(H37/H38-1)*100,"")</f>
+        <f>IF(COUNT(H37:H38)=2,(H37/H38-1)*100,"")</f>
         <v/>
       </c>
       <c r="J37" s="5" t="n">
         <v>75.06999999999999</v>
       </c>
       <c r="K37" s="5">
-        <f>IF(AND(ISNUMBER(J37),ISNUMBER(J38)),(J37/J38-1)*100,"")</f>
+        <f>IF(COUNT(J37:J38)=2,(J37/J38-1)*100,"")</f>
         <v/>
       </c>
       <c r="L37" s="5" t="n">
         <v>0.8511</v>
       </c>
       <c r="M37" s="5">
-        <f>IF(AND(ISNUMBER(L37),ISNUMBER(L38)),(L37/L38-1)*100,"")</f>
+        <f>IF(COUNT(L37:L38)=2,(L37/L38-1)*100,"")</f>
         <v/>
       </c>
       <c r="N37" s="5" t="n"/>
       <c r="O37" s="5">
-        <f>IF(AND(ISNUMBER(N37),ISNUMBER(N38)),(N37/N38-1)*100,"")</f>
+        <f>IF(COUNT(N37:N38)=2,(N37/N38-1)*100,"")</f>
         <v/>
       </c>
       <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5">
-        <f>IF(AND(ISNUMBER(P37),ISNUMBER(P38)),(P37/P38-1)*100,"")</f>
+        <f>IF(COUNT(P37:P38)=2,(P37/P38-1)*100,"")</f>
         <v/>
       </c>
       <c r="R37" s="5" t="n"/>
       <c r="S37" s="5">
-        <f>IF(AND(ISNUMBER(R37),ISNUMBER(R38)),(R37/R38-1)*100,"")</f>
+        <f>IF(COUNT(R37:R38)=2,(R37/R38-1)*100,"")</f>
         <v/>
       </c>
       <c r="T37" s="5" t="n"/>
       <c r="U37" s="5">
-        <f>IF(AND(ISNUMBER(T37),ISNUMBER(T38)),(T37/T38-1)*100,"")</f>
+        <f>IF(COUNT(T37:T38)=2,(T37/T38-1)*100,"")</f>
         <v/>
       </c>
       <c r="V37" s="5" t="n"/>
@@ -4209,31 +4286,31 @@
         <v/>
       </c>
       <c r="X37" s="5">
+        <f>IF(AND(K37&lt;0,M37&gt;0),C36,"")</f>
+        <v/>
+      </c>
+      <c r="Y37" s="5">
         <f>IF(AND(G37&gt;0,I37&lt;0,K37&gt;0),C36,"")</f>
         <v/>
       </c>
-      <c r="Y37" s="5">
-        <f>IF(AND(K37&lt;0,M37&gt;0),C36,"")</f>
-        <v/>
-      </c>
       <c r="Z37" s="5">
-        <f>IF(AND(ISNUMBER(W37),0.549579&gt;=MAX(IF(ISNUMBER(X37),0.299732,-1),IF(ISNUMBER(Y37),0.323835,-1))),W37,IF(AND(ISNUMBER(X37),0.299732&gt;MAX(IF(ISNUMBER(W37),0.549579,-1),IF(ISNUMBER(Y37),0.323835,-1))),X37,IF(AND(ISNUMBER(Y37),0.323835&gt;MAX(IF(ISNUMBER(W37),0.549579,-1),IF(ISNUMBER(X37),0.299732,-1))),Y37,"")))</f>
+        <f>IF(W37&lt;&gt;"",W37,IF(X37&lt;&gt;"",X37,Y37))</f>
         <v/>
       </c>
       <c r="AA37" s="5">
+        <f>IF(AND(S37&gt;0,U37&lt;0),E36,"")</f>
+        <v/>
+      </c>
+      <c r="AB37" s="5">
         <f>IF(AND(O37&lt;=-1,E37&lt;0),E36,"")</f>
         <v/>
       </c>
-      <c r="AB37" s="5">
+      <c r="AC37" s="5">
         <f>IF(AND(Q37&gt;0,S37&gt;0),E36,"")</f>
         <v/>
       </c>
-      <c r="AC37" s="5">
-        <f>IF(AND(S37&gt;0,U37&lt;0),E36,"")</f>
-        <v/>
-      </c>
       <c r="AD37" s="5">
-        <f>IF(AND(ISNUMBER(AA37),0.408167&gt;=MAX(IF(ISNUMBER(AB37),0.31868,-1),IF(ISNUMBER(AC37),0.510996,-1))),AA37,IF(AND(ISNUMBER(AB37),0.31868&gt;MAX(IF(ISNUMBER(AA37),0.408167,-1),IF(ISNUMBER(AC37),0.510996,-1))),AB37,IF(AND(ISNUMBER(AC37),0.510996&gt;MAX(IF(ISNUMBER(AA37),0.408167,-1),IF(ISNUMBER(AB37),0.31868,-1))),AC37,"")))</f>
+        <f>IF(AA37&lt;&gt;"",AA37,IF(AB37&lt;&gt;"",AB37,AC37))</f>
         <v/>
       </c>
     </row>
@@ -4247,62 +4324,62 @@
         <v>172.04</v>
       </c>
       <c r="C38" s="5">
-        <f>IF(AND(ISNUMBER(B38),ISNUMBER(B39)),(B38/B39-1)*100,"")</f>
+        <f>IF(COUNT(B38:B39)=2,(B38/B39-1)*100,"")</f>
         <v/>
       </c>
       <c r="D38" s="5" t="n">
         <v>68.41</v>
       </c>
       <c r="E38" s="5">
-        <f>IF(AND(ISNUMBER(D38),ISNUMBER(D39)),(D38/D39-1)*100,"")</f>
+        <f>IF(COUNT(D38:D39)=2,(D38/D39-1)*100,"")</f>
         <v/>
       </c>
       <c r="F38" s="5" t="n">
         <v>79.21639999999999</v>
       </c>
       <c r="G38" s="5">
-        <f>IF(AND(ISNUMBER(F38),ISNUMBER(F39)),(F38/F39-1)*100,"")</f>
+        <f>IF(COUNT(F38:F39)=2,(F38/F39-1)*100,"")</f>
         <v/>
       </c>
       <c r="H38" s="5" t="n">
         <v>53.61</v>
       </c>
       <c r="I38" s="5">
-        <f>IF(AND(ISNUMBER(H38),ISNUMBER(H39)),(H38/H39-1)*100,"")</f>
+        <f>IF(COUNT(H38:H39)=2,(H38/H39-1)*100,"")</f>
         <v/>
       </c>
       <c r="J38" s="5" t="n">
         <v>75.45</v>
       </c>
       <c r="K38" s="5">
-        <f>IF(AND(ISNUMBER(J38),ISNUMBER(J39)),(J38/J39-1)*100,"")</f>
+        <f>IF(COUNT(J38:J39)=2,(J38/J39-1)*100,"")</f>
         <v/>
       </c>
       <c r="L38" s="5" t="n">
         <v>-6.7989</v>
       </c>
       <c r="M38" s="5">
-        <f>IF(AND(ISNUMBER(L38),ISNUMBER(L39)),(L38/L39-1)*100,"")</f>
+        <f>IF(COUNT(L38:L39)=2,(L38/L39-1)*100,"")</f>
         <v/>
       </c>
       <c r="N38" s="5" t="n"/>
       <c r="O38" s="5">
-        <f>IF(AND(ISNUMBER(N38),ISNUMBER(N39)),(N38/N39-1)*100,"")</f>
+        <f>IF(COUNT(N38:N39)=2,(N38/N39-1)*100,"")</f>
         <v/>
       </c>
       <c r="P38" s="5" t="n"/>
       <c r="Q38" s="5">
-        <f>IF(AND(ISNUMBER(P38),ISNUMBER(P39)),(P38/P39-1)*100,"")</f>
+        <f>IF(COUNT(P38:P39)=2,(P38/P39-1)*100,"")</f>
         <v/>
       </c>
       <c r="R38" s="5" t="n"/>
       <c r="S38" s="5">
-        <f>IF(AND(ISNUMBER(R38),ISNUMBER(R39)),(R38/R39-1)*100,"")</f>
+        <f>IF(COUNT(R38:R39)=2,(R38/R39-1)*100,"")</f>
         <v/>
       </c>
       <c r="T38" s="5" t="n"/>
       <c r="U38" s="5">
-        <f>IF(AND(ISNUMBER(T38),ISNUMBER(T39)),(T38/T39-1)*100,"")</f>
+        <f>IF(COUNT(T38:T39)=2,(T38/T39-1)*100,"")</f>
         <v/>
       </c>
       <c r="V38" s="5" t="n"/>
@@ -4311,31 +4388,31 @@
         <v/>
       </c>
       <c r="X38" s="5">
+        <f>IF(AND(K38&lt;0,M38&gt;0),C37,"")</f>
+        <v/>
+      </c>
+      <c r="Y38" s="5">
         <f>IF(AND(G38&gt;0,I38&lt;0,K38&gt;0),C37,"")</f>
         <v/>
       </c>
-      <c r="Y38" s="5">
-        <f>IF(AND(K38&lt;0,M38&gt;0),C37,"")</f>
-        <v/>
-      </c>
       <c r="Z38" s="5">
-        <f>IF(AND(ISNUMBER(W38),0.549579&gt;=MAX(IF(ISNUMBER(X38),0.299732,-1),IF(ISNUMBER(Y38),0.323835,-1))),W38,IF(AND(ISNUMBER(X38),0.299732&gt;MAX(IF(ISNUMBER(W38),0.549579,-1),IF(ISNUMBER(Y38),0.323835,-1))),X38,IF(AND(ISNUMBER(Y38),0.323835&gt;MAX(IF(ISNUMBER(W38),0.549579,-1),IF(ISNUMBER(X38),0.299732,-1))),Y38,"")))</f>
+        <f>IF(W38&lt;&gt;"",W38,IF(X38&lt;&gt;"",X38,Y38))</f>
         <v/>
       </c>
       <c r="AA38" s="5">
+        <f>IF(AND(S38&gt;0,U38&lt;0),E37,"")</f>
+        <v/>
+      </c>
+      <c r="AB38" s="5">
         <f>IF(AND(O38&lt;=-1,E38&lt;0),E37,"")</f>
         <v/>
       </c>
-      <c r="AB38" s="5">
+      <c r="AC38" s="5">
         <f>IF(AND(Q38&gt;0,S38&gt;0),E37,"")</f>
         <v/>
       </c>
-      <c r="AC38" s="5">
-        <f>IF(AND(S38&gt;0,U38&lt;0),E37,"")</f>
-        <v/>
-      </c>
       <c r="AD38" s="5">
-        <f>IF(AND(ISNUMBER(AA38),0.408167&gt;=MAX(IF(ISNUMBER(AB38),0.31868,-1),IF(ISNUMBER(AC38),0.510996,-1))),AA38,IF(AND(ISNUMBER(AB38),0.31868&gt;MAX(IF(ISNUMBER(AA38),0.408167,-1),IF(ISNUMBER(AC38),0.510996,-1))),AB38,IF(AND(ISNUMBER(AC38),0.510996&gt;MAX(IF(ISNUMBER(AA38),0.408167,-1),IF(ISNUMBER(AB38),0.31868,-1))),AC38,"")))</f>
+        <f>IF(AA38&lt;&gt;"",AA38,IF(AB38&lt;&gt;"",AB38,AC38))</f>
         <v/>
       </c>
     </row>
@@ -4349,62 +4426,62 @@
         <v>166.43</v>
       </c>
       <c r="C39" s="5">
-        <f>IF(AND(ISNUMBER(B39),ISNUMBER(B40)),(B39/B40-1)*100,"")</f>
+        <f>IF(COUNT(B39:B40)=2,(B39/B40-1)*100,"")</f>
         <v/>
       </c>
       <c r="D39" s="5" t="n">
         <v>67.43000000000001</v>
       </c>
       <c r="E39" s="5">
-        <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40)),(D39/D40-1)*100,"")</f>
+        <f>IF(COUNT(D39:D40)=2,(D39/D40-1)*100,"")</f>
         <v/>
       </c>
       <c r="F39" s="5" t="n">
         <v>79.256</v>
       </c>
       <c r="G39" s="5">
-        <f>IF(AND(ISNUMBER(F39),ISNUMBER(F40)),(F39/F40-1)*100,"")</f>
+        <f>IF(COUNT(F39:F40)=2,(F39/F40-1)*100,"")</f>
         <v/>
       </c>
       <c r="H39" s="5" t="n">
         <v>53.72</v>
       </c>
       <c r="I39" s="5">
-        <f>IF(AND(ISNUMBER(H39),ISNUMBER(H40)),(H39/H40-1)*100,"")</f>
+        <f>IF(COUNT(H39:H40)=2,(H39/H40-1)*100,"")</f>
         <v/>
       </c>
       <c r="J39" s="5" t="n">
         <v>75.68000000000001</v>
       </c>
       <c r="K39" s="5">
-        <f>IF(AND(ISNUMBER(J39),ISNUMBER(J40)),(J39/J40-1)*100,"")</f>
+        <f>IF(COUNT(J39:J40)=2,(J39/J40-1)*100,"")</f>
         <v/>
       </c>
       <c r="L39" s="5" t="n">
         <v>-4.1282</v>
       </c>
       <c r="M39" s="5">
-        <f>IF(AND(ISNUMBER(L39),ISNUMBER(L40)),(L39/L40-1)*100,"")</f>
+        <f>IF(COUNT(L39:L40)=2,(L39/L40-1)*100,"")</f>
         <v/>
       </c>
       <c r="N39" s="5" t="n"/>
       <c r="O39" s="5">
-        <f>IF(AND(ISNUMBER(N39),ISNUMBER(N40)),(N39/N40-1)*100,"")</f>
+        <f>IF(COUNT(N39:N40)=2,(N39/N40-1)*100,"")</f>
         <v/>
       </c>
       <c r="P39" s="5" t="n"/>
       <c r="Q39" s="5">
-        <f>IF(AND(ISNUMBER(P39),ISNUMBER(P40)),(P39/P40-1)*100,"")</f>
+        <f>IF(COUNT(P39:P40)=2,(P39/P40-1)*100,"")</f>
         <v/>
       </c>
       <c r="R39" s="5" t="n"/>
       <c r="S39" s="5">
-        <f>IF(AND(ISNUMBER(R39),ISNUMBER(R40)),(R39/R40-1)*100,"")</f>
+        <f>IF(COUNT(R39:R40)=2,(R39/R40-1)*100,"")</f>
         <v/>
       </c>
       <c r="T39" s="5" t="n"/>
       <c r="U39" s="5">
-        <f>IF(AND(ISNUMBER(T39),ISNUMBER(T40)),(T39/T40-1)*100,"")</f>
+        <f>IF(COUNT(T39:T40)=2,(T39/T40-1)*100,"")</f>
         <v/>
       </c>
       <c r="V39" s="5" t="n"/>
@@ -4413,31 +4490,31 @@
         <v/>
       </c>
       <c r="X39" s="5">
+        <f>IF(AND(K39&lt;0,M39&gt;0),C38,"")</f>
+        <v/>
+      </c>
+      <c r="Y39" s="5">
         <f>IF(AND(G39&gt;0,I39&lt;0,K39&gt;0),C38,"")</f>
         <v/>
       </c>
-      <c r="Y39" s="5">
-        <f>IF(AND(K39&lt;0,M39&gt;0),C38,"")</f>
-        <v/>
-      </c>
       <c r="Z39" s="5">
-        <f>IF(AND(ISNUMBER(W39),0.549579&gt;=MAX(IF(ISNUMBER(X39),0.299732,-1),IF(ISNUMBER(Y39),0.323835,-1))),W39,IF(AND(ISNUMBER(X39),0.299732&gt;MAX(IF(ISNUMBER(W39),0.549579,-1),IF(ISNUMBER(Y39),0.323835,-1))),X39,IF(AND(ISNUMBER(Y39),0.323835&gt;MAX(IF(ISNUMBER(W39),0.549579,-1),IF(ISNUMBER(X39),0.299732,-1))),Y39,"")))</f>
+        <f>IF(W39&lt;&gt;"",W39,IF(X39&lt;&gt;"",X39,Y39))</f>
         <v/>
       </c>
       <c r="AA39" s="5">
+        <f>IF(AND(S39&gt;0,U39&lt;0),E38,"")</f>
+        <v/>
+      </c>
+      <c r="AB39" s="5">
         <f>IF(AND(O39&lt;=-1,E39&lt;0),E38,"")</f>
         <v/>
       </c>
-      <c r="AB39" s="5">
+      <c r="AC39" s="5">
         <f>IF(AND(Q39&gt;0,S39&gt;0),E38,"")</f>
         <v/>
       </c>
-      <c r="AC39" s="5">
-        <f>IF(AND(S39&gt;0,U39&lt;0),E38,"")</f>
-        <v/>
-      </c>
       <c r="AD39" s="5">
-        <f>IF(AND(ISNUMBER(AA39),0.408167&gt;=MAX(IF(ISNUMBER(AB39),0.31868,-1),IF(ISNUMBER(AC39),0.510996,-1))),AA39,IF(AND(ISNUMBER(AB39),0.31868&gt;MAX(IF(ISNUMBER(AA39),0.408167,-1),IF(ISNUMBER(AC39),0.510996,-1))),AB39,IF(AND(ISNUMBER(AC39),0.510996&gt;MAX(IF(ISNUMBER(AA39),0.408167,-1),IF(ISNUMBER(AB39),0.31868,-1))),AC39,"")))</f>
+        <f>IF(AA39&lt;&gt;"",AA39,IF(AB39&lt;&gt;"",AB39,AC39))</f>
         <v/>
       </c>
     </row>
@@ -4451,62 +4528,62 @@
         <v>159.19</v>
       </c>
       <c r="C40" s="5">
-        <f>IF(AND(ISNUMBER(B40),ISNUMBER(B41)),(B40/B41-1)*100,"")</f>
+        <f>IF(COUNT(B40:B41)=2,(B40/B41-1)*100,"")</f>
         <v/>
       </c>
       <c r="D40" s="5" t="n">
         <v>67.19</v>
       </c>
       <c r="E40" s="5">
-        <f>IF(AND(ISNUMBER(D40),ISNUMBER(D41)),(D40/D41-1)*100,"")</f>
+        <f>IF(COUNT(D40:D41)=2,(D40/D41-1)*100,"")</f>
         <v/>
       </c>
       <c r="F40" s="5" t="n">
         <v>79.07769999999999</v>
       </c>
       <c r="G40" s="5">
-        <f>IF(AND(ISNUMBER(F40),ISNUMBER(F41)),(F40/F41-1)*100,"")</f>
+        <f>IF(COUNT(F40:F41)=2,(F40/F41-1)*100,"")</f>
         <v/>
       </c>
       <c r="H40" s="5" t="n">
         <v>53.57</v>
       </c>
       <c r="I40" s="5">
-        <f>IF(AND(ISNUMBER(H40),ISNUMBER(H41)),(H40/H41-1)*100,"")</f>
+        <f>IF(COUNT(H40:H41)=2,(H40/H41-1)*100,"")</f>
         <v/>
       </c>
       <c r="J40" s="5" t="n">
         <v>77</v>
       </c>
       <c r="K40" s="5">
-        <f>IF(AND(ISNUMBER(J40),ISNUMBER(J41)),(J40/J41-1)*100,"")</f>
+        <f>IF(COUNT(J40:J41)=2,(J40/J41-1)*100,"")</f>
         <v/>
       </c>
       <c r="L40" s="5" t="n">
         <v>-2.541</v>
       </c>
       <c r="M40" s="5">
-        <f>IF(AND(ISNUMBER(L40),ISNUMBER(L41)),(L40/L41-1)*100,"")</f>
+        <f>IF(COUNT(L40:L41)=2,(L40/L41-1)*100,"")</f>
         <v/>
       </c>
       <c r="N40" s="5" t="n"/>
       <c r="O40" s="5">
-        <f>IF(AND(ISNUMBER(N40),ISNUMBER(N41)),(N40/N41-1)*100,"")</f>
+        <f>IF(COUNT(N40:N41)=2,(N40/N41-1)*100,"")</f>
         <v/>
       </c>
       <c r="P40" s="5" t="n"/>
       <c r="Q40" s="5">
-        <f>IF(AND(ISNUMBER(P40),ISNUMBER(P41)),(P40/P41-1)*100,"")</f>
+        <f>IF(COUNT(P40:P41)=2,(P40/P41-1)*100,"")</f>
         <v/>
       </c>
       <c r="R40" s="5" t="n"/>
       <c r="S40" s="5">
-        <f>IF(AND(ISNUMBER(R40),ISNUMBER(R41)),(R40/R41-1)*100,"")</f>
+        <f>IF(COUNT(R40:R41)=2,(R40/R41-1)*100,"")</f>
         <v/>
       </c>
       <c r="T40" s="5" t="n"/>
       <c r="U40" s="5">
-        <f>IF(AND(ISNUMBER(T40),ISNUMBER(T41)),(T40/T41-1)*100,"")</f>
+        <f>IF(COUNT(T40:T41)=2,(T40/T41-1)*100,"")</f>
         <v/>
       </c>
       <c r="V40" s="5" t="n"/>
@@ -4515,31 +4592,31 @@
         <v/>
       </c>
       <c r="X40" s="5">
+        <f>IF(AND(K40&lt;0,M40&gt;0),C39,"")</f>
+        <v/>
+      </c>
+      <c r="Y40" s="5">
         <f>IF(AND(G40&gt;0,I40&lt;0,K40&gt;0),C39,"")</f>
         <v/>
       </c>
-      <c r="Y40" s="5">
-        <f>IF(AND(K40&lt;0,M40&gt;0),C39,"")</f>
-        <v/>
-      </c>
       <c r="Z40" s="5">
-        <f>IF(AND(ISNUMBER(W40),0.549579&gt;=MAX(IF(ISNUMBER(X40),0.299732,-1),IF(ISNUMBER(Y40),0.323835,-1))),W40,IF(AND(ISNUMBER(X40),0.299732&gt;MAX(IF(ISNUMBER(W40),0.549579,-1),IF(ISNUMBER(Y40),0.323835,-1))),X40,IF(AND(ISNUMBER(Y40),0.323835&gt;MAX(IF(ISNUMBER(W40),0.549579,-1),IF(ISNUMBER(X40),0.299732,-1))),Y40,"")))</f>
+        <f>IF(W40&lt;&gt;"",W40,IF(X40&lt;&gt;"",X40,Y40))</f>
         <v/>
       </c>
       <c r="AA40" s="5">
+        <f>IF(AND(S40&gt;0,U40&lt;0),E39,"")</f>
+        <v/>
+      </c>
+      <c r="AB40" s="5">
         <f>IF(AND(O40&lt;=-1,E40&lt;0),E39,"")</f>
         <v/>
       </c>
-      <c r="AB40" s="5">
+      <c r="AC40" s="5">
         <f>IF(AND(Q40&gt;0,S40&gt;0),E39,"")</f>
         <v/>
       </c>
-      <c r="AC40" s="5">
-        <f>IF(AND(S40&gt;0,U40&lt;0),E39,"")</f>
-        <v/>
-      </c>
       <c r="AD40" s="5">
-        <f>IF(AND(ISNUMBER(AA40),0.408167&gt;=MAX(IF(ISNUMBER(AB40),0.31868,-1),IF(ISNUMBER(AC40),0.510996,-1))),AA40,IF(AND(ISNUMBER(AB40),0.31868&gt;MAX(IF(ISNUMBER(AA40),0.408167,-1),IF(ISNUMBER(AC40),0.510996,-1))),AB40,IF(AND(ISNUMBER(AC40),0.510996&gt;MAX(IF(ISNUMBER(AA40),0.408167,-1),IF(ISNUMBER(AB40),0.31868,-1))),AC40,"")))</f>
+        <f>IF(AA40&lt;&gt;"",AA40,IF(AB40&lt;&gt;"",AB40,AC40))</f>
         <v/>
       </c>
     </row>
@@ -4553,62 +4630,62 @@
         <v>162.93</v>
       </c>
       <c r="C41" s="5">
-        <f>IF(AND(ISNUMBER(B41),ISNUMBER(B42)),(B41/B42-1)*100,"")</f>
+        <f>IF(COUNT(B41:B42)=2,(B41/B42-1)*100,"")</f>
         <v/>
       </c>
       <c r="D41" s="5" t="n">
         <v>67.95999999999999</v>
       </c>
       <c r="E41" s="5">
-        <f>IF(AND(ISNUMBER(D41),ISNUMBER(D42)),(D41/D42-1)*100,"")</f>
+        <f>IF(COUNT(D41:D42)=2,(D41/D42-1)*100,"")</f>
         <v/>
       </c>
       <c r="F41" s="5" t="n">
         <v>79.12730000000001</v>
       </c>
       <c r="G41" s="5">
-        <f>IF(AND(ISNUMBER(F41),ISNUMBER(F42)),(F41/F42-1)*100,"")</f>
+        <f>IF(COUNT(F41:F42)=2,(F41/F42-1)*100,"")</f>
         <v/>
       </c>
       <c r="H41" s="5" t="n">
         <v>53.45</v>
       </c>
       <c r="I41" s="5">
-        <f>IF(AND(ISNUMBER(H41),ISNUMBER(H42)),(H41/H42-1)*100,"")</f>
+        <f>IF(COUNT(H41:H42)=2,(H41/H42-1)*100,"")</f>
         <v/>
       </c>
       <c r="J41" s="5" t="n">
         <v>75.67</v>
       </c>
       <c r="K41" s="5">
-        <f>IF(AND(ISNUMBER(J41),ISNUMBER(J42)),(J41/J42-1)*100,"")</f>
+        <f>IF(COUNT(J41:J42)=2,(J41/J42-1)*100,"")</f>
         <v/>
       </c>
       <c r="L41" s="5" t="n">
         <v>1.3956</v>
       </c>
       <c r="M41" s="5">
-        <f>IF(AND(ISNUMBER(L41),ISNUMBER(L42)),(L41/L42-1)*100,"")</f>
+        <f>IF(COUNT(L41:L42)=2,(L41/L42-1)*100,"")</f>
         <v/>
       </c>
       <c r="N41" s="5" t="n"/>
       <c r="O41" s="5">
-        <f>IF(AND(ISNUMBER(N41),ISNUMBER(N42)),(N41/N42-1)*100,"")</f>
+        <f>IF(COUNT(N41:N42)=2,(N41/N42-1)*100,"")</f>
         <v/>
       </c>
       <c r="P41" s="5" t="n"/>
       <c r="Q41" s="5">
-        <f>IF(AND(ISNUMBER(P41),ISNUMBER(P42)),(P41/P42-1)*100,"")</f>
+        <f>IF(COUNT(P41:P42)=2,(P41/P42-1)*100,"")</f>
         <v/>
       </c>
       <c r="R41" s="5" t="n"/>
       <c r="S41" s="5">
-        <f>IF(AND(ISNUMBER(R41),ISNUMBER(R42)),(R41/R42-1)*100,"")</f>
+        <f>IF(COUNT(R41:R42)=2,(R41/R42-1)*100,"")</f>
         <v/>
       </c>
       <c r="T41" s="5" t="n"/>
       <c r="U41" s="5">
-        <f>IF(AND(ISNUMBER(T41),ISNUMBER(T42)),(T41/T42-1)*100,"")</f>
+        <f>IF(COUNT(T41:T42)=2,(T41/T42-1)*100,"")</f>
         <v/>
       </c>
       <c r="V41" s="5" t="n"/>
@@ -4617,31 +4694,31 @@
         <v/>
       </c>
       <c r="X41" s="5">
+        <f>IF(AND(K41&lt;0,M41&gt;0),C40,"")</f>
+        <v/>
+      </c>
+      <c r="Y41" s="5">
         <f>IF(AND(G41&gt;0,I41&lt;0,K41&gt;0),C40,"")</f>
         <v/>
       </c>
-      <c r="Y41" s="5">
-        <f>IF(AND(K41&lt;0,M41&gt;0),C40,"")</f>
-        <v/>
-      </c>
       <c r="Z41" s="5">
-        <f>IF(AND(ISNUMBER(W41),0.549579&gt;=MAX(IF(ISNUMBER(X41),0.299732,-1),IF(ISNUMBER(Y41),0.323835,-1))),W41,IF(AND(ISNUMBER(X41),0.299732&gt;MAX(IF(ISNUMBER(W41),0.549579,-1),IF(ISNUMBER(Y41),0.323835,-1))),X41,IF(AND(ISNUMBER(Y41),0.323835&gt;MAX(IF(ISNUMBER(W41),0.549579,-1),IF(ISNUMBER(X41),0.299732,-1))),Y41,"")))</f>
+        <f>IF(W41&lt;&gt;"",W41,IF(X41&lt;&gt;"",X41,Y41))</f>
         <v/>
       </c>
       <c r="AA41" s="5">
+        <f>IF(AND(S41&gt;0,U41&lt;0),E40,"")</f>
+        <v/>
+      </c>
+      <c r="AB41" s="5">
         <f>IF(AND(O41&lt;=-1,E41&lt;0),E40,"")</f>
         <v/>
       </c>
-      <c r="AB41" s="5">
+      <c r="AC41" s="5">
         <f>IF(AND(Q41&gt;0,S41&gt;0),E40,"")</f>
         <v/>
       </c>
-      <c r="AC41" s="5">
-        <f>IF(AND(S41&gt;0,U41&lt;0),E40,"")</f>
-        <v/>
-      </c>
       <c r="AD41" s="5">
-        <f>IF(AND(ISNUMBER(AA41),0.408167&gt;=MAX(IF(ISNUMBER(AB41),0.31868,-1),IF(ISNUMBER(AC41),0.510996,-1))),AA41,IF(AND(ISNUMBER(AB41),0.31868&gt;MAX(IF(ISNUMBER(AA41),0.408167,-1),IF(ISNUMBER(AC41),0.510996,-1))),AB41,IF(AND(ISNUMBER(AC41),0.510996&gt;MAX(IF(ISNUMBER(AA41),0.408167,-1),IF(ISNUMBER(AB41),0.31868,-1))),AC41,"")))</f>
+        <f>IF(AA41&lt;&gt;"",AA41,IF(AB41&lt;&gt;"",AB41,AC41))</f>
         <v/>
       </c>
     </row>
@@ -4655,62 +4732,62 @@
         <v>160.52</v>
       </c>
       <c r="C42" s="5">
-        <f>IF(AND(ISNUMBER(B42),ISNUMBER(B43)),(B42/B43-1)*100,"")</f>
+        <f>IF(COUNT(B42:B43)=2,(B42/B43-1)*100,"")</f>
         <v/>
       </c>
       <c r="D42" s="5" t="n">
         <v>67.25</v>
       </c>
       <c r="E42" s="5">
-        <f>IF(AND(ISNUMBER(D42),ISNUMBER(D43)),(D42/D43-1)*100,"")</f>
+        <f>IF(COUNT(D42:D43)=2,(D42/D43-1)*100,"")</f>
         <v/>
       </c>
       <c r="F42" s="5" t="n">
         <v>79.0975</v>
       </c>
       <c r="G42" s="5">
-        <f>IF(AND(ISNUMBER(F42),ISNUMBER(F43)),(F42/F43-1)*100,"")</f>
+        <f>IF(COUNT(F42:F43)=2,(F42/F43-1)*100,"")</f>
         <v/>
       </c>
       <c r="H42" s="5" t="n">
         <v>53.72</v>
       </c>
       <c r="I42" s="5">
-        <f>IF(AND(ISNUMBER(H42),ISNUMBER(H43)),(H42/H43-1)*100,"")</f>
+        <f>IF(COUNT(H42:H43)=2,(H42/H43-1)*100,"")</f>
         <v/>
       </c>
       <c r="J42" s="5" t="n">
         <v>74.59</v>
       </c>
       <c r="K42" s="5">
-        <f>IF(AND(ISNUMBER(J42),ISNUMBER(J43)),(J42/J43-1)*100,"")</f>
+        <f>IF(COUNT(J42:J43)=2,(J42/J43-1)*100,"")</f>
         <v/>
       </c>
       <c r="L42" s="5" t="n">
         <v>-4.4125</v>
       </c>
       <c r="M42" s="5">
-        <f>IF(AND(ISNUMBER(L42),ISNUMBER(L43)),(L42/L43-1)*100,"")</f>
+        <f>IF(COUNT(L42:L43)=2,(L42/L43-1)*100,"")</f>
         <v/>
       </c>
       <c r="N42" s="5" t="n"/>
       <c r="O42" s="5">
-        <f>IF(AND(ISNUMBER(N42),ISNUMBER(N43)),(N42/N43-1)*100,"")</f>
+        <f>IF(COUNT(N42:N43)=2,(N42/N43-1)*100,"")</f>
         <v/>
       </c>
       <c r="P42" s="5" t="n"/>
       <c r="Q42" s="5">
-        <f>IF(AND(ISNUMBER(P42),ISNUMBER(P43)),(P42/P43-1)*100,"")</f>
+        <f>IF(COUNT(P42:P43)=2,(P42/P43-1)*100,"")</f>
         <v/>
       </c>
       <c r="R42" s="5" t="n"/>
       <c r="S42" s="5">
-        <f>IF(AND(ISNUMBER(R42),ISNUMBER(R43)),(R42/R43-1)*100,"")</f>
+        <f>IF(COUNT(R42:R43)=2,(R42/R43-1)*100,"")</f>
         <v/>
       </c>
       <c r="T42" s="5" t="n"/>
       <c r="U42" s="5">
-        <f>IF(AND(ISNUMBER(T42),ISNUMBER(T43)),(T42/T43-1)*100,"")</f>
+        <f>IF(COUNT(T42:T43)=2,(T42/T43-1)*100,"")</f>
         <v/>
       </c>
       <c r="V42" s="5" t="n"/>
@@ -4719,31 +4796,31 @@
         <v/>
       </c>
       <c r="X42" s="5">
+        <f>IF(AND(K42&lt;0,M42&gt;0),C41,"")</f>
+        <v/>
+      </c>
+      <c r="Y42" s="5">
         <f>IF(AND(G42&gt;0,I42&lt;0,K42&gt;0),C41,"")</f>
         <v/>
       </c>
-      <c r="Y42" s="5">
-        <f>IF(AND(K42&lt;0,M42&gt;0),C41,"")</f>
-        <v/>
-      </c>
       <c r="Z42" s="5">
-        <f>IF(AND(ISNUMBER(W42),0.549579&gt;=MAX(IF(ISNUMBER(X42),0.299732,-1),IF(ISNUMBER(Y42),0.323835,-1))),W42,IF(AND(ISNUMBER(X42),0.299732&gt;MAX(IF(ISNUMBER(W42),0.549579,-1),IF(ISNUMBER(Y42),0.323835,-1))),X42,IF(AND(ISNUMBER(Y42),0.323835&gt;MAX(IF(ISNUMBER(W42),0.549579,-1),IF(ISNUMBER(X42),0.299732,-1))),Y42,"")))</f>
+        <f>IF(W42&lt;&gt;"",W42,IF(X42&lt;&gt;"",X42,Y42))</f>
         <v/>
       </c>
       <c r="AA42" s="5">
+        <f>IF(AND(S42&gt;0,U42&lt;0),E41,"")</f>
+        <v/>
+      </c>
+      <c r="AB42" s="5">
         <f>IF(AND(O42&lt;=-1,E42&lt;0),E41,"")</f>
         <v/>
       </c>
-      <c r="AB42" s="5">
+      <c r="AC42" s="5">
         <f>IF(AND(Q42&gt;0,S42&gt;0),E41,"")</f>
         <v/>
       </c>
-      <c r="AC42" s="5">
-        <f>IF(AND(S42&gt;0,U42&lt;0),E41,"")</f>
-        <v/>
-      </c>
       <c r="AD42" s="5">
-        <f>IF(AND(ISNUMBER(AA42),0.408167&gt;=MAX(IF(ISNUMBER(AB42),0.31868,-1),IF(ISNUMBER(AC42),0.510996,-1))),AA42,IF(AND(ISNUMBER(AB42),0.31868&gt;MAX(IF(ISNUMBER(AA42),0.408167,-1),IF(ISNUMBER(AC42),0.510996,-1))),AB42,IF(AND(ISNUMBER(AC42),0.510996&gt;MAX(IF(ISNUMBER(AA42),0.408167,-1),IF(ISNUMBER(AB42),0.31868,-1))),AC42,"")))</f>
+        <f>IF(AA42&lt;&gt;"",AA42,IF(AB42&lt;&gt;"",AB42,AC42))</f>
         <v/>
       </c>
     </row>
@@ -4757,62 +4834,62 @@
         <v>161.96</v>
       </c>
       <c r="C43" s="5">
-        <f>IF(AND(ISNUMBER(B43),ISNUMBER(B44)),(B43/B44-1)*100,"")</f>
+        <f>IF(COUNT(B43:B44)=2,(B43/B44-1)*100,"")</f>
         <v/>
       </c>
       <c r="D43" s="5" t="n">
         <v>67.17</v>
       </c>
       <c r="E43" s="5">
-        <f>IF(AND(ISNUMBER(D43),ISNUMBER(D44)),(D43/D44-1)*100,"")</f>
+        <f>IF(COUNT(D43:D44)=2,(D43/D44-1)*100,"")</f>
         <v/>
       </c>
       <c r="F43" s="5" t="n">
         <v>79.1174</v>
       </c>
       <c r="G43" s="5">
-        <f>IF(AND(ISNUMBER(F43),ISNUMBER(F44)),(F43/F44-1)*100,"")</f>
+        <f>IF(COUNT(F43:F44)=2,(F43/F44-1)*100,"")</f>
         <v/>
       </c>
       <c r="H43" s="5" t="n">
         <v>53.88</v>
       </c>
       <c r="I43" s="5">
-        <f>IF(AND(ISNUMBER(H43),ISNUMBER(H44)),(H43/H44-1)*100,"")</f>
+        <f>IF(COUNT(H43:H44)=2,(H43/H44-1)*100,"")</f>
         <v/>
       </c>
       <c r="J43" s="5" t="n">
         <v>77.66</v>
       </c>
       <c r="K43" s="5">
-        <f>IF(AND(ISNUMBER(J43),ISNUMBER(J44)),(J43/J44-1)*100,"")</f>
+        <f>IF(COUNT(J43:J44)=2,(J43/J44-1)*100,"")</f>
         <v/>
       </c>
       <c r="L43" s="5" t="n">
         <v>12.7894</v>
       </c>
       <c r="M43" s="5">
-        <f>IF(AND(ISNUMBER(L43),ISNUMBER(L44)),(L43/L44-1)*100,"")</f>
+        <f>IF(COUNT(L43:L44)=2,(L43/L44-1)*100,"")</f>
         <v/>
       </c>
       <c r="N43" s="5" t="n"/>
       <c r="O43" s="5">
-        <f>IF(AND(ISNUMBER(N43),ISNUMBER(N44)),(N43/N44-1)*100,"")</f>
+        <f>IF(COUNT(N43:N44)=2,(N43/N44-1)*100,"")</f>
         <v/>
       </c>
       <c r="P43" s="5" t="n"/>
       <c r="Q43" s="5">
-        <f>IF(AND(ISNUMBER(P43),ISNUMBER(P44)),(P43/P44-1)*100,"")</f>
+        <f>IF(COUNT(P43:P44)=2,(P43/P44-1)*100,"")</f>
         <v/>
       </c>
       <c r="R43" s="5" t="n"/>
       <c r="S43" s="5">
-        <f>IF(AND(ISNUMBER(R43),ISNUMBER(R44)),(R43/R44-1)*100,"")</f>
+        <f>IF(COUNT(R43:R44)=2,(R43/R44-1)*100,"")</f>
         <v/>
       </c>
       <c r="T43" s="5" t="n"/>
       <c r="U43" s="5">
-        <f>IF(AND(ISNUMBER(T43),ISNUMBER(T44)),(T43/T44-1)*100,"")</f>
+        <f>IF(COUNT(T43:T44)=2,(T43/T44-1)*100,"")</f>
         <v/>
       </c>
       <c r="V43" s="5" t="n"/>
@@ -4821,31 +4898,31 @@
         <v/>
       </c>
       <c r="X43" s="5">
+        <f>IF(AND(K43&lt;0,M43&gt;0),C42,"")</f>
+        <v/>
+      </c>
+      <c r="Y43" s="5">
         <f>IF(AND(G43&gt;0,I43&lt;0,K43&gt;0),C42,"")</f>
         <v/>
       </c>
-      <c r="Y43" s="5">
-        <f>IF(AND(K43&lt;0,M43&gt;0),C42,"")</f>
-        <v/>
-      </c>
       <c r="Z43" s="5">
-        <f>IF(AND(ISNUMBER(W43),0.549579&gt;=MAX(IF(ISNUMBER(X43),0.299732,-1),IF(ISNUMBER(Y43),0.323835,-1))),W43,IF(AND(ISNUMBER(X43),0.299732&gt;MAX(IF(ISNUMBER(W43),0.549579,-1),IF(ISNUMBER(Y43),0.323835,-1))),X43,IF(AND(ISNUMBER(Y43),0.323835&gt;MAX(IF(ISNUMBER(W43),0.549579,-1),IF(ISNUMBER(X43),0.299732,-1))),Y43,"")))</f>
+        <f>IF(W43&lt;&gt;"",W43,IF(X43&lt;&gt;"",X43,Y43))</f>
         <v/>
       </c>
       <c r="AA43" s="5">
+        <f>IF(AND(S43&gt;0,U43&lt;0),E42,"")</f>
+        <v/>
+      </c>
+      <c r="AB43" s="5">
         <f>IF(AND(O43&lt;=-1,E43&lt;0),E42,"")</f>
         <v/>
       </c>
-      <c r="AB43" s="5">
+      <c r="AC43" s="5">
         <f>IF(AND(Q43&gt;0,S43&gt;0),E42,"")</f>
         <v/>
       </c>
-      <c r="AC43" s="5">
-        <f>IF(AND(S43&gt;0,U43&lt;0),E42,"")</f>
-        <v/>
-      </c>
       <c r="AD43" s="5">
-        <f>IF(AND(ISNUMBER(AA43),0.408167&gt;=MAX(IF(ISNUMBER(AB43),0.31868,-1),IF(ISNUMBER(AC43),0.510996,-1))),AA43,IF(AND(ISNUMBER(AB43),0.31868&gt;MAX(IF(ISNUMBER(AA43),0.408167,-1),IF(ISNUMBER(AC43),0.510996,-1))),AB43,IF(AND(ISNUMBER(AC43),0.510996&gt;MAX(IF(ISNUMBER(AA43),0.408167,-1),IF(ISNUMBER(AB43),0.31868,-1))),AC43,"")))</f>
+        <f>IF(AA43&lt;&gt;"",AA43,IF(AB43&lt;&gt;"",AB43,AC43))</f>
         <v/>
       </c>
     </row>
@@ -4859,62 +4936,62 @@
         <v>173.38</v>
       </c>
       <c r="C44" s="5">
-        <f>IF(AND(ISNUMBER(B44),ISNUMBER(B45)),(B44/B45-1)*100,"")</f>
+        <f>IF(COUNT(B44:B45)=2,(B44/B45-1)*100,"")</f>
         <v/>
       </c>
       <c r="D44" s="5" t="n">
         <v>71.20999999999999</v>
       </c>
       <c r="E44" s="5">
-        <f>IF(AND(ISNUMBER(D44),ISNUMBER(D45)),(D44/D45-1)*100,"")</f>
+        <f>IF(COUNT(D44:D45)=2,(D44/D45-1)*100,"")</f>
         <v/>
       </c>
       <c r="F44" s="5" t="n">
         <v>79.1867</v>
       </c>
       <c r="G44" s="5">
-        <f>IF(AND(ISNUMBER(F44),ISNUMBER(F45)),(F44/F45-1)*100,"")</f>
+        <f>IF(COUNT(F44:F45)=2,(F44/F45-1)*100,"")</f>
         <v/>
       </c>
       <c r="H44" s="5" t="n">
         <v>53.7</v>
       </c>
       <c r="I44" s="5">
-        <f>IF(AND(ISNUMBER(H44),ISNUMBER(H45)),(H44/H45-1)*100,"")</f>
+        <f>IF(COUNT(H44:H45)=2,(H44/H45-1)*100,"")</f>
         <v/>
       </c>
       <c r="J44" s="5" t="n">
         <v>81.44</v>
       </c>
       <c r="K44" s="5">
-        <f>IF(AND(ISNUMBER(J44),ISNUMBER(J45)),(J44/J45-1)*100,"")</f>
+        <f>IF(COUNT(J44:J45)=2,(J44/J45-1)*100,"")</f>
         <v/>
       </c>
       <c r="L44" s="5" t="n">
         <v>5.3659</v>
       </c>
       <c r="M44" s="5">
-        <f>IF(AND(ISNUMBER(L44),ISNUMBER(L45)),(L44/L45-1)*100,"")</f>
+        <f>IF(COUNT(L44:L45)=2,(L44/L45-1)*100,"")</f>
         <v/>
       </c>
       <c r="N44" s="5" t="n"/>
       <c r="O44" s="5">
-        <f>IF(AND(ISNUMBER(N44),ISNUMBER(N45)),(N44/N45-1)*100,"")</f>
+        <f>IF(COUNT(N44:N45)=2,(N44/N45-1)*100,"")</f>
         <v/>
       </c>
       <c r="P44" s="5" t="n"/>
       <c r="Q44" s="5">
-        <f>IF(AND(ISNUMBER(P44),ISNUMBER(P45)),(P44/P45-1)*100,"")</f>
+        <f>IF(COUNT(P44:P45)=2,(P44/P45-1)*100,"")</f>
         <v/>
       </c>
       <c r="R44" s="5" t="n"/>
       <c r="S44" s="5">
-        <f>IF(AND(ISNUMBER(R44),ISNUMBER(R45)),(R44/R45-1)*100,"")</f>
+        <f>IF(COUNT(R44:R45)=2,(R44/R45-1)*100,"")</f>
         <v/>
       </c>
       <c r="T44" s="5" t="n"/>
       <c r="U44" s="5">
-        <f>IF(AND(ISNUMBER(T44),ISNUMBER(T45)),(T44/T45-1)*100,"")</f>
+        <f>IF(COUNT(T44:T45)=2,(T44/T45-1)*100,"")</f>
         <v/>
       </c>
       <c r="V44" s="5" t="n"/>
@@ -4923,31 +5000,31 @@
         <v/>
       </c>
       <c r="X44" s="5">
+        <f>IF(AND(K44&lt;0,M44&gt;0),C43,"")</f>
+        <v/>
+      </c>
+      <c r="Y44" s="5">
         <f>IF(AND(G44&gt;0,I44&lt;0,K44&gt;0),C43,"")</f>
         <v/>
       </c>
-      <c r="Y44" s="5">
-        <f>IF(AND(K44&lt;0,M44&gt;0),C43,"")</f>
-        <v/>
-      </c>
       <c r="Z44" s="5">
-        <f>IF(AND(ISNUMBER(W44),0.549579&gt;=MAX(IF(ISNUMBER(X44),0.299732,-1),IF(ISNUMBER(Y44),0.323835,-1))),W44,IF(AND(ISNUMBER(X44),0.299732&gt;MAX(IF(ISNUMBER(W44),0.549579,-1),IF(ISNUMBER(Y44),0.323835,-1))),X44,IF(AND(ISNUMBER(Y44),0.323835&gt;MAX(IF(ISNUMBER(W44),0.549579,-1),IF(ISNUMBER(X44),0.299732,-1))),Y44,"")))</f>
+        <f>IF(W44&lt;&gt;"",W44,IF(X44&lt;&gt;"",X44,Y44))</f>
         <v/>
       </c>
       <c r="AA44" s="5">
+        <f>IF(AND(S44&gt;0,U44&lt;0),E43,"")</f>
+        <v/>
+      </c>
+      <c r="AB44" s="5">
         <f>IF(AND(O44&lt;=-1,E44&lt;0),E43,"")</f>
         <v/>
       </c>
-      <c r="AB44" s="5">
+      <c r="AC44" s="5">
         <f>IF(AND(Q44&gt;0,S44&gt;0),E43,"")</f>
         <v/>
       </c>
-      <c r="AC44" s="5">
-        <f>IF(AND(S44&gt;0,U44&lt;0),E43,"")</f>
-        <v/>
-      </c>
       <c r="AD44" s="5">
-        <f>IF(AND(ISNUMBER(AA44),0.408167&gt;=MAX(IF(ISNUMBER(AB44),0.31868,-1),IF(ISNUMBER(AC44),0.510996,-1))),AA44,IF(AND(ISNUMBER(AB44),0.31868&gt;MAX(IF(ISNUMBER(AA44),0.408167,-1),IF(ISNUMBER(AC44),0.510996,-1))),AB44,IF(AND(ISNUMBER(AC44),0.510996&gt;MAX(IF(ISNUMBER(AA44),0.408167,-1),IF(ISNUMBER(AB44),0.31868,-1))),AC44,"")))</f>
+        <f>IF(AA44&lt;&gt;"",AA44,IF(AB44&lt;&gt;"",AB44,AC44))</f>
         <v/>
       </c>
     </row>
@@ -4961,62 +5038,62 @@
         <v>174.19</v>
       </c>
       <c r="C45" s="5">
-        <f>IF(AND(ISNUMBER(B45),ISNUMBER(B46)),(B45/B46-1)*100,"")</f>
+        <f>IF(COUNT(B45:B46)=2,(B45/B46-1)*100,"")</f>
         <v/>
       </c>
       <c r="D45" s="5" t="n">
         <v>70.79000000000001</v>
       </c>
       <c r="E45" s="5">
-        <f>IF(AND(ISNUMBER(D45),ISNUMBER(D46)),(D45/D46-1)*100,"")</f>
+        <f>IF(COUNT(D45:D46)=2,(D45/D46-1)*100,"")</f>
         <v/>
       </c>
       <c r="F45" s="5" t="n">
         <v>79.256</v>
       </c>
       <c r="G45" s="5">
-        <f>IF(AND(ISNUMBER(F45),ISNUMBER(F46)),(F45/F46-1)*100,"")</f>
+        <f>IF(COUNT(F45:F46)=2,(F45/F46-1)*100,"")</f>
         <v/>
       </c>
       <c r="H45" s="5" t="n">
         <v>53.383</v>
       </c>
       <c r="I45" s="5">
-        <f>IF(AND(ISNUMBER(H45),ISNUMBER(H46)),(H45/H46-1)*100,"")</f>
+        <f>IF(COUNT(H45:H46)=2,(H45/H46-1)*100,"")</f>
         <v/>
       </c>
       <c r="J45" s="5" t="n">
         <v>82.51000000000001</v>
       </c>
       <c r="K45" s="5">
-        <f>IF(AND(ISNUMBER(J45),ISNUMBER(J46)),(J45/J46-1)*100,"")</f>
+        <f>IF(COUNT(J45:J46)=2,(J45/J46-1)*100,"")</f>
         <v/>
       </c>
       <c r="L45" s="5" t="n">
         <v>-11.0629</v>
       </c>
       <c r="M45" s="5">
-        <f>IF(AND(ISNUMBER(L45),ISNUMBER(L46)),(L45/L46-1)*100,"")</f>
+        <f>IF(COUNT(L45:L46)=2,(L45/L46-1)*100,"")</f>
         <v/>
       </c>
       <c r="N45" s="5" t="n"/>
       <c r="O45" s="5">
-        <f>IF(AND(ISNUMBER(N45),ISNUMBER(N46)),(N45/N46-1)*100,"")</f>
+        <f>IF(COUNT(N45:N46)=2,(N45/N46-1)*100,"")</f>
         <v/>
       </c>
       <c r="P45" s="5" t="n"/>
       <c r="Q45" s="5">
-        <f>IF(AND(ISNUMBER(P45),ISNUMBER(P46)),(P45/P46-1)*100,"")</f>
+        <f>IF(COUNT(P45:P46)=2,(P45/P46-1)*100,"")</f>
         <v/>
       </c>
       <c r="R45" s="5" t="n"/>
       <c r="S45" s="5">
-        <f>IF(AND(ISNUMBER(R45),ISNUMBER(R46)),(R45/R46-1)*100,"")</f>
+        <f>IF(COUNT(R45:R46)=2,(R45/R46-1)*100,"")</f>
         <v/>
       </c>
       <c r="T45" s="5" t="n"/>
       <c r="U45" s="5">
-        <f>IF(AND(ISNUMBER(T45),ISNUMBER(T46)),(T45/T46-1)*100,"")</f>
+        <f>IF(COUNT(T45:T46)=2,(T45/T46-1)*100,"")</f>
         <v/>
       </c>
       <c r="V45" s="5" t="n"/>
@@ -5025,31 +5102,31 @@
         <v/>
       </c>
       <c r="X45" s="5">
+        <f>IF(AND(K45&lt;0,M45&gt;0),C44,"")</f>
+        <v/>
+      </c>
+      <c r="Y45" s="5">
         <f>IF(AND(G45&gt;0,I45&lt;0,K45&gt;0),C44,"")</f>
         <v/>
       </c>
-      <c r="Y45" s="5">
-        <f>IF(AND(K45&lt;0,M45&gt;0),C44,"")</f>
-        <v/>
-      </c>
       <c r="Z45" s="5">
-        <f>IF(AND(ISNUMBER(W45),0.549579&gt;=MAX(IF(ISNUMBER(X45),0.299732,-1),IF(ISNUMBER(Y45),0.323835,-1))),W45,IF(AND(ISNUMBER(X45),0.299732&gt;MAX(IF(ISNUMBER(W45),0.549579,-1),IF(ISNUMBER(Y45),0.323835,-1))),X45,IF(AND(ISNUMBER(Y45),0.323835&gt;MAX(IF(ISNUMBER(W45),0.549579,-1),IF(ISNUMBER(X45),0.299732,-1))),Y45,"")))</f>
+        <f>IF(W45&lt;&gt;"",W45,IF(X45&lt;&gt;"",X45,Y45))</f>
         <v/>
       </c>
       <c r="AA45" s="5">
+        <f>IF(AND(S45&gt;0,U45&lt;0),E44,"")</f>
+        <v/>
+      </c>
+      <c r="AB45" s="5">
         <f>IF(AND(O45&lt;=-1,E45&lt;0),E44,"")</f>
         <v/>
       </c>
-      <c r="AB45" s="5">
+      <c r="AC45" s="5">
         <f>IF(AND(Q45&gt;0,S45&gt;0),E44,"")</f>
         <v/>
       </c>
-      <c r="AC45" s="5">
-        <f>IF(AND(S45&gt;0,U45&lt;0),E44,"")</f>
-        <v/>
-      </c>
       <c r="AD45" s="5">
-        <f>IF(AND(ISNUMBER(AA45),0.408167&gt;=MAX(IF(ISNUMBER(AB45),0.31868,-1),IF(ISNUMBER(AC45),0.510996,-1))),AA45,IF(AND(ISNUMBER(AB45),0.31868&gt;MAX(IF(ISNUMBER(AA45),0.408167,-1),IF(ISNUMBER(AC45),0.510996,-1))),AB45,IF(AND(ISNUMBER(AC45),0.510996&gt;MAX(IF(ISNUMBER(AA45),0.408167,-1),IF(ISNUMBER(AB45),0.31868,-1))),AC45,"")))</f>
+        <f>IF(AA45&lt;&gt;"",AA45,IF(AB45&lt;&gt;"",AB45,AC45))</f>
         <v/>
       </c>
     </row>
@@ -5063,62 +5140,62 @@
         <v>165.99</v>
       </c>
       <c r="C46" s="5">
-        <f>IF(AND(ISNUMBER(B46),ISNUMBER(B47)),(B46/B47-1)*100,"")</f>
+        <f>IF(COUNT(B46:B47)=2,(B46/B47-1)*100,"")</f>
         <v/>
       </c>
       <c r="D46" s="5" t="n">
         <v>68.56</v>
       </c>
       <c r="E46" s="5">
-        <f>IF(AND(ISNUMBER(D46),ISNUMBER(D47)),(D46/D47-1)*100,"")</f>
+        <f>IF(COUNT(D46:D47)=2,(D46/D47-1)*100,"")</f>
         <v/>
       </c>
       <c r="F46" s="5" t="n">
         <v>78.9787</v>
       </c>
       <c r="G46" s="5">
-        <f>IF(AND(ISNUMBER(F46),ISNUMBER(F47)),(F46/F47-1)*100,"")</f>
+        <f>IF(COUNT(F46:F47)=2,(F46/F47-1)*100,"")</f>
         <v/>
       </c>
       <c r="H46" s="5" t="n">
         <v>53.8613</v>
       </c>
       <c r="I46" s="5">
-        <f>IF(AND(ISNUMBER(H46),ISNUMBER(H47)),(H46/H47-1)*100,"")</f>
+        <f>IF(COUNT(H46:H47)=2,(H46/H47-1)*100,"")</f>
         <v/>
       </c>
       <c r="J46" s="5" t="n">
         <v>84.36</v>
       </c>
       <c r="K46" s="5">
-        <f>IF(AND(ISNUMBER(J46),ISNUMBER(J47)),(J46/J47-1)*100,"")</f>
+        <f>IF(COUNT(J46:J47)=2,(J46/J47-1)*100,"")</f>
         <v/>
       </c>
       <c r="L46" s="5" t="n">
         <v>12.3705</v>
       </c>
       <c r="M46" s="5">
-        <f>IF(AND(ISNUMBER(L46),ISNUMBER(L47)),(L46/L47-1)*100,"")</f>
+        <f>IF(COUNT(L46:L47)=2,(L46/L47-1)*100,"")</f>
         <v/>
       </c>
       <c r="N46" s="5" t="n"/>
       <c r="O46" s="5">
-        <f>IF(AND(ISNUMBER(N46),ISNUMBER(N47)),(N46/N47-1)*100,"")</f>
+        <f>IF(COUNT(N46:N47)=2,(N46/N47-1)*100,"")</f>
         <v/>
       </c>
       <c r="P46" s="5" t="n"/>
       <c r="Q46" s="5">
-        <f>IF(AND(ISNUMBER(P46),ISNUMBER(P47)),(P46/P47-1)*100,"")</f>
+        <f>IF(COUNT(P46:P47)=2,(P46/P47-1)*100,"")</f>
         <v/>
       </c>
       <c r="R46" s="5" t="n"/>
       <c r="S46" s="5">
-        <f>IF(AND(ISNUMBER(R46),ISNUMBER(R47)),(R46/R47-1)*100,"")</f>
+        <f>IF(COUNT(R46:R47)=2,(R46/R47-1)*100,"")</f>
         <v/>
       </c>
       <c r="T46" s="5" t="n"/>
       <c r="U46" s="5">
-        <f>IF(AND(ISNUMBER(T46),ISNUMBER(T47)),(T46/T47-1)*100,"")</f>
+        <f>IF(COUNT(T46:T47)=2,(T46/T47-1)*100,"")</f>
         <v/>
       </c>
       <c r="V46" s="5" t="n"/>
@@ -5127,31 +5204,31 @@
         <v/>
       </c>
       <c r="X46" s="5">
+        <f>IF(AND(K46&lt;0,M46&gt;0),C45,"")</f>
+        <v/>
+      </c>
+      <c r="Y46" s="5">
         <f>IF(AND(G46&gt;0,I46&lt;0,K46&gt;0),C45,"")</f>
         <v/>
       </c>
-      <c r="Y46" s="5">
-        <f>IF(AND(K46&lt;0,M46&gt;0),C45,"")</f>
-        <v/>
-      </c>
       <c r="Z46" s="5">
-        <f>IF(AND(ISNUMBER(W46),0.549579&gt;=MAX(IF(ISNUMBER(X46),0.299732,-1),IF(ISNUMBER(Y46),0.323835,-1))),W46,IF(AND(ISNUMBER(X46),0.299732&gt;MAX(IF(ISNUMBER(W46),0.549579,-1),IF(ISNUMBER(Y46),0.323835,-1))),X46,IF(AND(ISNUMBER(Y46),0.323835&gt;MAX(IF(ISNUMBER(W46),0.549579,-1),IF(ISNUMBER(X46),0.299732,-1))),Y46,"")))</f>
+        <f>IF(W46&lt;&gt;"",W46,IF(X46&lt;&gt;"",X46,Y46))</f>
         <v/>
       </c>
       <c r="AA46" s="5">
+        <f>IF(AND(S46&gt;0,U46&lt;0),E45,"")</f>
+        <v/>
+      </c>
+      <c r="AB46" s="5">
         <f>IF(AND(O46&lt;=-1,E46&lt;0),E45,"")</f>
         <v/>
       </c>
-      <c r="AB46" s="5">
+      <c r="AC46" s="5">
         <f>IF(AND(Q46&gt;0,S46&gt;0),E45,"")</f>
         <v/>
       </c>
-      <c r="AC46" s="5">
-        <f>IF(AND(S46&gt;0,U46&lt;0),E45,"")</f>
-        <v/>
-      </c>
       <c r="AD46" s="5">
-        <f>IF(AND(ISNUMBER(AA46),0.408167&gt;=MAX(IF(ISNUMBER(AB46),0.31868,-1),IF(ISNUMBER(AC46),0.510996,-1))),AA46,IF(AND(ISNUMBER(AB46),0.31868&gt;MAX(IF(ISNUMBER(AA46),0.408167,-1),IF(ISNUMBER(AC46),0.510996,-1))),AB46,IF(AND(ISNUMBER(AC46),0.510996&gt;MAX(IF(ISNUMBER(AA46),0.408167,-1),IF(ISNUMBER(AB46),0.31868,-1))),AC46,"")))</f>
+        <f>IF(AA46&lt;&gt;"",AA46,IF(AB46&lt;&gt;"",AB46,AC46))</f>
         <v/>
       </c>
     </row>
@@ -5165,62 +5242,62 @@
         <v>169.4</v>
       </c>
       <c r="C47" s="5">
-        <f>IF(AND(ISNUMBER(B47),ISNUMBER(B48)),(B47/B48-1)*100,"")</f>
+        <f>IF(COUNT(B47:B48)=2,(B47/B48-1)*100,"")</f>
         <v/>
       </c>
       <c r="D47" s="5" t="n">
         <v>68.64</v>
       </c>
       <c r="E47" s="5">
-        <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48)),(D47/D48-1)*100,"")</f>
+        <f>IF(COUNT(D47:D48)=2,(D47/D48-1)*100,"")</f>
         <v/>
       </c>
       <c r="F47" s="5" t="n">
         <v>79.2758</v>
       </c>
       <c r="G47" s="5">
-        <f>IF(AND(ISNUMBER(F47),ISNUMBER(F48)),(F47/F48-1)*100,"")</f>
+        <f>IF(COUNT(F47:F48)=2,(F47/F48-1)*100,"")</f>
         <v/>
       </c>
       <c r="H47" s="5" t="n">
         <v>54.1603</v>
       </c>
       <c r="I47" s="5">
-        <f>IF(AND(ISNUMBER(H47),ISNUMBER(H48)),(H47/H48-1)*100,"")</f>
+        <f>IF(COUNT(H47:H48)=2,(H47/H48-1)*100,"")</f>
         <v/>
       </c>
       <c r="J47" s="5" t="n">
         <v>87.23999999999999</v>
       </c>
       <c r="K47" s="5">
-        <f>IF(AND(ISNUMBER(J47),ISNUMBER(J48)),(J47/J48-1)*100,"")</f>
+        <f>IF(COUNT(J47:J48)=2,(J47/J48-1)*100,"")</f>
         <v/>
       </c>
       <c r="L47" s="5" t="n">
         <v>1.2963</v>
       </c>
       <c r="M47" s="5">
-        <f>IF(AND(ISNUMBER(L47),ISNUMBER(L48)),(L47/L48-1)*100,"")</f>
+        <f>IF(COUNT(L47:L48)=2,(L47/L48-1)*100,"")</f>
         <v/>
       </c>
       <c r="N47" s="5" t="n"/>
       <c r="O47" s="5">
-        <f>IF(AND(ISNUMBER(N47),ISNUMBER(N48)),(N47/N48-1)*100,"")</f>
+        <f>IF(COUNT(N47:N48)=2,(N47/N48-1)*100,"")</f>
         <v/>
       </c>
       <c r="P47" s="5" t="n"/>
       <c r="Q47" s="5">
-        <f>IF(AND(ISNUMBER(P47),ISNUMBER(P48)),(P47/P48-1)*100,"")</f>
+        <f>IF(COUNT(P47:P48)=2,(P47/P48-1)*100,"")</f>
         <v/>
       </c>
       <c r="R47" s="5" t="n"/>
       <c r="S47" s="5">
-        <f>IF(AND(ISNUMBER(R47),ISNUMBER(R48)),(R47/R48-1)*100,"")</f>
+        <f>IF(COUNT(R47:R48)=2,(R47/R48-1)*100,"")</f>
         <v/>
       </c>
       <c r="T47" s="5" t="n"/>
       <c r="U47" s="5">
-        <f>IF(AND(ISNUMBER(T47),ISNUMBER(T48)),(T47/T48-1)*100,"")</f>
+        <f>IF(COUNT(T47:T48)=2,(T47/T48-1)*100,"")</f>
         <v/>
       </c>
       <c r="V47" s="5" t="n"/>
@@ -5229,31 +5306,31 @@
         <v/>
       </c>
       <c r="X47" s="5">
+        <f>IF(AND(K47&lt;0,M47&gt;0),C46,"")</f>
+        <v/>
+      </c>
+      <c r="Y47" s="5">
         <f>IF(AND(G47&gt;0,I47&lt;0,K47&gt;0),C46,"")</f>
         <v/>
       </c>
-      <c r="Y47" s="5">
-        <f>IF(AND(K47&lt;0,M47&gt;0),C46,"")</f>
-        <v/>
-      </c>
       <c r="Z47" s="5">
-        <f>IF(AND(ISNUMBER(W47),0.549579&gt;=MAX(IF(ISNUMBER(X47),0.299732,-1),IF(ISNUMBER(Y47),0.323835,-1))),W47,IF(AND(ISNUMBER(X47),0.299732&gt;MAX(IF(ISNUMBER(W47),0.549579,-1),IF(ISNUMBER(Y47),0.323835,-1))),X47,IF(AND(ISNUMBER(Y47),0.323835&gt;MAX(IF(ISNUMBER(W47),0.549579,-1),IF(ISNUMBER(X47),0.299732,-1))),Y47,"")))</f>
+        <f>IF(W47&lt;&gt;"",W47,IF(X47&lt;&gt;"",X47,Y47))</f>
         <v/>
       </c>
       <c r="AA47" s="5">
+        <f>IF(AND(S47&gt;0,U47&lt;0),E46,"")</f>
+        <v/>
+      </c>
+      <c r="AB47" s="5">
         <f>IF(AND(O47&lt;=-1,E47&lt;0),E46,"")</f>
         <v/>
       </c>
-      <c r="AB47" s="5">
+      <c r="AC47" s="5">
         <f>IF(AND(Q47&gt;0,S47&gt;0),E46,"")</f>
         <v/>
       </c>
-      <c r="AC47" s="5">
-        <f>IF(AND(S47&gt;0,U47&lt;0),E46,"")</f>
-        <v/>
-      </c>
       <c r="AD47" s="5">
-        <f>IF(AND(ISNUMBER(AA47),0.408167&gt;=MAX(IF(ISNUMBER(AB47),0.31868,-1),IF(ISNUMBER(AC47),0.510996,-1))),AA47,IF(AND(ISNUMBER(AB47),0.31868&gt;MAX(IF(ISNUMBER(AA47),0.408167,-1),IF(ISNUMBER(AC47),0.510996,-1))),AB47,IF(AND(ISNUMBER(AC47),0.510996&gt;MAX(IF(ISNUMBER(AA47),0.408167,-1),IF(ISNUMBER(AB47),0.31868,-1))),AC47,"")))</f>
+        <f>IF(AA47&lt;&gt;"",AA47,IF(AB47&lt;&gt;"",AB47,AC47))</f>
         <v/>
       </c>
     </row>
@@ -5267,62 +5344,62 @@
         <v>176.04</v>
       </c>
       <c r="C48" s="5">
-        <f>IF(AND(ISNUMBER(B48),ISNUMBER(B49)),(B48/B49-1)*100,"")</f>
+        <f>IF(COUNT(B48:B49)=2,(B48/B49-1)*100,"")</f>
         <v/>
       </c>
       <c r="D48" s="5" t="n">
         <v>69.75</v>
       </c>
       <c r="E48" s="5">
-        <f>IF(AND(ISNUMBER(D48),ISNUMBER(D49)),(D48/D49-1)*100,"")</f>
+        <f>IF(COUNT(D48:D49)=2,(D48/D49-1)*100,"")</f>
         <v/>
       </c>
       <c r="F48" s="5" t="n">
         <v>79.28579999999999</v>
       </c>
       <c r="G48" s="5">
-        <f>IF(AND(ISNUMBER(F48),ISNUMBER(F49)),(F48/F49-1)*100,"")</f>
+        <f>IF(COUNT(F48:F49)=2,(F48/F49-1)*100,"")</f>
         <v/>
       </c>
       <c r="H48" s="5" t="n">
         <v>53.373</v>
       </c>
       <c r="I48" s="5">
-        <f>IF(AND(ISNUMBER(H48),ISNUMBER(H49)),(H48/H49-1)*100,"")</f>
+        <f>IF(COUNT(H48:H49)=2,(H48/H49-1)*100,"")</f>
         <v/>
       </c>
       <c r="J48" s="5" t="n">
         <v>85.27</v>
       </c>
       <c r="K48" s="5">
-        <f>IF(AND(ISNUMBER(J48),ISNUMBER(J49)),(J48/J49-1)*100,"")</f>
+        <f>IF(COUNT(J48:J49)=2,(J48/J49-1)*100,"")</f>
         <v/>
       </c>
       <c r="L48" s="5" t="n">
         <v>-8.371</v>
       </c>
       <c r="M48" s="5">
-        <f>IF(AND(ISNUMBER(L48),ISNUMBER(L49)),(L48/L49-1)*100,"")</f>
+        <f>IF(COUNT(L48:L49)=2,(L48/L49-1)*100,"")</f>
         <v/>
       </c>
       <c r="N48" s="5" t="n"/>
       <c r="O48" s="5">
-        <f>IF(AND(ISNUMBER(N48),ISNUMBER(N49)),(N48/N49-1)*100,"")</f>
+        <f>IF(COUNT(N48:N49)=2,(N48/N49-1)*100,"")</f>
         <v/>
       </c>
       <c r="P48" s="5" t="n"/>
       <c r="Q48" s="5">
-        <f>IF(AND(ISNUMBER(P48),ISNUMBER(P49)),(P48/P49-1)*100,"")</f>
+        <f>IF(COUNT(P48:P49)=2,(P48/P49-1)*100,"")</f>
         <v/>
       </c>
       <c r="R48" s="5" t="n"/>
       <c r="S48" s="5">
-        <f>IF(AND(ISNUMBER(R48),ISNUMBER(R49)),(R48/R49-1)*100,"")</f>
+        <f>IF(COUNT(R48:R49)=2,(R48/R49-1)*100,"")</f>
         <v/>
       </c>
       <c r="T48" s="5" t="n"/>
       <c r="U48" s="5">
-        <f>IF(AND(ISNUMBER(T48),ISNUMBER(T49)),(T48/T49-1)*100,"")</f>
+        <f>IF(COUNT(T48:T49)=2,(T48/T49-1)*100,"")</f>
         <v/>
       </c>
       <c r="V48" s="5" t="n"/>
@@ -5331,31 +5408,31 @@
         <v/>
       </c>
       <c r="X48" s="5">
+        <f>IF(AND(K48&lt;0,M48&gt;0),C47,"")</f>
+        <v/>
+      </c>
+      <c r="Y48" s="5">
         <f>IF(AND(G48&gt;0,I48&lt;0,K48&gt;0),C47,"")</f>
         <v/>
       </c>
-      <c r="Y48" s="5">
-        <f>IF(AND(K48&lt;0,M48&gt;0),C47,"")</f>
-        <v/>
-      </c>
       <c r="Z48" s="5">
-        <f>IF(AND(ISNUMBER(W48),0.549579&gt;=MAX(IF(ISNUMBER(X48),0.299732,-1),IF(ISNUMBER(Y48),0.323835,-1))),W48,IF(AND(ISNUMBER(X48),0.299732&gt;MAX(IF(ISNUMBER(W48),0.549579,-1),IF(ISNUMBER(Y48),0.323835,-1))),X48,IF(AND(ISNUMBER(Y48),0.323835&gt;MAX(IF(ISNUMBER(W48),0.549579,-1),IF(ISNUMBER(X48),0.299732,-1))),Y48,"")))</f>
+        <f>IF(W48&lt;&gt;"",W48,IF(X48&lt;&gt;"",X48,Y48))</f>
         <v/>
       </c>
       <c r="AA48" s="5">
+        <f>IF(AND(S48&gt;0,U48&lt;0),E47,"")</f>
+        <v/>
+      </c>
+      <c r="AB48" s="5">
         <f>IF(AND(O48&lt;=-1,E48&lt;0),E47,"")</f>
         <v/>
       </c>
-      <c r="AB48" s="5">
+      <c r="AC48" s="5">
         <f>IF(AND(Q48&gt;0,S48&gt;0),E47,"")</f>
         <v/>
       </c>
-      <c r="AC48" s="5">
-        <f>IF(AND(S48&gt;0,U48&lt;0),E47,"")</f>
-        <v/>
-      </c>
       <c r="AD48" s="5">
-        <f>IF(AND(ISNUMBER(AA48),0.408167&gt;=MAX(IF(ISNUMBER(AB48),0.31868,-1),IF(ISNUMBER(AC48),0.510996,-1))),AA48,IF(AND(ISNUMBER(AB48),0.31868&gt;MAX(IF(ISNUMBER(AA48),0.408167,-1),IF(ISNUMBER(AC48),0.510996,-1))),AB48,IF(AND(ISNUMBER(AC48),0.510996&gt;MAX(IF(ISNUMBER(AA48),0.408167,-1),IF(ISNUMBER(AB48),0.31868,-1))),AC48,"")))</f>
+        <f>IF(AA48&lt;&gt;"",AA48,IF(AB48&lt;&gt;"",AB48,AC48))</f>
         <v/>
       </c>
     </row>
@@ -5369,62 +5446,62 @@
         <v>165.93</v>
       </c>
       <c r="C49" s="5">
-        <f>IF(AND(ISNUMBER(B49),ISNUMBER(B50)),(B49/B50-1)*100,"")</f>
+        <f>IF(COUNT(B49:B50)=2,(B49/B50-1)*100,"")</f>
         <v/>
       </c>
       <c r="D49" s="5" t="n">
         <v>67.529</v>
       </c>
       <c r="E49" s="5">
-        <f>IF(AND(ISNUMBER(D49),ISNUMBER(D50)),(D49/D50-1)*100,"")</f>
+        <f>IF(COUNT(D49:D50)=2,(D49/D50-1)*100,"")</f>
         <v/>
       </c>
       <c r="F49" s="5" t="n">
         <v>79.1867</v>
       </c>
       <c r="G49" s="5">
-        <f>IF(AND(ISNUMBER(F49),ISNUMBER(F50)),(F49/F50-1)*100,"")</f>
+        <f>IF(COUNT(F49:F50)=2,(F49/F50-1)*100,"")</f>
         <v/>
       </c>
       <c r="H49" s="5" t="n">
         <v>53.1538</v>
       </c>
       <c r="I49" s="5">
-        <f>IF(AND(ISNUMBER(H49),ISNUMBER(H50)),(H49/H50-1)*100,"")</f>
+        <f>IF(COUNT(H49:H50)=2,(H49/H50-1)*100,"")</f>
         <v/>
       </c>
       <c r="J49" s="5" t="n">
         <v>80.03</v>
       </c>
       <c r="K49" s="5">
-        <f>IF(AND(ISNUMBER(J49),ISNUMBER(J50)),(J49/J50-1)*100,"")</f>
+        <f>IF(COUNT(J49:J50)=2,(J49/J50-1)*100,"")</f>
         <v/>
       </c>
       <c r="L49" s="5" t="n">
         <v>-9.0535</v>
       </c>
       <c r="M49" s="5">
-        <f>IF(AND(ISNUMBER(L49),ISNUMBER(L50)),(L49/L50-1)*100,"")</f>
+        <f>IF(COUNT(L49:L50)=2,(L49/L50-1)*100,"")</f>
         <v/>
       </c>
       <c r="N49" s="5" t="n"/>
       <c r="O49" s="5">
-        <f>IF(AND(ISNUMBER(N49),ISNUMBER(N50)),(N49/N50-1)*100,"")</f>
+        <f>IF(COUNT(N49:N50)=2,(N49/N50-1)*100,"")</f>
         <v/>
       </c>
       <c r="P49" s="5" t="n"/>
       <c r="Q49" s="5">
-        <f>IF(AND(ISNUMBER(P49),ISNUMBER(P50)),(P49/P50-1)*100,"")</f>
+        <f>IF(COUNT(P49:P50)=2,(P49/P50-1)*100,"")</f>
         <v/>
       </c>
       <c r="R49" s="5" t="n"/>
       <c r="S49" s="5">
-        <f>IF(AND(ISNUMBER(R49),ISNUMBER(R50)),(R49/R50-1)*100,"")</f>
+        <f>IF(COUNT(R49:R50)=2,(R49/R50-1)*100,"")</f>
         <v/>
       </c>
       <c r="T49" s="5" t="n"/>
       <c r="U49" s="5">
-        <f>IF(AND(ISNUMBER(T49),ISNUMBER(T50)),(T49/T50-1)*100,"")</f>
+        <f>IF(COUNT(T49:T50)=2,(T49/T50-1)*100,"")</f>
         <v/>
       </c>
       <c r="V49" s="5" t="n"/>
@@ -5433,31 +5510,31 @@
         <v/>
       </c>
       <c r="X49" s="5">
+        <f>IF(AND(K49&lt;0,M49&gt;0),C48,"")</f>
+        <v/>
+      </c>
+      <c r="Y49" s="5">
         <f>IF(AND(G49&gt;0,I49&lt;0,K49&gt;0),C48,"")</f>
         <v/>
       </c>
-      <c r="Y49" s="5">
-        <f>IF(AND(K49&lt;0,M49&gt;0),C48,"")</f>
-        <v/>
-      </c>
       <c r="Z49" s="5">
-        <f>IF(AND(ISNUMBER(W49),0.549579&gt;=MAX(IF(ISNUMBER(X49),0.299732,-1),IF(ISNUMBER(Y49),0.323835,-1))),W49,IF(AND(ISNUMBER(X49),0.299732&gt;MAX(IF(ISNUMBER(W49),0.549579,-1),IF(ISNUMBER(Y49),0.323835,-1))),X49,IF(AND(ISNUMBER(Y49),0.323835&gt;MAX(IF(ISNUMBER(W49),0.549579,-1),IF(ISNUMBER(X49),0.299732,-1))),Y49,"")))</f>
+        <f>IF(W49&lt;&gt;"",W49,IF(X49&lt;&gt;"",X49,Y49))</f>
         <v/>
       </c>
       <c r="AA49" s="5">
+        <f>IF(AND(S49&gt;0,U49&lt;0),E48,"")</f>
+        <v/>
+      </c>
+      <c r="AB49" s="5">
         <f>IF(AND(O49&lt;=-1,E49&lt;0),E48,"")</f>
         <v/>
       </c>
-      <c r="AB49" s="5">
+      <c r="AC49" s="5">
         <f>IF(AND(Q49&gt;0,S49&gt;0),E48,"")</f>
         <v/>
       </c>
-      <c r="AC49" s="5">
-        <f>IF(AND(S49&gt;0,U49&lt;0),E48,"")</f>
-        <v/>
-      </c>
       <c r="AD49" s="5">
-        <f>IF(AND(ISNUMBER(AA49),0.408167&gt;=MAX(IF(ISNUMBER(AB49),0.31868,-1),IF(ISNUMBER(AC49),0.510996,-1))),AA49,IF(AND(ISNUMBER(AB49),0.31868&gt;MAX(IF(ISNUMBER(AA49),0.408167,-1),IF(ISNUMBER(AC49),0.510996,-1))),AB49,IF(AND(ISNUMBER(AC49),0.510996&gt;MAX(IF(ISNUMBER(AA49),0.408167,-1),IF(ISNUMBER(AB49),0.31868,-1))),AC49,"")))</f>
+        <f>IF(AA49&lt;&gt;"",AA49,IF(AB49&lt;&gt;"",AB49,AC49))</f>
         <v/>
       </c>
     </row>
@@ -5471,62 +5548,62 @@
         <v>163.86</v>
       </c>
       <c r="C50" s="5">
-        <f>IF(AND(ISNUMBER(B50),ISNUMBER(B51)),(B50/B51-1)*100,"")</f>
+        <f>IF(COUNT(B50:B51)=2,(B50/B51-1)*100,"")</f>
         <v/>
       </c>
       <c r="D50" s="5" t="n">
         <v>67.151</v>
       </c>
       <c r="E50" s="5">
-        <f>IF(AND(ISNUMBER(D50),ISNUMBER(D51)),(D50/D51-1)*100,"")</f>
+        <f>IF(COUNT(D50:D51)=2,(D50/D51-1)*100,"")</f>
         <v/>
       </c>
       <c r="F50" s="5" t="n">
         <v>79.1867</v>
       </c>
       <c r="G50" s="5">
-        <f>IF(AND(ISNUMBER(F50),ISNUMBER(F51)),(F50/F51-1)*100,"")</f>
+        <f>IF(COUNT(F50:F51)=2,(F50/F51-1)*100,"")</f>
         <v/>
       </c>
       <c r="H50" s="5" t="n">
         <v>52.4363</v>
       </c>
       <c r="I50" s="5">
-        <f>IF(AND(ISNUMBER(H50),ISNUMBER(H51)),(H50/H51-1)*100,"")</f>
+        <f>IF(COUNT(H50:H51)=2,(H50/H51-1)*100,"")</f>
         <v/>
       </c>
       <c r="J50" s="5" t="n">
         <v>77.72</v>
       </c>
       <c r="K50" s="5">
-        <f>IF(AND(ISNUMBER(J50),ISNUMBER(J51)),(J50/J51-1)*100,"")</f>
+        <f>IF(COUNT(J50:J51)=2,(J50/J51-1)*100,"")</f>
         <v/>
       </c>
       <c r="L50" s="5" t="n">
         <v>-12.5113</v>
       </c>
       <c r="M50" s="5">
-        <f>IF(AND(ISNUMBER(L50),ISNUMBER(L51)),(L50/L51-1)*100,"")</f>
+        <f>IF(COUNT(L50:L51)=2,(L50/L51-1)*100,"")</f>
         <v/>
       </c>
       <c r="N50" s="5" t="n"/>
       <c r="O50" s="5">
-        <f>IF(AND(ISNUMBER(N50),ISNUMBER(N51)),(N50/N51-1)*100,"")</f>
+        <f>IF(COUNT(N50:N51)=2,(N50/N51-1)*100,"")</f>
         <v/>
       </c>
       <c r="P50" s="5" t="n"/>
       <c r="Q50" s="5">
-        <f>IF(AND(ISNUMBER(P50),ISNUMBER(P51)),(P50/P51-1)*100,"")</f>
+        <f>IF(COUNT(P50:P51)=2,(P50/P51-1)*100,"")</f>
         <v/>
       </c>
       <c r="R50" s="5" t="n"/>
       <c r="S50" s="5">
-        <f>IF(AND(ISNUMBER(R50),ISNUMBER(R51)),(R50/R51-1)*100,"")</f>
+        <f>IF(COUNT(R50:R51)=2,(R50/R51-1)*100,"")</f>
         <v/>
       </c>
       <c r="T50" s="5" t="n"/>
       <c r="U50" s="5">
-        <f>IF(AND(ISNUMBER(T50),ISNUMBER(T51)),(T50/T51-1)*100,"")</f>
+        <f>IF(COUNT(T50:T51)=2,(T50/T51-1)*100,"")</f>
         <v/>
       </c>
       <c r="V50" s="5" t="n"/>
@@ -5535,31 +5612,31 @@
         <v/>
       </c>
       <c r="X50" s="5">
+        <f>IF(AND(K50&lt;0,M50&gt;0),C49,"")</f>
+        <v/>
+      </c>
+      <c r="Y50" s="5">
         <f>IF(AND(G50&gt;0,I50&lt;0,K50&gt;0),C49,"")</f>
         <v/>
       </c>
-      <c r="Y50" s="5">
-        <f>IF(AND(K50&lt;0,M50&gt;0),C49,"")</f>
-        <v/>
-      </c>
       <c r="Z50" s="5">
-        <f>IF(AND(ISNUMBER(W50),0.549579&gt;=MAX(IF(ISNUMBER(X50),0.299732,-1),IF(ISNUMBER(Y50),0.323835,-1))),W50,IF(AND(ISNUMBER(X50),0.299732&gt;MAX(IF(ISNUMBER(W50),0.549579,-1),IF(ISNUMBER(Y50),0.323835,-1))),X50,IF(AND(ISNUMBER(Y50),0.323835&gt;MAX(IF(ISNUMBER(W50),0.549579,-1),IF(ISNUMBER(X50),0.299732,-1))),Y50,"")))</f>
+        <f>IF(W50&lt;&gt;"",W50,IF(X50&lt;&gt;"",X50,Y50))</f>
         <v/>
       </c>
       <c r="AA50" s="5">
+        <f>IF(AND(S50&gt;0,U50&lt;0),E49,"")</f>
+        <v/>
+      </c>
+      <c r="AB50" s="5">
         <f>IF(AND(O50&lt;=-1,E50&lt;0),E49,"")</f>
         <v/>
       </c>
-      <c r="AB50" s="5">
+      <c r="AC50" s="5">
         <f>IF(AND(Q50&gt;0,S50&gt;0),E49,"")</f>
         <v/>
       </c>
-      <c r="AC50" s="5">
-        <f>IF(AND(S50&gt;0,U50&lt;0),E49,"")</f>
-        <v/>
-      </c>
       <c r="AD50" s="5">
-        <f>IF(AND(ISNUMBER(AA50),0.408167&gt;=MAX(IF(ISNUMBER(AB50),0.31868,-1),IF(ISNUMBER(AC50),0.510996,-1))),AA50,IF(AND(ISNUMBER(AB50),0.31868&gt;MAX(IF(ISNUMBER(AA50),0.408167,-1),IF(ISNUMBER(AC50),0.510996,-1))),AB50,IF(AND(ISNUMBER(AC50),0.510996&gt;MAX(IF(ISNUMBER(AA50),0.408167,-1),IF(ISNUMBER(AB50),0.31868,-1))),AC50,"")))</f>
+        <f>IF(AA50&lt;&gt;"",AA50,IF(AB50&lt;&gt;"",AB50,AC50))</f>
         <v/>
       </c>
     </row>
@@ -5573,62 +5650,62 @@
         <v>153.76</v>
       </c>
       <c r="C51" s="5">
-        <f>IF(AND(ISNUMBER(B51),ISNUMBER(B52)),(B51/B52-1)*100,"")</f>
+        <f>IF(COUNT(B51:B52)=2,(B51/B52-1)*100,"")</f>
         <v/>
       </c>
       <c r="D51" s="5" t="n">
         <v>64.3257</v>
       </c>
       <c r="E51" s="5">
-        <f>IF(AND(ISNUMBER(D51),ISNUMBER(D52)),(D51/D52-1)*100,"")</f>
+        <f>IF(COUNT(D51:D52)=2,(D51/D52-1)*100,"")</f>
         <v/>
       </c>
       <c r="F51" s="5" t="n">
         <v>78.72110000000001</v>
       </c>
       <c r="G51" s="5">
-        <f>IF(AND(ISNUMBER(F51),ISNUMBER(F52)),(F51/F52-1)*100,"")</f>
+        <f>IF(COUNT(F51:F52)=2,(F51/F52-1)*100,"")</f>
         <v/>
       </c>
       <c r="H51" s="5" t="n">
         <v>52.0477</v>
       </c>
       <c r="I51" s="5">
-        <f>IF(AND(ISNUMBER(H51),ISNUMBER(H52)),(H51/H52-1)*100,"")</f>
+        <f>IF(COUNT(H51:H52)=2,(H51/H52-1)*100,"")</f>
         <v/>
       </c>
       <c r="J51" s="5" t="n">
         <v>73.81</v>
       </c>
       <c r="K51" s="5">
-        <f>IF(AND(ISNUMBER(J51),ISNUMBER(J52)),(J51/J52-1)*100,"")</f>
+        <f>IF(COUNT(J51:J52)=2,(J51/J52-1)*100,"")</f>
         <v/>
       </c>
       <c r="L51" s="5" t="n">
         <v>11.8269</v>
       </c>
       <c r="M51" s="5">
-        <f>IF(AND(ISNUMBER(L51),ISNUMBER(L52)),(L51/L52-1)*100,"")</f>
+        <f>IF(COUNT(L51:L52)=2,(L51/L52-1)*100,"")</f>
         <v/>
       </c>
       <c r="N51" s="5" t="n"/>
       <c r="O51" s="5">
-        <f>IF(AND(ISNUMBER(N51),ISNUMBER(N52)),(N51/N52-1)*100,"")</f>
+        <f>IF(COUNT(N51:N52)=2,(N51/N52-1)*100,"")</f>
         <v/>
       </c>
       <c r="P51" s="5" t="n"/>
       <c r="Q51" s="5">
-        <f>IF(AND(ISNUMBER(P51),ISNUMBER(P52)),(P51/P52-1)*100,"")</f>
+        <f>IF(COUNT(P51:P52)=2,(P51/P52-1)*100,"")</f>
         <v/>
       </c>
       <c r="R51" s="5" t="n"/>
       <c r="S51" s="5">
-        <f>IF(AND(ISNUMBER(R51),ISNUMBER(R52)),(R51/R52-1)*100,"")</f>
+        <f>IF(COUNT(R51:R52)=2,(R51/R52-1)*100,"")</f>
         <v/>
       </c>
       <c r="T51" s="5" t="n"/>
       <c r="U51" s="5">
-        <f>IF(AND(ISNUMBER(T51),ISNUMBER(T52)),(T51/T52-1)*100,"")</f>
+        <f>IF(COUNT(T51:T52)=2,(T51/T52-1)*100,"")</f>
         <v/>
       </c>
       <c r="V51" s="5" t="n"/>
@@ -5637,31 +5714,31 @@
         <v/>
       </c>
       <c r="X51" s="5">
+        <f>IF(AND(K51&lt;0,M51&gt;0),C50,"")</f>
+        <v/>
+      </c>
+      <c r="Y51" s="5">
         <f>IF(AND(G51&gt;0,I51&lt;0,K51&gt;0),C50,"")</f>
         <v/>
       </c>
-      <c r="Y51" s="5">
-        <f>IF(AND(K51&lt;0,M51&gt;0),C50,"")</f>
-        <v/>
-      </c>
       <c r="Z51" s="5">
-        <f>IF(AND(ISNUMBER(W51),0.549579&gt;=MAX(IF(ISNUMBER(X51),0.299732,-1),IF(ISNUMBER(Y51),0.323835,-1))),W51,IF(AND(ISNUMBER(X51),0.299732&gt;MAX(IF(ISNUMBER(W51),0.549579,-1),IF(ISNUMBER(Y51),0.323835,-1))),X51,IF(AND(ISNUMBER(Y51),0.323835&gt;MAX(IF(ISNUMBER(W51),0.549579,-1),IF(ISNUMBER(X51),0.299732,-1))),Y51,"")))</f>
+        <f>IF(W51&lt;&gt;"",W51,IF(X51&lt;&gt;"",X51,Y51))</f>
         <v/>
       </c>
       <c r="AA51" s="5">
+        <f>IF(AND(S51&gt;0,U51&lt;0),E50,"")</f>
+        <v/>
+      </c>
+      <c r="AB51" s="5">
         <f>IF(AND(O51&lt;=-1,E51&lt;0),E50,"")</f>
         <v/>
       </c>
-      <c r="AB51" s="5">
+      <c r="AC51" s="5">
         <f>IF(AND(Q51&gt;0,S51&gt;0),E50,"")</f>
         <v/>
       </c>
-      <c r="AC51" s="5">
-        <f>IF(AND(S51&gt;0,U51&lt;0),E50,"")</f>
-        <v/>
-      </c>
       <c r="AD51" s="5">
-        <f>IF(AND(ISNUMBER(AA51),0.408167&gt;=MAX(IF(ISNUMBER(AB51),0.31868,-1),IF(ISNUMBER(AC51),0.510996,-1))),AA51,IF(AND(ISNUMBER(AB51),0.31868&gt;MAX(IF(ISNUMBER(AA51),0.408167,-1),IF(ISNUMBER(AC51),0.510996,-1))),AB51,IF(AND(ISNUMBER(AC51),0.510996&gt;MAX(IF(ISNUMBER(AA51),0.408167,-1),IF(ISNUMBER(AB51),0.31868,-1))),AC51,"")))</f>
+        <f>IF(AA51&lt;&gt;"",AA51,IF(AB51&lt;&gt;"",AB51,AC51))</f>
         <v/>
       </c>
     </row>
@@ -5675,62 +5752,62 @@
         <v>160.13</v>
       </c>
       <c r="C52" s="5">
-        <f>IF(AND(ISNUMBER(B52),ISNUMBER(B53)),(B52/B53-1)*100,"")</f>
+        <f>IF(COUNT(B52:B53)=2,(B52/B53-1)*100,"")</f>
         <v/>
       </c>
       <c r="D52" s="5" t="n">
         <v>65.47969999999999</v>
       </c>
       <c r="E52" s="5">
-        <f>IF(AND(ISNUMBER(D52),ISNUMBER(D53)),(D52/D53-1)*100,"")</f>
+        <f>IF(COUNT(D52:D53)=2,(D52/D53-1)*100,"")</f>
         <v/>
       </c>
       <c r="F52" s="5" t="n">
         <v>78.86969999999999</v>
       </c>
       <c r="G52" s="5">
-        <f>IF(AND(ISNUMBER(F52),ISNUMBER(F53)),(F52/F53-1)*100,"")</f>
+        <f>IF(COUNT(F52:F53)=2,(F52/F53-1)*100,"")</f>
         <v/>
       </c>
       <c r="H52" s="5" t="n">
         <v>52.2769</v>
       </c>
       <c r="I52" s="5">
-        <f>IF(AND(ISNUMBER(H52),ISNUMBER(H53)),(H52/H53-1)*100,"")</f>
+        <f>IF(COUNT(H52:H53)=2,(H52/H53-1)*100,"")</f>
         <v/>
       </c>
       <c r="J52" s="5" t="n">
         <v>77.59</v>
       </c>
       <c r="K52" s="5">
-        <f>IF(AND(ISNUMBER(J52),ISNUMBER(J53)),(J52/J53-1)*100,"")</f>
+        <f>IF(COUNT(J52:J53)=2,(J52/J53-1)*100,"")</f>
         <v/>
       </c>
       <c r="L52" s="5" t="n">
         <v>5.0211</v>
       </c>
       <c r="M52" s="5">
-        <f>IF(AND(ISNUMBER(L52),ISNUMBER(L53)),(L52/L53-1)*100,"")</f>
+        <f>IF(COUNT(L52:L53)=2,(L52/L53-1)*100,"")</f>
         <v/>
       </c>
       <c r="N52" s="5" t="n"/>
       <c r="O52" s="5">
-        <f>IF(AND(ISNUMBER(N52),ISNUMBER(N53)),(N52/N53-1)*100,"")</f>
+        <f>IF(COUNT(N52:N53)=2,(N52/N53-1)*100,"")</f>
         <v/>
       </c>
       <c r="P52" s="5" t="n"/>
       <c r="Q52" s="5">
-        <f>IF(AND(ISNUMBER(P52),ISNUMBER(P53)),(P52/P53-1)*100,"")</f>
+        <f>IF(COUNT(P52:P53)=2,(P52/P53-1)*100,"")</f>
         <v/>
       </c>
       <c r="R52" s="5" t="n"/>
       <c r="S52" s="5">
-        <f>IF(AND(ISNUMBER(R52),ISNUMBER(R53)),(R52/R53-1)*100,"")</f>
+        <f>IF(COUNT(R52:R53)=2,(R52/R53-1)*100,"")</f>
         <v/>
       </c>
       <c r="T52" s="5" t="n"/>
       <c r="U52" s="5">
-        <f>IF(AND(ISNUMBER(T52),ISNUMBER(T53)),(T52/T53-1)*100,"")</f>
+        <f>IF(COUNT(T52:T53)=2,(T52/T53-1)*100,"")</f>
         <v/>
       </c>
       <c r="V52" s="5" t="n"/>
@@ -5739,31 +5816,31 @@
         <v/>
       </c>
       <c r="X52" s="5">
+        <f>IF(AND(K52&lt;0,M52&gt;0),C51,"")</f>
+        <v/>
+      </c>
+      <c r="Y52" s="5">
         <f>IF(AND(G52&gt;0,I52&lt;0,K52&gt;0),C51,"")</f>
         <v/>
       </c>
-      <c r="Y52" s="5">
-        <f>IF(AND(K52&lt;0,M52&gt;0),C51,"")</f>
-        <v/>
-      </c>
       <c r="Z52" s="5">
-        <f>IF(AND(ISNUMBER(W52),0.549579&gt;=MAX(IF(ISNUMBER(X52),0.299732,-1),IF(ISNUMBER(Y52),0.323835,-1))),W52,IF(AND(ISNUMBER(X52),0.299732&gt;MAX(IF(ISNUMBER(W52),0.549579,-1),IF(ISNUMBER(Y52),0.323835,-1))),X52,IF(AND(ISNUMBER(Y52),0.323835&gt;MAX(IF(ISNUMBER(W52),0.549579,-1),IF(ISNUMBER(X52),0.299732,-1))),Y52,"")))</f>
+        <f>IF(W52&lt;&gt;"",W52,IF(X52&lt;&gt;"",X52,Y52))</f>
         <v/>
       </c>
       <c r="AA52" s="5">
+        <f>IF(AND(S52&gt;0,U52&lt;0),E51,"")</f>
+        <v/>
+      </c>
+      <c r="AB52" s="5">
         <f>IF(AND(O52&lt;=-1,E52&lt;0),E51,"")</f>
         <v/>
       </c>
-      <c r="AB52" s="5">
+      <c r="AC52" s="5">
         <f>IF(AND(Q52&gt;0,S52&gt;0),E51,"")</f>
         <v/>
       </c>
-      <c r="AC52" s="5">
-        <f>IF(AND(S52&gt;0,U52&lt;0),E51,"")</f>
-        <v/>
-      </c>
       <c r="AD52" s="5">
-        <f>IF(AND(ISNUMBER(AA52),0.408167&gt;=MAX(IF(ISNUMBER(AB52),0.31868,-1),IF(ISNUMBER(AC52),0.510996,-1))),AA52,IF(AND(ISNUMBER(AB52),0.31868&gt;MAX(IF(ISNUMBER(AA52),0.408167,-1),IF(ISNUMBER(AC52),0.510996,-1))),AB52,IF(AND(ISNUMBER(AC52),0.510996&gt;MAX(IF(ISNUMBER(AA52),0.408167,-1),IF(ISNUMBER(AB52),0.31868,-1))),AC52,"")))</f>
+        <f>IF(AA52&lt;&gt;"",AA52,IF(AB52&lt;&gt;"",AB52,AC52))</f>
         <v/>
       </c>
     </row>
@@ -5777,62 +5854,62 @@
         <v>163.85</v>
       </c>
       <c r="C53" s="5">
-        <f>IF(AND(ISNUMBER(B53),ISNUMBER(B54)),(B53/B54-1)*100,"")</f>
+        <f>IF(COUNT(B53:B54)=2,(B53/B54-1)*100,"")</f>
         <v/>
       </c>
       <c r="D53" s="5" t="n">
         <v>65.41</v>
       </c>
       <c r="E53" s="5">
-        <f>IF(AND(ISNUMBER(D53),ISNUMBER(D54)),(D53/D54-1)*100,"")</f>
+        <f>IF(COUNT(D53:D54)=2,(D53/D54-1)*100,"")</f>
         <v/>
       </c>
       <c r="F53" s="5" t="n">
         <v>78.79049999999999</v>
       </c>
       <c r="G53" s="5">
-        <f>IF(AND(ISNUMBER(F53),ISNUMBER(F54)),(F53/F54-1)*100,"")</f>
+        <f>IF(COUNT(F53:F54)=2,(F53/F54-1)*100,"")</f>
         <v/>
       </c>
       <c r="H53" s="5" t="n">
         <v>51.7886</v>
       </c>
       <c r="I53" s="5">
-        <f>IF(AND(ISNUMBER(H53),ISNUMBER(H54)),(H53/H54-1)*100,"")</f>
+        <f>IF(COUNT(H53:H54)=2,(H53/H54-1)*100,"")</f>
         <v/>
       </c>
       <c r="J53" s="5" t="n">
         <v>78.67</v>
       </c>
       <c r="K53" s="5">
-        <f>IF(AND(ISNUMBER(J53),ISNUMBER(J54)),(J53/J54-1)*100,"")</f>
+        <f>IF(COUNT(J53:J54)=2,(J53/J54-1)*100,"")</f>
         <v/>
       </c>
       <c r="L53" s="5" t="n">
         <v>-12.0409</v>
       </c>
       <c r="M53" s="5">
-        <f>IF(AND(ISNUMBER(L53),ISNUMBER(L54)),(L53/L54-1)*100,"")</f>
+        <f>IF(COUNT(L53:L54)=2,(L53/L54-1)*100,"")</f>
         <v/>
       </c>
       <c r="N53" s="5" t="n"/>
       <c r="O53" s="5">
-        <f>IF(AND(ISNUMBER(N53),ISNUMBER(N54)),(N53/N54-1)*100,"")</f>
+        <f>IF(COUNT(N53:N54)=2,(N53/N54-1)*100,"")</f>
         <v/>
       </c>
       <c r="P53" s="5" t="n"/>
       <c r="Q53" s="5">
-        <f>IF(AND(ISNUMBER(P53),ISNUMBER(P54)),(P53/P54-1)*100,"")</f>
+        <f>IF(COUNT(P53:P54)=2,(P53/P54-1)*100,"")</f>
         <v/>
       </c>
       <c r="R53" s="5" t="n"/>
       <c r="S53" s="5">
-        <f>IF(AND(ISNUMBER(R53),ISNUMBER(R54)),(R53/R54-1)*100,"")</f>
+        <f>IF(COUNT(R53:R54)=2,(R53/R54-1)*100,"")</f>
         <v/>
       </c>
       <c r="T53" s="5" t="n"/>
       <c r="U53" s="5">
-        <f>IF(AND(ISNUMBER(T53),ISNUMBER(T54)),(T53/T54-1)*100,"")</f>
+        <f>IF(COUNT(T53:T54)=2,(T53/T54-1)*100,"")</f>
         <v/>
       </c>
       <c r="V53" s="5" t="n"/>
@@ -5841,31 +5918,31 @@
         <v/>
       </c>
       <c r="X53" s="5">
+        <f>IF(AND(K53&lt;0,M53&gt;0),C52,"")</f>
+        <v/>
+      </c>
+      <c r="Y53" s="5">
         <f>IF(AND(G53&gt;0,I53&lt;0,K53&gt;0),C52,"")</f>
         <v/>
       </c>
-      <c r="Y53" s="5">
-        <f>IF(AND(K53&lt;0,M53&gt;0),C52,"")</f>
-        <v/>
-      </c>
       <c r="Z53" s="5">
-        <f>IF(AND(ISNUMBER(W53),0.549579&gt;=MAX(IF(ISNUMBER(X53),0.299732,-1),IF(ISNUMBER(Y53),0.323835,-1))),W53,IF(AND(ISNUMBER(X53),0.299732&gt;MAX(IF(ISNUMBER(W53),0.549579,-1),IF(ISNUMBER(Y53),0.323835,-1))),X53,IF(AND(ISNUMBER(Y53),0.323835&gt;MAX(IF(ISNUMBER(W53),0.549579,-1),IF(ISNUMBER(X53),0.299732,-1))),Y53,"")))</f>
+        <f>IF(W53&lt;&gt;"",W53,IF(X53&lt;&gt;"",X53,Y53))</f>
         <v/>
       </c>
       <c r="AA53" s="5">
+        <f>IF(AND(S53&gt;0,U53&lt;0),E52,"")</f>
+        <v/>
+      </c>
+      <c r="AB53" s="5">
         <f>IF(AND(O53&lt;=-1,E53&lt;0),E52,"")</f>
         <v/>
       </c>
-      <c r="AB53" s="5">
+      <c r="AC53" s="5">
         <f>IF(AND(Q53&gt;0,S53&gt;0),E52,"")</f>
         <v/>
       </c>
-      <c r="AC53" s="5">
-        <f>IF(AND(S53&gt;0,U53&lt;0),E52,"")</f>
-        <v/>
-      </c>
       <c r="AD53" s="5">
-        <f>IF(AND(ISNUMBER(AA53),0.408167&gt;=MAX(IF(ISNUMBER(AB53),0.31868,-1),IF(ISNUMBER(AC53),0.510996,-1))),AA53,IF(AND(ISNUMBER(AB53),0.31868&gt;MAX(IF(ISNUMBER(AA53),0.408167,-1),IF(ISNUMBER(AC53),0.510996,-1))),AB53,IF(AND(ISNUMBER(AC53),0.510996&gt;MAX(IF(ISNUMBER(AA53),0.408167,-1),IF(ISNUMBER(AB53),0.31868,-1))),AC53,"")))</f>
+        <f>IF(AA53&lt;&gt;"",AA53,IF(AB53&lt;&gt;"",AB53,AC53))</f>
         <v/>
       </c>
     </row>
@@ -5879,62 +5956,62 @@
         <v>158.91</v>
       </c>
       <c r="C54" s="5">
-        <f>IF(AND(ISNUMBER(B54),ISNUMBER(B55)),(B54/B55-1)*100,"")</f>
+        <f>IF(COUNT(B54:B55)=2,(B54/B55-1)*100,"")</f>
         <v/>
       </c>
       <c r="D54" s="5" t="n">
         <v>64.256</v>
       </c>
       <c r="E54" s="5">
-        <f>IF(AND(ISNUMBER(D54),ISNUMBER(D55)),(D54/D55-1)*100,"")</f>
+        <f>IF(COUNT(D54:D55)=2,(D54/D55-1)*100,"")</f>
         <v/>
       </c>
       <c r="F54" s="5" t="n">
         <v>78.6815</v>
       </c>
       <c r="G54" s="5">
-        <f>IF(AND(ISNUMBER(F54),ISNUMBER(F55)),(F54/F55-1)*100,"")</f>
+        <f>IF(COUNT(F54:F55)=2,(F54/F55-1)*100,"")</f>
         <v/>
       </c>
       <c r="H54" s="5" t="n">
         <v>52.1174</v>
       </c>
       <c r="I54" s="5">
-        <f>IF(AND(ISNUMBER(H54),ISNUMBER(H55)),(H54/H55-1)*100,"")</f>
+        <f>IF(COUNT(H54:H55)=2,(H54/H55-1)*100,"")</f>
         <v/>
       </c>
       <c r="J54" s="5" t="n">
         <v>78.84</v>
       </c>
       <c r="K54" s="5">
-        <f>IF(AND(ISNUMBER(J54),ISNUMBER(J55)),(J54/J55-1)*100,"")</f>
+        <f>IF(COUNT(J54:J55)=2,(J54/J55-1)*100,"")</f>
         <v/>
       </c>
       <c r="L54" s="5" t="n">
         <v>39.6753</v>
       </c>
       <c r="M54" s="5">
-        <f>IF(AND(ISNUMBER(L54),ISNUMBER(L55)),(L54/L55-1)*100,"")</f>
+        <f>IF(COUNT(L54:L55)=2,(L54/L55-1)*100,"")</f>
         <v/>
       </c>
       <c r="N54" s="5" t="n"/>
       <c r="O54" s="5">
-        <f>IF(AND(ISNUMBER(N54),ISNUMBER(N55)),(N54/N55-1)*100,"")</f>
+        <f>IF(COUNT(N54:N55)=2,(N54/N55-1)*100,"")</f>
         <v/>
       </c>
       <c r="P54" s="5" t="n"/>
       <c r="Q54" s="5">
-        <f>IF(AND(ISNUMBER(P54),ISNUMBER(P55)),(P54/P55-1)*100,"")</f>
+        <f>IF(COUNT(P54:P55)=2,(P54/P55-1)*100,"")</f>
         <v/>
       </c>
       <c r="R54" s="5" t="n"/>
       <c r="S54" s="5">
-        <f>IF(AND(ISNUMBER(R54),ISNUMBER(R55)),(R54/R55-1)*100,"")</f>
+        <f>IF(COUNT(R54:R55)=2,(R54/R55-1)*100,"")</f>
         <v/>
       </c>
       <c r="T54" s="5" t="n"/>
       <c r="U54" s="5">
-        <f>IF(AND(ISNUMBER(T54),ISNUMBER(T55)),(T54/T55-1)*100,"")</f>
+        <f>IF(COUNT(T54:T55)=2,(T54/T55-1)*100,"")</f>
         <v/>
       </c>
       <c r="V54" s="5" t="n"/>
@@ -5943,31 +6020,31 @@
         <v/>
       </c>
       <c r="X54" s="5">
+        <f>IF(AND(K54&lt;0,M54&gt;0),C53,"")</f>
+        <v/>
+      </c>
+      <c r="Y54" s="5">
         <f>IF(AND(G54&gt;0,I54&lt;0,K54&gt;0),C53,"")</f>
         <v/>
       </c>
-      <c r="Y54" s="5">
-        <f>IF(AND(K54&lt;0,M54&gt;0),C53,"")</f>
-        <v/>
-      </c>
       <c r="Z54" s="5">
-        <f>IF(AND(ISNUMBER(W54),0.549579&gt;=MAX(IF(ISNUMBER(X54),0.299732,-1),IF(ISNUMBER(Y54),0.323835,-1))),W54,IF(AND(ISNUMBER(X54),0.299732&gt;MAX(IF(ISNUMBER(W54),0.549579,-1),IF(ISNUMBER(Y54),0.323835,-1))),X54,IF(AND(ISNUMBER(Y54),0.323835&gt;MAX(IF(ISNUMBER(W54),0.549579,-1),IF(ISNUMBER(X54),0.299732,-1))),Y54,"")))</f>
+        <f>IF(W54&lt;&gt;"",W54,IF(X54&lt;&gt;"",X54,Y54))</f>
         <v/>
       </c>
       <c r="AA54" s="5">
+        <f>IF(AND(S54&gt;0,U54&lt;0),E53,"")</f>
+        <v/>
+      </c>
+      <c r="AB54" s="5">
         <f>IF(AND(O54&lt;=-1,E54&lt;0),E53,"")</f>
         <v/>
       </c>
-      <c r="AB54" s="5">
+      <c r="AC54" s="5">
         <f>IF(AND(Q54&gt;0,S54&gt;0),E53,"")</f>
         <v/>
       </c>
-      <c r="AC54" s="5">
-        <f>IF(AND(S54&gt;0,U54&lt;0),E53,"")</f>
-        <v/>
-      </c>
       <c r="AD54" s="5">
-        <f>IF(AND(ISNUMBER(AA54),0.408167&gt;=MAX(IF(ISNUMBER(AB54),0.31868,-1),IF(ISNUMBER(AC54),0.510996,-1))),AA54,IF(AND(ISNUMBER(AB54),0.31868&gt;MAX(IF(ISNUMBER(AA54),0.408167,-1),IF(ISNUMBER(AC54),0.510996,-1))),AB54,IF(AND(ISNUMBER(AC54),0.510996&gt;MAX(IF(ISNUMBER(AA54),0.408167,-1),IF(ISNUMBER(AB54),0.31868,-1))),AC54,"")))</f>
+        <f>IF(AA54&lt;&gt;"",AA54,IF(AB54&lt;&gt;"",AB54,AC54))</f>
         <v/>
       </c>
     </row>
@@ -5981,62 +6058,62 @@
         <v>175.71</v>
       </c>
       <c r="C55" s="5">
-        <f>IF(AND(ISNUMBER(B55),ISNUMBER(B56)),(B55/B56-1)*100,"")</f>
+        <f>IF(COUNT(B55:B56)=2,(B55/B56-1)*100,"")</f>
         <v/>
       </c>
       <c r="D55" s="5" t="n">
         <v>68.7427</v>
       </c>
       <c r="E55" s="5">
-        <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56)),(D55/D56-1)*100,"")</f>
+        <f>IF(COUNT(D55:D56)=2,(D55/D56-1)*100,"")</f>
         <v/>
       </c>
       <c r="F55" s="5" t="n">
         <v>79.07769999999999</v>
       </c>
       <c r="G55" s="5">
-        <f>IF(AND(ISNUMBER(F55),ISNUMBER(F56)),(F55/F56-1)*100,"")</f>
+        <f>IF(COUNT(F55:F56)=2,(F55/F56-1)*100,"")</f>
         <v/>
       </c>
       <c r="H55" s="5" t="n">
         <v>52.0078</v>
       </c>
       <c r="I55" s="5">
-        <f>IF(AND(ISNUMBER(H55),ISNUMBER(H56)),(H55/H56-1)*100,"")</f>
+        <f>IF(COUNT(H55:H56)=2,(H55/H56-1)*100,"")</f>
         <v/>
       </c>
       <c r="J55" s="5" t="n">
         <v>86.40000000000001</v>
       </c>
       <c r="K55" s="5">
-        <f>IF(AND(ISNUMBER(J55),ISNUMBER(J56)),(J55/J56-1)*100,"")</f>
+        <f>IF(COUNT(J55:J56)=2,(J55/J56-1)*100,"")</f>
         <v/>
       </c>
       <c r="L55" s="5" t="n">
         <v>-4.1096</v>
       </c>
       <c r="M55" s="5">
-        <f>IF(AND(ISNUMBER(L55),ISNUMBER(L56)),(L55/L56-1)*100,"")</f>
+        <f>IF(COUNT(L55:L56)=2,(L55/L56-1)*100,"")</f>
         <v/>
       </c>
       <c r="N55" s="5" t="n"/>
       <c r="O55" s="5">
-        <f>IF(AND(ISNUMBER(N55),ISNUMBER(N56)),(N55/N56-1)*100,"")</f>
+        <f>IF(COUNT(N55:N56)=2,(N55/N56-1)*100,"")</f>
         <v/>
       </c>
       <c r="P55" s="5" t="n"/>
       <c r="Q55" s="5">
-        <f>IF(AND(ISNUMBER(P55),ISNUMBER(P56)),(P55/P56-1)*100,"")</f>
+        <f>IF(COUNT(P55:P56)=2,(P55/P56-1)*100,"")</f>
         <v/>
       </c>
       <c r="R55" s="5" t="n"/>
       <c r="S55" s="5">
-        <f>IF(AND(ISNUMBER(R55),ISNUMBER(R56)),(R55/R56-1)*100,"")</f>
+        <f>IF(COUNT(R55:R56)=2,(R55/R56-1)*100,"")</f>
         <v/>
       </c>
       <c r="T55" s="5" t="n"/>
       <c r="U55" s="5">
-        <f>IF(AND(ISNUMBER(T55),ISNUMBER(T56)),(T55/T56-1)*100,"")</f>
+        <f>IF(COUNT(T55:T56)=2,(T55/T56-1)*100,"")</f>
         <v/>
       </c>
       <c r="V55" s="5" t="n"/>
@@ -6045,31 +6122,31 @@
         <v/>
       </c>
       <c r="X55" s="5">
+        <f>IF(AND(K55&lt;0,M55&gt;0),C54,"")</f>
+        <v/>
+      </c>
+      <c r="Y55" s="5">
         <f>IF(AND(G55&gt;0,I55&lt;0,K55&gt;0),C54,"")</f>
         <v/>
       </c>
-      <c r="Y55" s="5">
-        <f>IF(AND(K55&lt;0,M55&gt;0),C54,"")</f>
-        <v/>
-      </c>
       <c r="Z55" s="5">
-        <f>IF(AND(ISNUMBER(W55),0.549579&gt;=MAX(IF(ISNUMBER(X55),0.299732,-1),IF(ISNUMBER(Y55),0.323835,-1))),W55,IF(AND(ISNUMBER(X55),0.299732&gt;MAX(IF(ISNUMBER(W55),0.549579,-1),IF(ISNUMBER(Y55),0.323835,-1))),X55,IF(AND(ISNUMBER(Y55),0.323835&gt;MAX(IF(ISNUMBER(W55),0.549579,-1),IF(ISNUMBER(X55),0.299732,-1))),Y55,"")))</f>
+        <f>IF(W55&lt;&gt;"",W55,IF(X55&lt;&gt;"",X55,Y55))</f>
         <v/>
       </c>
       <c r="AA55" s="5">
+        <f>IF(AND(S55&gt;0,U55&lt;0),E54,"")</f>
+        <v/>
+      </c>
+      <c r="AB55" s="5">
         <f>IF(AND(O55&lt;=-1,E55&lt;0),E54,"")</f>
         <v/>
       </c>
-      <c r="AB55" s="5">
+      <c r="AC55" s="5">
         <f>IF(AND(Q55&gt;0,S55&gt;0),E54,"")</f>
         <v/>
       </c>
-      <c r="AC55" s="5">
-        <f>IF(AND(S55&gt;0,U55&lt;0),E54,"")</f>
-        <v/>
-      </c>
       <c r="AD55" s="5">
-        <f>IF(AND(ISNUMBER(AA55),0.408167&gt;=MAX(IF(ISNUMBER(AB55),0.31868,-1),IF(ISNUMBER(AC55),0.510996,-1))),AA55,IF(AND(ISNUMBER(AB55),0.31868&gt;MAX(IF(ISNUMBER(AA55),0.408167,-1),IF(ISNUMBER(AC55),0.510996,-1))),AB55,IF(AND(ISNUMBER(AC55),0.510996&gt;MAX(IF(ISNUMBER(AA55),0.408167,-1),IF(ISNUMBER(AB55),0.31868,-1))),AC55,"")))</f>
+        <f>IF(AA55&lt;&gt;"",AA55,IF(AB55&lt;&gt;"",AB55,AC55))</f>
         <v/>
       </c>
     </row>
@@ -6083,62 +6160,62 @@
         <v>177.54</v>
       </c>
       <c r="C56" s="5">
-        <f>IF(AND(ISNUMBER(B56),ISNUMBER(B57)),(B56/B57-1)*100,"")</f>
+        <f>IF(COUNT(B56:B57)=2,(B56/B57-1)*100,"")</f>
         <v/>
       </c>
       <c r="D56" s="5" t="n">
         <v>69.55840000000001</v>
       </c>
       <c r="E56" s="5">
-        <f>IF(AND(ISNUMBER(D56),ISNUMBER(D57)),(D56/D57-1)*100,"")</f>
+        <f>IF(COUNT(D56:D57)=2,(D56/D57-1)*100,"")</f>
         <v/>
       </c>
       <c r="F56" s="5" t="n">
         <v>78.92910000000001</v>
       </c>
       <c r="G56" s="5">
-        <f>IF(AND(ISNUMBER(F56),ISNUMBER(F57)),(F56/F57-1)*100,"")</f>
+        <f>IF(COUNT(F56:F57)=2,(F56/F57-1)*100,"")</f>
         <v/>
       </c>
       <c r="H56" s="5" t="n">
         <v>50.6924</v>
       </c>
       <c r="I56" s="5">
-        <f>IF(AND(ISNUMBER(H56),ISNUMBER(H57)),(H56/H57-1)*100,"")</f>
+        <f>IF(COUNT(H56:H57)=2,(H56/H57-1)*100,"")</f>
         <v/>
       </c>
       <c r="J56" s="5" t="n">
         <v>85</v>
       </c>
       <c r="K56" s="5">
-        <f>IF(AND(ISNUMBER(J56),ISNUMBER(J57)),(J56/J57-1)*100,"")</f>
+        <f>IF(COUNT(J56:J57)=2,(J56/J57-1)*100,"")</f>
         <v/>
       </c>
       <c r="L56" s="5" t="n">
         <v>1.8389</v>
       </c>
       <c r="M56" s="5">
-        <f>IF(AND(ISNUMBER(L56),ISNUMBER(L57)),(L56/L57-1)*100,"")</f>
+        <f>IF(COUNT(L56:L57)=2,(L56/L57-1)*100,"")</f>
         <v/>
       </c>
       <c r="N56" s="5" t="n"/>
       <c r="O56" s="5">
-        <f>IF(AND(ISNUMBER(N56),ISNUMBER(N57)),(N56/N57-1)*100,"")</f>
+        <f>IF(COUNT(N56:N57)=2,(N56/N57-1)*100,"")</f>
         <v/>
       </c>
       <c r="P56" s="5" t="n"/>
       <c r="Q56" s="5">
-        <f>IF(AND(ISNUMBER(P56),ISNUMBER(P57)),(P56/P57-1)*100,"")</f>
+        <f>IF(COUNT(P56:P57)=2,(P56/P57-1)*100,"")</f>
         <v/>
       </c>
       <c r="R56" s="5" t="n"/>
       <c r="S56" s="5">
-        <f>IF(AND(ISNUMBER(R56),ISNUMBER(R57)),(R56/R57-1)*100,"")</f>
+        <f>IF(COUNT(R56:R57)=2,(R56/R57-1)*100,"")</f>
         <v/>
       </c>
       <c r="T56" s="5" t="n"/>
       <c r="U56" s="5">
-        <f>IF(AND(ISNUMBER(T56),ISNUMBER(T57)),(T56/T57-1)*100,"")</f>
+        <f>IF(COUNT(T56:T57)=2,(T56/T57-1)*100,"")</f>
         <v/>
       </c>
       <c r="V56" s="5" t="n"/>
@@ -6147,31 +6224,31 @@
         <v/>
       </c>
       <c r="X56" s="5">
+        <f>IF(AND(K56&lt;0,M56&gt;0),C55,"")</f>
+        <v/>
+      </c>
+      <c r="Y56" s="5">
         <f>IF(AND(G56&gt;0,I56&lt;0,K56&gt;0),C55,"")</f>
         <v/>
       </c>
-      <c r="Y56" s="5">
-        <f>IF(AND(K56&lt;0,M56&gt;0),C55,"")</f>
-        <v/>
-      </c>
       <c r="Z56" s="5">
-        <f>IF(AND(ISNUMBER(W56),0.549579&gt;=MAX(IF(ISNUMBER(X56),0.299732,-1),IF(ISNUMBER(Y56),0.323835,-1))),W56,IF(AND(ISNUMBER(X56),0.299732&gt;MAX(IF(ISNUMBER(W56),0.549579,-1),IF(ISNUMBER(Y56),0.323835,-1))),X56,IF(AND(ISNUMBER(Y56),0.323835&gt;MAX(IF(ISNUMBER(W56),0.549579,-1),IF(ISNUMBER(X56),0.299732,-1))),Y56,"")))</f>
+        <f>IF(W56&lt;&gt;"",W56,IF(X56&lt;&gt;"",X56,Y56))</f>
         <v/>
       </c>
       <c r="AA56" s="5">
+        <f>IF(AND(S56&gt;0,U56&lt;0),E55,"")</f>
+        <v/>
+      </c>
+      <c r="AB56" s="5">
         <f>IF(AND(O56&lt;=-1,E56&lt;0),E55,"")</f>
         <v/>
       </c>
-      <c r="AB56" s="5">
+      <c r="AC56" s="5">
         <f>IF(AND(Q56&gt;0,S56&gt;0),E55,"")</f>
         <v/>
       </c>
-      <c r="AC56" s="5">
-        <f>IF(AND(S56&gt;0,U56&lt;0),E55,"")</f>
-        <v/>
-      </c>
       <c r="AD56" s="5">
-        <f>IF(AND(ISNUMBER(AA56),0.408167&gt;=MAX(IF(ISNUMBER(AB56),0.31868,-1),IF(ISNUMBER(AC56),0.510996,-1))),AA56,IF(AND(ISNUMBER(AB56),0.31868&gt;MAX(IF(ISNUMBER(AA56),0.408167,-1),IF(ISNUMBER(AC56),0.510996,-1))),AB56,IF(AND(ISNUMBER(AC56),0.510996&gt;MAX(IF(ISNUMBER(AA56),0.408167,-1),IF(ISNUMBER(AB56),0.31868,-1))),AC56,"")))</f>
+        <f>IF(AA56&lt;&gt;"",AA56,IF(AB56&lt;&gt;"",AB56,AC56))</f>
         <v/>
       </c>
     </row>
@@ -6185,62 +6262,62 @@
         <v>178.58</v>
       </c>
       <c r="C57" s="5">
-        <f>IF(AND(ISNUMBER(B57),ISNUMBER(B58)),(B57/B58-1)*100,"")</f>
+        <f>IF(COUNT(B57:B58)=2,(B57/B58-1)*100,"")</f>
         <v/>
       </c>
       <c r="D57" s="5" t="n">
         <v>70.43389999999999</v>
       </c>
       <c r="E57" s="5">
-        <f>IF(AND(ISNUMBER(D57),ISNUMBER(D58)),(D57/D58-1)*100,"")</f>
+        <f>IF(COUNT(D57:D58)=2,(D57/D58-1)*100,"")</f>
         <v/>
       </c>
       <c r="F57" s="5" t="n">
         <v>79.14709999999999</v>
       </c>
       <c r="G57" s="5">
-        <f>IF(AND(ISNUMBER(F57),ISNUMBER(F58)),(F57/F58-1)*100,"")</f>
+        <f>IF(COUNT(F57:F58)=2,(F57/F58-1)*100,"")</f>
         <v/>
       </c>
       <c r="H57" s="5" t="n">
         <v>51.2804</v>
       </c>
       <c r="I57" s="5">
-        <f>IF(AND(ISNUMBER(H57),ISNUMBER(H58)),(H57/H58-1)*100,"")</f>
+        <f>IF(COUNT(H57:H58)=2,(H57/H58-1)*100,"")</f>
         <v/>
       </c>
       <c r="J57" s="5" t="n">
         <v>88.05</v>
       </c>
       <c r="K57" s="5">
-        <f>IF(AND(ISNUMBER(J57),ISNUMBER(J58)),(J57/J58-1)*100,"")</f>
+        <f>IF(COUNT(J57:J58)=2,(J57/J58-1)*100,"")</f>
         <v/>
       </c>
       <c r="L57" s="5" t="n">
         <v>-1.7445</v>
       </c>
       <c r="M57" s="5">
-        <f>IF(AND(ISNUMBER(L57),ISNUMBER(L58)),(L57/L58-1)*100,"")</f>
+        <f>IF(COUNT(L57:L58)=2,(L57/L58-1)*100,"")</f>
         <v/>
       </c>
       <c r="N57" s="5" t="n"/>
       <c r="O57" s="5">
-        <f>IF(AND(ISNUMBER(N57),ISNUMBER(N58)),(N57/N58-1)*100,"")</f>
+        <f>IF(COUNT(N57:N58)=2,(N57/N58-1)*100,"")</f>
         <v/>
       </c>
       <c r="P57" s="5" t="n"/>
       <c r="Q57" s="5">
-        <f>IF(AND(ISNUMBER(P57),ISNUMBER(P58)),(P57/P58-1)*100,"")</f>
+        <f>IF(COUNT(P57:P58)=2,(P57/P58-1)*100,"")</f>
         <v/>
       </c>
       <c r="R57" s="5" t="n"/>
       <c r="S57" s="5">
-        <f>IF(AND(ISNUMBER(R57),ISNUMBER(R58)),(R57/R58-1)*100,"")</f>
+        <f>IF(COUNT(R57:R58)=2,(R57/R58-1)*100,"")</f>
         <v/>
       </c>
       <c r="T57" s="5" t="n"/>
       <c r="U57" s="5">
-        <f>IF(AND(ISNUMBER(T57),ISNUMBER(T58)),(T57/T58-1)*100,"")</f>
+        <f>IF(COUNT(T57:T58)=2,(T57/T58-1)*100,"")</f>
         <v/>
       </c>
       <c r="V57" s="5" t="n"/>
@@ -6249,31 +6326,31 @@
         <v/>
       </c>
       <c r="X57" s="5">
+        <f>IF(AND(K57&lt;0,M57&gt;0),C56,"")</f>
+        <v/>
+      </c>
+      <c r="Y57" s="5">
         <f>IF(AND(G57&gt;0,I57&lt;0,K57&gt;0),C56,"")</f>
         <v/>
       </c>
-      <c r="Y57" s="5">
-        <f>IF(AND(K57&lt;0,M57&gt;0),C56,"")</f>
-        <v/>
-      </c>
       <c r="Z57" s="5">
-        <f>IF(AND(ISNUMBER(W57),0.549579&gt;=MAX(IF(ISNUMBER(X57),0.299732,-1),IF(ISNUMBER(Y57),0.323835,-1))),W57,IF(AND(ISNUMBER(X57),0.299732&gt;MAX(IF(ISNUMBER(W57),0.549579,-1),IF(ISNUMBER(Y57),0.323835,-1))),X57,IF(AND(ISNUMBER(Y57),0.323835&gt;MAX(IF(ISNUMBER(W57),0.549579,-1),IF(ISNUMBER(X57),0.299732,-1))),Y57,"")))</f>
+        <f>IF(W57&lt;&gt;"",W57,IF(X57&lt;&gt;"",X57,Y57))</f>
         <v/>
       </c>
       <c r="AA57" s="5">
+        <f>IF(AND(S57&gt;0,U57&lt;0),E56,"")</f>
+        <v/>
+      </c>
+      <c r="AB57" s="5">
         <f>IF(AND(O57&lt;=-1,E57&lt;0),E56,"")</f>
         <v/>
       </c>
-      <c r="AB57" s="5">
+      <c r="AC57" s="5">
         <f>IF(AND(Q57&gt;0,S57&gt;0),E56,"")</f>
         <v/>
       </c>
-      <c r="AC57" s="5">
-        <f>IF(AND(S57&gt;0,U57&lt;0),E56,"")</f>
-        <v/>
-      </c>
       <c r="AD57" s="5">
-        <f>IF(AND(ISNUMBER(AA57),0.408167&gt;=MAX(IF(ISNUMBER(AB57),0.31868,-1),IF(ISNUMBER(AC57),0.510996,-1))),AA57,IF(AND(ISNUMBER(AB57),0.31868&gt;MAX(IF(ISNUMBER(AA57),0.408167,-1),IF(ISNUMBER(AC57),0.510996,-1))),AB57,IF(AND(ISNUMBER(AC57),0.510996&gt;MAX(IF(ISNUMBER(AA57),0.408167,-1),IF(ISNUMBER(AB57),0.31868,-1))),AC57,"")))</f>
+        <f>IF(AA57&lt;&gt;"",AA57,IF(AB57&lt;&gt;"",AB57,AC57))</f>
         <v/>
       </c>
     </row>
@@ -6287,62 +6364,62 @@
         <v>176.92</v>
       </c>
       <c r="C58" s="5">
-        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B59)),(B58/B59-1)*100,"")</f>
+        <f>IF(COUNT(B58:B59)=2,(B58/B59-1)*100,"")</f>
         <v/>
       </c>
       <c r="D58" s="5" t="n">
         <v>69.7176</v>
       </c>
       <c r="E58" s="5">
-        <f>IF(AND(ISNUMBER(D58),ISNUMBER(D59)),(D58/D59-1)*100,"")</f>
+        <f>IF(COUNT(D58:D59)=2,(D58/D59-1)*100,"")</f>
         <v/>
       </c>
       <c r="F58" s="5" t="n">
         <v>79.08759999999999</v>
       </c>
       <c r="G58" s="5">
-        <f>IF(AND(ISNUMBER(F58),ISNUMBER(F59)),(F58/F59-1)*100,"")</f>
+        <f>IF(COUNT(F58:F59)=2,(F58/F59-1)*100,"")</f>
         <v/>
       </c>
       <c r="H58" s="5" t="n">
         <v>51.2505</v>
       </c>
       <c r="I58" s="5">
-        <f>IF(AND(ISNUMBER(H58),ISNUMBER(H59)),(H58/H59-1)*100,"")</f>
+        <f>IF(COUNT(H58:H59)=2,(H58/H59-1)*100,"")</f>
         <v/>
       </c>
       <c r="J58" s="5" t="n">
         <v>86.68000000000001</v>
       </c>
       <c r="K58" s="5">
-        <f>IF(AND(ISNUMBER(J58),ISNUMBER(J59)),(J58/J59-1)*100,"")</f>
+        <f>IF(COUNT(J58:J59)=2,(J58/J59-1)*100,"")</f>
         <v/>
       </c>
       <c r="L58" s="5" t="n">
         <v>4.765</v>
       </c>
       <c r="M58" s="5">
-        <f>IF(AND(ISNUMBER(L58),ISNUMBER(L59)),(L58/L59-1)*100,"")</f>
+        <f>IF(COUNT(L58:L59)=2,(L58/L59-1)*100,"")</f>
         <v/>
       </c>
       <c r="N58" s="5" t="n"/>
       <c r="O58" s="5">
-        <f>IF(AND(ISNUMBER(N58),ISNUMBER(N59)),(N58/N59-1)*100,"")</f>
+        <f>IF(COUNT(N58:N59)=2,(N58/N59-1)*100,"")</f>
         <v/>
       </c>
       <c r="P58" s="5" t="n"/>
       <c r="Q58" s="5">
-        <f>IF(AND(ISNUMBER(P58),ISNUMBER(P59)),(P58/P59-1)*100,"")</f>
+        <f>IF(COUNT(P58:P59)=2,(P58/P59-1)*100,"")</f>
         <v/>
       </c>
       <c r="R58" s="5" t="n"/>
       <c r="S58" s="5">
-        <f>IF(AND(ISNUMBER(R58),ISNUMBER(R59)),(R58/R59-1)*100,"")</f>
+        <f>IF(COUNT(R58:R59)=2,(R58/R59-1)*100,"")</f>
         <v/>
       </c>
       <c r="T58" s="5" t="n"/>
       <c r="U58" s="5">
-        <f>IF(AND(ISNUMBER(T58),ISNUMBER(T59)),(T58/T59-1)*100,"")</f>
+        <f>IF(COUNT(T58:T59)=2,(T58/T59-1)*100,"")</f>
         <v/>
       </c>
       <c r="V58" s="5" t="n"/>
@@ -6351,31 +6428,31 @@
         <v/>
       </c>
       <c r="X58" s="5">
+        <f>IF(AND(K58&lt;0,M58&gt;0),C57,"")</f>
+        <v/>
+      </c>
+      <c r="Y58" s="5">
         <f>IF(AND(G58&gt;0,I58&lt;0,K58&gt;0),C57,"")</f>
         <v/>
       </c>
-      <c r="Y58" s="5">
-        <f>IF(AND(K58&lt;0,M58&gt;0),C57,"")</f>
-        <v/>
-      </c>
       <c r="Z58" s="5">
-        <f>IF(AND(ISNUMBER(W58),0.549579&gt;=MAX(IF(ISNUMBER(X58),0.299732,-1),IF(ISNUMBER(Y58),0.323835,-1))),W58,IF(AND(ISNUMBER(X58),0.299732&gt;MAX(IF(ISNUMBER(W58),0.549579,-1),IF(ISNUMBER(Y58),0.323835,-1))),X58,IF(AND(ISNUMBER(Y58),0.323835&gt;MAX(IF(ISNUMBER(W58),0.549579,-1),IF(ISNUMBER(X58),0.299732,-1))),Y58,"")))</f>
+        <f>IF(W58&lt;&gt;"",W58,IF(X58&lt;&gt;"",X58,Y58))</f>
         <v/>
       </c>
       <c r="AA58" s="5">
+        <f>IF(AND(S58&gt;0,U58&lt;0),E57,"")</f>
+        <v/>
+      </c>
+      <c r="AB58" s="5">
         <f>IF(AND(O58&lt;=-1,E58&lt;0),E57,"")</f>
         <v/>
       </c>
-      <c r="AB58" s="5">
+      <c r="AC58" s="5">
         <f>IF(AND(Q58&gt;0,S58&gt;0),E57,"")</f>
         <v/>
       </c>
-      <c r="AC58" s="5">
-        <f>IF(AND(S58&gt;0,U58&lt;0),E57,"")</f>
-        <v/>
-      </c>
       <c r="AD58" s="5">
-        <f>IF(AND(ISNUMBER(AA58),0.408167&gt;=MAX(IF(ISNUMBER(AB58),0.31868,-1),IF(ISNUMBER(AC58),0.510996,-1))),AA58,IF(AND(ISNUMBER(AB58),0.31868&gt;MAX(IF(ISNUMBER(AA58),0.408167,-1),IF(ISNUMBER(AC58),0.510996,-1))),AB58,IF(AND(ISNUMBER(AC58),0.510996&gt;MAX(IF(ISNUMBER(AA58),0.408167,-1),IF(ISNUMBER(AB58),0.31868,-1))),AC58,"")))</f>
+        <f>IF(AA58&lt;&gt;"",AA58,IF(AB58&lt;&gt;"",AB58,AC58))</f>
         <v/>
       </c>
     </row>
@@ -6389,62 +6466,62 @@
         <v>174.92</v>
       </c>
       <c r="C59" s="5">
-        <f>IF(AND(ISNUMBER(B59),ISNUMBER(B60)),(B59/B60-1)*100,"")</f>
+        <f>IF(COUNT(B59:B60)=2,(B59/B60-1)*100,"")</f>
         <v/>
       </c>
       <c r="D59" s="5" t="n">
         <v>68.2453</v>
       </c>
       <c r="E59" s="5">
-        <f>IF(AND(ISNUMBER(D59),ISNUMBER(D60)),(D59/D60-1)*100,"")</f>
+        <f>IF(COUNT(D59:D60)=2,(D59/D60-1)*100,"")</f>
         <v/>
       </c>
       <c r="F59" s="5" t="n">
         <v>79.1481</v>
       </c>
       <c r="G59" s="5">
-        <f>IF(AND(ISNUMBER(F59),ISNUMBER(F60)),(F59/F60-1)*100,"")</f>
+        <f>IF(COUNT(F59:F60)=2,(F59/F60-1)*100,"")</f>
         <v/>
       </c>
       <c r="H59" s="5" t="n">
         <v>51.3999</v>
       </c>
       <c r="I59" s="5">
-        <f>IF(AND(ISNUMBER(H59),ISNUMBER(H60)),(H59/H60-1)*100,"")</f>
+        <f>IF(COUNT(H59:H60)=2,(H59/H60-1)*100,"")</f>
         <v/>
       </c>
       <c r="J59" s="5" t="n">
         <v>89.48999999999999</v>
       </c>
       <c r="K59" s="5">
-        <f>IF(AND(ISNUMBER(J59),ISNUMBER(J60)),(J59/J60-1)*100,"")</f>
+        <f>IF(COUNT(J59:J60)=2,(J59/J60-1)*100,"")</f>
         <v/>
       </c>
       <c r="L59" s="5" t="n">
         <v>-2.6684</v>
       </c>
       <c r="M59" s="5">
-        <f>IF(AND(ISNUMBER(L59),ISNUMBER(L60)),(L59/L60-1)*100,"")</f>
+        <f>IF(COUNT(L59:L60)=2,(L59/L60-1)*100,"")</f>
         <v/>
       </c>
       <c r="N59" s="5" t="n"/>
       <c r="O59" s="5">
-        <f>IF(AND(ISNUMBER(N59),ISNUMBER(N60)),(N59/N60-1)*100,"")</f>
+        <f>IF(COUNT(N59:N60)=2,(N59/N60-1)*100,"")</f>
         <v/>
       </c>
       <c r="P59" s="5" t="n"/>
       <c r="Q59" s="5">
-        <f>IF(AND(ISNUMBER(P59),ISNUMBER(P60)),(P59/P60-1)*100,"")</f>
+        <f>IF(COUNT(P59:P60)=2,(P59/P60-1)*100,"")</f>
         <v/>
       </c>
       <c r="R59" s="5" t="n"/>
       <c r="S59" s="5">
-        <f>IF(AND(ISNUMBER(R59),ISNUMBER(R60)),(R59/R60-1)*100,"")</f>
+        <f>IF(COUNT(R59:R60)=2,(R59/R60-1)*100,"")</f>
         <v/>
       </c>
       <c r="T59" s="5" t="n"/>
       <c r="U59" s="5">
-        <f>IF(AND(ISNUMBER(T59),ISNUMBER(T60)),(T59/T60-1)*100,"")</f>
+        <f>IF(COUNT(T59:T60)=2,(T59/T60-1)*100,"")</f>
         <v/>
       </c>
       <c r="V59" s="5" t="n"/>
@@ -6453,31 +6530,31 @@
         <v/>
       </c>
       <c r="X59" s="5">
+        <f>IF(AND(K59&lt;0,M59&gt;0),C58,"")</f>
+        <v/>
+      </c>
+      <c r="Y59" s="5">
         <f>IF(AND(G59&gt;0,I59&lt;0,K59&gt;0),C58,"")</f>
         <v/>
       </c>
-      <c r="Y59" s="5">
-        <f>IF(AND(K59&lt;0,M59&gt;0),C58,"")</f>
-        <v/>
-      </c>
       <c r="Z59" s="5">
-        <f>IF(AND(ISNUMBER(W59),0.549579&gt;=MAX(IF(ISNUMBER(X59),0.299732,-1),IF(ISNUMBER(Y59),0.323835,-1))),W59,IF(AND(ISNUMBER(X59),0.299732&gt;MAX(IF(ISNUMBER(W59),0.549579,-1),IF(ISNUMBER(Y59),0.323835,-1))),X59,IF(AND(ISNUMBER(Y59),0.323835&gt;MAX(IF(ISNUMBER(W59),0.549579,-1),IF(ISNUMBER(X59),0.299732,-1))),Y59,"")))</f>
+        <f>IF(W59&lt;&gt;"",W59,IF(X59&lt;&gt;"",X59,Y59))</f>
         <v/>
       </c>
       <c r="AA59" s="5">
+        <f>IF(AND(S59&gt;0,U59&lt;0),E58,"")</f>
+        <v/>
+      </c>
+      <c r="AB59" s="5">
         <f>IF(AND(O59&lt;=-1,E59&lt;0),E58,"")</f>
         <v/>
       </c>
-      <c r="AB59" s="5">
+      <c r="AC59" s="5">
         <f>IF(AND(Q59&gt;0,S59&gt;0),E58,"")</f>
         <v/>
       </c>
-      <c r="AC59" s="5">
-        <f>IF(AND(S59&gt;0,U59&lt;0),E58,"")</f>
-        <v/>
-      </c>
       <c r="AD59" s="5">
-        <f>IF(AND(ISNUMBER(AA59),0.408167&gt;=MAX(IF(ISNUMBER(AB59),0.31868,-1),IF(ISNUMBER(AC59),0.510996,-1))),AA59,IF(AND(ISNUMBER(AB59),0.31868&gt;MAX(IF(ISNUMBER(AA59),0.408167,-1),IF(ISNUMBER(AC59),0.510996,-1))),AB59,IF(AND(ISNUMBER(AC59),0.510996&gt;MAX(IF(ISNUMBER(AA59),0.408167,-1),IF(ISNUMBER(AB59),0.31868,-1))),AC59,"")))</f>
+        <f>IF(AA59&lt;&gt;"",AA59,IF(AB59&lt;&gt;"",AB59,AC59))</f>
         <v/>
       </c>
     </row>
@@ -6491,62 +6568,62 @@
         <v>173.68</v>
       </c>
       <c r="C60" s="5">
-        <f>IF(AND(ISNUMBER(B60),ISNUMBER(B61)),(B60/B61-1)*100,"")</f>
+        <f>IF(COUNT(B60:B61)=2,(B60/B61-1)*100,"")</f>
         <v/>
       </c>
       <c r="D60" s="5" t="n">
         <v>68.2552</v>
       </c>
       <c r="E60" s="5">
-        <f>IF(AND(ISNUMBER(D60),ISNUMBER(D61)),(D60/D61-1)*100,"")</f>
+        <f>IF(COUNT(D60:D61)=2,(D60/D61-1)*100,"")</f>
         <v/>
       </c>
       <c r="F60" s="5" t="n">
         <v>79.0692</v>
       </c>
       <c r="G60" s="5">
-        <f>IF(AND(ISNUMBER(F60),ISNUMBER(F61)),(F60/F61-1)*100,"")</f>
+        <f>IF(COUNT(F60:F61)=2,(F60/F61-1)*100,"")</f>
         <v/>
       </c>
       <c r="H60" s="5" t="n">
         <v>51.091</v>
       </c>
       <c r="I60" s="5">
-        <f>IF(AND(ISNUMBER(H60),ISNUMBER(H61)),(H60/H61-1)*100,"")</f>
+        <f>IF(COUNT(H60:H61)=2,(H60/H61-1)*100,"")</f>
         <v/>
       </c>
       <c r="J60" s="5" t="n">
         <v>87.18000000000001</v>
       </c>
       <c r="K60" s="5">
-        <f>IF(AND(ISNUMBER(J60),ISNUMBER(J61)),(J60/J61-1)*100,"")</f>
+        <f>IF(COUNT(J60:J61)=2,(J60/J61-1)*100,"")</f>
         <v/>
       </c>
       <c r="L60" s="5" t="n">
         <v>-3.3763</v>
       </c>
       <c r="M60" s="5">
-        <f>IF(AND(ISNUMBER(L60),ISNUMBER(L61)),(L60/L61-1)*100,"")</f>
+        <f>IF(COUNT(L60:L61)=2,(L60/L61-1)*100,"")</f>
         <v/>
       </c>
       <c r="N60" s="5" t="n"/>
       <c r="O60" s="5">
-        <f>IF(AND(ISNUMBER(N60),ISNUMBER(N61)),(N60/N61-1)*100,"")</f>
+        <f>IF(COUNT(N60:N61)=2,(N60/N61-1)*100,"")</f>
         <v/>
       </c>
       <c r="P60" s="5" t="n"/>
       <c r="Q60" s="5">
-        <f>IF(AND(ISNUMBER(P60),ISNUMBER(P61)),(P60/P61-1)*100,"")</f>
+        <f>IF(COUNT(P60:P61)=2,(P60/P61-1)*100,"")</f>
         <v/>
       </c>
       <c r="R60" s="5" t="n"/>
       <c r="S60" s="5">
-        <f>IF(AND(ISNUMBER(R60),ISNUMBER(R61)),(R60/R61-1)*100,"")</f>
+        <f>IF(COUNT(R60:R61)=2,(R60/R61-1)*100,"")</f>
         <v/>
       </c>
       <c r="T60" s="5" t="n"/>
       <c r="U60" s="5">
-        <f>IF(AND(ISNUMBER(T60),ISNUMBER(T61)),(T60/T61-1)*100,"")</f>
+        <f>IF(COUNT(T60:T61)=2,(T60/T61-1)*100,"")</f>
         <v/>
       </c>
       <c r="V60" s="5" t="n"/>
@@ -6555,31 +6632,31 @@
         <v/>
       </c>
       <c r="X60" s="5">
+        <f>IF(AND(K60&lt;0,M60&gt;0),C59,"")</f>
+        <v/>
+      </c>
+      <c r="Y60" s="5">
         <f>IF(AND(G60&gt;0,I60&lt;0,K60&gt;0),C59,"")</f>
         <v/>
       </c>
-      <c r="Y60" s="5">
-        <f>IF(AND(K60&lt;0,M60&gt;0),C59,"")</f>
-        <v/>
-      </c>
       <c r="Z60" s="5">
-        <f>IF(AND(ISNUMBER(W60),0.549579&gt;=MAX(IF(ISNUMBER(X60),0.299732,-1),IF(ISNUMBER(Y60),0.323835,-1))),W60,IF(AND(ISNUMBER(X60),0.299732&gt;MAX(IF(ISNUMBER(W60),0.549579,-1),IF(ISNUMBER(Y60),0.323835,-1))),X60,IF(AND(ISNUMBER(Y60),0.323835&gt;MAX(IF(ISNUMBER(W60),0.549579,-1),IF(ISNUMBER(X60),0.299732,-1))),Y60,"")))</f>
+        <f>IF(W60&lt;&gt;"",W60,IF(X60&lt;&gt;"",X60,Y60))</f>
         <v/>
       </c>
       <c r="AA60" s="5">
+        <f>IF(AND(S60&gt;0,U60&lt;0),E59,"")</f>
+        <v/>
+      </c>
+      <c r="AB60" s="5">
         <f>IF(AND(O60&lt;=-1,E60&lt;0),E59,"")</f>
         <v/>
       </c>
-      <c r="AB60" s="5">
+      <c r="AC60" s="5">
         <f>IF(AND(Q60&gt;0,S60&gt;0),E59,"")</f>
         <v/>
       </c>
-      <c r="AC60" s="5">
-        <f>IF(AND(S60&gt;0,U60&lt;0),E59,"")</f>
-        <v/>
-      </c>
       <c r="AD60" s="5">
-        <f>IF(AND(ISNUMBER(AA60),0.408167&gt;=MAX(IF(ISNUMBER(AB60),0.31868,-1),IF(ISNUMBER(AC60),0.510996,-1))),AA60,IF(AND(ISNUMBER(AB60),0.31868&gt;MAX(IF(ISNUMBER(AA60),0.408167,-1),IF(ISNUMBER(AC60),0.510996,-1))),AB60,IF(AND(ISNUMBER(AC60),0.510996&gt;MAX(IF(ISNUMBER(AA60),0.408167,-1),IF(ISNUMBER(AB60),0.31868,-1))),AC60,"")))</f>
+        <f>IF(AA60&lt;&gt;"",AA60,IF(AB60&lt;&gt;"",AB60,AC60))</f>
         <v/>
       </c>
     </row>
@@ -6593,62 +6670,62 @@
         <v>170.84</v>
       </c>
       <c r="C61" s="5">
-        <f>IF(AND(ISNUMBER(B61),ISNUMBER(B62)),(B61/B62-1)*100,"")</f>
+        <f>IF(COUNT(B61:B62)=2,(B61/B62-1)*100,"")</f>
         <v/>
       </c>
       <c r="D61" s="5" t="n">
         <v>68.0364</v>
       </c>
       <c r="E61" s="5">
-        <f>IF(AND(ISNUMBER(D61),ISNUMBER(D62)),(D61/D62-1)*100,"")</f>
+        <f>IF(COUNT(D61:D62)=2,(D61/D62-1)*100,"")</f>
         <v/>
       </c>
       <c r="F61" s="5" t="n">
         <v>78.97069999999999</v>
       </c>
       <c r="G61" s="5">
-        <f>IF(AND(ISNUMBER(F61),ISNUMBER(F62)),(F61/F62-1)*100,"")</f>
+        <f>IF(COUNT(F61:F62)=2,(F61/F62-1)*100,"")</f>
         <v/>
       </c>
       <c r="H61" s="5" t="n">
         <v>51.2405</v>
       </c>
       <c r="I61" s="5">
-        <f>IF(AND(ISNUMBER(H61),ISNUMBER(H62)),(H61/H62-1)*100,"")</f>
+        <f>IF(COUNT(H61:H62)=2,(H61/H62-1)*100,"")</f>
         <v/>
       </c>
       <c r="J61" s="5" t="n">
         <v>85.44</v>
       </c>
       <c r="K61" s="5">
-        <f>IF(AND(ISNUMBER(J61),ISNUMBER(J62)),(J61/J62-1)*100,"")</f>
+        <f>IF(COUNT(J61:J62)=2,(J61/J62-1)*100,"")</f>
         <v/>
       </c>
       <c r="L61" s="5" t="n">
         <v>-4.2328</v>
       </c>
       <c r="M61" s="5">
-        <f>IF(AND(ISNUMBER(L61),ISNUMBER(L62)),(L61/L62-1)*100,"")</f>
+        <f>IF(COUNT(L61:L62)=2,(L61/L62-1)*100,"")</f>
         <v/>
       </c>
       <c r="N61" s="5" t="n"/>
       <c r="O61" s="5">
-        <f>IF(AND(ISNUMBER(N61),ISNUMBER(N62)),(N61/N62-1)*100,"")</f>
+        <f>IF(COUNT(N61:N62)=2,(N61/N62-1)*100,"")</f>
         <v/>
       </c>
       <c r="P61" s="5" t="n"/>
       <c r="Q61" s="5">
-        <f>IF(AND(ISNUMBER(P61),ISNUMBER(P62)),(P61/P62-1)*100,"")</f>
+        <f>IF(COUNT(P61:P62)=2,(P61/P62-1)*100,"")</f>
         <v/>
       </c>
       <c r="R61" s="5" t="n"/>
       <c r="S61" s="5">
-        <f>IF(AND(ISNUMBER(R61),ISNUMBER(R62)),(R61/R62-1)*100,"")</f>
+        <f>IF(COUNT(R61:R62)=2,(R61/R62-1)*100,"")</f>
         <v/>
       </c>
       <c r="T61" s="5" t="n"/>
       <c r="U61" s="5">
-        <f>IF(AND(ISNUMBER(T61),ISNUMBER(T62)),(T61/T62-1)*100,"")</f>
+        <f>IF(COUNT(T61:T62)=2,(T61/T62-1)*100,"")</f>
         <v/>
       </c>
       <c r="V61" s="5" t="n"/>
@@ -6657,31 +6734,31 @@
         <v/>
       </c>
       <c r="X61" s="5">
+        <f>IF(AND(K61&lt;0,M61&gt;0),C60,"")</f>
+        <v/>
+      </c>
+      <c r="Y61" s="5">
         <f>IF(AND(G61&gt;0,I61&lt;0,K61&gt;0),C60,"")</f>
         <v/>
       </c>
-      <c r="Y61" s="5">
-        <f>IF(AND(K61&lt;0,M61&gt;0),C60,"")</f>
-        <v/>
-      </c>
       <c r="Z61" s="5">
-        <f>IF(AND(ISNUMBER(W61),0.549579&gt;=MAX(IF(ISNUMBER(X61),0.299732,-1),IF(ISNUMBER(Y61),0.323835,-1))),W61,IF(AND(ISNUMBER(X61),0.299732&gt;MAX(IF(ISNUMBER(W61),0.549579,-1),IF(ISNUMBER(Y61),0.323835,-1))),X61,IF(AND(ISNUMBER(Y61),0.323835&gt;MAX(IF(ISNUMBER(W61),0.549579,-1),IF(ISNUMBER(X61),0.299732,-1))),Y61,"")))</f>
+        <f>IF(W61&lt;&gt;"",W61,IF(X61&lt;&gt;"",X61,Y61))</f>
         <v/>
       </c>
       <c r="AA61" s="5">
+        <f>IF(AND(S61&gt;0,U61&lt;0),E60,"")</f>
+        <v/>
+      </c>
+      <c r="AB61" s="5">
         <f>IF(AND(O61&lt;=-1,E61&lt;0),E60,"")</f>
         <v/>
       </c>
-      <c r="AB61" s="5">
+      <c r="AC61" s="5">
         <f>IF(AND(Q61&gt;0,S61&gt;0),E60,"")</f>
         <v/>
       </c>
-      <c r="AC61" s="5">
-        <f>IF(AND(S61&gt;0,U61&lt;0),E60,"")</f>
-        <v/>
-      </c>
       <c r="AD61" s="5">
-        <f>IF(AND(ISNUMBER(AA61),0.408167&gt;=MAX(IF(ISNUMBER(AB61),0.31868,-1),IF(ISNUMBER(AC61),0.510996,-1))),AA61,IF(AND(ISNUMBER(AB61),0.31868&gt;MAX(IF(ISNUMBER(AA61),0.408167,-1),IF(ISNUMBER(AC61),0.510996,-1))),AB61,IF(AND(ISNUMBER(AC61),0.510996&gt;MAX(IF(ISNUMBER(AA61),0.408167,-1),IF(ISNUMBER(AB61),0.31868,-1))),AC61,"")))</f>
+        <f>IF(AA61&lt;&gt;"",AA61,IF(AB61&lt;&gt;"",AB61,AC61))</f>
         <v/>
       </c>
     </row>
@@ -6695,62 +6772,62 @@
         <v>171.19</v>
       </c>
       <c r="C62" s="5">
-        <f>IF(AND(ISNUMBER(B62),ISNUMBER(B63)),(B62/B63-1)*100,"")</f>
+        <f>IF(COUNT(B62:B63)=2,(B62/B63-1)*100,"")</f>
         <v/>
       </c>
       <c r="D62" s="5" t="n">
         <v>68.0463</v>
       </c>
       <c r="E62" s="5">
-        <f>IF(AND(ISNUMBER(D62),ISNUMBER(D63)),(D62/D63-1)*100,"")</f>
+        <f>IF(COUNT(D62:D63)=2,(D62/D63-1)*100,"")</f>
         <v/>
       </c>
       <c r="F62" s="5" t="n">
         <v>79.01990000000001</v>
       </c>
       <c r="G62" s="5">
-        <f>IF(AND(ISNUMBER(F62),ISNUMBER(F63)),(F62/F63-1)*100,"")</f>
+        <f>IF(COUNT(F62:F63)=2,(F62/F63-1)*100,"")</f>
         <v/>
       </c>
       <c r="H62" s="5" t="n">
         <v>51.669</v>
       </c>
       <c r="I62" s="5">
-        <f>IF(AND(ISNUMBER(H62),ISNUMBER(H63)),(H62/H63-1)*100,"")</f>
+        <f>IF(COUNT(H62:H63)=2,(H62/H63-1)*100,"")</f>
         <v/>
       </c>
       <c r="J62" s="5" t="n">
         <v>88.5</v>
       </c>
       <c r="K62" s="5">
-        <f>IF(AND(ISNUMBER(J62),ISNUMBER(J63)),(J62/J63-1)*100,"")</f>
+        <f>IF(COUNT(J62:J63)=2,(J62/J63-1)*100,"")</f>
         <v/>
       </c>
       <c r="L62" s="5" t="n">
         <v>1.8563</v>
       </c>
       <c r="M62" s="5">
-        <f>IF(AND(ISNUMBER(L62),ISNUMBER(L63)),(L62/L63-1)*100,"")</f>
+        <f>IF(COUNT(L62:L63)=2,(L62/L63-1)*100,"")</f>
         <v/>
       </c>
       <c r="N62" s="5" t="n"/>
       <c r="O62" s="5">
-        <f>IF(AND(ISNUMBER(N62),ISNUMBER(N63)),(N62/N63-1)*100,"")</f>
+        <f>IF(COUNT(N62:N63)=2,(N62/N63-1)*100,"")</f>
         <v/>
       </c>
       <c r="P62" s="5" t="n"/>
       <c r="Q62" s="5">
-        <f>IF(AND(ISNUMBER(P62),ISNUMBER(P63)),(P62/P63-1)*100,"")</f>
+        <f>IF(COUNT(P62:P63)=2,(P62/P63-1)*100,"")</f>
         <v/>
       </c>
       <c r="R62" s="5" t="n"/>
       <c r="S62" s="5">
-        <f>IF(AND(ISNUMBER(R62),ISNUMBER(R63)),(R62/R63-1)*100,"")</f>
+        <f>IF(COUNT(R62:R63)=2,(R62/R63-1)*100,"")</f>
         <v/>
       </c>
       <c r="T62" s="5" t="n"/>
       <c r="U62" s="5">
-        <f>IF(AND(ISNUMBER(T62),ISNUMBER(T63)),(T62/T63-1)*100,"")</f>
+        <f>IF(COUNT(T62:T63)=2,(T62/T63-1)*100,"")</f>
         <v/>
       </c>
       <c r="V62" s="5" t="n"/>
@@ -6759,31 +6836,31 @@
         <v/>
       </c>
       <c r="X62" s="5">
+        <f>IF(AND(K62&lt;0,M62&gt;0),C61,"")</f>
+        <v/>
+      </c>
+      <c r="Y62" s="5">
         <f>IF(AND(G62&gt;0,I62&lt;0,K62&gt;0),C61,"")</f>
         <v/>
       </c>
-      <c r="Y62" s="5">
-        <f>IF(AND(K62&lt;0,M62&gt;0),C61,"")</f>
-        <v/>
-      </c>
       <c r="Z62" s="5">
-        <f>IF(AND(ISNUMBER(W62),0.549579&gt;=MAX(IF(ISNUMBER(X62),0.299732,-1),IF(ISNUMBER(Y62),0.323835,-1))),W62,IF(AND(ISNUMBER(X62),0.299732&gt;MAX(IF(ISNUMBER(W62),0.549579,-1),IF(ISNUMBER(Y62),0.323835,-1))),X62,IF(AND(ISNUMBER(Y62),0.323835&gt;MAX(IF(ISNUMBER(W62),0.549579,-1),IF(ISNUMBER(X62),0.299732,-1))),Y62,"")))</f>
+        <f>IF(W62&lt;&gt;"",W62,IF(X62&lt;&gt;"",X62,Y62))</f>
         <v/>
       </c>
       <c r="AA62" s="5">
+        <f>IF(AND(S62&gt;0,U62&lt;0),E61,"")</f>
+        <v/>
+      </c>
+      <c r="AB62" s="5">
         <f>IF(AND(O62&lt;=-1,E62&lt;0),E61,"")</f>
         <v/>
       </c>
-      <c r="AB62" s="5">
+      <c r="AC62" s="5">
         <f>IF(AND(Q62&gt;0,S62&gt;0),E61,"")</f>
         <v/>
       </c>
-      <c r="AC62" s="5">
-        <f>IF(AND(S62&gt;0,U62&lt;0),E61,"")</f>
-        <v/>
-      </c>
       <c r="AD62" s="5">
-        <f>IF(AND(ISNUMBER(AA62),0.408167&gt;=MAX(IF(ISNUMBER(AB62),0.31868,-1),IF(ISNUMBER(AC62),0.510996,-1))),AA62,IF(AND(ISNUMBER(AB62),0.31868&gt;MAX(IF(ISNUMBER(AA62),0.408167,-1),IF(ISNUMBER(AC62),0.510996,-1))),AB62,IF(AND(ISNUMBER(AC62),0.510996&gt;MAX(IF(ISNUMBER(AA62),0.408167,-1),IF(ISNUMBER(AB62),0.31868,-1))),AC62,"")))</f>
+        <f>IF(AA62&lt;&gt;"",AA62,IF(AB62&lt;&gt;"",AB62,AC62))</f>
         <v/>
       </c>
     </row>
@@ -6797,62 +6874,62 @@
         <v>165.46</v>
       </c>
       <c r="C63" s="5">
-        <f>IF(AND(ISNUMBER(B63),ISNUMBER(B64)),(B63/B64-1)*100,"")</f>
+        <f>IF(COUNT(B63:B64)=2,(B63/B64-1)*100,"")</f>
         <v/>
       </c>
       <c r="D63" s="5" t="n">
         <v>65.5393</v>
       </c>
       <c r="E63" s="5">
-        <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64)),(D63/D64-1)*100,"")</f>
+        <f>IF(COUNT(D63:D64)=2,(D63/D64-1)*100,"")</f>
         <v/>
       </c>
       <c r="F63" s="5" t="n">
         <v>78.7539</v>
       </c>
       <c r="G63" s="5">
-        <f>IF(AND(ISNUMBER(F63),ISNUMBER(F64)),(F63/F64-1)*100,"")</f>
+        <f>IF(COUNT(F63:F64)=2,(F63/F64-1)*100,"")</f>
         <v/>
       </c>
       <c r="H63" s="5" t="n">
         <v>51.7587</v>
       </c>
       <c r="I63" s="5">
-        <f>IF(AND(ISNUMBER(H63),ISNUMBER(H64)),(H63/H64-1)*100,"")</f>
+        <f>IF(COUNT(H63:H64)=2,(H63/H64-1)*100,"")</f>
         <v/>
       </c>
       <c r="J63" s="5" t="n">
         <v>85.02</v>
       </c>
       <c r="K63" s="5">
-        <f>IF(AND(ISNUMBER(J63),ISNUMBER(J64)),(J63/J64-1)*100,"")</f>
+        <f>IF(COUNT(J63:J64)=2,(J63/J64-1)*100,"")</f>
         <v/>
       </c>
       <c r="L63" s="5" t="n">
         <v>-0.358</v>
       </c>
       <c r="M63" s="5">
-        <f>IF(AND(ISNUMBER(L63),ISNUMBER(L64)),(L63/L64-1)*100,"")</f>
+        <f>IF(COUNT(L63:L64)=2,(L63/L64-1)*100,"")</f>
         <v/>
       </c>
       <c r="N63" s="5" t="n"/>
       <c r="O63" s="5">
-        <f>IF(AND(ISNUMBER(N63),ISNUMBER(N64)),(N63/N64-1)*100,"")</f>
+        <f>IF(COUNT(N63:N64)=2,(N63/N64-1)*100,"")</f>
         <v/>
       </c>
       <c r="P63" s="5" t="n"/>
       <c r="Q63" s="5">
-        <f>IF(AND(ISNUMBER(P63),ISNUMBER(P64)),(P63/P64-1)*100,"")</f>
+        <f>IF(COUNT(P63:P64)=2,(P63/P64-1)*100,"")</f>
         <v/>
       </c>
       <c r="R63" s="5" t="n"/>
       <c r="S63" s="5">
-        <f>IF(AND(ISNUMBER(R63),ISNUMBER(R64)),(R63/R64-1)*100,"")</f>
+        <f>IF(COUNT(R63:R64)=2,(R63/R64-1)*100,"")</f>
         <v/>
       </c>
       <c r="T63" s="5" t="n"/>
       <c r="U63" s="5">
-        <f>IF(AND(ISNUMBER(T63),ISNUMBER(T64)),(T63/T64-1)*100,"")</f>
+        <f>IF(COUNT(T63:T64)=2,(T63/T64-1)*100,"")</f>
         <v/>
       </c>
       <c r="V63" s="5" t="n"/>
@@ -6861,31 +6938,31 @@
         <v/>
       </c>
       <c r="X63" s="5">
+        <f>IF(AND(K63&lt;0,M63&gt;0),C62,"")</f>
+        <v/>
+      </c>
+      <c r="Y63" s="5">
         <f>IF(AND(G63&gt;0,I63&lt;0,K63&gt;0),C62,"")</f>
         <v/>
       </c>
-      <c r="Y63" s="5">
-        <f>IF(AND(K63&lt;0,M63&gt;0),C62,"")</f>
-        <v/>
-      </c>
       <c r="Z63" s="5">
-        <f>IF(AND(ISNUMBER(W63),0.549579&gt;=MAX(IF(ISNUMBER(X63),0.299732,-1),IF(ISNUMBER(Y63),0.323835,-1))),W63,IF(AND(ISNUMBER(X63),0.299732&gt;MAX(IF(ISNUMBER(W63),0.549579,-1),IF(ISNUMBER(Y63),0.323835,-1))),X63,IF(AND(ISNUMBER(Y63),0.323835&gt;MAX(IF(ISNUMBER(W63),0.549579,-1),IF(ISNUMBER(X63),0.299732,-1))),Y63,"")))</f>
+        <f>IF(W63&lt;&gt;"",W63,IF(X63&lt;&gt;"",X63,Y63))</f>
         <v/>
       </c>
       <c r="AA63" s="5">
+        <f>IF(AND(S63&gt;0,U63&lt;0),E62,"")</f>
+        <v/>
+      </c>
+      <c r="AB63" s="5">
         <f>IF(AND(O63&lt;=-1,E63&lt;0),E62,"")</f>
         <v/>
       </c>
-      <c r="AB63" s="5">
+      <c r="AC63" s="5">
         <f>IF(AND(Q63&gt;0,S63&gt;0),E62,"")</f>
         <v/>
       </c>
-      <c r="AC63" s="5">
-        <f>IF(AND(S63&gt;0,U63&lt;0),E62,"")</f>
-        <v/>
-      </c>
       <c r="AD63" s="5">
-        <f>IF(AND(ISNUMBER(AA63),0.408167&gt;=MAX(IF(ISNUMBER(AB63),0.31868,-1),IF(ISNUMBER(AC63),0.510996,-1))),AA63,IF(AND(ISNUMBER(AB63),0.31868&gt;MAX(IF(ISNUMBER(AA63),0.408167,-1),IF(ISNUMBER(AC63),0.510996,-1))),AB63,IF(AND(ISNUMBER(AC63),0.510996&gt;MAX(IF(ISNUMBER(AA63),0.408167,-1),IF(ISNUMBER(AB63),0.31868,-1))),AC63,"")))</f>
+        <f>IF(AA63&lt;&gt;"",AA63,IF(AB63&lt;&gt;"",AB63,AC63))</f>
         <v/>
       </c>
     </row>
@@ -6899,62 +6976,62 @@
         <v>164.1</v>
       </c>
       <c r="C64" s="5">
-        <f>IF(AND(ISNUMBER(B64),ISNUMBER(B65)),(B64/B65-1)*100,"")</f>
+        <f>IF(COUNT(B64:B65)=2,(B64/B65-1)*100,"")</f>
         <v/>
       </c>
       <c r="D64" s="5" t="n">
         <v>65.68859999999999</v>
       </c>
       <c r="E64" s="5">
-        <f>IF(AND(ISNUMBER(D64),ISNUMBER(D65)),(D64/D65-1)*100,"")</f>
+        <f>IF(COUNT(D64:D65)=2,(D64/D65-1)*100,"")</f>
         <v/>
       </c>
       <c r="F64" s="5" t="n">
         <v>78.744</v>
       </c>
       <c r="G64" s="5">
-        <f>IF(AND(ISNUMBER(F64),ISNUMBER(F65)),(F64/F65-1)*100,"")</f>
+        <f>IF(COUNT(F64:F65)=2,(F64/F65-1)*100,"")</f>
         <v/>
       </c>
       <c r="H64" s="5" t="n">
         <v>51.5494</v>
       </c>
       <c r="I64" s="5">
-        <f>IF(AND(ISNUMBER(H64),ISNUMBER(H65)),(H64/H65-1)*100,"")</f>
+        <f>IF(COUNT(H64:H65)=2,(H64/H65-1)*100,"")</f>
         <v/>
       </c>
       <c r="J64" s="5" t="n">
         <v>85.98999999999999</v>
       </c>
       <c r="K64" s="5">
-        <f>IF(AND(ISNUMBER(J64),ISNUMBER(J65)),(J64/J65-1)*100,"")</f>
+        <f>IF(COUNT(J64:J65)=2,(J64/J65-1)*100,"")</f>
         <v/>
       </c>
       <c r="L64" s="5" t="n">
         <v>-3.8991</v>
       </c>
       <c r="M64" s="5">
-        <f>IF(AND(ISNUMBER(L64),ISNUMBER(L65)),(L64/L65-1)*100,"")</f>
+        <f>IF(COUNT(L64:L65)=2,(L64/L65-1)*100,"")</f>
         <v/>
       </c>
       <c r="N64" s="5" t="n"/>
       <c r="O64" s="5">
-        <f>IF(AND(ISNUMBER(N64),ISNUMBER(N65)),(N64/N65-1)*100,"")</f>
+        <f>IF(COUNT(N64:N65)=2,(N64/N65-1)*100,"")</f>
         <v/>
       </c>
       <c r="P64" s="5" t="n"/>
       <c r="Q64" s="5">
-        <f>IF(AND(ISNUMBER(P64),ISNUMBER(P65)),(P64/P65-1)*100,"")</f>
+        <f>IF(COUNT(P64:P65)=2,(P64/P65-1)*100,"")</f>
         <v/>
       </c>
       <c r="R64" s="5" t="n"/>
       <c r="S64" s="5">
-        <f>IF(AND(ISNUMBER(R64),ISNUMBER(R65)),(R64/R65-1)*100,"")</f>
+        <f>IF(COUNT(R64:R65)=2,(R64/R65-1)*100,"")</f>
         <v/>
       </c>
       <c r="T64" s="5" t="n"/>
       <c r="U64" s="5">
-        <f>IF(AND(ISNUMBER(T64),ISNUMBER(T65)),(T64/T65-1)*100,"")</f>
+        <f>IF(COUNT(T64:T65)=2,(T64/T65-1)*100,"")</f>
         <v/>
       </c>
       <c r="V64" s="5" t="n"/>
@@ -6963,31 +7040,31 @@
         <v/>
       </c>
       <c r="X64" s="5">
+        <f>IF(AND(K64&lt;0,M64&gt;0),C63,"")</f>
+        <v/>
+      </c>
+      <c r="Y64" s="5">
         <f>IF(AND(G64&gt;0,I64&lt;0,K64&gt;0),C63,"")</f>
         <v/>
       </c>
-      <c r="Y64" s="5">
-        <f>IF(AND(K64&lt;0,M64&gt;0),C63,"")</f>
-        <v/>
-      </c>
       <c r="Z64" s="5">
-        <f>IF(AND(ISNUMBER(W64),0.549579&gt;=MAX(IF(ISNUMBER(X64),0.299732,-1),IF(ISNUMBER(Y64),0.323835,-1))),W64,IF(AND(ISNUMBER(X64),0.299732&gt;MAX(IF(ISNUMBER(W64),0.549579,-1),IF(ISNUMBER(Y64),0.323835,-1))),X64,IF(AND(ISNUMBER(Y64),0.323835&gt;MAX(IF(ISNUMBER(W64),0.549579,-1),IF(ISNUMBER(X64),0.299732,-1))),Y64,"")))</f>
+        <f>IF(W64&lt;&gt;"",W64,IF(X64&lt;&gt;"",X64,Y64))</f>
         <v/>
       </c>
       <c r="AA64" s="5">
+        <f>IF(AND(S64&gt;0,U64&lt;0),E63,"")</f>
+        <v/>
+      </c>
+      <c r="AB64" s="5">
         <f>IF(AND(O64&lt;=-1,E64&lt;0),E63,"")</f>
         <v/>
       </c>
-      <c r="AB64" s="5">
+      <c r="AC64" s="5">
         <f>IF(AND(Q64&gt;0,S64&gt;0),E63,"")</f>
         <v/>
       </c>
-      <c r="AC64" s="5">
-        <f>IF(AND(S64&gt;0,U64&lt;0),E63,"")</f>
-        <v/>
-      </c>
       <c r="AD64" s="5">
-        <f>IF(AND(ISNUMBER(AA64),0.408167&gt;=MAX(IF(ISNUMBER(AB64),0.31868,-1),IF(ISNUMBER(AC64),0.510996,-1))),AA64,IF(AND(ISNUMBER(AB64),0.31868&gt;MAX(IF(ISNUMBER(AA64),0.408167,-1),IF(ISNUMBER(AC64),0.510996,-1))),AB64,IF(AND(ISNUMBER(AC64),0.510996&gt;MAX(IF(ISNUMBER(AA64),0.408167,-1),IF(ISNUMBER(AB64),0.31868,-1))),AC64,"")))</f>
+        <f>IF(AA64&lt;&gt;"",AA64,IF(AB64&lt;&gt;"",AB64,AC64))</f>
         <v/>
       </c>
     </row>
@@ -7001,62 +7078,62 @@
         <v>163.44</v>
       </c>
       <c r="C65" s="5">
-        <f>IF(AND(ISNUMBER(B65),ISNUMBER(B66)),(B65/B66-1)*100,"")</f>
+        <f>IF(COUNT(B65:B66)=2,(B65/B66-1)*100,"")</f>
         <v/>
       </c>
       <c r="D65" s="5" t="n">
         <v>65.1215</v>
       </c>
       <c r="E65" s="5">
-        <f>IF(AND(ISNUMBER(D65),ISNUMBER(D66)),(D65/D66-1)*100,"")</f>
+        <f>IF(COUNT(D65:D66)=2,(D65/D66-1)*100,"")</f>
         <v/>
       </c>
       <c r="F65" s="5" t="n">
         <v>78.7046</v>
       </c>
       <c r="G65" s="5">
-        <f>IF(AND(ISNUMBER(F65),ISNUMBER(F66)),(F65/F66-1)*100,"")</f>
+        <f>IF(COUNT(F65:F66)=2,(F65/F66-1)*100,"")</f>
         <v/>
       </c>
       <c r="H65" s="5" t="n">
         <v>51.4797</v>
       </c>
       <c r="I65" s="5">
-        <f>IF(AND(ISNUMBER(H65),ISNUMBER(H66)),(H65/H66-1)*100,"")</f>
+        <f>IF(COUNT(H65:H66)=2,(H65/H66-1)*100,"")</f>
         <v/>
       </c>
       <c r="J65" s="5" t="n">
         <v>86.36</v>
       </c>
       <c r="K65" s="5">
-        <f>IF(AND(ISNUMBER(J65),ISNUMBER(J66)),(J65/J66-1)*100,"")</f>
+        <f>IF(COUNT(J65:J66)=2,(J65/J66-1)*100,"")</f>
         <v/>
       </c>
       <c r="L65" s="5" t="n">
         <v>-3.433</v>
       </c>
       <c r="M65" s="5">
-        <f>IF(AND(ISNUMBER(L65),ISNUMBER(L66)),(L65/L66-1)*100,"")</f>
+        <f>IF(COUNT(L65:L66)=2,(L65/L66-1)*100,"")</f>
         <v/>
       </c>
       <c r="N65" s="5" t="n"/>
       <c r="O65" s="5">
-        <f>IF(AND(ISNUMBER(N65),ISNUMBER(N66)),(N65/N66-1)*100,"")</f>
+        <f>IF(COUNT(N65:N66)=2,(N65/N66-1)*100,"")</f>
         <v/>
       </c>
       <c r="P65" s="5" t="n"/>
       <c r="Q65" s="5">
-        <f>IF(AND(ISNUMBER(P65),ISNUMBER(P66)),(P65/P66-1)*100,"")</f>
+        <f>IF(COUNT(P65:P66)=2,(P65/P66-1)*100,"")</f>
         <v/>
       </c>
       <c r="R65" s="5" t="n"/>
       <c r="S65" s="5">
-        <f>IF(AND(ISNUMBER(R65),ISNUMBER(R66)),(R65/R66-1)*100,"")</f>
+        <f>IF(COUNT(R65:R66)=2,(R65/R66-1)*100,"")</f>
         <v/>
       </c>
       <c r="T65" s="5" t="n"/>
       <c r="U65" s="5">
-        <f>IF(AND(ISNUMBER(T65),ISNUMBER(T66)),(T65/T66-1)*100,"")</f>
+        <f>IF(COUNT(T65:T66)=2,(T65/T66-1)*100,"")</f>
         <v/>
       </c>
       <c r="V65" s="5" t="n"/>
@@ -7065,31 +7142,31 @@
         <v/>
       </c>
       <c r="X65" s="5">
+        <f>IF(AND(K65&lt;0,M65&gt;0),C64,"")</f>
+        <v/>
+      </c>
+      <c r="Y65" s="5">
         <f>IF(AND(G65&gt;0,I65&lt;0,K65&gt;0),C64,"")</f>
         <v/>
       </c>
-      <c r="Y65" s="5">
-        <f>IF(AND(K65&lt;0,M65&gt;0),C64,"")</f>
-        <v/>
-      </c>
       <c r="Z65" s="5">
-        <f>IF(AND(ISNUMBER(W65),0.549579&gt;=MAX(IF(ISNUMBER(X65),0.299732,-1),IF(ISNUMBER(Y65),0.323835,-1))),W65,IF(AND(ISNUMBER(X65),0.299732&gt;MAX(IF(ISNUMBER(W65),0.549579,-1),IF(ISNUMBER(Y65),0.323835,-1))),X65,IF(AND(ISNUMBER(Y65),0.323835&gt;MAX(IF(ISNUMBER(W65),0.549579,-1),IF(ISNUMBER(X65),0.299732,-1))),Y65,"")))</f>
+        <f>IF(W65&lt;&gt;"",W65,IF(X65&lt;&gt;"",X65,Y65))</f>
         <v/>
       </c>
       <c r="AA65" s="5">
+        <f>IF(AND(S65&gt;0,U65&lt;0),E64,"")</f>
+        <v/>
+      </c>
+      <c r="AB65" s="5">
         <f>IF(AND(O65&lt;=-1,E65&lt;0),E64,"")</f>
         <v/>
       </c>
-      <c r="AB65" s="5">
+      <c r="AC65" s="5">
         <f>IF(AND(Q65&gt;0,S65&gt;0),E64,"")</f>
         <v/>
       </c>
-      <c r="AC65" s="5">
-        <f>IF(AND(S65&gt;0,U65&lt;0),E64,"")</f>
-        <v/>
-      </c>
       <c r="AD65" s="5">
-        <f>IF(AND(ISNUMBER(AA65),0.408167&gt;=MAX(IF(ISNUMBER(AB65),0.31868,-1),IF(ISNUMBER(AC65),0.510996,-1))),AA65,IF(AND(ISNUMBER(AB65),0.31868&gt;MAX(IF(ISNUMBER(AA65),0.408167,-1),IF(ISNUMBER(AC65),0.510996,-1))),AB65,IF(AND(ISNUMBER(AC65),0.510996&gt;MAX(IF(ISNUMBER(AA65),0.408167,-1),IF(ISNUMBER(AB65),0.31868,-1))),AC65,"")))</f>
+        <f>IF(AA65&lt;&gt;"",AA65,IF(AB65&lt;&gt;"",AB65,AC65))</f>
         <v/>
       </c>
     </row>
@@ -7103,62 +7180,62 @@
         <v>158.19</v>
       </c>
       <c r="C66" s="5">
-        <f>IF(AND(ISNUMBER(B66),ISNUMBER(B67)),(B66/B67-1)*100,"")</f>
+        <f>IF(COUNT(B66:B67)=2,(B66/B67-1)*100,"")</f>
         <v/>
       </c>
       <c r="D66" s="5" t="n">
         <v>63.9277</v>
       </c>
       <c r="E66" s="5">
-        <f>IF(AND(ISNUMBER(D66),ISNUMBER(D67)),(D66/D67-1)*100,"")</f>
+        <f>IF(COUNT(D66:D67)=2,(D66/D67-1)*100,"")</f>
         <v/>
       </c>
       <c r="F66" s="5" t="n">
         <v>78.202</v>
       </c>
       <c r="G66" s="5">
-        <f>IF(AND(ISNUMBER(F66),ISNUMBER(F67)),(F66/F67-1)*100,"")</f>
+        <f>IF(COUNT(F66:F67)=2,(F66/F67-1)*100,"")</f>
         <v/>
       </c>
       <c r="H66" s="5" t="n">
         <v>50.9216</v>
       </c>
       <c r="I66" s="5">
-        <f>IF(AND(ISNUMBER(H66),ISNUMBER(H67)),(H66/H67-1)*100,"")</f>
+        <f>IF(COUNT(H66:H67)=2,(H66/H67-1)*100,"")</f>
         <v/>
       </c>
       <c r="J66" s="5" t="n">
         <v>83.78</v>
       </c>
       <c r="K66" s="5">
-        <f>IF(AND(ISNUMBER(J66),ISNUMBER(J67)),(J66/J67-1)*100,"")</f>
+        <f>IF(COUNT(J66:J67)=2,(J66/J67-1)*100,"")</f>
         <v/>
       </c>
       <c r="L66" s="5" t="n">
         <v>1.3468</v>
       </c>
       <c r="M66" s="5">
-        <f>IF(AND(ISNUMBER(L66),ISNUMBER(L67)),(L66/L67-1)*100,"")</f>
+        <f>IF(COUNT(L66:L67)=2,(L66/L67-1)*100,"")</f>
         <v/>
       </c>
       <c r="N66" s="5" t="n"/>
       <c r="O66" s="5">
-        <f>IF(AND(ISNUMBER(N66),ISNUMBER(N67)),(N66/N67-1)*100,"")</f>
+        <f>IF(COUNT(N66:N67)=2,(N66/N67-1)*100,"")</f>
         <v/>
       </c>
       <c r="P66" s="5" t="n"/>
       <c r="Q66" s="5">
-        <f>IF(AND(ISNUMBER(P66),ISNUMBER(P67)),(P66/P67-1)*100,"")</f>
+        <f>IF(COUNT(P66:P67)=2,(P66/P67-1)*100,"")</f>
         <v/>
       </c>
       <c r="R66" s="5" t="n"/>
       <c r="S66" s="5">
-        <f>IF(AND(ISNUMBER(R66),ISNUMBER(R67)),(R66/R67-1)*100,"")</f>
+        <f>IF(COUNT(R66:R67)=2,(R66/R67-1)*100,"")</f>
         <v/>
       </c>
       <c r="T66" s="5" t="n"/>
       <c r="U66" s="5">
-        <f>IF(AND(ISNUMBER(T66),ISNUMBER(T67)),(T66/T67-1)*100,"")</f>
+        <f>IF(COUNT(T66:T67)=2,(T66/T67-1)*100,"")</f>
         <v/>
       </c>
       <c r="V66" s="5" t="n"/>
@@ -7167,31 +7244,31 @@
         <v/>
       </c>
       <c r="X66" s="5">
+        <f>IF(AND(K66&lt;0,M66&gt;0),C65,"")</f>
+        <v/>
+      </c>
+      <c r="Y66" s="5">
         <f>IF(AND(G66&gt;0,I66&lt;0,K66&gt;0),C65,"")</f>
         <v/>
       </c>
-      <c r="Y66" s="5">
-        <f>IF(AND(K66&lt;0,M66&gt;0),C65,"")</f>
-        <v/>
-      </c>
       <c r="Z66" s="5">
-        <f>IF(AND(ISNUMBER(W66),0.549579&gt;=MAX(IF(ISNUMBER(X66),0.299732,-1),IF(ISNUMBER(Y66),0.323835,-1))),W66,IF(AND(ISNUMBER(X66),0.299732&gt;MAX(IF(ISNUMBER(W66),0.549579,-1),IF(ISNUMBER(Y66),0.323835,-1))),X66,IF(AND(ISNUMBER(Y66),0.323835&gt;MAX(IF(ISNUMBER(W66),0.549579,-1),IF(ISNUMBER(X66),0.299732,-1))),Y66,"")))</f>
+        <f>IF(W66&lt;&gt;"",W66,IF(X66&lt;&gt;"",X66,Y66))</f>
         <v/>
       </c>
       <c r="AA66" s="5">
+        <f>IF(AND(S66&gt;0,U66&lt;0),E65,"")</f>
+        <v/>
+      </c>
+      <c r="AB66" s="5">
         <f>IF(AND(O66&lt;=-1,E66&lt;0),E65,"")</f>
         <v/>
       </c>
-      <c r="AB66" s="5">
+      <c r="AC66" s="5">
         <f>IF(AND(Q66&gt;0,S66&gt;0),E65,"")</f>
         <v/>
       </c>
-      <c r="AC66" s="5">
-        <f>IF(AND(S66&gt;0,U66&lt;0),E65,"")</f>
-        <v/>
-      </c>
       <c r="AD66" s="5">
-        <f>IF(AND(ISNUMBER(AA66),0.408167&gt;=MAX(IF(ISNUMBER(AB66),0.31868,-1),IF(ISNUMBER(AC66),0.510996,-1))),AA66,IF(AND(ISNUMBER(AB66),0.31868&gt;MAX(IF(ISNUMBER(AA66),0.408167,-1),IF(ISNUMBER(AC66),0.510996,-1))),AB66,IF(AND(ISNUMBER(AC66),0.510996&gt;MAX(IF(ISNUMBER(AA66),0.408167,-1),IF(ISNUMBER(AB66),0.31868,-1))),AC66,"")))</f>
+        <f>IF(AA66&lt;&gt;"",AA66,IF(AB66&lt;&gt;"",AB66,AC66))</f>
         <v/>
       </c>
     </row>
@@ -7205,62 +7282,62 @@
         <v>160.16</v>
       </c>
       <c r="C67" s="5">
-        <f>IF(AND(ISNUMBER(B67),ISNUMBER(B68)),(B67/B68-1)*100,"")</f>
+        <f>IF(COUNT(B67:B68)=2,(B67/B68-1)*100,"")</f>
         <v/>
       </c>
       <c r="D67" s="5" t="n">
         <v>64.634</v>
       </c>
       <c r="E67" s="5">
-        <f>IF(AND(ISNUMBER(D67),ISNUMBER(D68)),(D67/D68-1)*100,"")</f>
+        <f>IF(COUNT(D67:D68)=2,(D67/D68-1)*100,"")</f>
         <v/>
       </c>
       <c r="F67" s="5" t="n">
         <v>78.3892</v>
       </c>
       <c r="G67" s="5">
-        <f>IF(AND(ISNUMBER(F67),ISNUMBER(F68)),(F67/F68-1)*100,"")</f>
+        <f>IF(COUNT(F67:F68)=2,(F67/F68-1)*100,"")</f>
         <v/>
       </c>
       <c r="H67" s="5" t="n">
         <v>51.5594</v>
       </c>
       <c r="I67" s="5">
-        <f>IF(AND(ISNUMBER(H67),ISNUMBER(H68)),(H67/H68-1)*100,"")</f>
+        <f>IF(COUNT(H67:H68)=2,(H67/H68-1)*100,"")</f>
         <v/>
       </c>
       <c r="J67" s="5" t="n">
         <v>87.14</v>
       </c>
       <c r="K67" s="5">
-        <f>IF(AND(ISNUMBER(J67),ISNUMBER(J68)),(J67/J68-1)*100,"")</f>
+        <f>IF(COUNT(J67:J68)=2,(J67/J68-1)*100,"")</f>
         <v/>
       </c>
       <c r="L67" s="5" t="n">
         <v>-3.3098</v>
       </c>
       <c r="M67" s="5">
-        <f>IF(AND(ISNUMBER(L67),ISNUMBER(L68)),(L67/L68-1)*100,"")</f>
+        <f>IF(COUNT(L67:L68)=2,(L67/L68-1)*100,"")</f>
         <v/>
       </c>
       <c r="N67" s="5" t="n"/>
       <c r="O67" s="5">
-        <f>IF(AND(ISNUMBER(N67),ISNUMBER(N68)),(N67/N68-1)*100,"")</f>
+        <f>IF(COUNT(N67:N68)=2,(N67/N68-1)*100,"")</f>
         <v/>
       </c>
       <c r="P67" s="5" t="n"/>
       <c r="Q67" s="5">
-        <f>IF(AND(ISNUMBER(P67),ISNUMBER(P68)),(P67/P68-1)*100,"")</f>
+        <f>IF(COUNT(P67:P68)=2,(P67/P68-1)*100,"")</f>
         <v/>
       </c>
       <c r="R67" s="5" t="n"/>
       <c r="S67" s="5">
-        <f>IF(AND(ISNUMBER(R67),ISNUMBER(R68)),(R67/R68-1)*100,"")</f>
+        <f>IF(COUNT(R67:R68)=2,(R67/R68-1)*100,"")</f>
         <v/>
       </c>
       <c r="T67" s="5" t="n"/>
       <c r="U67" s="5">
-        <f>IF(AND(ISNUMBER(T67),ISNUMBER(T68)),(T67/T68-1)*100,"")</f>
+        <f>IF(COUNT(T67:T68)=2,(T67/T68-1)*100,"")</f>
         <v/>
       </c>
       <c r="V67" s="5" t="n"/>
@@ -7269,31 +7346,31 @@
         <v/>
       </c>
       <c r="X67" s="5">
+        <f>IF(AND(K67&lt;0,M67&gt;0),C66,"")</f>
+        <v/>
+      </c>
+      <c r="Y67" s="5">
         <f>IF(AND(G67&gt;0,I67&lt;0,K67&gt;0),C66,"")</f>
         <v/>
       </c>
-      <c r="Y67" s="5">
-        <f>IF(AND(K67&lt;0,M67&gt;0),C66,"")</f>
-        <v/>
-      </c>
       <c r="Z67" s="5">
-        <f>IF(AND(ISNUMBER(W67),0.549579&gt;=MAX(IF(ISNUMBER(X67),0.299732,-1),IF(ISNUMBER(Y67),0.323835,-1))),W67,IF(AND(ISNUMBER(X67),0.299732&gt;MAX(IF(ISNUMBER(W67),0.549579,-1),IF(ISNUMBER(Y67),0.323835,-1))),X67,IF(AND(ISNUMBER(Y67),0.323835&gt;MAX(IF(ISNUMBER(W67),0.549579,-1),IF(ISNUMBER(X67),0.299732,-1))),Y67,"")))</f>
+        <f>IF(W67&lt;&gt;"",W67,IF(X67&lt;&gt;"",X67,Y67))</f>
         <v/>
       </c>
       <c r="AA67" s="5">
+        <f>IF(AND(S67&gt;0,U67&lt;0),E66,"")</f>
+        <v/>
+      </c>
+      <c r="AB67" s="5">
         <f>IF(AND(O67&lt;=-1,E67&lt;0),E66,"")</f>
         <v/>
       </c>
-      <c r="AB67" s="5">
+      <c r="AC67" s="5">
         <f>IF(AND(Q67&gt;0,S67&gt;0),E66,"")</f>
         <v/>
       </c>
-      <c r="AC67" s="5">
-        <f>IF(AND(S67&gt;0,U67&lt;0),E66,"")</f>
-        <v/>
-      </c>
       <c r="AD67" s="5">
-        <f>IF(AND(ISNUMBER(AA67),0.408167&gt;=MAX(IF(ISNUMBER(AB67),0.31868,-1),IF(ISNUMBER(AC67),0.510996,-1))),AA67,IF(AND(ISNUMBER(AB67),0.31868&gt;MAX(IF(ISNUMBER(AA67),0.408167,-1),IF(ISNUMBER(AC67),0.510996,-1))),AB67,IF(AND(ISNUMBER(AC67),0.510996&gt;MAX(IF(ISNUMBER(AA67),0.408167,-1),IF(ISNUMBER(AB67),0.31868,-1))),AC67,"")))</f>
+        <f>IF(AA67&lt;&gt;"",AA67,IF(AB67&lt;&gt;"",AB67,AC67))</f>
         <v/>
       </c>
     </row>
@@ -7307,62 +7384,62 @@
         <v>161.66</v>
       </c>
       <c r="C68" s="5">
-        <f>IF(AND(ISNUMBER(B68),ISNUMBER(B69)),(B68/B69-1)*100,"")</f>
+        <f>IF(COUNT(B68:B69)=2,(B68/B69-1)*100,"")</f>
         <v/>
       </c>
       <c r="D68" s="5" t="n">
         <v>64.73350000000001</v>
       </c>
       <c r="E68" s="5">
-        <f>IF(AND(ISNUMBER(D68),ISNUMBER(D69)),(D68/D69-1)*100,"")</f>
+        <f>IF(COUNT(D68:D69)=2,(D68/D69-1)*100,"")</f>
         <v/>
       </c>
       <c r="F68" s="5" t="n">
         <v>78.3104</v>
       </c>
       <c r="G68" s="5">
-        <f>IF(AND(ISNUMBER(F68),ISNUMBER(F69)),(F68/F69-1)*100,"")</f>
+        <f>IF(COUNT(F68:F69)=2,(F68/F69-1)*100,"")</f>
         <v/>
       </c>
       <c r="H68" s="5" t="n">
         <v>50.9216</v>
       </c>
       <c r="I68" s="5">
-        <f>IF(AND(ISNUMBER(H68),ISNUMBER(H69)),(H68/H69-1)*100,"")</f>
+        <f>IF(COUNT(H68:H69)=2,(H68/H69-1)*100,"")</f>
         <v/>
       </c>
       <c r="J68" s="5" t="n">
         <v>87.34999999999999</v>
       </c>
       <c r="K68" s="5">
-        <f>IF(AND(ISNUMBER(J68),ISNUMBER(J69)),(J68/J69-1)*100,"")</f>
+        <f>IF(COUNT(J68:J69)=2,(J68/J69-1)*100,"")</f>
         <v/>
       </c>
       <c r="L68" s="5" t="n">
         <v>6.7787</v>
       </c>
       <c r="M68" s="5">
-        <f>IF(AND(ISNUMBER(L68),ISNUMBER(L69)),(L68/L69-1)*100,"")</f>
+        <f>IF(COUNT(L68:L69)=2,(L68/L69-1)*100,"")</f>
         <v/>
       </c>
       <c r="N68" s="5" t="n"/>
       <c r="O68" s="5">
-        <f>IF(AND(ISNUMBER(N68),ISNUMBER(N69)),(N68/N69-1)*100,"")</f>
+        <f>IF(COUNT(N68:N69)=2,(N68/N69-1)*100,"")</f>
         <v/>
       </c>
       <c r="P68" s="5" t="n"/>
       <c r="Q68" s="5">
-        <f>IF(AND(ISNUMBER(P68),ISNUMBER(P69)),(P68/P69-1)*100,"")</f>
+        <f>IF(COUNT(P68:P69)=2,(P68/P69-1)*100,"")</f>
         <v/>
       </c>
       <c r="R68" s="5" t="n"/>
       <c r="S68" s="5">
-        <f>IF(AND(ISNUMBER(R68),ISNUMBER(R69)),(R68/R69-1)*100,"")</f>
+        <f>IF(COUNT(R68:R69)=2,(R68/R69-1)*100,"")</f>
         <v/>
       </c>
       <c r="T68" s="5" t="n"/>
       <c r="U68" s="5">
-        <f>IF(AND(ISNUMBER(T68),ISNUMBER(T69)),(T68/T69-1)*100,"")</f>
+        <f>IF(COUNT(T68:T69)=2,(T68/T69-1)*100,"")</f>
         <v/>
       </c>
       <c r="V68" s="5" t="n"/>
@@ -7371,31 +7448,31 @@
         <v/>
       </c>
       <c r="X68" s="5">
+        <f>IF(AND(K68&lt;0,M68&gt;0),C67,"")</f>
+        <v/>
+      </c>
+      <c r="Y68" s="5">
         <f>IF(AND(G68&gt;0,I68&lt;0,K68&gt;0),C67,"")</f>
         <v/>
       </c>
-      <c r="Y68" s="5">
-        <f>IF(AND(K68&lt;0,M68&gt;0),C67,"")</f>
-        <v/>
-      </c>
       <c r="Z68" s="5">
-        <f>IF(AND(ISNUMBER(W68),0.549579&gt;=MAX(IF(ISNUMBER(X68),0.299732,-1),IF(ISNUMBER(Y68),0.323835,-1))),W68,IF(AND(ISNUMBER(X68),0.299732&gt;MAX(IF(ISNUMBER(W68),0.549579,-1),IF(ISNUMBER(Y68),0.323835,-1))),X68,IF(AND(ISNUMBER(Y68),0.323835&gt;MAX(IF(ISNUMBER(W68),0.549579,-1),IF(ISNUMBER(X68),0.299732,-1))),Y68,"")))</f>
+        <f>IF(W68&lt;&gt;"",W68,IF(X68&lt;&gt;"",X68,Y68))</f>
         <v/>
       </c>
       <c r="AA68" s="5">
+        <f>IF(AND(S68&gt;0,U68&lt;0),E67,"")</f>
+        <v/>
+      </c>
+      <c r="AB68" s="5">
         <f>IF(AND(O68&lt;=-1,E68&lt;0),E67,"")</f>
         <v/>
       </c>
-      <c r="AB68" s="5">
+      <c r="AC68" s="5">
         <f>IF(AND(Q68&gt;0,S68&gt;0),E67,"")</f>
         <v/>
       </c>
-      <c r="AC68" s="5">
-        <f>IF(AND(S68&gt;0,U68&lt;0),E67,"")</f>
-        <v/>
-      </c>
       <c r="AD68" s="5">
-        <f>IF(AND(ISNUMBER(AA68),0.408167&gt;=MAX(IF(ISNUMBER(AB68),0.31868,-1),IF(ISNUMBER(AC68),0.510996,-1))),AA68,IF(AND(ISNUMBER(AB68),0.31868&gt;MAX(IF(ISNUMBER(AA68),0.408167,-1),IF(ISNUMBER(AC68),0.510996,-1))),AB68,IF(AND(ISNUMBER(AC68),0.510996&gt;MAX(IF(ISNUMBER(AA68),0.408167,-1),IF(ISNUMBER(AB68),0.31868,-1))),AC68,"")))</f>
+        <f>IF(AA68&lt;&gt;"",AA68,IF(AB68&lt;&gt;"",AB68,AC68))</f>
         <v/>
       </c>
     </row>
@@ -7409,62 +7486,62 @@
         <v>166.77</v>
       </c>
       <c r="C69" s="5">
-        <f>IF(AND(ISNUMBER(B69),ISNUMBER(B70)),(B69/B70-1)*100,"")</f>
+        <f>IF(COUNT(B69:B70)=2,(B69/B70-1)*100,"")</f>
         <v/>
       </c>
       <c r="D69" s="5" t="n">
         <v>67.0316</v>
       </c>
       <c r="E69" s="5">
-        <f>IF(AND(ISNUMBER(D69),ISNUMBER(D70)),(D69/D70-1)*100,"")</f>
+        <f>IF(COUNT(D69:D70)=2,(D69/D70-1)*100,"")</f>
         <v/>
       </c>
       <c r="F69" s="5" t="n">
         <v>78.6947</v>
       </c>
       <c r="G69" s="5">
-        <f>IF(AND(ISNUMBER(F69),ISNUMBER(F70)),(F69/F70-1)*100,"")</f>
+        <f>IF(COUNT(F69:F70)=2,(F69/F70-1)*100,"")</f>
         <v/>
       </c>
       <c r="H69" s="5" t="n">
         <v>51.111</v>
       </c>
       <c r="I69" s="5">
-        <f>IF(AND(ISNUMBER(H69),ISNUMBER(H70)),(H69/H70-1)*100,"")</f>
+        <f>IF(COUNT(H69:H70)=2,(H69/H70-1)*100,"")</f>
         <v/>
       </c>
       <c r="J69" s="5" t="n">
         <v>93.95</v>
       </c>
       <c r="K69" s="5">
-        <f>IF(AND(ISNUMBER(J69),ISNUMBER(J70)),(J69/J70-1)*100,"")</f>
+        <f>IF(COUNT(J69:J70)=2,(J69/J70-1)*100,"")</f>
         <v/>
       </c>
       <c r="L69" s="5" t="n">
         <v>-3.4135</v>
       </c>
       <c r="M69" s="5">
-        <f>IF(AND(ISNUMBER(L69),ISNUMBER(L70)),(L69/L70-1)*100,"")</f>
+        <f>IF(COUNT(L69:L70)=2,(L69/L70-1)*100,"")</f>
         <v/>
       </c>
       <c r="N69" s="5" t="n"/>
       <c r="O69" s="5">
-        <f>IF(AND(ISNUMBER(N69),ISNUMBER(N70)),(N69/N70-1)*100,"")</f>
+        <f>IF(COUNT(N69:N70)=2,(N69/N70-1)*100,"")</f>
         <v/>
       </c>
       <c r="P69" s="5" t="n"/>
       <c r="Q69" s="5">
-        <f>IF(AND(ISNUMBER(P69),ISNUMBER(P70)),(P69/P70-1)*100,"")</f>
+        <f>IF(COUNT(P69:P70)=2,(P69/P70-1)*100,"")</f>
         <v/>
       </c>
       <c r="R69" s="5" t="n"/>
       <c r="S69" s="5">
-        <f>IF(AND(ISNUMBER(R69),ISNUMBER(R70)),(R69/R70-1)*100,"")</f>
+        <f>IF(COUNT(R69:R70)=2,(R69/R70-1)*100,"")</f>
         <v/>
       </c>
       <c r="T69" s="5" t="n"/>
       <c r="U69" s="5">
-        <f>IF(AND(ISNUMBER(T69),ISNUMBER(T70)),(T69/T70-1)*100,"")</f>
+        <f>IF(COUNT(T69:T70)=2,(T69/T70-1)*100,"")</f>
         <v/>
       </c>
       <c r="V69" s="5" t="n"/>
@@ -7473,31 +7550,31 @@
         <v/>
       </c>
       <c r="X69" s="5">
+        <f>IF(AND(K69&lt;0,M69&gt;0),C68,"")</f>
+        <v/>
+      </c>
+      <c r="Y69" s="5">
         <f>IF(AND(G69&gt;0,I69&lt;0,K69&gt;0),C68,"")</f>
         <v/>
       </c>
-      <c r="Y69" s="5">
-        <f>IF(AND(K69&lt;0,M69&gt;0),C68,"")</f>
-        <v/>
-      </c>
       <c r="Z69" s="5">
-        <f>IF(AND(ISNUMBER(W69),0.549579&gt;=MAX(IF(ISNUMBER(X69),0.299732,-1),IF(ISNUMBER(Y69),0.323835,-1))),W69,IF(AND(ISNUMBER(X69),0.299732&gt;MAX(IF(ISNUMBER(W69),0.549579,-1),IF(ISNUMBER(Y69),0.323835,-1))),X69,IF(AND(ISNUMBER(Y69),0.323835&gt;MAX(IF(ISNUMBER(W69),0.549579,-1),IF(ISNUMBER(X69),0.299732,-1))),Y69,"")))</f>
+        <f>IF(W69&lt;&gt;"",W69,IF(X69&lt;&gt;"",X69,Y69))</f>
         <v/>
       </c>
       <c r="AA69" s="5">
+        <f>IF(AND(S69&gt;0,U69&lt;0),E68,"")</f>
+        <v/>
+      </c>
+      <c r="AB69" s="5">
         <f>IF(AND(O69&lt;=-1,E69&lt;0),E68,"")</f>
         <v/>
       </c>
-      <c r="AB69" s="5">
+      <c r="AC69" s="5">
         <f>IF(AND(Q69&gt;0,S69&gt;0),E68,"")</f>
         <v/>
       </c>
-      <c r="AC69" s="5">
-        <f>IF(AND(S69&gt;0,U69&lt;0),E68,"")</f>
-        <v/>
-      </c>
       <c r="AD69" s="5">
-        <f>IF(AND(ISNUMBER(AA69),0.408167&gt;=MAX(IF(ISNUMBER(AB69),0.31868,-1),IF(ISNUMBER(AC69),0.510996,-1))),AA69,IF(AND(ISNUMBER(AB69),0.31868&gt;MAX(IF(ISNUMBER(AA69),0.408167,-1),IF(ISNUMBER(AC69),0.510996,-1))),AB69,IF(AND(ISNUMBER(AC69),0.510996&gt;MAX(IF(ISNUMBER(AA69),0.408167,-1),IF(ISNUMBER(AB69),0.31868,-1))),AC69,"")))</f>
+        <f>IF(AA69&lt;&gt;"",AA69,IF(AB69&lt;&gt;"",AB69,AC69))</f>
         <v/>
       </c>
     </row>
@@ -7511,62 +7588,62 @@
         <v>164.41</v>
       </c>
       <c r="C70" s="5">
-        <f>IF(AND(ISNUMBER(B70),ISNUMBER(B71)),(B70/B71-1)*100,"")</f>
+        <f>IF(COUNT(B70:B71)=2,(B70/B71-1)*100,"")</f>
         <v/>
       </c>
       <c r="D70" s="5" t="n">
         <v>66.8625</v>
       </c>
       <c r="E70" s="5">
-        <f>IF(AND(ISNUMBER(D70),ISNUMBER(D71)),(D70/D71-1)*100,"")</f>
+        <f>IF(COUNT(D70:D71)=2,(D70/D71-1)*100,"")</f>
         <v/>
       </c>
       <c r="F70" s="5" t="n">
         <v>78.7539</v>
       </c>
       <c r="G70" s="5">
-        <f>IF(AND(ISNUMBER(F70),ISNUMBER(F71)),(F70/F71-1)*100,"")</f>
+        <f>IF(COUNT(F70:F71)=2,(F70/F71-1)*100,"")</f>
         <v/>
       </c>
       <c r="H70" s="5" t="n">
         <v>50.812</v>
       </c>
       <c r="I70" s="5">
-        <f>IF(AND(ISNUMBER(H70),ISNUMBER(H71)),(H70/H71-1)*100,"")</f>
+        <f>IF(COUNT(H70:H71)=2,(H70/H71-1)*100,"")</f>
         <v/>
       </c>
       <c r="J70" s="5" t="n">
         <v>96.23</v>
       </c>
       <c r="K70" s="5">
-        <f>IF(AND(ISNUMBER(J70),ISNUMBER(J71)),(J70/J71-1)*100,"")</f>
+        <f>IF(COUNT(J70:J71)=2,(J70/J71-1)*100,"")</f>
         <v/>
       </c>
       <c r="L70" s="5" t="n">
         <v>-0.667</v>
       </c>
       <c r="M70" s="5">
-        <f>IF(AND(ISNUMBER(L70),ISNUMBER(L71)),(L70/L71-1)*100,"")</f>
+        <f>IF(COUNT(L70:L71)=2,(L70/L71-1)*100,"")</f>
         <v/>
       </c>
       <c r="N70" s="5" t="n"/>
       <c r="O70" s="5">
-        <f>IF(AND(ISNUMBER(N70),ISNUMBER(N71)),(N70/N71-1)*100,"")</f>
+        <f>IF(COUNT(N70:N71)=2,(N70/N71-1)*100,"")</f>
         <v/>
       </c>
       <c r="P70" s="5" t="n"/>
       <c r="Q70" s="5">
-        <f>IF(AND(ISNUMBER(P70),ISNUMBER(P71)),(P70/P71-1)*100,"")</f>
+        <f>IF(COUNT(P70:P71)=2,(P70/P71-1)*100,"")</f>
         <v/>
       </c>
       <c r="R70" s="5" t="n"/>
       <c r="S70" s="5">
-        <f>IF(AND(ISNUMBER(R70),ISNUMBER(R71)),(R70/R71-1)*100,"")</f>
+        <f>IF(COUNT(R70:R71)=2,(R70/R71-1)*100,"")</f>
         <v/>
       </c>
       <c r="T70" s="5" t="n"/>
       <c r="U70" s="5">
-        <f>IF(AND(ISNUMBER(T70),ISNUMBER(T71)),(T70/T71-1)*100,"")</f>
+        <f>IF(COUNT(T70:T71)=2,(T70/T71-1)*100,"")</f>
         <v/>
       </c>
       <c r="V70" s="5" t="n"/>
@@ -7575,31 +7652,31 @@
         <v/>
       </c>
       <c r="X70" s="5">
+        <f>IF(AND(K70&lt;0,M70&gt;0),C69,"")</f>
+        <v/>
+      </c>
+      <c r="Y70" s="5">
         <f>IF(AND(G70&gt;0,I70&lt;0,K70&gt;0),C69,"")</f>
         <v/>
       </c>
-      <c r="Y70" s="5">
-        <f>IF(AND(K70&lt;0,M70&gt;0),C69,"")</f>
-        <v/>
-      </c>
       <c r="Z70" s="5">
-        <f>IF(AND(ISNUMBER(W70),0.549579&gt;=MAX(IF(ISNUMBER(X70),0.299732,-1),IF(ISNUMBER(Y70),0.323835,-1))),W70,IF(AND(ISNUMBER(X70),0.299732&gt;MAX(IF(ISNUMBER(W70),0.549579,-1),IF(ISNUMBER(Y70),0.323835,-1))),X70,IF(AND(ISNUMBER(Y70),0.323835&gt;MAX(IF(ISNUMBER(W70),0.549579,-1),IF(ISNUMBER(X70),0.299732,-1))),Y70,"")))</f>
+        <f>IF(W70&lt;&gt;"",W70,IF(X70&lt;&gt;"",X70,Y70))</f>
         <v/>
       </c>
       <c r="AA70" s="5">
+        <f>IF(AND(S70&gt;0,U70&lt;0),E69,"")</f>
+        <v/>
+      </c>
+      <c r="AB70" s="5">
         <f>IF(AND(O70&lt;=-1,E70&lt;0),E69,"")</f>
         <v/>
       </c>
-      <c r="AB70" s="5">
+      <c r="AC70" s="5">
         <f>IF(AND(Q70&gt;0,S70&gt;0),E69,"")</f>
         <v/>
       </c>
-      <c r="AC70" s="5">
-        <f>IF(AND(S70&gt;0,U70&lt;0),E69,"")</f>
-        <v/>
-      </c>
       <c r="AD70" s="5">
-        <f>IF(AND(ISNUMBER(AA70),0.408167&gt;=MAX(IF(ISNUMBER(AB70),0.31868,-1),IF(ISNUMBER(AC70),0.510996,-1))),AA70,IF(AND(ISNUMBER(AB70),0.31868&gt;MAX(IF(ISNUMBER(AA70),0.408167,-1),IF(ISNUMBER(AC70),0.510996,-1))),AB70,IF(AND(ISNUMBER(AC70),0.510996&gt;MAX(IF(ISNUMBER(AA70),0.408167,-1),IF(ISNUMBER(AB70),0.31868,-1))),AC70,"")))</f>
+        <f>IF(AA70&lt;&gt;"",AA70,IF(AB70&lt;&gt;"",AB70,AC70))</f>
         <v/>
       </c>
     </row>
@@ -7613,62 +7690,62 @@
         <v>161.07</v>
       </c>
       <c r="C71" s="5">
-        <f>IF(AND(ISNUMBER(B71),ISNUMBER(B72)),(B71/B72-1)*100,"")</f>
+        <f>IF(COUNT(B71:B72)=2,(B71/B72-1)*100,"")</f>
         <v/>
       </c>
       <c r="D71" s="5" t="n">
         <v>65.47969999999999</v>
       </c>
       <c r="E71" s="5">
-        <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72)),(D71/D72-1)*100,"")</f>
+        <f>IF(COUNT(D71:D72)=2,(D71/D72-1)*100,"")</f>
         <v/>
       </c>
       <c r="F71" s="5" t="n">
         <v>78.7144</v>
       </c>
       <c r="G71" s="5">
-        <f>IF(AND(ISNUMBER(F71),ISNUMBER(F72)),(F71/F72-1)*100,"")</f>
+        <f>IF(COUNT(F71:F72)=2,(F71/F72-1)*100,"")</f>
         <v/>
       </c>
       <c r="H71" s="5" t="n">
         <v>51.3999</v>
       </c>
       <c r="I71" s="5">
-        <f>IF(AND(ISNUMBER(H71),ISNUMBER(H72)),(H71/H72-1)*100,"")</f>
+        <f>IF(COUNT(H71:H72)=2,(H71/H72-1)*100,"")</f>
         <v/>
       </c>
       <c r="J71" s="5" t="n">
         <v>97.14</v>
       </c>
       <c r="K71" s="5">
-        <f>IF(AND(ISNUMBER(J71),ISNUMBER(J72)),(J71/J72-1)*100,"")</f>
+        <f>IF(COUNT(J71:J72)=2,(J71/J72-1)*100,"")</f>
         <v/>
       </c>
       <c r="L71" s="5" t="n">
         <v>-2.1219</v>
       </c>
       <c r="M71" s="5">
-        <f>IF(AND(ISNUMBER(L71),ISNUMBER(L72)),(L71/L72-1)*100,"")</f>
+        <f>IF(COUNT(L71:L72)=2,(L71/L72-1)*100,"")</f>
         <v/>
       </c>
       <c r="N71" s="5" t="n"/>
       <c r="O71" s="5">
-        <f>IF(AND(ISNUMBER(N71),ISNUMBER(N72)),(N71/N72-1)*100,"")</f>
+        <f>IF(COUNT(N71:N72)=2,(N71/N72-1)*100,"")</f>
         <v/>
       </c>
       <c r="P71" s="5" t="n"/>
       <c r="Q71" s="5">
-        <f>IF(AND(ISNUMBER(P71),ISNUMBER(P72)),(P71/P72-1)*100,"")</f>
+        <f>IF(COUNT(P71:P72)=2,(P71/P72-1)*100,"")</f>
         <v/>
       </c>
       <c r="R71" s="5" t="n"/>
       <c r="S71" s="5">
-        <f>IF(AND(ISNUMBER(R71),ISNUMBER(R72)),(R71/R72-1)*100,"")</f>
+        <f>IF(COUNT(R71:R72)=2,(R71/R72-1)*100,"")</f>
         <v/>
       </c>
       <c r="T71" s="5" t="n"/>
       <c r="U71" s="5">
-        <f>IF(AND(ISNUMBER(T71),ISNUMBER(T72)),(T71/T72-1)*100,"")</f>
+        <f>IF(COUNT(T71:T72)=2,(T71/T72-1)*100,"")</f>
         <v/>
       </c>
       <c r="V71" s="5" t="n"/>
@@ -7677,31 +7754,31 @@
         <v/>
       </c>
       <c r="X71" s="5">
+        <f>IF(AND(K71&lt;0,M71&gt;0),C70,"")</f>
+        <v/>
+      </c>
+      <c r="Y71" s="5">
         <f>IF(AND(G71&gt;0,I71&lt;0,K71&gt;0),C70,"")</f>
         <v/>
       </c>
-      <c r="Y71" s="5">
-        <f>IF(AND(K71&lt;0,M71&gt;0),C70,"")</f>
-        <v/>
-      </c>
       <c r="Z71" s="5">
-        <f>IF(AND(ISNUMBER(W71),0.549579&gt;=MAX(IF(ISNUMBER(X71),0.299732,-1),IF(ISNUMBER(Y71),0.323835,-1))),W71,IF(AND(ISNUMBER(X71),0.299732&gt;MAX(IF(ISNUMBER(W71),0.549579,-1),IF(ISNUMBER(Y71),0.323835,-1))),X71,IF(AND(ISNUMBER(Y71),0.323835&gt;MAX(IF(ISNUMBER(W71),0.549579,-1),IF(ISNUMBER(X71),0.299732,-1))),Y71,"")))</f>
+        <f>IF(W71&lt;&gt;"",W71,IF(X71&lt;&gt;"",X71,Y71))</f>
         <v/>
       </c>
       <c r="AA71" s="5">
+        <f>IF(AND(S71&gt;0,U71&lt;0),E70,"")</f>
+        <v/>
+      </c>
+      <c r="AB71" s="5">
         <f>IF(AND(O71&lt;=-1,E71&lt;0),E70,"")</f>
         <v/>
       </c>
-      <c r="AB71" s="5">
+      <c r="AC71" s="5">
         <f>IF(AND(Q71&gt;0,S71&gt;0),E70,"")</f>
         <v/>
       </c>
-      <c r="AC71" s="5">
-        <f>IF(AND(S71&gt;0,U71&lt;0),E70,"")</f>
-        <v/>
-      </c>
       <c r="AD71" s="5">
-        <f>IF(AND(ISNUMBER(AA71),0.408167&gt;=MAX(IF(ISNUMBER(AB71),0.31868,-1),IF(ISNUMBER(AC71),0.510996,-1))),AA71,IF(AND(ISNUMBER(AB71),0.31868&gt;MAX(IF(ISNUMBER(AA71),0.408167,-1),IF(ISNUMBER(AC71),0.510996,-1))),AB71,IF(AND(ISNUMBER(AC71),0.510996&gt;MAX(IF(ISNUMBER(AA71),0.408167,-1),IF(ISNUMBER(AB71),0.31868,-1))),AC71,"")))</f>
+        <f>IF(AA71&lt;&gt;"",AA71,IF(AB71&lt;&gt;"",AB71,AC71))</f>
         <v/>
       </c>
     </row>
@@ -7715,62 +7792,62 @@
         <v>163.95</v>
       </c>
       <c r="C72" s="5">
-        <f>IF(AND(ISNUMBER(B72),ISNUMBER(B73)),(B72/B73-1)*100,"")</f>
+        <f>IF(COUNT(B72:B73)=2,(B72/B73-1)*100,"")</f>
         <v/>
       </c>
       <c r="D72" s="5" t="n">
         <v>67.5389</v>
       </c>
       <c r="E72" s="5">
-        <f>IF(AND(ISNUMBER(D72),ISNUMBER(D73)),(D72/D73-1)*100,"")</f>
+        <f>IF(COUNT(D72:D73)=2,(D72/D73-1)*100,"")</f>
         <v/>
       </c>
       <c r="F72" s="5" t="n">
         <v>78.8228</v>
       </c>
       <c r="G72" s="5">
-        <f>IF(AND(ISNUMBER(F72),ISNUMBER(F73)),(F72/F73-1)*100,"")</f>
+        <f>IF(COUNT(F72:F73)=2,(F72/F73-1)*100,"")</f>
         <v/>
       </c>
       <c r="H72" s="5" t="n">
         <v>51.0013</v>
       </c>
       <c r="I72" s="5">
-        <f>IF(AND(ISNUMBER(H72),ISNUMBER(H73)),(H72/H73-1)*100,"")</f>
+        <f>IF(COUNT(H72:H73)=2,(H72/H73-1)*100,"")</f>
         <v/>
       </c>
       <c r="J72" s="5" t="n">
         <v>97.59999999999999</v>
       </c>
       <c r="K72" s="5">
-        <f>IF(AND(ISNUMBER(J72),ISNUMBER(J73)),(J72/J73-1)*100,"")</f>
+        <f>IF(COUNT(J72:J73)=2,(J72/J73-1)*100,"")</f>
         <v/>
       </c>
       <c r="L72" s="5" t="n">
         <v>6.9226</v>
       </c>
       <c r="M72" s="5">
-        <f>IF(AND(ISNUMBER(L72),ISNUMBER(L73)),(L72/L73-1)*100,"")</f>
+        <f>IF(COUNT(L72:L73)=2,(L72/L73-1)*100,"")</f>
         <v/>
       </c>
       <c r="N72" s="5" t="n"/>
       <c r="O72" s="5">
-        <f>IF(AND(ISNUMBER(N72),ISNUMBER(N73)),(N72/N73-1)*100,"")</f>
+        <f>IF(COUNT(N72:N73)=2,(N72/N73-1)*100,"")</f>
         <v/>
       </c>
       <c r="P72" s="5" t="n"/>
       <c r="Q72" s="5">
-        <f>IF(AND(ISNUMBER(P72),ISNUMBER(P73)),(P72/P73-1)*100,"")</f>
+        <f>IF(COUNT(P72:P73)=2,(P72/P73-1)*100,"")</f>
         <v/>
       </c>
       <c r="R72" s="5" t="n"/>
       <c r="S72" s="5">
-        <f>IF(AND(ISNUMBER(R72),ISNUMBER(R73)),(R72/R73-1)*100,"")</f>
+        <f>IF(COUNT(R72:R73)=2,(R72/R73-1)*100,"")</f>
         <v/>
       </c>
       <c r="T72" s="5" t="n"/>
       <c r="U72" s="5">
-        <f>IF(AND(ISNUMBER(T72),ISNUMBER(T73)),(T72/T73-1)*100,"")</f>
+        <f>IF(COUNT(T72:T73)=2,(T72/T73-1)*100,"")</f>
         <v/>
       </c>
       <c r="V72" s="5" t="n"/>
@@ -7779,31 +7856,31 @@
         <v/>
       </c>
       <c r="X72" s="5">
+        <f>IF(AND(K72&lt;0,M72&gt;0),C71,"")</f>
+        <v/>
+      </c>
+      <c r="Y72" s="5">
         <f>IF(AND(G72&gt;0,I72&lt;0,K72&gt;0),C71,"")</f>
         <v/>
       </c>
-      <c r="Y72" s="5">
-        <f>IF(AND(K72&lt;0,M72&gt;0),C71,"")</f>
-        <v/>
-      </c>
       <c r="Z72" s="5">
-        <f>IF(AND(ISNUMBER(W72),0.549579&gt;=MAX(IF(ISNUMBER(X72),0.299732,-1),IF(ISNUMBER(Y72),0.323835,-1))),W72,IF(AND(ISNUMBER(X72),0.299732&gt;MAX(IF(ISNUMBER(W72),0.549579,-1),IF(ISNUMBER(Y72),0.323835,-1))),X72,IF(AND(ISNUMBER(Y72),0.323835&gt;MAX(IF(ISNUMBER(W72),0.549579,-1),IF(ISNUMBER(X72),0.299732,-1))),Y72,"")))</f>
+        <f>IF(W72&lt;&gt;"",W72,IF(X72&lt;&gt;"",X72,Y72))</f>
         <v/>
       </c>
       <c r="AA72" s="5">
+        <f>IF(AND(S72&gt;0,U72&lt;0),E71,"")</f>
+        <v/>
+      </c>
+      <c r="AB72" s="5">
         <f>IF(AND(O72&lt;=-1,E72&lt;0),E71,"")</f>
         <v/>
       </c>
-      <c r="AB72" s="5">
+      <c r="AC72" s="5">
         <f>IF(AND(Q72&gt;0,S72&gt;0),E71,"")</f>
         <v/>
       </c>
-      <c r="AC72" s="5">
-        <f>IF(AND(S72&gt;0,U72&lt;0),E71,"")</f>
-        <v/>
-      </c>
       <c r="AD72" s="5">
-        <f>IF(AND(ISNUMBER(AA72),0.408167&gt;=MAX(IF(ISNUMBER(AB72),0.31868,-1),IF(ISNUMBER(AC72),0.510996,-1))),AA72,IF(AND(ISNUMBER(AB72),0.31868&gt;MAX(IF(ISNUMBER(AA72),0.408167,-1),IF(ISNUMBER(AC72),0.510996,-1))),AB72,IF(AND(ISNUMBER(AC72),0.510996&gt;MAX(IF(ISNUMBER(AA72),0.408167,-1),IF(ISNUMBER(AB72),0.31868,-1))),AC72,"")))</f>
+        <f>IF(AA72&lt;&gt;"",AA72,IF(AB72&lt;&gt;"",AB72,AC72))</f>
         <v/>
       </c>
     </row>
@@ -7851,31 +7928,31 @@
         <v/>
       </c>
       <c r="X73" s="5">
+        <f>IF(AND(K73&lt;0,M73&gt;0),C72,"")</f>
+        <v/>
+      </c>
+      <c r="Y73" s="5">
         <f>IF(AND(G73&gt;0,I73&lt;0,K73&gt;0),C72,"")</f>
         <v/>
       </c>
-      <c r="Y73" s="5">
-        <f>IF(AND(K73&lt;0,M73&gt;0),C72,"")</f>
-        <v/>
-      </c>
       <c r="Z73" s="5">
-        <f>IF(AND(ISNUMBER(W73),0.549579&gt;=MAX(IF(ISNUMBER(X73),0.299732,-1),IF(ISNUMBER(Y73),0.323835,-1))),W73,IF(AND(ISNUMBER(X73),0.299732&gt;MAX(IF(ISNUMBER(W73),0.549579,-1),IF(ISNUMBER(Y73),0.323835,-1))),X73,IF(AND(ISNUMBER(Y73),0.323835&gt;MAX(IF(ISNUMBER(W73),0.549579,-1),IF(ISNUMBER(X73),0.299732,-1))),Y73,"")))</f>
+        <f>IF(W73&lt;&gt;"",W73,IF(X73&lt;&gt;"",X73,Y73))</f>
         <v/>
       </c>
       <c r="AA73" s="5">
+        <f>IF(AND(S73&gt;0,U73&lt;0),E72,"")</f>
+        <v/>
+      </c>
+      <c r="AB73" s="5">
         <f>IF(AND(O73&lt;=-1,E73&lt;0),E72,"")</f>
         <v/>
       </c>
-      <c r="AB73" s="5">
+      <c r="AC73" s="5">
         <f>IF(AND(Q73&gt;0,S73&gt;0),E72,"")</f>
         <v/>
       </c>
-      <c r="AC73" s="5">
-        <f>IF(AND(S73&gt;0,U73&lt;0),E72,"")</f>
-        <v/>
-      </c>
       <c r="AD73" s="5">
-        <f>IF(AND(ISNUMBER(AA73),0.408167&gt;=MAX(IF(ISNUMBER(AB73),0.31868,-1),IF(ISNUMBER(AC73),0.510996,-1))),AA73,IF(AND(ISNUMBER(AB73),0.31868&gt;MAX(IF(ISNUMBER(AA73),0.408167,-1),IF(ISNUMBER(AC73),0.510996,-1))),AB73,IF(AND(ISNUMBER(AC73),0.510996&gt;MAX(IF(ISNUMBER(AA73),0.408167,-1),IF(ISNUMBER(AB73),0.31868,-1))),AC73,"")))</f>
+        <f>IF(AA73&lt;&gt;"",AA73,IF(AB73&lt;&gt;"",AB73,AC73))</f>
         <v/>
       </c>
     </row>

--- a/04_结果/示例审批/两基金_m30新版式示例_公式说明版.xlsx
+++ b/04_结果/示例审批/两基金_m30新版式示例_公式说明版.xlsx
@@ -2106,14 +2106,14 @@
         <v/>
       </c>
       <c r="V14" s="5" t="n">
-        <v/>
+        <v>16.5</v>
       </c>
       <c r="W14" s="5">
         <f>IF(COUNT(V14:V15)=2,(V14/V15-1)*100,"")</f>
         <v/>
       </c>
       <c r="X14" s="5" t="n">
-        <v/>
+        <v>4.0353</v>
       </c>
       <c r="Y14" s="5" t="inlineStr"/>
       <c r="Z14" s="5" t="inlineStr"/>
@@ -2207,14 +2207,14 @@
         <v/>
       </c>
       <c r="V15" s="5" t="n">
-        <v/>
+        <v>15.86</v>
       </c>
       <c r="W15" s="5">
         <f>IF(COUNT(V15:V16)=2,(V15/V16-1)*100,"")</f>
         <v/>
       </c>
       <c r="X15" s="5" t="n">
-        <v/>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="Y15" s="5">
         <f>IF(AND(X15&gt;$Y$11,C15&lt;=$Y$12),C14,"")</f>
@@ -2326,14 +2326,14 @@
         <v/>
       </c>
       <c r="V16" s="5" t="n">
-        <v/>
+        <v>15.99</v>
       </c>
       <c r="W16" s="5">
         <f>IF(COUNT(V16:V17)=2,(V16/V17-1)*100,"")</f>
         <v/>
       </c>
       <c r="X16" s="5" t="n">
-        <v/>
+        <v>-6.4365</v>
       </c>
       <c r="Y16" s="5">
         <f>IF(AND(X16&gt;$Y$11,C16&lt;=$Y$12),C15,"")</f>
@@ -2445,14 +2445,14 @@
         <v/>
       </c>
       <c r="V17" s="5" t="n">
-        <v/>
+        <v>17.09</v>
       </c>
       <c r="W17" s="5">
         <f>IF(COUNT(V17:V18)=2,(V17/V18-1)*100,"")</f>
         <v/>
       </c>
       <c r="X17" s="5" t="n">
-        <v/>
+        <v>-17.2798</v>
       </c>
       <c r="Y17" s="5">
         <f>IF(AND(X17&gt;$Y$11,C17&lt;=$Y$12),C16,"")</f>
@@ -2564,14 +2564,14 @@
         <v/>
       </c>
       <c r="V18" s="5" t="n">
-        <v/>
+        <v>20.66</v>
       </c>
       <c r="W18" s="5">
         <f>IF(COUNT(V18:V19)=2,(V18/V19-1)*100,"")</f>
         <v/>
       </c>
       <c r="X18" s="5" t="n">
-        <v/>
+        <v>13.4541</v>
       </c>
       <c r="Y18" s="5">
         <f>IF(AND(X18&gt;$Y$11,C18&lt;=$Y$12),C17,"")</f>
@@ -2683,14 +2683,14 @@
         <v/>
       </c>
       <c r="V19" s="5" t="n">
-        <v/>
+        <v>18.21</v>
       </c>
       <c r="W19" s="5">
         <f>IF(COUNT(V19:V20)=2,(V19/V20-1)*100,"")</f>
         <v/>
       </c>
       <c r="X19" s="5" t="n">
-        <v/>
+        <v>-2.4638</v>
       </c>
       <c r="Y19" s="5">
         <f>IF(AND(X19&gt;$Y$11,C19&lt;=$Y$12),C18,"")</f>
@@ -2802,14 +2802,14 @@
         <v/>
       </c>
       <c r="V20" s="5" t="n">
-        <v/>
+        <v>18.67</v>
       </c>
       <c r="W20" s="5">
         <f>IF(COUNT(V20:V21)=2,(V20/V21-1)*100,"")</f>
         <v/>
       </c>
       <c r="X20" s="5" t="n">
-        <v/>
+        <v>0.4844</v>
       </c>
       <c r="Y20" s="5">
         <f>IF(AND(X20&gt;$Y$11,C20&lt;=$Y$12),C19,"")</f>

--- a/04_结果/示例审批/两基金_m30新版式示例_公式说明版.xlsx
+++ b/04_结果/示例审批/两基金_m30新版式示例_公式说明版.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -512,14 +512,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   =IF(COUNT(B14:B15)=2,(B14/B15-1)*100,"")</t>
+          <t xml:space="preserve">   =IF(COUNT(B15:B16)=2,(B15/B16-1)*100,"")</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   B14 是今日 Adj Close，B15 是前一交易日 Adj Close；</t>
+          <t xml:space="preserve">   B15 是今日 Adj Close，B16 是前一交易日 Adj Close；</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   每个策略列正上方的第11/12行是该策略条件阈值，修改数字可调整条件，公式自动更新。</t>
+          <t xml:space="preserve">   每个策略列正上方的第11/12/13行是该策略条件阈值：二条件用12/13行，三条件额外用11行；</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   修改数字可调整条件，公式自动更新。</t>
         </is>
       </c>
     </row>
@@ -611,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AF73"/>
+  <dimension ref="A2:AF74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -786,127 +793,127 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(B14:B73,"&gt;0")</f>
+        <f>COUNTIF(B15:B74,"&gt;0")</f>
         <v/>
       </c>
       <c r="C3" s="3">
-        <f>COUNTIF(C14:C73,"&gt;0")</f>
+        <f>COUNTIF(C15:C74,"&gt;0")</f>
         <v/>
       </c>
       <c r="D3" s="3">
-        <f>COUNTIF(D14:D73,"&gt;0")</f>
+        <f>COUNTIF(D15:D74,"&gt;0")</f>
         <v/>
       </c>
       <c r="E3" s="3">
-        <f>COUNTIF(E14:E73,"&gt;0")</f>
+        <f>COUNTIF(E15:E74,"&gt;0")</f>
         <v/>
       </c>
       <c r="F3" s="3">
-        <f>COUNTIF(F14:F73,"&gt;0")</f>
+        <f>COUNTIF(F15:F74,"&gt;0")</f>
         <v/>
       </c>
       <c r="G3" s="3">
-        <f>COUNTIF(G14:G73,"&gt;0")</f>
+        <f>COUNTIF(G15:G74,"&gt;0")</f>
         <v/>
       </c>
       <c r="H3" s="3">
-        <f>COUNTIF(H14:H73,"&gt;0")</f>
+        <f>COUNTIF(H15:H74,"&gt;0")</f>
         <v/>
       </c>
       <c r="I3" s="3">
-        <f>COUNTIF(I14:I73,"&gt;0")</f>
+        <f>COUNTIF(I15:I74,"&gt;0")</f>
         <v/>
       </c>
       <c r="J3" s="3">
-        <f>COUNTIF(J14:J73,"&gt;0")</f>
+        <f>COUNTIF(J15:J74,"&gt;0")</f>
         <v/>
       </c>
       <c r="K3" s="3">
-        <f>COUNTIF(K14:K73,"&gt;0")</f>
+        <f>COUNTIF(K15:K74,"&gt;0")</f>
         <v/>
       </c>
       <c r="L3" s="3">
-        <f>COUNTIF(L14:L73,"&gt;0")</f>
+        <f>COUNTIF(L15:L74,"&gt;0")</f>
         <v/>
       </c>
       <c r="M3" s="3">
-        <f>COUNTIF(M14:M73,"&gt;0")</f>
+        <f>COUNTIF(M15:M74,"&gt;0")</f>
         <v/>
       </c>
       <c r="N3" s="3">
-        <f>COUNTIF(N14:N73,"&gt;0")</f>
+        <f>COUNTIF(N15:N74,"&gt;0")</f>
         <v/>
       </c>
       <c r="O3" s="3">
-        <f>COUNTIF(O14:O73,"&gt;0")</f>
+        <f>COUNTIF(O15:O74,"&gt;0")</f>
         <v/>
       </c>
       <c r="P3" s="3">
-        <f>COUNTIF(P14:P73,"&gt;0")</f>
+        <f>COUNTIF(P15:P74,"&gt;0")</f>
         <v/>
       </c>
       <c r="Q3" s="3">
-        <f>COUNTIF(Q14:Q73,"&gt;0")</f>
+        <f>COUNTIF(Q15:Q74,"&gt;0")</f>
         <v/>
       </c>
       <c r="R3" s="3">
-        <f>COUNTIF(R14:R73,"&gt;0")</f>
+        <f>COUNTIF(R15:R74,"&gt;0")</f>
         <v/>
       </c>
       <c r="S3" s="3">
-        <f>COUNTIF(S14:S73,"&gt;0")</f>
+        <f>COUNTIF(S15:S74,"&gt;0")</f>
         <v/>
       </c>
       <c r="T3" s="3">
-        <f>COUNTIF(T14:T73,"&gt;0")</f>
+        <f>COUNTIF(T15:T74,"&gt;0")</f>
         <v/>
       </c>
       <c r="U3" s="3">
-        <f>COUNTIF(U14:U73,"&gt;0")</f>
+        <f>COUNTIF(U15:U74,"&gt;0")</f>
         <v/>
       </c>
       <c r="V3" s="3">
-        <f>COUNTIF(V14:V73,"&gt;0")</f>
+        <f>COUNTIF(V15:V74,"&gt;0")</f>
         <v/>
       </c>
       <c r="W3" s="3">
-        <f>COUNTIF(W14:W73,"&gt;0")</f>
+        <f>COUNTIF(W15:W74,"&gt;0")</f>
         <v/>
       </c>
       <c r="X3" s="3">
-        <f>COUNTIF(X14:X73,"&gt;0")</f>
+        <f>COUNTIF(X15:X74,"&gt;0")</f>
         <v/>
       </c>
       <c r="Y3" s="3">
-        <f>COUNTIF(Y14:Y73,"&gt;0")</f>
+        <f>COUNTIF(Y15:Y74,"&gt;0")</f>
         <v/>
       </c>
       <c r="Z3" s="3">
-        <f>COUNTIF(Z14:Z73,"&gt;0")</f>
+        <f>COUNTIF(Z15:Z74,"&gt;0")</f>
         <v/>
       </c>
       <c r="AA3" s="3">
-        <f>COUNTIF(AA14:AA73,"&gt;0")</f>
+        <f>COUNTIF(AA15:AA74,"&gt;0")</f>
         <v/>
       </c>
       <c r="AB3" s="3">
-        <f>COUNTIF(AB14:AB73,"&gt;0")</f>
+        <f>COUNTIF(AB15:AB74,"&gt;0")</f>
         <v/>
       </c>
       <c r="AC3" s="3">
-        <f>COUNTIF(AC14:AC73,"&gt;0")</f>
+        <f>COUNTIF(AC15:AC74,"&gt;0")</f>
         <v/>
       </c>
       <c r="AD3" s="3">
-        <f>COUNTIF(AD14:AD73,"&gt;0")</f>
+        <f>COUNTIF(AD15:AD74,"&gt;0")</f>
         <v/>
       </c>
       <c r="AE3" s="3">
-        <f>COUNTIF(AE14:AE73,"&gt;0")</f>
+        <f>COUNTIF(AE15:AE74,"&gt;0")</f>
         <v/>
       </c>
       <c r="AF3" s="3">
-        <f>COUNTIF(AF14:AF73,"&gt;0")</f>
+        <f>COUNTIF(AF15:AF74,"&gt;0")</f>
         <v/>
       </c>
     </row>
@@ -917,127 +924,127 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF(B14:B73,"&lt;0")</f>
+        <f>COUNTIF(B15:B74,"&lt;0")</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>COUNTIF(C14:C73,"&lt;0")</f>
+        <f>COUNTIF(C15:C74,"&lt;0")</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>COUNTIF(D14:D73,"&lt;0")</f>
+        <f>COUNTIF(D15:D74,"&lt;0")</f>
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>COUNTIF(E14:E73,"&lt;0")</f>
+        <f>COUNTIF(E15:E74,"&lt;0")</f>
         <v/>
       </c>
       <c r="F4" s="3">
-        <f>COUNTIF(F14:F73,"&lt;0")</f>
+        <f>COUNTIF(F15:F74,"&lt;0")</f>
         <v/>
       </c>
       <c r="G4" s="3">
-        <f>COUNTIF(G14:G73,"&lt;0")</f>
+        <f>COUNTIF(G15:G74,"&lt;0")</f>
         <v/>
       </c>
       <c r="H4" s="3">
-        <f>COUNTIF(H14:H73,"&lt;0")</f>
+        <f>COUNTIF(H15:H74,"&lt;0")</f>
         <v/>
       </c>
       <c r="I4" s="3">
-        <f>COUNTIF(I14:I73,"&lt;0")</f>
+        <f>COUNTIF(I15:I74,"&lt;0")</f>
         <v/>
       </c>
       <c r="J4" s="3">
-        <f>COUNTIF(J14:J73,"&lt;0")</f>
+        <f>COUNTIF(J15:J74,"&lt;0")</f>
         <v/>
       </c>
       <c r="K4" s="3">
-        <f>COUNTIF(K14:K73,"&lt;0")</f>
+        <f>COUNTIF(K15:K74,"&lt;0")</f>
         <v/>
       </c>
       <c r="L4" s="3">
-        <f>COUNTIF(L14:L73,"&lt;0")</f>
+        <f>COUNTIF(L15:L74,"&lt;0")</f>
         <v/>
       </c>
       <c r="M4" s="3">
-        <f>COUNTIF(M14:M73,"&lt;0")</f>
+        <f>COUNTIF(M15:M74,"&lt;0")</f>
         <v/>
       </c>
       <c r="N4" s="3">
-        <f>COUNTIF(N14:N73,"&lt;0")</f>
+        <f>COUNTIF(N15:N74,"&lt;0")</f>
         <v/>
       </c>
       <c r="O4" s="3">
-        <f>COUNTIF(O14:O73,"&lt;0")</f>
+        <f>COUNTIF(O15:O74,"&lt;0")</f>
         <v/>
       </c>
       <c r="P4" s="3">
-        <f>COUNTIF(P14:P73,"&lt;0")</f>
+        <f>COUNTIF(P15:P74,"&lt;0")</f>
         <v/>
       </c>
       <c r="Q4" s="3">
-        <f>COUNTIF(Q14:Q73,"&lt;0")</f>
+        <f>COUNTIF(Q15:Q74,"&lt;0")</f>
         <v/>
       </c>
       <c r="R4" s="3">
-        <f>COUNTIF(R14:R73,"&lt;0")</f>
+        <f>COUNTIF(R15:R74,"&lt;0")</f>
         <v/>
       </c>
       <c r="S4" s="3">
-        <f>COUNTIF(S14:S73,"&lt;0")</f>
+        <f>COUNTIF(S15:S74,"&lt;0")</f>
         <v/>
       </c>
       <c r="T4" s="3">
-        <f>COUNTIF(T14:T73,"&lt;0")</f>
+        <f>COUNTIF(T15:T74,"&lt;0")</f>
         <v/>
       </c>
       <c r="U4" s="3">
-        <f>COUNTIF(U14:U73,"&lt;0")</f>
+        <f>COUNTIF(U15:U74,"&lt;0")</f>
         <v/>
       </c>
       <c r="V4" s="3">
-        <f>COUNTIF(V14:V73,"&lt;0")</f>
+        <f>COUNTIF(V15:V74,"&lt;0")</f>
         <v/>
       </c>
       <c r="W4" s="3">
-        <f>COUNTIF(W14:W73,"&lt;0")</f>
+        <f>COUNTIF(W15:W74,"&lt;0")</f>
         <v/>
       </c>
       <c r="X4" s="3">
-        <f>COUNTIF(X14:X73,"&lt;0")</f>
+        <f>COUNTIF(X15:X74,"&lt;0")</f>
         <v/>
       </c>
       <c r="Y4" s="3">
-        <f>COUNTIF(Y14:Y73,"&lt;0")</f>
+        <f>COUNTIF(Y15:Y74,"&lt;0")</f>
         <v/>
       </c>
       <c r="Z4" s="3">
-        <f>COUNTIF(Z14:Z73,"&lt;0")</f>
+        <f>COUNTIF(Z15:Z74,"&lt;0")</f>
         <v/>
       </c>
       <c r="AA4" s="3">
-        <f>COUNTIF(AA14:AA73,"&lt;0")</f>
+        <f>COUNTIF(AA15:AA74,"&lt;0")</f>
         <v/>
       </c>
       <c r="AB4" s="3">
-        <f>COUNTIF(AB14:AB73,"&lt;0")</f>
+        <f>COUNTIF(AB15:AB74,"&lt;0")</f>
         <v/>
       </c>
       <c r="AC4" s="3">
-        <f>COUNTIF(AC14:AC73,"&lt;0")</f>
+        <f>COUNTIF(AC15:AC74,"&lt;0")</f>
         <v/>
       </c>
       <c r="AD4" s="3">
-        <f>COUNTIF(AD14:AD73,"&lt;0")</f>
+        <f>COUNTIF(AD15:AD74,"&lt;0")</f>
         <v/>
       </c>
       <c r="AE4" s="3">
-        <f>COUNTIF(AE14:AE73,"&lt;0")</f>
+        <f>COUNTIF(AE15:AE74,"&lt;0")</f>
         <v/>
       </c>
       <c r="AF4" s="3">
-        <f>COUNTIF(AF14:AF73,"&lt;0")</f>
+        <f>COUNTIF(AF15:AF74,"&lt;0")</f>
         <v/>
       </c>
     </row>
@@ -1048,127 +1055,127 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>AVERAGE(B14:B73)</f>
+        <f>AVERAGE(B15:B74)</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>AVERAGE(C14:C73)</f>
+        <f>AVERAGE(C15:C74)</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>AVERAGE(D14:D73)</f>
+        <f>AVERAGE(D15:D74)</f>
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>AVERAGE(E14:E73)</f>
+        <f>AVERAGE(E15:E74)</f>
         <v/>
       </c>
       <c r="F5" s="3">
-        <f>AVERAGE(F14:F73)</f>
+        <f>AVERAGE(F15:F74)</f>
         <v/>
       </c>
       <c r="G5" s="3">
-        <f>AVERAGE(G14:G73)</f>
+        <f>AVERAGE(G15:G74)</f>
         <v/>
       </c>
       <c r="H5" s="3">
-        <f>AVERAGE(H14:H73)</f>
+        <f>AVERAGE(H15:H74)</f>
         <v/>
       </c>
       <c r="I5" s="3">
-        <f>AVERAGE(I14:I73)</f>
+        <f>AVERAGE(I15:I74)</f>
         <v/>
       </c>
       <c r="J5" s="3">
-        <f>AVERAGE(J14:J73)</f>
+        <f>AVERAGE(J15:J74)</f>
         <v/>
       </c>
       <c r="K5" s="3">
-        <f>AVERAGE(K14:K73)</f>
+        <f>AVERAGE(K15:K74)</f>
         <v/>
       </c>
       <c r="L5" s="3">
-        <f>AVERAGE(L14:L73)</f>
+        <f>AVERAGE(L15:L74)</f>
         <v/>
       </c>
       <c r="M5" s="3">
-        <f>AVERAGE(M14:M73)</f>
+        <f>AVERAGE(M15:M74)</f>
         <v/>
       </c>
       <c r="N5" s="3">
-        <f>AVERAGE(N14:N73)</f>
+        <f>AVERAGE(N15:N74)</f>
         <v/>
       </c>
       <c r="O5" s="3">
-        <f>AVERAGE(O14:O73)</f>
+        <f>AVERAGE(O15:O74)</f>
         <v/>
       </c>
       <c r="P5" s="3">
-        <f>AVERAGE(P14:P73)</f>
+        <f>AVERAGE(P15:P74)</f>
         <v/>
       </c>
       <c r="Q5" s="3">
-        <f>AVERAGE(Q14:Q73)</f>
+        <f>AVERAGE(Q15:Q74)</f>
         <v/>
       </c>
       <c r="R5" s="3">
-        <f>AVERAGE(R14:R73)</f>
+        <f>AVERAGE(R15:R74)</f>
         <v/>
       </c>
       <c r="S5" s="3">
-        <f>AVERAGE(S14:S73)</f>
+        <f>AVERAGE(S15:S74)</f>
         <v/>
       </c>
       <c r="T5" s="3">
-        <f>AVERAGE(T14:T73)</f>
+        <f>AVERAGE(T15:T74)</f>
         <v/>
       </c>
       <c r="U5" s="3">
-        <f>AVERAGE(U14:U73)</f>
+        <f>AVERAGE(U15:U74)</f>
         <v/>
       </c>
       <c r="V5" s="3">
-        <f>AVERAGE(V14:V73)</f>
+        <f>AVERAGE(V15:V74)</f>
         <v/>
       </c>
       <c r="W5" s="3">
-        <f>AVERAGE(W14:W73)</f>
+        <f>AVERAGE(W15:W74)</f>
         <v/>
       </c>
       <c r="X5" s="3">
-        <f>AVERAGE(X14:X73)</f>
+        <f>AVERAGE(X15:X74)</f>
         <v/>
       </c>
       <c r="Y5" s="3">
-        <f>AVERAGE(Y14:Y73)</f>
+        <f>AVERAGE(Y15:Y74)</f>
         <v/>
       </c>
       <c r="Z5" s="3">
-        <f>AVERAGE(Z14:Z73)</f>
+        <f>AVERAGE(Z15:Z74)</f>
         <v/>
       </c>
       <c r="AA5" s="3">
-        <f>AVERAGE(AA14:AA73)</f>
+        <f>AVERAGE(AA15:AA74)</f>
         <v/>
       </c>
       <c r="AB5" s="3">
-        <f>AVERAGE(AB14:AB73)</f>
+        <f>AVERAGE(AB15:AB74)</f>
         <v/>
       </c>
       <c r="AC5" s="3">
-        <f>AVERAGE(AC14:AC73)</f>
+        <f>AVERAGE(AC15:AC74)</f>
         <v/>
       </c>
       <c r="AD5" s="3">
-        <f>AVERAGE(AD14:AD73)</f>
+        <f>AVERAGE(AD15:AD74)</f>
         <v/>
       </c>
       <c r="AE5" s="3">
-        <f>AVERAGE(AE14:AE73)</f>
+        <f>AVERAGE(AE15:AE74)</f>
         <v/>
       </c>
       <c r="AF5" s="3">
-        <f>AVERAGE(AF14:AF73)</f>
+        <f>AVERAGE(AF15:AF74)</f>
         <v/>
       </c>
     </row>
@@ -1179,127 +1186,127 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>MAX(B14:B73)</f>
+        <f>MAX(B15:B74)</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>MAX(C14:C73)</f>
+        <f>MAX(C15:C74)</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>MAX(D14:D73)</f>
+        <f>MAX(D15:D74)</f>
         <v/>
       </c>
       <c r="E6" s="3">
-        <f>MAX(E14:E73)</f>
+        <f>MAX(E15:E74)</f>
         <v/>
       </c>
       <c r="F6" s="3">
-        <f>MAX(F14:F73)</f>
+        <f>MAX(F15:F74)</f>
         <v/>
       </c>
       <c r="G6" s="3">
-        <f>MAX(G14:G73)</f>
+        <f>MAX(G15:G74)</f>
         <v/>
       </c>
       <c r="H6" s="3">
-        <f>MAX(H14:H73)</f>
+        <f>MAX(H15:H74)</f>
         <v/>
       </c>
       <c r="I6" s="3">
-        <f>MAX(I14:I73)</f>
+        <f>MAX(I15:I74)</f>
         <v/>
       </c>
       <c r="J6" s="3">
-        <f>MAX(J14:J73)</f>
+        <f>MAX(J15:J74)</f>
         <v/>
       </c>
       <c r="K6" s="3">
-        <f>MAX(K14:K73)</f>
+        <f>MAX(K15:K74)</f>
         <v/>
       </c>
       <c r="L6" s="3">
-        <f>MAX(L14:L73)</f>
+        <f>MAX(L15:L74)</f>
         <v/>
       </c>
       <c r="M6" s="3">
-        <f>MAX(M14:M73)</f>
+        <f>MAX(M15:M74)</f>
         <v/>
       </c>
       <c r="N6" s="3">
-        <f>MAX(N14:N73)</f>
+        <f>MAX(N15:N74)</f>
         <v/>
       </c>
       <c r="O6" s="3">
-        <f>MAX(O14:O73)</f>
+        <f>MAX(O15:O74)</f>
         <v/>
       </c>
       <c r="P6" s="3">
-        <f>MAX(P14:P73)</f>
+        <f>MAX(P15:P74)</f>
         <v/>
       </c>
       <c r="Q6" s="3">
-        <f>MAX(Q14:Q73)</f>
+        <f>MAX(Q15:Q74)</f>
         <v/>
       </c>
       <c r="R6" s="3">
-        <f>MAX(R14:R73)</f>
+        <f>MAX(R15:R74)</f>
         <v/>
       </c>
       <c r="S6" s="3">
-        <f>MAX(S14:S73)</f>
+        <f>MAX(S15:S74)</f>
         <v/>
       </c>
       <c r="T6" s="3">
-        <f>MAX(T14:T73)</f>
+        <f>MAX(T15:T74)</f>
         <v/>
       </c>
       <c r="U6" s="3">
-        <f>MAX(U14:U73)</f>
+        <f>MAX(U15:U74)</f>
         <v/>
       </c>
       <c r="V6" s="3">
-        <f>MAX(V14:V73)</f>
+        <f>MAX(V15:V74)</f>
         <v/>
       </c>
       <c r="W6" s="3">
-        <f>MAX(W14:W73)</f>
+        <f>MAX(W15:W74)</f>
         <v/>
       </c>
       <c r="X6" s="3">
-        <f>MAX(X14:X73)</f>
+        <f>MAX(X15:X74)</f>
         <v/>
       </c>
       <c r="Y6" s="3">
-        <f>MAX(Y14:Y73)</f>
+        <f>MAX(Y15:Y74)</f>
         <v/>
       </c>
       <c r="Z6" s="3">
-        <f>MAX(Z14:Z73)</f>
+        <f>MAX(Z15:Z74)</f>
         <v/>
       </c>
       <c r="AA6" s="3">
-        <f>MAX(AA14:AA73)</f>
+        <f>MAX(AA15:AA74)</f>
         <v/>
       </c>
       <c r="AB6" s="3">
-        <f>MAX(AB14:AB73)</f>
+        <f>MAX(AB15:AB74)</f>
         <v/>
       </c>
       <c r="AC6" s="3">
-        <f>MAX(AC14:AC73)</f>
+        <f>MAX(AC15:AC74)</f>
         <v/>
       </c>
       <c r="AD6" s="3">
-        <f>MAX(AD14:AD73)</f>
+        <f>MAX(AD15:AD74)</f>
         <v/>
       </c>
       <c r="AE6" s="3">
-        <f>MAX(AE14:AE73)</f>
+        <f>MAX(AE15:AE74)</f>
         <v/>
       </c>
       <c r="AF6" s="3">
-        <f>MAX(AF14:AF73)</f>
+        <f>MAX(AF15:AF74)</f>
         <v/>
       </c>
     </row>
@@ -1310,127 +1317,127 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>MIN(B14:B73)</f>
+        <f>MIN(B15:B74)</f>
         <v/>
       </c>
       <c r="C7" s="3">
-        <f>MIN(C14:C73)</f>
+        <f>MIN(C15:C74)</f>
         <v/>
       </c>
       <c r="D7" s="3">
-        <f>MIN(D14:D73)</f>
+        <f>MIN(D15:D74)</f>
         <v/>
       </c>
       <c r="E7" s="3">
-        <f>MIN(E14:E73)</f>
+        <f>MIN(E15:E74)</f>
         <v/>
       </c>
       <c r="F7" s="3">
-        <f>MIN(F14:F73)</f>
+        <f>MIN(F15:F74)</f>
         <v/>
       </c>
       <c r="G7" s="3">
-        <f>MIN(G14:G73)</f>
+        <f>MIN(G15:G74)</f>
         <v/>
       </c>
       <c r="H7" s="3">
-        <f>MIN(H14:H73)</f>
+        <f>MIN(H15:H74)</f>
         <v/>
       </c>
       <c r="I7" s="3">
-        <f>MIN(I14:I73)</f>
+        <f>MIN(I15:I74)</f>
         <v/>
       </c>
       <c r="J7" s="3">
-        <f>MIN(J14:J73)</f>
+        <f>MIN(J15:J74)</f>
         <v/>
       </c>
       <c r="K7" s="3">
-        <f>MIN(K14:K73)</f>
+        <f>MIN(K15:K74)</f>
         <v/>
       </c>
       <c r="L7" s="3">
-        <f>MIN(L14:L73)</f>
+        <f>MIN(L15:L74)</f>
         <v/>
       </c>
       <c r="M7" s="3">
-        <f>MIN(M14:M73)</f>
+        <f>MIN(M15:M74)</f>
         <v/>
       </c>
       <c r="N7" s="3">
-        <f>MIN(N14:N73)</f>
+        <f>MIN(N15:N74)</f>
         <v/>
       </c>
       <c r="O7" s="3">
-        <f>MIN(O14:O73)</f>
+        <f>MIN(O15:O74)</f>
         <v/>
       </c>
       <c r="P7" s="3">
-        <f>MIN(P14:P73)</f>
+        <f>MIN(P15:P74)</f>
         <v/>
       </c>
       <c r="Q7" s="3">
-        <f>MIN(Q14:Q73)</f>
+        <f>MIN(Q15:Q74)</f>
         <v/>
       </c>
       <c r="R7" s="3">
-        <f>MIN(R14:R73)</f>
+        <f>MIN(R15:R74)</f>
         <v/>
       </c>
       <c r="S7" s="3">
-        <f>MIN(S14:S73)</f>
+        <f>MIN(S15:S74)</f>
         <v/>
       </c>
       <c r="T7" s="3">
-        <f>MIN(T14:T73)</f>
+        <f>MIN(T15:T74)</f>
         <v/>
       </c>
       <c r="U7" s="3">
-        <f>MIN(U14:U73)</f>
+        <f>MIN(U15:U74)</f>
         <v/>
       </c>
       <c r="V7" s="3">
-        <f>MIN(V14:V73)</f>
+        <f>MIN(V15:V74)</f>
         <v/>
       </c>
       <c r="W7" s="3">
-        <f>MIN(W14:W73)</f>
+        <f>MIN(W15:W74)</f>
         <v/>
       </c>
       <c r="X7" s="3">
-        <f>MIN(X14:X73)</f>
+        <f>MIN(X15:X74)</f>
         <v/>
       </c>
       <c r="Y7" s="3">
-        <f>MIN(Y14:Y73)</f>
+        <f>MIN(Y15:Y74)</f>
         <v/>
       </c>
       <c r="Z7" s="3">
-        <f>MIN(Z14:Z73)</f>
+        <f>MIN(Z15:Z74)</f>
         <v/>
       </c>
       <c r="AA7" s="3">
-        <f>MIN(AA14:AA73)</f>
+        <f>MIN(AA15:AA74)</f>
         <v/>
       </c>
       <c r="AB7" s="3">
-        <f>MIN(AB14:AB73)</f>
+        <f>MIN(AB15:AB74)</f>
         <v/>
       </c>
       <c r="AC7" s="3">
-        <f>MIN(AC14:AC73)</f>
+        <f>MIN(AC15:AC74)</f>
         <v/>
       </c>
       <c r="AD7" s="3">
-        <f>MIN(AD14:AD73)</f>
+        <f>MIN(AD15:AD74)</f>
         <v/>
       </c>
       <c r="AE7" s="3">
-        <f>MIN(AE14:AE73)</f>
+        <f>MIN(AE15:AE74)</f>
         <v/>
       </c>
       <c r="AF7" s="3">
-        <f>MIN(AF14:AF73)</f>
+        <f>MIN(AF15:AF74)</f>
         <v/>
       </c>
     </row>
@@ -1441,127 +1448,127 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNT(B14:B73)</f>
+        <f>COUNT(B15:B74)</f>
         <v/>
       </c>
       <c r="C8" s="3">
-        <f>COUNT(C14:C73)</f>
+        <f>COUNT(C15:C74)</f>
         <v/>
       </c>
       <c r="D8" s="3">
-        <f>COUNT(D14:D73)</f>
+        <f>COUNT(D15:D74)</f>
         <v/>
       </c>
       <c r="E8" s="3">
-        <f>COUNT(E14:E73)</f>
+        <f>COUNT(E15:E74)</f>
         <v/>
       </c>
       <c r="F8" s="3">
-        <f>COUNT(F14:F73)</f>
+        <f>COUNT(F15:F74)</f>
         <v/>
       </c>
       <c r="G8" s="3">
-        <f>COUNT(G14:G73)</f>
+        <f>COUNT(G15:G74)</f>
         <v/>
       </c>
       <c r="H8" s="3">
-        <f>COUNT(H14:H73)</f>
+        <f>COUNT(H15:H74)</f>
         <v/>
       </c>
       <c r="I8" s="3">
-        <f>COUNT(I14:I73)</f>
+        <f>COUNT(I15:I74)</f>
         <v/>
       </c>
       <c r="J8" s="3">
-        <f>COUNT(J14:J73)</f>
+        <f>COUNT(J15:J74)</f>
         <v/>
       </c>
       <c r="K8" s="3">
-        <f>COUNT(K14:K73)</f>
+        <f>COUNT(K15:K74)</f>
         <v/>
       </c>
       <c r="L8" s="3">
-        <f>COUNT(L14:L73)</f>
+        <f>COUNT(L15:L74)</f>
         <v/>
       </c>
       <c r="M8" s="3">
-        <f>COUNT(M14:M73)</f>
+        <f>COUNT(M15:M74)</f>
         <v/>
       </c>
       <c r="N8" s="3">
-        <f>COUNT(N14:N73)</f>
+        <f>COUNT(N15:N74)</f>
         <v/>
       </c>
       <c r="O8" s="3">
-        <f>COUNT(O14:O73)</f>
+        <f>COUNT(O15:O74)</f>
         <v/>
       </c>
       <c r="P8" s="3">
-        <f>COUNT(P14:P73)</f>
+        <f>COUNT(P15:P74)</f>
         <v/>
       </c>
       <c r="Q8" s="3">
-        <f>COUNT(Q14:Q73)</f>
+        <f>COUNT(Q15:Q74)</f>
         <v/>
       </c>
       <c r="R8" s="3">
-        <f>COUNT(R14:R73)</f>
+        <f>COUNT(R15:R74)</f>
         <v/>
       </c>
       <c r="S8" s="3">
-        <f>COUNT(S14:S73)</f>
+        <f>COUNT(S15:S74)</f>
         <v/>
       </c>
       <c r="T8" s="3">
-        <f>COUNT(T14:T73)</f>
+        <f>COUNT(T15:T74)</f>
         <v/>
       </c>
       <c r="U8" s="3">
-        <f>COUNT(U14:U73)</f>
+        <f>COUNT(U15:U74)</f>
         <v/>
       </c>
       <c r="V8" s="3">
-        <f>COUNT(V14:V73)</f>
+        <f>COUNT(V15:V74)</f>
         <v/>
       </c>
       <c r="W8" s="3">
-        <f>COUNT(W14:W73)</f>
+        <f>COUNT(W15:W74)</f>
         <v/>
       </c>
       <c r="X8" s="3">
-        <f>COUNT(X14:X73)</f>
+        <f>COUNT(X15:X74)</f>
         <v/>
       </c>
       <c r="Y8" s="3">
-        <f>COUNT(Y14:Y73)</f>
+        <f>COUNT(Y15:Y74)</f>
         <v/>
       </c>
       <c r="Z8" s="3">
-        <f>COUNT(Z14:Z73)</f>
+        <f>COUNT(Z15:Z74)</f>
         <v/>
       </c>
       <c r="AA8" s="3">
-        <f>COUNT(AA14:AA73)</f>
+        <f>COUNT(AA15:AA74)</f>
         <v/>
       </c>
       <c r="AB8" s="3">
-        <f>COUNT(AB14:AB73)</f>
+        <f>COUNT(AB15:AB74)</f>
         <v/>
       </c>
       <c r="AC8" s="3">
-        <f>COUNT(AC14:AC73)</f>
+        <f>COUNT(AC15:AC74)</f>
         <v/>
       </c>
       <c r="AD8" s="3">
-        <f>COUNT(AD14:AD73)</f>
+        <f>COUNT(AD15:AD74)</f>
         <v/>
       </c>
       <c r="AE8" s="3">
-        <f>COUNT(AE14:AE73)</f>
+        <f>COUNT(AE15:AE74)</f>
         <v/>
       </c>
       <c r="AF8" s="3">
-        <f>COUNT(AF14:AF73)</f>
+        <f>COUNT(AF15:AF74)</f>
         <v/>
       </c>
     </row>
@@ -1572,127 +1579,127 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>STDEV(B14:B73)</f>
+        <f>STDEV(B15:B74)</f>
         <v/>
       </c>
       <c r="C9" s="3">
-        <f>STDEV(C14:C73)</f>
+        <f>STDEV(C15:C74)</f>
         <v/>
       </c>
       <c r="D9" s="3">
-        <f>STDEV(D14:D73)</f>
+        <f>STDEV(D15:D74)</f>
         <v/>
       </c>
       <c r="E9" s="3">
-        <f>STDEV(E14:E73)</f>
+        <f>STDEV(E15:E74)</f>
         <v/>
       </c>
       <c r="F9" s="3">
-        <f>STDEV(F14:F73)</f>
+        <f>STDEV(F15:F74)</f>
         <v/>
       </c>
       <c r="G9" s="3">
-        <f>STDEV(G14:G73)</f>
+        <f>STDEV(G15:G74)</f>
         <v/>
       </c>
       <c r="H9" s="3">
-        <f>STDEV(H14:H73)</f>
+        <f>STDEV(H15:H74)</f>
         <v/>
       </c>
       <c r="I9" s="3">
-        <f>STDEV(I14:I73)</f>
+        <f>STDEV(I15:I74)</f>
         <v/>
       </c>
       <c r="J9" s="3">
-        <f>STDEV(J14:J73)</f>
+        <f>STDEV(J15:J74)</f>
         <v/>
       </c>
       <c r="K9" s="3">
-        <f>STDEV(K14:K73)</f>
+        <f>STDEV(K15:K74)</f>
         <v/>
       </c>
       <c r="L9" s="3">
-        <f>STDEV(L14:L73)</f>
+        <f>STDEV(L15:L74)</f>
         <v/>
       </c>
       <c r="M9" s="3">
-        <f>STDEV(M14:M73)</f>
+        <f>STDEV(M15:M74)</f>
         <v/>
       </c>
       <c r="N9" s="3">
-        <f>STDEV(N14:N73)</f>
+        <f>STDEV(N15:N74)</f>
         <v/>
       </c>
       <c r="O9" s="3">
-        <f>STDEV(O14:O73)</f>
+        <f>STDEV(O15:O74)</f>
         <v/>
       </c>
       <c r="P9" s="3">
-        <f>STDEV(P14:P73)</f>
+        <f>STDEV(P15:P74)</f>
         <v/>
       </c>
       <c r="Q9" s="3">
-        <f>STDEV(Q14:Q73)</f>
+        <f>STDEV(Q15:Q74)</f>
         <v/>
       </c>
       <c r="R9" s="3">
-        <f>STDEV(R14:R73)</f>
+        <f>STDEV(R15:R74)</f>
         <v/>
       </c>
       <c r="S9" s="3">
-        <f>STDEV(S14:S73)</f>
+        <f>STDEV(S15:S74)</f>
         <v/>
       </c>
       <c r="T9" s="3">
-        <f>STDEV(T14:T73)</f>
+        <f>STDEV(T15:T74)</f>
         <v/>
       </c>
       <c r="U9" s="3">
-        <f>STDEV(U14:U73)</f>
+        <f>STDEV(U15:U74)</f>
         <v/>
       </c>
       <c r="V9" s="3">
-        <f>STDEV(V14:V73)</f>
+        <f>STDEV(V15:V74)</f>
         <v/>
       </c>
       <c r="W9" s="3">
-        <f>STDEV(W14:W73)</f>
+        <f>STDEV(W15:W74)</f>
         <v/>
       </c>
       <c r="X9" s="3">
-        <f>STDEV(X14:X73)</f>
+        <f>STDEV(X15:X74)</f>
         <v/>
       </c>
       <c r="Y9" s="3">
-        <f>STDEV(Y14:Y73)</f>
+        <f>STDEV(Y15:Y74)</f>
         <v/>
       </c>
       <c r="Z9" s="3">
-        <f>STDEV(Z14:Z73)</f>
+        <f>STDEV(Z15:Z74)</f>
         <v/>
       </c>
       <c r="AA9" s="3">
-        <f>STDEV(AA14:AA73)</f>
+        <f>STDEV(AA15:AA74)</f>
         <v/>
       </c>
       <c r="AB9" s="3">
-        <f>STDEV(AB14:AB73)</f>
+        <f>STDEV(AB15:AB74)</f>
         <v/>
       </c>
       <c r="AC9" s="3">
-        <f>STDEV(AC14:AC73)</f>
+        <f>STDEV(AC15:AC74)</f>
         <v/>
       </c>
       <c r="AD9" s="3">
-        <f>STDEV(AD14:AD73)</f>
+        <f>STDEV(AD15:AD74)</f>
         <v/>
       </c>
       <c r="AE9" s="3">
-        <f>STDEV(AE14:AE73)</f>
+        <f>STDEV(AE15:AE74)</f>
         <v/>
       </c>
       <c r="AF9" s="3">
-        <f>STDEV(AF14:AF73)</f>
+        <f>STDEV(AF15:AF74)</f>
         <v/>
       </c>
     </row>
@@ -1703,153 +1710,143 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>SUM(B14:B73)</f>
+        <f>SUM(B15:B74)</f>
         <v/>
       </c>
       <c r="C10" s="3">
-        <f>SUM(C14:C73)</f>
+        <f>SUM(C15:C74)</f>
         <v/>
       </c>
       <c r="D10" s="3">
-        <f>SUM(D14:D73)</f>
+        <f>SUM(D15:D74)</f>
         <v/>
       </c>
       <c r="E10" s="3">
-        <f>SUM(E14:E73)</f>
+        <f>SUM(E15:E74)</f>
         <v/>
       </c>
       <c r="F10" s="3">
-        <f>SUM(F14:F73)</f>
+        <f>SUM(F15:F74)</f>
         <v/>
       </c>
       <c r="G10" s="3">
-        <f>SUM(G14:G73)</f>
+        <f>SUM(G15:G74)</f>
         <v/>
       </c>
       <c r="H10" s="3">
-        <f>SUM(H14:H73)</f>
+        <f>SUM(H15:H74)</f>
         <v/>
       </c>
       <c r="I10" s="3">
-        <f>SUM(I14:I73)</f>
+        <f>SUM(I15:I74)</f>
         <v/>
       </c>
       <c r="J10" s="3">
-        <f>SUM(J14:J73)</f>
+        <f>SUM(J15:J74)</f>
         <v/>
       </c>
       <c r="K10" s="3">
-        <f>SUM(K14:K73)</f>
+        <f>SUM(K15:K74)</f>
         <v/>
       </c>
       <c r="L10" s="3">
-        <f>SUM(L14:L73)</f>
+        <f>SUM(L15:L74)</f>
         <v/>
       </c>
       <c r="M10" s="3">
-        <f>SUM(M14:M73)</f>
+        <f>SUM(M15:M74)</f>
         <v/>
       </c>
       <c r="N10" s="3">
-        <f>SUM(N14:N73)</f>
+        <f>SUM(N15:N74)</f>
         <v/>
       </c>
       <c r="O10" s="3">
-        <f>SUM(O14:O73)</f>
+        <f>SUM(O15:O74)</f>
         <v/>
       </c>
       <c r="P10" s="3">
-        <f>SUM(P14:P73)</f>
+        <f>SUM(P15:P74)</f>
         <v/>
       </c>
       <c r="Q10" s="3">
-        <f>SUM(Q14:Q73)</f>
+        <f>SUM(Q15:Q74)</f>
         <v/>
       </c>
       <c r="R10" s="3">
-        <f>SUM(R14:R73)</f>
+        <f>SUM(R15:R74)</f>
         <v/>
       </c>
       <c r="S10" s="3">
-        <f>SUM(S14:S73)</f>
+        <f>SUM(S15:S74)</f>
         <v/>
       </c>
       <c r="T10" s="3">
-        <f>SUM(T14:T73)</f>
+        <f>SUM(T15:T74)</f>
         <v/>
       </c>
       <c r="U10" s="3">
-        <f>SUM(U14:U73)</f>
+        <f>SUM(U15:U74)</f>
         <v/>
       </c>
       <c r="V10" s="3">
-        <f>SUM(V14:V73)</f>
+        <f>SUM(V15:V74)</f>
         <v/>
       </c>
       <c r="W10" s="3">
-        <f>SUM(W14:W73)</f>
+        <f>SUM(W15:W74)</f>
         <v/>
       </c>
       <c r="X10" s="3">
-        <f>SUM(X14:X73)</f>
+        <f>SUM(X15:X74)</f>
         <v/>
       </c>
       <c r="Y10" s="3">
-        <f>SUM(Y14:Y73)</f>
+        <f>SUM(Y15:Y74)</f>
         <v/>
       </c>
       <c r="Z10" s="3">
-        <f>SUM(Z14:Z73)</f>
+        <f>SUM(Z15:Z74)</f>
         <v/>
       </c>
       <c r="AA10" s="3">
-        <f>SUM(AA14:AA73)</f>
+        <f>SUM(AA15:AA74)</f>
         <v/>
       </c>
       <c r="AB10" s="3">
-        <f>SUM(AB14:AB73)</f>
+        <f>SUM(AB15:AB74)</f>
         <v/>
       </c>
       <c r="AC10" s="3">
-        <f>SUM(AC14:AC73)</f>
+        <f>SUM(AC15:AC74)</f>
         <v/>
       </c>
       <c r="AD10" s="3">
-        <f>SUM(AD14:AD73)</f>
+        <f>SUM(AD15:AD74)</f>
         <v/>
       </c>
       <c r="AE10" s="3">
-        <f>SUM(AE14:AE73)</f>
+        <f>SUM(AE15:AE74)</f>
         <v/>
       </c>
       <c r="AF10" s="3">
-        <f>SUM(AF14:AF73)</f>
+        <f>SUM(AF15:AF74)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="Y11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y11" s="3" t="n"/>
+      <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AC11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE11" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC11" s="3" t="n"/>
+      <c r="AD11" s="3" t="n"/>
+      <c r="AE11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="Y12" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>0</v>
@@ -1861,389 +1858,290 @@
         <v>0</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AE12" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="Y13" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Ultra NASDAQ-100 ProFunds Investor Class（UOPIX） Adj Close</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Ultra NASDAQ-100 ProFunds Investor Class（UOPIX）回报</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>UltraBull ProFund Investor Shares（ULPIX） Adj Close</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>UltraBull ProFund Investor Shares（ULPIX）回报</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>EEM Adj Close</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>EEM回报</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>GLD Adj Close</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>GLD回报</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>HYG Adj Close</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>HYG回报</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>TIP Adj Close</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>TIP回报</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>XLF Adj Close</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>XLF回报</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>FXY Adj Close</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>FXY回报</t>
         </is>
       </c>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="R14" s="4" t="inlineStr">
         <is>
           <t>GDX Adj Close</t>
         </is>
       </c>
-      <c r="S13" s="4" t="inlineStr">
+      <c r="S14" s="4" t="inlineStr">
         <is>
           <t>GDX回报</t>
         </is>
       </c>
-      <c r="T13" s="4" t="inlineStr">
+      <c r="T14" s="4" t="inlineStr">
         <is>
           <t>XLC Adj Close</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr">
+      <c r="U14" s="4" t="inlineStr">
         <is>
           <t>XLC回报</t>
         </is>
       </c>
-      <c r="V13" s="4" t="inlineStr">
+      <c r="V14" s="4" t="inlineStr">
         <is>
           <t>VIX_Close</t>
         </is>
       </c>
-      <c r="W13" s="4" t="inlineStr">
+      <c r="W14" s="4" t="inlineStr">
         <is>
           <t>VIX回报</t>
         </is>
       </c>
-      <c r="X13" s="4" t="inlineStr">
+      <c r="X14" s="4" t="inlineStr">
         <is>
           <t>VIX_Chg%</t>
         </is>
       </c>
-      <c r="Y13" s="4" t="inlineStr">
+      <c r="Y14" s="4" t="inlineStr">
         <is>
           <t>VIX&gt;0 且 该基金当日回报&lt;=-2%，买基金第二天</t>
         </is>
       </c>
-      <c r="Z13" s="4" t="inlineStr">
+      <c r="Z14" s="4" t="inlineStr">
         <is>
           <t>HYG&lt;0 且 TIP&gt;0，买基金第二天</t>
         </is>
       </c>
-      <c r="AA13" s="4" t="inlineStr">
+      <c r="AA14" s="4" t="inlineStr">
         <is>
           <t>EEM&gt;0 且 GLD&lt;0 且 HYG&gt;0，买基金第二天</t>
         </is>
       </c>
-      <c r="AB13" s="4" t="inlineStr">
+      <c r="AB14" s="4" t="inlineStr">
         <is>
           <t>Ultra NASDAQ-100 ProFunds Investor Class（UOPIX）合并效果</t>
         </is>
       </c>
-      <c r="AC13" s="4" t="inlineStr">
+      <c r="AC14" s="4" t="inlineStr">
         <is>
           <t>GDX&gt;0 且 XLC&lt;0，买基金第二天</t>
         </is>
       </c>
-      <c r="AD13" s="4" t="inlineStr">
+      <c r="AD14" s="4" t="inlineStr">
         <is>
           <t>XLF&lt;=-1% 且 该基金当日回报&lt;0，买基金第二天</t>
         </is>
       </c>
-      <c r="AE13" s="4" t="inlineStr">
+      <c r="AE14" s="4" t="inlineStr">
         <is>
           <t>FXY&gt;0 且 GDX&gt;0，买基金第二天</t>
         </is>
       </c>
-      <c r="AF13" s="4" t="inlineStr">
+      <c r="AF14" s="4" t="inlineStr">
         <is>
           <t>UltraBull ProFund Investor Shares（ULPIX）合并效果</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>2026/08/04</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>164.02</v>
-      </c>
-      <c r="C14" s="5">
-        <f>IF(COUNT(B14:B15)=2,(B14/B15-1)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>194.03</v>
-      </c>
-      <c r="E14" s="5">
-        <f>IF(COUNT(D14:D15)=2,(D14/D15-1)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="G14" s="5">
-        <f>IF(COUNT(F14:F15)=2,(F14/F15-1)*100,"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>374.16</v>
-      </c>
-      <c r="I14" s="5">
-        <f>IF(COUNT(H14:H15)=2,(H14/H15-1)*100,"")</f>
-        <v/>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>79.55</v>
-      </c>
-      <c r="K14" s="5">
-        <f>IF(COUNT(J14:J15)=2,(J14/J15-1)*100,"")</f>
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>107.05</v>
-      </c>
-      <c r="M14" s="5">
-        <f>IF(COUNT(L14:L15)=2,(L14/L15-1)*100,"")</f>
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>57.88</v>
-      </c>
-      <c r="O14" s="5">
-        <f>IF(COUNT(N14:N15)=2,(N14/N15-1)*100,"")</f>
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>58.15</v>
-      </c>
-      <c r="Q14" s="5">
-        <f>IF(COUNT(P14:P15)=2,(P14/P15-1)*100,"")</f>
-        <v/>
-      </c>
-      <c r="R14" s="5" t="n">
-        <v>77.92</v>
-      </c>
-      <c r="S14" s="5">
-        <f>IF(COUNT(R14:R15)=2,(R14/R15-1)*100,"")</f>
-        <v/>
-      </c>
-      <c r="T14" s="5" t="n">
-        <v>112.04</v>
-      </c>
-      <c r="U14" s="5">
-        <f>IF(COUNT(T14:T15)=2,(T14/T15-1)*100,"")</f>
-        <v/>
-      </c>
-      <c r="V14" s="5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="W14" s="5">
-        <f>IF(COUNT(V14:V15)=2,(V14/V15-1)*100,"")</f>
-        <v/>
-      </c>
-      <c r="X14" s="5" t="n">
-        <v>4.0353</v>
-      </c>
-      <c r="Y14" s="5" t="inlineStr"/>
-      <c r="Z14" s="5" t="inlineStr"/>
-      <c r="AA14" s="5" t="inlineStr"/>
-      <c r="AB14" s="5">
-        <f>IF(Y14&lt;&gt;"",Y14,IF(Z14&lt;&gt;"",Z14,AA14))</f>
-        <v/>
-      </c>
-      <c r="AC14" s="5" t="inlineStr"/>
-      <c r="AD14" s="5" t="inlineStr"/>
-      <c r="AE14" s="5" t="inlineStr"/>
-      <c r="AF14" s="5">
-        <f>IF(AC14&lt;&gt;"",AC14,IF(AD14&lt;&gt;"",AD14,AE14))</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>153.8</v>
+        <v>164.02</v>
       </c>
       <c r="C15" s="5">
         <f>IF(COUNT(B15:B16)=2,(B15/B16-1)*100,"")</f>
         <v/>
       </c>
       <c r="D15" s="5" t="n">
-        <v>187.34</v>
+        <v>194.03</v>
       </c>
       <c r="E15" s="5">
         <f>IF(COUNT(D15:D16)=2,(D15/D16-1)*100,"")</f>
         <v/>
       </c>
       <c r="F15" s="5" t="n">
-        <v>64.31999999999999</v>
+        <v>66</v>
       </c>
       <c r="G15" s="5">
         <f>IF(COUNT(F15:F16)=2,(F15/F16-1)*100,"")</f>
         <v/>
       </c>
       <c r="H15" s="5" t="n">
-        <v>371.71</v>
+        <v>374.16</v>
       </c>
       <c r="I15" s="5">
         <f>IF(COUNT(H15:H16)=2,(H15/H16-1)*100,"")</f>
         <v/>
       </c>
       <c r="J15" s="5" t="n">
-        <v>79.31</v>
+        <v>79.55</v>
       </c>
       <c r="K15" s="5">
         <f>IF(COUNT(J15:J16)=2,(J15/J16-1)*100,"")</f>
         <v/>
       </c>
       <c r="L15" s="5" t="n">
-        <v>106.86</v>
+        <v>107.05</v>
       </c>
       <c r="M15" s="5">
         <f>IF(COUNT(L15:L16)=2,(L15/L16-1)*100,"")</f>
         <v/>
       </c>
       <c r="N15" s="5" t="n">
-        <v>57.38</v>
+        <v>57.88</v>
       </c>
       <c r="O15" s="5">
         <f>IF(COUNT(N15:N16)=2,(N15/N16-1)*100,"")</f>
         <v/>
       </c>
       <c r="P15" s="5" t="n">
-        <v>58.5</v>
+        <v>58.15</v>
       </c>
       <c r="Q15" s="5">
         <f>IF(COUNT(P15:P16)=2,(P15/P16-1)*100,"")</f>
         <v/>
       </c>
       <c r="R15" s="5" t="n">
-        <v>76.05</v>
+        <v>77.92</v>
       </c>
       <c r="S15" s="5">
         <f>IF(COUNT(R15:R16)=2,(R15/R16-1)*100,"")</f>
         <v/>
       </c>
       <c r="T15" s="5" t="n">
-        <v>111.34</v>
+        <v>112.04</v>
       </c>
       <c r="U15" s="5">
         <f>IF(COUNT(T15:T16)=2,(T15/T16-1)*100,"")</f>
         <v/>
       </c>
       <c r="V15" s="5" t="n">
-        <v>15.86</v>
+        <v>16.5</v>
       </c>
       <c r="W15" s="5">
         <f>IF(COUNT(V15:V16)=2,(V15/V16-1)*100,"")</f>
         <v/>
       </c>
       <c r="X15" s="5" t="n">
-        <v>-0.8129999999999999</v>
-      </c>
-      <c r="Y15" s="5">
-        <f>IF(AND(X15&gt;$Y$11,C15&lt;=$Y$12),C14,"")</f>
-        <v/>
-      </c>
-      <c r="Z15" s="5">
-        <f>IF(AND(K15&lt;$Z$11,M15&gt;$Z$12),C14,"")</f>
-        <v/>
-      </c>
-      <c r="AA15" s="5">
-        <f>IF(AND(G15&gt;$AA$11,I15&lt;$AA$12,K15&gt;$AA$12),C14,"")</f>
-        <v/>
-      </c>
+        <v>4.0353</v>
+      </c>
+      <c r="Y15" s="5" t="inlineStr"/>
+      <c r="Z15" s="5" t="inlineStr"/>
+      <c r="AA15" s="5" t="inlineStr"/>
       <c r="AB15" s="5">
         <f>IF(Y15&lt;&gt;"",Y15,IF(Z15&lt;&gt;"",Z15,AA15))</f>
         <v/>
       </c>
-      <c r="AC15" s="5">
-        <f>IF(AND(S15&gt;$AC$11,U15&lt;$AC$12),E14,"")</f>
-        <v/>
-      </c>
-      <c r="AD15" s="5">
-        <f>IF(AND(O15&lt;=$AD$11,E15&lt;$AD$12),E14,"")</f>
-        <v/>
-      </c>
-      <c r="AE15" s="5">
-        <f>IF(AND(Q15&gt;$AE$11,S15&gt;$AE$12),E14,"")</f>
-        <v/>
-      </c>
+      <c r="AC15" s="5" t="inlineStr"/>
+      <c r="AD15" s="5" t="inlineStr"/>
+      <c r="AE15" s="5" t="inlineStr"/>
       <c r="AF15" s="5">
         <f>IF(AC15&lt;&gt;"",AC15,IF(AD15&lt;&gt;"",AD15,AE15))</f>
         <v/>
@@ -2252,99 +2150,99 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>2026/07/31</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>148.6</v>
+        <v>153.8</v>
       </c>
       <c r="C16" s="5">
         <f>IF(COUNT(B16:B17)=2,(B16/B17-1)*100,"")</f>
         <v/>
       </c>
       <c r="D16" s="5" t="n">
-        <v>182.05</v>
+        <v>187.34</v>
       </c>
       <c r="E16" s="5">
         <f>IF(COUNT(D16:D17)=2,(D16/D17-1)*100,"")</f>
         <v/>
       </c>
       <c r="F16" s="5" t="n">
-        <v>64.09</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="G16" s="5">
         <f>IF(COUNT(F16:F17)=2,(F16/F17-1)*100,"")</f>
         <v/>
       </c>
       <c r="H16" s="5" t="n">
-        <v>371.54</v>
+        <v>371.71</v>
       </c>
       <c r="I16" s="5">
         <f>IF(COUNT(H16:H17)=2,(H16/H17-1)*100,"")</f>
         <v/>
       </c>
       <c r="J16" s="5" t="n">
-        <v>79.096</v>
+        <v>79.31</v>
       </c>
       <c r="K16" s="5">
         <f>IF(COUNT(J16:J17)=2,(J16/J17-1)*100,"")</f>
         <v/>
       </c>
       <c r="L16" s="5" t="n">
-        <v>106.846</v>
+        <v>106.86</v>
       </c>
       <c r="M16" s="5">
         <f>IF(COUNT(L16:L17)=2,(L16/L17-1)*100,"")</f>
         <v/>
       </c>
       <c r="N16" s="5" t="n">
-        <v>56.94</v>
+        <v>57.38</v>
       </c>
       <c r="O16" s="5">
         <f>IF(COUNT(N16:N17)=2,(N16/N17-1)*100,"")</f>
         <v/>
       </c>
       <c r="P16" s="5" t="n">
-        <v>57.66</v>
+        <v>58.5</v>
       </c>
       <c r="Q16" s="5">
         <f>IF(COUNT(P16:P17)=2,(P16/P17-1)*100,"")</f>
         <v/>
       </c>
       <c r="R16" s="5" t="n">
-        <v>74.09999999999999</v>
+        <v>76.05</v>
       </c>
       <c r="S16" s="5">
         <f>IF(COUNT(R16:R17)=2,(R16/R17-1)*100,"")</f>
         <v/>
       </c>
       <c r="T16" s="5" t="n">
-        <v>108.24</v>
+        <v>111.34</v>
       </c>
       <c r="U16" s="5">
         <f>IF(COUNT(T16:T17)=2,(T16/T17-1)*100,"")</f>
         <v/>
       </c>
       <c r="V16" s="5" t="n">
-        <v>15.99</v>
+        <v>15.86</v>
       </c>
       <c r="W16" s="5">
         <f>IF(COUNT(V16:V17)=2,(V16/V17-1)*100,"")</f>
         <v/>
       </c>
       <c r="X16" s="5" t="n">
-        <v>-6.4365</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="Y16" s="5">
-        <f>IF(AND(X16&gt;$Y$11,C16&lt;=$Y$12),C15,"")</f>
+        <f>IF(AND(X16&gt;$Y$12,C16&lt;=$Y$13),C15,"")</f>
         <v/>
       </c>
       <c r="Z16" s="5">
-        <f>IF(AND(K16&lt;$Z$11,M16&gt;$Z$12),C15,"")</f>
+        <f>IF(AND(K16&lt;$Z$12,M16&gt;$Z$13),C15,"")</f>
         <v/>
       </c>
       <c r="AA16" s="5">
-        <f>IF(AND(G16&gt;$AA$11,I16&lt;$AA$12,K16&gt;$AA$12),C15,"")</f>
+        <f>IF(AND(G16&gt;$AA$12,I16&lt;$AA$13,K16&gt;$AA$11),C15,"")</f>
         <v/>
       </c>
       <c r="AB16" s="5">
@@ -2352,15 +2250,15 @@
         <v/>
       </c>
       <c r="AC16" s="5">
-        <f>IF(AND(S16&gt;$AC$11,U16&lt;$AC$12),E15,"")</f>
+        <f>IF(AND(S16&gt;$AC$12,U16&lt;$AC$13),E15,"")</f>
         <v/>
       </c>
       <c r="AD16" s="5">
-        <f>IF(AND(O16&lt;=$AD$11,E16&lt;$AD$12),E15,"")</f>
+        <f>IF(AND(O16&lt;=$AD$12,E16&lt;$AD$13),E15,"")</f>
         <v/>
       </c>
       <c r="AE16" s="5">
-        <f>IF(AND(Q16&gt;$AE$11,S16&gt;$AE$12),E15,"")</f>
+        <f>IF(AND(Q16&gt;$AE$12,S16&gt;$AE$13),E15,"")</f>
         <v/>
       </c>
       <c r="AF16" s="5">
@@ -2371,99 +2269,99 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>146.84</v>
+        <v>148.6</v>
       </c>
       <c r="C17" s="5">
         <f>IF(COUNT(B17:B18)=2,(B17/B18-1)*100,"")</f>
         <v/>
       </c>
       <c r="D17" s="5" t="n">
-        <v>179.55</v>
+        <v>182.05</v>
       </c>
       <c r="E17" s="5">
         <f>IF(COUNT(D17:D18)=2,(D17/D18-1)*100,"")</f>
         <v/>
       </c>
       <c r="F17" s="5" t="n">
-        <v>63.59</v>
+        <v>64.09</v>
       </c>
       <c r="G17" s="5">
         <f>IF(COUNT(F17:F18)=2,(F17/F18-1)*100,"")</f>
         <v/>
       </c>
       <c r="H17" s="5" t="n">
-        <v>377.16</v>
+        <v>371.54</v>
       </c>
       <c r="I17" s="5">
         <f>IF(COUNT(H17:H18)=2,(H17/H18-1)*100,"")</f>
         <v/>
       </c>
       <c r="J17" s="5" t="n">
-        <v>79.086</v>
+        <v>79.096</v>
       </c>
       <c r="K17" s="5">
         <f>IF(COUNT(J17:J18)=2,(J17/J18-1)*100,"")</f>
         <v/>
       </c>
       <c r="L17" s="5" t="n">
-        <v>106.9552</v>
+        <v>106.846</v>
       </c>
       <c r="M17" s="5">
         <f>IF(COUNT(L17:L18)=2,(L17/L18-1)*100,"")</f>
         <v/>
       </c>
       <c r="N17" s="5" t="n">
-        <v>57</v>
+        <v>56.94</v>
       </c>
       <c r="O17" s="5">
         <f>IF(COUNT(N17:N18)=2,(N17/N18-1)*100,"")</f>
         <v/>
       </c>
       <c r="P17" s="5" t="n">
-        <v>57.58</v>
+        <v>57.66</v>
       </c>
       <c r="Q17" s="5">
         <f>IF(COUNT(P17:P18)=2,(P17/P18-1)*100,"")</f>
         <v/>
       </c>
       <c r="R17" s="5" t="n">
-        <v>76.78</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="S17" s="5">
         <f>IF(COUNT(R17:R18)=2,(R17/R18-1)*100,"")</f>
         <v/>
       </c>
       <c r="T17" s="5" t="n">
-        <v>106.58</v>
+        <v>108.24</v>
       </c>
       <c r="U17" s="5">
         <f>IF(COUNT(T17:T18)=2,(T17/T18-1)*100,"")</f>
         <v/>
       </c>
       <c r="V17" s="5" t="n">
-        <v>17.09</v>
+        <v>15.99</v>
       </c>
       <c r="W17" s="5">
         <f>IF(COUNT(V17:V18)=2,(V17/V18-1)*100,"")</f>
         <v/>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-17.2798</v>
+        <v>-6.4365</v>
       </c>
       <c r="Y17" s="5">
-        <f>IF(AND(X17&gt;$Y$11,C17&lt;=$Y$12),C16,"")</f>
+        <f>IF(AND(X17&gt;$Y$12,C17&lt;=$Y$13),C16,"")</f>
         <v/>
       </c>
       <c r="Z17" s="5">
-        <f>IF(AND(K17&lt;$Z$11,M17&gt;$Z$12),C16,"")</f>
+        <f>IF(AND(K17&lt;$Z$12,M17&gt;$Z$13),C16,"")</f>
         <v/>
       </c>
       <c r="AA17" s="5">
-        <f>IF(AND(G17&gt;$AA$11,I17&lt;$AA$12,K17&gt;$AA$12),C16,"")</f>
+        <f>IF(AND(G17&gt;$AA$12,I17&lt;$AA$13,K17&gt;$AA$11),C16,"")</f>
         <v/>
       </c>
       <c r="AB17" s="5">
@@ -2471,15 +2369,15 @@
         <v/>
       </c>
       <c r="AC17" s="5">
-        <f>IF(AND(S17&gt;$AC$11,U17&lt;$AC$12),E16,"")</f>
+        <f>IF(AND(S17&gt;$AC$12,U17&lt;$AC$13),E16,"")</f>
         <v/>
       </c>
       <c r="AD17" s="5">
-        <f>IF(AND(O17&lt;=$AD$11,E17&lt;$AD$12),E16,"")</f>
+        <f>IF(AND(O17&lt;=$AD$12,E17&lt;$AD$13),E16,"")</f>
         <v/>
       </c>
       <c r="AE17" s="5">
-        <f>IF(AND(Q17&gt;$AE$11,S17&gt;$AE$12),E16,"")</f>
+        <f>IF(AND(Q17&gt;$AE$12,S17&gt;$AE$13),E16,"")</f>
         <v/>
       </c>
       <c r="AF17" s="5">
@@ -2490,99 +2388,99 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/07/30</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>137.65</v>
+        <v>146.84</v>
       </c>
       <c r="C18" s="5">
         <f>IF(COUNT(B18:B19)=2,(B18/B19-1)*100,"")</f>
         <v/>
       </c>
       <c r="D18" s="5" t="n">
-        <v>173.8</v>
+        <v>179.55</v>
       </c>
       <c r="E18" s="5">
         <f>IF(COUNT(D18:D19)=2,(D18/D19-1)*100,"")</f>
         <v/>
       </c>
       <c r="F18" s="5" t="n">
-        <v>61.07</v>
+        <v>63.59</v>
       </c>
       <c r="G18" s="5">
         <f>IF(COUNT(F18:F19)=2,(F18/F19-1)*100,"")</f>
         <v/>
       </c>
       <c r="H18" s="5" t="n">
-        <v>371.08</v>
+        <v>377.16</v>
       </c>
       <c r="I18" s="5">
         <f>IF(COUNT(H18:H19)=2,(H18/H19-1)*100,"")</f>
         <v/>
       </c>
       <c r="J18" s="5" t="n">
-        <v>78.85720000000001</v>
+        <v>79.086</v>
       </c>
       <c r="K18" s="5">
         <f>IF(COUNT(J18:J19)=2,(J18/J19-1)*100,"")</f>
         <v/>
       </c>
       <c r="L18" s="5" t="n">
-        <v>106.985</v>
+        <v>106.9552</v>
       </c>
       <c r="M18" s="5">
         <f>IF(COUNT(L18:L19)=2,(L18/L19-1)*100,"")</f>
         <v/>
       </c>
       <c r="N18" s="5" t="n">
-        <v>56.68</v>
+        <v>57</v>
       </c>
       <c r="O18" s="5">
         <f>IF(COUNT(N18:N19)=2,(N18/N19-1)*100,"")</f>
         <v/>
       </c>
       <c r="P18" s="5" t="n">
-        <v>56.13</v>
+        <v>57.58</v>
       </c>
       <c r="Q18" s="5">
         <f>IF(COUNT(P18:P19)=2,(P18/P19-1)*100,"")</f>
         <v/>
       </c>
       <c r="R18" s="5" t="n">
-        <v>73.56999999999999</v>
+        <v>76.78</v>
       </c>
       <c r="S18" s="5">
         <f>IF(COUNT(R18:R19)=2,(R18/R19-1)*100,"")</f>
         <v/>
       </c>
       <c r="T18" s="5" t="n">
-        <v>109.51</v>
+        <v>106.58</v>
       </c>
       <c r="U18" s="5">
         <f>IF(COUNT(T18:T19)=2,(T18/T19-1)*100,"")</f>
         <v/>
       </c>
       <c r="V18" s="5" t="n">
-        <v>20.66</v>
+        <v>17.09</v>
       </c>
       <c r="W18" s="5">
         <f>IF(COUNT(V18:V19)=2,(V18/V19-1)*100,"")</f>
         <v/>
       </c>
       <c r="X18" s="5" t="n">
-        <v>13.4541</v>
+        <v>-17.2798</v>
       </c>
       <c r="Y18" s="5">
-        <f>IF(AND(X18&gt;$Y$11,C18&lt;=$Y$12),C17,"")</f>
+        <f>IF(AND(X18&gt;$Y$12,C18&lt;=$Y$13),C17,"")</f>
         <v/>
       </c>
       <c r="Z18" s="5">
-        <f>IF(AND(K18&lt;$Z$11,M18&gt;$Z$12),C17,"")</f>
+        <f>IF(AND(K18&lt;$Z$12,M18&gt;$Z$13),C17,"")</f>
         <v/>
       </c>
       <c r="AA18" s="5">
-        <f>IF(AND(G18&gt;$AA$11,I18&lt;$AA$12,K18&gt;$AA$12),C17,"")</f>
+        <f>IF(AND(G18&gt;$AA$12,I18&lt;$AA$13,K18&gt;$AA$11),C17,"")</f>
         <v/>
       </c>
       <c r="AB18" s="5">
@@ -2590,15 +2488,15 @@
         <v/>
       </c>
       <c r="AC18" s="5">
-        <f>IF(AND(S18&gt;$AC$11,U18&lt;$AC$12),E17,"")</f>
+        <f>IF(AND(S18&gt;$AC$12,U18&lt;$AC$13),E17,"")</f>
         <v/>
       </c>
       <c r="AD18" s="5">
-        <f>IF(AND(O18&lt;=$AD$11,E18&lt;$AD$12),E17,"")</f>
+        <f>IF(AND(O18&lt;=$AD$12,E18&lt;$AD$13),E17,"")</f>
         <v/>
       </c>
       <c r="AE18" s="5">
-        <f>IF(AND(Q18&gt;$AE$11,S18&gt;$AE$12),E17,"")</f>
+        <f>IF(AND(Q18&gt;$AE$12,S18&gt;$AE$13),E17,"")</f>
         <v/>
       </c>
       <c r="AF18" s="5">
@@ -2609,99 +2507,99 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026/07/28</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>143.57</v>
+        <v>137.65</v>
       </c>
       <c r="C19" s="5">
         <f>IF(COUNT(B19:B20)=2,(B19/B20-1)*100,"")</f>
         <v/>
       </c>
       <c r="D19" s="5" t="n">
-        <v>179.29</v>
+        <v>173.8</v>
       </c>
       <c r="E19" s="5">
         <f>IF(COUNT(D19:D20)=2,(D19/D20-1)*100,"")</f>
         <v/>
       </c>
       <c r="F19" s="5" t="n">
-        <v>62.36</v>
+        <v>61.07</v>
       </c>
       <c r="G19" s="5">
         <f>IF(COUNT(F19:F20)=2,(F19/F20-1)*100,"")</f>
         <v/>
       </c>
       <c r="H19" s="5" t="n">
-        <v>369.37</v>
+        <v>371.08</v>
       </c>
       <c r="I19" s="5">
         <f>IF(COUNT(H19:H20)=2,(H19/H20-1)*100,"")</f>
         <v/>
       </c>
       <c r="J19" s="5" t="n">
-        <v>79.0363</v>
+        <v>78.85720000000001</v>
       </c>
       <c r="K19" s="5">
         <f>IF(COUNT(J19:J20)=2,(J19/J20-1)*100,"")</f>
         <v/>
       </c>
       <c r="L19" s="5" t="n">
-        <v>106.8758</v>
+        <v>106.985</v>
       </c>
       <c r="M19" s="5">
         <f>IF(COUNT(L19:L20)=2,(L19/L20-1)*100,"")</f>
         <v/>
       </c>
       <c r="N19" s="5" t="n">
-        <v>57.6</v>
+        <v>56.68</v>
       </c>
       <c r="O19" s="5">
         <f>IF(COUNT(N19:N20)=2,(N19/N20-1)*100,"")</f>
         <v/>
       </c>
       <c r="P19" s="5" t="n">
-        <v>56</v>
+        <v>56.13</v>
       </c>
       <c r="Q19" s="5">
         <f>IF(COUNT(P19:P20)=2,(P19/P20-1)*100,"")</f>
         <v/>
       </c>
       <c r="R19" s="5" t="n">
-        <v>74.20999999999999</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="S19" s="5">
         <f>IF(COUNT(R19:R20)=2,(R19/R20-1)*100,"")</f>
         <v/>
       </c>
       <c r="T19" s="5" t="n">
-        <v>109.67</v>
+        <v>109.51</v>
       </c>
       <c r="U19" s="5">
         <f>IF(COUNT(T19:T20)=2,(T19/T20-1)*100,"")</f>
         <v/>
       </c>
       <c r="V19" s="5" t="n">
-        <v>18.21</v>
+        <v>20.66</v>
       </c>
       <c r="W19" s="5">
         <f>IF(COUNT(V19:V20)=2,(V19/V20-1)*100,"")</f>
         <v/>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-2.4638</v>
+        <v>13.4541</v>
       </c>
       <c r="Y19" s="5">
-        <f>IF(AND(X19&gt;$Y$11,C19&lt;=$Y$12),C18,"")</f>
+        <f>IF(AND(X19&gt;$Y$12,C19&lt;=$Y$13),C18,"")</f>
         <v/>
       </c>
       <c r="Z19" s="5">
-        <f>IF(AND(K19&lt;$Z$11,M19&gt;$Z$12),C18,"")</f>
+        <f>IF(AND(K19&lt;$Z$12,M19&gt;$Z$13),C18,"")</f>
         <v/>
       </c>
       <c r="AA19" s="5">
-        <f>IF(AND(G19&gt;$AA$11,I19&lt;$AA$12,K19&gt;$AA$12),C18,"")</f>
+        <f>IF(AND(G19&gt;$AA$12,I19&lt;$AA$13,K19&gt;$AA$11),C18,"")</f>
         <v/>
       </c>
       <c r="AB19" s="5">
@@ -2709,15 +2607,15 @@
         <v/>
       </c>
       <c r="AC19" s="5">
-        <f>IF(AND(S19&gt;$AC$11,U19&lt;$AC$12),E18,"")</f>
+        <f>IF(AND(S19&gt;$AC$12,U19&lt;$AC$13),E18,"")</f>
         <v/>
       </c>
       <c r="AD19" s="5">
-        <f>IF(AND(O19&lt;=$AD$11,E19&lt;$AD$12),E18,"")</f>
+        <f>IF(AND(O19&lt;=$AD$12,E19&lt;$AD$13),E18,"")</f>
         <v/>
       </c>
       <c r="AE19" s="5">
-        <f>IF(AND(Q19&gt;$AE$11,S19&gt;$AE$12),E18,"")</f>
+        <f>IF(AND(Q19&gt;$AE$12,S19&gt;$AE$13),E18,"")</f>
         <v/>
       </c>
       <c r="AF19" s="5">
@@ -2728,99 +2626,99 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/28</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>146.46</v>
+        <v>143.57</v>
       </c>
       <c r="C20" s="5">
         <f>IF(COUNT(B20:B21)=2,(B20/B21-1)*100,"")</f>
         <v/>
       </c>
       <c r="D20" s="5" t="n">
-        <v>178.54</v>
+        <v>179.29</v>
       </c>
       <c r="E20" s="5">
         <f>IF(COUNT(D20:D21)=2,(D20/D21-1)*100,"")</f>
         <v/>
       </c>
       <c r="F20" s="5" t="n">
-        <v>63.62</v>
+        <v>62.36</v>
       </c>
       <c r="G20" s="5">
         <f>IF(COUNT(F20:F21)=2,(F20/F21-1)*100,"")</f>
         <v/>
       </c>
       <c r="H20" s="5" t="n">
-        <v>374.63</v>
+        <v>369.37</v>
       </c>
       <c r="I20" s="5">
         <f>IF(COUNT(H20:H21)=2,(H20/H21-1)*100,"")</f>
         <v/>
       </c>
       <c r="J20" s="5" t="n">
-        <v>78.887</v>
+        <v>79.0363</v>
       </c>
       <c r="K20" s="5">
         <f>IF(COUNT(J20:J21)=2,(J20/J21-1)*100,"")</f>
         <v/>
       </c>
       <c r="L20" s="5" t="n">
-        <v>106.6077</v>
+        <v>106.8758</v>
       </c>
       <c r="M20" s="5">
         <f>IF(COUNT(L20:L21)=2,(L20/L21-1)*100,"")</f>
         <v/>
       </c>
       <c r="N20" s="5" t="n">
-        <v>56.88</v>
+        <v>57.6</v>
       </c>
       <c r="O20" s="5">
         <f>IF(COUNT(N20:N21)=2,(N20/N21-1)*100,"")</f>
         <v/>
       </c>
       <c r="P20" s="5" t="n">
-        <v>56.01</v>
+        <v>56</v>
       </c>
       <c r="Q20" s="5">
         <f>IF(COUNT(P20:P21)=2,(P20/P21-1)*100,"")</f>
         <v/>
       </c>
       <c r="R20" s="5" t="n">
-        <v>75.73</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="S20" s="5">
         <f>IF(COUNT(R20:R21)=2,(R20/R21-1)*100,"")</f>
         <v/>
       </c>
       <c r="T20" s="5" t="n">
-        <v>107.66</v>
+        <v>109.67</v>
       </c>
       <c r="U20" s="5">
         <f>IF(COUNT(T20:T21)=2,(T20/T21-1)*100,"")</f>
         <v/>
       </c>
       <c r="V20" s="5" t="n">
-        <v>18.67</v>
+        <v>18.21</v>
       </c>
       <c r="W20" s="5">
         <f>IF(COUNT(V20:V21)=2,(V20/V21-1)*100,"")</f>
         <v/>
       </c>
       <c r="X20" s="5" t="n">
-        <v>0.4844</v>
+        <v>-2.4638</v>
       </c>
       <c r="Y20" s="5">
-        <f>IF(AND(X20&gt;$Y$11,C20&lt;=$Y$12),C19,"")</f>
+        <f>IF(AND(X20&gt;$Y$12,C20&lt;=$Y$13),C19,"")</f>
         <v/>
       </c>
       <c r="Z20" s="5">
-        <f>IF(AND(K20&lt;$Z$11,M20&gt;$Z$12),C19,"")</f>
+        <f>IF(AND(K20&lt;$Z$12,M20&gt;$Z$13),C19,"")</f>
         <v/>
       </c>
       <c r="AA20" s="5">
-        <f>IF(AND(G20&gt;$AA$11,I20&lt;$AA$12,K20&gt;$AA$12),C19,"")</f>
+        <f>IF(AND(G20&gt;$AA$12,I20&lt;$AA$13,K20&gt;$AA$11),C19,"")</f>
         <v/>
       </c>
       <c r="AB20" s="5">
@@ -2828,15 +2726,15 @@
         <v/>
       </c>
       <c r="AC20" s="5">
-        <f>IF(AND(S20&gt;$AC$11,U20&lt;$AC$12),E19,"")</f>
+        <f>IF(AND(S20&gt;$AC$12,U20&lt;$AC$13),E19,"")</f>
         <v/>
       </c>
       <c r="AD20" s="5">
-        <f>IF(AND(O20&lt;=$AD$11,E20&lt;$AD$12),E19,"")</f>
+        <f>IF(AND(O20&lt;=$AD$12,E20&lt;$AD$13),E19,"")</f>
         <v/>
       </c>
       <c r="AE20" s="5">
-        <f>IF(AND(Q20&gt;$AE$11,S20&gt;$AE$12),E19,"")</f>
+        <f>IF(AND(Q20&gt;$AE$12,S20&gt;$AE$13),E19,"")</f>
         <v/>
       </c>
       <c r="AF20" s="5">
@@ -2847,99 +2745,99 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>147.47</v>
+        <v>146.46</v>
       </c>
       <c r="C21" s="5">
         <f>IF(COUNT(B21:B22)=2,(B21/B22-1)*100,"")</f>
         <v/>
       </c>
       <c r="D21" s="5" t="n">
-        <v>178.56</v>
+        <v>178.54</v>
       </c>
       <c r="E21" s="5">
         <f>IF(COUNT(D21:D22)=2,(D21/D22-1)*100,"")</f>
         <v/>
       </c>
       <c r="F21" s="5" t="n">
-        <v>63.33</v>
+        <v>63.62</v>
       </c>
       <c r="G21" s="5">
         <f>IF(COUNT(F21:F22)=2,(F21/F22-1)*100,"")</f>
         <v/>
       </c>
       <c r="H21" s="5" t="n">
-        <v>371.9</v>
+        <v>374.63</v>
       </c>
       <c r="I21" s="5">
         <f>IF(COUNT(H21:H22)=2,(H21/H22-1)*100,"")</f>
         <v/>
       </c>
       <c r="J21" s="5" t="n">
-        <v>78.8472</v>
+        <v>78.887</v>
       </c>
       <c r="K21" s="5">
         <f>IF(COUNT(J21:J22)=2,(J21/J22-1)*100,"")</f>
         <v/>
       </c>
       <c r="L21" s="5" t="n">
-        <v>106.7169</v>
+        <v>106.6077</v>
       </c>
       <c r="M21" s="5">
         <f>IF(COUNT(L21:L22)=2,(L21/L22-1)*100,"")</f>
         <v/>
       </c>
       <c r="N21" s="5" t="n">
-        <v>56.31</v>
+        <v>56.88</v>
       </c>
       <c r="O21" s="5">
         <f>IF(COUNT(N21:N22)=2,(N21/N22-1)*100,"")</f>
         <v/>
       </c>
       <c r="P21" s="5" t="n">
-        <v>56.04</v>
+        <v>56.01</v>
       </c>
       <c r="Q21" s="5">
         <f>IF(COUNT(P21:P22)=2,(P21/P22-1)*100,"")</f>
         <v/>
       </c>
       <c r="R21" s="5" t="n">
-        <v>75.23</v>
+        <v>75.73</v>
       </c>
       <c r="S21" s="5">
         <f>IF(COUNT(R21:R22)=2,(R21/R22-1)*100,"")</f>
         <v/>
       </c>
       <c r="T21" s="5" t="n">
-        <v>106.3</v>
+        <v>107.66</v>
       </c>
       <c r="U21" s="5">
         <f>IF(COUNT(T21:T22)=2,(T21/T22-1)*100,"")</f>
         <v/>
       </c>
       <c r="V21" s="5" t="n">
-        <v>18.58</v>
+        <v>18.67</v>
       </c>
       <c r="W21" s="5">
         <f>IF(COUNT(V21:V22)=2,(V21/V22-1)*100,"")</f>
         <v/>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-0.6417</v>
+        <v>0.4844</v>
       </c>
       <c r="Y21" s="5">
-        <f>IF(AND(X21&gt;$Y$11,C21&lt;=$Y$12),C20,"")</f>
+        <f>IF(AND(X21&gt;$Y$12,C21&lt;=$Y$13),C20,"")</f>
         <v/>
       </c>
       <c r="Z21" s="5">
-        <f>IF(AND(K21&lt;$Z$11,M21&gt;$Z$12),C20,"")</f>
+        <f>IF(AND(K21&lt;$Z$12,M21&gt;$Z$13),C20,"")</f>
         <v/>
       </c>
       <c r="AA21" s="5">
-        <f>IF(AND(G21&gt;$AA$11,I21&lt;$AA$12,K21&gt;$AA$12),C20,"")</f>
+        <f>IF(AND(G21&gt;$AA$12,I21&lt;$AA$13,K21&gt;$AA$11),C20,"")</f>
         <v/>
       </c>
       <c r="AB21" s="5">
@@ -2947,15 +2845,15 @@
         <v/>
       </c>
       <c r="AC21" s="5">
-        <f>IF(AND(S21&gt;$AC$11,U21&lt;$AC$12),E20,"")</f>
+        <f>IF(AND(S21&gt;$AC$12,U21&lt;$AC$13),E20,"")</f>
         <v/>
       </c>
       <c r="AD21" s="5">
-        <f>IF(AND(O21&lt;=$AD$11,E21&lt;$AD$12),E20,"")</f>
+        <f>IF(AND(O21&lt;=$AD$12,E21&lt;$AD$13),E20,"")</f>
         <v/>
       </c>
       <c r="AE21" s="5">
-        <f>IF(AND(Q21&gt;$AE$11,S21&gt;$AE$12),E20,"")</f>
+        <f>IF(AND(Q21&gt;$AE$12,S21&gt;$AE$13),E20,"")</f>
         <v/>
       </c>
       <c r="AF21" s="5">
@@ -2966,32 +2864,32 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>150.94</v>
+        <v>147.47</v>
       </c>
       <c r="C22" s="5">
         <f>IF(COUNT(B22:B23)=2,(B22/B23-1)*100,"")</f>
         <v/>
       </c>
       <c r="D22" s="5" t="n">
-        <v>178.37</v>
+        <v>178.56</v>
       </c>
       <c r="E22" s="5">
         <f>IF(COUNT(D22:D23)=2,(D22/D23-1)*100,"")</f>
         <v/>
       </c>
       <c r="F22" s="5" t="n">
-        <v>64.59999999999999</v>
+        <v>63.33</v>
       </c>
       <c r="G22" s="5">
         <f>IF(COUNT(F22:F23)=2,(F22/F23-1)*100,"")</f>
         <v/>
       </c>
       <c r="H22" s="5" t="n">
-        <v>371.52</v>
+        <v>371.9</v>
       </c>
       <c r="I22" s="5">
         <f>IF(COUNT(H22:H23)=2,(H22/H23-1)*100,"")</f>
@@ -3005,60 +2903,60 @@
         <v/>
       </c>
       <c r="L22" s="5" t="n">
-        <v>106.707</v>
+        <v>106.7169</v>
       </c>
       <c r="M22" s="5">
         <f>IF(COUNT(L22:L23)=2,(L22/L23-1)*100,"")</f>
         <v/>
       </c>
       <c r="N22" s="5" t="n">
-        <v>55.83</v>
+        <v>56.31</v>
       </c>
       <c r="O22" s="5">
         <f>IF(COUNT(N22:N23)=2,(N22/N23-1)*100,"")</f>
         <v/>
       </c>
       <c r="P22" s="5" t="n">
-        <v>56.01</v>
+        <v>56.04</v>
       </c>
       <c r="Q22" s="5">
         <f>IF(COUNT(P22:P23)=2,(P22/P23-1)*100,"")</f>
         <v/>
       </c>
       <c r="R22" s="5" t="n">
-        <v>75.02</v>
+        <v>75.23</v>
       </c>
       <c r="S22" s="5">
         <f>IF(COUNT(R22:R23)=2,(R22/R23-1)*100,"")</f>
         <v/>
       </c>
       <c r="T22" s="5" t="n">
-        <v>105.38</v>
+        <v>106.3</v>
       </c>
       <c r="U22" s="5">
         <f>IF(COUNT(T22:T23)=2,(T22/T23-1)*100,"")</f>
         <v/>
       </c>
       <c r="V22" s="5" t="n">
-        <v>18.7</v>
+        <v>18.58</v>
       </c>
       <c r="W22" s="5">
         <f>IF(COUNT(V22:V23)=2,(V22/V23-1)*100,"")</f>
         <v/>
       </c>
       <c r="X22" s="5" t="n">
-        <v>12.3798</v>
+        <v>-0.6417</v>
       </c>
       <c r="Y22" s="5">
-        <f>IF(AND(X22&gt;$Y$11,C22&lt;=$Y$12),C21,"")</f>
+        <f>IF(AND(X22&gt;$Y$12,C22&lt;=$Y$13),C21,"")</f>
         <v/>
       </c>
       <c r="Z22" s="5">
-        <f>IF(AND(K22&lt;$Z$11,M22&gt;$Z$12),C21,"")</f>
+        <f>IF(AND(K22&lt;$Z$12,M22&gt;$Z$13),C21,"")</f>
         <v/>
       </c>
       <c r="AA22" s="5">
-        <f>IF(AND(G22&gt;$AA$11,I22&lt;$AA$12,K22&gt;$AA$12),C21,"")</f>
+        <f>IF(AND(G22&gt;$AA$12,I22&lt;$AA$13,K22&gt;$AA$11),C21,"")</f>
         <v/>
       </c>
       <c r="AB22" s="5">
@@ -3066,15 +2964,15 @@
         <v/>
       </c>
       <c r="AC22" s="5">
-        <f>IF(AND(S22&gt;$AC$11,U22&lt;$AC$12),E21,"")</f>
+        <f>IF(AND(S22&gt;$AC$12,U22&lt;$AC$13),E21,"")</f>
         <v/>
       </c>
       <c r="AD22" s="5">
-        <f>IF(AND(O22&lt;=$AD$11,E22&lt;$AD$12),E21,"")</f>
+        <f>IF(AND(O22&lt;=$AD$12,E22&lt;$AD$13),E21,"")</f>
         <v/>
       </c>
       <c r="AE22" s="5">
-        <f>IF(AND(Q22&gt;$AE$11,S22&gt;$AE$12),E21,"")</f>
+        <f>IF(AND(Q22&gt;$AE$12,S22&gt;$AE$13),E21,"")</f>
         <v/>
       </c>
       <c r="AF22" s="5">
@@ -3085,99 +2983,99 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026/07/22</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>156.87</v>
+        <v>150.94</v>
       </c>
       <c r="C23" s="5">
         <f>IF(COUNT(B23:B24)=2,(B23/B24-1)*100,"")</f>
         <v/>
       </c>
       <c r="D23" s="5" t="n">
-        <v>182.85</v>
+        <v>178.37</v>
       </c>
       <c r="E23" s="5">
         <f>IF(COUNT(D23:D24)=2,(D23/D24-1)*100,"")</f>
         <v/>
       </c>
       <c r="F23" s="5" t="n">
-        <v>64.98999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G23" s="5">
         <f>IF(COUNT(F23:F24)=2,(F23/F24-1)*100,"")</f>
         <v/>
       </c>
       <c r="H23" s="5" t="n">
-        <v>379.12</v>
+        <v>371.52</v>
       </c>
       <c r="I23" s="5">
         <f>IF(COUNT(H23:H24)=2,(H23/H24-1)*100,"")</f>
         <v/>
       </c>
       <c r="J23" s="5" t="n">
-        <v>79.1358</v>
+        <v>78.8472</v>
       </c>
       <c r="K23" s="5">
         <f>IF(COUNT(J23:J24)=2,(J23/J24-1)*100,"")</f>
         <v/>
       </c>
       <c r="L23" s="5" t="n">
-        <v>106.985</v>
+        <v>106.707</v>
       </c>
       <c r="M23" s="5">
         <f>IF(COUNT(L23:L24)=2,(L23/L24-1)*100,"")</f>
         <v/>
       </c>
       <c r="N23" s="5" t="n">
-        <v>56.05</v>
+        <v>55.83</v>
       </c>
       <c r="O23" s="5">
         <f>IF(COUNT(N23:N24)=2,(N23/N24-1)*100,"")</f>
         <v/>
       </c>
       <c r="P23" s="5" t="n">
-        <v>56.23</v>
+        <v>56.01</v>
       </c>
       <c r="Q23" s="5">
         <f>IF(COUNT(P23:P24)=2,(P23/P24-1)*100,"")</f>
         <v/>
       </c>
       <c r="R23" s="5" t="n">
-        <v>76.68000000000001</v>
+        <v>75.02</v>
       </c>
       <c r="S23" s="5">
         <f>IF(COUNT(R23:R24)=2,(R23/R24-1)*100,"")</f>
         <v/>
       </c>
       <c r="T23" s="5" t="n">
-        <v>109.2</v>
+        <v>105.38</v>
       </c>
       <c r="U23" s="5">
         <f>IF(COUNT(T23:T24)=2,(T23/T24-1)*100,"")</f>
         <v/>
       </c>
       <c r="V23" s="5" t="n">
-        <v>16.64</v>
+        <v>18.7</v>
       </c>
       <c r="W23" s="5">
         <f>IF(COUNT(V23:V24)=2,(V23/V24-1)*100,"")</f>
         <v/>
       </c>
       <c r="X23" s="5" t="n">
-        <v>-2.4047</v>
+        <v>12.3798</v>
       </c>
       <c r="Y23" s="5">
-        <f>IF(AND(X23&gt;$Y$11,C23&lt;=$Y$12),C22,"")</f>
+        <f>IF(AND(X23&gt;$Y$12,C23&lt;=$Y$13),C22,"")</f>
         <v/>
       </c>
       <c r="Z23" s="5">
-        <f>IF(AND(K23&lt;$Z$11,M23&gt;$Z$12),C22,"")</f>
+        <f>IF(AND(K23&lt;$Z$12,M23&gt;$Z$13),C22,"")</f>
         <v/>
       </c>
       <c r="AA23" s="5">
-        <f>IF(AND(G23&gt;$AA$11,I23&lt;$AA$12,K23&gt;$AA$12),C22,"")</f>
+        <f>IF(AND(G23&gt;$AA$12,I23&lt;$AA$13,K23&gt;$AA$11),C22,"")</f>
         <v/>
       </c>
       <c r="AB23" s="5">
@@ -3185,15 +3083,15 @@
         <v/>
       </c>
       <c r="AC23" s="5">
-        <f>IF(AND(S23&gt;$AC$11,U23&lt;$AC$12),E22,"")</f>
+        <f>IF(AND(S23&gt;$AC$12,U23&lt;$AC$13),E22,"")</f>
         <v/>
       </c>
       <c r="AD23" s="5">
-        <f>IF(AND(O23&lt;=$AD$11,E23&lt;$AD$12),E22,"")</f>
+        <f>IF(AND(O23&lt;=$AD$12,E23&lt;$AD$13),E22,"")</f>
         <v/>
       </c>
       <c r="AE23" s="5">
-        <f>IF(AND(Q23&gt;$AE$11,S23&gt;$AE$12),E22,"")</f>
+        <f>IF(AND(Q23&gt;$AE$12,S23&gt;$AE$13),E22,"")</f>
         <v/>
       </c>
       <c r="AF23" s="5">
@@ -3204,99 +3102,99 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2026/07/21</t>
+          <t>2026/07/22</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>158.58</v>
+        <v>156.87</v>
       </c>
       <c r="C24" s="5">
         <f>IF(COUNT(B24:B25)=2,(B24/B25-1)*100,"")</f>
         <v/>
       </c>
       <c r="D24" s="5" t="n">
-        <v>183.34</v>
+        <v>182.85</v>
       </c>
       <c r="E24" s="5">
         <f>IF(COUNT(D24:D25)=2,(D24/D25-1)*100,"")</f>
         <v/>
       </c>
       <c r="F24" s="5" t="n">
-        <v>65.34</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="G24" s="5">
         <f>IF(COUNT(F24:F25)=2,(F24/F25-1)*100,"")</f>
         <v/>
       </c>
       <c r="H24" s="5" t="n">
-        <v>374.81</v>
+        <v>379.12</v>
       </c>
       <c r="I24" s="5">
         <f>IF(COUNT(H24:H25)=2,(H24/H25-1)*100,"")</f>
         <v/>
       </c>
       <c r="J24" s="5" t="n">
-        <v>79.26519999999999</v>
+        <v>79.1358</v>
       </c>
       <c r="K24" s="5">
         <f>IF(COUNT(J24:J25)=2,(J24/J25-1)*100,"")</f>
         <v/>
       </c>
       <c r="L24" s="5" t="n">
-        <v>107.0942</v>
+        <v>106.985</v>
       </c>
       <c r="M24" s="5">
         <f>IF(COUNT(L24:L25)=2,(L24/L25-1)*100,"")</f>
         <v/>
       </c>
       <c r="N24" s="5" t="n">
-        <v>56.11</v>
+        <v>56.05</v>
       </c>
       <c r="O24" s="5">
         <f>IF(COUNT(N24:N25)=2,(N24/N25-1)*100,"")</f>
         <v/>
       </c>
       <c r="P24" s="5" t="n">
-        <v>56.22</v>
+        <v>56.23</v>
       </c>
       <c r="Q24" s="5">
         <f>IF(COUNT(P24:P25)=2,(P24/P25-1)*100,"")</f>
         <v/>
       </c>
       <c r="R24" s="5" t="n">
-        <v>74.19</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="S24" s="5">
         <f>IF(COUNT(R24:R25)=2,(R24/R25-1)*100,"")</f>
         <v/>
       </c>
       <c r="T24" s="5" t="n">
-        <v>110.03</v>
+        <v>109.2</v>
       </c>
       <c r="U24" s="5">
         <f>IF(COUNT(T24:T25)=2,(T24/T25-1)*100,"")</f>
         <v/>
       </c>
       <c r="V24" s="5" t="n">
-        <v>17.05</v>
+        <v>16.64</v>
       </c>
       <c r="W24" s="5">
         <f>IF(COUNT(V24:V25)=2,(V24/V25-1)*100,"")</f>
         <v/>
       </c>
       <c r="X24" s="5" t="n">
-        <v>-8.5791</v>
+        <v>-2.4047</v>
       </c>
       <c r="Y24" s="5">
-        <f>IF(AND(X24&gt;$Y$11,C24&lt;=$Y$12),C23,"")</f>
+        <f>IF(AND(X24&gt;$Y$12,C24&lt;=$Y$13),C23,"")</f>
         <v/>
       </c>
       <c r="Z24" s="5">
-        <f>IF(AND(K24&lt;$Z$11,M24&gt;$Z$12),C23,"")</f>
+        <f>IF(AND(K24&lt;$Z$12,M24&gt;$Z$13),C23,"")</f>
         <v/>
       </c>
       <c r="AA24" s="5">
-        <f>IF(AND(G24&gt;$AA$11,I24&lt;$AA$12,K24&gt;$AA$12),C23,"")</f>
+        <f>IF(AND(G24&gt;$AA$12,I24&lt;$AA$13,K24&gt;$AA$11),C23,"")</f>
         <v/>
       </c>
       <c r="AB24" s="5">
@@ -3304,15 +3202,15 @@
         <v/>
       </c>
       <c r="AC24" s="5">
-        <f>IF(AND(S24&gt;$AC$11,U24&lt;$AC$12),E23,"")</f>
+        <f>IF(AND(S24&gt;$AC$12,U24&lt;$AC$13),E23,"")</f>
         <v/>
       </c>
       <c r="AD24" s="5">
-        <f>IF(AND(O24&lt;=$AD$11,E24&lt;$AD$12),E23,"")</f>
+        <f>IF(AND(O24&lt;=$AD$12,E24&lt;$AD$13),E23,"")</f>
         <v/>
       </c>
       <c r="AE24" s="5">
-        <f>IF(AND(Q24&gt;$AE$11,S24&gt;$AE$12),E23,"")</f>
+        <f>IF(AND(Q24&gt;$AE$12,S24&gt;$AE$13),E23,"")</f>
         <v/>
       </c>
       <c r="AF24" s="5">
@@ -3323,99 +3221,99 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/07/21</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>152.76</v>
+        <v>158.58</v>
       </c>
       <c r="C25" s="5">
         <f>IF(COUNT(B25:B26)=2,(B25/B26-1)*100,"")</f>
         <v/>
       </c>
       <c r="D25" s="5" t="n">
-        <v>180.23</v>
+        <v>183.34</v>
       </c>
       <c r="E25" s="5">
         <f>IF(COUNT(D25:D26)=2,(D25/D26-1)*100,"")</f>
         <v/>
       </c>
       <c r="F25" s="5" t="n">
-        <v>63.56</v>
+        <v>65.34</v>
       </c>
       <c r="G25" s="5">
         <f>IF(COUNT(F25:F26)=2,(F25/F26-1)*100,"")</f>
         <v/>
       </c>
       <c r="H25" s="5" t="n">
-        <v>367.6</v>
+        <v>374.81</v>
       </c>
       <c r="I25" s="5">
         <f>IF(COUNT(H25:H26)=2,(H25/H26-1)*100,"")</f>
         <v/>
       </c>
       <c r="J25" s="5" t="n">
-        <v>79.295</v>
+        <v>79.26519999999999</v>
       </c>
       <c r="K25" s="5">
         <f>IF(COUNT(J25:J26)=2,(J25/J26-1)*100,"")</f>
         <v/>
       </c>
       <c r="L25" s="5" t="n">
-        <v>107.2629</v>
+        <v>107.0942</v>
       </c>
       <c r="M25" s="5">
         <f>IF(COUNT(L25:L26)=2,(L25/L26-1)*100,"")</f>
         <v/>
       </c>
       <c r="N25" s="5" t="n">
-        <v>56.04</v>
+        <v>56.11</v>
       </c>
       <c r="O25" s="5">
         <f>IF(COUNT(N25:N26)=2,(N25/N26-1)*100,"")</f>
         <v/>
       </c>
       <c r="P25" s="5" t="n">
-        <v>56.46</v>
+        <v>56.22</v>
       </c>
       <c r="Q25" s="5">
         <f>IF(COUNT(P25:P26)=2,(P25/P26-1)*100,"")</f>
         <v/>
       </c>
       <c r="R25" s="5" t="n">
-        <v>70.73999999999999</v>
+        <v>74.19</v>
       </c>
       <c r="S25" s="5">
         <f>IF(COUNT(R25:R26)=2,(R25/R26-1)*100,"")</f>
         <v/>
       </c>
       <c r="T25" s="5" t="n">
-        <v>110.8</v>
+        <v>110.03</v>
       </c>
       <c r="U25" s="5">
         <f>IF(COUNT(T25:T26)=2,(T25/T26-1)*100,"")</f>
         <v/>
       </c>
       <c r="V25" s="5" t="n">
-        <v>18.65</v>
+        <v>17.05</v>
       </c>
       <c r="W25" s="5">
         <f>IF(COUNT(V25:V26)=2,(V25/V26-1)*100,"")</f>
         <v/>
       </c>
       <c r="X25" s="5" t="n">
-        <v>-0.6393</v>
+        <v>-8.5791</v>
       </c>
       <c r="Y25" s="5">
-        <f>IF(AND(X25&gt;$Y$11,C25&lt;=$Y$12),C24,"")</f>
+        <f>IF(AND(X25&gt;$Y$12,C25&lt;=$Y$13),C24,"")</f>
         <v/>
       </c>
       <c r="Z25" s="5">
-        <f>IF(AND(K25&lt;$Z$11,M25&gt;$Z$12),C24,"")</f>
+        <f>IF(AND(K25&lt;$Z$12,M25&gt;$Z$13),C24,"")</f>
         <v/>
       </c>
       <c r="AA25" s="5">
-        <f>IF(AND(G25&gt;$AA$11,I25&lt;$AA$12,K25&gt;$AA$12),C24,"")</f>
+        <f>IF(AND(G25&gt;$AA$12,I25&lt;$AA$13,K25&gt;$AA$11),C24,"")</f>
         <v/>
       </c>
       <c r="AB25" s="5">
@@ -3423,15 +3321,15 @@
         <v/>
       </c>
       <c r="AC25" s="5">
-        <f>IF(AND(S25&gt;$AC$11,U25&lt;$AC$12),E24,"")</f>
+        <f>IF(AND(S25&gt;$AC$12,U25&lt;$AC$13),E24,"")</f>
         <v/>
       </c>
       <c r="AD25" s="5">
-        <f>IF(AND(O25&lt;=$AD$11,E25&lt;$AD$12),E24,"")</f>
+        <f>IF(AND(O25&lt;=$AD$12,E25&lt;$AD$13),E24,"")</f>
         <v/>
       </c>
       <c r="AE25" s="5">
-        <f>IF(AND(Q25&gt;$AE$11,S25&gt;$AE$12),E24,"")</f>
+        <f>IF(AND(Q25&gt;$AE$12,S25&gt;$AE$13),E24,"")</f>
         <v/>
       </c>
       <c r="AF25" s="5">
@@ -3442,99 +3340,99 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/20</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>152.68</v>
+        <v>152.76</v>
       </c>
       <c r="C26" s="5">
         <f>IF(COUNT(B26:B27)=2,(B26/B27-1)*100,"")</f>
         <v/>
       </c>
       <c r="D26" s="5" t="n">
-        <v>180.98</v>
+        <v>180.23</v>
       </c>
       <c r="E26" s="5">
         <f>IF(COUNT(D26:D27)=2,(D26/D27-1)*100,"")</f>
         <v/>
       </c>
       <c r="F26" s="5" t="n">
-        <v>63.29</v>
+        <v>63.56</v>
       </c>
       <c r="G26" s="5">
         <f>IF(COUNT(F26:F27)=2,(F26/F27-1)*100,"")</f>
         <v/>
       </c>
       <c r="H26" s="5" t="n">
-        <v>368.41</v>
+        <v>367.6</v>
       </c>
       <c r="I26" s="5">
         <f>IF(COUNT(H26:H27)=2,(H26/H27-1)*100,"")</f>
         <v/>
       </c>
       <c r="J26" s="5" t="n">
-        <v>79.26519999999999</v>
+        <v>79.295</v>
       </c>
       <c r="K26" s="5">
         <f>IF(COUNT(J26:J27)=2,(J26/J27-1)*100,"")</f>
         <v/>
       </c>
       <c r="L26" s="5" t="n">
-        <v>107.4813</v>
+        <v>107.2629</v>
       </c>
       <c r="M26" s="5">
         <f>IF(COUNT(L26:L27)=2,(L26/L27-1)*100,"")</f>
         <v/>
       </c>
       <c r="N26" s="5" t="n">
-        <v>56.26</v>
+        <v>56.04</v>
       </c>
       <c r="O26" s="5">
         <f>IF(COUNT(N26:N27)=2,(N26/N27-1)*100,"")</f>
         <v/>
       </c>
       <c r="P26" s="5" t="n">
-        <v>56.51</v>
+        <v>56.46</v>
       </c>
       <c r="Q26" s="5">
         <f>IF(COUNT(P26:P27)=2,(P26/P27-1)*100,"")</f>
         <v/>
       </c>
       <c r="R26" s="5" t="n">
-        <v>71.31999999999999</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="S26" s="5">
         <f>IF(COUNT(R26:R27)=2,(R26/R27-1)*100,"")</f>
         <v/>
       </c>
       <c r="T26" s="5" t="n">
-        <v>110.65</v>
+        <v>110.8</v>
       </c>
       <c r="U26" s="5">
         <f>IF(COUNT(T26:T27)=2,(T26/T27-1)*100,"")</f>
         <v/>
       </c>
       <c r="V26" s="5" t="n">
-        <v>18.77</v>
+        <v>18.65</v>
       </c>
       <c r="W26" s="5">
         <f>IF(COUNT(V26:V27)=2,(V26/V27-1)*100,"")</f>
         <v/>
       </c>
       <c r="X26" s="5" t="n">
-        <v>12.1937</v>
+        <v>-0.6393</v>
       </c>
       <c r="Y26" s="5">
-        <f>IF(AND(X26&gt;$Y$11,C26&lt;=$Y$12),C25,"")</f>
+        <f>IF(AND(X26&gt;$Y$12,C26&lt;=$Y$13),C25,"")</f>
         <v/>
       </c>
       <c r="Z26" s="5">
-        <f>IF(AND(K26&lt;$Z$11,M26&gt;$Z$12),C25,"")</f>
+        <f>IF(AND(K26&lt;$Z$12,M26&gt;$Z$13),C25,"")</f>
         <v/>
       </c>
       <c r="AA26" s="5">
-        <f>IF(AND(G26&gt;$AA$11,I26&lt;$AA$12,K26&gt;$AA$12),C25,"")</f>
+        <f>IF(AND(G26&gt;$AA$12,I26&lt;$AA$13,K26&gt;$AA$11),C25,"")</f>
         <v/>
       </c>
       <c r="AB26" s="5">
@@ -3542,15 +3440,15 @@
         <v/>
       </c>
       <c r="AC26" s="5">
-        <f>IF(AND(S26&gt;$AC$11,U26&lt;$AC$12),E25,"")</f>
+        <f>IF(AND(S26&gt;$AC$12,U26&lt;$AC$13),E25,"")</f>
         <v/>
       </c>
       <c r="AD26" s="5">
-        <f>IF(AND(O26&lt;=$AD$11,E26&lt;$AD$12),E25,"")</f>
+        <f>IF(AND(O26&lt;=$AD$12,E26&lt;$AD$13),E25,"")</f>
         <v/>
       </c>
       <c r="AE26" s="5">
-        <f>IF(AND(Q26&gt;$AE$11,S26&gt;$AE$12),E25,"")</f>
+        <f>IF(AND(Q26&gt;$AE$12,S26&gt;$AE$13),E25,"")</f>
         <v/>
       </c>
       <c r="AF26" s="5">
@@ -3561,99 +3459,99 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>157.41</v>
+        <v>152.68</v>
       </c>
       <c r="C27" s="5">
         <f>IF(COUNT(B27:B28)=2,(B27/B28-1)*100,"")</f>
         <v/>
       </c>
       <c r="D27" s="5" t="n">
-        <v>184.73</v>
+        <v>180.98</v>
       </c>
       <c r="E27" s="5">
         <f>IF(COUNT(D27:D28)=2,(D27/D28-1)*100,"")</f>
         <v/>
       </c>
       <c r="F27" s="5" t="n">
-        <v>64.19</v>
+        <v>63.29</v>
       </c>
       <c r="G27" s="5">
         <f>IF(COUNT(F27:F28)=2,(F27/F28-1)*100,"")</f>
         <v/>
       </c>
       <c r="H27" s="5" t="n">
-        <v>364.96</v>
+        <v>368.41</v>
       </c>
       <c r="I27" s="5">
         <f>IF(COUNT(H27:H28)=2,(H27/H28-1)*100,"")</f>
         <v/>
       </c>
       <c r="J27" s="5" t="n">
-        <v>79.4145</v>
+        <v>79.26519999999999</v>
       </c>
       <c r="K27" s="5">
         <f>IF(COUNT(J27:J28)=2,(J27/J28-1)*100,"")</f>
         <v/>
       </c>
       <c r="L27" s="5" t="n">
-        <v>107.1835</v>
+        <v>107.4813</v>
       </c>
       <c r="M27" s="5">
         <f>IF(COUNT(L27:L28)=2,(L27/L28-1)*100,"")</f>
         <v/>
       </c>
       <c r="N27" s="5" t="n">
-        <v>56.75</v>
+        <v>56.26</v>
       </c>
       <c r="O27" s="5">
         <f>IF(COUNT(N27:N28)=2,(N27/N28-1)*100,"")</f>
         <v/>
       </c>
       <c r="P27" s="5" t="n">
-        <v>56.45</v>
+        <v>56.51</v>
       </c>
       <c r="Q27" s="5">
         <f>IF(COUNT(P27:P28)=2,(P27/P28-1)*100,"")</f>
         <v/>
       </c>
       <c r="R27" s="5" t="n">
-        <v>71.40000000000001</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="S27" s="5">
         <f>IF(COUNT(R27:R28)=2,(R27/R28-1)*100,"")</f>
         <v/>
       </c>
       <c r="T27" s="5" t="n">
-        <v>112.65</v>
+        <v>110.65</v>
       </c>
       <c r="U27" s="5">
         <f>IF(COUNT(T27:T28)=2,(T27/T28-1)*100,"")</f>
         <v/>
       </c>
       <c r="V27" s="5" t="n">
-        <v>16.73</v>
+        <v>18.77</v>
       </c>
       <c r="W27" s="5">
         <f>IF(COUNT(V27:V28)=2,(V27/V28-1)*100,"")</f>
         <v/>
       </c>
       <c r="X27" s="5" t="n">
-        <v>6.7645</v>
+        <v>12.1937</v>
       </c>
       <c r="Y27" s="5">
-        <f>IF(AND(X27&gt;$Y$11,C27&lt;=$Y$12),C26,"")</f>
+        <f>IF(AND(X27&gt;$Y$12,C27&lt;=$Y$13),C26,"")</f>
         <v/>
       </c>
       <c r="Z27" s="5">
-        <f>IF(AND(K27&lt;$Z$11,M27&gt;$Z$12),C26,"")</f>
+        <f>IF(AND(K27&lt;$Z$12,M27&gt;$Z$13),C26,"")</f>
         <v/>
       </c>
       <c r="AA27" s="5">
-        <f>IF(AND(G27&gt;$AA$11,I27&lt;$AA$12,K27&gt;$AA$12),C26,"")</f>
+        <f>IF(AND(G27&gt;$AA$12,I27&lt;$AA$13,K27&gt;$AA$11),C26,"")</f>
         <v/>
       </c>
       <c r="AB27" s="5">
@@ -3661,15 +3559,15 @@
         <v/>
       </c>
       <c r="AC27" s="5">
-        <f>IF(AND(S27&gt;$AC$11,U27&lt;$AC$12),E26,"")</f>
+        <f>IF(AND(S27&gt;$AC$12,U27&lt;$AC$13),E26,"")</f>
         <v/>
       </c>
       <c r="AD27" s="5">
-        <f>IF(AND(O27&lt;=$AD$11,E27&lt;$AD$12),E26,"")</f>
+        <f>IF(AND(O27&lt;=$AD$12,E27&lt;$AD$13),E26,"")</f>
         <v/>
       </c>
       <c r="AE27" s="5">
-        <f>IF(AND(Q27&gt;$AE$11,S27&gt;$AE$12),E26,"")</f>
+        <f>IF(AND(Q27&gt;$AE$12,S27&gt;$AE$13),E26,"")</f>
         <v/>
       </c>
       <c r="AF27" s="5">
@@ -3680,99 +3578,99 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>162.7</v>
+        <v>157.41</v>
       </c>
       <c r="C28" s="5">
         <f>IF(COUNT(B28:B29)=2,(B28/B29-1)*100,"")</f>
         <v/>
       </c>
       <c r="D28" s="5" t="n">
-        <v>186.67</v>
+        <v>184.73</v>
       </c>
       <c r="E28" s="5">
         <f>IF(COUNT(D28:D29)=2,(D28/D29-1)*100,"")</f>
         <v/>
       </c>
       <c r="F28" s="5" t="n">
-        <v>65.56999999999999</v>
+        <v>64.19</v>
       </c>
       <c r="G28" s="5">
         <f>IF(COUNT(F28:F29)=2,(F28/F29-1)*100,"")</f>
         <v/>
       </c>
       <c r="H28" s="5" t="n">
-        <v>372.35</v>
+        <v>364.96</v>
       </c>
       <c r="I28" s="5">
         <f>IF(COUNT(H28:H29)=2,(H28/H29-1)*100,"")</f>
         <v/>
       </c>
       <c r="J28" s="5" t="n">
-        <v>79.42440000000001</v>
+        <v>79.4145</v>
       </c>
       <c r="K28" s="5">
         <f>IF(COUNT(J28:J29)=2,(J28/J29-1)*100,"")</f>
         <v/>
       </c>
       <c r="L28" s="5" t="n">
-        <v>107.2828</v>
+        <v>107.1835</v>
       </c>
       <c r="M28" s="5">
         <f>IF(COUNT(L28:L29)=2,(L28/L29-1)*100,"")</f>
         <v/>
       </c>
       <c r="N28" s="5" t="n">
-        <v>56.56</v>
+        <v>56.75</v>
       </c>
       <c r="O28" s="5">
         <f>IF(COUNT(N28:N29)=2,(N28/N29-1)*100,"")</f>
         <v/>
       </c>
       <c r="P28" s="5" t="n">
-        <v>56.53</v>
+        <v>56.45</v>
       </c>
       <c r="Q28" s="5">
         <f>IF(COUNT(P28:P29)=2,(P28/P29-1)*100,"")</f>
         <v/>
       </c>
       <c r="R28" s="5" t="n">
-        <v>74</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="S28" s="5">
         <f>IF(COUNT(R28:R29)=2,(R28/R29-1)*100,"")</f>
         <v/>
       </c>
       <c r="T28" s="5" t="n">
-        <v>113.38</v>
+        <v>112.65</v>
       </c>
       <c r="U28" s="5">
         <f>IF(COUNT(T28:T29)=2,(T28/T29-1)*100,"")</f>
         <v/>
       </c>
       <c r="V28" s="5" t="n">
-        <v>15.67</v>
+        <v>16.73</v>
       </c>
       <c r="W28" s="5">
         <f>IF(COUNT(V28:V29)=2,(V28/V29-1)*100,"")</f>
         <v/>
       </c>
       <c r="X28" s="5" t="n">
-        <v>-5.0303</v>
+        <v>6.7645</v>
       </c>
       <c r="Y28" s="5">
-        <f>IF(AND(X28&gt;$Y$11,C28&lt;=$Y$12),C27,"")</f>
+        <f>IF(AND(X28&gt;$Y$12,C28&lt;=$Y$13),C27,"")</f>
         <v/>
       </c>
       <c r="Z28" s="5">
-        <f>IF(AND(K28&lt;$Z$11,M28&gt;$Z$12),C27,"")</f>
+        <f>IF(AND(K28&lt;$Z$12,M28&gt;$Z$13),C27,"")</f>
         <v/>
       </c>
       <c r="AA28" s="5">
-        <f>IF(AND(G28&gt;$AA$11,I28&lt;$AA$12,K28&gt;$AA$12),C27,"")</f>
+        <f>IF(AND(G28&gt;$AA$12,I28&lt;$AA$13,K28&gt;$AA$11),C27,"")</f>
         <v/>
       </c>
       <c r="AB28" s="5">
@@ -3780,15 +3678,15 @@
         <v/>
       </c>
       <c r="AC28" s="5">
-        <f>IF(AND(S28&gt;$AC$11,U28&lt;$AC$12),E27,"")</f>
+        <f>IF(AND(S28&gt;$AC$12,U28&lt;$AC$13),E27,"")</f>
         <v/>
       </c>
       <c r="AD28" s="5">
-        <f>IF(AND(O28&lt;=$AD$11,E28&lt;$AD$12),E27,"")</f>
+        <f>IF(AND(O28&lt;=$AD$12,E28&lt;$AD$13),E27,"")</f>
         <v/>
       </c>
       <c r="AE28" s="5">
-        <f>IF(AND(Q28&gt;$AE$11,S28&gt;$AE$12),E27,"")</f>
+        <f>IF(AND(Q28&gt;$AE$12,S28&gt;$AE$13),E27,"")</f>
         <v/>
       </c>
       <c r="AF28" s="5">
@@ -3799,99 +3697,99 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>2026/07/15</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>163.66</v>
+        <v>162.7</v>
       </c>
       <c r="C29" s="5">
         <f>IF(COUNT(B29:B30)=2,(B29/B30-1)*100,"")</f>
         <v/>
       </c>
       <c r="D29" s="5" t="n">
-        <v>185.27</v>
+        <v>186.67</v>
       </c>
       <c r="E29" s="5">
         <f>IF(COUNT(D29:D30)=2,(D29/D30-1)*100,"")</f>
         <v/>
       </c>
       <c r="F29" s="5" t="n">
-        <v>65.67</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="G29" s="5">
         <f>IF(COUNT(F29:F30)=2,(F29/F30-1)*100,"")</f>
         <v/>
       </c>
       <c r="H29" s="5" t="n">
-        <v>372.15</v>
+        <v>372.35</v>
       </c>
       <c r="I29" s="5">
         <f>IF(COUNT(H29:H30)=2,(H29/H30-1)*100,"")</f>
         <v/>
       </c>
       <c r="J29" s="5" t="n">
-        <v>79.295</v>
+        <v>79.42440000000001</v>
       </c>
       <c r="K29" s="5">
         <f>IF(COUNT(J29:J30)=2,(J29/J30-1)*100,"")</f>
         <v/>
       </c>
       <c r="L29" s="5" t="n">
-        <v>107.2232</v>
+        <v>107.2828</v>
       </c>
       <c r="M29" s="5">
         <f>IF(COUNT(L29:L30)=2,(L29/L30-1)*100,"")</f>
         <v/>
       </c>
       <c r="N29" s="5" t="n">
-        <v>56.18</v>
+        <v>56.56</v>
       </c>
       <c r="O29" s="5">
         <f>IF(COUNT(N29:N30)=2,(N29/N30-1)*100,"")</f>
         <v/>
       </c>
       <c r="P29" s="5" t="n">
-        <v>56.57</v>
+        <v>56.53</v>
       </c>
       <c r="Q29" s="5">
         <f>IF(COUNT(P29:P30)=2,(P29/P30-1)*100,"")</f>
         <v/>
       </c>
       <c r="R29" s="5" t="n">
-        <v>74.88</v>
+        <v>74</v>
       </c>
       <c r="S29" s="5">
         <f>IF(COUNT(R29:R30)=2,(R29/R30-1)*100,"")</f>
         <v/>
       </c>
       <c r="T29" s="5" t="n">
-        <v>111.45</v>
+        <v>113.38</v>
       </c>
       <c r="U29" s="5">
         <f>IF(COUNT(T29:T30)=2,(T29/T30-1)*100,"")</f>
         <v/>
       </c>
       <c r="V29" s="5" t="n">
-        <v>16.5</v>
+        <v>15.67</v>
       </c>
       <c r="W29" s="5">
         <f>IF(COUNT(V29:V30)=2,(V29/V30-1)*100,"")</f>
         <v/>
       </c>
       <c r="X29" s="5" t="n">
-        <v>-3.8462</v>
+        <v>-5.0303</v>
       </c>
       <c r="Y29" s="5">
-        <f>IF(AND(X29&gt;$Y$11,C29&lt;=$Y$12),C28,"")</f>
+        <f>IF(AND(X29&gt;$Y$12,C29&lt;=$Y$13),C28,"")</f>
         <v/>
       </c>
       <c r="Z29" s="5">
-        <f>IF(AND(K29&lt;$Z$11,M29&gt;$Z$12),C28,"")</f>
+        <f>IF(AND(K29&lt;$Z$12,M29&gt;$Z$13),C28,"")</f>
         <v/>
       </c>
       <c r="AA29" s="5">
-        <f>IF(AND(G29&gt;$AA$11,I29&lt;$AA$12,K29&gt;$AA$12),C28,"")</f>
+        <f>IF(AND(G29&gt;$AA$12,I29&lt;$AA$13,K29&gt;$AA$11),C28,"")</f>
         <v/>
       </c>
       <c r="AB29" s="5">
@@ -3899,15 +3797,15 @@
         <v/>
       </c>
       <c r="AC29" s="5">
-        <f>IF(AND(S29&gt;$AC$11,U29&lt;$AC$12),E28,"")</f>
+        <f>IF(AND(S29&gt;$AC$12,U29&lt;$AC$13),E28,"")</f>
         <v/>
       </c>
       <c r="AD29" s="5">
-        <f>IF(AND(O29&lt;=$AD$11,E29&lt;$AD$12),E28,"")</f>
+        <f>IF(AND(O29&lt;=$AD$12,E29&lt;$AD$13),E28,"")</f>
         <v/>
       </c>
       <c r="AE29" s="5">
-        <f>IF(AND(Q29&gt;$AE$11,S29&gt;$AE$12),E28,"")</f>
+        <f>IF(AND(Q29&gt;$AE$12,S29&gt;$AE$13),E28,"")</f>
         <v/>
       </c>
       <c r="AF29" s="5">
@@ -3918,99 +3816,99 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>160.15</v>
+        <v>163.66</v>
       </c>
       <c r="C30" s="5">
         <f>IF(COUNT(B30:B31)=2,(B30/B31-1)*100,"")</f>
         <v/>
       </c>
       <c r="D30" s="5" t="n">
-        <v>183.93</v>
+        <v>185.27</v>
       </c>
       <c r="E30" s="5">
         <f>IF(COUNT(D30:D31)=2,(D30/D31-1)*100,"")</f>
         <v/>
       </c>
       <c r="F30" s="5" t="n">
-        <v>64.5</v>
+        <v>65.67</v>
       </c>
       <c r="G30" s="5">
         <f>IF(COUNT(F30:F31)=2,(F30/F31-1)*100,"")</f>
         <v/>
       </c>
       <c r="H30" s="5" t="n">
-        <v>367.13</v>
+        <v>372.15</v>
       </c>
       <c r="I30" s="5">
         <f>IF(COUNT(H30:H31)=2,(H30/H31-1)*100,"")</f>
         <v/>
       </c>
       <c r="J30" s="5" t="n">
-        <v>79.1358</v>
+        <v>79.295</v>
       </c>
       <c r="K30" s="5">
         <f>IF(COUNT(J30:J31)=2,(J30/J31-1)*100,"")</f>
         <v/>
       </c>
       <c r="L30" s="5" t="n">
-        <v>107.124</v>
+        <v>107.2232</v>
       </c>
       <c r="M30" s="5">
         <f>IF(COUNT(L30:L31)=2,(L30/L31-1)*100,"")</f>
         <v/>
       </c>
       <c r="N30" s="5" t="n">
-        <v>56.07</v>
+        <v>56.18</v>
       </c>
       <c r="O30" s="5">
         <f>IF(COUNT(N30:N31)=2,(N30/N31-1)*100,"")</f>
         <v/>
       </c>
       <c r="P30" s="5" t="n">
-        <v>56.46</v>
+        <v>56.57</v>
       </c>
       <c r="Q30" s="5">
         <f>IF(COUNT(P30:P31)=2,(P30/P31-1)*100,"")</f>
         <v/>
       </c>
       <c r="R30" s="5" t="n">
-        <v>73.37</v>
+        <v>74.88</v>
       </c>
       <c r="S30" s="5">
         <f>IF(COUNT(R30:R31)=2,(R30/R31-1)*100,"")</f>
         <v/>
       </c>
       <c r="T30" s="5" t="n">
-        <v>111.59</v>
+        <v>111.45</v>
       </c>
       <c r="U30" s="5">
         <f>IF(COUNT(T30:T31)=2,(T30/T31-1)*100,"")</f>
         <v/>
       </c>
       <c r="V30" s="5" t="n">
-        <v>17.16</v>
+        <v>16.5</v>
       </c>
       <c r="W30" s="5">
         <f>IF(COUNT(V30:V31)=2,(V30/V31-1)*100,"")</f>
         <v/>
       </c>
       <c r="X30" s="5" t="n">
-        <v>14.1717</v>
+        <v>-3.8462</v>
       </c>
       <c r="Y30" s="5">
-        <f>IF(AND(X30&gt;$Y$11,C30&lt;=$Y$12),C29,"")</f>
+        <f>IF(AND(X30&gt;$Y$12,C30&lt;=$Y$13),C29,"")</f>
         <v/>
       </c>
       <c r="Z30" s="5">
-        <f>IF(AND(K30&lt;$Z$11,M30&gt;$Z$12),C29,"")</f>
+        <f>IF(AND(K30&lt;$Z$12,M30&gt;$Z$13),C29,"")</f>
         <v/>
       </c>
       <c r="AA30" s="5">
-        <f>IF(AND(G30&gt;$AA$11,I30&lt;$AA$12,K30&gt;$AA$12),C29,"")</f>
+        <f>IF(AND(G30&gt;$AA$12,I30&lt;$AA$13,K30&gt;$AA$11),C29,"")</f>
         <v/>
       </c>
       <c r="AB30" s="5">
@@ -4018,15 +3916,15 @@
         <v/>
       </c>
       <c r="AC30" s="5">
-        <f>IF(AND(S30&gt;$AC$11,U30&lt;$AC$12),E29,"")</f>
+        <f>IF(AND(S30&gt;$AC$12,U30&lt;$AC$13),E29,"")</f>
         <v/>
       </c>
       <c r="AD30" s="5">
-        <f>IF(AND(O30&lt;=$AD$11,E30&lt;$AD$12),E29,"")</f>
+        <f>IF(AND(O30&lt;=$AD$12,E30&lt;$AD$13),E29,"")</f>
         <v/>
       </c>
       <c r="AE30" s="5">
-        <f>IF(AND(Q30&gt;$AE$11,S30&gt;$AE$12),E29,"")</f>
+        <f>IF(AND(Q30&gt;$AE$12,S30&gt;$AE$13),E29,"")</f>
         <v/>
       </c>
       <c r="AF30" s="5">
@@ -4037,99 +3935,99 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>166.49</v>
+        <v>160.15</v>
       </c>
       <c r="C31" s="5">
         <f>IF(COUNT(B31:B32)=2,(B31/B32-1)*100,"")</f>
         <v/>
       </c>
       <c r="D31" s="5" t="n">
-        <v>186.95</v>
+        <v>183.93</v>
       </c>
       <c r="E31" s="5">
         <f>IF(COUNT(D31:D32)=2,(D31/D32-1)*100,"")</f>
         <v/>
       </c>
       <c r="F31" s="5" t="n">
-        <v>66.90000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="G31" s="5">
         <f>IF(COUNT(F31:F32)=2,(F31/F32-1)*100,"")</f>
         <v/>
       </c>
       <c r="H31" s="5" t="n">
-        <v>377.01</v>
+        <v>367.13</v>
       </c>
       <c r="I31" s="5">
         <f>IF(COUNT(H31:H32)=2,(H31/H32-1)*100,"")</f>
         <v/>
       </c>
       <c r="J31" s="5" t="n">
-        <v>79.3249</v>
+        <v>79.1358</v>
       </c>
       <c r="K31" s="5">
         <f>IF(COUNT(J31:J32)=2,(J31/J32-1)*100,"")</f>
         <v/>
       </c>
       <c r="L31" s="5" t="n">
-        <v>107.3424</v>
+        <v>107.124</v>
       </c>
       <c r="M31" s="5">
         <f>IF(COUNT(L31:L32)=2,(L31/L32-1)*100,"")</f>
         <v/>
       </c>
       <c r="N31" s="5" t="n">
-        <v>55.71</v>
+        <v>56.07</v>
       </c>
       <c r="O31" s="5">
         <f>IF(COUNT(N31:N32)=2,(N31/N32-1)*100,"")</f>
         <v/>
       </c>
       <c r="P31" s="5" t="n">
-        <v>56.74</v>
+        <v>56.46</v>
       </c>
       <c r="Q31" s="5">
         <f>IF(COUNT(P31:P32)=2,(P31/P32-1)*100,"")</f>
         <v/>
       </c>
       <c r="R31" s="5" t="n">
-        <v>75.53</v>
+        <v>73.37</v>
       </c>
       <c r="S31" s="5">
         <f>IF(COUNT(R31:R32)=2,(R31/R32-1)*100,"")</f>
         <v/>
       </c>
       <c r="T31" s="5" t="n">
-        <v>111.64</v>
+        <v>111.59</v>
       </c>
       <c r="U31" s="5">
         <f>IF(COUNT(T31:T32)=2,(T31/T32-1)*100,"")</f>
         <v/>
       </c>
       <c r="V31" s="5" t="n">
-        <v>15.03</v>
+        <v>17.16</v>
       </c>
       <c r="W31" s="5">
         <f>IF(COUNT(V31:V32)=2,(V31/V32-1)*100,"")</f>
         <v/>
       </c>
       <c r="X31" s="5" t="n">
-        <v>-5.1136</v>
+        <v>14.1717</v>
       </c>
       <c r="Y31" s="5">
-        <f>IF(AND(X31&gt;$Y$11,C31&lt;=$Y$12),C30,"")</f>
+        <f>IF(AND(X31&gt;$Y$12,C31&lt;=$Y$13),C30,"")</f>
         <v/>
       </c>
       <c r="Z31" s="5">
-        <f>IF(AND(K31&lt;$Z$11,M31&gt;$Z$12),C30,"")</f>
+        <f>IF(AND(K31&lt;$Z$12,M31&gt;$Z$13),C30,"")</f>
         <v/>
       </c>
       <c r="AA31" s="5">
-        <f>IF(AND(G31&gt;$AA$11,I31&lt;$AA$12,K31&gt;$AA$12),C30,"")</f>
+        <f>IF(AND(G31&gt;$AA$12,I31&lt;$AA$13,K31&gt;$AA$11),C30,"")</f>
         <v/>
       </c>
       <c r="AB31" s="5">
@@ -4137,15 +4035,15 @@
         <v/>
       </c>
       <c r="AC31" s="5">
-        <f>IF(AND(S31&gt;$AC$11,U31&lt;$AC$12),E30,"")</f>
+        <f>IF(AND(S31&gt;$AC$12,U31&lt;$AC$13),E30,"")</f>
         <v/>
       </c>
       <c r="AD31" s="5">
-        <f>IF(AND(O31&lt;=$AD$11,E31&lt;$AD$12),E30,"")</f>
+        <f>IF(AND(O31&lt;=$AD$12,E31&lt;$AD$13),E30,"")</f>
         <v/>
       </c>
       <c r="AE31" s="5">
-        <f>IF(AND(Q31&gt;$AE$11,S31&gt;$AE$12),E30,"")</f>
+        <f>IF(AND(Q31&gt;$AE$12,S31&gt;$AE$13),E30,"")</f>
         <v/>
       </c>
       <c r="AF31" s="5">
@@ -4156,99 +4054,99 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2026/07/09</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>165.43</v>
+        <v>166.49</v>
       </c>
       <c r="C32" s="5">
         <f>IF(COUNT(B32:B33)=2,(B32/B33-1)*100,"")</f>
         <v/>
       </c>
       <c r="D32" s="5" t="n">
-        <v>185.38</v>
+        <v>186.95</v>
       </c>
       <c r="E32" s="5">
         <f>IF(COUNT(D32:D33)=2,(D32/D33-1)*100,"")</f>
         <v/>
       </c>
       <c r="F32" s="5" t="n">
-        <v>66.78</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G32" s="5">
         <f>IF(COUNT(F32:F33)=2,(F32/F33-1)*100,"")</f>
         <v/>
       </c>
       <c r="H32" s="5" t="n">
-        <v>378.18</v>
+        <v>377.01</v>
       </c>
       <c r="I32" s="5">
         <f>IF(COUNT(H32:H33)=2,(H32/H33-1)*100,"")</f>
         <v/>
       </c>
       <c r="J32" s="5" t="n">
-        <v>79.3647</v>
+        <v>79.3249</v>
       </c>
       <c r="K32" s="5">
         <f>IF(COUNT(J32:J33)=2,(J32/J33-1)*100,"")</f>
         <v/>
       </c>
       <c r="L32" s="5" t="n">
-        <v>107.3324</v>
+        <v>107.3424</v>
       </c>
       <c r="M32" s="5">
         <f>IF(COUNT(L32:L33)=2,(L32/L33-1)*100,"")</f>
         <v/>
       </c>
       <c r="N32" s="5" t="n">
-        <v>55.54</v>
+        <v>55.71</v>
       </c>
       <c r="O32" s="5">
         <f>IF(COUNT(N32:N33)=2,(N32/N33-1)*100,"")</f>
         <v/>
       </c>
       <c r="P32" s="5" t="n">
-        <v>56.48</v>
+        <v>56.74</v>
       </c>
       <c r="Q32" s="5">
         <f>IF(COUNT(P32:P33)=2,(P32/P33-1)*100,"")</f>
         <v/>
       </c>
       <c r="R32" s="5" t="n">
-        <v>75.78</v>
+        <v>75.53</v>
       </c>
       <c r="S32" s="5">
         <f>IF(COUNT(R32:R33)=2,(R32/R33-1)*100,"")</f>
         <v/>
       </c>
       <c r="T32" s="5" t="n">
-        <v>110.51</v>
+        <v>111.64</v>
       </c>
       <c r="U32" s="5">
         <f>IF(COUNT(T32:T33)=2,(T32/T33-1)*100,"")</f>
         <v/>
       </c>
       <c r="V32" s="5" t="n">
-        <v>15.84</v>
+        <v>15.03</v>
       </c>
       <c r="W32" s="5">
         <f>IF(COUNT(V32:V33)=2,(V32/V33-1)*100,"")</f>
         <v/>
       </c>
       <c r="X32" s="5" t="n">
-        <v>-6.2722</v>
+        <v>-5.1136</v>
       </c>
       <c r="Y32" s="5">
-        <f>IF(AND(X32&gt;$Y$11,C32&lt;=$Y$12),C31,"")</f>
+        <f>IF(AND(X32&gt;$Y$12,C32&lt;=$Y$13),C31,"")</f>
         <v/>
       </c>
       <c r="Z32" s="5">
-        <f>IF(AND(K32&lt;$Z$11,M32&gt;$Z$12),C31,"")</f>
+        <f>IF(AND(K32&lt;$Z$12,M32&gt;$Z$13),C31,"")</f>
         <v/>
       </c>
       <c r="AA32" s="5">
-        <f>IF(AND(G32&gt;$AA$11,I32&lt;$AA$12,K32&gt;$AA$12),C31,"")</f>
+        <f>IF(AND(G32&gt;$AA$12,I32&lt;$AA$13,K32&gt;$AA$11),C31,"")</f>
         <v/>
       </c>
       <c r="AB32" s="5">
@@ -4256,15 +4154,15 @@
         <v/>
       </c>
       <c r="AC32" s="5">
-        <f>IF(AND(S32&gt;$AC$11,U32&lt;$AC$12),E31,"")</f>
+        <f>IF(AND(S32&gt;$AC$12,U32&lt;$AC$13),E31,"")</f>
         <v/>
       </c>
       <c r="AD32" s="5">
-        <f>IF(AND(O32&lt;=$AD$11,E32&lt;$AD$12),E31,"")</f>
+        <f>IF(AND(O32&lt;=$AD$12,E32&lt;$AD$13),E31,"")</f>
         <v/>
       </c>
       <c r="AE32" s="5">
-        <f>IF(AND(Q32&gt;$AE$11,S32&gt;$AE$12),E31,"")</f>
+        <f>IF(AND(Q32&gt;$AE$12,S32&gt;$AE$13),E31,"")</f>
         <v/>
       </c>
       <c r="AF32" s="5">
@@ -4275,99 +4173,99 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/09</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>160.25</v>
+        <v>165.43</v>
       </c>
       <c r="C33" s="5">
         <f>IF(COUNT(B33:B34)=2,(B33/B34-1)*100,"")</f>
         <v/>
       </c>
       <c r="D33" s="5" t="n">
-        <v>182.42</v>
+        <v>185.38</v>
       </c>
       <c r="E33" s="5">
         <f>IF(COUNT(D33:D34)=2,(D33/D34-1)*100,"")</f>
         <v/>
       </c>
       <c r="F33" s="5" t="n">
-        <v>66.23</v>
+        <v>66.78</v>
       </c>
       <c r="G33" s="5">
         <f>IF(COUNT(F33:F34)=2,(F33/F34-1)*100,"")</f>
         <v/>
       </c>
       <c r="H33" s="5" t="n">
-        <v>374.45</v>
+        <v>378.18</v>
       </c>
       <c r="I33" s="5">
         <f>IF(COUNT(H33:H34)=2,(H33/H34-1)*100,"")</f>
         <v/>
       </c>
       <c r="J33" s="5" t="n">
-        <v>79.27509999999999</v>
+        <v>79.3647</v>
       </c>
       <c r="K33" s="5">
         <f>IF(COUNT(J33:J34)=2,(J33/J34-1)*100,"")</f>
         <v/>
       </c>
       <c r="L33" s="5" t="n">
-        <v>107.2629</v>
+        <v>107.3324</v>
       </c>
       <c r="M33" s="5">
         <f>IF(COUNT(L33:L34)=2,(L33/L34-1)*100,"")</f>
         <v/>
       </c>
       <c r="N33" s="5" t="n">
-        <v>54.97</v>
+        <v>55.54</v>
       </c>
       <c r="O33" s="5">
         <f>IF(COUNT(N33:N34)=2,(N33/N34-1)*100,"")</f>
         <v/>
       </c>
       <c r="P33" s="5" t="n">
-        <v>56.46</v>
+        <v>56.48</v>
       </c>
       <c r="Q33" s="5">
         <f>IF(COUNT(P33:P34)=2,(P33/P34-1)*100,"")</f>
         <v/>
       </c>
       <c r="R33" s="5" t="n">
-        <v>73.53</v>
+        <v>75.78</v>
       </c>
       <c r="S33" s="5">
         <f>IF(COUNT(R33:R34)=2,(R33/R34-1)*100,"")</f>
         <v/>
       </c>
       <c r="T33" s="5" t="n">
-        <v>109.46</v>
+        <v>110.51</v>
       </c>
       <c r="U33" s="5">
         <f>IF(COUNT(T33:T34)=2,(T33/T34-1)*100,"")</f>
         <v/>
       </c>
       <c r="V33" s="5" t="n">
-        <v>16.9</v>
+        <v>15.84</v>
       </c>
       <c r="W33" s="5">
         <f>IF(COUNT(V33:V34)=2,(V33/V34-1)*100,"")</f>
         <v/>
       </c>
       <c r="X33" s="5" t="n">
-        <v>4.7737</v>
+        <v>-6.2722</v>
       </c>
       <c r="Y33" s="5">
-        <f>IF(AND(X33&gt;$Y$11,C33&lt;=$Y$12),C32,"")</f>
+        <f>IF(AND(X33&gt;$Y$12,C33&lt;=$Y$13),C32,"")</f>
         <v/>
       </c>
       <c r="Z33" s="5">
-        <f>IF(AND(K33&lt;$Z$11,M33&gt;$Z$12),C32,"")</f>
+        <f>IF(AND(K33&lt;$Z$12,M33&gt;$Z$13),C32,"")</f>
         <v/>
       </c>
       <c r="AA33" s="5">
-        <f>IF(AND(G33&gt;$AA$11,I33&lt;$AA$12,K33&gt;$AA$12),C32,"")</f>
+        <f>IF(AND(G33&gt;$AA$12,I33&lt;$AA$13,K33&gt;$AA$11),C32,"")</f>
         <v/>
       </c>
       <c r="AB33" s="5">
@@ -4375,15 +4273,15 @@
         <v/>
       </c>
       <c r="AC33" s="5">
-        <f>IF(AND(S33&gt;$AC$11,U33&lt;$AC$12),E32,"")</f>
+        <f>IF(AND(S33&gt;$AC$12,U33&lt;$AC$13),E32,"")</f>
         <v/>
       </c>
       <c r="AD33" s="5">
-        <f>IF(AND(O33&lt;=$AD$11,E33&lt;$AD$12),E32,"")</f>
+        <f>IF(AND(O33&lt;=$AD$12,E33&lt;$AD$13),E32,"")</f>
         <v/>
       </c>
       <c r="AE33" s="5">
-        <f>IF(AND(Q33&gt;$AE$11,S33&gt;$AE$12),E32,"")</f>
+        <f>IF(AND(Q33&gt;$AE$12,S33&gt;$AE$13),E32,"")</f>
         <v/>
       </c>
       <c r="AF33" s="5">
@@ -4394,99 +4292,99 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>2026/07/07</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>159.4</v>
+        <v>160.25</v>
       </c>
       <c r="C34" s="5">
         <f>IF(COUNT(B34:B35)=2,(B34/B35-1)*100,"")</f>
         <v/>
       </c>
       <c r="D34" s="5" t="n">
-        <v>183.5</v>
+        <v>182.42</v>
       </c>
       <c r="E34" s="5">
         <f>IF(COUNT(D34:D35)=2,(D34/D35-1)*100,"")</f>
         <v/>
       </c>
       <c r="F34" s="5" t="n">
-        <v>65.72</v>
+        <v>66.23</v>
       </c>
       <c r="G34" s="5">
         <f>IF(COUNT(F34:F35)=2,(F34/F35-1)*100,"")</f>
         <v/>
       </c>
       <c r="H34" s="5" t="n">
-        <v>377.49</v>
+        <v>374.45</v>
       </c>
       <c r="I34" s="5">
         <f>IF(COUNT(H34:H35)=2,(H34/H35-1)*100,"")</f>
         <v/>
       </c>
       <c r="J34" s="5" t="n">
-        <v>79.3746</v>
+        <v>79.27509999999999</v>
       </c>
       <c r="K34" s="5">
         <f>IF(COUNT(J34:J35)=2,(J34/J35-1)*100,"")</f>
         <v/>
       </c>
       <c r="L34" s="5" t="n">
-        <v>107.3821</v>
+        <v>107.2629</v>
       </c>
       <c r="M34" s="5">
         <f>IF(COUNT(L34:L35)=2,(L34/L35-1)*100,"")</f>
         <v/>
       </c>
       <c r="N34" s="5" t="n">
-        <v>56.05</v>
+        <v>54.97</v>
       </c>
       <c r="O34" s="5">
         <f>IF(COUNT(N34:N35)=2,(N34/N35-1)*100,"")</f>
         <v/>
       </c>
       <c r="P34" s="5" t="n">
-        <v>56.63</v>
+        <v>56.46</v>
       </c>
       <c r="Q34" s="5">
         <f>IF(COUNT(P34:P35)=2,(P34/P35-1)*100,"")</f>
         <v/>
       </c>
       <c r="R34" s="5" t="n">
-        <v>75.76000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="S34" s="5">
         <f>IF(COUNT(R34:R35)=2,(R34/R35-1)*100,"")</f>
         <v/>
       </c>
       <c r="T34" s="5" t="n">
-        <v>111.02</v>
+        <v>109.46</v>
       </c>
       <c r="U34" s="5">
         <f>IF(COUNT(T34:T35)=2,(T34/T35-1)*100,"")</f>
         <v/>
       </c>
       <c r="V34" s="5" t="n">
-        <v>16.13</v>
+        <v>16.9</v>
       </c>
       <c r="W34" s="5">
         <f>IF(COUNT(V34:V35)=2,(V34/V35-1)*100,"")</f>
         <v/>
       </c>
       <c r="X34" s="5" t="n">
-        <v>3.5967</v>
+        <v>4.7737</v>
       </c>
       <c r="Y34" s="5">
-        <f>IF(AND(X34&gt;$Y$11,C34&lt;=$Y$12),C33,"")</f>
+        <f>IF(AND(X34&gt;$Y$12,C34&lt;=$Y$13),C33,"")</f>
         <v/>
       </c>
       <c r="Z34" s="5">
-        <f>IF(AND(K34&lt;$Z$11,M34&gt;$Z$12),C33,"")</f>
+        <f>IF(AND(K34&lt;$Z$12,M34&gt;$Z$13),C33,"")</f>
         <v/>
       </c>
       <c r="AA34" s="5">
-        <f>IF(AND(G34&gt;$AA$11,I34&lt;$AA$12,K34&gt;$AA$12),C33,"")</f>
+        <f>IF(AND(G34&gt;$AA$12,I34&lt;$AA$13,K34&gt;$AA$11),C33,"")</f>
         <v/>
       </c>
       <c r="AB34" s="5">
@@ -4494,15 +4392,15 @@
         <v/>
       </c>
       <c r="AC34" s="5">
-        <f>IF(AND(S34&gt;$AC$11,U34&lt;$AC$12),E33,"")</f>
+        <f>IF(AND(S34&gt;$AC$12,U34&lt;$AC$13),E33,"")</f>
         <v/>
       </c>
       <c r="AD34" s="5">
-        <f>IF(AND(O34&lt;=$AD$11,E34&lt;$AD$12),E33,"")</f>
+        <f>IF(AND(O34&lt;=$AD$12,E34&lt;$AD$13),E33,"")</f>
         <v/>
       </c>
       <c r="AE34" s="5">
-        <f>IF(AND(Q34&gt;$AE$11,S34&gt;$AE$12),E33,"")</f>
+        <f>IF(AND(Q34&gt;$AE$12,S34&gt;$AE$13),E33,"")</f>
         <v/>
       </c>
       <c r="AF34" s="5">
@@ -4513,99 +4411,99 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/07/07</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>165.32</v>
+        <v>159.4</v>
       </c>
       <c r="C35" s="5">
         <f>IF(COUNT(B35:B36)=2,(B35/B36-1)*100,"")</f>
         <v/>
       </c>
       <c r="D35" s="5" t="n">
-        <v>185.21</v>
+        <v>183.5</v>
       </c>
       <c r="E35" s="5">
         <f>IF(COUNT(D35:D36)=2,(D35/D36-1)*100,"")</f>
         <v/>
       </c>
       <c r="F35" s="5" t="n">
-        <v>67.56999999999999</v>
+        <v>65.72</v>
       </c>
       <c r="G35" s="5">
         <f>IF(COUNT(F35:F36)=2,(F35/F36-1)*100,"")</f>
         <v/>
       </c>
       <c r="H35" s="5" t="n">
-        <v>382.13</v>
+        <v>377.49</v>
       </c>
       <c r="I35" s="5">
         <f>IF(COUNT(H35:H36)=2,(H35/H36-1)*100,"")</f>
         <v/>
       </c>
       <c r="J35" s="5" t="n">
-        <v>79.4841</v>
+        <v>79.3746</v>
       </c>
       <c r="K35" s="5">
         <f>IF(COUNT(J35:J36)=2,(J35/J36-1)*100,"")</f>
         <v/>
       </c>
       <c r="L35" s="5" t="n">
-        <v>107.6997</v>
+        <v>107.3821</v>
       </c>
       <c r="M35" s="5">
         <f>IF(COUNT(L35:L36)=2,(L35/L36-1)*100,"")</f>
         <v/>
       </c>
       <c r="N35" s="5" t="n">
-        <v>56.14</v>
+        <v>56.05</v>
       </c>
       <c r="O35" s="5">
         <f>IF(COUNT(N35:N36)=2,(N35/N36-1)*100,"")</f>
         <v/>
       </c>
       <c r="P35" s="5" t="n">
-        <v>56.59</v>
+        <v>56.63</v>
       </c>
       <c r="Q35" s="5">
         <f>IF(COUNT(P35:P36)=2,(P35/P36-1)*100,"")</f>
         <v/>
       </c>
       <c r="R35" s="5" t="n">
-        <v>78.73999999999999</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="S35" s="5">
         <f>IF(COUNT(R35:R36)=2,(R35/R36-1)*100,"")</f>
         <v/>
       </c>
       <c r="T35" s="5" t="n">
-        <v>110.21</v>
+        <v>111.02</v>
       </c>
       <c r="U35" s="5">
         <f>IF(COUNT(T35:T36)=2,(T35/T36-1)*100,"")</f>
         <v/>
       </c>
       <c r="V35" s="5" t="n">
-        <v>15.57</v>
+        <v>16.13</v>
       </c>
       <c r="W35" s="5">
         <f>IF(COUNT(V35:V36)=2,(V35/V36-1)*100,"")</f>
         <v/>
       </c>
       <c r="X35" s="5" t="n">
-        <v>-3.5913</v>
+        <v>3.5967</v>
       </c>
       <c r="Y35" s="5">
-        <f>IF(AND(X35&gt;$Y$11,C35&lt;=$Y$12),C34,"")</f>
+        <f>IF(AND(X35&gt;$Y$12,C35&lt;=$Y$13),C34,"")</f>
         <v/>
       </c>
       <c r="Z35" s="5">
-        <f>IF(AND(K35&lt;$Z$11,M35&gt;$Z$12),C34,"")</f>
+        <f>IF(AND(K35&lt;$Z$12,M35&gt;$Z$13),C34,"")</f>
         <v/>
       </c>
       <c r="AA35" s="5">
-        <f>IF(AND(G35&gt;$AA$11,I35&lt;$AA$12,K35&gt;$AA$12),C34,"")</f>
+        <f>IF(AND(G35&gt;$AA$12,I35&lt;$AA$13,K35&gt;$AA$11),C34,"")</f>
         <v/>
       </c>
       <c r="AB35" s="5">
@@ -4613,15 +4511,15 @@
         <v/>
       </c>
       <c r="AC35" s="5">
-        <f>IF(AND(S35&gt;$AC$11,U35&lt;$AC$12),E34,"")</f>
+        <f>IF(AND(S35&gt;$AC$12,U35&lt;$AC$13),E34,"")</f>
         <v/>
       </c>
       <c r="AD35" s="5">
-        <f>IF(AND(O35&lt;=$AD$11,E35&lt;$AD$12),E34,"")</f>
+        <f>IF(AND(O35&lt;=$AD$12,E35&lt;$AD$13),E34,"")</f>
         <v/>
       </c>
       <c r="AE35" s="5">
-        <f>IF(AND(Q35&gt;$AE$11,S35&gt;$AE$12),E34,"")</f>
+        <f>IF(AND(Q35&gt;$AE$12,S35&gt;$AE$13),E34,"")</f>
         <v/>
       </c>
       <c r="AF35" s="5">
@@ -4632,99 +4530,99 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>2026/07/02</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>161.26</v>
+        <v>165.32</v>
       </c>
       <c r="C36" s="5">
         <f>IF(COUNT(B36:B37)=2,(B36/B37-1)*100,"")</f>
         <v/>
       </c>
       <c r="D36" s="5" t="n">
-        <v>182.53</v>
+        <v>185.21</v>
       </c>
       <c r="E36" s="5">
         <f>IF(COUNT(D36:D37)=2,(D36/D37-1)*100,"")</f>
         <v/>
       </c>
       <c r="F36" s="5" t="n">
-        <v>65.7</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="G36" s="5">
         <f>IF(COUNT(F36:F37)=2,(F36/F37-1)*100,"")</f>
         <v/>
       </c>
       <c r="H36" s="5" t="n">
-        <v>378.13</v>
+        <v>382.13</v>
       </c>
       <c r="I36" s="5">
         <f>IF(COUNT(H36:H37)=2,(H36/H37-1)*100,"")</f>
         <v/>
       </c>
       <c r="J36" s="5" t="n">
-        <v>79.3249</v>
+        <v>79.4841</v>
       </c>
       <c r="K36" s="5">
         <f>IF(COUNT(J36:J37)=2,(J36/J37-1)*100,"")</f>
         <v/>
       </c>
       <c r="L36" s="5" t="n">
-        <v>107.5409</v>
+        <v>107.6997</v>
       </c>
       <c r="M36" s="5">
         <f>IF(COUNT(L36:L37)=2,(L36/L37-1)*100,"")</f>
         <v/>
       </c>
       <c r="N36" s="5" t="n">
-        <v>55.62</v>
+        <v>56.14</v>
       </c>
       <c r="O36" s="5">
         <f>IF(COUNT(N36:N37)=2,(N36/N37-1)*100,"")</f>
         <v/>
       </c>
       <c r="P36" s="5" t="n">
-        <v>56.95</v>
+        <v>56.59</v>
       </c>
       <c r="Q36" s="5">
         <f>IF(COUNT(P36:P37)=2,(P36/P37-1)*100,"")</f>
         <v/>
       </c>
       <c r="R36" s="5" t="n">
-        <v>78.43000000000001</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="S36" s="5">
         <f>IF(COUNT(R36:R37)=2,(R36/R37-1)*100,"")</f>
         <v/>
       </c>
       <c r="T36" s="5" t="n">
-        <v>109.6</v>
+        <v>110.21</v>
       </c>
       <c r="U36" s="5">
         <f>IF(COUNT(T36:T37)=2,(T36/T37-1)*100,"")</f>
         <v/>
       </c>
       <c r="V36" s="5" t="n">
-        <v>16.15</v>
+        <v>15.57</v>
       </c>
       <c r="W36" s="5">
         <f>IF(COUNT(V36:V37)=2,(V36/V37-1)*100,"")</f>
         <v/>
       </c>
       <c r="X36" s="5" t="n">
-        <v>-2.6522</v>
+        <v>-3.5913</v>
       </c>
       <c r="Y36" s="5">
-        <f>IF(AND(X36&gt;$Y$11,C36&lt;=$Y$12),C35,"")</f>
+        <f>IF(AND(X36&gt;$Y$12,C36&lt;=$Y$13),C35,"")</f>
         <v/>
       </c>
       <c r="Z36" s="5">
-        <f>IF(AND(K36&lt;$Z$11,M36&gt;$Z$12),C35,"")</f>
+        <f>IF(AND(K36&lt;$Z$12,M36&gt;$Z$13),C35,"")</f>
         <v/>
       </c>
       <c r="AA36" s="5">
-        <f>IF(AND(G36&gt;$AA$11,I36&lt;$AA$12,K36&gt;$AA$12),C35,"")</f>
+        <f>IF(AND(G36&gt;$AA$12,I36&lt;$AA$13,K36&gt;$AA$11),C35,"")</f>
         <v/>
       </c>
       <c r="AB36" s="5">
@@ -4732,15 +4630,15 @@
         <v/>
       </c>
       <c r="AC36" s="5">
-        <f>IF(AND(S36&gt;$AC$11,U36&lt;$AC$12),E35,"")</f>
+        <f>IF(AND(S36&gt;$AC$12,U36&lt;$AC$13),E35,"")</f>
         <v/>
       </c>
       <c r="AD36" s="5">
-        <f>IF(AND(O36&lt;=$AD$11,E36&lt;$AD$12),E35,"")</f>
+        <f>IF(AND(O36&lt;=$AD$12,E36&lt;$AD$13),E35,"")</f>
         <v/>
       </c>
       <c r="AE36" s="5">
-        <f>IF(AND(Q36&gt;$AE$11,S36&gt;$AE$12),E35,"")</f>
+        <f>IF(AND(Q36&gt;$AE$12,S36&gt;$AE$13),E35,"")</f>
         <v/>
       </c>
       <c r="AF36" s="5">
@@ -4751,99 +4649,99 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026/07/01</t>
+          <t>2026/07/02</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>166.74</v>
+        <v>161.26</v>
       </c>
       <c r="C37" s="5">
         <f>IF(COUNT(B37:B38)=2,(B37/B38-1)*100,"")</f>
         <v/>
       </c>
       <c r="D37" s="5" t="n">
-        <v>182.68</v>
+        <v>182.53</v>
       </c>
       <c r="E37" s="5">
         <f>IF(COUNT(D37:D38)=2,(D37/D38-1)*100,"")</f>
         <v/>
       </c>
       <c r="F37" s="5" t="n">
-        <v>66.48</v>
+        <v>65.7</v>
       </c>
       <c r="G37" s="5">
         <f>IF(COUNT(F37:F38)=2,(F37/F38-1)*100,"")</f>
         <v/>
       </c>
       <c r="H37" s="5" t="n">
-        <v>370.6</v>
+        <v>378.13</v>
       </c>
       <c r="I37" s="5">
         <f>IF(COUNT(H37:H38)=2,(H37/H38-1)*100,"")</f>
         <v/>
       </c>
       <c r="J37" s="5" t="n">
-        <v>79.2055</v>
+        <v>79.3249</v>
       </c>
       <c r="K37" s="5">
         <f>IF(COUNT(J37:J38)=2,(J37/J38-1)*100,"")</f>
         <v/>
       </c>
       <c r="L37" s="5" t="n">
-        <v>107.3821</v>
+        <v>107.5409</v>
       </c>
       <c r="M37" s="5">
         <f>IF(COUNT(L37:L38)=2,(L37/L38-1)*100,"")</f>
         <v/>
       </c>
       <c r="N37" s="5" t="n">
-        <v>54.78</v>
+        <v>55.62</v>
       </c>
       <c r="O37" s="5">
         <f>IF(COUNT(N37:N38)=2,(N37/N38-1)*100,"")</f>
         <v/>
       </c>
       <c r="P37" s="5" t="n">
-        <v>56.43</v>
+        <v>56.95</v>
       </c>
       <c r="Q37" s="5">
         <f>IF(COUNT(P37:P38)=2,(P37/P38-1)*100,"")</f>
         <v/>
       </c>
       <c r="R37" s="5" t="n">
-        <v>75.06999999999999</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="S37" s="5">
         <f>IF(COUNT(R37:R38)=2,(R37/R38-1)*100,"")</f>
         <v/>
       </c>
       <c r="T37" s="5" t="n">
-        <v>109.74</v>
+        <v>109.6</v>
       </c>
       <c r="U37" s="5">
         <f>IF(COUNT(T37:T38)=2,(T37/T38-1)*100,"")</f>
         <v/>
       </c>
       <c r="V37" s="5" t="n">
-        <v>16.59</v>
+        <v>16.15</v>
       </c>
       <c r="W37" s="5">
         <f>IF(COUNT(V37:V38)=2,(V37/V38-1)*100,"")</f>
         <v/>
       </c>
       <c r="X37" s="5" t="n">
-        <v>0.8511</v>
+        <v>-2.6522</v>
       </c>
       <c r="Y37" s="5">
-        <f>IF(AND(X37&gt;$Y$11,C37&lt;=$Y$12),C36,"")</f>
+        <f>IF(AND(X37&gt;$Y$12,C37&lt;=$Y$13),C36,"")</f>
         <v/>
       </c>
       <c r="Z37" s="5">
-        <f>IF(AND(K37&lt;$Z$11,M37&gt;$Z$12),C36,"")</f>
+        <f>IF(AND(K37&lt;$Z$12,M37&gt;$Z$13),C36,"")</f>
         <v/>
       </c>
       <c r="AA37" s="5">
-        <f>IF(AND(G37&gt;$AA$11,I37&lt;$AA$12,K37&gt;$AA$12),C36,"")</f>
+        <f>IF(AND(G37&gt;$AA$12,I37&lt;$AA$13,K37&gt;$AA$11),C36,"")</f>
         <v/>
       </c>
       <c r="AB37" s="5">
@@ -4851,15 +4749,15 @@
         <v/>
       </c>
       <c r="AC37" s="5">
-        <f>IF(AND(S37&gt;$AC$11,U37&lt;$AC$12),E36,"")</f>
+        <f>IF(AND(S37&gt;$AC$12,U37&lt;$AC$13),E36,"")</f>
         <v/>
       </c>
       <c r="AD37" s="5">
-        <f>IF(AND(O37&lt;=$AD$11,E37&lt;$AD$12),E36,"")</f>
+        <f>IF(AND(O37&lt;=$AD$12,E37&lt;$AD$13),E36,"")</f>
         <v/>
       </c>
       <c r="AE37" s="5">
-        <f>IF(AND(Q37&gt;$AE$11,S37&gt;$AE$12),E36,"")</f>
+        <f>IF(AND(Q37&gt;$AE$12,S37&gt;$AE$13),E36,"")</f>
         <v/>
       </c>
       <c r="AF37" s="5">
@@ -4870,99 +4768,99 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>2026/06/30</t>
+          <t>2026/07/01</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>172.04</v>
+        <v>166.74</v>
       </c>
       <c r="C38" s="5">
         <f>IF(COUNT(B38:B39)=2,(B38/B39-1)*100,"")</f>
         <v/>
       </c>
       <c r="D38" s="5" t="n">
-        <v>183.4</v>
+        <v>182.68</v>
       </c>
       <c r="E38" s="5">
         <f>IF(COUNT(D38:D39)=2,(D38/D39-1)*100,"")</f>
         <v/>
       </c>
       <c r="F38" s="5" t="n">
-        <v>68.41</v>
+        <v>66.48</v>
       </c>
       <c r="G38" s="5">
         <f>IF(COUNT(F38:F39)=2,(F38/F39-1)*100,"")</f>
         <v/>
       </c>
       <c r="H38" s="5" t="n">
-        <v>368.38</v>
+        <v>370.6</v>
       </c>
       <c r="I38" s="5">
         <f>IF(COUNT(H38:H39)=2,(H38/H39-1)*100,"")</f>
         <v/>
       </c>
       <c r="J38" s="5" t="n">
-        <v>79.21639999999999</v>
+        <v>79.2055</v>
       </c>
       <c r="K38" s="5">
         <f>IF(COUNT(J38:J39)=2,(J38/J39-1)*100,"")</f>
         <v/>
       </c>
       <c r="L38" s="5" t="n">
-        <v>107.5826</v>
+        <v>107.3821</v>
       </c>
       <c r="M38" s="5">
         <f>IF(COUNT(L38:L39)=2,(L38/L39-1)*100,"")</f>
         <v/>
       </c>
       <c r="N38" s="5" t="n">
-        <v>53.61</v>
+        <v>54.78</v>
       </c>
       <c r="O38" s="5">
         <f>IF(COUNT(N38:N39)=2,(N38/N39-1)*100,"")</f>
         <v/>
       </c>
       <c r="P38" s="5" t="n">
-        <v>56.44</v>
+        <v>56.43</v>
       </c>
       <c r="Q38" s="5">
         <f>IF(COUNT(P38:P39)=2,(P38/P39-1)*100,"")</f>
         <v/>
       </c>
       <c r="R38" s="5" t="n">
-        <v>75.45</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="S38" s="5">
         <f>IF(COUNT(R38:R39)=2,(R38/R39-1)*100,"")</f>
         <v/>
       </c>
       <c r="T38" s="5" t="n">
-        <v>107.13</v>
+        <v>109.74</v>
       </c>
       <c r="U38" s="5">
         <f>IF(COUNT(T38:T39)=2,(T38/T39-1)*100,"")</f>
         <v/>
       </c>
       <c r="V38" s="5" t="n">
-        <v>16.45</v>
+        <v>16.59</v>
       </c>
       <c r="W38" s="5">
         <f>IF(COUNT(V38:V39)=2,(V38/V39-1)*100,"")</f>
         <v/>
       </c>
       <c r="X38" s="5" t="n">
-        <v>-6.7989</v>
+        <v>0.8511</v>
       </c>
       <c r="Y38" s="5">
-        <f>IF(AND(X38&gt;$Y$11,C38&lt;=$Y$12),C37,"")</f>
+        <f>IF(AND(X38&gt;$Y$12,C38&lt;=$Y$13),C37,"")</f>
         <v/>
       </c>
       <c r="Z38" s="5">
-        <f>IF(AND(K38&lt;$Z$11,M38&gt;$Z$12),C37,"")</f>
+        <f>IF(AND(K38&lt;$Z$12,M38&gt;$Z$13),C37,"")</f>
         <v/>
       </c>
       <c r="AA38" s="5">
-        <f>IF(AND(G38&gt;$AA$11,I38&lt;$AA$12,K38&gt;$AA$12),C37,"")</f>
+        <f>IF(AND(G38&gt;$AA$12,I38&lt;$AA$13,K38&gt;$AA$11),C37,"")</f>
         <v/>
       </c>
       <c r="AB38" s="5">
@@ -4970,15 +4868,15 @@
         <v/>
       </c>
       <c r="AC38" s="5">
-        <f>IF(AND(S38&gt;$AC$11,U38&lt;$AC$12),E37,"")</f>
+        <f>IF(AND(S38&gt;$AC$12,U38&lt;$AC$13),E37,"")</f>
         <v/>
       </c>
       <c r="AD38" s="5">
-        <f>IF(AND(O38&lt;=$AD$11,E38&lt;$AD$12),E37,"")</f>
+        <f>IF(AND(O38&lt;=$AD$12,E38&lt;$AD$13),E37,"")</f>
         <v/>
       </c>
       <c r="AE38" s="5">
-        <f>IF(AND(Q38&gt;$AE$11,S38&gt;$AE$12),E37,"")</f>
+        <f>IF(AND(Q38&gt;$AE$12,S38&gt;$AE$13),E37,"")</f>
         <v/>
       </c>
       <c r="AF38" s="5">
@@ -4989,99 +4887,99 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/06/30</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>166.43</v>
+        <v>172.04</v>
       </c>
       <c r="C39" s="5">
         <f>IF(COUNT(B39:B40)=2,(B39/B40-1)*100,"")</f>
         <v/>
       </c>
       <c r="D39" s="5" t="n">
-        <v>180.59</v>
+        <v>183.4</v>
       </c>
       <c r="E39" s="5">
         <f>IF(COUNT(D39:D40)=2,(D39/D40-1)*100,"")</f>
         <v/>
       </c>
       <c r="F39" s="5" t="n">
-        <v>67.43000000000001</v>
+        <v>68.41</v>
       </c>
       <c r="G39" s="5">
         <f>IF(COUNT(F39:F40)=2,(F39/F40-1)*100,"")</f>
         <v/>
       </c>
       <c r="H39" s="5" t="n">
-        <v>368.58</v>
+        <v>368.38</v>
       </c>
       <c r="I39" s="5">
         <f>IF(COUNT(H39:H40)=2,(H39/H40-1)*100,"")</f>
         <v/>
       </c>
       <c r="J39" s="5" t="n">
-        <v>79.256</v>
+        <v>79.21639999999999</v>
       </c>
       <c r="K39" s="5">
         <f>IF(COUNT(J39:J40)=2,(J39/J40-1)*100,"")</f>
         <v/>
       </c>
       <c r="L39" s="5" t="n">
-        <v>108.0447</v>
+        <v>107.5826</v>
       </c>
       <c r="M39" s="5">
         <f>IF(COUNT(L39:L40)=2,(L39/L40-1)*100,"")</f>
         <v/>
       </c>
       <c r="N39" s="5" t="n">
-        <v>53.72</v>
+        <v>53.61</v>
       </c>
       <c r="O39" s="5">
         <f>IF(COUNT(N39:N40)=2,(N39/N40-1)*100,"")</f>
         <v/>
       </c>
       <c r="P39" s="5" t="n">
-        <v>56.66</v>
+        <v>56.44</v>
       </c>
       <c r="Q39" s="5">
         <f>IF(COUNT(P39:P40)=2,(P39/P40-1)*100,"")</f>
         <v/>
       </c>
       <c r="R39" s="5" t="n">
-        <v>75.68000000000001</v>
+        <v>75.45</v>
       </c>
       <c r="S39" s="5">
         <f>IF(COUNT(R39:R40)=2,(R39/R40-1)*100,"")</f>
         <v/>
       </c>
       <c r="T39" s="5" t="n">
-        <v>107.88</v>
+        <v>107.13</v>
       </c>
       <c r="U39" s="5">
         <f>IF(COUNT(T39:T40)=2,(T39/T40-1)*100,"")</f>
         <v/>
       </c>
       <c r="V39" s="5" t="n">
-        <v>17.65</v>
+        <v>16.45</v>
       </c>
       <c r="W39" s="5">
         <f>IF(COUNT(V39:V40)=2,(V39/V40-1)*100,"")</f>
         <v/>
       </c>
       <c r="X39" s="5" t="n">
-        <v>-4.1282</v>
+        <v>-6.7989</v>
       </c>
       <c r="Y39" s="5">
-        <f>IF(AND(X39&gt;$Y$11,C39&lt;=$Y$12),C38,"")</f>
+        <f>IF(AND(X39&gt;$Y$12,C39&lt;=$Y$13),C38,"")</f>
         <v/>
       </c>
       <c r="Z39" s="5">
-        <f>IF(AND(K39&lt;$Z$11,M39&gt;$Z$12),C38,"")</f>
+        <f>IF(AND(K39&lt;$Z$12,M39&gt;$Z$13),C38,"")</f>
         <v/>
       </c>
       <c r="AA39" s="5">
-        <f>IF(AND(G39&gt;$AA$11,I39&lt;$AA$12,K39&gt;$AA$12),C38,"")</f>
+        <f>IF(AND(G39&gt;$AA$12,I39&lt;$AA$13,K39&gt;$AA$11),C38,"")</f>
         <v/>
       </c>
       <c r="AB39" s="5">
@@ -5089,15 +4987,15 @@
         <v/>
       </c>
       <c r="AC39" s="5">
-        <f>IF(AND(S39&gt;$AC$11,U39&lt;$AC$12),E38,"")</f>
+        <f>IF(AND(S39&gt;$AC$12,U39&lt;$AC$13),E38,"")</f>
         <v/>
       </c>
       <c r="AD39" s="5">
-        <f>IF(AND(O39&lt;=$AD$11,E39&lt;$AD$12),E38,"")</f>
+        <f>IF(AND(O39&lt;=$AD$12,E39&lt;$AD$13),E38,"")</f>
         <v/>
       </c>
       <c r="AE39" s="5">
-        <f>IF(AND(Q39&gt;$AE$11,S39&gt;$AE$12),E38,"")</f>
+        <f>IF(AND(Q39&gt;$AE$12,S39&gt;$AE$13),E38,"")</f>
         <v/>
       </c>
       <c r="AF39" s="5">
@@ -5108,99 +5006,99 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>2026/06/26</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>159.19</v>
+        <v>166.43</v>
       </c>
       <c r="C40" s="5">
         <f>IF(COUNT(B40:B41)=2,(B40/B41-1)*100,"")</f>
         <v/>
       </c>
       <c r="D40" s="5" t="n">
-        <v>176.27</v>
+        <v>180.59</v>
       </c>
       <c r="E40" s="5">
         <f>IF(COUNT(D40:D41)=2,(D40/D41-1)*100,"")</f>
         <v/>
       </c>
       <c r="F40" s="5" t="n">
-        <v>67.19</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="G40" s="5">
         <f>IF(COUNT(F40:F41)=2,(F40/F41-1)*100,"")</f>
         <v/>
       </c>
       <c r="H40" s="5" t="n">
-        <v>373.63</v>
+        <v>368.58</v>
       </c>
       <c r="I40" s="5">
         <f>IF(COUNT(H40:H41)=2,(H40/H41-1)*100,"")</f>
         <v/>
       </c>
       <c r="J40" s="5" t="n">
-        <v>79.07769999999999</v>
+        <v>79.256</v>
       </c>
       <c r="K40" s="5">
         <f>IF(COUNT(J40:J41)=2,(J40/J41-1)*100,"")</f>
         <v/>
       </c>
       <c r="L40" s="5" t="n">
-        <v>107.848</v>
+        <v>108.0447</v>
       </c>
       <c r="M40" s="5">
         <f>IF(COUNT(L40:L41)=2,(L40/L41-1)*100,"")</f>
         <v/>
       </c>
       <c r="N40" s="5" t="n">
-        <v>53.57</v>
+        <v>53.72</v>
       </c>
       <c r="O40" s="5">
         <f>IF(COUNT(N40:N41)=2,(N40/N41-1)*100,"")</f>
         <v/>
       </c>
       <c r="P40" s="5" t="n">
-        <v>56.71</v>
+        <v>56.66</v>
       </c>
       <c r="Q40" s="5">
         <f>IF(COUNT(P40:P41)=2,(P40/P41-1)*100,"")</f>
         <v/>
       </c>
       <c r="R40" s="5" t="n">
-        <v>77</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="S40" s="5">
         <f>IF(COUNT(R40:R41)=2,(R40/R41-1)*100,"")</f>
         <v/>
       </c>
       <c r="T40" s="5" t="n">
-        <v>106.18</v>
+        <v>107.88</v>
       </c>
       <c r="U40" s="5">
         <f>IF(COUNT(T40:T41)=2,(T40/T41-1)*100,"")</f>
         <v/>
       </c>
       <c r="V40" s="5" t="n">
-        <v>18.41</v>
+        <v>17.65</v>
       </c>
       <c r="W40" s="5">
         <f>IF(COUNT(V40:V41)=2,(V40/V41-1)*100,"")</f>
         <v/>
       </c>
       <c r="X40" s="5" t="n">
-        <v>-2.541</v>
+        <v>-4.1282</v>
       </c>
       <c r="Y40" s="5">
-        <f>IF(AND(X40&gt;$Y$11,C40&lt;=$Y$12),C39,"")</f>
+        <f>IF(AND(X40&gt;$Y$12,C40&lt;=$Y$13),C39,"")</f>
         <v/>
       </c>
       <c r="Z40" s="5">
-        <f>IF(AND(K40&lt;$Z$11,M40&gt;$Z$12),C39,"")</f>
+        <f>IF(AND(K40&lt;$Z$12,M40&gt;$Z$13),C39,"")</f>
         <v/>
       </c>
       <c r="AA40" s="5">
-        <f>IF(AND(G40&gt;$AA$11,I40&lt;$AA$12,K40&gt;$AA$12),C39,"")</f>
+        <f>IF(AND(G40&gt;$AA$12,I40&lt;$AA$13,K40&gt;$AA$11),C39,"")</f>
         <v/>
       </c>
       <c r="AB40" s="5">
@@ -5208,15 +5106,15 @@
         <v/>
       </c>
       <c r="AC40" s="5">
-        <f>IF(AND(S40&gt;$AC$11,U40&lt;$AC$12),E39,"")</f>
+        <f>IF(AND(S40&gt;$AC$12,U40&lt;$AC$13),E39,"")</f>
         <v/>
       </c>
       <c r="AD40" s="5">
-        <f>IF(AND(O40&lt;=$AD$11,E40&lt;$AD$12),E39,"")</f>
+        <f>IF(AND(O40&lt;=$AD$12,E40&lt;$AD$13),E39,"")</f>
         <v/>
       </c>
       <c r="AE40" s="5">
-        <f>IF(AND(Q40&gt;$AE$11,S40&gt;$AE$12),E39,"")</f>
+        <f>IF(AND(Q40&gt;$AE$12,S40&gt;$AE$13),E39,"")</f>
         <v/>
       </c>
       <c r="AF40" s="5">
@@ -5227,99 +5125,99 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/06/26</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>162.93</v>
+        <v>159.19</v>
       </c>
       <c r="C41" s="5">
         <f>IF(COUNT(B41:B42)=2,(B41/B42-1)*100,"")</f>
         <v/>
       </c>
       <c r="D41" s="5" t="n">
-        <v>176.82</v>
+        <v>176.27</v>
       </c>
       <c r="E41" s="5">
         <f>IF(COUNT(D41:D42)=2,(D41/D42-1)*100,"")</f>
         <v/>
       </c>
       <c r="F41" s="5" t="n">
-        <v>67.95999999999999</v>
+        <v>67.19</v>
       </c>
       <c r="G41" s="5">
         <f>IF(COUNT(F41:F42)=2,(F41/F42-1)*100,"")</f>
         <v/>
       </c>
       <c r="H41" s="5" t="n">
-        <v>369.46</v>
+        <v>373.63</v>
       </c>
       <c r="I41" s="5">
         <f>IF(COUNT(H41:H42)=2,(H41/H42-1)*100,"")</f>
         <v/>
       </c>
       <c r="J41" s="5" t="n">
-        <v>79.12730000000001</v>
+        <v>79.07769999999999</v>
       </c>
       <c r="K41" s="5">
         <f>IF(COUNT(J41:J42)=2,(J41/J42-1)*100,"")</f>
         <v/>
       </c>
       <c r="L41" s="5" t="n">
-        <v>107.6514</v>
+        <v>107.848</v>
       </c>
       <c r="M41" s="5">
         <f>IF(COUNT(L41:L42)=2,(L41/L42-1)*100,"")</f>
         <v/>
       </c>
       <c r="N41" s="5" t="n">
-        <v>53.45</v>
+        <v>53.57</v>
       </c>
       <c r="O41" s="5">
         <f>IF(COUNT(N41:N42)=2,(N41/N42-1)*100,"")</f>
         <v/>
       </c>
       <c r="P41" s="5" t="n">
-        <v>56.69</v>
+        <v>56.71</v>
       </c>
       <c r="Q41" s="5">
         <f>IF(COUNT(P41:P42)=2,(P41/P42-1)*100,"")</f>
         <v/>
       </c>
       <c r="R41" s="5" t="n">
-        <v>75.67</v>
+        <v>77</v>
       </c>
       <c r="S41" s="5">
         <f>IF(COUNT(R41:R42)=2,(R41/R42-1)*100,"")</f>
         <v/>
       </c>
       <c r="T41" s="5" t="n">
-        <v>105.58</v>
+        <v>106.18</v>
       </c>
       <c r="U41" s="5">
         <f>IF(COUNT(T41:T42)=2,(T41/T42-1)*100,"")</f>
         <v/>
       </c>
       <c r="V41" s="5" t="n">
-        <v>18.89</v>
+        <v>18.41</v>
       </c>
       <c r="W41" s="5">
         <f>IF(COUNT(V41:V42)=2,(V41/V42-1)*100,"")</f>
         <v/>
       </c>
       <c r="X41" s="5" t="n">
-        <v>1.3956</v>
+        <v>-2.541</v>
       </c>
       <c r="Y41" s="5">
-        <f>IF(AND(X41&gt;$Y$11,C41&lt;=$Y$12),C40,"")</f>
+        <f>IF(AND(X41&gt;$Y$12,C41&lt;=$Y$13),C40,"")</f>
         <v/>
       </c>
       <c r="Z41" s="5">
-        <f>IF(AND(K41&lt;$Z$11,M41&gt;$Z$12),C40,"")</f>
+        <f>IF(AND(K41&lt;$Z$12,M41&gt;$Z$13),C40,"")</f>
         <v/>
       </c>
       <c r="AA41" s="5">
-        <f>IF(AND(G41&gt;$AA$11,I41&lt;$AA$12,K41&gt;$AA$12),C40,"")</f>
+        <f>IF(AND(G41&gt;$AA$12,I41&lt;$AA$13,K41&gt;$AA$11),C40,"")</f>
         <v/>
       </c>
       <c r="AB41" s="5">
@@ -5327,15 +5225,15 @@
         <v/>
       </c>
       <c r="AC41" s="5">
-        <f>IF(AND(S41&gt;$AC$11,U41&lt;$AC$12),E40,"")</f>
+        <f>IF(AND(S41&gt;$AC$12,U41&lt;$AC$13),E40,"")</f>
         <v/>
       </c>
       <c r="AD41" s="5">
-        <f>IF(AND(O41&lt;=$AD$11,E41&lt;$AD$12),E40,"")</f>
+        <f>IF(AND(O41&lt;=$AD$12,E41&lt;$AD$13),E40,"")</f>
         <v/>
       </c>
       <c r="AE41" s="5">
-        <f>IF(AND(Q41&gt;$AE$11,S41&gt;$AE$12),E40,"")</f>
+        <f>IF(AND(Q41&gt;$AE$12,S41&gt;$AE$13),E40,"")</f>
         <v/>
       </c>
       <c r="AF41" s="5">
@@ -5346,11 +5244,11 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>2026/06/24</t>
+          <t>2026/06/25</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>160.52</v>
+        <v>162.93</v>
       </c>
       <c r="C42" s="5">
         <f>IF(COUNT(B42:B43)=2,(B42/B43-1)*100,"")</f>
@@ -5364,81 +5262,81 @@
         <v/>
       </c>
       <c r="F42" s="5" t="n">
-        <v>67.25</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="G42" s="5">
         <f>IF(COUNT(F42:F43)=2,(F42/F43-1)*100,"")</f>
         <v/>
       </c>
       <c r="H42" s="5" t="n">
-        <v>365.92</v>
+        <v>369.46</v>
       </c>
       <c r="I42" s="5">
         <f>IF(COUNT(H42:H43)=2,(H42/H43-1)*100,"")</f>
         <v/>
       </c>
       <c r="J42" s="5" t="n">
-        <v>79.0975</v>
+        <v>79.12730000000001</v>
       </c>
       <c r="K42" s="5">
         <f>IF(COUNT(J42:J43)=2,(J42/J43-1)*100,"")</f>
         <v/>
       </c>
       <c r="L42" s="5" t="n">
-        <v>107.4744</v>
+        <v>107.6514</v>
       </c>
       <c r="M42" s="5">
         <f>IF(COUNT(L42:L43)=2,(L42/L43-1)*100,"")</f>
         <v/>
       </c>
       <c r="N42" s="5" t="n">
-        <v>53.72</v>
+        <v>53.45</v>
       </c>
       <c r="O42" s="5">
         <f>IF(COUNT(N42:N43)=2,(N42/N43-1)*100,"")</f>
         <v/>
       </c>
       <c r="P42" s="5" t="n">
-        <v>56.7</v>
+        <v>56.69</v>
       </c>
       <c r="Q42" s="5">
         <f>IF(COUNT(P42:P43)=2,(P42/P43-1)*100,"")</f>
         <v/>
       </c>
       <c r="R42" s="5" t="n">
-        <v>74.59</v>
+        <v>75.67</v>
       </c>
       <c r="S42" s="5">
         <f>IF(COUNT(R42:R43)=2,(R42/R43-1)*100,"")</f>
         <v/>
       </c>
       <c r="T42" s="5" t="n">
-        <v>106.54</v>
+        <v>105.58</v>
       </c>
       <c r="U42" s="5">
         <f>IF(COUNT(T42:T43)=2,(T42/T43-1)*100,"")</f>
         <v/>
       </c>
       <c r="V42" s="5" t="n">
-        <v>18.63</v>
+        <v>18.89</v>
       </c>
       <c r="W42" s="5">
         <f>IF(COUNT(V42:V43)=2,(V42/V43-1)*100,"")</f>
         <v/>
       </c>
       <c r="X42" s="5" t="n">
-        <v>-4.4125</v>
+        <v>1.3956</v>
       </c>
       <c r="Y42" s="5">
-        <f>IF(AND(X42&gt;$Y$11,C42&lt;=$Y$12),C41,"")</f>
+        <f>IF(AND(X42&gt;$Y$12,C42&lt;=$Y$13),C41,"")</f>
         <v/>
       </c>
       <c r="Z42" s="5">
-        <f>IF(AND(K42&lt;$Z$11,M42&gt;$Z$12),C41,"")</f>
+        <f>IF(AND(K42&lt;$Z$12,M42&gt;$Z$13),C41,"")</f>
         <v/>
       </c>
       <c r="AA42" s="5">
-        <f>IF(AND(G42&gt;$AA$11,I42&lt;$AA$12,K42&gt;$AA$12),C41,"")</f>
+        <f>IF(AND(G42&gt;$AA$12,I42&lt;$AA$13,K42&gt;$AA$11),C41,"")</f>
         <v/>
       </c>
       <c r="AB42" s="5">
@@ -5446,15 +5344,15 @@
         <v/>
       </c>
       <c r="AC42" s="5">
-        <f>IF(AND(S42&gt;$AC$11,U42&lt;$AC$12),E41,"")</f>
+        <f>IF(AND(S42&gt;$AC$12,U42&lt;$AC$13),E41,"")</f>
         <v/>
       </c>
       <c r="AD42" s="5">
-        <f>IF(AND(O42&lt;=$AD$11,E42&lt;$AD$12),E41,"")</f>
+        <f>IF(AND(O42&lt;=$AD$12,E42&lt;$AD$13),E41,"")</f>
         <v/>
       </c>
       <c r="AE42" s="5">
-        <f>IF(AND(Q42&gt;$AE$11,S42&gt;$AE$12),E41,"")</f>
+        <f>IF(AND(Q42&gt;$AE$12,S42&gt;$AE$13),E41,"")</f>
         <v/>
       </c>
       <c r="AF42" s="5">
@@ -5465,99 +5363,99 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026/06/23</t>
+          <t>2026/06/24</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>161.96</v>
+        <v>160.52</v>
       </c>
       <c r="C43" s="5">
         <f>IF(COUNT(B43:B44)=2,(B43/B44-1)*100,"")</f>
         <v/>
       </c>
       <c r="D43" s="5" t="n">
-        <v>177.18</v>
+        <v>176.82</v>
       </c>
       <c r="E43" s="5">
         <f>IF(COUNT(D43:D44)=2,(D43/D44-1)*100,"")</f>
         <v/>
       </c>
       <c r="F43" s="5" t="n">
-        <v>67.17</v>
+        <v>67.25</v>
       </c>
       <c r="G43" s="5">
         <f>IF(COUNT(F43:F44)=2,(F43/F44-1)*100,"")</f>
         <v/>
       </c>
       <c r="H43" s="5" t="n">
-        <v>377.32</v>
+        <v>365.92</v>
       </c>
       <c r="I43" s="5">
         <f>IF(COUNT(H43:H44)=2,(H43/H44-1)*100,"")</f>
         <v/>
       </c>
       <c r="J43" s="5" t="n">
-        <v>79.1174</v>
+        <v>79.0975</v>
       </c>
       <c r="K43" s="5">
         <f>IF(COUNT(J43:J44)=2,(J43/J44-1)*100,"")</f>
         <v/>
       </c>
       <c r="L43" s="5" t="n">
-        <v>107.0615</v>
+        <v>107.4744</v>
       </c>
       <c r="M43" s="5">
         <f>IF(COUNT(L43:L44)=2,(L43/L44-1)*100,"")</f>
         <v/>
       </c>
       <c r="N43" s="5" t="n">
-        <v>53.88</v>
+        <v>53.72</v>
       </c>
       <c r="O43" s="5">
         <f>IF(COUNT(N43:N44)=2,(N43/N44-1)*100,"")</f>
         <v/>
       </c>
       <c r="P43" s="5" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
       <c r="Q43" s="5">
         <f>IF(COUNT(P43:P44)=2,(P43/P44-1)*100,"")</f>
         <v/>
       </c>
       <c r="R43" s="5" t="n">
-        <v>77.66</v>
+        <v>74.59</v>
       </c>
       <c r="S43" s="5">
         <f>IF(COUNT(R43:R44)=2,(R43/R44-1)*100,"")</f>
         <v/>
       </c>
       <c r="T43" s="5" t="n">
-        <v>107.27</v>
+        <v>106.54</v>
       </c>
       <c r="U43" s="5">
         <f>IF(COUNT(T43:T44)=2,(T43/T44-1)*100,"")</f>
         <v/>
       </c>
       <c r="V43" s="5" t="n">
-        <v>19.49</v>
+        <v>18.63</v>
       </c>
       <c r="W43" s="5">
         <f>IF(COUNT(V43:V44)=2,(V43/V44-1)*100,"")</f>
         <v/>
       </c>
       <c r="X43" s="5" t="n">
-        <v>12.7894</v>
+        <v>-4.4125</v>
       </c>
       <c r="Y43" s="5">
-        <f>IF(AND(X43&gt;$Y$11,C43&lt;=$Y$12),C42,"")</f>
+        <f>IF(AND(X43&gt;$Y$12,C43&lt;=$Y$13),C42,"")</f>
         <v/>
       </c>
       <c r="Z43" s="5">
-        <f>IF(AND(K43&lt;$Z$11,M43&gt;$Z$12),C42,"")</f>
+        <f>IF(AND(K43&lt;$Z$12,M43&gt;$Z$13),C42,"")</f>
         <v/>
       </c>
       <c r="AA43" s="5">
-        <f>IF(AND(G43&gt;$AA$11,I43&lt;$AA$12,K43&gt;$AA$12),C42,"")</f>
+        <f>IF(AND(G43&gt;$AA$12,I43&lt;$AA$13,K43&gt;$AA$11),C42,"")</f>
         <v/>
       </c>
       <c r="AB43" s="5">
@@ -5565,15 +5463,15 @@
         <v/>
       </c>
       <c r="AC43" s="5">
-        <f>IF(AND(S43&gt;$AC$11,U43&lt;$AC$12),E42,"")</f>
+        <f>IF(AND(S43&gt;$AC$12,U43&lt;$AC$13),E42,"")</f>
         <v/>
       </c>
       <c r="AD43" s="5">
-        <f>IF(AND(O43&lt;=$AD$11,E43&lt;$AD$12),E42,"")</f>
+        <f>IF(AND(O43&lt;=$AD$12,E43&lt;$AD$13),E42,"")</f>
         <v/>
       </c>
       <c r="AE43" s="5">
-        <f>IF(AND(Q43&gt;$AE$11,S43&gt;$AE$12),E42,"")</f>
+        <f>IF(AND(Q43&gt;$AE$12,S43&gt;$AE$13),E42,"")</f>
         <v/>
       </c>
       <c r="AF43" s="5">
@@ -5584,99 +5482,99 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/06/23</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>173.38</v>
+        <v>161.96</v>
       </c>
       <c r="C44" s="5">
         <f>IF(COUNT(B44:B45)=2,(B44/B45-1)*100,"")</f>
         <v/>
       </c>
       <c r="D44" s="5" t="n">
-        <v>182.43</v>
+        <v>177.18</v>
       </c>
       <c r="E44" s="5">
         <f>IF(COUNT(D44:D45)=2,(D44/D45-1)*100,"")</f>
         <v/>
       </c>
       <c r="F44" s="5" t="n">
-        <v>71.20999999999999</v>
+        <v>67.17</v>
       </c>
       <c r="G44" s="5">
         <f>IF(COUNT(F44:F45)=2,(F44/F45-1)*100,"")</f>
         <v/>
       </c>
       <c r="H44" s="5" t="n">
-        <v>384.59</v>
+        <v>377.32</v>
       </c>
       <c r="I44" s="5">
         <f>IF(COUNT(H44:H45)=2,(H44/H45-1)*100,"")</f>
         <v/>
       </c>
       <c r="J44" s="5" t="n">
-        <v>79.1867</v>
+        <v>79.1174</v>
       </c>
       <c r="K44" s="5">
         <f>IF(COUNT(J44:J45)=2,(J44/J45-1)*100,"")</f>
         <v/>
       </c>
       <c r="L44" s="5" t="n">
-        <v>107.1009</v>
+        <v>107.0615</v>
       </c>
       <c r="M44" s="5">
         <f>IF(COUNT(L44:L45)=2,(L44/L45-1)*100,"")</f>
         <v/>
       </c>
       <c r="N44" s="5" t="n">
-        <v>53.7</v>
+        <v>53.88</v>
       </c>
       <c r="O44" s="5">
         <f>IF(COUNT(N44:N45)=2,(N44/N45-1)*100,"")</f>
         <v/>
       </c>
       <c r="P44" s="5" t="n">
-        <v>56.79</v>
+        <v>56.8</v>
       </c>
       <c r="Q44" s="5">
         <f>IF(COUNT(P44:P45)=2,(P44/P45-1)*100,"")</f>
         <v/>
       </c>
       <c r="R44" s="5" t="n">
-        <v>81.44</v>
+        <v>77.66</v>
       </c>
       <c r="S44" s="5">
         <f>IF(COUNT(R44:R45)=2,(R44/R45-1)*100,"")</f>
         <v/>
       </c>
       <c r="T44" s="5" t="n">
-        <v>106.86</v>
+        <v>107.27</v>
       </c>
       <c r="U44" s="5">
         <f>IF(COUNT(T44:T45)=2,(T44/T45-1)*100,"")</f>
         <v/>
       </c>
       <c r="V44" s="5" t="n">
-        <v>17.28</v>
+        <v>19.49</v>
       </c>
       <c r="W44" s="5">
         <f>IF(COUNT(V44:V45)=2,(V44/V45-1)*100,"")</f>
         <v/>
       </c>
       <c r="X44" s="5" t="n">
-        <v>5.3659</v>
+        <v>12.7894</v>
       </c>
       <c r="Y44" s="5">
-        <f>IF(AND(X44&gt;$Y$11,C44&lt;=$Y$12),C43,"")</f>
+        <f>IF(AND(X44&gt;$Y$12,C44&lt;=$Y$13),C43,"")</f>
         <v/>
       </c>
       <c r="Z44" s="5">
-        <f>IF(AND(K44&lt;$Z$11,M44&gt;$Z$12),C43,"")</f>
+        <f>IF(AND(K44&lt;$Z$12,M44&gt;$Z$13),C43,"")</f>
         <v/>
       </c>
       <c r="AA44" s="5">
-        <f>IF(AND(G44&gt;$AA$11,I44&lt;$AA$12,K44&gt;$AA$12),C43,"")</f>
+        <f>IF(AND(G44&gt;$AA$12,I44&lt;$AA$13,K44&gt;$AA$11),C43,"")</f>
         <v/>
       </c>
       <c r="AB44" s="5">
@@ -5684,15 +5582,15 @@
         <v/>
       </c>
       <c r="AC44" s="5">
-        <f>IF(AND(S44&gt;$AC$11,U44&lt;$AC$12),E43,"")</f>
+        <f>IF(AND(S44&gt;$AC$12,U44&lt;$AC$13),E43,"")</f>
         <v/>
       </c>
       <c r="AD44" s="5">
-        <f>IF(AND(O44&lt;=$AD$11,E44&lt;$AD$12),E43,"")</f>
+        <f>IF(AND(O44&lt;=$AD$12,E44&lt;$AD$13),E43,"")</f>
         <v/>
       </c>
       <c r="AE44" s="5">
-        <f>IF(AND(Q44&gt;$AE$11,S44&gt;$AE$12),E43,"")</f>
+        <f>IF(AND(Q44&gt;$AE$12,S44&gt;$AE$13),E43,"")</f>
         <v/>
       </c>
       <c r="AF44" s="5">
@@ -5703,99 +5601,99 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026/06/18</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>174.19</v>
+        <v>173.38</v>
       </c>
       <c r="C45" s="5">
         <f>IF(COUNT(B45:B46)=2,(B45/B46-1)*100,"")</f>
         <v/>
       </c>
       <c r="D45" s="5" t="n">
-        <v>183.86</v>
+        <v>182.43</v>
       </c>
       <c r="E45" s="5">
         <f>IF(COUNT(D45:D46)=2,(D45/D46-1)*100,"")</f>
         <v/>
       </c>
       <c r="F45" s="5" t="n">
-        <v>70.79000000000001</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="G45" s="5">
         <f>IF(COUNT(F45:F46)=2,(F45/F46-1)*100,"")</f>
         <v/>
       </c>
       <c r="H45" s="5" t="n">
-        <v>387.12</v>
+        <v>384.59</v>
       </c>
       <c r="I45" s="5">
         <f>IF(COUNT(H45:H46)=2,(H45/H46-1)*100,"")</f>
         <v/>
       </c>
       <c r="J45" s="5" t="n">
-        <v>79.256</v>
+        <v>79.1867</v>
       </c>
       <c r="K45" s="5">
         <f>IF(COUNT(J45:J46)=2,(J45/J46-1)*100,"")</f>
         <v/>
       </c>
       <c r="L45" s="5" t="n">
-        <v>107.5433</v>
+        <v>107.1009</v>
       </c>
       <c r="M45" s="5">
         <f>IF(COUNT(L45:L46)=2,(L45/L46-1)*100,"")</f>
         <v/>
       </c>
       <c r="N45" s="5" t="n">
-        <v>53.383</v>
+        <v>53.7</v>
       </c>
       <c r="O45" s="5">
         <f>IF(COUNT(N45:N46)=2,(N45/N46-1)*100,"")</f>
         <v/>
       </c>
       <c r="P45" s="5" t="n">
-        <v>56.85</v>
+        <v>56.79</v>
       </c>
       <c r="Q45" s="5">
         <f>IF(COUNT(P45:P46)=2,(P45/P46-1)*100,"")</f>
         <v/>
       </c>
       <c r="R45" s="5" t="n">
-        <v>82.51000000000001</v>
+        <v>81.44</v>
       </c>
       <c r="S45" s="5">
         <f>IF(COUNT(R45:R46)=2,(R45/R46-1)*100,"")</f>
         <v/>
       </c>
       <c r="T45" s="5" t="n">
-        <v>109.166</v>
+        <v>106.86</v>
       </c>
       <c r="U45" s="5">
         <f>IF(COUNT(T45:T46)=2,(T45/T46-1)*100,"")</f>
         <v/>
       </c>
       <c r="V45" s="5" t="n">
-        <v>16.4</v>
+        <v>17.28</v>
       </c>
       <c r="W45" s="5">
         <f>IF(COUNT(V45:V46)=2,(V45/V46-1)*100,"")</f>
         <v/>
       </c>
       <c r="X45" s="5" t="n">
-        <v>-11.0629</v>
+        <v>5.3659</v>
       </c>
       <c r="Y45" s="5">
-        <f>IF(AND(X45&gt;$Y$11,C45&lt;=$Y$12),C44,"")</f>
+        <f>IF(AND(X45&gt;$Y$12,C45&lt;=$Y$13),C44,"")</f>
         <v/>
       </c>
       <c r="Z45" s="5">
-        <f>IF(AND(K45&lt;$Z$11,M45&gt;$Z$12),C44,"")</f>
+        <f>IF(AND(K45&lt;$Z$12,M45&gt;$Z$13),C44,"")</f>
         <v/>
       </c>
       <c r="AA45" s="5">
-        <f>IF(AND(G45&gt;$AA$11,I45&lt;$AA$12,K45&gt;$AA$12),C44,"")</f>
+        <f>IF(AND(G45&gt;$AA$12,I45&lt;$AA$13,K45&gt;$AA$11),C44,"")</f>
         <v/>
       </c>
       <c r="AB45" s="5">
@@ -5803,15 +5701,15 @@
         <v/>
       </c>
       <c r="AC45" s="5">
-        <f>IF(AND(S45&gt;$AC$11,U45&lt;$AC$12),E44,"")</f>
+        <f>IF(AND(S45&gt;$AC$12,U45&lt;$AC$13),E44,"")</f>
         <v/>
       </c>
       <c r="AD45" s="5">
-        <f>IF(AND(O45&lt;=$AD$11,E45&lt;$AD$12),E44,"")</f>
+        <f>IF(AND(O45&lt;=$AD$12,E45&lt;$AD$13),E44,"")</f>
         <v/>
       </c>
       <c r="AE45" s="5">
-        <f>IF(AND(Q45&gt;$AE$11,S45&gt;$AE$12),E44,"")</f>
+        <f>IF(AND(Q45&gt;$AE$12,S45&gt;$AE$13),E44,"")</f>
         <v/>
       </c>
       <c r="AF45" s="5">
@@ -5822,99 +5720,99 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>2026/06/17</t>
+          <t>2026/06/18</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>165.99</v>
+        <v>174.19</v>
       </c>
       <c r="C46" s="5">
         <f>IF(COUNT(B46:B47)=2,(B46/B47-1)*100,"")</f>
         <v/>
       </c>
       <c r="D46" s="5" t="n">
-        <v>180</v>
+        <v>183.86</v>
       </c>
       <c r="E46" s="5">
         <f>IF(COUNT(D46:D47)=2,(D46/D47-1)*100,"")</f>
         <v/>
       </c>
       <c r="F46" s="5" t="n">
-        <v>68.56</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="G46" s="5">
         <f>IF(COUNT(F46:F47)=2,(F46/F47-1)*100,"")</f>
         <v/>
       </c>
       <c r="H46" s="5" t="n">
-        <v>388.6</v>
+        <v>387.12</v>
       </c>
       <c r="I46" s="5">
         <f>IF(COUNT(H46:H47)=2,(H46/H47-1)*100,"")</f>
         <v/>
       </c>
       <c r="J46" s="5" t="n">
-        <v>78.9787</v>
+        <v>79.256</v>
       </c>
       <c r="K46" s="5">
         <f>IF(COUNT(J46:J47)=2,(J46/J47-1)*100,"")</f>
         <v/>
       </c>
       <c r="L46" s="5" t="n">
-        <v>107.1893</v>
+        <v>107.5433</v>
       </c>
       <c r="M46" s="5">
         <f>IF(COUNT(L46:L47)=2,(L46/L47-1)*100,"")</f>
         <v/>
       </c>
       <c r="N46" s="5" t="n">
-        <v>53.8613</v>
+        <v>53.383</v>
       </c>
       <c r="O46" s="5">
         <f>IF(COUNT(N46:N47)=2,(N46/N47-1)*100,"")</f>
         <v/>
       </c>
       <c r="P46" s="5" t="n">
-        <v>57.09</v>
+        <v>56.85</v>
       </c>
       <c r="Q46" s="5">
         <f>IF(COUNT(P46:P47)=2,(P46/P47-1)*100,"")</f>
         <v/>
       </c>
       <c r="R46" s="5" t="n">
-        <v>84.36</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="S46" s="5">
         <f>IF(COUNT(R46:R47)=2,(R46/R47-1)*100,"")</f>
         <v/>
       </c>
       <c r="T46" s="5" t="n">
-        <v>108.9166</v>
+        <v>109.166</v>
       </c>
       <c r="U46" s="5">
         <f>IF(COUNT(T46:T47)=2,(T46/T47-1)*100,"")</f>
         <v/>
       </c>
       <c r="V46" s="5" t="n">
-        <v>18.44</v>
+        <v>16.4</v>
       </c>
       <c r="W46" s="5">
         <f>IF(COUNT(V46:V47)=2,(V46/V47-1)*100,"")</f>
         <v/>
       </c>
       <c r="X46" s="5" t="n">
-        <v>12.3705</v>
+        <v>-11.0629</v>
       </c>
       <c r="Y46" s="5">
-        <f>IF(AND(X46&gt;$Y$11,C46&lt;=$Y$12),C45,"")</f>
+        <f>IF(AND(X46&gt;$Y$12,C46&lt;=$Y$13),C45,"")</f>
         <v/>
       </c>
       <c r="Z46" s="5">
-        <f>IF(AND(K46&lt;$Z$11,M46&gt;$Z$12),C45,"")</f>
+        <f>IF(AND(K46&lt;$Z$12,M46&gt;$Z$13),C45,"")</f>
         <v/>
       </c>
       <c r="AA46" s="5">
-        <f>IF(AND(G46&gt;$AA$11,I46&lt;$AA$12,K46&gt;$AA$12),C45,"")</f>
+        <f>IF(AND(G46&gt;$AA$12,I46&lt;$AA$13,K46&gt;$AA$11),C45,"")</f>
         <v/>
       </c>
       <c r="AB46" s="5">
@@ -5922,15 +5820,15 @@
         <v/>
       </c>
       <c r="AC46" s="5">
-        <f>IF(AND(S46&gt;$AC$11,U46&lt;$AC$12),E45,"")</f>
+        <f>IF(AND(S46&gt;$AC$12,U46&lt;$AC$13),E45,"")</f>
         <v/>
       </c>
       <c r="AD46" s="5">
-        <f>IF(AND(O46&lt;=$AD$11,E46&lt;$AD$12),E45,"")</f>
+        <f>IF(AND(O46&lt;=$AD$12,E46&lt;$AD$13),E45,"")</f>
         <v/>
       </c>
       <c r="AE46" s="5">
-        <f>IF(AND(Q46&gt;$AE$11,S46&gt;$AE$12),E45,"")</f>
+        <f>IF(AND(Q46&gt;$AE$12,S46&gt;$AE$13),E45,"")</f>
         <v/>
       </c>
       <c r="AF46" s="5">
@@ -5941,99 +5839,99 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026/06/16</t>
+          <t>2026/06/17</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>169.4</v>
+        <v>165.99</v>
       </c>
       <c r="C47" s="5">
         <f>IF(COUNT(B47:B48)=2,(B47/B48-1)*100,"")</f>
         <v/>
       </c>
       <c r="D47" s="5" t="n">
-        <v>184.56</v>
+        <v>180</v>
       </c>
       <c r="E47" s="5">
         <f>IF(COUNT(D47:D48)=2,(D47/D48-1)*100,"")</f>
         <v/>
       </c>
       <c r="F47" s="5" t="n">
-        <v>68.64</v>
+        <v>68.56</v>
       </c>
       <c r="G47" s="5">
         <f>IF(COUNT(F47:F48)=2,(F47/F48-1)*100,"")</f>
         <v/>
       </c>
       <c r="H47" s="5" t="n">
-        <v>397.63</v>
+        <v>388.6</v>
       </c>
       <c r="I47" s="5">
         <f>IF(COUNT(H47:H48)=2,(H47/H48-1)*100,"")</f>
         <v/>
       </c>
       <c r="J47" s="5" t="n">
-        <v>79.2758</v>
+        <v>78.9787</v>
       </c>
       <c r="K47" s="5">
         <f>IF(COUNT(J47:J48)=2,(J47/J48-1)*100,"")</f>
         <v/>
       </c>
       <c r="L47" s="5" t="n">
-        <v>107.907</v>
+        <v>107.1893</v>
       </c>
       <c r="M47" s="5">
         <f>IF(COUNT(L47:L48)=2,(L47/L48-1)*100,"")</f>
         <v/>
       </c>
       <c r="N47" s="5" t="n">
-        <v>54.1603</v>
+        <v>53.8613</v>
       </c>
       <c r="O47" s="5">
         <f>IF(COUNT(N47:N48)=2,(N47/N48-1)*100,"")</f>
         <v/>
       </c>
       <c r="P47" s="5" t="n">
-        <v>57.19</v>
+        <v>57.09</v>
       </c>
       <c r="Q47" s="5">
         <f>IF(COUNT(P47:P48)=2,(P47/P48-1)*100,"")</f>
         <v/>
       </c>
       <c r="R47" s="5" t="n">
-        <v>87.23999999999999</v>
+        <v>84.36</v>
       </c>
       <c r="S47" s="5">
         <f>IF(COUNT(R47:R48)=2,(R47/R48-1)*100,"")</f>
         <v/>
       </c>
       <c r="T47" s="5" t="n">
-        <v>112.0286</v>
+        <v>108.9166</v>
       </c>
       <c r="U47" s="5">
         <f>IF(COUNT(T47:T48)=2,(T47/T48-1)*100,"")</f>
         <v/>
       </c>
       <c r="V47" s="5" t="n">
-        <v>16.41</v>
+        <v>18.44</v>
       </c>
       <c r="W47" s="5">
         <f>IF(COUNT(V47:V48)=2,(V47/V48-1)*100,"")</f>
         <v/>
       </c>
       <c r="X47" s="5" t="n">
-        <v>1.2963</v>
+        <v>12.3705</v>
       </c>
       <c r="Y47" s="5">
-        <f>IF(AND(X47&gt;$Y$11,C47&lt;=$Y$12),C46,"")</f>
+        <f>IF(AND(X47&gt;$Y$12,C47&lt;=$Y$13),C46,"")</f>
         <v/>
       </c>
       <c r="Z47" s="5">
-        <f>IF(AND(K47&lt;$Z$11,M47&gt;$Z$12),C46,"")</f>
+        <f>IF(AND(K47&lt;$Z$12,M47&gt;$Z$13),C46,"")</f>
         <v/>
       </c>
       <c r="AA47" s="5">
-        <f>IF(AND(G47&gt;$AA$11,I47&lt;$AA$12,K47&gt;$AA$12),C46,"")</f>
+        <f>IF(AND(G47&gt;$AA$12,I47&lt;$AA$13,K47&gt;$AA$11),C46,"")</f>
         <v/>
       </c>
       <c r="AB47" s="5">
@@ -6041,15 +5939,15 @@
         <v/>
       </c>
       <c r="AC47" s="5">
-        <f>IF(AND(S47&gt;$AC$11,U47&lt;$AC$12),E46,"")</f>
+        <f>IF(AND(S47&gt;$AC$12,U47&lt;$AC$13),E46,"")</f>
         <v/>
       </c>
       <c r="AD47" s="5">
-        <f>IF(AND(O47&lt;=$AD$11,E47&lt;$AD$12),E46,"")</f>
+        <f>IF(AND(O47&lt;=$AD$12,E47&lt;$AD$13),E46,"")</f>
         <v/>
       </c>
       <c r="AE47" s="5">
-        <f>IF(AND(Q47&gt;$AE$11,S47&gt;$AE$12),E46,"")</f>
+        <f>IF(AND(Q47&gt;$AE$12,S47&gt;$AE$13),E46,"")</f>
         <v/>
       </c>
       <c r="AF47" s="5">
@@ -6060,39 +5958,39 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
+          <t>2026/06/16</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>176.04</v>
+        <v>169.4</v>
       </c>
       <c r="C48" s="5">
         <f>IF(COUNT(B48:B49)=2,(B48/B49-1)*100,"")</f>
         <v/>
       </c>
       <c r="D48" s="5" t="n">
-        <v>186.69</v>
+        <v>184.56</v>
       </c>
       <c r="E48" s="5">
         <f>IF(COUNT(D48:D49)=2,(D48/D49-1)*100,"")</f>
         <v/>
       </c>
       <c r="F48" s="5" t="n">
-        <v>69.75</v>
+        <v>68.64</v>
       </c>
       <c r="G48" s="5">
         <f>IF(COUNT(F48:F49)=2,(F48/F49-1)*100,"")</f>
         <v/>
       </c>
       <c r="H48" s="5" t="n">
-        <v>396.55</v>
+        <v>397.63</v>
       </c>
       <c r="I48" s="5">
         <f>IF(COUNT(H48:H49)=2,(H48/H49-1)*100,"")</f>
         <v/>
       </c>
       <c r="J48" s="5" t="n">
-        <v>79.28579999999999</v>
+        <v>79.2758</v>
       </c>
       <c r="K48" s="5">
         <f>IF(COUNT(J48:J49)=2,(J48/J49-1)*100,"")</f>
@@ -6106,53 +6004,53 @@
         <v/>
       </c>
       <c r="N48" s="5" t="n">
-        <v>53.373</v>
+        <v>54.1603</v>
       </c>
       <c r="O48" s="5">
         <f>IF(COUNT(N48:N49)=2,(N48/N49-1)*100,"")</f>
         <v/>
       </c>
       <c r="P48" s="5" t="n">
-        <v>57.24</v>
+        <v>57.19</v>
       </c>
       <c r="Q48" s="5">
         <f>IF(COUNT(P48:P49)=2,(P48/P49-1)*100,"")</f>
         <v/>
       </c>
       <c r="R48" s="5" t="n">
-        <v>85.27</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="S48" s="5">
         <f>IF(COUNT(R48:R49)=2,(R48/R49-1)*100,"")</f>
         <v/>
       </c>
       <c r="T48" s="5" t="n">
-        <v>111.8989</v>
+        <v>112.0286</v>
       </c>
       <c r="U48" s="5">
         <f>IF(COUNT(T48:T49)=2,(T48/T49-1)*100,"")</f>
         <v/>
       </c>
       <c r="V48" s="5" t="n">
-        <v>16.2</v>
+        <v>16.41</v>
       </c>
       <c r="W48" s="5">
         <f>IF(COUNT(V48:V49)=2,(V48/V49-1)*100,"")</f>
         <v/>
       </c>
       <c r="X48" s="5" t="n">
-        <v>-8.371</v>
+        <v>1.2963</v>
       </c>
       <c r="Y48" s="5">
-        <f>IF(AND(X48&gt;$Y$11,C48&lt;=$Y$12),C47,"")</f>
+        <f>IF(AND(X48&gt;$Y$12,C48&lt;=$Y$13),C47,"")</f>
         <v/>
       </c>
       <c r="Z48" s="5">
-        <f>IF(AND(K48&lt;$Z$11,M48&gt;$Z$12),C47,"")</f>
+        <f>IF(AND(K48&lt;$Z$12,M48&gt;$Z$13),C47,"")</f>
         <v/>
       </c>
       <c r="AA48" s="5">
-        <f>IF(AND(G48&gt;$AA$11,I48&lt;$AA$12,K48&gt;$AA$12),C47,"")</f>
+        <f>IF(AND(G48&gt;$AA$12,I48&lt;$AA$13,K48&gt;$AA$11),C47,"")</f>
         <v/>
       </c>
       <c r="AB48" s="5">
@@ -6160,15 +6058,15 @@
         <v/>
       </c>
       <c r="AC48" s="5">
-        <f>IF(AND(S48&gt;$AC$11,U48&lt;$AC$12),E47,"")</f>
+        <f>IF(AND(S48&gt;$AC$12,U48&lt;$AC$13),E47,"")</f>
         <v/>
       </c>
       <c r="AD48" s="5">
-        <f>IF(AND(O48&lt;=$AD$11,E48&lt;$AD$12),E47,"")</f>
+        <f>IF(AND(O48&lt;=$AD$12,E48&lt;$AD$13),E47,"")</f>
         <v/>
       </c>
       <c r="AE48" s="5">
-        <f>IF(AND(Q48&gt;$AE$11,S48&gt;$AE$12),E47,"")</f>
+        <f>IF(AND(Q48&gt;$AE$12,S48&gt;$AE$13),E47,"")</f>
         <v/>
       </c>
       <c r="AF48" s="5">
@@ -6179,99 +6077,99 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026/06/12</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>165.93</v>
+        <v>176.04</v>
       </c>
       <c r="C49" s="5">
         <f>IF(COUNT(B49:B50)=2,(B49/B50-1)*100,"")</f>
         <v/>
       </c>
       <c r="D49" s="5" t="n">
-        <v>180.68</v>
+        <v>186.69</v>
       </c>
       <c r="E49" s="5">
         <f>IF(COUNT(D49:D50)=2,(D49/D50-1)*100,"")</f>
         <v/>
       </c>
       <c r="F49" s="5" t="n">
-        <v>67.529</v>
+        <v>69.75</v>
       </c>
       <c r="G49" s="5">
         <f>IF(COUNT(F49:F50)=2,(F49/F50-1)*100,"")</f>
         <v/>
       </c>
       <c r="H49" s="5" t="n">
-        <v>386.54</v>
+        <v>396.55</v>
       </c>
       <c r="I49" s="5">
         <f>IF(COUNT(H49:H50)=2,(H49/H50-1)*100,"")</f>
         <v/>
       </c>
       <c r="J49" s="5" t="n">
-        <v>79.1867</v>
+        <v>79.28579999999999</v>
       </c>
       <c r="K49" s="5">
         <f>IF(COUNT(J49:J50)=2,(J49/J50-1)*100,"")</f>
         <v/>
       </c>
       <c r="L49" s="5" t="n">
-        <v>107.7596</v>
+        <v>107.907</v>
       </c>
       <c r="M49" s="5">
         <f>IF(COUNT(L49:L50)=2,(L49/L50-1)*100,"")</f>
         <v/>
       </c>
       <c r="N49" s="5" t="n">
-        <v>53.1538</v>
+        <v>53.373</v>
       </c>
       <c r="O49" s="5">
         <f>IF(COUNT(N49:N50)=2,(N49/N50-1)*100,"")</f>
         <v/>
       </c>
       <c r="P49" s="5" t="n">
-        <v>57.26</v>
+        <v>57.24</v>
       </c>
       <c r="Q49" s="5">
         <f>IF(COUNT(P49:P50)=2,(P49/P50-1)*100,"")</f>
         <v/>
       </c>
       <c r="R49" s="5" t="n">
-        <v>80.03</v>
+        <v>85.27</v>
       </c>
       <c r="S49" s="5">
         <f>IF(COUNT(R49:R50)=2,(R49/R50-1)*100,"")</f>
         <v/>
       </c>
       <c r="T49" s="5" t="n">
-        <v>111.3603</v>
+        <v>111.8989</v>
       </c>
       <c r="U49" s="5">
         <f>IF(COUNT(T49:T50)=2,(T49/T50-1)*100,"")</f>
         <v/>
       </c>
       <c r="V49" s="5" t="n">
-        <v>17.68</v>
+        <v>16.2</v>
       </c>
       <c r="W49" s="5">
         <f>IF(COUNT(V49:V50)=2,(V49/V50-1)*100,"")</f>
         <v/>
       </c>
       <c r="X49" s="5" t="n">
-        <v>-9.0535</v>
+        <v>-8.371</v>
       </c>
       <c r="Y49" s="5">
-        <f>IF(AND(X49&gt;$Y$11,C49&lt;=$Y$12),C48,"")</f>
+        <f>IF(AND(X49&gt;$Y$12,C49&lt;=$Y$13),C48,"")</f>
         <v/>
       </c>
       <c r="Z49" s="5">
-        <f>IF(AND(K49&lt;$Z$11,M49&gt;$Z$12),C48,"")</f>
+        <f>IF(AND(K49&lt;$Z$12,M49&gt;$Z$13),C48,"")</f>
         <v/>
       </c>
       <c r="AA49" s="5">
-        <f>IF(AND(G49&gt;$AA$11,I49&lt;$AA$12,K49&gt;$AA$12),C48,"")</f>
+        <f>IF(AND(G49&gt;$AA$12,I49&lt;$AA$13,K49&gt;$AA$11),C48,"")</f>
         <v/>
       </c>
       <c r="AB49" s="5">
@@ -6279,15 +6177,15 @@
         <v/>
       </c>
       <c r="AC49" s="5">
-        <f>IF(AND(S49&gt;$AC$11,U49&lt;$AC$12),E48,"")</f>
+        <f>IF(AND(S49&gt;$AC$12,U49&lt;$AC$13),E48,"")</f>
         <v/>
       </c>
       <c r="AD49" s="5">
-        <f>IF(AND(O49&lt;=$AD$11,E49&lt;$AD$12),E48,"")</f>
+        <f>IF(AND(O49&lt;=$AD$12,E49&lt;$AD$13),E48,"")</f>
         <v/>
       </c>
       <c r="AE49" s="5">
-        <f>IF(AND(Q49&gt;$AE$11,S49&gt;$AE$12),E48,"")</f>
+        <f>IF(AND(Q49&gt;$AE$12,S49&gt;$AE$13),E48,"")</f>
         <v/>
       </c>
       <c r="AF49" s="5">
@@ -6298,32 +6196,32 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>2026/06/11</t>
+          <t>2026/06/12</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>163.86</v>
+        <v>165.93</v>
       </c>
       <c r="C50" s="5">
         <f>IF(COUNT(B50:B51)=2,(B50/B51-1)*100,"")</f>
         <v/>
       </c>
       <c r="D50" s="5" t="n">
-        <v>178.87</v>
+        <v>180.68</v>
       </c>
       <c r="E50" s="5">
         <f>IF(COUNT(D50:D51)=2,(D50/D51-1)*100,"")</f>
         <v/>
       </c>
       <c r="F50" s="5" t="n">
-        <v>67.151</v>
+        <v>67.529</v>
       </c>
       <c r="G50" s="5">
         <f>IF(COUNT(F50:F51)=2,(F50/F51-1)*100,"")</f>
         <v/>
       </c>
       <c r="H50" s="5" t="n">
-        <v>386.32</v>
+        <v>386.54</v>
       </c>
       <c r="I50" s="5">
         <f>IF(COUNT(H50:H51)=2,(H50/H51-1)*100,"")</f>
@@ -6337,60 +6235,60 @@
         <v/>
       </c>
       <c r="L50" s="5" t="n">
-        <v>107.7497</v>
+        <v>107.7596</v>
       </c>
       <c r="M50" s="5">
         <f>IF(COUNT(L50:L51)=2,(L50/L51-1)*100,"")</f>
         <v/>
       </c>
       <c r="N50" s="5" t="n">
-        <v>52.4363</v>
+        <v>53.1538</v>
       </c>
       <c r="O50" s="5">
         <f>IF(COUNT(N50:N51)=2,(N50/N51-1)*100,"")</f>
         <v/>
       </c>
       <c r="P50" s="5" t="n">
-        <v>57.43</v>
+        <v>57.26</v>
       </c>
       <c r="Q50" s="5">
         <f>IF(COUNT(P50:P51)=2,(P50/P51-1)*100,"")</f>
         <v/>
       </c>
       <c r="R50" s="5" t="n">
-        <v>77.72</v>
+        <v>80.03</v>
       </c>
       <c r="S50" s="5">
         <f>IF(COUNT(R50:R51)=2,(R50/R51-1)*100,"")</f>
         <v/>
       </c>
       <c r="T50" s="5" t="n">
-        <v>111.8291</v>
+        <v>111.3603</v>
       </c>
       <c r="U50" s="5">
         <f>IF(COUNT(T50:T51)=2,(T50/T51-1)*100,"")</f>
         <v/>
       </c>
       <c r="V50" s="5" t="n">
-        <v>19.44</v>
+        <v>17.68</v>
       </c>
       <c r="W50" s="5">
         <f>IF(COUNT(V50:V51)=2,(V50/V51-1)*100,"")</f>
         <v/>
       </c>
       <c r="X50" s="5" t="n">
-        <v>-12.5113</v>
+        <v>-9.0535</v>
       </c>
       <c r="Y50" s="5">
-        <f>IF(AND(X50&gt;$Y$11,C50&lt;=$Y$12),C49,"")</f>
+        <f>IF(AND(X50&gt;$Y$12,C50&lt;=$Y$13),C49,"")</f>
         <v/>
       </c>
       <c r="Z50" s="5">
-        <f>IF(AND(K50&lt;$Z$11,M50&gt;$Z$12),C49,"")</f>
+        <f>IF(AND(K50&lt;$Z$12,M50&gt;$Z$13),C49,"")</f>
         <v/>
       </c>
       <c r="AA50" s="5">
-        <f>IF(AND(G50&gt;$AA$11,I50&lt;$AA$12,K50&gt;$AA$12),C49,"")</f>
+        <f>IF(AND(G50&gt;$AA$12,I50&lt;$AA$13,K50&gt;$AA$11),C49,"")</f>
         <v/>
       </c>
       <c r="AB50" s="5">
@@ -6398,15 +6296,15 @@
         <v/>
       </c>
       <c r="AC50" s="5">
-        <f>IF(AND(S50&gt;$AC$11,U50&lt;$AC$12),E49,"")</f>
+        <f>IF(AND(S50&gt;$AC$12,U50&lt;$AC$13),E49,"")</f>
         <v/>
       </c>
       <c r="AD50" s="5">
-        <f>IF(AND(O50&lt;=$AD$11,E50&lt;$AD$12),E49,"")</f>
+        <f>IF(AND(O50&lt;=$AD$12,E50&lt;$AD$13),E49,"")</f>
         <v/>
       </c>
       <c r="AE50" s="5">
-        <f>IF(AND(Q50&gt;$AE$11,S50&gt;$AE$12),E49,"")</f>
+        <f>IF(AND(Q50&gt;$AE$12,S50&gt;$AE$13),E49,"")</f>
         <v/>
       </c>
       <c r="AF50" s="5">
@@ -6417,99 +6315,99 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026/06/10</t>
+          <t>2026/06/11</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>153.76</v>
+        <v>163.86</v>
       </c>
       <c r="C51" s="5">
         <f>IF(COUNT(B51:B52)=2,(B51/B52-1)*100,"")</f>
         <v/>
       </c>
       <c r="D51" s="5" t="n">
-        <v>172.89</v>
+        <v>178.87</v>
       </c>
       <c r="E51" s="5">
         <f>IF(COUNT(D51:D52)=2,(D51/D52-1)*100,"")</f>
         <v/>
       </c>
       <c r="F51" s="5" t="n">
-        <v>64.3257</v>
+        <v>67.151</v>
       </c>
       <c r="G51" s="5">
         <f>IF(COUNT(F51:F52)=2,(F51/F52-1)*100,"")</f>
         <v/>
       </c>
       <c r="H51" s="5" t="n">
-        <v>374.58</v>
+        <v>386.32</v>
       </c>
       <c r="I51" s="5">
         <f>IF(COUNT(H51:H52)=2,(H51/H52-1)*100,"")</f>
         <v/>
       </c>
       <c r="J51" s="5" t="n">
-        <v>78.72110000000001</v>
+        <v>79.1867</v>
       </c>
       <c r="K51" s="5">
         <f>IF(COUNT(J51:J52)=2,(J51/J52-1)*100,"")</f>
         <v/>
       </c>
       <c r="L51" s="5" t="n">
-        <v>107.3663</v>
+        <v>107.7497</v>
       </c>
       <c r="M51" s="5">
         <f>IF(COUNT(L51:L52)=2,(L51/L52-1)*100,"")</f>
         <v/>
       </c>
       <c r="N51" s="5" t="n">
-        <v>52.0477</v>
+        <v>52.4363</v>
       </c>
       <c r="O51" s="5">
         <f>IF(COUNT(N51:N52)=2,(N51/N52-1)*100,"")</f>
         <v/>
       </c>
       <c r="P51" s="5" t="n">
-        <v>57.17</v>
+        <v>57.43</v>
       </c>
       <c r="Q51" s="5">
         <f>IF(COUNT(P51:P52)=2,(P51/P52-1)*100,"")</f>
         <v/>
       </c>
       <c r="R51" s="5" t="n">
-        <v>73.81</v>
+        <v>77.72</v>
       </c>
       <c r="S51" s="5">
         <f>IF(COUNT(R51:R52)=2,(R51/R52-1)*100,"")</f>
         <v/>
       </c>
       <c r="T51" s="5" t="n">
-        <v>110.722</v>
+        <v>111.8291</v>
       </c>
       <c r="U51" s="5">
         <f>IF(COUNT(T51:T52)=2,(T51/T52-1)*100,"")</f>
         <v/>
       </c>
       <c r="V51" s="5" t="n">
-        <v>22.22</v>
+        <v>19.44</v>
       </c>
       <c r="W51" s="5">
         <f>IF(COUNT(V51:V52)=2,(V51/V52-1)*100,"")</f>
         <v/>
       </c>
       <c r="X51" s="5" t="n">
-        <v>11.8269</v>
+        <v>-12.5113</v>
       </c>
       <c r="Y51" s="5">
-        <f>IF(AND(X51&gt;$Y$11,C51&lt;=$Y$12),C50,"")</f>
+        <f>IF(AND(X51&gt;$Y$12,C51&lt;=$Y$13),C50,"")</f>
         <v/>
       </c>
       <c r="Z51" s="5">
-        <f>IF(AND(K51&lt;$Z$11,M51&gt;$Z$12),C50,"")</f>
+        <f>IF(AND(K51&lt;$Z$12,M51&gt;$Z$13),C50,"")</f>
         <v/>
       </c>
       <c r="AA51" s="5">
-        <f>IF(AND(G51&gt;$AA$11,I51&lt;$AA$12,K51&gt;$AA$12),C50,"")</f>
+        <f>IF(AND(G51&gt;$AA$12,I51&lt;$AA$13,K51&gt;$AA$11),C50,"")</f>
         <v/>
       </c>
       <c r="AB51" s="5">
@@ -6517,15 +6415,15 @@
         <v/>
       </c>
       <c r="AC51" s="5">
-        <f>IF(AND(S51&gt;$AC$11,U51&lt;$AC$12),E50,"")</f>
+        <f>IF(AND(S51&gt;$AC$12,U51&lt;$AC$13),E50,"")</f>
         <v/>
       </c>
       <c r="AD51" s="5">
-        <f>IF(AND(O51&lt;=$AD$11,E51&lt;$AD$12),E50,"")</f>
+        <f>IF(AND(O51&lt;=$AD$12,E51&lt;$AD$13),E50,"")</f>
         <v/>
       </c>
       <c r="AE51" s="5">
-        <f>IF(AND(Q51&gt;$AE$11,S51&gt;$AE$12),E50,"")</f>
+        <f>IF(AND(Q51&gt;$AE$12,S51&gt;$AE$13),E50,"")</f>
         <v/>
       </c>
       <c r="AF51" s="5">
@@ -6536,99 +6434,99 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/06/10</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>160.13</v>
+        <v>153.76</v>
       </c>
       <c r="C52" s="5">
         <f>IF(COUNT(B52:B53)=2,(B52/B53-1)*100,"")</f>
         <v/>
       </c>
       <c r="D52" s="5" t="n">
-        <v>178.67</v>
+        <v>172.89</v>
       </c>
       <c r="E52" s="5">
         <f>IF(COUNT(D52:D53)=2,(D52/D53-1)*100,"")</f>
         <v/>
       </c>
       <c r="F52" s="5" t="n">
-        <v>65.47969999999999</v>
+        <v>64.3257</v>
       </c>
       <c r="G52" s="5">
         <f>IF(COUNT(F52:F53)=2,(F52/F53-1)*100,"")</f>
         <v/>
       </c>
       <c r="H52" s="5" t="n">
-        <v>390.78</v>
+        <v>374.58</v>
       </c>
       <c r="I52" s="5">
         <f>IF(COUNT(H52:H53)=2,(H52/H53-1)*100,"")</f>
         <v/>
       </c>
       <c r="J52" s="5" t="n">
-        <v>78.86969999999999</v>
+        <v>78.72110000000001</v>
       </c>
       <c r="K52" s="5">
         <f>IF(COUNT(J52:J53)=2,(J52/J53-1)*100,"")</f>
         <v/>
       </c>
       <c r="L52" s="5" t="n">
-        <v>107.4744</v>
+        <v>107.3663</v>
       </c>
       <c r="M52" s="5">
         <f>IF(COUNT(L52:L53)=2,(L52/L53-1)*100,"")</f>
         <v/>
       </c>
       <c r="N52" s="5" t="n">
-        <v>52.2769</v>
+        <v>52.0477</v>
       </c>
       <c r="O52" s="5">
         <f>IF(COUNT(N52:N53)=2,(N52/N53-1)*100,"")</f>
         <v/>
       </c>
       <c r="P52" s="5" t="n">
-        <v>57.23</v>
+        <v>57.17</v>
       </c>
       <c r="Q52" s="5">
         <f>IF(COUNT(P52:P53)=2,(P52/P53-1)*100,"")</f>
         <v/>
       </c>
       <c r="R52" s="5" t="n">
-        <v>77.59</v>
+        <v>73.81</v>
       </c>
       <c r="S52" s="5">
         <f>IF(COUNT(R52:R53)=2,(R52/R53-1)*100,"")</f>
         <v/>
       </c>
       <c r="T52" s="5" t="n">
-        <v>111.1907</v>
+        <v>110.722</v>
       </c>
       <c r="U52" s="5">
         <f>IF(COUNT(T52:T53)=2,(T52/T53-1)*100,"")</f>
         <v/>
       </c>
       <c r="V52" s="5" t="n">
-        <v>19.87</v>
+        <v>22.22</v>
       </c>
       <c r="W52" s="5">
         <f>IF(COUNT(V52:V53)=2,(V52/V53-1)*100,"")</f>
         <v/>
       </c>
       <c r="X52" s="5" t="n">
-        <v>5.0211</v>
+        <v>11.8269</v>
       </c>
       <c r="Y52" s="5">
-        <f>IF(AND(X52&gt;$Y$11,C52&lt;=$Y$12),C51,"")</f>
+        <f>IF(AND(X52&gt;$Y$12,C52&lt;=$Y$13),C51,"")</f>
         <v/>
       </c>
       <c r="Z52" s="5">
-        <f>IF(AND(K52&lt;$Z$11,M52&gt;$Z$12),C51,"")</f>
+        <f>IF(AND(K52&lt;$Z$12,M52&gt;$Z$13),C51,"")</f>
         <v/>
       </c>
       <c r="AA52" s="5">
-        <f>IF(AND(G52&gt;$AA$11,I52&lt;$AA$12,K52&gt;$AA$12),C51,"")</f>
+        <f>IF(AND(G52&gt;$AA$12,I52&lt;$AA$13,K52&gt;$AA$11),C51,"")</f>
         <v/>
       </c>
       <c r="AB52" s="5">
@@ -6636,15 +6534,15 @@
         <v/>
       </c>
       <c r="AC52" s="5">
-        <f>IF(AND(S52&gt;$AC$11,U52&lt;$AC$12),E51,"")</f>
+        <f>IF(AND(S52&gt;$AC$12,U52&lt;$AC$13),E51,"")</f>
         <v/>
       </c>
       <c r="AD52" s="5">
-        <f>IF(AND(O52&lt;=$AD$11,E52&lt;$AD$12),E51,"")</f>
+        <f>IF(AND(O52&lt;=$AD$12,E52&lt;$AD$13),E51,"")</f>
         <v/>
       </c>
       <c r="AE52" s="5">
-        <f>IF(AND(Q52&gt;$AE$11,S52&gt;$AE$12),E51,"")</f>
+        <f>IF(AND(Q52&gt;$AE$12,S52&gt;$AE$13),E51,"")</f>
         <v/>
       </c>
       <c r="AF52" s="5">
@@ -6655,99 +6553,99 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026/06/08</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>163.85</v>
+        <v>160.13</v>
       </c>
       <c r="C53" s="5">
         <f>IF(COUNT(B53:B54)=2,(B53/B54-1)*100,"")</f>
         <v/>
       </c>
       <c r="D53" s="5" t="n">
-        <v>179.65</v>
+        <v>178.67</v>
       </c>
       <c r="E53" s="5">
         <f>IF(COUNT(D53:D54)=2,(D53/D54-1)*100,"")</f>
         <v/>
       </c>
       <c r="F53" s="5" t="n">
-        <v>65.41</v>
+        <v>65.47969999999999</v>
       </c>
       <c r="G53" s="5">
         <f>IF(COUNT(F53:F54)=2,(F53/F54-1)*100,"")</f>
         <v/>
       </c>
       <c r="H53" s="5" t="n">
-        <v>397.27</v>
+        <v>390.78</v>
       </c>
       <c r="I53" s="5">
         <f>IF(COUNT(H53:H54)=2,(H53/H54-1)*100,"")</f>
         <v/>
       </c>
       <c r="J53" s="5" t="n">
-        <v>78.79049999999999</v>
+        <v>78.86969999999999</v>
       </c>
       <c r="K53" s="5">
         <f>IF(COUNT(J53:J54)=2,(J53/J54-1)*100,"")</f>
         <v/>
       </c>
       <c r="L53" s="5" t="n">
-        <v>107.2877</v>
+        <v>107.4744</v>
       </c>
       <c r="M53" s="5">
         <f>IF(COUNT(L53:L54)=2,(L53/L54-1)*100,"")</f>
         <v/>
       </c>
       <c r="N53" s="5" t="n">
-        <v>51.7886</v>
+        <v>52.2769</v>
       </c>
       <c r="O53" s="5">
         <f>IF(COUNT(N53:N54)=2,(N53/N54-1)*100,"")</f>
         <v/>
       </c>
       <c r="P53" s="5" t="n">
-        <v>57.28</v>
+        <v>57.23</v>
       </c>
       <c r="Q53" s="5">
         <f>IF(COUNT(P53:P54)=2,(P53/P54-1)*100,"")</f>
         <v/>
       </c>
       <c r="R53" s="5" t="n">
-        <v>78.67</v>
+        <v>77.59</v>
       </c>
       <c r="S53" s="5">
         <f>IF(COUNT(R53:R54)=2,(R53/R54-1)*100,"")</f>
         <v/>
       </c>
       <c r="T53" s="5" t="n">
-        <v>110.8017</v>
+        <v>111.1907</v>
       </c>
       <c r="U53" s="5">
         <f>IF(COUNT(T53:T54)=2,(T53/T54-1)*100,"")</f>
         <v/>
       </c>
       <c r="V53" s="5" t="n">
-        <v>18.92</v>
+        <v>19.87</v>
       </c>
       <c r="W53" s="5">
         <f>IF(COUNT(V53:V54)=2,(V53/V54-1)*100,"")</f>
         <v/>
       </c>
       <c r="X53" s="5" t="n">
-        <v>-12.0409</v>
+        <v>5.0211</v>
       </c>
       <c r="Y53" s="5">
-        <f>IF(AND(X53&gt;$Y$11,C53&lt;=$Y$12),C52,"")</f>
+        <f>IF(AND(X53&gt;$Y$12,C53&lt;=$Y$13),C52,"")</f>
         <v/>
       </c>
       <c r="Z53" s="5">
-        <f>IF(AND(K53&lt;$Z$11,M53&gt;$Z$12),C52,"")</f>
+        <f>IF(AND(K53&lt;$Z$12,M53&gt;$Z$13),C52,"")</f>
         <v/>
       </c>
       <c r="AA53" s="5">
-        <f>IF(AND(G53&gt;$AA$11,I53&lt;$AA$12,K53&gt;$AA$12),C52,"")</f>
+        <f>IF(AND(G53&gt;$AA$12,I53&lt;$AA$13,K53&gt;$AA$11),C52,"")</f>
         <v/>
       </c>
       <c r="AB53" s="5">
@@ -6755,15 +6653,15 @@
         <v/>
       </c>
       <c r="AC53" s="5">
-        <f>IF(AND(S53&gt;$AC$11,U53&lt;$AC$12),E52,"")</f>
+        <f>IF(AND(S53&gt;$AC$12,U53&lt;$AC$13),E52,"")</f>
         <v/>
       </c>
       <c r="AD53" s="5">
-        <f>IF(AND(O53&lt;=$AD$11,E53&lt;$AD$12),E52,"")</f>
+        <f>IF(AND(O53&lt;=$AD$12,E53&lt;$AD$13),E52,"")</f>
         <v/>
       </c>
       <c r="AE53" s="5">
-        <f>IF(AND(Q53&gt;$AE$11,S53&gt;$AE$12),E52,"")</f>
+        <f>IF(AND(Q53&gt;$AE$12,S53&gt;$AE$13),E52,"")</f>
         <v/>
       </c>
       <c r="AF53" s="5">
@@ -6774,99 +6672,99 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>2026/06/05</t>
+          <t>2026/06/08</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>158.91</v>
+        <v>163.85</v>
       </c>
       <c r="C54" s="5">
         <f>IF(COUNT(B54:B55)=2,(B54/B55-1)*100,"")</f>
         <v/>
       </c>
       <c r="D54" s="5" t="n">
-        <v>178.71</v>
+        <v>179.65</v>
       </c>
       <c r="E54" s="5">
         <f>IF(COUNT(D54:D55)=2,(D54/D55-1)*100,"")</f>
         <v/>
       </c>
       <c r="F54" s="5" t="n">
-        <v>64.256</v>
+        <v>65.41</v>
       </c>
       <c r="G54" s="5">
         <f>IF(COUNT(F54:F55)=2,(F54/F55-1)*100,"")</f>
         <v/>
       </c>
       <c r="H54" s="5" t="n">
-        <v>396.24</v>
+        <v>397.27</v>
       </c>
       <c r="I54" s="5">
         <f>IF(COUNT(H54:H55)=2,(H54/H55-1)*100,"")</f>
         <v/>
       </c>
       <c r="J54" s="5" t="n">
-        <v>78.6815</v>
+        <v>78.79049999999999</v>
       </c>
       <c r="K54" s="5">
         <f>IF(COUNT(J54:J55)=2,(J54/J55-1)*100,"")</f>
         <v/>
       </c>
       <c r="L54" s="5" t="n">
-        <v>107.4056</v>
+        <v>107.2877</v>
       </c>
       <c r="M54" s="5">
         <f>IF(COUNT(L54:L55)=2,(L54/L55-1)*100,"")</f>
         <v/>
       </c>
       <c r="N54" s="5" t="n">
-        <v>52.1174</v>
+        <v>51.7886</v>
       </c>
       <c r="O54" s="5">
         <f>IF(COUNT(N54:N55)=2,(N54/N55-1)*100,"")</f>
         <v/>
       </c>
       <c r="P54" s="5" t="n">
-        <v>57.31</v>
+        <v>57.28</v>
       </c>
       <c r="Q54" s="5">
         <f>IF(COUNT(P54:P55)=2,(P54/P55-1)*100,"")</f>
         <v/>
       </c>
       <c r="R54" s="5" t="n">
-        <v>78.84</v>
+        <v>78.67</v>
       </c>
       <c r="S54" s="5">
         <f>IF(COUNT(R54:R55)=2,(R54/R55-1)*100,"")</f>
         <v/>
       </c>
       <c r="T54" s="5" t="n">
-        <v>111.3802</v>
+        <v>110.8017</v>
       </c>
       <c r="U54" s="5">
         <f>IF(COUNT(T54:T55)=2,(T54/T55-1)*100,"")</f>
         <v/>
       </c>
       <c r="V54" s="5" t="n">
-        <v>21.51</v>
+        <v>18.92</v>
       </c>
       <c r="W54" s="5">
         <f>IF(COUNT(V54:V55)=2,(V54/V55-1)*100,"")</f>
         <v/>
       </c>
       <c r="X54" s="5" t="n">
-        <v>39.6753</v>
+        <v>-12.0409</v>
       </c>
       <c r="Y54" s="5">
-        <f>IF(AND(X54&gt;$Y$11,C54&lt;=$Y$12),C53,"")</f>
+        <f>IF(AND(X54&gt;$Y$12,C54&lt;=$Y$13),C53,"")</f>
         <v/>
       </c>
       <c r="Z54" s="5">
-        <f>IF(AND(K54&lt;$Z$11,M54&gt;$Z$12),C53,"")</f>
+        <f>IF(AND(K54&lt;$Z$12,M54&gt;$Z$13),C53,"")</f>
         <v/>
       </c>
       <c r="AA54" s="5">
-        <f>IF(AND(G54&gt;$AA$11,I54&lt;$AA$12,K54&gt;$AA$12),C53,"")</f>
+        <f>IF(AND(G54&gt;$AA$12,I54&lt;$AA$13,K54&gt;$AA$11),C53,"")</f>
         <v/>
       </c>
       <c r="AB54" s="5">
@@ -6874,15 +6772,15 @@
         <v/>
       </c>
       <c r="AC54" s="5">
-        <f>IF(AND(S54&gt;$AC$11,U54&lt;$AC$12),E53,"")</f>
+        <f>IF(AND(S54&gt;$AC$12,U54&lt;$AC$13),E53,"")</f>
         <v/>
       </c>
       <c r="AD54" s="5">
-        <f>IF(AND(O54&lt;=$AD$11,E54&lt;$AD$12),E53,"")</f>
+        <f>IF(AND(O54&lt;=$AD$12,E54&lt;$AD$13),E53,"")</f>
         <v/>
       </c>
       <c r="AE54" s="5">
-        <f>IF(AND(Q54&gt;$AE$11,S54&gt;$AE$12),E53,"")</f>
+        <f>IF(AND(Q54&gt;$AE$12,S54&gt;$AE$13),E53,"")</f>
         <v/>
       </c>
       <c r="AF54" s="5">
@@ -6893,99 +6791,99 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026/06/04</t>
+          <t>2026/06/05</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>175.71</v>
+        <v>158.91</v>
       </c>
       <c r="C55" s="5">
         <f>IF(COUNT(B55:B56)=2,(B55/B56-1)*100,"")</f>
         <v/>
       </c>
       <c r="D55" s="5" t="n">
-        <v>188.65</v>
+        <v>178.71</v>
       </c>
       <c r="E55" s="5">
         <f>IF(COUNT(D55:D56)=2,(D55/D56-1)*100,"")</f>
         <v/>
       </c>
       <c r="F55" s="5" t="n">
-        <v>68.7427</v>
+        <v>64.256</v>
       </c>
       <c r="G55" s="5">
         <f>IF(COUNT(F55:F56)=2,(F55/F56-1)*100,"")</f>
         <v/>
       </c>
       <c r="H55" s="5" t="n">
-        <v>411.27</v>
+        <v>396.24</v>
       </c>
       <c r="I55" s="5">
         <f>IF(COUNT(H55:H56)=2,(H55/H56-1)*100,"")</f>
         <v/>
       </c>
       <c r="J55" s="5" t="n">
-        <v>79.07769999999999</v>
+        <v>78.6815</v>
       </c>
       <c r="K55" s="5">
         <f>IF(COUNT(J55:J56)=2,(J55/J56-1)*100,"")</f>
         <v/>
       </c>
       <c r="L55" s="5" t="n">
-        <v>107.9267</v>
+        <v>107.4056</v>
       </c>
       <c r="M55" s="5">
         <f>IF(COUNT(L55:L56)=2,(L55/L56-1)*100,"")</f>
         <v/>
       </c>
       <c r="N55" s="5" t="n">
-        <v>52.0078</v>
+        <v>52.1174</v>
       </c>
       <c r="O55" s="5">
         <f>IF(COUNT(N55:N56)=2,(N55/N56-1)*100,"")</f>
         <v/>
       </c>
       <c r="P55" s="5" t="n">
-        <v>57.35</v>
+        <v>57.31</v>
       </c>
       <c r="Q55" s="5">
         <f>IF(COUNT(P55:P56)=2,(P55/P56-1)*100,"")</f>
         <v/>
       </c>
       <c r="R55" s="5" t="n">
-        <v>86.40000000000001</v>
+        <v>78.84</v>
       </c>
       <c r="S55" s="5">
         <f>IF(COUNT(R55:R56)=2,(R55/R56-1)*100,"")</f>
         <v/>
       </c>
       <c r="T55" s="5" t="n">
-        <v>112.8165</v>
+        <v>111.3802</v>
       </c>
       <c r="U55" s="5">
         <f>IF(COUNT(T55:T56)=2,(T55/T56-1)*100,"")</f>
         <v/>
       </c>
       <c r="V55" s="5" t="n">
-        <v>15.4</v>
+        <v>21.51</v>
       </c>
       <c r="W55" s="5">
         <f>IF(COUNT(V55:V56)=2,(V55/V56-1)*100,"")</f>
         <v/>
       </c>
       <c r="X55" s="5" t="n">
-        <v>-4.1096</v>
+        <v>39.6753</v>
       </c>
       <c r="Y55" s="5">
-        <f>IF(AND(X55&gt;$Y$11,C55&lt;=$Y$12),C54,"")</f>
+        <f>IF(AND(X55&gt;$Y$12,C55&lt;=$Y$13),C54,"")</f>
         <v/>
       </c>
       <c r="Z55" s="5">
-        <f>IF(AND(K55&lt;$Z$11,M55&gt;$Z$12),C54,"")</f>
+        <f>IF(AND(K55&lt;$Z$12,M55&gt;$Z$13),C54,"")</f>
         <v/>
       </c>
       <c r="AA55" s="5">
-        <f>IF(AND(G55&gt;$AA$11,I55&lt;$AA$12,K55&gt;$AA$12),C54,"")</f>
+        <f>IF(AND(G55&gt;$AA$12,I55&lt;$AA$13,K55&gt;$AA$11),C54,"")</f>
         <v/>
       </c>
       <c r="AB55" s="5">
@@ -6993,15 +6891,15 @@
         <v/>
       </c>
       <c r="AC55" s="5">
-        <f>IF(AND(S55&gt;$AC$11,U55&lt;$AC$12),E54,"")</f>
+        <f>IF(AND(S55&gt;$AC$12,U55&lt;$AC$13),E54,"")</f>
         <v/>
       </c>
       <c r="AD55" s="5">
-        <f>IF(AND(O55&lt;=$AD$11,E55&lt;$AD$12),E54,"")</f>
+        <f>IF(AND(O55&lt;=$AD$12,E55&lt;$AD$13),E54,"")</f>
         <v/>
       </c>
       <c r="AE55" s="5">
-        <f>IF(AND(Q55&gt;$AE$11,S55&gt;$AE$12),E54,"")</f>
+        <f>IF(AND(Q55&gt;$AE$12,S55&gt;$AE$13),E54,"")</f>
         <v/>
       </c>
       <c r="AF55" s="5">
@@ -7012,99 +6910,99 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>2026/06/03</t>
+          <t>2026/06/04</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>177.54</v>
+        <v>175.71</v>
       </c>
       <c r="C56" s="5">
         <f>IF(COUNT(B56:B57)=2,(B56/B57-1)*100,"")</f>
         <v/>
       </c>
       <c r="D56" s="5" t="n">
-        <v>187.13</v>
+        <v>188.65</v>
       </c>
       <c r="E56" s="5">
         <f>IF(COUNT(D56:D57)=2,(D56/D57-1)*100,"")</f>
         <v/>
       </c>
       <c r="F56" s="5" t="n">
-        <v>69.55840000000001</v>
+        <v>68.7427</v>
       </c>
       <c r="G56" s="5">
         <f>IF(COUNT(F56:F57)=2,(F56/F57-1)*100,"")</f>
         <v/>
       </c>
       <c r="H56" s="5" t="n">
-        <v>407.87</v>
+        <v>411.27</v>
       </c>
       <c r="I56" s="5">
         <f>IF(COUNT(H56:H57)=2,(H56/H57-1)*100,"")</f>
         <v/>
       </c>
       <c r="J56" s="5" t="n">
-        <v>78.92910000000001</v>
+        <v>79.07769999999999</v>
       </c>
       <c r="K56" s="5">
         <f>IF(COUNT(J56:J57)=2,(J56/J57-1)*100,"")</f>
         <v/>
       </c>
       <c r="L56" s="5" t="n">
-        <v>107.9168</v>
+        <v>107.9267</v>
       </c>
       <c r="M56" s="5">
         <f>IF(COUNT(L56:L57)=2,(L56/L57-1)*100,"")</f>
         <v/>
       </c>
       <c r="N56" s="5" t="n">
-        <v>50.6924</v>
+        <v>52.0078</v>
       </c>
       <c r="O56" s="5">
         <f>IF(COUNT(N56:N57)=2,(N56/N57-1)*100,"")</f>
         <v/>
       </c>
       <c r="P56" s="5" t="n">
-        <v>57.34</v>
+        <v>57.35</v>
       </c>
       <c r="Q56" s="5">
         <f>IF(COUNT(P56:P57)=2,(P56/P57-1)*100,"")</f>
         <v/>
       </c>
       <c r="R56" s="5" t="n">
-        <v>85</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="S56" s="5">
         <f>IF(COUNT(R56:R57)=2,(R56/R57-1)*100,"")</f>
         <v/>
       </c>
       <c r="T56" s="5" t="n">
-        <v>111.7892</v>
+        <v>112.8165</v>
       </c>
       <c r="U56" s="5">
         <f>IF(COUNT(T56:T57)=2,(T56/T57-1)*100,"")</f>
         <v/>
       </c>
       <c r="V56" s="5" t="n">
-        <v>16.06</v>
+        <v>15.4</v>
       </c>
       <c r="W56" s="5">
         <f>IF(COUNT(V56:V57)=2,(V56/V57-1)*100,"")</f>
         <v/>
       </c>
       <c r="X56" s="5" t="n">
-        <v>1.8389</v>
+        <v>-4.1096</v>
       </c>
       <c r="Y56" s="5">
-        <f>IF(AND(X56&gt;$Y$11,C56&lt;=$Y$12),C55,"")</f>
+        <f>IF(AND(X56&gt;$Y$12,C56&lt;=$Y$13),C55,"")</f>
         <v/>
       </c>
       <c r="Z56" s="5">
-        <f>IF(AND(K56&lt;$Z$11,M56&gt;$Z$12),C55,"")</f>
+        <f>IF(AND(K56&lt;$Z$12,M56&gt;$Z$13),C55,"")</f>
         <v/>
       </c>
       <c r="AA56" s="5">
-        <f>IF(AND(G56&gt;$AA$11,I56&lt;$AA$12,K56&gt;$AA$12),C55,"")</f>
+        <f>IF(AND(G56&gt;$AA$12,I56&lt;$AA$13,K56&gt;$AA$11),C55,"")</f>
         <v/>
       </c>
       <c r="AB56" s="5">
@@ -7112,15 +7010,15 @@
         <v/>
       </c>
       <c r="AC56" s="5">
-        <f>IF(AND(S56&gt;$AC$11,U56&lt;$AC$12),E55,"")</f>
+        <f>IF(AND(S56&gt;$AC$12,U56&lt;$AC$13),E55,"")</f>
         <v/>
       </c>
       <c r="AD56" s="5">
-        <f>IF(AND(O56&lt;=$AD$11,E56&lt;$AD$12),E55,"")</f>
+        <f>IF(AND(O56&lt;=$AD$12,E56&lt;$AD$13),E55,"")</f>
         <v/>
       </c>
       <c r="AE56" s="5">
-        <f>IF(AND(Q56&gt;$AE$11,S56&gt;$AE$12),E55,"")</f>
+        <f>IF(AND(Q56&gt;$AE$12,S56&gt;$AE$13),E55,"")</f>
         <v/>
       </c>
       <c r="AF56" s="5">
@@ -7131,99 +7029,99 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2026/06/03</t>
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>178.58</v>
+        <v>177.54</v>
       </c>
       <c r="C57" s="5">
         <f>IF(COUNT(B57:B58)=2,(B57/B58-1)*100,"")</f>
         <v/>
       </c>
       <c r="D57" s="5" t="n">
-        <v>189.9</v>
+        <v>187.13</v>
       </c>
       <c r="E57" s="5">
         <f>IF(COUNT(D57:D58)=2,(D57/D58-1)*100,"")</f>
         <v/>
       </c>
       <c r="F57" s="5" t="n">
-        <v>70.43389999999999</v>
+        <v>69.55840000000001</v>
       </c>
       <c r="G57" s="5">
         <f>IF(COUNT(F57:F58)=2,(F57/F58-1)*100,"")</f>
         <v/>
       </c>
       <c r="H57" s="5" t="n">
-        <v>411.95</v>
+        <v>407.87</v>
       </c>
       <c r="I57" s="5">
         <f>IF(COUNT(H57:H58)=2,(H57/H58-1)*100,"")</f>
         <v/>
       </c>
       <c r="J57" s="5" t="n">
-        <v>79.14709999999999</v>
+        <v>78.92910000000001</v>
       </c>
       <c r="K57" s="5">
         <f>IF(COUNT(J57:J58)=2,(J57/J58-1)*100,"")</f>
         <v/>
       </c>
       <c r="L57" s="5" t="n">
-        <v>108.1135</v>
+        <v>107.9168</v>
       </c>
       <c r="M57" s="5">
         <f>IF(COUNT(L57:L58)=2,(L57/L58-1)*100,"")</f>
         <v/>
       </c>
       <c r="N57" s="5" t="n">
-        <v>51.2804</v>
+        <v>50.6924</v>
       </c>
       <c r="O57" s="5">
         <f>IF(COUNT(N57:N58)=2,(N57/N58-1)*100,"")</f>
         <v/>
       </c>
       <c r="P57" s="5" t="n">
-        <v>57.43</v>
+        <v>57.34</v>
       </c>
       <c r="Q57" s="5">
         <f>IF(COUNT(P57:P58)=2,(P57/P58-1)*100,"")</f>
         <v/>
       </c>
       <c r="R57" s="5" t="n">
-        <v>88.05</v>
+        <v>85</v>
       </c>
       <c r="S57" s="5">
         <f>IF(COUNT(R57:R58)=2,(R57/R58-1)*100,"")</f>
         <v/>
       </c>
       <c r="T57" s="5" t="n">
-        <v>113.2753</v>
+        <v>111.7892</v>
       </c>
       <c r="U57" s="5">
         <f>IF(COUNT(T57:T58)=2,(T57/T58-1)*100,"")</f>
         <v/>
       </c>
       <c r="V57" s="5" t="n">
-        <v>15.77</v>
+        <v>16.06</v>
       </c>
       <c r="W57" s="5">
         <f>IF(COUNT(V57:V58)=2,(V57/V58-1)*100,"")</f>
         <v/>
       </c>
       <c r="X57" s="5" t="n">
-        <v>-1.7445</v>
+        <v>1.8389</v>
       </c>
       <c r="Y57" s="5">
-        <f>IF(AND(X57&gt;$Y$11,C57&lt;=$Y$12),C56,"")</f>
+        <f>IF(AND(X57&gt;$Y$12,C57&lt;=$Y$13),C56,"")</f>
         <v/>
       </c>
       <c r="Z57" s="5">
-        <f>IF(AND(K57&lt;$Z$11,M57&gt;$Z$12),C56,"")</f>
+        <f>IF(AND(K57&lt;$Z$12,M57&gt;$Z$13),C56,"")</f>
         <v/>
       </c>
       <c r="AA57" s="5">
-        <f>IF(AND(G57&gt;$AA$11,I57&lt;$AA$12,K57&gt;$AA$12),C56,"")</f>
+        <f>IF(AND(G57&gt;$AA$12,I57&lt;$AA$13,K57&gt;$AA$11),C56,"")</f>
         <v/>
       </c>
       <c r="AB57" s="5">
@@ -7231,15 +7129,15 @@
         <v/>
       </c>
       <c r="AC57" s="5">
-        <f>IF(AND(S57&gt;$AC$11,U57&lt;$AC$12),E56,"")</f>
+        <f>IF(AND(S57&gt;$AC$12,U57&lt;$AC$13),E56,"")</f>
         <v/>
       </c>
       <c r="AD57" s="5">
-        <f>IF(AND(O57&lt;=$AD$11,E57&lt;$AD$12),E56,"")</f>
+        <f>IF(AND(O57&lt;=$AD$12,E57&lt;$AD$13),E56,"")</f>
         <v/>
       </c>
       <c r="AE57" s="5">
-        <f>IF(AND(Q57&gt;$AE$11,S57&gt;$AE$12),E56,"")</f>
+        <f>IF(AND(Q57&gt;$AE$12,S57&gt;$AE$13),E56,"")</f>
         <v/>
       </c>
       <c r="AF57" s="5">
@@ -7250,99 +7148,99 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/06/02</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>176.92</v>
+        <v>178.58</v>
       </c>
       <c r="C58" s="5">
         <f>IF(COUNT(B58:B59)=2,(B58/B59-1)*100,"")</f>
         <v/>
       </c>
       <c r="D58" s="5" t="n">
-        <v>189.42</v>
+        <v>189.9</v>
       </c>
       <c r="E58" s="5">
         <f>IF(COUNT(D58:D59)=2,(D58/D59-1)*100,"")</f>
         <v/>
       </c>
       <c r="F58" s="5" t="n">
-        <v>69.7176</v>
+        <v>70.43389999999999</v>
       </c>
       <c r="G58" s="5">
         <f>IF(COUNT(F58:F59)=2,(F58/F59-1)*100,"")</f>
         <v/>
       </c>
       <c r="H58" s="5" t="n">
-        <v>411.26</v>
+        <v>411.95</v>
       </c>
       <c r="I58" s="5">
         <f>IF(COUNT(H58:H59)=2,(H58/H59-1)*100,"")</f>
         <v/>
       </c>
       <c r="J58" s="5" t="n">
-        <v>79.08759999999999</v>
+        <v>79.14709999999999</v>
       </c>
       <c r="K58" s="5">
         <f>IF(COUNT(J58:J59)=2,(J58/J59-1)*100,"")</f>
         <v/>
       </c>
       <c r="L58" s="5" t="n">
-        <v>108.1233</v>
+        <v>108.1135</v>
       </c>
       <c r="M58" s="5">
         <f>IF(COUNT(L58:L59)=2,(L58/L59-1)*100,"")</f>
         <v/>
       </c>
       <c r="N58" s="5" t="n">
-        <v>51.2505</v>
+        <v>51.2804</v>
       </c>
       <c r="O58" s="5">
         <f>IF(COUNT(N58:N59)=2,(N58/N59-1)*100,"")</f>
         <v/>
       </c>
       <c r="P58" s="5" t="n">
-        <v>57.51</v>
+        <v>57.43</v>
       </c>
       <c r="Q58" s="5">
         <f>IF(COUNT(P58:P59)=2,(P58/P59-1)*100,"")</f>
         <v/>
       </c>
       <c r="R58" s="5" t="n">
-        <v>86.68000000000001</v>
+        <v>88.05</v>
       </c>
       <c r="S58" s="5">
         <f>IF(COUNT(R58:R59)=2,(R58/R59-1)*100,"")</f>
         <v/>
       </c>
       <c r="T58" s="5" t="n">
-        <v>115.31</v>
+        <v>113.2753</v>
       </c>
       <c r="U58" s="5">
         <f>IF(COUNT(T58:T59)=2,(T58/T59-1)*100,"")</f>
         <v/>
       </c>
       <c r="V58" s="5" t="n">
-        <v>16.05</v>
+        <v>15.77</v>
       </c>
       <c r="W58" s="5">
         <f>IF(COUNT(V58:V59)=2,(V58/V59-1)*100,"")</f>
         <v/>
       </c>
       <c r="X58" s="5" t="n">
-        <v>4.765</v>
+        <v>-1.7445</v>
       </c>
       <c r="Y58" s="5">
-        <f>IF(AND(X58&gt;$Y$11,C58&lt;=$Y$12),C57,"")</f>
+        <f>IF(AND(X58&gt;$Y$12,C58&lt;=$Y$13),C57,"")</f>
         <v/>
       </c>
       <c r="Z58" s="5">
-        <f>IF(AND(K58&lt;$Z$11,M58&gt;$Z$12),C57,"")</f>
+        <f>IF(AND(K58&lt;$Z$12,M58&gt;$Z$13),C57,"")</f>
         <v/>
       </c>
       <c r="AA58" s="5">
-        <f>IF(AND(G58&gt;$AA$11,I58&lt;$AA$12,K58&gt;$AA$12),C57,"")</f>
+        <f>IF(AND(G58&gt;$AA$12,I58&lt;$AA$13,K58&gt;$AA$11),C57,"")</f>
         <v/>
       </c>
       <c r="AB58" s="5">
@@ -7350,15 +7248,15 @@
         <v/>
       </c>
       <c r="AC58" s="5">
-        <f>IF(AND(S58&gt;$AC$11,U58&lt;$AC$12),E57,"")</f>
+        <f>IF(AND(S58&gt;$AC$12,U58&lt;$AC$13),E57,"")</f>
         <v/>
       </c>
       <c r="AD58" s="5">
-        <f>IF(AND(O58&lt;=$AD$11,E58&lt;$AD$12),E57,"")</f>
+        <f>IF(AND(O58&lt;=$AD$12,E58&lt;$AD$13),E57,"")</f>
         <v/>
       </c>
       <c r="AE58" s="5">
-        <f>IF(AND(Q58&gt;$AE$11,S58&gt;$AE$12),E57,"")</f>
+        <f>IF(AND(Q58&gt;$AE$12,S58&gt;$AE$13),E57,"")</f>
         <v/>
       </c>
       <c r="AF58" s="5">
@@ -7369,99 +7267,99 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/06/01</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>174.92</v>
+        <v>176.92</v>
       </c>
       <c r="C59" s="5">
         <f>IF(COUNT(B59:B60)=2,(B59/B60-1)*100,"")</f>
         <v/>
       </c>
       <c r="D59" s="5" t="n">
-        <v>188.5</v>
+        <v>189.42</v>
       </c>
       <c r="E59" s="5">
         <f>IF(COUNT(D59:D60)=2,(D59/D60-1)*100,"")</f>
         <v/>
       </c>
       <c r="F59" s="5" t="n">
-        <v>68.2453</v>
+        <v>69.7176</v>
       </c>
       <c r="G59" s="5">
         <f>IF(COUNT(F59:F60)=2,(F59/F60-1)*100,"")</f>
         <v/>
       </c>
       <c r="H59" s="5" t="n">
-        <v>417.12</v>
+        <v>411.26</v>
       </c>
       <c r="I59" s="5">
         <f>IF(COUNT(H59:H60)=2,(H59/H60-1)*100,"")</f>
         <v/>
       </c>
       <c r="J59" s="5" t="n">
-        <v>79.1481</v>
+        <v>79.08759999999999</v>
       </c>
       <c r="K59" s="5">
         <f>IF(COUNT(J59:J60)=2,(J59/J60-1)*100,"")</f>
         <v/>
       </c>
       <c r="L59" s="5" t="n">
-        <v>108.0761</v>
+        <v>108.1233</v>
       </c>
       <c r="M59" s="5">
         <f>IF(COUNT(L59:L60)=2,(L59/L60-1)*100,"")</f>
         <v/>
       </c>
       <c r="N59" s="5" t="n">
-        <v>51.3999</v>
+        <v>51.2505</v>
       </c>
       <c r="O59" s="5">
         <f>IF(COUNT(N59:N60)=2,(N59/N60-1)*100,"")</f>
         <v/>
       </c>
       <c r="P59" s="5" t="n">
-        <v>57.62</v>
+        <v>57.51</v>
       </c>
       <c r="Q59" s="5">
         <f>IF(COUNT(P59:P60)=2,(P59/P60-1)*100,"")</f>
         <v/>
       </c>
       <c r="R59" s="5" t="n">
-        <v>89.48999999999999</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="S59" s="5">
         <f>IF(COUNT(R59:R60)=2,(R59/R60-1)*100,"")</f>
         <v/>
       </c>
       <c r="T59" s="5" t="n">
-        <v>115.3898</v>
+        <v>115.31</v>
       </c>
       <c r="U59" s="5">
         <f>IF(COUNT(T59:T60)=2,(T59/T60-1)*100,"")</f>
         <v/>
       </c>
       <c r="V59" s="5" t="n">
-        <v>15.32</v>
+        <v>16.05</v>
       </c>
       <c r="W59" s="5">
         <f>IF(COUNT(V59:V60)=2,(V59/V60-1)*100,"")</f>
         <v/>
       </c>
       <c r="X59" s="5" t="n">
-        <v>-2.6684</v>
+        <v>4.765</v>
       </c>
       <c r="Y59" s="5">
-        <f>IF(AND(X59&gt;$Y$11,C59&lt;=$Y$12),C58,"")</f>
+        <f>IF(AND(X59&gt;$Y$12,C59&lt;=$Y$13),C58,"")</f>
         <v/>
       </c>
       <c r="Z59" s="5">
-        <f>IF(AND(K59&lt;$Z$11,M59&gt;$Z$12),C58,"")</f>
+        <f>IF(AND(K59&lt;$Z$12,M59&gt;$Z$13),C58,"")</f>
         <v/>
       </c>
       <c r="AA59" s="5">
-        <f>IF(AND(G59&gt;$AA$11,I59&lt;$AA$12,K59&gt;$AA$12),C58,"")</f>
+        <f>IF(AND(G59&gt;$AA$12,I59&lt;$AA$13,K59&gt;$AA$11),C58,"")</f>
         <v/>
       </c>
       <c r="AB59" s="5">
@@ -7469,15 +7367,15 @@
         <v/>
       </c>
       <c r="AC59" s="5">
-        <f>IF(AND(S59&gt;$AC$11,U59&lt;$AC$12),E58,"")</f>
+        <f>IF(AND(S59&gt;$AC$12,U59&lt;$AC$13),E58,"")</f>
         <v/>
       </c>
       <c r="AD59" s="5">
-        <f>IF(AND(O59&lt;=$AD$11,E59&lt;$AD$12),E58,"")</f>
+        <f>IF(AND(O59&lt;=$AD$12,E59&lt;$AD$13),E58,"")</f>
         <v/>
       </c>
       <c r="AE59" s="5">
-        <f>IF(AND(Q59&gt;$AE$11,S59&gt;$AE$12),E58,"")</f>
+        <f>IF(AND(Q59&gt;$AE$12,S59&gt;$AE$13),E58,"")</f>
         <v/>
       </c>
       <c r="AF59" s="5">
@@ -7488,99 +7386,99 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>2026/05/28</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>173.68</v>
+        <v>174.92</v>
       </c>
       <c r="C60" s="5">
         <f>IF(COUNT(B60:B61)=2,(B60/B61-1)*100,"")</f>
         <v/>
       </c>
       <c r="D60" s="5" t="n">
-        <v>187.68</v>
+        <v>188.5</v>
       </c>
       <c r="E60" s="5">
         <f>IF(COUNT(D60:D61)=2,(D60/D61-1)*100,"")</f>
         <v/>
       </c>
       <c r="F60" s="5" t="n">
-        <v>68.2552</v>
+        <v>68.2453</v>
       </c>
       <c r="G60" s="5">
         <f>IF(COUNT(F60:F61)=2,(F60/F61-1)*100,"")</f>
         <v/>
       </c>
       <c r="H60" s="5" t="n">
-        <v>412.77</v>
+        <v>417.12</v>
       </c>
       <c r="I60" s="5">
         <f>IF(COUNT(H60:H61)=2,(H60/H61-1)*100,"")</f>
         <v/>
       </c>
       <c r="J60" s="5" t="n">
-        <v>79.0692</v>
+        <v>79.1481</v>
       </c>
       <c r="K60" s="5">
         <f>IF(COUNT(J60:J61)=2,(J60/J61-1)*100,"")</f>
         <v/>
       </c>
       <c r="L60" s="5" t="n">
-        <v>108.047</v>
+        <v>108.0761</v>
       </c>
       <c r="M60" s="5">
         <f>IF(COUNT(L60:L61)=2,(L60/L61-1)*100,"")</f>
         <v/>
       </c>
       <c r="N60" s="5" t="n">
-        <v>51.091</v>
+        <v>51.3999</v>
       </c>
       <c r="O60" s="5">
         <f>IF(COUNT(N60:N61)=2,(N60/N61-1)*100,"")</f>
         <v/>
       </c>
       <c r="P60" s="5" t="n">
-        <v>57.65</v>
+        <v>57.62</v>
       </c>
       <c r="Q60" s="5">
         <f>IF(COUNT(P60:P61)=2,(P60/P61-1)*100,"")</f>
         <v/>
       </c>
       <c r="R60" s="5" t="n">
-        <v>87.18000000000001</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="S60" s="5">
         <f>IF(COUNT(R60:R61)=2,(R60/R61-1)*100,"")</f>
         <v/>
       </c>
       <c r="T60" s="5" t="n">
-        <v>116.3673</v>
+        <v>115.3898</v>
       </c>
       <c r="U60" s="5">
         <f>IF(COUNT(T60:T61)=2,(T60/T61-1)*100,"")</f>
         <v/>
       </c>
       <c r="V60" s="5" t="n">
-        <v>15.74</v>
+        <v>15.32</v>
       </c>
       <c r="W60" s="5">
         <f>IF(COUNT(V60:V61)=2,(V60/V61-1)*100,"")</f>
         <v/>
       </c>
       <c r="X60" s="5" t="n">
-        <v>-3.3763</v>
+        <v>-2.6684</v>
       </c>
       <c r="Y60" s="5">
-        <f>IF(AND(X60&gt;$Y$11,C60&lt;=$Y$12),C59,"")</f>
+        <f>IF(AND(X60&gt;$Y$12,C60&lt;=$Y$13),C59,"")</f>
         <v/>
       </c>
       <c r="Z60" s="5">
-        <f>IF(AND(K60&lt;$Z$11,M60&gt;$Z$12),C59,"")</f>
+        <f>IF(AND(K60&lt;$Z$12,M60&gt;$Z$13),C59,"")</f>
         <v/>
       </c>
       <c r="AA60" s="5">
-        <f>IF(AND(G60&gt;$AA$11,I60&lt;$AA$12,K60&gt;$AA$12),C59,"")</f>
+        <f>IF(AND(G60&gt;$AA$12,I60&lt;$AA$13,K60&gt;$AA$11),C59,"")</f>
         <v/>
       </c>
       <c r="AB60" s="5">
@@ -7588,15 +7486,15 @@
         <v/>
       </c>
       <c r="AC60" s="5">
-        <f>IF(AND(S60&gt;$AC$11,U60&lt;$AC$12),E59,"")</f>
+        <f>IF(AND(S60&gt;$AC$12,U60&lt;$AC$13),E59,"")</f>
         <v/>
       </c>
       <c r="AD60" s="5">
-        <f>IF(AND(O60&lt;=$AD$11,E60&lt;$AD$12),E59,"")</f>
+        <f>IF(AND(O60&lt;=$AD$12,E60&lt;$AD$13),E59,"")</f>
         <v/>
       </c>
       <c r="AE60" s="5">
-        <f>IF(AND(Q60&gt;$AE$11,S60&gt;$AE$12),E59,"")</f>
+        <f>IF(AND(Q60&gt;$AE$12,S60&gt;$AE$13),E59,"")</f>
         <v/>
       </c>
       <c r="AF60" s="5">
@@ -7607,99 +7505,99 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>2026/05/27</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>170.84</v>
+        <v>173.68</v>
       </c>
       <c r="C61" s="5">
         <f>IF(COUNT(B61:B62)=2,(B61/B62-1)*100,"")</f>
         <v/>
       </c>
       <c r="D61" s="5" t="n">
-        <v>185.59</v>
+        <v>187.68</v>
       </c>
       <c r="E61" s="5">
         <f>IF(COUNT(D61:D62)=2,(D61/D62-1)*100,"")</f>
         <v/>
       </c>
       <c r="F61" s="5" t="n">
-        <v>68.0364</v>
+        <v>68.2552</v>
       </c>
       <c r="G61" s="5">
         <f>IF(COUNT(F61:F62)=2,(F61/F62-1)*100,"")</f>
         <v/>
       </c>
       <c r="H61" s="5" t="n">
-        <v>408.49</v>
+        <v>412.77</v>
       </c>
       <c r="I61" s="5">
         <f>IF(COUNT(H61:H62)=2,(H61/H62-1)*100,"")</f>
         <v/>
       </c>
       <c r="J61" s="5" t="n">
-        <v>78.97069999999999</v>
+        <v>79.0692</v>
       </c>
       <c r="K61" s="5">
         <f>IF(COUNT(J61:J62)=2,(J61/J62-1)*100,"")</f>
         <v/>
       </c>
       <c r="L61" s="5" t="n">
-        <v>107.7554</v>
+        <v>108.047</v>
       </c>
       <c r="M61" s="5">
         <f>IF(COUNT(L61:L62)=2,(L61/L62-1)*100,"")</f>
         <v/>
       </c>
       <c r="N61" s="5" t="n">
-        <v>51.2405</v>
+        <v>51.091</v>
       </c>
       <c r="O61" s="5">
         <f>IF(COUNT(N61:N62)=2,(N61/N62-1)*100,"")</f>
         <v/>
       </c>
       <c r="P61" s="5" t="n">
-        <v>57.54</v>
+        <v>57.65</v>
       </c>
       <c r="Q61" s="5">
         <f>IF(COUNT(P61:P62)=2,(P61/P62-1)*100,"")</f>
         <v/>
       </c>
       <c r="R61" s="5" t="n">
-        <v>85.44</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="S61" s="5">
         <f>IF(COUNT(R61:R62)=2,(R61/R62-1)*100,"")</f>
         <v/>
       </c>
       <c r="T61" s="5" t="n">
-        <v>115.9583</v>
+        <v>116.3673</v>
       </c>
       <c r="U61" s="5">
         <f>IF(COUNT(T61:T62)=2,(T61/T62-1)*100,"")</f>
         <v/>
       </c>
       <c r="V61" s="5" t="n">
-        <v>16.29</v>
+        <v>15.74</v>
       </c>
       <c r="W61" s="5">
         <f>IF(COUNT(V61:V62)=2,(V61/V62-1)*100,"")</f>
         <v/>
       </c>
       <c r="X61" s="5" t="n">
-        <v>-4.2328</v>
+        <v>-3.3763</v>
       </c>
       <c r="Y61" s="5">
-        <f>IF(AND(X61&gt;$Y$11,C61&lt;=$Y$12),C60,"")</f>
+        <f>IF(AND(X61&gt;$Y$12,C61&lt;=$Y$13),C60,"")</f>
         <v/>
       </c>
       <c r="Z61" s="5">
-        <f>IF(AND(K61&lt;$Z$11,M61&gt;$Z$12),C60,"")</f>
+        <f>IF(AND(K61&lt;$Z$12,M61&gt;$Z$13),C60,"")</f>
         <v/>
       </c>
       <c r="AA61" s="5">
-        <f>IF(AND(G61&gt;$AA$11,I61&lt;$AA$12,K61&gt;$AA$12),C60,"")</f>
+        <f>IF(AND(G61&gt;$AA$12,I61&lt;$AA$13,K61&gt;$AA$11),C60,"")</f>
         <v/>
       </c>
       <c r="AB61" s="5">
@@ -7707,15 +7605,15 @@
         <v/>
       </c>
       <c r="AC61" s="5">
-        <f>IF(AND(S61&gt;$AC$11,U61&lt;$AC$12),E60,"")</f>
+        <f>IF(AND(S61&gt;$AC$12,U61&lt;$AC$13),E60,"")</f>
         <v/>
       </c>
       <c r="AD61" s="5">
-        <f>IF(AND(O61&lt;=$AD$11,E61&lt;$AD$12),E60,"")</f>
+        <f>IF(AND(O61&lt;=$AD$12,E61&lt;$AD$13),E60,"")</f>
         <v/>
       </c>
       <c r="AE61" s="5">
-        <f>IF(AND(Q61&gt;$AE$11,S61&gt;$AE$12),E60,"")</f>
+        <f>IF(AND(Q61&gt;$AE$12,S61&gt;$AE$13),E60,"")</f>
         <v/>
       </c>
       <c r="AF61" s="5">
@@ -7726,99 +7624,99 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2026/05/27</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>171.19</v>
+        <v>170.84</v>
       </c>
       <c r="C62" s="5">
         <f>IF(COUNT(B62:B63)=2,(B62/B63-1)*100,"")</f>
         <v/>
       </c>
       <c r="D62" s="5" t="n">
-        <v>185.57</v>
+        <v>185.59</v>
       </c>
       <c r="E62" s="5">
         <f>IF(COUNT(D62:D63)=2,(D62/D63-1)*100,"")</f>
         <v/>
       </c>
       <c r="F62" s="5" t="n">
-        <v>68.0463</v>
+        <v>68.0364</v>
       </c>
       <c r="G62" s="5">
         <f>IF(COUNT(F62:F63)=2,(F62/F63-1)*100,"")</f>
         <v/>
       </c>
       <c r="H62" s="5" t="n">
-        <v>414</v>
+        <v>408.49</v>
       </c>
       <c r="I62" s="5">
         <f>IF(COUNT(H62:H63)=2,(H62/H63-1)*100,"")</f>
         <v/>
       </c>
       <c r="J62" s="5" t="n">
-        <v>79.01990000000001</v>
+        <v>78.97069999999999</v>
       </c>
       <c r="K62" s="5">
         <f>IF(COUNT(J62:J63)=2,(J62/J63-1)*100,"")</f>
         <v/>
       </c>
       <c r="L62" s="5" t="n">
-        <v>107.6971</v>
+        <v>107.7554</v>
       </c>
       <c r="M62" s="5">
         <f>IF(COUNT(L62:L63)=2,(L62/L63-1)*100,"")</f>
         <v/>
       </c>
       <c r="N62" s="5" t="n">
-        <v>51.669</v>
+        <v>51.2405</v>
       </c>
       <c r="O62" s="5">
         <f>IF(COUNT(N62:N63)=2,(N62/N63-1)*100,"")</f>
         <v/>
       </c>
       <c r="P62" s="5" t="n">
-        <v>57.63</v>
+        <v>57.54</v>
       </c>
       <c r="Q62" s="5">
         <f>IF(COUNT(P62:P63)=2,(P62/P63-1)*100,"")</f>
         <v/>
       </c>
       <c r="R62" s="5" t="n">
-        <v>88.5</v>
+        <v>85.44</v>
       </c>
       <c r="S62" s="5">
         <f>IF(COUNT(R62:R63)=2,(R62/R63-1)*100,"")</f>
         <v/>
       </c>
       <c r="T62" s="5" t="n">
-        <v>115.2502</v>
+        <v>115.9583</v>
       </c>
       <c r="U62" s="5">
         <f>IF(COUNT(T62:T63)=2,(T62/T63-1)*100,"")</f>
         <v/>
       </c>
       <c r="V62" s="5" t="n">
-        <v>17.01</v>
+        <v>16.29</v>
       </c>
       <c r="W62" s="5">
         <f>IF(COUNT(V62:V63)=2,(V62/V63-1)*100,"")</f>
         <v/>
       </c>
       <c r="X62" s="5" t="n">
-        <v>1.8563</v>
+        <v>-4.2328</v>
       </c>
       <c r="Y62" s="5">
-        <f>IF(AND(X62&gt;$Y$11,C62&lt;=$Y$12),C61,"")</f>
+        <f>IF(AND(X62&gt;$Y$12,C62&lt;=$Y$13),C61,"")</f>
         <v/>
       </c>
       <c r="Z62" s="5">
-        <f>IF(AND(K62&lt;$Z$11,M62&gt;$Z$12),C61,"")</f>
+        <f>IF(AND(K62&lt;$Z$12,M62&gt;$Z$13),C61,"")</f>
         <v/>
       </c>
       <c r="AA62" s="5">
-        <f>IF(AND(G62&gt;$AA$11,I62&lt;$AA$12,K62&gt;$AA$12),C61,"")</f>
+        <f>IF(AND(G62&gt;$AA$12,I62&lt;$AA$13,K62&gt;$AA$11),C61,"")</f>
         <v/>
       </c>
       <c r="AB62" s="5">
@@ -7826,15 +7724,15 @@
         <v/>
       </c>
       <c r="AC62" s="5">
-        <f>IF(AND(S62&gt;$AC$11,U62&lt;$AC$12),E61,"")</f>
+        <f>IF(AND(S62&gt;$AC$12,U62&lt;$AC$13),E61,"")</f>
         <v/>
       </c>
       <c r="AD62" s="5">
-        <f>IF(AND(O62&lt;=$AD$11,E62&lt;$AD$12),E61,"")</f>
+        <f>IF(AND(O62&lt;=$AD$12,E62&lt;$AD$13),E61,"")</f>
         <v/>
       </c>
       <c r="AE62" s="5">
-        <f>IF(AND(Q62&gt;$AE$11,S62&gt;$AE$12),E61,"")</f>
+        <f>IF(AND(Q62&gt;$AE$12,S62&gt;$AE$13),E61,"")</f>
         <v/>
       </c>
       <c r="AF62" s="5">
@@ -7845,99 +7743,99 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>2026/05/22</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>165.46</v>
+        <v>171.19</v>
       </c>
       <c r="C63" s="5">
         <f>IF(COUNT(B63:B64)=2,(B63/B64-1)*100,"")</f>
         <v/>
       </c>
       <c r="D63" s="5" t="n">
-        <v>183.39</v>
+        <v>185.57</v>
       </c>
       <c r="E63" s="5">
         <f>IF(COUNT(D63:D64)=2,(D63/D64-1)*100,"")</f>
         <v/>
       </c>
       <c r="F63" s="5" t="n">
-        <v>65.5393</v>
+        <v>68.0463</v>
       </c>
       <c r="G63" s="5">
         <f>IF(COUNT(F63:F64)=2,(F63/F64-1)*100,"")</f>
         <v/>
       </c>
       <c r="H63" s="5" t="n">
-        <v>413.82</v>
+        <v>414</v>
       </c>
       <c r="I63" s="5">
         <f>IF(COUNT(H63:H64)=2,(H63/H64-1)*100,"")</f>
         <v/>
       </c>
       <c r="J63" s="5" t="n">
-        <v>78.7539</v>
+        <v>79.01990000000001</v>
       </c>
       <c r="K63" s="5">
         <f>IF(COUNT(J63:J64)=2,(J63/J64-1)*100,"")</f>
         <v/>
       </c>
       <c r="L63" s="5" t="n">
-        <v>107.2695</v>
+        <v>107.6971</v>
       </c>
       <c r="M63" s="5">
         <f>IF(COUNT(L63:L64)=2,(L63/L64-1)*100,"")</f>
         <v/>
       </c>
       <c r="N63" s="5" t="n">
-        <v>51.7587</v>
+        <v>51.669</v>
       </c>
       <c r="O63" s="5">
         <f>IF(COUNT(N63:N64)=2,(N63/N64-1)*100,"")</f>
         <v/>
       </c>
       <c r="P63" s="5" t="n">
-        <v>57.7</v>
+        <v>57.63</v>
       </c>
       <c r="Q63" s="5">
         <f>IF(COUNT(P63:P64)=2,(P63/P64-1)*100,"")</f>
         <v/>
       </c>
       <c r="R63" s="5" t="n">
-        <v>85.02</v>
+        <v>88.5</v>
       </c>
       <c r="S63" s="5">
         <f>IF(COUNT(R63:R64)=2,(R63/R64-1)*100,"")</f>
         <v/>
       </c>
       <c r="T63" s="5" t="n">
-        <v>115.1604</v>
+        <v>115.2502</v>
       </c>
       <c r="U63" s="5">
         <f>IF(COUNT(T63:T64)=2,(T63/T64-1)*100,"")</f>
         <v/>
       </c>
       <c r="V63" s="5" t="n">
-        <v>16.7</v>
+        <v>17.01</v>
       </c>
       <c r="W63" s="5">
         <f>IF(COUNT(V63:V64)=2,(V63/V64-1)*100,"")</f>
         <v/>
       </c>
       <c r="X63" s="5" t="n">
-        <v>-0.358</v>
+        <v>1.8563</v>
       </c>
       <c r="Y63" s="5">
-        <f>IF(AND(X63&gt;$Y$11,C63&lt;=$Y$12),C62,"")</f>
+        <f>IF(AND(X63&gt;$Y$12,C63&lt;=$Y$13),C62,"")</f>
         <v/>
       </c>
       <c r="Z63" s="5">
-        <f>IF(AND(K63&lt;$Z$11,M63&gt;$Z$12),C62,"")</f>
+        <f>IF(AND(K63&lt;$Z$12,M63&gt;$Z$13),C62,"")</f>
         <v/>
       </c>
       <c r="AA63" s="5">
-        <f>IF(AND(G63&gt;$AA$11,I63&lt;$AA$12,K63&gt;$AA$12),C62,"")</f>
+        <f>IF(AND(G63&gt;$AA$12,I63&lt;$AA$13,K63&gt;$AA$11),C62,"")</f>
         <v/>
       </c>
       <c r="AB63" s="5">
@@ -7945,15 +7843,15 @@
         <v/>
       </c>
       <c r="AC63" s="5">
-        <f>IF(AND(S63&gt;$AC$11,U63&lt;$AC$12),E62,"")</f>
+        <f>IF(AND(S63&gt;$AC$12,U63&lt;$AC$13),E62,"")</f>
         <v/>
       </c>
       <c r="AD63" s="5">
-        <f>IF(AND(O63&lt;=$AD$11,E63&lt;$AD$12),E62,"")</f>
+        <f>IF(AND(O63&lt;=$AD$12,E63&lt;$AD$13),E62,"")</f>
         <v/>
       </c>
       <c r="AE63" s="5">
-        <f>IF(AND(Q63&gt;$AE$11,S63&gt;$AE$12),E62,"")</f>
+        <f>IF(AND(Q63&gt;$AE$12,S63&gt;$AE$13),E62,"")</f>
         <v/>
       </c>
       <c r="AF63" s="5">
@@ -7964,99 +7862,99 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>2026/05/21</t>
+          <t>2026/05/22</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>164.1</v>
+        <v>165.46</v>
       </c>
       <c r="C64" s="5">
         <f>IF(COUNT(B64:B65)=2,(B64/B65-1)*100,"")</f>
         <v/>
       </c>
       <c r="D64" s="5" t="n">
-        <v>182.04</v>
+        <v>183.39</v>
       </c>
       <c r="E64" s="5">
         <f>IF(COUNT(D64:D65)=2,(D64/D65-1)*100,"")</f>
         <v/>
       </c>
       <c r="F64" s="5" t="n">
-        <v>65.68859999999999</v>
+        <v>65.5393</v>
       </c>
       <c r="G64" s="5">
         <f>IF(COUNT(F64:F65)=2,(F64/F65-1)*100,"")</f>
         <v/>
       </c>
       <c r="H64" s="5" t="n">
-        <v>416.99</v>
+        <v>413.82</v>
       </c>
       <c r="I64" s="5">
         <f>IF(COUNT(H64:H65)=2,(H64/H65-1)*100,"")</f>
         <v/>
       </c>
       <c r="J64" s="5" t="n">
-        <v>78.744</v>
+        <v>78.7539</v>
       </c>
       <c r="K64" s="5">
         <f>IF(COUNT(J64:J65)=2,(J64/J65-1)*100,"")</f>
         <v/>
       </c>
       <c r="L64" s="5" t="n">
-        <v>107.2598</v>
+        <v>107.2695</v>
       </c>
       <c r="M64" s="5">
         <f>IF(COUNT(L64:L65)=2,(L64/L65-1)*100,"")</f>
         <v/>
       </c>
       <c r="N64" s="5" t="n">
-        <v>51.5494</v>
+        <v>51.7587</v>
       </c>
       <c r="O64" s="5">
         <f>IF(COUNT(N64:N65)=2,(N64/N65-1)*100,"")</f>
         <v/>
       </c>
       <c r="P64" s="5" t="n">
-        <v>57.77</v>
+        <v>57.7</v>
       </c>
       <c r="Q64" s="5">
         <f>IF(COUNT(P64:P65)=2,(P64/P65-1)*100,"")</f>
         <v/>
       </c>
       <c r="R64" s="5" t="n">
-        <v>85.98999999999999</v>
+        <v>85.02</v>
       </c>
       <c r="S64" s="5">
         <f>IF(COUNT(R64:R65)=2,(R64/R65-1)*100,"")</f>
         <v/>
       </c>
       <c r="T64" s="5" t="n">
-        <v>115.7987</v>
+        <v>115.1604</v>
       </c>
       <c r="U64" s="5">
         <f>IF(COUNT(T64:T65)=2,(T64/T65-1)*100,"")</f>
         <v/>
       </c>
       <c r="V64" s="5" t="n">
-        <v>16.76</v>
+        <v>16.7</v>
       </c>
       <c r="W64" s="5">
         <f>IF(COUNT(V64:V65)=2,(V64/V65-1)*100,"")</f>
         <v/>
       </c>
       <c r="X64" s="5" t="n">
-        <v>-3.8991</v>
+        <v>-0.358</v>
       </c>
       <c r="Y64" s="5">
-        <f>IF(AND(X64&gt;$Y$11,C64&lt;=$Y$12),C63,"")</f>
+        <f>IF(AND(X64&gt;$Y$12,C64&lt;=$Y$13),C63,"")</f>
         <v/>
       </c>
       <c r="Z64" s="5">
-        <f>IF(AND(K64&lt;$Z$11,M64&gt;$Z$12),C63,"")</f>
+        <f>IF(AND(K64&lt;$Z$12,M64&gt;$Z$13),C63,"")</f>
         <v/>
       </c>
       <c r="AA64" s="5">
-        <f>IF(AND(G64&gt;$AA$11,I64&lt;$AA$12,K64&gt;$AA$12),C63,"")</f>
+        <f>IF(AND(G64&gt;$AA$12,I64&lt;$AA$13,K64&gt;$AA$11),C63,"")</f>
         <v/>
       </c>
       <c r="AB64" s="5">
@@ -8064,15 +7962,15 @@
         <v/>
       </c>
       <c r="AC64" s="5">
-        <f>IF(AND(S64&gt;$AC$11,U64&lt;$AC$12),E63,"")</f>
+        <f>IF(AND(S64&gt;$AC$12,U64&lt;$AC$13),E63,"")</f>
         <v/>
       </c>
       <c r="AD64" s="5">
-        <f>IF(AND(O64&lt;=$AD$11,E64&lt;$AD$12),E63,"")</f>
+        <f>IF(AND(O64&lt;=$AD$12,E64&lt;$AD$13),E63,"")</f>
         <v/>
       </c>
       <c r="AE64" s="5">
-        <f>IF(AND(Q64&gt;$AE$11,S64&gt;$AE$12),E63,"")</f>
+        <f>IF(AND(Q64&gt;$AE$12,S64&gt;$AE$13),E63,"")</f>
         <v/>
       </c>
       <c r="AF64" s="5">
@@ -8083,39 +7981,39 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/21</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
-        <v>163.44</v>
+        <v>164.1</v>
       </c>
       <c r="C65" s="5">
         <f>IF(COUNT(B65:B66)=2,(B65/B66-1)*100,"")</f>
         <v/>
       </c>
       <c r="D65" s="5" t="n">
-        <v>181.4</v>
+        <v>182.04</v>
       </c>
       <c r="E65" s="5">
         <f>IF(COUNT(D65:D66)=2,(D65/D66-1)*100,"")</f>
         <v/>
       </c>
       <c r="F65" s="5" t="n">
-        <v>65.1215</v>
+        <v>65.68859999999999</v>
       </c>
       <c r="G65" s="5">
         <f>IF(COUNT(F65:F66)=2,(F65/F66-1)*100,"")</f>
         <v/>
       </c>
       <c r="H65" s="5" t="n">
-        <v>417.4</v>
+        <v>416.99</v>
       </c>
       <c r="I65" s="5">
         <f>IF(COUNT(H65:H66)=2,(H65/H66-1)*100,"")</f>
         <v/>
       </c>
       <c r="J65" s="5" t="n">
-        <v>78.7046</v>
+        <v>78.744</v>
       </c>
       <c r="K65" s="5">
         <f>IF(COUNT(J65:J66)=2,(J65/J66-1)*100,"")</f>
@@ -8129,21 +8027,21 @@
         <v/>
       </c>
       <c r="N65" s="5" t="n">
-        <v>51.4797</v>
+        <v>51.5494</v>
       </c>
       <c r="O65" s="5">
         <f>IF(COUNT(N65:N66)=2,(N65/N66-1)*100,"")</f>
         <v/>
       </c>
       <c r="P65" s="5" t="n">
-        <v>57.78</v>
+        <v>57.77</v>
       </c>
       <c r="Q65" s="5">
         <f>IF(COUNT(P65:P66)=2,(P65/P66-1)*100,"")</f>
         <v/>
       </c>
       <c r="R65" s="5" t="n">
-        <v>86.36</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="S65" s="5">
         <f>IF(COUNT(R65:R66)=2,(R65/R66-1)*100,"")</f>
@@ -8157,25 +8055,25 @@
         <v/>
       </c>
       <c r="V65" s="5" t="n">
-        <v>17.44</v>
+        <v>16.76</v>
       </c>
       <c r="W65" s="5">
         <f>IF(COUNT(V65:V66)=2,(V65/V66-1)*100,"")</f>
         <v/>
       </c>
       <c r="X65" s="5" t="n">
-        <v>-3.433</v>
+        <v>-3.8991</v>
       </c>
       <c r="Y65" s="5">
-        <f>IF(AND(X65&gt;$Y$11,C65&lt;=$Y$12),C64,"")</f>
+        <f>IF(AND(X65&gt;$Y$12,C65&lt;=$Y$13),C64,"")</f>
         <v/>
       </c>
       <c r="Z65" s="5">
-        <f>IF(AND(K65&lt;$Z$11,M65&gt;$Z$12),C64,"")</f>
+        <f>IF(AND(K65&lt;$Z$12,M65&gt;$Z$13),C64,"")</f>
         <v/>
       </c>
       <c r="AA65" s="5">
-        <f>IF(AND(G65&gt;$AA$11,I65&lt;$AA$12,K65&gt;$AA$12),C64,"")</f>
+        <f>IF(AND(G65&gt;$AA$12,I65&lt;$AA$13,K65&gt;$AA$11),C64,"")</f>
         <v/>
       </c>
       <c r="AB65" s="5">
@@ -8183,15 +8081,15 @@
         <v/>
       </c>
       <c r="AC65" s="5">
-        <f>IF(AND(S65&gt;$AC$11,U65&lt;$AC$12),E64,"")</f>
+        <f>IF(AND(S65&gt;$AC$12,U65&lt;$AC$13),E64,"")</f>
         <v/>
       </c>
       <c r="AD65" s="5">
-        <f>IF(AND(O65&lt;=$AD$11,E65&lt;$AD$12),E64,"")</f>
+        <f>IF(AND(O65&lt;=$AD$12,E65&lt;$AD$13),E64,"")</f>
         <v/>
       </c>
       <c r="AE65" s="5">
-        <f>IF(AND(Q65&gt;$AE$11,S65&gt;$AE$12),E64,"")</f>
+        <f>IF(AND(Q65&gt;$AE$12,S65&gt;$AE$13),E64,"")</f>
         <v/>
       </c>
       <c r="AF65" s="5">
@@ -8202,99 +8100,99 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
-        <v>158.19</v>
+        <v>163.44</v>
       </c>
       <c r="C66" s="5">
         <f>IF(COUNT(B66:B67)=2,(B66/B67-1)*100,"")</f>
         <v/>
       </c>
       <c r="D66" s="5" t="n">
-        <v>177.64</v>
+        <v>181.4</v>
       </c>
       <c r="E66" s="5">
         <f>IF(COUNT(D66:D67)=2,(D66/D67-1)*100,"")</f>
         <v/>
       </c>
       <c r="F66" s="5" t="n">
-        <v>63.9277</v>
+        <v>65.1215</v>
       </c>
       <c r="G66" s="5">
         <f>IF(COUNT(F66:F67)=2,(F66/F67-1)*100,"")</f>
         <v/>
       </c>
       <c r="H66" s="5" t="n">
-        <v>411.5</v>
+        <v>417.4</v>
       </c>
       <c r="I66" s="5">
         <f>IF(COUNT(H66:H67)=2,(H66/H67-1)*100,"")</f>
         <v/>
       </c>
       <c r="J66" s="5" t="n">
-        <v>78.202</v>
+        <v>78.7046</v>
       </c>
       <c r="K66" s="5">
         <f>IF(COUNT(J66:J67)=2,(J66/J67-1)*100,"")</f>
         <v/>
       </c>
       <c r="L66" s="5" t="n">
-        <v>107.0071</v>
+        <v>107.2598</v>
       </c>
       <c r="M66" s="5">
         <f>IF(COUNT(L66:L67)=2,(L66/L67-1)*100,"")</f>
         <v/>
       </c>
       <c r="N66" s="5" t="n">
-        <v>50.9216</v>
+        <v>51.4797</v>
       </c>
       <c r="O66" s="5">
         <f>IF(COUNT(N66:N67)=2,(N66/N67-1)*100,"")</f>
         <v/>
       </c>
       <c r="P66" s="5" t="n">
-        <v>57.72</v>
+        <v>57.78</v>
       </c>
       <c r="Q66" s="5">
         <f>IF(COUNT(P66:P67)=2,(P66/P67-1)*100,"")</f>
         <v/>
       </c>
       <c r="R66" s="5" t="n">
-        <v>83.78</v>
+        <v>86.36</v>
       </c>
       <c r="S66" s="5">
         <f>IF(COUNT(R66:R67)=2,(R66/R67-1)*100,"")</f>
         <v/>
       </c>
       <c r="T66" s="5" t="n">
-        <v>115.5494</v>
+        <v>115.7987</v>
       </c>
       <c r="U66" s="5">
         <f>IF(COUNT(T66:T67)=2,(T66/T67-1)*100,"")</f>
         <v/>
       </c>
       <c r="V66" s="5" t="n">
-        <v>18.06</v>
+        <v>17.44</v>
       </c>
       <c r="W66" s="5">
         <f>IF(COUNT(V66:V67)=2,(V66/V67-1)*100,"")</f>
         <v/>
       </c>
       <c r="X66" s="5" t="n">
-        <v>1.3468</v>
+        <v>-3.433</v>
       </c>
       <c r="Y66" s="5">
-        <f>IF(AND(X66&gt;$Y$11,C66&lt;=$Y$12),C65,"")</f>
+        <f>IF(AND(X66&gt;$Y$12,C66&lt;=$Y$13),C65,"")</f>
         <v/>
       </c>
       <c r="Z66" s="5">
-        <f>IF(AND(K66&lt;$Z$11,M66&gt;$Z$12),C65,"")</f>
+        <f>IF(AND(K66&lt;$Z$12,M66&gt;$Z$13),C65,"")</f>
         <v/>
       </c>
       <c r="AA66" s="5">
-        <f>IF(AND(G66&gt;$AA$11,I66&lt;$AA$12,K66&gt;$AA$12),C65,"")</f>
+        <f>IF(AND(G66&gt;$AA$12,I66&lt;$AA$13,K66&gt;$AA$11),C65,"")</f>
         <v/>
       </c>
       <c r="AB66" s="5">
@@ -8302,15 +8200,15 @@
         <v/>
       </c>
       <c r="AC66" s="5">
-        <f>IF(AND(S66&gt;$AC$11,U66&lt;$AC$12),E65,"")</f>
+        <f>IF(AND(S66&gt;$AC$12,U66&lt;$AC$13),E65,"")</f>
         <v/>
       </c>
       <c r="AD66" s="5">
-        <f>IF(AND(O66&lt;=$AD$11,E66&lt;$AD$12),E65,"")</f>
+        <f>IF(AND(O66&lt;=$AD$12,E66&lt;$AD$13),E65,"")</f>
         <v/>
       </c>
       <c r="AE66" s="5">
-        <f>IF(AND(Q66&gt;$AE$11,S66&gt;$AE$12),E65,"")</f>
+        <f>IF(AND(Q66&gt;$AE$12,S66&gt;$AE$13),E65,"")</f>
         <v/>
       </c>
       <c r="AF66" s="5">
@@ -8321,99 +8219,99 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>2026/05/18</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
-        <v>160.16</v>
+        <v>158.19</v>
       </c>
       <c r="C67" s="5">
         <f>IF(COUNT(B67:B68)=2,(B67/B68-1)*100,"")</f>
         <v/>
       </c>
       <c r="D67" s="5" t="n">
-        <v>180.04</v>
+        <v>177.64</v>
       </c>
       <c r="E67" s="5">
         <f>IF(COUNT(D67:D68)=2,(D67/D68-1)*100,"")</f>
         <v/>
       </c>
       <c r="F67" s="5" t="n">
-        <v>64.634</v>
+        <v>63.9277</v>
       </c>
       <c r="G67" s="5">
         <f>IF(COUNT(F67:F68)=2,(F67/F68-1)*100,"")</f>
         <v/>
       </c>
       <c r="H67" s="5" t="n">
-        <v>418.43</v>
+        <v>411.5</v>
       </c>
       <c r="I67" s="5">
         <f>IF(COUNT(H67:H68)=2,(H67/H68-1)*100,"")</f>
         <v/>
       </c>
       <c r="J67" s="5" t="n">
-        <v>78.3892</v>
+        <v>78.202</v>
       </c>
       <c r="K67" s="5">
         <f>IF(COUNT(J67:J68)=2,(J67/J68-1)*100,"")</f>
         <v/>
       </c>
       <c r="L67" s="5" t="n">
-        <v>107.3667</v>
+        <v>107.0071</v>
       </c>
       <c r="M67" s="5">
         <f>IF(COUNT(L67:L68)=2,(L67/L68-1)*100,"")</f>
         <v/>
       </c>
       <c r="N67" s="5" t="n">
-        <v>51.5594</v>
+        <v>50.9216</v>
       </c>
       <c r="O67" s="5">
         <f>IF(COUNT(N67:N68)=2,(N67/N68-1)*100,"")</f>
         <v/>
       </c>
       <c r="P67" s="5" t="n">
-        <v>57.8</v>
+        <v>57.72</v>
       </c>
       <c r="Q67" s="5">
         <f>IF(COUNT(P67:P68)=2,(P67/P68-1)*100,"")</f>
         <v/>
       </c>
       <c r="R67" s="5" t="n">
-        <v>87.14</v>
+        <v>83.78</v>
       </c>
       <c r="S67" s="5">
         <f>IF(COUNT(R67:R68)=2,(R67/R68-1)*100,"")</f>
         <v/>
       </c>
       <c r="T67" s="5" t="n">
-        <v>116.6765</v>
+        <v>115.5494</v>
       </c>
       <c r="U67" s="5">
         <f>IF(COUNT(T67:T68)=2,(T67/T68-1)*100,"")</f>
         <v/>
       </c>
       <c r="V67" s="5" t="n">
-        <v>17.82</v>
+        <v>18.06</v>
       </c>
       <c r="W67" s="5">
         <f>IF(COUNT(V67:V68)=2,(V67/V68-1)*100,"")</f>
         <v/>
       </c>
       <c r="X67" s="5" t="n">
-        <v>-3.3098</v>
+        <v>1.3468</v>
       </c>
       <c r="Y67" s="5">
-        <f>IF(AND(X67&gt;$Y$11,C67&lt;=$Y$12),C66,"")</f>
+        <f>IF(AND(X67&gt;$Y$12,C67&lt;=$Y$13),C66,"")</f>
         <v/>
       </c>
       <c r="Z67" s="5">
-        <f>IF(AND(K67&lt;$Z$11,M67&gt;$Z$12),C66,"")</f>
+        <f>IF(AND(K67&lt;$Z$12,M67&gt;$Z$13),C66,"")</f>
         <v/>
       </c>
       <c r="AA67" s="5">
-        <f>IF(AND(G67&gt;$AA$11,I67&lt;$AA$12,K67&gt;$AA$12),C66,"")</f>
+        <f>IF(AND(G67&gt;$AA$12,I67&lt;$AA$13,K67&gt;$AA$11),C66,"")</f>
         <v/>
       </c>
       <c r="AB67" s="5">
@@ -8421,15 +8319,15 @@
         <v/>
       </c>
       <c r="AC67" s="5">
-        <f>IF(AND(S67&gt;$AC$11,U67&lt;$AC$12),E66,"")</f>
+        <f>IF(AND(S67&gt;$AC$12,U67&lt;$AC$13),E66,"")</f>
         <v/>
       </c>
       <c r="AD67" s="5">
-        <f>IF(AND(O67&lt;=$AD$11,E67&lt;$AD$12),E66,"")</f>
+        <f>IF(AND(O67&lt;=$AD$12,E67&lt;$AD$13),E66,"")</f>
         <v/>
       </c>
       <c r="AE67" s="5">
-        <f>IF(AND(Q67&gt;$AE$11,S67&gt;$AE$12),E66,"")</f>
+        <f>IF(AND(Q67&gt;$AE$12,S67&gt;$AE$13),E66,"")</f>
         <v/>
       </c>
       <c r="AF67" s="5">
@@ -8440,99 +8338,99 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/05/18</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>161.66</v>
+        <v>160.16</v>
       </c>
       <c r="C68" s="5">
         <f>IF(COUNT(B68:B69)=2,(B68/B69-1)*100,"")</f>
         <v/>
       </c>
       <c r="D68" s="5" t="n">
-        <v>180.37</v>
+        <v>180.04</v>
       </c>
       <c r="E68" s="5">
         <f>IF(COUNT(D68:D69)=2,(D68/D69-1)*100,"")</f>
         <v/>
       </c>
       <c r="F68" s="5" t="n">
-        <v>64.73350000000001</v>
+        <v>64.634</v>
       </c>
       <c r="G68" s="5">
         <f>IF(COUNT(F68:F69)=2,(F68/F69-1)*100,"")</f>
         <v/>
       </c>
       <c r="H68" s="5" t="n">
-        <v>417.29</v>
+        <v>418.43</v>
       </c>
       <c r="I68" s="5">
         <f>IF(COUNT(H68:H69)=2,(H68/H69-1)*100,"")</f>
         <v/>
       </c>
       <c r="J68" s="5" t="n">
-        <v>78.3104</v>
+        <v>78.3892</v>
       </c>
       <c r="K68" s="5">
         <f>IF(COUNT(J68:J69)=2,(J68/J69-1)*100,"")</f>
         <v/>
       </c>
       <c r="L68" s="5" t="n">
-        <v>107.493</v>
+        <v>107.3667</v>
       </c>
       <c r="M68" s="5">
         <f>IF(COUNT(L68:L69)=2,(L68/L69-1)*100,"")</f>
         <v/>
       </c>
       <c r="N68" s="5" t="n">
-        <v>50.9216</v>
+        <v>51.5594</v>
       </c>
       <c r="O68" s="5">
         <f>IF(COUNT(N68:N69)=2,(N68/N69-1)*100,"")</f>
         <v/>
       </c>
       <c r="P68" s="5" t="n">
-        <v>57.85</v>
+        <v>57.8</v>
       </c>
       <c r="Q68" s="5">
         <f>IF(COUNT(P68:P69)=2,(P68/P69-1)*100,"")</f>
         <v/>
       </c>
       <c r="R68" s="5" t="n">
-        <v>87.34999999999999</v>
+        <v>87.14</v>
       </c>
       <c r="S68" s="5">
         <f>IF(COUNT(R68:R69)=2,(R68/R69-1)*100,"")</f>
         <v/>
       </c>
       <c r="T68" s="5" t="n">
-        <v>115.7788</v>
+        <v>116.6765</v>
       </c>
       <c r="U68" s="5">
         <f>IF(COUNT(T68:T69)=2,(T68/T69-1)*100,"")</f>
         <v/>
       </c>
       <c r="V68" s="5" t="n">
-        <v>18.43</v>
+        <v>17.82</v>
       </c>
       <c r="W68" s="5">
         <f>IF(COUNT(V68:V69)=2,(V68/V69-1)*100,"")</f>
         <v/>
       </c>
       <c r="X68" s="5" t="n">
-        <v>6.7787</v>
+        <v>-3.3098</v>
       </c>
       <c r="Y68" s="5">
-        <f>IF(AND(X68&gt;$Y$11,C68&lt;=$Y$12),C67,"")</f>
+        <f>IF(AND(X68&gt;$Y$12,C68&lt;=$Y$13),C67,"")</f>
         <v/>
       </c>
       <c r="Z68" s="5">
-        <f>IF(AND(K68&lt;$Z$11,M68&gt;$Z$12),C67,"")</f>
+        <f>IF(AND(K68&lt;$Z$12,M68&gt;$Z$13),C67,"")</f>
         <v/>
       </c>
       <c r="AA68" s="5">
-        <f>IF(AND(G68&gt;$AA$11,I68&lt;$AA$12,K68&gt;$AA$12),C67,"")</f>
+        <f>IF(AND(G68&gt;$AA$12,I68&lt;$AA$13,K68&gt;$AA$11),C67,"")</f>
         <v/>
       </c>
       <c r="AB68" s="5">
@@ -8540,15 +8438,15 @@
         <v/>
       </c>
       <c r="AC68" s="5">
-        <f>IF(AND(S68&gt;$AC$11,U68&lt;$AC$12),E67,"")</f>
+        <f>IF(AND(S68&gt;$AC$12,U68&lt;$AC$13),E67,"")</f>
         <v/>
       </c>
       <c r="AD68" s="5">
-        <f>IF(AND(O68&lt;=$AD$11,E68&lt;$AD$12),E67,"")</f>
+        <f>IF(AND(O68&lt;=$AD$12,E68&lt;$AD$13),E67,"")</f>
         <v/>
       </c>
       <c r="AE68" s="5">
-        <f>IF(AND(Q68&gt;$AE$11,S68&gt;$AE$12),E67,"")</f>
+        <f>IF(AND(Q68&gt;$AE$12,S68&gt;$AE$13),E67,"")</f>
         <v/>
       </c>
       <c r="AF68" s="5">
@@ -8559,99 +8457,99 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>2026/05/14</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
-        <v>166.77</v>
+        <v>161.66</v>
       </c>
       <c r="C69" s="5">
         <f>IF(COUNT(B69:B70)=2,(B69/B70-1)*100,"")</f>
         <v/>
       </c>
       <c r="D69" s="5" t="n">
-        <v>184.9</v>
+        <v>180.37</v>
       </c>
       <c r="E69" s="5">
         <f>IF(COUNT(D69:D70)=2,(D69/D70-1)*100,"")</f>
         <v/>
       </c>
       <c r="F69" s="5" t="n">
-        <v>67.0316</v>
+        <v>64.73350000000001</v>
       </c>
       <c r="G69" s="5">
         <f>IF(COUNT(F69:F70)=2,(F69/F70-1)*100,"")</f>
         <v/>
       </c>
       <c r="H69" s="5" t="n">
-        <v>427.21</v>
+        <v>417.29</v>
       </c>
       <c r="I69" s="5">
         <f>IF(COUNT(H69:H70)=2,(H69/H70-1)*100,"")</f>
         <v/>
       </c>
       <c r="J69" s="5" t="n">
-        <v>78.6947</v>
+        <v>78.3104</v>
       </c>
       <c r="K69" s="5">
         <f>IF(COUNT(J69:J70)=2,(J69/J70-1)*100,"")</f>
         <v/>
       </c>
       <c r="L69" s="5" t="n">
-        <v>107.8818</v>
+        <v>107.493</v>
       </c>
       <c r="M69" s="5">
         <f>IF(COUNT(L69:L70)=2,(L69/L70-1)*100,"")</f>
         <v/>
       </c>
       <c r="N69" s="5" t="n">
-        <v>51.111</v>
+        <v>50.9216</v>
       </c>
       <c r="O69" s="5">
         <f>IF(COUNT(N69:N70)=2,(N69/N70-1)*100,"")</f>
         <v/>
       </c>
       <c r="P69" s="5" t="n">
-        <v>58</v>
+        <v>57.85</v>
       </c>
       <c r="Q69" s="5">
         <f>IF(COUNT(P69:P70)=2,(P69/P70-1)*100,"")</f>
         <v/>
       </c>
       <c r="R69" s="5" t="n">
-        <v>93.95</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="S69" s="5">
         <f>IF(COUNT(R69:R70)=2,(R69/R70-1)*100,"")</f>
         <v/>
       </c>
       <c r="T69" s="5" t="n">
-        <v>116.8061</v>
+        <v>115.7788</v>
       </c>
       <c r="U69" s="5">
         <f>IF(COUNT(T69:T70)=2,(T69/T70-1)*100,"")</f>
         <v/>
       </c>
       <c r="V69" s="5" t="n">
-        <v>17.26</v>
+        <v>18.43</v>
       </c>
       <c r="W69" s="5">
         <f>IF(COUNT(V69:V70)=2,(V69/V70-1)*100,"")</f>
         <v/>
       </c>
       <c r="X69" s="5" t="n">
-        <v>-3.4135</v>
+        <v>6.7787</v>
       </c>
       <c r="Y69" s="5">
-        <f>IF(AND(X69&gt;$Y$11,C69&lt;=$Y$12),C68,"")</f>
+        <f>IF(AND(X69&gt;$Y$12,C69&lt;=$Y$13),C68,"")</f>
         <v/>
       </c>
       <c r="Z69" s="5">
-        <f>IF(AND(K69&lt;$Z$11,M69&gt;$Z$12),C68,"")</f>
+        <f>IF(AND(K69&lt;$Z$12,M69&gt;$Z$13),C68,"")</f>
         <v/>
       </c>
       <c r="AA69" s="5">
-        <f>IF(AND(G69&gt;$AA$11,I69&lt;$AA$12,K69&gt;$AA$12),C68,"")</f>
+        <f>IF(AND(G69&gt;$AA$12,I69&lt;$AA$13,K69&gt;$AA$11),C68,"")</f>
         <v/>
       </c>
       <c r="AB69" s="5">
@@ -8659,15 +8557,15 @@
         <v/>
       </c>
       <c r="AC69" s="5">
-        <f>IF(AND(S69&gt;$AC$11,U69&lt;$AC$12),E68,"")</f>
+        <f>IF(AND(S69&gt;$AC$12,U69&lt;$AC$13),E68,"")</f>
         <v/>
       </c>
       <c r="AD69" s="5">
-        <f>IF(AND(O69&lt;=$AD$11,E69&lt;$AD$12),E68,"")</f>
+        <f>IF(AND(O69&lt;=$AD$12,E69&lt;$AD$13),E68,"")</f>
         <v/>
       </c>
       <c r="AE69" s="5">
-        <f>IF(AND(Q69&gt;$AE$11,S69&gt;$AE$12),E68,"")</f>
+        <f>IF(AND(Q69&gt;$AE$12,S69&gt;$AE$13),E68,"")</f>
         <v/>
       </c>
       <c r="AF69" s="5">
@@ -8678,99 +8576,99 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>2026/05/13</t>
+          <t>2026/05/14</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
-        <v>164.41</v>
+        <v>166.77</v>
       </c>
       <c r="C70" s="5">
         <f>IF(COUNT(B70:B71)=2,(B70/B71-1)*100,"")</f>
         <v/>
       </c>
       <c r="D70" s="5" t="n">
-        <v>182.13</v>
+        <v>184.9</v>
       </c>
       <c r="E70" s="5">
         <f>IF(COUNT(D70:D71)=2,(D70/D71-1)*100,"")</f>
         <v/>
       </c>
       <c r="F70" s="5" t="n">
-        <v>66.8625</v>
+        <v>67.0316</v>
       </c>
       <c r="G70" s="5">
         <f>IF(COUNT(F70:F71)=2,(F70/F71-1)*100,"")</f>
         <v/>
       </c>
       <c r="H70" s="5" t="n">
-        <v>430.5</v>
+        <v>427.21</v>
       </c>
       <c r="I70" s="5">
         <f>IF(COUNT(H70:H71)=2,(H70/H71-1)*100,"")</f>
         <v/>
       </c>
       <c r="J70" s="5" t="n">
-        <v>78.7539</v>
+        <v>78.6947</v>
       </c>
       <c r="K70" s="5">
         <f>IF(COUNT(J70:J71)=2,(J70/J71-1)*100,"")</f>
         <v/>
       </c>
       <c r="L70" s="5" t="n">
-        <v>107.9887</v>
+        <v>107.8818</v>
       </c>
       <c r="M70" s="5">
         <f>IF(COUNT(L70:L71)=2,(L70/L71-1)*100,"")</f>
         <v/>
       </c>
       <c r="N70" s="5" t="n">
-        <v>50.812</v>
+        <v>51.111</v>
       </c>
       <c r="O70" s="5">
         <f>IF(COUNT(N70:N71)=2,(N70/N71-1)*100,"")</f>
         <v/>
       </c>
       <c r="P70" s="5" t="n">
-        <v>58.17</v>
+        <v>58</v>
       </c>
       <c r="Q70" s="5">
         <f>IF(COUNT(P70:P71)=2,(P70/P71-1)*100,"")</f>
         <v/>
       </c>
       <c r="R70" s="5" t="n">
-        <v>96.23</v>
+        <v>93.95</v>
       </c>
       <c r="S70" s="5">
         <f>IF(COUNT(R70:R71)=2,(R70/R71-1)*100,"")</f>
         <v/>
       </c>
       <c r="T70" s="5" t="n">
-        <v>116.457</v>
+        <v>116.8061</v>
       </c>
       <c r="U70" s="5">
         <f>IF(COUNT(T70:T71)=2,(T70/T71-1)*100,"")</f>
         <v/>
       </c>
       <c r="V70" s="5" t="n">
-        <v>17.87</v>
+        <v>17.26</v>
       </c>
       <c r="W70" s="5">
         <f>IF(COUNT(V70:V71)=2,(V70/V71-1)*100,"")</f>
         <v/>
       </c>
       <c r="X70" s="5" t="n">
-        <v>-0.667</v>
+        <v>-3.4135</v>
       </c>
       <c r="Y70" s="5">
-        <f>IF(AND(X70&gt;$Y$11,C70&lt;=$Y$12),C69,"")</f>
+        <f>IF(AND(X70&gt;$Y$12,C70&lt;=$Y$13),C69,"")</f>
         <v/>
       </c>
       <c r="Z70" s="5">
-        <f>IF(AND(K70&lt;$Z$11,M70&gt;$Z$12),C69,"")</f>
+        <f>IF(AND(K70&lt;$Z$12,M70&gt;$Z$13),C69,"")</f>
         <v/>
       </c>
       <c r="AA70" s="5">
-        <f>IF(AND(G70&gt;$AA$11,I70&lt;$AA$12,K70&gt;$AA$12),C69,"")</f>
+        <f>IF(AND(G70&gt;$AA$12,I70&lt;$AA$13,K70&gt;$AA$11),C69,"")</f>
         <v/>
       </c>
       <c r="AB70" s="5">
@@ -8778,15 +8676,15 @@
         <v/>
       </c>
       <c r="AC70" s="5">
-        <f>IF(AND(S70&gt;$AC$11,U70&lt;$AC$12),E69,"")</f>
+        <f>IF(AND(S70&gt;$AC$12,U70&lt;$AC$13),E69,"")</f>
         <v/>
       </c>
       <c r="AD70" s="5">
-        <f>IF(AND(O70&lt;=$AD$11,E70&lt;$AD$12),E69,"")</f>
+        <f>IF(AND(O70&lt;=$AD$12,E70&lt;$AD$13),E69,"")</f>
         <v/>
       </c>
       <c r="AE70" s="5">
-        <f>IF(AND(Q70&gt;$AE$11,S70&gt;$AE$12),E69,"")</f>
+        <f>IF(AND(Q70&gt;$AE$12,S70&gt;$AE$13),E69,"")</f>
         <v/>
       </c>
       <c r="AF70" s="5">
@@ -8797,39 +8695,39 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>2026/05/12</t>
+          <t>2026/05/13</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>161.07</v>
+        <v>164.41</v>
       </c>
       <c r="C71" s="5">
         <f>IF(COUNT(B71:B72)=2,(B71/B72-1)*100,"")</f>
         <v/>
       </c>
       <c r="D71" s="5" t="n">
-        <v>180.05</v>
+        <v>182.13</v>
       </c>
       <c r="E71" s="5">
         <f>IF(COUNT(D71:D72)=2,(D71/D72-1)*100,"")</f>
         <v/>
       </c>
       <c r="F71" s="5" t="n">
-        <v>65.47969999999999</v>
+        <v>66.8625</v>
       </c>
       <c r="G71" s="5">
         <f>IF(COUNT(F71:F72)=2,(F71/F72-1)*100,"")</f>
         <v/>
       </c>
       <c r="H71" s="5" t="n">
-        <v>432.93</v>
+        <v>430.5</v>
       </c>
       <c r="I71" s="5">
         <f>IF(COUNT(H71:H72)=2,(H71/H72-1)*100,"")</f>
         <v/>
       </c>
       <c r="J71" s="5" t="n">
-        <v>78.7144</v>
+        <v>78.7539</v>
       </c>
       <c r="K71" s="5">
         <f>IF(COUNT(J71:J72)=2,(J71/J72-1)*100,"")</f>
@@ -8843,53 +8741,53 @@
         <v/>
       </c>
       <c r="N71" s="5" t="n">
-        <v>51.3999</v>
+        <v>50.812</v>
       </c>
       <c r="O71" s="5">
         <f>IF(COUNT(N71:N72)=2,(N71/N72-1)*100,"")</f>
         <v/>
       </c>
       <c r="P71" s="5" t="n">
-        <v>58.27</v>
+        <v>58.17</v>
       </c>
       <c r="Q71" s="5">
         <f>IF(COUNT(P71:P72)=2,(P71/P72-1)*100,"")</f>
         <v/>
       </c>
       <c r="R71" s="5" t="n">
-        <v>97.14</v>
+        <v>96.23</v>
       </c>
       <c r="S71" s="5">
         <f>IF(COUNT(R71:R72)=2,(R71/R72-1)*100,"")</f>
         <v/>
       </c>
       <c r="T71" s="5" t="n">
-        <v>115.5594</v>
+        <v>116.457</v>
       </c>
       <c r="U71" s="5">
         <f>IF(COUNT(T71:T72)=2,(T71/T72-1)*100,"")</f>
         <v/>
       </c>
       <c r="V71" s="5" t="n">
-        <v>17.99</v>
+        <v>17.87</v>
       </c>
       <c r="W71" s="5">
         <f>IF(COUNT(V71:V72)=2,(V71/V72-1)*100,"")</f>
         <v/>
       </c>
       <c r="X71" s="5" t="n">
-        <v>-2.1219</v>
+        <v>-0.667</v>
       </c>
       <c r="Y71" s="5">
-        <f>IF(AND(X71&gt;$Y$11,C71&lt;=$Y$12),C70,"")</f>
+        <f>IF(AND(X71&gt;$Y$12,C71&lt;=$Y$13),C70,"")</f>
         <v/>
       </c>
       <c r="Z71" s="5">
-        <f>IF(AND(K71&lt;$Z$11,M71&gt;$Z$12),C70,"")</f>
+        <f>IF(AND(K71&lt;$Z$12,M71&gt;$Z$13),C70,"")</f>
         <v/>
       </c>
       <c r="AA71" s="5">
-        <f>IF(AND(G71&gt;$AA$11,I71&lt;$AA$12,K71&gt;$AA$12),C70,"")</f>
+        <f>IF(AND(G71&gt;$AA$12,I71&lt;$AA$13,K71&gt;$AA$11),C70,"")</f>
         <v/>
       </c>
       <c r="AB71" s="5">
@@ -8897,15 +8795,15 @@
         <v/>
       </c>
       <c r="AC71" s="5">
-        <f>IF(AND(S71&gt;$AC$11,U71&lt;$AC$12),E70,"")</f>
+        <f>IF(AND(S71&gt;$AC$12,U71&lt;$AC$13),E70,"")</f>
         <v/>
       </c>
       <c r="AD71" s="5">
-        <f>IF(AND(O71&lt;=$AD$11,E71&lt;$AD$12),E70,"")</f>
+        <f>IF(AND(O71&lt;=$AD$12,E71&lt;$AD$13),E70,"")</f>
         <v/>
       </c>
       <c r="AE71" s="5">
-        <f>IF(AND(Q71&gt;$AE$11,S71&gt;$AE$12),E70,"")</f>
+        <f>IF(AND(Q71&gt;$AE$12,S71&gt;$AE$13),E70,"")</f>
         <v/>
       </c>
       <c r="AF71" s="5">
@@ -8916,99 +8814,99 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>2026/05/11</t>
+          <t>2026/05/12</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
-        <v>163.95</v>
+        <v>161.07</v>
       </c>
       <c r="C72" s="5">
         <f>IF(COUNT(B72:B73)=2,(B72/B73-1)*100,"")</f>
         <v/>
       </c>
       <c r="D72" s="5" t="n">
-        <v>180.64</v>
+        <v>180.05</v>
       </c>
       <c r="E72" s="5">
         <f>IF(COUNT(D72:D73)=2,(D72/D73-1)*100,"")</f>
         <v/>
       </c>
       <c r="F72" s="5" t="n">
-        <v>67.5389</v>
+        <v>65.47969999999999</v>
       </c>
       <c r="G72" s="5">
         <f>IF(COUNT(F72:F73)=2,(F72/F73-1)*100,"")</f>
         <v/>
       </c>
       <c r="H72" s="5" t="n">
-        <v>434.65</v>
+        <v>432.93</v>
       </c>
       <c r="I72" s="5">
         <f>IF(COUNT(H72:H73)=2,(H72/H73-1)*100,"")</f>
         <v/>
       </c>
       <c r="J72" s="5" t="n">
-        <v>78.8228</v>
+        <v>78.7144</v>
       </c>
       <c r="K72" s="5">
         <f>IF(COUNT(J72:J73)=2,(J72/J73-1)*100,"")</f>
         <v/>
       </c>
       <c r="L72" s="5" t="n">
-        <v>108.1733</v>
+        <v>107.9887</v>
       </c>
       <c r="M72" s="5">
         <f>IF(COUNT(L72:L73)=2,(L72/L73-1)*100,"")</f>
         <v/>
       </c>
       <c r="N72" s="5" t="n">
-        <v>51.0013</v>
+        <v>51.3999</v>
       </c>
       <c r="O72" s="5">
         <f>IF(COUNT(N72:N73)=2,(N72/N73-1)*100,"")</f>
         <v/>
       </c>
       <c r="P72" s="5" t="n">
-        <v>58.42</v>
+        <v>58.27</v>
       </c>
       <c r="Q72" s="5">
         <f>IF(COUNT(P72:P73)=2,(P72/P73-1)*100,"")</f>
         <v/>
       </c>
       <c r="R72" s="5" t="n">
-        <v>97.59999999999999</v>
+        <v>97.14</v>
       </c>
       <c r="S72" s="5">
         <f>IF(COUNT(R72:R73)=2,(R72/R73-1)*100,"")</f>
         <v/>
       </c>
       <c r="T72" s="5" t="n">
-        <v>115.2801</v>
+        <v>115.5594</v>
       </c>
       <c r="U72" s="5">
         <f>IF(COUNT(T72:T73)=2,(T72/T73-1)*100,"")</f>
         <v/>
       </c>
       <c r="V72" s="5" t="n">
-        <v>18.38</v>
+        <v>17.99</v>
       </c>
       <c r="W72" s="5">
         <f>IF(COUNT(V72:V73)=2,(V72/V73-1)*100,"")</f>
         <v/>
       </c>
       <c r="X72" s="5" t="n">
-        <v>6.9226</v>
+        <v>-2.1219</v>
       </c>
       <c r="Y72" s="5">
-        <f>IF(AND(X72&gt;$Y$11,C72&lt;=$Y$12),C71,"")</f>
+        <f>IF(AND(X72&gt;$Y$12,C72&lt;=$Y$13),C71,"")</f>
         <v/>
       </c>
       <c r="Z72" s="5">
-        <f>IF(AND(K72&lt;$Z$11,M72&gt;$Z$12),C71,"")</f>
+        <f>IF(AND(K72&lt;$Z$12,M72&gt;$Z$13),C71,"")</f>
         <v/>
       </c>
       <c r="AA72" s="5">
-        <f>IF(AND(G72&gt;$AA$11,I72&lt;$AA$12,K72&gt;$AA$12),C71,"")</f>
+        <f>IF(AND(G72&gt;$AA$12,I72&lt;$AA$13,K72&gt;$AA$11),C71,"")</f>
         <v/>
       </c>
       <c r="AB72" s="5">
@@ -9016,15 +8914,15 @@
         <v/>
       </c>
       <c r="AC72" s="5">
-        <f>IF(AND(S72&gt;$AC$11,U72&lt;$AC$12),E71,"")</f>
+        <f>IF(AND(S72&gt;$AC$12,U72&lt;$AC$13),E71,"")</f>
         <v/>
       </c>
       <c r="AD72" s="5">
-        <f>IF(AND(O72&lt;=$AD$11,E72&lt;$AD$12),E71,"")</f>
+        <f>IF(AND(O72&lt;=$AD$12,E72&lt;$AD$13),E71,"")</f>
         <v/>
       </c>
       <c r="AE72" s="5">
-        <f>IF(AND(Q72&gt;$AE$11,S72&gt;$AE$12),E71,"")</f>
+        <f>IF(AND(Q72&gt;$AE$12,S72&gt;$AE$13),E71,"")</f>
         <v/>
       </c>
       <c r="AF72" s="5">
@@ -9035,66 +8933,99 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/11</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>163.06</v>
-      </c>
-      <c r="C73" s="5" t="inlineStr"/>
+        <v>163.95</v>
+      </c>
+      <c r="C73" s="5">
+        <f>IF(COUNT(B73:B74)=2,(B73/B74-1)*100,"")</f>
+        <v/>
+      </c>
       <c r="D73" s="5" t="n">
-        <v>179.98</v>
-      </c>
-      <c r="E73" s="5" t="inlineStr"/>
+        <v>180.64</v>
+      </c>
+      <c r="E73" s="5">
+        <f>IF(COUNT(D73:D74)=2,(D73/D74-1)*100,"")</f>
+        <v/>
+      </c>
       <c r="F73" s="5" t="n">
-        <v>67.5887</v>
-      </c>
-      <c r="G73" s="5" t="inlineStr"/>
+        <v>67.5389</v>
+      </c>
+      <c r="G73" s="5">
+        <f>IF(COUNT(F73:F74)=2,(F73/F74-1)*100,"")</f>
+        <v/>
+      </c>
       <c r="H73" s="5" t="n">
-        <v>433.77</v>
-      </c>
-      <c r="I73" s="5" t="inlineStr"/>
+        <v>434.65</v>
+      </c>
+      <c r="I73" s="5">
+        <f>IF(COUNT(H73:H74)=2,(H73/H74-1)*100,"")</f>
+        <v/>
+      </c>
       <c r="J73" s="5" t="n">
-        <v>78.98050000000001</v>
-      </c>
-      <c r="K73" s="5" t="inlineStr"/>
+        <v>78.8228</v>
+      </c>
+      <c r="K73" s="5">
+        <f>IF(COUNT(J73:J74)=2,(J73/J74-1)*100,"")</f>
+        <v/>
+      </c>
       <c r="L73" s="5" t="n">
-        <v>108.2608</v>
-      </c>
-      <c r="M73" s="5" t="inlineStr"/>
+        <v>108.1733</v>
+      </c>
+      <c r="M73" s="5">
+        <f>IF(COUNT(L73:L74)=2,(L73/L74-1)*100,"")</f>
+        <v/>
+      </c>
       <c r="N73" s="5" t="n">
-        <v>51.0611</v>
-      </c>
-      <c r="O73" s="5" t="inlineStr"/>
+        <v>51.0013</v>
+      </c>
+      <c r="O73" s="5">
+        <f>IF(COUNT(N73:N74)=2,(N73/N74-1)*100,"")</f>
+        <v/>
+      </c>
       <c r="P73" s="5" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="Q73" s="5" t="inlineStr"/>
+        <v>58.42</v>
+      </c>
+      <c r="Q73" s="5">
+        <f>IF(COUNT(P73:P74)=2,(P73/P74-1)*100,"")</f>
+        <v/>
+      </c>
       <c r="R73" s="5" t="n">
-        <v>94.59</v>
-      </c>
-      <c r="S73" s="5" t="inlineStr"/>
+        <v>97.59999999999999</v>
+      </c>
+      <c r="S73" s="5">
+        <f>IF(COUNT(R73:R74)=2,(R73/R74-1)*100,"")</f>
+        <v/>
+      </c>
       <c r="T73" s="5" t="n">
-        <v>116.6366</v>
-      </c>
-      <c r="U73" s="5" t="inlineStr"/>
+        <v>115.2801</v>
+      </c>
+      <c r="U73" s="5">
+        <f>IF(COUNT(T73:T74)=2,(T73/T74-1)*100,"")</f>
+        <v/>
+      </c>
       <c r="V73" s="5" t="n">
-        <v>17.19</v>
-      </c>
-      <c r="W73" s="5" t="inlineStr"/>
+        <v>18.38</v>
+      </c>
+      <c r="W73" s="5">
+        <f>IF(COUNT(V73:V74)=2,(V73/V74-1)*100,"")</f>
+        <v/>
+      </c>
       <c r="X73" s="5" t="n">
-        <v>0.644</v>
+        <v>6.9226</v>
       </c>
       <c r="Y73" s="5">
-        <f>IF(AND(X73&gt;$Y$11,C73&lt;=$Y$12),C72,"")</f>
+        <f>IF(AND(X73&gt;$Y$12,C73&lt;=$Y$13),C72,"")</f>
         <v/>
       </c>
       <c r="Z73" s="5">
-        <f>IF(AND(K73&lt;$Z$11,M73&gt;$Z$12),C72,"")</f>
+        <f>IF(AND(K73&lt;$Z$12,M73&gt;$Z$13),C72,"")</f>
         <v/>
       </c>
       <c r="AA73" s="5">
-        <f>IF(AND(G73&gt;$AA$11,I73&lt;$AA$12,K73&gt;$AA$12),C72,"")</f>
+        <f>IF(AND(G73&gt;$AA$12,I73&lt;$AA$13,K73&gt;$AA$11),C72,"")</f>
         <v/>
       </c>
       <c r="AB73" s="5">
@@ -9102,19 +9033,105 @@
         <v/>
       </c>
       <c r="AC73" s="5">
-        <f>IF(AND(S73&gt;$AC$11,U73&lt;$AC$12),E72,"")</f>
+        <f>IF(AND(S73&gt;$AC$12,U73&lt;$AC$13),E72,"")</f>
         <v/>
       </c>
       <c r="AD73" s="5">
-        <f>IF(AND(O73&lt;=$AD$11,E73&lt;$AD$12),E72,"")</f>
+        <f>IF(AND(O73&lt;=$AD$12,E73&lt;$AD$13),E72,"")</f>
         <v/>
       </c>
       <c r="AE73" s="5">
-        <f>IF(AND(Q73&gt;$AE$11,S73&gt;$AE$12),E72,"")</f>
+        <f>IF(AND(Q73&gt;$AE$12,S73&gt;$AE$13),E72,"")</f>
         <v/>
       </c>
       <c r="AF73" s="5">
         <f>IF(AC73&lt;&gt;"",AC73,IF(AD73&lt;&gt;"",AD73,AE73))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>163.06</v>
+      </c>
+      <c r="C74" s="5" t="inlineStr"/>
+      <c r="D74" s="5" t="n">
+        <v>179.98</v>
+      </c>
+      <c r="E74" s="5" t="inlineStr"/>
+      <c r="F74" s="5" t="n">
+        <v>67.5887</v>
+      </c>
+      <c r="G74" s="5" t="inlineStr"/>
+      <c r="H74" s="5" t="n">
+        <v>433.77</v>
+      </c>
+      <c r="I74" s="5" t="inlineStr"/>
+      <c r="J74" s="5" t="n">
+        <v>78.98050000000001</v>
+      </c>
+      <c r="K74" s="5" t="inlineStr"/>
+      <c r="L74" s="5" t="n">
+        <v>108.2608</v>
+      </c>
+      <c r="M74" s="5" t="inlineStr"/>
+      <c r="N74" s="5" t="n">
+        <v>51.0611</v>
+      </c>
+      <c r="O74" s="5" t="inlineStr"/>
+      <c r="P74" s="5" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="Q74" s="5" t="inlineStr"/>
+      <c r="R74" s="5" t="n">
+        <v>94.59</v>
+      </c>
+      <c r="S74" s="5" t="inlineStr"/>
+      <c r="T74" s="5" t="n">
+        <v>116.6366</v>
+      </c>
+      <c r="U74" s="5" t="inlineStr"/>
+      <c r="V74" s="5" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="W74" s="5" t="inlineStr"/>
+      <c r="X74" s="5" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="Y74" s="5">
+        <f>IF(AND(X74&gt;$Y$12,C74&lt;=$Y$13),C73,"")</f>
+        <v/>
+      </c>
+      <c r="Z74" s="5">
+        <f>IF(AND(K74&lt;$Z$12,M74&gt;$Z$13),C73,"")</f>
+        <v/>
+      </c>
+      <c r="AA74" s="5">
+        <f>IF(AND(G74&gt;$AA$12,I74&lt;$AA$13,K74&gt;$AA$11),C73,"")</f>
+        <v/>
+      </c>
+      <c r="AB74" s="5">
+        <f>IF(Y74&lt;&gt;"",Y74,IF(Z74&lt;&gt;"",Z74,AA74))</f>
+        <v/>
+      </c>
+      <c r="AC74" s="5">
+        <f>IF(AND(S74&gt;$AC$12,U74&lt;$AC$13),E73,"")</f>
+        <v/>
+      </c>
+      <c r="AD74" s="5">
+        <f>IF(AND(O74&lt;=$AD$12,E74&lt;$AD$13),E73,"")</f>
+        <v/>
+      </c>
+      <c r="AE74" s="5">
+        <f>IF(AND(Q74&gt;$AE$12,S74&gt;$AE$13),E73,"")</f>
+        <v/>
+      </c>
+      <c r="AF74" s="5">
+        <f>IF(AC74&lt;&gt;"",AC74,IF(AD74&lt;&gt;"",AD74,AE74))</f>
         <v/>
       </c>
     </row>

--- a/04_结果/示例审批/两基金_m30新版式示例_公式说明版.xlsx
+++ b/04_结果/示例审批/两基金_m30新版式示例_公式说明版.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000&quot;%&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -515,7 +515,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   =IF(COUNT(B15:B16)=2,(B15/B16-1)*100,"")</t>
+          <t xml:space="preserve">   =IF(COUNT(B15:B16)=2,ROUND((B15/B16-1)*100,4),"")</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   所有回报率均以百分比显示并保留4位小数。</t>
+          <t xml:space="preserve">   所有回报率均以百分比显示并保留4位小数（公式 ROUND 到4位，显示格式 0.0000%）。</t>
         </is>
       </c>
     </row>
@@ -3427,11 +3427,11 @@
         <v>194.03</v>
       </c>
       <c r="D15" s="6">
-        <f>IF(COUNT(B15:B16)=2,(B15/B16-1)*100,"")</f>
+        <f>IF(COUNT(B15:B16)=2,ROUND((B15/B16-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E15" s="6">
-        <f>IF(COUNT(C15:C16)=2,(C15/C16-1)*100,"")</f>
+        <f>IF(COUNT(C15:C16)=2,ROUND((C15/C16-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F15" s="5" t="n">
@@ -3555,42 +3555,42 @@
         <v>112.04</v>
       </c>
       <c r="AT15" s="6">
-        <f>IF(COUNT(J15:J16)=2,(J15/J16-1)*100,"")</f>
+        <f>IF(COUNT(J15:J16)=2,ROUND((J15/J16-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU15" s="6">
-        <f>IF(COUNT(O15:O16)=2,(O15/O16-1)*100,"")</f>
+        <f>IF(COUNT(O15:O16)=2,ROUND((O15/O16-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV15" s="6">
-        <f>IF(COUNT(T15:T16)=2,(T15/T16-1)*100,"")</f>
+        <f>IF(COUNT(T15:T16)=2,ROUND((T15/T16-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW15" s="6">
-        <f>IF(COUNT(Y15:Y16)=2,(Y15/Y16-1)*100,"")</f>
+        <f>IF(COUNT(Y15:Y16)=2,ROUND((Y15/Y16-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX15" s="6">
-        <f>IF(COUNT(AD15:AD16)=2,(AD15/AD16-1)*100,"")</f>
+        <f>IF(COUNT(AD15:AD16)=2,ROUND((AD15/AD16-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY15" s="6">
-        <f>IF(COUNT(AI15:AI16)=2,(AI15/AI16-1)*100,"")</f>
+        <f>IF(COUNT(AI15:AI16)=2,ROUND((AI15/AI16-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ15" s="6">
-        <f>IF(COUNT(AN15:AN16)=2,(AN15/AN16-1)*100,"")</f>
+        <f>IF(COUNT(AN15:AN16)=2,ROUND((AN15/AN16-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA15" s="6">
-        <f>IF(COUNT(AS15:AS16)=2,(AS15/AS16-1)*100,"")</f>
+        <f>IF(COUNT(AS15:AS16)=2,ROUND((AS15/AS16-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB15" s="5" t="n">
         <v>16.5</v>
       </c>
       <c r="BC15" s="6">
-        <f>IF(COUNT(BB15:BB16)=2,(BB15/BB16-1)*100,"")</f>
+        <f>IF(COUNT(BB15:BB16)=2,ROUND((BB15/BB16-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD15" s="6" t="n">
@@ -3624,11 +3624,11 @@
         <v>187.34</v>
       </c>
       <c r="D16" s="6">
-        <f>IF(COUNT(B16:B17)=2,(B16/B17-1)*100,"")</f>
+        <f>IF(COUNT(B16:B17)=2,ROUND((B16/B17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E16" s="6">
-        <f>IF(COUNT(C16:C17)=2,(C16/C17-1)*100,"")</f>
+        <f>IF(COUNT(C16:C17)=2,ROUND((C16/C17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F16" s="5" t="n">
@@ -3752,42 +3752,42 @@
         <v>111.34</v>
       </c>
       <c r="AT16" s="6">
-        <f>IF(COUNT(J16:J17)=2,(J16/J17-1)*100,"")</f>
+        <f>IF(COUNT(J16:J17)=2,ROUND((J16/J17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU16" s="6">
-        <f>IF(COUNT(O16:O17)=2,(O16/O17-1)*100,"")</f>
+        <f>IF(COUNT(O16:O17)=2,ROUND((O16/O17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV16" s="6">
-        <f>IF(COUNT(T16:T17)=2,(T16/T17-1)*100,"")</f>
+        <f>IF(COUNT(T16:T17)=2,ROUND((T16/T17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW16" s="6">
-        <f>IF(COUNT(Y16:Y17)=2,(Y16/Y17-1)*100,"")</f>
+        <f>IF(COUNT(Y16:Y17)=2,ROUND((Y16/Y17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX16" s="6">
-        <f>IF(COUNT(AD16:AD17)=2,(AD16/AD17-1)*100,"")</f>
+        <f>IF(COUNT(AD16:AD17)=2,ROUND((AD16/AD17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY16" s="6">
-        <f>IF(COUNT(AI16:AI17)=2,(AI16/AI17-1)*100,"")</f>
+        <f>IF(COUNT(AI16:AI17)=2,ROUND((AI16/AI17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ16" s="6">
-        <f>IF(COUNT(AN16:AN17)=2,(AN16/AN17-1)*100,"")</f>
+        <f>IF(COUNT(AN16:AN17)=2,ROUND((AN16/AN17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA16" s="6">
-        <f>IF(COUNT(AS16:AS17)=2,(AS16/AS17-1)*100,"")</f>
+        <f>IF(COUNT(AS16:AS17)=2,ROUND((AS16/AS17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB16" s="5" t="n">
         <v>15.86</v>
       </c>
       <c r="BC16" s="6">
-        <f>IF(COUNT(BB16:BB17)=2,(BB16/BB17-1)*100,"")</f>
+        <f>IF(COUNT(BB16:BB17)=2,ROUND((BB16/BB17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD16" s="6" t="n">
@@ -3839,11 +3839,11 @@
         <v>182.05</v>
       </c>
       <c r="D17" s="6">
-        <f>IF(COUNT(B17:B18)=2,(B17/B18-1)*100,"")</f>
+        <f>IF(COUNT(B17:B18)=2,ROUND((B17/B18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E17" s="6">
-        <f>IF(COUNT(C17:C18)=2,(C17/C18-1)*100,"")</f>
+        <f>IF(COUNT(C17:C18)=2,ROUND((C17/C18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F17" s="5" t="n">
@@ -3967,42 +3967,42 @@
         <v>108.24</v>
       </c>
       <c r="AT17" s="6">
-        <f>IF(COUNT(J17:J18)=2,(J17/J18-1)*100,"")</f>
+        <f>IF(COUNT(J17:J18)=2,ROUND((J17/J18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU17" s="6">
-        <f>IF(COUNT(O17:O18)=2,(O17/O18-1)*100,"")</f>
+        <f>IF(COUNT(O17:O18)=2,ROUND((O17/O18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV17" s="6">
-        <f>IF(COUNT(T17:T18)=2,(T17/T18-1)*100,"")</f>
+        <f>IF(COUNT(T17:T18)=2,ROUND((T17/T18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW17" s="6">
-        <f>IF(COUNT(Y17:Y18)=2,(Y17/Y18-1)*100,"")</f>
+        <f>IF(COUNT(Y17:Y18)=2,ROUND((Y17/Y18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX17" s="6">
-        <f>IF(COUNT(AD17:AD18)=2,(AD17/AD18-1)*100,"")</f>
+        <f>IF(COUNT(AD17:AD18)=2,ROUND((AD17/AD18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY17" s="6">
-        <f>IF(COUNT(AI17:AI18)=2,(AI17/AI18-1)*100,"")</f>
+        <f>IF(COUNT(AI17:AI18)=2,ROUND((AI17/AI18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ17" s="6">
-        <f>IF(COUNT(AN17:AN18)=2,(AN17/AN18-1)*100,"")</f>
+        <f>IF(COUNT(AN17:AN18)=2,ROUND((AN17/AN18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA17" s="6">
-        <f>IF(COUNT(AS17:AS18)=2,(AS17/AS18-1)*100,"")</f>
+        <f>IF(COUNT(AS17:AS18)=2,ROUND((AS17/AS18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB17" s="5" t="n">
         <v>15.99</v>
       </c>
       <c r="BC17" s="6">
-        <f>IF(COUNT(BB17:BB18)=2,(BB17/BB18-1)*100,"")</f>
+        <f>IF(COUNT(BB17:BB18)=2,ROUND((BB17/BB18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD17" s="6" t="n">
@@ -4054,11 +4054,11 @@
         <v>179.55</v>
       </c>
       <c r="D18" s="6">
-        <f>IF(COUNT(B18:B19)=2,(B18/B19-1)*100,"")</f>
+        <f>IF(COUNT(B18:B19)=2,ROUND((B18/B19-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E18" s="6">
-        <f>IF(COUNT(C18:C19)=2,(C18/C19-1)*100,"")</f>
+        <f>IF(COUNT(C18:C19)=2,ROUND((C18/C19-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F18" s="5" t="n">
@@ -4182,42 +4182,42 @@
         <v>106.58</v>
       </c>
       <c r="AT18" s="6">
-        <f>IF(COUNT(J18:J19)=2,(J18/J19-1)*100,"")</f>
+        <f>IF(COUNT(J18:J19)=2,ROUND((J18/J19-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU18" s="6">
-        <f>IF(COUNT(O18:O19)=2,(O18/O19-1)*100,"")</f>
+        <f>IF(COUNT(O18:O19)=2,ROUND((O18/O19-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV18" s="6">
-        <f>IF(COUNT(T18:T19)=2,(T18/T19-1)*100,"")</f>
+        <f>IF(COUNT(T18:T19)=2,ROUND((T18/T19-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW18" s="6">
-        <f>IF(COUNT(Y18:Y19)=2,(Y18/Y19-1)*100,"")</f>
+        <f>IF(COUNT(Y18:Y19)=2,ROUND((Y18/Y19-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX18" s="6">
-        <f>IF(COUNT(AD18:AD19)=2,(AD18/AD19-1)*100,"")</f>
+        <f>IF(COUNT(AD18:AD19)=2,ROUND((AD18/AD19-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY18" s="6">
-        <f>IF(COUNT(AI18:AI19)=2,(AI18/AI19-1)*100,"")</f>
+        <f>IF(COUNT(AI18:AI19)=2,ROUND((AI18/AI19-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ18" s="6">
-        <f>IF(COUNT(AN18:AN19)=2,(AN18/AN19-1)*100,"")</f>
+        <f>IF(COUNT(AN18:AN19)=2,ROUND((AN18/AN19-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA18" s="6">
-        <f>IF(COUNT(AS18:AS19)=2,(AS18/AS19-1)*100,"")</f>
+        <f>IF(COUNT(AS18:AS19)=2,ROUND((AS18/AS19-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB18" s="5" t="n">
         <v>17.09</v>
       </c>
       <c r="BC18" s="6">
-        <f>IF(COUNT(BB18:BB19)=2,(BB18/BB19-1)*100,"")</f>
+        <f>IF(COUNT(BB18:BB19)=2,ROUND((BB18/BB19-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD18" s="6" t="n">
@@ -4269,11 +4269,11 @@
         <v>173.8</v>
       </c>
       <c r="D19" s="6">
-        <f>IF(COUNT(B19:B20)=2,(B19/B20-1)*100,"")</f>
+        <f>IF(COUNT(B19:B20)=2,ROUND((B19/B20-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E19" s="6">
-        <f>IF(COUNT(C19:C20)=2,(C19/C20-1)*100,"")</f>
+        <f>IF(COUNT(C19:C20)=2,ROUND((C19/C20-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F19" s="5" t="n">
@@ -4397,42 +4397,42 @@
         <v>109.51</v>
       </c>
       <c r="AT19" s="6">
-        <f>IF(COUNT(J19:J20)=2,(J19/J20-1)*100,"")</f>
+        <f>IF(COUNT(J19:J20)=2,ROUND((J19/J20-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU19" s="6">
-        <f>IF(COUNT(O19:O20)=2,(O19/O20-1)*100,"")</f>
+        <f>IF(COUNT(O19:O20)=2,ROUND((O19/O20-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV19" s="6">
-        <f>IF(COUNT(T19:T20)=2,(T19/T20-1)*100,"")</f>
+        <f>IF(COUNT(T19:T20)=2,ROUND((T19/T20-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW19" s="6">
-        <f>IF(COUNT(Y19:Y20)=2,(Y19/Y20-1)*100,"")</f>
+        <f>IF(COUNT(Y19:Y20)=2,ROUND((Y19/Y20-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX19" s="6">
-        <f>IF(COUNT(AD19:AD20)=2,(AD19/AD20-1)*100,"")</f>
+        <f>IF(COUNT(AD19:AD20)=2,ROUND((AD19/AD20-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY19" s="6">
-        <f>IF(COUNT(AI19:AI20)=2,(AI19/AI20-1)*100,"")</f>
+        <f>IF(COUNT(AI19:AI20)=2,ROUND((AI19/AI20-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ19" s="6">
-        <f>IF(COUNT(AN19:AN20)=2,(AN19/AN20-1)*100,"")</f>
+        <f>IF(COUNT(AN19:AN20)=2,ROUND((AN19/AN20-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA19" s="6">
-        <f>IF(COUNT(AS19:AS20)=2,(AS19/AS20-1)*100,"")</f>
+        <f>IF(COUNT(AS19:AS20)=2,ROUND((AS19/AS20-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB19" s="5" t="n">
         <v>20.66</v>
       </c>
       <c r="BC19" s="6">
-        <f>IF(COUNT(BB19:BB20)=2,(BB19/BB20-1)*100,"")</f>
+        <f>IF(COUNT(BB19:BB20)=2,ROUND((BB19/BB20-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD19" s="6" t="n">
@@ -4484,11 +4484,11 @@
         <v>179.29</v>
       </c>
       <c r="D20" s="6">
-        <f>IF(COUNT(B20:B21)=2,(B20/B21-1)*100,"")</f>
+        <f>IF(COUNT(B20:B21)=2,ROUND((B20/B21-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E20" s="6">
-        <f>IF(COUNT(C20:C21)=2,(C20/C21-1)*100,"")</f>
+        <f>IF(COUNT(C20:C21)=2,ROUND((C20/C21-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F20" s="5" t="n">
@@ -4612,42 +4612,42 @@
         <v>109.67</v>
       </c>
       <c r="AT20" s="6">
-        <f>IF(COUNT(J20:J21)=2,(J20/J21-1)*100,"")</f>
+        <f>IF(COUNT(J20:J21)=2,ROUND((J20/J21-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU20" s="6">
-        <f>IF(COUNT(O20:O21)=2,(O20/O21-1)*100,"")</f>
+        <f>IF(COUNT(O20:O21)=2,ROUND((O20/O21-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV20" s="6">
-        <f>IF(COUNT(T20:T21)=2,(T20/T21-1)*100,"")</f>
+        <f>IF(COUNT(T20:T21)=2,ROUND((T20/T21-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW20" s="6">
-        <f>IF(COUNT(Y20:Y21)=2,(Y20/Y21-1)*100,"")</f>
+        <f>IF(COUNT(Y20:Y21)=2,ROUND((Y20/Y21-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX20" s="6">
-        <f>IF(COUNT(AD20:AD21)=2,(AD20/AD21-1)*100,"")</f>
+        <f>IF(COUNT(AD20:AD21)=2,ROUND((AD20/AD21-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY20" s="6">
-        <f>IF(COUNT(AI20:AI21)=2,(AI20/AI21-1)*100,"")</f>
+        <f>IF(COUNT(AI20:AI21)=2,ROUND((AI20/AI21-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ20" s="6">
-        <f>IF(COUNT(AN20:AN21)=2,(AN20/AN21-1)*100,"")</f>
+        <f>IF(COUNT(AN20:AN21)=2,ROUND((AN20/AN21-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA20" s="6">
-        <f>IF(COUNT(AS20:AS21)=2,(AS20/AS21-1)*100,"")</f>
+        <f>IF(COUNT(AS20:AS21)=2,ROUND((AS20/AS21-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB20" s="5" t="n">
         <v>18.21</v>
       </c>
       <c r="BC20" s="6">
-        <f>IF(COUNT(BB20:BB21)=2,(BB20/BB21-1)*100,"")</f>
+        <f>IF(COUNT(BB20:BB21)=2,ROUND((BB20/BB21-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD20" s="6" t="n">
@@ -4699,11 +4699,11 @@
         <v>178.54</v>
       </c>
       <c r="D21" s="6">
-        <f>IF(COUNT(B21:B22)=2,(B21/B22-1)*100,"")</f>
+        <f>IF(COUNT(B21:B22)=2,ROUND((B21/B22-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E21" s="6">
-        <f>IF(COUNT(C21:C22)=2,(C21/C22-1)*100,"")</f>
+        <f>IF(COUNT(C21:C22)=2,ROUND((C21/C22-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F21" s="5" t="n">
@@ -4827,42 +4827,42 @@
         <v>107.66</v>
       </c>
       <c r="AT21" s="6">
-        <f>IF(COUNT(J21:J22)=2,(J21/J22-1)*100,"")</f>
+        <f>IF(COUNT(J21:J22)=2,ROUND((J21/J22-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU21" s="6">
-        <f>IF(COUNT(O21:O22)=2,(O21/O22-1)*100,"")</f>
+        <f>IF(COUNT(O21:O22)=2,ROUND((O21/O22-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV21" s="6">
-        <f>IF(COUNT(T21:T22)=2,(T21/T22-1)*100,"")</f>
+        <f>IF(COUNT(T21:T22)=2,ROUND((T21/T22-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW21" s="6">
-        <f>IF(COUNT(Y21:Y22)=2,(Y21/Y22-1)*100,"")</f>
+        <f>IF(COUNT(Y21:Y22)=2,ROUND((Y21/Y22-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX21" s="6">
-        <f>IF(COUNT(AD21:AD22)=2,(AD21/AD22-1)*100,"")</f>
+        <f>IF(COUNT(AD21:AD22)=2,ROUND((AD21/AD22-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY21" s="6">
-        <f>IF(COUNT(AI21:AI22)=2,(AI21/AI22-1)*100,"")</f>
+        <f>IF(COUNT(AI21:AI22)=2,ROUND((AI21/AI22-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ21" s="6">
-        <f>IF(COUNT(AN21:AN22)=2,(AN21/AN22-1)*100,"")</f>
+        <f>IF(COUNT(AN21:AN22)=2,ROUND((AN21/AN22-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA21" s="6">
-        <f>IF(COUNT(AS21:AS22)=2,(AS21/AS22-1)*100,"")</f>
+        <f>IF(COUNT(AS21:AS22)=2,ROUND((AS21/AS22-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB21" s="5" t="n">
         <v>18.67</v>
       </c>
       <c r="BC21" s="6">
-        <f>IF(COUNT(BB21:BB22)=2,(BB21/BB22-1)*100,"")</f>
+        <f>IF(COUNT(BB21:BB22)=2,ROUND((BB21/BB22-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD21" s="6" t="n">
@@ -4914,11 +4914,11 @@
         <v>178.56</v>
       </c>
       <c r="D22" s="6">
-        <f>IF(COUNT(B22:B23)=2,(B22/B23-1)*100,"")</f>
+        <f>IF(COUNT(B22:B23)=2,ROUND((B22/B23-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E22" s="6">
-        <f>IF(COUNT(C22:C23)=2,(C22/C23-1)*100,"")</f>
+        <f>IF(COUNT(C22:C23)=2,ROUND((C22/C23-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F22" s="5" t="n">
@@ -5042,42 +5042,42 @@
         <v>106.3</v>
       </c>
       <c r="AT22" s="6">
-        <f>IF(COUNT(J22:J23)=2,(J22/J23-1)*100,"")</f>
+        <f>IF(COUNT(J22:J23)=2,ROUND((J22/J23-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU22" s="6">
-        <f>IF(COUNT(O22:O23)=2,(O22/O23-1)*100,"")</f>
+        <f>IF(COUNT(O22:O23)=2,ROUND((O22/O23-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV22" s="6">
-        <f>IF(COUNT(T22:T23)=2,(T22/T23-1)*100,"")</f>
+        <f>IF(COUNT(T22:T23)=2,ROUND((T22/T23-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW22" s="6">
-        <f>IF(COUNT(Y22:Y23)=2,(Y22/Y23-1)*100,"")</f>
+        <f>IF(COUNT(Y22:Y23)=2,ROUND((Y22/Y23-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX22" s="6">
-        <f>IF(COUNT(AD22:AD23)=2,(AD22/AD23-1)*100,"")</f>
+        <f>IF(COUNT(AD22:AD23)=2,ROUND((AD22/AD23-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY22" s="6">
-        <f>IF(COUNT(AI22:AI23)=2,(AI22/AI23-1)*100,"")</f>
+        <f>IF(COUNT(AI22:AI23)=2,ROUND((AI22/AI23-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ22" s="6">
-        <f>IF(COUNT(AN22:AN23)=2,(AN22/AN23-1)*100,"")</f>
+        <f>IF(COUNT(AN22:AN23)=2,ROUND((AN22/AN23-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA22" s="6">
-        <f>IF(COUNT(AS22:AS23)=2,(AS22/AS23-1)*100,"")</f>
+        <f>IF(COUNT(AS22:AS23)=2,ROUND((AS22/AS23-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB22" s="5" t="n">
         <v>18.58</v>
       </c>
       <c r="BC22" s="6">
-        <f>IF(COUNT(BB22:BB23)=2,(BB22/BB23-1)*100,"")</f>
+        <f>IF(COUNT(BB22:BB23)=2,ROUND((BB22/BB23-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD22" s="6" t="n">
@@ -5129,11 +5129,11 @@
         <v>178.37</v>
       </c>
       <c r="D23" s="6">
-        <f>IF(COUNT(B23:B24)=2,(B23/B24-1)*100,"")</f>
+        <f>IF(COUNT(B23:B24)=2,ROUND((B23/B24-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E23" s="6">
-        <f>IF(COUNT(C23:C24)=2,(C23/C24-1)*100,"")</f>
+        <f>IF(COUNT(C23:C24)=2,ROUND((C23/C24-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F23" s="5" t="n">
@@ -5257,42 +5257,42 @@
         <v>105.38</v>
       </c>
       <c r="AT23" s="6">
-        <f>IF(COUNT(J23:J24)=2,(J23/J24-1)*100,"")</f>
+        <f>IF(COUNT(J23:J24)=2,ROUND((J23/J24-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU23" s="6">
-        <f>IF(COUNT(O23:O24)=2,(O23/O24-1)*100,"")</f>
+        <f>IF(COUNT(O23:O24)=2,ROUND((O23/O24-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV23" s="6">
-        <f>IF(COUNT(T23:T24)=2,(T23/T24-1)*100,"")</f>
+        <f>IF(COUNT(T23:T24)=2,ROUND((T23/T24-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW23" s="6">
-        <f>IF(COUNT(Y23:Y24)=2,(Y23/Y24-1)*100,"")</f>
+        <f>IF(COUNT(Y23:Y24)=2,ROUND((Y23/Y24-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX23" s="6">
-        <f>IF(COUNT(AD23:AD24)=2,(AD23/AD24-1)*100,"")</f>
+        <f>IF(COUNT(AD23:AD24)=2,ROUND((AD23/AD24-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY23" s="6">
-        <f>IF(COUNT(AI23:AI24)=2,(AI23/AI24-1)*100,"")</f>
+        <f>IF(COUNT(AI23:AI24)=2,ROUND((AI23/AI24-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ23" s="6">
-        <f>IF(COUNT(AN23:AN24)=2,(AN23/AN24-1)*100,"")</f>
+        <f>IF(COUNT(AN23:AN24)=2,ROUND((AN23/AN24-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA23" s="6">
-        <f>IF(COUNT(AS23:AS24)=2,(AS23/AS24-1)*100,"")</f>
+        <f>IF(COUNT(AS23:AS24)=2,ROUND((AS23/AS24-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB23" s="5" t="n">
         <v>18.7</v>
       </c>
       <c r="BC23" s="6">
-        <f>IF(COUNT(BB23:BB24)=2,(BB23/BB24-1)*100,"")</f>
+        <f>IF(COUNT(BB23:BB24)=2,ROUND((BB23/BB24-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD23" s="6" t="n">
@@ -5344,11 +5344,11 @@
         <v>182.85</v>
       </c>
       <c r="D24" s="6">
-        <f>IF(COUNT(B24:B25)=2,(B24/B25-1)*100,"")</f>
+        <f>IF(COUNT(B24:B25)=2,ROUND((B24/B25-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E24" s="6">
-        <f>IF(COUNT(C24:C25)=2,(C24/C25-1)*100,"")</f>
+        <f>IF(COUNT(C24:C25)=2,ROUND((C24/C25-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F24" s="5" t="n">
@@ -5472,42 +5472,42 @@
         <v>109.2</v>
       </c>
       <c r="AT24" s="6">
-        <f>IF(COUNT(J24:J25)=2,(J24/J25-1)*100,"")</f>
+        <f>IF(COUNT(J24:J25)=2,ROUND((J24/J25-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU24" s="6">
-        <f>IF(COUNT(O24:O25)=2,(O24/O25-1)*100,"")</f>
+        <f>IF(COUNT(O24:O25)=2,ROUND((O24/O25-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV24" s="6">
-        <f>IF(COUNT(T24:T25)=2,(T24/T25-1)*100,"")</f>
+        <f>IF(COUNT(T24:T25)=2,ROUND((T24/T25-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW24" s="6">
-        <f>IF(COUNT(Y24:Y25)=2,(Y24/Y25-1)*100,"")</f>
+        <f>IF(COUNT(Y24:Y25)=2,ROUND((Y24/Y25-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX24" s="6">
-        <f>IF(COUNT(AD24:AD25)=2,(AD24/AD25-1)*100,"")</f>
+        <f>IF(COUNT(AD24:AD25)=2,ROUND((AD24/AD25-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY24" s="6">
-        <f>IF(COUNT(AI24:AI25)=2,(AI24/AI25-1)*100,"")</f>
+        <f>IF(COUNT(AI24:AI25)=2,ROUND((AI24/AI25-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ24" s="6">
-        <f>IF(COUNT(AN24:AN25)=2,(AN24/AN25-1)*100,"")</f>
+        <f>IF(COUNT(AN24:AN25)=2,ROUND((AN24/AN25-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA24" s="6">
-        <f>IF(COUNT(AS24:AS25)=2,(AS24/AS25-1)*100,"")</f>
+        <f>IF(COUNT(AS24:AS25)=2,ROUND((AS24/AS25-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB24" s="5" t="n">
         <v>16.64</v>
       </c>
       <c r="BC24" s="6">
-        <f>IF(COUNT(BB24:BB25)=2,(BB24/BB25-1)*100,"")</f>
+        <f>IF(COUNT(BB24:BB25)=2,ROUND((BB24/BB25-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD24" s="6" t="n">
@@ -5559,11 +5559,11 @@
         <v>183.34</v>
       </c>
       <c r="D25" s="6">
-        <f>IF(COUNT(B25:B26)=2,(B25/B26-1)*100,"")</f>
+        <f>IF(COUNT(B25:B26)=2,ROUND((B25/B26-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E25" s="6">
-        <f>IF(COUNT(C25:C26)=2,(C25/C26-1)*100,"")</f>
+        <f>IF(COUNT(C25:C26)=2,ROUND((C25/C26-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F25" s="5" t="n">
@@ -5687,42 +5687,42 @@
         <v>110.03</v>
       </c>
       <c r="AT25" s="6">
-        <f>IF(COUNT(J25:J26)=2,(J25/J26-1)*100,"")</f>
+        <f>IF(COUNT(J25:J26)=2,ROUND((J25/J26-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU25" s="6">
-        <f>IF(COUNT(O25:O26)=2,(O25/O26-1)*100,"")</f>
+        <f>IF(COUNT(O25:O26)=2,ROUND((O25/O26-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV25" s="6">
-        <f>IF(COUNT(T25:T26)=2,(T25/T26-1)*100,"")</f>
+        <f>IF(COUNT(T25:T26)=2,ROUND((T25/T26-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW25" s="6">
-        <f>IF(COUNT(Y25:Y26)=2,(Y25/Y26-1)*100,"")</f>
+        <f>IF(COUNT(Y25:Y26)=2,ROUND((Y25/Y26-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX25" s="6">
-        <f>IF(COUNT(AD25:AD26)=2,(AD25/AD26-1)*100,"")</f>
+        <f>IF(COUNT(AD25:AD26)=2,ROUND((AD25/AD26-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY25" s="6">
-        <f>IF(COUNT(AI25:AI26)=2,(AI25/AI26-1)*100,"")</f>
+        <f>IF(COUNT(AI25:AI26)=2,ROUND((AI25/AI26-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ25" s="6">
-        <f>IF(COUNT(AN25:AN26)=2,(AN25/AN26-1)*100,"")</f>
+        <f>IF(COUNT(AN25:AN26)=2,ROUND((AN25/AN26-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA25" s="6">
-        <f>IF(COUNT(AS25:AS26)=2,(AS25/AS26-1)*100,"")</f>
+        <f>IF(COUNT(AS25:AS26)=2,ROUND((AS25/AS26-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB25" s="5" t="n">
         <v>17.05</v>
       </c>
       <c r="BC25" s="6">
-        <f>IF(COUNT(BB25:BB26)=2,(BB25/BB26-1)*100,"")</f>
+        <f>IF(COUNT(BB25:BB26)=2,ROUND((BB25/BB26-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD25" s="6" t="n">
@@ -5774,11 +5774,11 @@
         <v>180.23</v>
       </c>
       <c r="D26" s="6">
-        <f>IF(COUNT(B26:B27)=2,(B26/B27-1)*100,"")</f>
+        <f>IF(COUNT(B26:B27)=2,ROUND((B26/B27-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E26" s="6">
-        <f>IF(COUNT(C26:C27)=2,(C26/C27-1)*100,"")</f>
+        <f>IF(COUNT(C26:C27)=2,ROUND((C26/C27-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F26" s="5" t="n">
@@ -5902,42 +5902,42 @@
         <v>110.8</v>
       </c>
       <c r="AT26" s="6">
-        <f>IF(COUNT(J26:J27)=2,(J26/J27-1)*100,"")</f>
+        <f>IF(COUNT(J26:J27)=2,ROUND((J26/J27-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU26" s="6">
-        <f>IF(COUNT(O26:O27)=2,(O26/O27-1)*100,"")</f>
+        <f>IF(COUNT(O26:O27)=2,ROUND((O26/O27-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV26" s="6">
-        <f>IF(COUNT(T26:T27)=2,(T26/T27-1)*100,"")</f>
+        <f>IF(COUNT(T26:T27)=2,ROUND((T26/T27-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW26" s="6">
-        <f>IF(COUNT(Y26:Y27)=2,(Y26/Y27-1)*100,"")</f>
+        <f>IF(COUNT(Y26:Y27)=2,ROUND((Y26/Y27-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX26" s="6">
-        <f>IF(COUNT(AD26:AD27)=2,(AD26/AD27-1)*100,"")</f>
+        <f>IF(COUNT(AD26:AD27)=2,ROUND((AD26/AD27-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY26" s="6">
-        <f>IF(COUNT(AI26:AI27)=2,(AI26/AI27-1)*100,"")</f>
+        <f>IF(COUNT(AI26:AI27)=2,ROUND((AI26/AI27-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ26" s="6">
-        <f>IF(COUNT(AN26:AN27)=2,(AN26/AN27-1)*100,"")</f>
+        <f>IF(COUNT(AN26:AN27)=2,ROUND((AN26/AN27-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA26" s="6">
-        <f>IF(COUNT(AS26:AS27)=2,(AS26/AS27-1)*100,"")</f>
+        <f>IF(COUNT(AS26:AS27)=2,ROUND((AS26/AS27-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB26" s="5" t="n">
         <v>18.65</v>
       </c>
       <c r="BC26" s="6">
-        <f>IF(COUNT(BB26:BB27)=2,(BB26/BB27-1)*100,"")</f>
+        <f>IF(COUNT(BB26:BB27)=2,ROUND((BB26/BB27-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD26" s="6" t="n">
@@ -5989,11 +5989,11 @@
         <v>180.98</v>
       </c>
       <c r="D27" s="6">
-        <f>IF(COUNT(B27:B28)=2,(B27/B28-1)*100,"")</f>
+        <f>IF(COUNT(B27:B28)=2,ROUND((B27/B28-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E27" s="6">
-        <f>IF(COUNT(C27:C28)=2,(C27/C28-1)*100,"")</f>
+        <f>IF(COUNT(C27:C28)=2,ROUND((C27/C28-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F27" s="5" t="n">
@@ -6117,42 +6117,42 @@
         <v>110.65</v>
       </c>
       <c r="AT27" s="6">
-        <f>IF(COUNT(J27:J28)=2,(J27/J28-1)*100,"")</f>
+        <f>IF(COUNT(J27:J28)=2,ROUND((J27/J28-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU27" s="6">
-        <f>IF(COUNT(O27:O28)=2,(O27/O28-1)*100,"")</f>
+        <f>IF(COUNT(O27:O28)=2,ROUND((O27/O28-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV27" s="6">
-        <f>IF(COUNT(T27:T28)=2,(T27/T28-1)*100,"")</f>
+        <f>IF(COUNT(T27:T28)=2,ROUND((T27/T28-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW27" s="6">
-        <f>IF(COUNT(Y27:Y28)=2,(Y27/Y28-1)*100,"")</f>
+        <f>IF(COUNT(Y27:Y28)=2,ROUND((Y27/Y28-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX27" s="6">
-        <f>IF(COUNT(AD27:AD28)=2,(AD27/AD28-1)*100,"")</f>
+        <f>IF(COUNT(AD27:AD28)=2,ROUND((AD27/AD28-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY27" s="6">
-        <f>IF(COUNT(AI27:AI28)=2,(AI27/AI28-1)*100,"")</f>
+        <f>IF(COUNT(AI27:AI28)=2,ROUND((AI27/AI28-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ27" s="6">
-        <f>IF(COUNT(AN27:AN28)=2,(AN27/AN28-1)*100,"")</f>
+        <f>IF(COUNT(AN27:AN28)=2,ROUND((AN27/AN28-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA27" s="6">
-        <f>IF(COUNT(AS27:AS28)=2,(AS27/AS28-1)*100,"")</f>
+        <f>IF(COUNT(AS27:AS28)=2,ROUND((AS27/AS28-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB27" s="5" t="n">
         <v>18.77</v>
       </c>
       <c r="BC27" s="6">
-        <f>IF(COUNT(BB27:BB28)=2,(BB27/BB28-1)*100,"")</f>
+        <f>IF(COUNT(BB27:BB28)=2,ROUND((BB27/BB28-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD27" s="6" t="n">
@@ -6204,11 +6204,11 @@
         <v>184.73</v>
       </c>
       <c r="D28" s="6">
-        <f>IF(COUNT(B28:B29)=2,(B28/B29-1)*100,"")</f>
+        <f>IF(COUNT(B28:B29)=2,ROUND((B28/B29-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E28" s="6">
-        <f>IF(COUNT(C28:C29)=2,(C28/C29-1)*100,"")</f>
+        <f>IF(COUNT(C28:C29)=2,ROUND((C28/C29-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F28" s="5" t="n">
@@ -6332,42 +6332,42 @@
         <v>112.65</v>
       </c>
       <c r="AT28" s="6">
-        <f>IF(COUNT(J28:J29)=2,(J28/J29-1)*100,"")</f>
+        <f>IF(COUNT(J28:J29)=2,ROUND((J28/J29-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU28" s="6">
-        <f>IF(COUNT(O28:O29)=2,(O28/O29-1)*100,"")</f>
+        <f>IF(COUNT(O28:O29)=2,ROUND((O28/O29-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV28" s="6">
-        <f>IF(COUNT(T28:T29)=2,(T28/T29-1)*100,"")</f>
+        <f>IF(COUNT(T28:T29)=2,ROUND((T28/T29-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW28" s="6">
-        <f>IF(COUNT(Y28:Y29)=2,(Y28/Y29-1)*100,"")</f>
+        <f>IF(COUNT(Y28:Y29)=2,ROUND((Y28/Y29-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX28" s="6">
-        <f>IF(COUNT(AD28:AD29)=2,(AD28/AD29-1)*100,"")</f>
+        <f>IF(COUNT(AD28:AD29)=2,ROUND((AD28/AD29-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY28" s="6">
-        <f>IF(COUNT(AI28:AI29)=2,(AI28/AI29-1)*100,"")</f>
+        <f>IF(COUNT(AI28:AI29)=2,ROUND((AI28/AI29-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ28" s="6">
-        <f>IF(COUNT(AN28:AN29)=2,(AN28/AN29-1)*100,"")</f>
+        <f>IF(COUNT(AN28:AN29)=2,ROUND((AN28/AN29-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA28" s="6">
-        <f>IF(COUNT(AS28:AS29)=2,(AS28/AS29-1)*100,"")</f>
+        <f>IF(COUNT(AS28:AS29)=2,ROUND((AS28/AS29-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB28" s="5" t="n">
         <v>16.73</v>
       </c>
       <c r="BC28" s="6">
-        <f>IF(COUNT(BB28:BB29)=2,(BB28/BB29-1)*100,"")</f>
+        <f>IF(COUNT(BB28:BB29)=2,ROUND((BB28/BB29-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD28" s="6" t="n">
@@ -6419,11 +6419,11 @@
         <v>186.67</v>
       </c>
       <c r="D29" s="6">
-        <f>IF(COUNT(B29:B30)=2,(B29/B30-1)*100,"")</f>
+        <f>IF(COUNT(B29:B30)=2,ROUND((B29/B30-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E29" s="6">
-        <f>IF(COUNT(C29:C30)=2,(C29/C30-1)*100,"")</f>
+        <f>IF(COUNT(C29:C30)=2,ROUND((C29/C30-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F29" s="5" t="n">
@@ -6547,42 +6547,42 @@
         <v>113.38</v>
       </c>
       <c r="AT29" s="6">
-        <f>IF(COUNT(J29:J30)=2,(J29/J30-1)*100,"")</f>
+        <f>IF(COUNT(J29:J30)=2,ROUND((J29/J30-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU29" s="6">
-        <f>IF(COUNT(O29:O30)=2,(O29/O30-1)*100,"")</f>
+        <f>IF(COUNT(O29:O30)=2,ROUND((O29/O30-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV29" s="6">
-        <f>IF(COUNT(T29:T30)=2,(T29/T30-1)*100,"")</f>
+        <f>IF(COUNT(T29:T30)=2,ROUND((T29/T30-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW29" s="6">
-        <f>IF(COUNT(Y29:Y30)=2,(Y29/Y30-1)*100,"")</f>
+        <f>IF(COUNT(Y29:Y30)=2,ROUND((Y29/Y30-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX29" s="6">
-        <f>IF(COUNT(AD29:AD30)=2,(AD29/AD30-1)*100,"")</f>
+        <f>IF(COUNT(AD29:AD30)=2,ROUND((AD29/AD30-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY29" s="6">
-        <f>IF(COUNT(AI29:AI30)=2,(AI29/AI30-1)*100,"")</f>
+        <f>IF(COUNT(AI29:AI30)=2,ROUND((AI29/AI30-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ29" s="6">
-        <f>IF(COUNT(AN29:AN30)=2,(AN29/AN30-1)*100,"")</f>
+        <f>IF(COUNT(AN29:AN30)=2,ROUND((AN29/AN30-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA29" s="6">
-        <f>IF(COUNT(AS29:AS30)=2,(AS29/AS30-1)*100,"")</f>
+        <f>IF(COUNT(AS29:AS30)=2,ROUND((AS29/AS30-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB29" s="5" t="n">
         <v>15.67</v>
       </c>
       <c r="BC29" s="6">
-        <f>IF(COUNT(BB29:BB30)=2,(BB29/BB30-1)*100,"")</f>
+        <f>IF(COUNT(BB29:BB30)=2,ROUND((BB29/BB30-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD29" s="6" t="n">
@@ -6634,11 +6634,11 @@
         <v>185.27</v>
       </c>
       <c r="D30" s="6">
-        <f>IF(COUNT(B30:B31)=2,(B30/B31-1)*100,"")</f>
+        <f>IF(COUNT(B30:B31)=2,ROUND((B30/B31-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E30" s="6">
-        <f>IF(COUNT(C30:C31)=2,(C30/C31-1)*100,"")</f>
+        <f>IF(COUNT(C30:C31)=2,ROUND((C30/C31-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F30" s="5" t="n">
@@ -6762,42 +6762,42 @@
         <v>111.45</v>
       </c>
       <c r="AT30" s="6">
-        <f>IF(COUNT(J30:J31)=2,(J30/J31-1)*100,"")</f>
+        <f>IF(COUNT(J30:J31)=2,ROUND((J30/J31-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU30" s="6">
-        <f>IF(COUNT(O30:O31)=2,(O30/O31-1)*100,"")</f>
+        <f>IF(COUNT(O30:O31)=2,ROUND((O30/O31-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV30" s="6">
-        <f>IF(COUNT(T30:T31)=2,(T30/T31-1)*100,"")</f>
+        <f>IF(COUNT(T30:T31)=2,ROUND((T30/T31-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW30" s="6">
-        <f>IF(COUNT(Y30:Y31)=2,(Y30/Y31-1)*100,"")</f>
+        <f>IF(COUNT(Y30:Y31)=2,ROUND((Y30/Y31-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX30" s="6">
-        <f>IF(COUNT(AD30:AD31)=2,(AD30/AD31-1)*100,"")</f>
+        <f>IF(COUNT(AD30:AD31)=2,ROUND((AD30/AD31-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY30" s="6">
-        <f>IF(COUNT(AI30:AI31)=2,(AI30/AI31-1)*100,"")</f>
+        <f>IF(COUNT(AI30:AI31)=2,ROUND((AI30/AI31-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ30" s="6">
-        <f>IF(COUNT(AN30:AN31)=2,(AN30/AN31-1)*100,"")</f>
+        <f>IF(COUNT(AN30:AN31)=2,ROUND((AN30/AN31-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA30" s="6">
-        <f>IF(COUNT(AS30:AS31)=2,(AS30/AS31-1)*100,"")</f>
+        <f>IF(COUNT(AS30:AS31)=2,ROUND((AS30/AS31-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB30" s="5" t="n">
         <v>16.5</v>
       </c>
       <c r="BC30" s="6">
-        <f>IF(COUNT(BB30:BB31)=2,(BB30/BB31-1)*100,"")</f>
+        <f>IF(COUNT(BB30:BB31)=2,ROUND((BB30/BB31-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD30" s="6" t="n">
@@ -6849,11 +6849,11 @@
         <v>183.93</v>
       </c>
       <c r="D31" s="6">
-        <f>IF(COUNT(B31:B32)=2,(B31/B32-1)*100,"")</f>
+        <f>IF(COUNT(B31:B32)=2,ROUND((B31/B32-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E31" s="6">
-        <f>IF(COUNT(C31:C32)=2,(C31/C32-1)*100,"")</f>
+        <f>IF(COUNT(C31:C32)=2,ROUND((C31/C32-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F31" s="5" t="n">
@@ -6977,42 +6977,42 @@
         <v>111.59</v>
       </c>
       <c r="AT31" s="6">
-        <f>IF(COUNT(J31:J32)=2,(J31/J32-1)*100,"")</f>
+        <f>IF(COUNT(J31:J32)=2,ROUND((J31/J32-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU31" s="6">
-        <f>IF(COUNT(O31:O32)=2,(O31/O32-1)*100,"")</f>
+        <f>IF(COUNT(O31:O32)=2,ROUND((O31/O32-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV31" s="6">
-        <f>IF(COUNT(T31:T32)=2,(T31/T32-1)*100,"")</f>
+        <f>IF(COUNT(T31:T32)=2,ROUND((T31/T32-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW31" s="6">
-        <f>IF(COUNT(Y31:Y32)=2,(Y31/Y32-1)*100,"")</f>
+        <f>IF(COUNT(Y31:Y32)=2,ROUND((Y31/Y32-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX31" s="6">
-        <f>IF(COUNT(AD31:AD32)=2,(AD31/AD32-1)*100,"")</f>
+        <f>IF(COUNT(AD31:AD32)=2,ROUND((AD31/AD32-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY31" s="6">
-        <f>IF(COUNT(AI31:AI32)=2,(AI31/AI32-1)*100,"")</f>
+        <f>IF(COUNT(AI31:AI32)=2,ROUND((AI31/AI32-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ31" s="6">
-        <f>IF(COUNT(AN31:AN32)=2,(AN31/AN32-1)*100,"")</f>
+        <f>IF(COUNT(AN31:AN32)=2,ROUND((AN31/AN32-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA31" s="6">
-        <f>IF(COUNT(AS31:AS32)=2,(AS31/AS32-1)*100,"")</f>
+        <f>IF(COUNT(AS31:AS32)=2,ROUND((AS31/AS32-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB31" s="5" t="n">
         <v>17.16</v>
       </c>
       <c r="BC31" s="6">
-        <f>IF(COUNT(BB31:BB32)=2,(BB31/BB32-1)*100,"")</f>
+        <f>IF(COUNT(BB31:BB32)=2,ROUND((BB31/BB32-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD31" s="6" t="n">
@@ -7064,11 +7064,11 @@
         <v>186.95</v>
       </c>
       <c r="D32" s="6">
-        <f>IF(COUNT(B32:B33)=2,(B32/B33-1)*100,"")</f>
+        <f>IF(COUNT(B32:B33)=2,ROUND((B32/B33-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E32" s="6">
-        <f>IF(COUNT(C32:C33)=2,(C32/C33-1)*100,"")</f>
+        <f>IF(COUNT(C32:C33)=2,ROUND((C32/C33-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F32" s="5" t="n">
@@ -7192,42 +7192,42 @@
         <v>111.64</v>
       </c>
       <c r="AT32" s="6">
-        <f>IF(COUNT(J32:J33)=2,(J32/J33-1)*100,"")</f>
+        <f>IF(COUNT(J32:J33)=2,ROUND((J32/J33-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU32" s="6">
-        <f>IF(COUNT(O32:O33)=2,(O32/O33-1)*100,"")</f>
+        <f>IF(COUNT(O32:O33)=2,ROUND((O32/O33-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV32" s="6">
-        <f>IF(COUNT(T32:T33)=2,(T32/T33-1)*100,"")</f>
+        <f>IF(COUNT(T32:T33)=2,ROUND((T32/T33-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW32" s="6">
-        <f>IF(COUNT(Y32:Y33)=2,(Y32/Y33-1)*100,"")</f>
+        <f>IF(COUNT(Y32:Y33)=2,ROUND((Y32/Y33-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX32" s="6">
-        <f>IF(COUNT(AD32:AD33)=2,(AD32/AD33-1)*100,"")</f>
+        <f>IF(COUNT(AD32:AD33)=2,ROUND((AD32/AD33-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY32" s="6">
-        <f>IF(COUNT(AI32:AI33)=2,(AI32/AI33-1)*100,"")</f>
+        <f>IF(COUNT(AI32:AI33)=2,ROUND((AI32/AI33-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ32" s="6">
-        <f>IF(COUNT(AN32:AN33)=2,(AN32/AN33-1)*100,"")</f>
+        <f>IF(COUNT(AN32:AN33)=2,ROUND((AN32/AN33-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA32" s="6">
-        <f>IF(COUNT(AS32:AS33)=2,(AS32/AS33-1)*100,"")</f>
+        <f>IF(COUNT(AS32:AS33)=2,ROUND((AS32/AS33-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB32" s="5" t="n">
         <v>15.03</v>
       </c>
       <c r="BC32" s="6">
-        <f>IF(COUNT(BB32:BB33)=2,(BB32/BB33-1)*100,"")</f>
+        <f>IF(COUNT(BB32:BB33)=2,ROUND((BB32/BB33-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD32" s="6" t="n">
@@ -7279,11 +7279,11 @@
         <v>185.38</v>
       </c>
       <c r="D33" s="6">
-        <f>IF(COUNT(B33:B34)=2,(B33/B34-1)*100,"")</f>
+        <f>IF(COUNT(B33:B34)=2,ROUND((B33/B34-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E33" s="6">
-        <f>IF(COUNT(C33:C34)=2,(C33/C34-1)*100,"")</f>
+        <f>IF(COUNT(C33:C34)=2,ROUND((C33/C34-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F33" s="5" t="n">
@@ -7407,42 +7407,42 @@
         <v>110.51</v>
       </c>
       <c r="AT33" s="6">
-        <f>IF(COUNT(J33:J34)=2,(J33/J34-1)*100,"")</f>
+        <f>IF(COUNT(J33:J34)=2,ROUND((J33/J34-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU33" s="6">
-        <f>IF(COUNT(O33:O34)=2,(O33/O34-1)*100,"")</f>
+        <f>IF(COUNT(O33:O34)=2,ROUND((O33/O34-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV33" s="6">
-        <f>IF(COUNT(T33:T34)=2,(T33/T34-1)*100,"")</f>
+        <f>IF(COUNT(T33:T34)=2,ROUND((T33/T34-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW33" s="6">
-        <f>IF(COUNT(Y33:Y34)=2,(Y33/Y34-1)*100,"")</f>
+        <f>IF(COUNT(Y33:Y34)=2,ROUND((Y33/Y34-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX33" s="6">
-        <f>IF(COUNT(AD33:AD34)=2,(AD33/AD34-1)*100,"")</f>
+        <f>IF(COUNT(AD33:AD34)=2,ROUND((AD33/AD34-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY33" s="6">
-        <f>IF(COUNT(AI33:AI34)=2,(AI33/AI34-1)*100,"")</f>
+        <f>IF(COUNT(AI33:AI34)=2,ROUND((AI33/AI34-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ33" s="6">
-        <f>IF(COUNT(AN33:AN34)=2,(AN33/AN34-1)*100,"")</f>
+        <f>IF(COUNT(AN33:AN34)=2,ROUND((AN33/AN34-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA33" s="6">
-        <f>IF(COUNT(AS33:AS34)=2,(AS33/AS34-1)*100,"")</f>
+        <f>IF(COUNT(AS33:AS34)=2,ROUND((AS33/AS34-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB33" s="5" t="n">
         <v>15.84</v>
       </c>
       <c r="BC33" s="6">
-        <f>IF(COUNT(BB33:BB34)=2,(BB33/BB34-1)*100,"")</f>
+        <f>IF(COUNT(BB33:BB34)=2,ROUND((BB33/BB34-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD33" s="6" t="n">
@@ -7494,11 +7494,11 @@
         <v>182.42</v>
       </c>
       <c r="D34" s="6">
-        <f>IF(COUNT(B34:B35)=2,(B34/B35-1)*100,"")</f>
+        <f>IF(COUNT(B34:B35)=2,ROUND((B34/B35-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E34" s="6">
-        <f>IF(COUNT(C34:C35)=2,(C34/C35-1)*100,"")</f>
+        <f>IF(COUNT(C34:C35)=2,ROUND((C34/C35-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F34" s="5" t="n">
@@ -7622,42 +7622,42 @@
         <v>109.46</v>
       </c>
       <c r="AT34" s="6">
-        <f>IF(COUNT(J34:J35)=2,(J34/J35-1)*100,"")</f>
+        <f>IF(COUNT(J34:J35)=2,ROUND((J34/J35-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU34" s="6">
-        <f>IF(COUNT(O34:O35)=2,(O34/O35-1)*100,"")</f>
+        <f>IF(COUNT(O34:O35)=2,ROUND((O34/O35-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV34" s="6">
-        <f>IF(COUNT(T34:T35)=2,(T34/T35-1)*100,"")</f>
+        <f>IF(COUNT(T34:T35)=2,ROUND((T34/T35-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW34" s="6">
-        <f>IF(COUNT(Y34:Y35)=2,(Y34/Y35-1)*100,"")</f>
+        <f>IF(COUNT(Y34:Y35)=2,ROUND((Y34/Y35-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX34" s="6">
-        <f>IF(COUNT(AD34:AD35)=2,(AD34/AD35-1)*100,"")</f>
+        <f>IF(COUNT(AD34:AD35)=2,ROUND((AD34/AD35-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY34" s="6">
-        <f>IF(COUNT(AI34:AI35)=2,(AI34/AI35-1)*100,"")</f>
+        <f>IF(COUNT(AI34:AI35)=2,ROUND((AI34/AI35-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ34" s="6">
-        <f>IF(COUNT(AN34:AN35)=2,(AN34/AN35-1)*100,"")</f>
+        <f>IF(COUNT(AN34:AN35)=2,ROUND((AN34/AN35-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA34" s="6">
-        <f>IF(COUNT(AS34:AS35)=2,(AS34/AS35-1)*100,"")</f>
+        <f>IF(COUNT(AS34:AS35)=2,ROUND((AS34/AS35-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB34" s="5" t="n">
         <v>16.9</v>
       </c>
       <c r="BC34" s="6">
-        <f>IF(COUNT(BB34:BB35)=2,(BB34/BB35-1)*100,"")</f>
+        <f>IF(COUNT(BB34:BB35)=2,ROUND((BB34/BB35-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD34" s="6" t="n">
@@ -7709,11 +7709,11 @@
         <v>183.5</v>
       </c>
       <c r="D35" s="6">
-        <f>IF(COUNT(B35:B36)=2,(B35/B36-1)*100,"")</f>
+        <f>IF(COUNT(B35:B36)=2,ROUND((B35/B36-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E35" s="6">
-        <f>IF(COUNT(C35:C36)=2,(C35/C36-1)*100,"")</f>
+        <f>IF(COUNT(C35:C36)=2,ROUND((C35/C36-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F35" s="5" t="n">
@@ -7837,42 +7837,42 @@
         <v>111.02</v>
       </c>
       <c r="AT35" s="6">
-        <f>IF(COUNT(J35:J36)=2,(J35/J36-1)*100,"")</f>
+        <f>IF(COUNT(J35:J36)=2,ROUND((J35/J36-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU35" s="6">
-        <f>IF(COUNT(O35:O36)=2,(O35/O36-1)*100,"")</f>
+        <f>IF(COUNT(O35:O36)=2,ROUND((O35/O36-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV35" s="6">
-        <f>IF(COUNT(T35:T36)=2,(T35/T36-1)*100,"")</f>
+        <f>IF(COUNT(T35:T36)=2,ROUND((T35/T36-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW35" s="6">
-        <f>IF(COUNT(Y35:Y36)=2,(Y35/Y36-1)*100,"")</f>
+        <f>IF(COUNT(Y35:Y36)=2,ROUND((Y35/Y36-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX35" s="6">
-        <f>IF(COUNT(AD35:AD36)=2,(AD35/AD36-1)*100,"")</f>
+        <f>IF(COUNT(AD35:AD36)=2,ROUND((AD35/AD36-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY35" s="6">
-        <f>IF(COUNT(AI35:AI36)=2,(AI35/AI36-1)*100,"")</f>
+        <f>IF(COUNT(AI35:AI36)=2,ROUND((AI35/AI36-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ35" s="6">
-        <f>IF(COUNT(AN35:AN36)=2,(AN35/AN36-1)*100,"")</f>
+        <f>IF(COUNT(AN35:AN36)=2,ROUND((AN35/AN36-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA35" s="6">
-        <f>IF(COUNT(AS35:AS36)=2,(AS35/AS36-1)*100,"")</f>
+        <f>IF(COUNT(AS35:AS36)=2,ROUND((AS35/AS36-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB35" s="5" t="n">
         <v>16.13</v>
       </c>
       <c r="BC35" s="6">
-        <f>IF(COUNT(BB35:BB36)=2,(BB35/BB36-1)*100,"")</f>
+        <f>IF(COUNT(BB35:BB36)=2,ROUND((BB35/BB36-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD35" s="6" t="n">
@@ -7924,11 +7924,11 @@
         <v>185.21</v>
       </c>
       <c r="D36" s="6">
-        <f>IF(COUNT(B36:B37)=2,(B36/B37-1)*100,"")</f>
+        <f>IF(COUNT(B36:B37)=2,ROUND((B36/B37-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E36" s="6">
-        <f>IF(COUNT(C36:C37)=2,(C36/C37-1)*100,"")</f>
+        <f>IF(COUNT(C36:C37)=2,ROUND((C36/C37-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F36" s="5" t="n">
@@ -8052,42 +8052,42 @@
         <v>110.21</v>
       </c>
       <c r="AT36" s="6">
-        <f>IF(COUNT(J36:J37)=2,(J36/J37-1)*100,"")</f>
+        <f>IF(COUNT(J36:J37)=2,ROUND((J36/J37-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU36" s="6">
-        <f>IF(COUNT(O36:O37)=2,(O36/O37-1)*100,"")</f>
+        <f>IF(COUNT(O36:O37)=2,ROUND((O36/O37-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV36" s="6">
-        <f>IF(COUNT(T36:T37)=2,(T36/T37-1)*100,"")</f>
+        <f>IF(COUNT(T36:T37)=2,ROUND((T36/T37-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW36" s="6">
-        <f>IF(COUNT(Y36:Y37)=2,(Y36/Y37-1)*100,"")</f>
+        <f>IF(COUNT(Y36:Y37)=2,ROUND((Y36/Y37-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX36" s="6">
-        <f>IF(COUNT(AD36:AD37)=2,(AD36/AD37-1)*100,"")</f>
+        <f>IF(COUNT(AD36:AD37)=2,ROUND((AD36/AD37-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY36" s="6">
-        <f>IF(COUNT(AI36:AI37)=2,(AI36/AI37-1)*100,"")</f>
+        <f>IF(COUNT(AI36:AI37)=2,ROUND((AI36/AI37-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ36" s="6">
-        <f>IF(COUNT(AN36:AN37)=2,(AN36/AN37-1)*100,"")</f>
+        <f>IF(COUNT(AN36:AN37)=2,ROUND((AN36/AN37-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA36" s="6">
-        <f>IF(COUNT(AS36:AS37)=2,(AS36/AS37-1)*100,"")</f>
+        <f>IF(COUNT(AS36:AS37)=2,ROUND((AS36/AS37-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB36" s="5" t="n">
         <v>15.57</v>
       </c>
       <c r="BC36" s="6">
-        <f>IF(COUNT(BB36:BB37)=2,(BB36/BB37-1)*100,"")</f>
+        <f>IF(COUNT(BB36:BB37)=2,ROUND((BB36/BB37-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD36" s="6" t="n">
@@ -8139,11 +8139,11 @@
         <v>182.53</v>
       </c>
       <c r="D37" s="6">
-        <f>IF(COUNT(B37:B38)=2,(B37/B38-1)*100,"")</f>
+        <f>IF(COUNT(B37:B38)=2,ROUND((B37/B38-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E37" s="6">
-        <f>IF(COUNT(C37:C38)=2,(C37/C38-1)*100,"")</f>
+        <f>IF(COUNT(C37:C38)=2,ROUND((C37/C38-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F37" s="5" t="n">
@@ -8267,42 +8267,42 @@
         <v>109.6</v>
       </c>
       <c r="AT37" s="6">
-        <f>IF(COUNT(J37:J38)=2,(J37/J38-1)*100,"")</f>
+        <f>IF(COUNT(J37:J38)=2,ROUND((J37/J38-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU37" s="6">
-        <f>IF(COUNT(O37:O38)=2,(O37/O38-1)*100,"")</f>
+        <f>IF(COUNT(O37:O38)=2,ROUND((O37/O38-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV37" s="6">
-        <f>IF(COUNT(T37:T38)=2,(T37/T38-1)*100,"")</f>
+        <f>IF(COUNT(T37:T38)=2,ROUND((T37/T38-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW37" s="6">
-        <f>IF(COUNT(Y37:Y38)=2,(Y37/Y38-1)*100,"")</f>
+        <f>IF(COUNT(Y37:Y38)=2,ROUND((Y37/Y38-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX37" s="6">
-        <f>IF(COUNT(AD37:AD38)=2,(AD37/AD38-1)*100,"")</f>
+        <f>IF(COUNT(AD37:AD38)=2,ROUND((AD37/AD38-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY37" s="6">
-        <f>IF(COUNT(AI37:AI38)=2,(AI37/AI38-1)*100,"")</f>
+        <f>IF(COUNT(AI37:AI38)=2,ROUND((AI37/AI38-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ37" s="6">
-        <f>IF(COUNT(AN37:AN38)=2,(AN37/AN38-1)*100,"")</f>
+        <f>IF(COUNT(AN37:AN38)=2,ROUND((AN37/AN38-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA37" s="6">
-        <f>IF(COUNT(AS37:AS38)=2,(AS37/AS38-1)*100,"")</f>
+        <f>IF(COUNT(AS37:AS38)=2,ROUND((AS37/AS38-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB37" s="5" t="n">
         <v>16.15</v>
       </c>
       <c r="BC37" s="6">
-        <f>IF(COUNT(BB37:BB38)=2,(BB37/BB38-1)*100,"")</f>
+        <f>IF(COUNT(BB37:BB38)=2,ROUND((BB37/BB38-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD37" s="6" t="n">
@@ -8354,11 +8354,11 @@
         <v>182.68</v>
       </c>
       <c r="D38" s="6">
-        <f>IF(COUNT(B38:B39)=2,(B38/B39-1)*100,"")</f>
+        <f>IF(COUNT(B38:B39)=2,ROUND((B38/B39-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E38" s="6">
-        <f>IF(COUNT(C38:C39)=2,(C38/C39-1)*100,"")</f>
+        <f>IF(COUNT(C38:C39)=2,ROUND((C38/C39-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F38" s="5" t="n">
@@ -8482,42 +8482,42 @@
         <v>109.74</v>
       </c>
       <c r="AT38" s="6">
-        <f>IF(COUNT(J38:J39)=2,(J38/J39-1)*100,"")</f>
+        <f>IF(COUNT(J38:J39)=2,ROUND((J38/J39-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU38" s="6">
-        <f>IF(COUNT(O38:O39)=2,(O38/O39-1)*100,"")</f>
+        <f>IF(COUNT(O38:O39)=2,ROUND((O38/O39-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV38" s="6">
-        <f>IF(COUNT(T38:T39)=2,(T38/T39-1)*100,"")</f>
+        <f>IF(COUNT(T38:T39)=2,ROUND((T38/T39-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW38" s="6">
-        <f>IF(COUNT(Y38:Y39)=2,(Y38/Y39-1)*100,"")</f>
+        <f>IF(COUNT(Y38:Y39)=2,ROUND((Y38/Y39-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX38" s="6">
-        <f>IF(COUNT(AD38:AD39)=2,(AD38/AD39-1)*100,"")</f>
+        <f>IF(COUNT(AD38:AD39)=2,ROUND((AD38/AD39-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY38" s="6">
-        <f>IF(COUNT(AI38:AI39)=2,(AI38/AI39-1)*100,"")</f>
+        <f>IF(COUNT(AI38:AI39)=2,ROUND((AI38/AI39-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ38" s="6">
-        <f>IF(COUNT(AN38:AN39)=2,(AN38/AN39-1)*100,"")</f>
+        <f>IF(COUNT(AN38:AN39)=2,ROUND((AN38/AN39-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA38" s="6">
-        <f>IF(COUNT(AS38:AS39)=2,(AS38/AS39-1)*100,"")</f>
+        <f>IF(COUNT(AS38:AS39)=2,ROUND((AS38/AS39-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB38" s="5" t="n">
         <v>16.59</v>
       </c>
       <c r="BC38" s="6">
-        <f>IF(COUNT(BB38:BB39)=2,(BB38/BB39-1)*100,"")</f>
+        <f>IF(COUNT(BB38:BB39)=2,ROUND((BB38/BB39-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD38" s="6" t="n">
@@ -8569,11 +8569,11 @@
         <v>183.4</v>
       </c>
       <c r="D39" s="6">
-        <f>IF(COUNT(B39:B40)=2,(B39/B40-1)*100,"")</f>
+        <f>IF(COUNT(B39:B40)=2,ROUND((B39/B40-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E39" s="6">
-        <f>IF(COUNT(C39:C40)=2,(C39/C40-1)*100,"")</f>
+        <f>IF(COUNT(C39:C40)=2,ROUND((C39/C40-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F39" s="5" t="n">
@@ -8697,42 +8697,42 @@
         <v>107.13</v>
       </c>
       <c r="AT39" s="6">
-        <f>IF(COUNT(J39:J40)=2,(J39/J40-1)*100,"")</f>
+        <f>IF(COUNT(J39:J40)=2,ROUND((J39/J40-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU39" s="6">
-        <f>IF(COUNT(O39:O40)=2,(O39/O40-1)*100,"")</f>
+        <f>IF(COUNT(O39:O40)=2,ROUND((O39/O40-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV39" s="6">
-        <f>IF(COUNT(T39:T40)=2,(T39/T40-1)*100,"")</f>
+        <f>IF(COUNT(T39:T40)=2,ROUND((T39/T40-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW39" s="6">
-        <f>IF(COUNT(Y39:Y40)=2,(Y39/Y40-1)*100,"")</f>
+        <f>IF(COUNT(Y39:Y40)=2,ROUND((Y39/Y40-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX39" s="6">
-        <f>IF(COUNT(AD39:AD40)=2,(AD39/AD40-1)*100,"")</f>
+        <f>IF(COUNT(AD39:AD40)=2,ROUND((AD39/AD40-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY39" s="6">
-        <f>IF(COUNT(AI39:AI40)=2,(AI39/AI40-1)*100,"")</f>
+        <f>IF(COUNT(AI39:AI40)=2,ROUND((AI39/AI40-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ39" s="6">
-        <f>IF(COUNT(AN39:AN40)=2,(AN39/AN40-1)*100,"")</f>
+        <f>IF(COUNT(AN39:AN40)=2,ROUND((AN39/AN40-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA39" s="6">
-        <f>IF(COUNT(AS39:AS40)=2,(AS39/AS40-1)*100,"")</f>
+        <f>IF(COUNT(AS39:AS40)=2,ROUND((AS39/AS40-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB39" s="5" t="n">
         <v>16.45</v>
       </c>
       <c r="BC39" s="6">
-        <f>IF(COUNT(BB39:BB40)=2,(BB39/BB40-1)*100,"")</f>
+        <f>IF(COUNT(BB39:BB40)=2,ROUND((BB39/BB40-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD39" s="6" t="n">
@@ -8784,11 +8784,11 @@
         <v>180.59</v>
       </c>
       <c r="D40" s="6">
-        <f>IF(COUNT(B40:B41)=2,(B40/B41-1)*100,"")</f>
+        <f>IF(COUNT(B40:B41)=2,ROUND((B40/B41-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E40" s="6">
-        <f>IF(COUNT(C40:C41)=2,(C40/C41-1)*100,"")</f>
+        <f>IF(COUNT(C40:C41)=2,ROUND((C40/C41-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F40" s="5" t="n">
@@ -8912,42 +8912,42 @@
         <v>107.88</v>
       </c>
       <c r="AT40" s="6">
-        <f>IF(COUNT(J40:J41)=2,(J40/J41-1)*100,"")</f>
+        <f>IF(COUNT(J40:J41)=2,ROUND((J40/J41-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU40" s="6">
-        <f>IF(COUNT(O40:O41)=2,(O40/O41-1)*100,"")</f>
+        <f>IF(COUNT(O40:O41)=2,ROUND((O40/O41-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV40" s="6">
-        <f>IF(COUNT(T40:T41)=2,(T40/T41-1)*100,"")</f>
+        <f>IF(COUNT(T40:T41)=2,ROUND((T40/T41-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW40" s="6">
-        <f>IF(COUNT(Y40:Y41)=2,(Y40/Y41-1)*100,"")</f>
+        <f>IF(COUNT(Y40:Y41)=2,ROUND((Y40/Y41-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX40" s="6">
-        <f>IF(COUNT(AD40:AD41)=2,(AD40/AD41-1)*100,"")</f>
+        <f>IF(COUNT(AD40:AD41)=2,ROUND((AD40/AD41-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY40" s="6">
-        <f>IF(COUNT(AI40:AI41)=2,(AI40/AI41-1)*100,"")</f>
+        <f>IF(COUNT(AI40:AI41)=2,ROUND((AI40/AI41-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ40" s="6">
-        <f>IF(COUNT(AN40:AN41)=2,(AN40/AN41-1)*100,"")</f>
+        <f>IF(COUNT(AN40:AN41)=2,ROUND((AN40/AN41-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA40" s="6">
-        <f>IF(COUNT(AS40:AS41)=2,(AS40/AS41-1)*100,"")</f>
+        <f>IF(COUNT(AS40:AS41)=2,ROUND((AS40/AS41-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB40" s="5" t="n">
         <v>17.65</v>
       </c>
       <c r="BC40" s="6">
-        <f>IF(COUNT(BB40:BB41)=2,(BB40/BB41-1)*100,"")</f>
+        <f>IF(COUNT(BB40:BB41)=2,ROUND((BB40/BB41-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD40" s="6" t="n">
@@ -8999,11 +8999,11 @@
         <v>176.27</v>
       </c>
       <c r="D41" s="6">
-        <f>IF(COUNT(B41:B42)=2,(B41/B42-1)*100,"")</f>
+        <f>IF(COUNT(B41:B42)=2,ROUND((B41/B42-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E41" s="6">
-        <f>IF(COUNT(C41:C42)=2,(C41/C42-1)*100,"")</f>
+        <f>IF(COUNT(C41:C42)=2,ROUND((C41/C42-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F41" s="5" t="n">
@@ -9127,42 +9127,42 @@
         <v>106.18</v>
       </c>
       <c r="AT41" s="6">
-        <f>IF(COUNT(J41:J42)=2,(J41/J42-1)*100,"")</f>
+        <f>IF(COUNT(J41:J42)=2,ROUND((J41/J42-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU41" s="6">
-        <f>IF(COUNT(O41:O42)=2,(O41/O42-1)*100,"")</f>
+        <f>IF(COUNT(O41:O42)=2,ROUND((O41/O42-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV41" s="6">
-        <f>IF(COUNT(T41:T42)=2,(T41/T42-1)*100,"")</f>
+        <f>IF(COUNT(T41:T42)=2,ROUND((T41/T42-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW41" s="6">
-        <f>IF(COUNT(Y41:Y42)=2,(Y41/Y42-1)*100,"")</f>
+        <f>IF(COUNT(Y41:Y42)=2,ROUND((Y41/Y42-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX41" s="6">
-        <f>IF(COUNT(AD41:AD42)=2,(AD41/AD42-1)*100,"")</f>
+        <f>IF(COUNT(AD41:AD42)=2,ROUND((AD41/AD42-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY41" s="6">
-        <f>IF(COUNT(AI41:AI42)=2,(AI41/AI42-1)*100,"")</f>
+        <f>IF(COUNT(AI41:AI42)=2,ROUND((AI41/AI42-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ41" s="6">
-        <f>IF(COUNT(AN41:AN42)=2,(AN41/AN42-1)*100,"")</f>
+        <f>IF(COUNT(AN41:AN42)=2,ROUND((AN41/AN42-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA41" s="6">
-        <f>IF(COUNT(AS41:AS42)=2,(AS41/AS42-1)*100,"")</f>
+        <f>IF(COUNT(AS41:AS42)=2,ROUND((AS41/AS42-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB41" s="5" t="n">
         <v>18.41</v>
       </c>
       <c r="BC41" s="6">
-        <f>IF(COUNT(BB41:BB42)=2,(BB41/BB42-1)*100,"")</f>
+        <f>IF(COUNT(BB41:BB42)=2,ROUND((BB41/BB42-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD41" s="6" t="n">
@@ -9214,11 +9214,11 @@
         <v>176.82</v>
       </c>
       <c r="D42" s="6">
-        <f>IF(COUNT(B42:B43)=2,(B42/B43-1)*100,"")</f>
+        <f>IF(COUNT(B42:B43)=2,ROUND((B42/B43-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E42" s="6">
-        <f>IF(COUNT(C42:C43)=2,(C42/C43-1)*100,"")</f>
+        <f>IF(COUNT(C42:C43)=2,ROUND((C42/C43-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F42" s="5" t="n">
@@ -9342,42 +9342,42 @@
         <v>105.58</v>
       </c>
       <c r="AT42" s="6">
-        <f>IF(COUNT(J42:J43)=2,(J42/J43-1)*100,"")</f>
+        <f>IF(COUNT(J42:J43)=2,ROUND((J42/J43-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU42" s="6">
-        <f>IF(COUNT(O42:O43)=2,(O42/O43-1)*100,"")</f>
+        <f>IF(COUNT(O42:O43)=2,ROUND((O42/O43-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV42" s="6">
-        <f>IF(COUNT(T42:T43)=2,(T42/T43-1)*100,"")</f>
+        <f>IF(COUNT(T42:T43)=2,ROUND((T42/T43-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW42" s="6">
-        <f>IF(COUNT(Y42:Y43)=2,(Y42/Y43-1)*100,"")</f>
+        <f>IF(COUNT(Y42:Y43)=2,ROUND((Y42/Y43-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX42" s="6">
-        <f>IF(COUNT(AD42:AD43)=2,(AD42/AD43-1)*100,"")</f>
+        <f>IF(COUNT(AD42:AD43)=2,ROUND((AD42/AD43-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY42" s="6">
-        <f>IF(COUNT(AI42:AI43)=2,(AI42/AI43-1)*100,"")</f>
+        <f>IF(COUNT(AI42:AI43)=2,ROUND((AI42/AI43-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ42" s="6">
-        <f>IF(COUNT(AN42:AN43)=2,(AN42/AN43-1)*100,"")</f>
+        <f>IF(COUNT(AN42:AN43)=2,ROUND((AN42/AN43-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA42" s="6">
-        <f>IF(COUNT(AS42:AS43)=2,(AS42/AS43-1)*100,"")</f>
+        <f>IF(COUNT(AS42:AS43)=2,ROUND((AS42/AS43-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB42" s="5" t="n">
         <v>18.89</v>
       </c>
       <c r="BC42" s="6">
-        <f>IF(COUNT(BB42:BB43)=2,(BB42/BB43-1)*100,"")</f>
+        <f>IF(COUNT(BB42:BB43)=2,ROUND((BB42/BB43-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD42" s="6" t="n">
@@ -9429,11 +9429,11 @@
         <v>176.82</v>
       </c>
       <c r="D43" s="6">
-        <f>IF(COUNT(B43:B44)=2,(B43/B44-1)*100,"")</f>
+        <f>IF(COUNT(B43:B44)=2,ROUND((B43/B44-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E43" s="6">
-        <f>IF(COUNT(C43:C44)=2,(C43/C44-1)*100,"")</f>
+        <f>IF(COUNT(C43:C44)=2,ROUND((C43/C44-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F43" s="5" t="n">
@@ -9557,42 +9557,42 @@
         <v>106.54</v>
       </c>
       <c r="AT43" s="6">
-        <f>IF(COUNT(J43:J44)=2,(J43/J44-1)*100,"")</f>
+        <f>IF(COUNT(J43:J44)=2,ROUND((J43/J44-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU43" s="6">
-        <f>IF(COUNT(O43:O44)=2,(O43/O44-1)*100,"")</f>
+        <f>IF(COUNT(O43:O44)=2,ROUND((O43/O44-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV43" s="6">
-        <f>IF(COUNT(T43:T44)=2,(T43/T44-1)*100,"")</f>
+        <f>IF(COUNT(T43:T44)=2,ROUND((T43/T44-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW43" s="6">
-        <f>IF(COUNT(Y43:Y44)=2,(Y43/Y44-1)*100,"")</f>
+        <f>IF(COUNT(Y43:Y44)=2,ROUND((Y43/Y44-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX43" s="6">
-        <f>IF(COUNT(AD43:AD44)=2,(AD43/AD44-1)*100,"")</f>
+        <f>IF(COUNT(AD43:AD44)=2,ROUND((AD43/AD44-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY43" s="6">
-        <f>IF(COUNT(AI43:AI44)=2,(AI43/AI44-1)*100,"")</f>
+        <f>IF(COUNT(AI43:AI44)=2,ROUND((AI43/AI44-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ43" s="6">
-        <f>IF(COUNT(AN43:AN44)=2,(AN43/AN44-1)*100,"")</f>
+        <f>IF(COUNT(AN43:AN44)=2,ROUND((AN43/AN44-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA43" s="6">
-        <f>IF(COUNT(AS43:AS44)=2,(AS43/AS44-1)*100,"")</f>
+        <f>IF(COUNT(AS43:AS44)=2,ROUND((AS43/AS44-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB43" s="5" t="n">
         <v>18.63</v>
       </c>
       <c r="BC43" s="6">
-        <f>IF(COUNT(BB43:BB44)=2,(BB43/BB44-1)*100,"")</f>
+        <f>IF(COUNT(BB43:BB44)=2,ROUND((BB43/BB44-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD43" s="6" t="n">
@@ -9644,11 +9644,11 @@
         <v>177.18</v>
       </c>
       <c r="D44" s="6">
-        <f>IF(COUNT(B44:B45)=2,(B44/B45-1)*100,"")</f>
+        <f>IF(COUNT(B44:B45)=2,ROUND((B44/B45-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E44" s="6">
-        <f>IF(COUNT(C44:C45)=2,(C44/C45-1)*100,"")</f>
+        <f>IF(COUNT(C44:C45)=2,ROUND((C44/C45-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F44" s="5" t="n">
@@ -9772,42 +9772,42 @@
         <v>107.27</v>
       </c>
       <c r="AT44" s="6">
-        <f>IF(COUNT(J44:J45)=2,(J44/J45-1)*100,"")</f>
+        <f>IF(COUNT(J44:J45)=2,ROUND((J44/J45-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU44" s="6">
-        <f>IF(COUNT(O44:O45)=2,(O44/O45-1)*100,"")</f>
+        <f>IF(COUNT(O44:O45)=2,ROUND((O44/O45-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV44" s="6">
-        <f>IF(COUNT(T44:T45)=2,(T44/T45-1)*100,"")</f>
+        <f>IF(COUNT(T44:T45)=2,ROUND((T44/T45-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW44" s="6">
-        <f>IF(COUNT(Y44:Y45)=2,(Y44/Y45-1)*100,"")</f>
+        <f>IF(COUNT(Y44:Y45)=2,ROUND((Y44/Y45-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX44" s="6">
-        <f>IF(COUNT(AD44:AD45)=2,(AD44/AD45-1)*100,"")</f>
+        <f>IF(COUNT(AD44:AD45)=2,ROUND((AD44/AD45-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY44" s="6">
-        <f>IF(COUNT(AI44:AI45)=2,(AI44/AI45-1)*100,"")</f>
+        <f>IF(COUNT(AI44:AI45)=2,ROUND((AI44/AI45-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ44" s="6">
-        <f>IF(COUNT(AN44:AN45)=2,(AN44/AN45-1)*100,"")</f>
+        <f>IF(COUNT(AN44:AN45)=2,ROUND((AN44/AN45-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA44" s="6">
-        <f>IF(COUNT(AS44:AS45)=2,(AS44/AS45-1)*100,"")</f>
+        <f>IF(COUNT(AS44:AS45)=2,ROUND((AS44/AS45-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB44" s="5" t="n">
         <v>19.49</v>
       </c>
       <c r="BC44" s="6">
-        <f>IF(COUNT(BB44:BB45)=2,(BB44/BB45-1)*100,"")</f>
+        <f>IF(COUNT(BB44:BB45)=2,ROUND((BB44/BB45-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD44" s="6" t="n">
@@ -9859,11 +9859,11 @@
         <v>182.43</v>
       </c>
       <c r="D45" s="6">
-        <f>IF(COUNT(B45:B46)=2,(B45/B46-1)*100,"")</f>
+        <f>IF(COUNT(B45:B46)=2,ROUND((B45/B46-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E45" s="6">
-        <f>IF(COUNT(C45:C46)=2,(C45/C46-1)*100,"")</f>
+        <f>IF(COUNT(C45:C46)=2,ROUND((C45/C46-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F45" s="5" t="n">
@@ -9987,42 +9987,42 @@
         <v>106.86</v>
       </c>
       <c r="AT45" s="6">
-        <f>IF(COUNT(J45:J46)=2,(J45/J46-1)*100,"")</f>
+        <f>IF(COUNT(J45:J46)=2,ROUND((J45/J46-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU45" s="6">
-        <f>IF(COUNT(O45:O46)=2,(O45/O46-1)*100,"")</f>
+        <f>IF(COUNT(O45:O46)=2,ROUND((O45/O46-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV45" s="6">
-        <f>IF(COUNT(T45:T46)=2,(T45/T46-1)*100,"")</f>
+        <f>IF(COUNT(T45:T46)=2,ROUND((T45/T46-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW45" s="6">
-        <f>IF(COUNT(Y45:Y46)=2,(Y45/Y46-1)*100,"")</f>
+        <f>IF(COUNT(Y45:Y46)=2,ROUND((Y45/Y46-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX45" s="6">
-        <f>IF(COUNT(AD45:AD46)=2,(AD45/AD46-1)*100,"")</f>
+        <f>IF(COUNT(AD45:AD46)=2,ROUND((AD45/AD46-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY45" s="6">
-        <f>IF(COUNT(AI45:AI46)=2,(AI45/AI46-1)*100,"")</f>
+        <f>IF(COUNT(AI45:AI46)=2,ROUND((AI45/AI46-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ45" s="6">
-        <f>IF(COUNT(AN45:AN46)=2,(AN45/AN46-1)*100,"")</f>
+        <f>IF(COUNT(AN45:AN46)=2,ROUND((AN45/AN46-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA45" s="6">
-        <f>IF(COUNT(AS45:AS46)=2,(AS45/AS46-1)*100,"")</f>
+        <f>IF(COUNT(AS45:AS46)=2,ROUND((AS45/AS46-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB45" s="5" t="n">
         <v>17.28</v>
       </c>
       <c r="BC45" s="6">
-        <f>IF(COUNT(BB45:BB46)=2,(BB45/BB46-1)*100,"")</f>
+        <f>IF(COUNT(BB45:BB46)=2,ROUND((BB45/BB46-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD45" s="6" t="n">
@@ -10074,11 +10074,11 @@
         <v>183.86</v>
       </c>
       <c r="D46" s="6">
-        <f>IF(COUNT(B46:B47)=2,(B46/B47-1)*100,"")</f>
+        <f>IF(COUNT(B46:B47)=2,ROUND((B46/B47-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E46" s="6">
-        <f>IF(COUNT(C46:C47)=2,(C46/C47-1)*100,"")</f>
+        <f>IF(COUNT(C46:C47)=2,ROUND((C46/C47-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F46" s="5" t="n">
@@ -10202,42 +10202,42 @@
         <v>109.166</v>
       </c>
       <c r="AT46" s="6">
-        <f>IF(COUNT(J46:J47)=2,(J46/J47-1)*100,"")</f>
+        <f>IF(COUNT(J46:J47)=2,ROUND((J46/J47-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU46" s="6">
-        <f>IF(COUNT(O46:O47)=2,(O46/O47-1)*100,"")</f>
+        <f>IF(COUNT(O46:O47)=2,ROUND((O46/O47-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV46" s="6">
-        <f>IF(COUNT(T46:T47)=2,(T46/T47-1)*100,"")</f>
+        <f>IF(COUNT(T46:T47)=2,ROUND((T46/T47-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW46" s="6">
-        <f>IF(COUNT(Y46:Y47)=2,(Y46/Y47-1)*100,"")</f>
+        <f>IF(COUNT(Y46:Y47)=2,ROUND((Y46/Y47-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX46" s="6">
-        <f>IF(COUNT(AD46:AD47)=2,(AD46/AD47-1)*100,"")</f>
+        <f>IF(COUNT(AD46:AD47)=2,ROUND((AD46/AD47-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY46" s="6">
-        <f>IF(COUNT(AI46:AI47)=2,(AI46/AI47-1)*100,"")</f>
+        <f>IF(COUNT(AI46:AI47)=2,ROUND((AI46/AI47-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ46" s="6">
-        <f>IF(COUNT(AN46:AN47)=2,(AN46/AN47-1)*100,"")</f>
+        <f>IF(COUNT(AN46:AN47)=2,ROUND((AN46/AN47-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA46" s="6">
-        <f>IF(COUNT(AS46:AS47)=2,(AS46/AS47-1)*100,"")</f>
+        <f>IF(COUNT(AS46:AS47)=2,ROUND((AS46/AS47-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB46" s="5" t="n">
         <v>16.4</v>
       </c>
       <c r="BC46" s="6">
-        <f>IF(COUNT(BB46:BB47)=2,(BB46/BB47-1)*100,"")</f>
+        <f>IF(COUNT(BB46:BB47)=2,ROUND((BB46/BB47-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD46" s="6" t="n">
@@ -10289,11 +10289,11 @@
         <v>180</v>
       </c>
       <c r="D47" s="6">
-        <f>IF(COUNT(B47:B48)=2,(B47/B48-1)*100,"")</f>
+        <f>IF(COUNT(B47:B48)=2,ROUND((B47/B48-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E47" s="6">
-        <f>IF(COUNT(C47:C48)=2,(C47/C48-1)*100,"")</f>
+        <f>IF(COUNT(C47:C48)=2,ROUND((C47/C48-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F47" s="5" t="n">
@@ -10417,42 +10417,42 @@
         <v>108.9166</v>
       </c>
       <c r="AT47" s="6">
-        <f>IF(COUNT(J47:J48)=2,(J47/J48-1)*100,"")</f>
+        <f>IF(COUNT(J47:J48)=2,ROUND((J47/J48-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU47" s="6">
-        <f>IF(COUNT(O47:O48)=2,(O47/O48-1)*100,"")</f>
+        <f>IF(COUNT(O47:O48)=2,ROUND((O47/O48-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV47" s="6">
-        <f>IF(COUNT(T47:T48)=2,(T47/T48-1)*100,"")</f>
+        <f>IF(COUNT(T47:T48)=2,ROUND((T47/T48-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW47" s="6">
-        <f>IF(COUNT(Y47:Y48)=2,(Y47/Y48-1)*100,"")</f>
+        <f>IF(COUNT(Y47:Y48)=2,ROUND((Y47/Y48-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX47" s="6">
-        <f>IF(COUNT(AD47:AD48)=2,(AD47/AD48-1)*100,"")</f>
+        <f>IF(COUNT(AD47:AD48)=2,ROUND((AD47/AD48-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY47" s="6">
-        <f>IF(COUNT(AI47:AI48)=2,(AI47/AI48-1)*100,"")</f>
+        <f>IF(COUNT(AI47:AI48)=2,ROUND((AI47/AI48-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ47" s="6">
-        <f>IF(COUNT(AN47:AN48)=2,(AN47/AN48-1)*100,"")</f>
+        <f>IF(COUNT(AN47:AN48)=2,ROUND((AN47/AN48-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA47" s="6">
-        <f>IF(COUNT(AS47:AS48)=2,(AS47/AS48-1)*100,"")</f>
+        <f>IF(COUNT(AS47:AS48)=2,ROUND((AS47/AS48-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB47" s="5" t="n">
         <v>18.44</v>
       </c>
       <c r="BC47" s="6">
-        <f>IF(COUNT(BB47:BB48)=2,(BB47/BB48-1)*100,"")</f>
+        <f>IF(COUNT(BB47:BB48)=2,ROUND((BB47/BB48-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD47" s="6" t="n">
@@ -10504,11 +10504,11 @@
         <v>184.56</v>
       </c>
       <c r="D48" s="6">
-        <f>IF(COUNT(B48:B49)=2,(B48/B49-1)*100,"")</f>
+        <f>IF(COUNT(B48:B49)=2,ROUND((B48/B49-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E48" s="6">
-        <f>IF(COUNT(C48:C49)=2,(C48/C49-1)*100,"")</f>
+        <f>IF(COUNT(C48:C49)=2,ROUND((C48/C49-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F48" s="5" t="n">
@@ -10632,42 +10632,42 @@
         <v>112.0286</v>
       </c>
       <c r="AT48" s="6">
-        <f>IF(COUNT(J48:J49)=2,(J48/J49-1)*100,"")</f>
+        <f>IF(COUNT(J48:J49)=2,ROUND((J48/J49-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU48" s="6">
-        <f>IF(COUNT(O48:O49)=2,(O48/O49-1)*100,"")</f>
+        <f>IF(COUNT(O48:O49)=2,ROUND((O48/O49-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV48" s="6">
-        <f>IF(COUNT(T48:T49)=2,(T48/T49-1)*100,"")</f>
+        <f>IF(COUNT(T48:T49)=2,ROUND((T48/T49-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW48" s="6">
-        <f>IF(COUNT(Y48:Y49)=2,(Y48/Y49-1)*100,"")</f>
+        <f>IF(COUNT(Y48:Y49)=2,ROUND((Y48/Y49-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX48" s="6">
-        <f>IF(COUNT(AD48:AD49)=2,(AD48/AD49-1)*100,"")</f>
+        <f>IF(COUNT(AD48:AD49)=2,ROUND((AD48/AD49-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY48" s="6">
-        <f>IF(COUNT(AI48:AI49)=2,(AI48/AI49-1)*100,"")</f>
+        <f>IF(COUNT(AI48:AI49)=2,ROUND((AI48/AI49-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ48" s="6">
-        <f>IF(COUNT(AN48:AN49)=2,(AN48/AN49-1)*100,"")</f>
+        <f>IF(COUNT(AN48:AN49)=2,ROUND((AN48/AN49-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA48" s="6">
-        <f>IF(COUNT(AS48:AS49)=2,(AS48/AS49-1)*100,"")</f>
+        <f>IF(COUNT(AS48:AS49)=2,ROUND((AS48/AS49-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB48" s="5" t="n">
         <v>16.41</v>
       </c>
       <c r="BC48" s="6">
-        <f>IF(COUNT(BB48:BB49)=2,(BB48/BB49-1)*100,"")</f>
+        <f>IF(COUNT(BB48:BB49)=2,ROUND((BB48/BB49-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD48" s="6" t="n">
@@ -10719,11 +10719,11 @@
         <v>186.69</v>
       </c>
       <c r="D49" s="6">
-        <f>IF(COUNT(B49:B50)=2,(B49/B50-1)*100,"")</f>
+        <f>IF(COUNT(B49:B50)=2,ROUND((B49/B50-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E49" s="6">
-        <f>IF(COUNT(C49:C50)=2,(C49/C50-1)*100,"")</f>
+        <f>IF(COUNT(C49:C50)=2,ROUND((C49/C50-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F49" s="5" t="n">
@@ -10847,42 +10847,42 @@
         <v>111.8989</v>
       </c>
       <c r="AT49" s="6">
-        <f>IF(COUNT(J49:J50)=2,(J49/J50-1)*100,"")</f>
+        <f>IF(COUNT(J49:J50)=2,ROUND((J49/J50-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU49" s="6">
-        <f>IF(COUNT(O49:O50)=2,(O49/O50-1)*100,"")</f>
+        <f>IF(COUNT(O49:O50)=2,ROUND((O49/O50-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV49" s="6">
-        <f>IF(COUNT(T49:T50)=2,(T49/T50-1)*100,"")</f>
+        <f>IF(COUNT(T49:T50)=2,ROUND((T49/T50-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW49" s="6">
-        <f>IF(COUNT(Y49:Y50)=2,(Y49/Y50-1)*100,"")</f>
+        <f>IF(COUNT(Y49:Y50)=2,ROUND((Y49/Y50-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX49" s="6">
-        <f>IF(COUNT(AD49:AD50)=2,(AD49/AD50-1)*100,"")</f>
+        <f>IF(COUNT(AD49:AD50)=2,ROUND((AD49/AD50-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY49" s="6">
-        <f>IF(COUNT(AI49:AI50)=2,(AI49/AI50-1)*100,"")</f>
+        <f>IF(COUNT(AI49:AI50)=2,ROUND((AI49/AI50-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ49" s="6">
-        <f>IF(COUNT(AN49:AN50)=2,(AN49/AN50-1)*100,"")</f>
+        <f>IF(COUNT(AN49:AN50)=2,ROUND((AN49/AN50-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA49" s="6">
-        <f>IF(COUNT(AS49:AS50)=2,(AS49/AS50-1)*100,"")</f>
+        <f>IF(COUNT(AS49:AS50)=2,ROUND((AS49/AS50-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB49" s="5" t="n">
         <v>16.2</v>
       </c>
       <c r="BC49" s="6">
-        <f>IF(COUNT(BB49:BB50)=2,(BB49/BB50-1)*100,"")</f>
+        <f>IF(COUNT(BB49:BB50)=2,ROUND((BB49/BB50-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD49" s="6" t="n">
@@ -10934,11 +10934,11 @@
         <v>180.68</v>
       </c>
       <c r="D50" s="6">
-        <f>IF(COUNT(B50:B51)=2,(B50/B51-1)*100,"")</f>
+        <f>IF(COUNT(B50:B51)=2,ROUND((B50/B51-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E50" s="6">
-        <f>IF(COUNT(C50:C51)=2,(C50/C51-1)*100,"")</f>
+        <f>IF(COUNT(C50:C51)=2,ROUND((C50/C51-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F50" s="5" t="n">
@@ -11062,42 +11062,42 @@
         <v>111.3603</v>
       </c>
       <c r="AT50" s="6">
-        <f>IF(COUNT(J50:J51)=2,(J50/J51-1)*100,"")</f>
+        <f>IF(COUNT(J50:J51)=2,ROUND((J50/J51-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU50" s="6">
-        <f>IF(COUNT(O50:O51)=2,(O50/O51-1)*100,"")</f>
+        <f>IF(COUNT(O50:O51)=2,ROUND((O50/O51-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV50" s="6">
-        <f>IF(COUNT(T50:T51)=2,(T50/T51-1)*100,"")</f>
+        <f>IF(COUNT(T50:T51)=2,ROUND((T50/T51-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW50" s="6">
-        <f>IF(COUNT(Y50:Y51)=2,(Y50/Y51-1)*100,"")</f>
+        <f>IF(COUNT(Y50:Y51)=2,ROUND((Y50/Y51-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX50" s="6">
-        <f>IF(COUNT(AD50:AD51)=2,(AD50/AD51-1)*100,"")</f>
+        <f>IF(COUNT(AD50:AD51)=2,ROUND((AD50/AD51-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY50" s="6">
-        <f>IF(COUNT(AI50:AI51)=2,(AI50/AI51-1)*100,"")</f>
+        <f>IF(COUNT(AI50:AI51)=2,ROUND((AI50/AI51-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ50" s="6">
-        <f>IF(COUNT(AN50:AN51)=2,(AN50/AN51-1)*100,"")</f>
+        <f>IF(COUNT(AN50:AN51)=2,ROUND((AN50/AN51-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA50" s="6">
-        <f>IF(COUNT(AS50:AS51)=2,(AS50/AS51-1)*100,"")</f>
+        <f>IF(COUNT(AS50:AS51)=2,ROUND((AS50/AS51-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB50" s="5" t="n">
         <v>17.68</v>
       </c>
       <c r="BC50" s="6">
-        <f>IF(COUNT(BB50:BB51)=2,(BB50/BB51-1)*100,"")</f>
+        <f>IF(COUNT(BB50:BB51)=2,ROUND((BB50/BB51-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD50" s="6" t="n">
@@ -11149,11 +11149,11 @@
         <v>178.87</v>
       </c>
       <c r="D51" s="6">
-        <f>IF(COUNT(B51:B52)=2,(B51/B52-1)*100,"")</f>
+        <f>IF(COUNT(B51:B52)=2,ROUND((B51/B52-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E51" s="6">
-        <f>IF(COUNT(C51:C52)=2,(C51/C52-1)*100,"")</f>
+        <f>IF(COUNT(C51:C52)=2,ROUND((C51/C52-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F51" s="5" t="n">
@@ -11277,42 +11277,42 @@
         <v>111.8291</v>
       </c>
       <c r="AT51" s="6">
-        <f>IF(COUNT(J51:J52)=2,(J51/J52-1)*100,"")</f>
+        <f>IF(COUNT(J51:J52)=2,ROUND((J51/J52-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU51" s="6">
-        <f>IF(COUNT(O51:O52)=2,(O51/O52-1)*100,"")</f>
+        <f>IF(COUNT(O51:O52)=2,ROUND((O51/O52-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV51" s="6">
-        <f>IF(COUNT(T51:T52)=2,(T51/T52-1)*100,"")</f>
+        <f>IF(COUNT(T51:T52)=2,ROUND((T51/T52-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW51" s="6">
-        <f>IF(COUNT(Y51:Y52)=2,(Y51/Y52-1)*100,"")</f>
+        <f>IF(COUNT(Y51:Y52)=2,ROUND((Y51/Y52-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX51" s="6">
-        <f>IF(COUNT(AD51:AD52)=2,(AD51/AD52-1)*100,"")</f>
+        <f>IF(COUNT(AD51:AD52)=2,ROUND((AD51/AD52-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY51" s="6">
-        <f>IF(COUNT(AI51:AI52)=2,(AI51/AI52-1)*100,"")</f>
+        <f>IF(COUNT(AI51:AI52)=2,ROUND((AI51/AI52-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ51" s="6">
-        <f>IF(COUNT(AN51:AN52)=2,(AN51/AN52-1)*100,"")</f>
+        <f>IF(COUNT(AN51:AN52)=2,ROUND((AN51/AN52-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA51" s="6">
-        <f>IF(COUNT(AS51:AS52)=2,(AS51/AS52-1)*100,"")</f>
+        <f>IF(COUNT(AS51:AS52)=2,ROUND((AS51/AS52-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB51" s="5" t="n">
         <v>19.44</v>
       </c>
       <c r="BC51" s="6">
-        <f>IF(COUNT(BB51:BB52)=2,(BB51/BB52-1)*100,"")</f>
+        <f>IF(COUNT(BB51:BB52)=2,ROUND((BB51/BB52-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD51" s="6" t="n">
@@ -11364,11 +11364,11 @@
         <v>172.89</v>
       </c>
       <c r="D52" s="6">
-        <f>IF(COUNT(B52:B53)=2,(B52/B53-1)*100,"")</f>
+        <f>IF(COUNT(B52:B53)=2,ROUND((B52/B53-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E52" s="6">
-        <f>IF(COUNT(C52:C53)=2,(C52/C53-1)*100,"")</f>
+        <f>IF(COUNT(C52:C53)=2,ROUND((C52/C53-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F52" s="5" t="n">
@@ -11492,42 +11492,42 @@
         <v>110.722</v>
       </c>
       <c r="AT52" s="6">
-        <f>IF(COUNT(J52:J53)=2,(J52/J53-1)*100,"")</f>
+        <f>IF(COUNT(J52:J53)=2,ROUND((J52/J53-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU52" s="6">
-        <f>IF(COUNT(O52:O53)=2,(O52/O53-1)*100,"")</f>
+        <f>IF(COUNT(O52:O53)=2,ROUND((O52/O53-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV52" s="6">
-        <f>IF(COUNT(T52:T53)=2,(T52/T53-1)*100,"")</f>
+        <f>IF(COUNT(T52:T53)=2,ROUND((T52/T53-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW52" s="6">
-        <f>IF(COUNT(Y52:Y53)=2,(Y52/Y53-1)*100,"")</f>
+        <f>IF(COUNT(Y52:Y53)=2,ROUND((Y52/Y53-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX52" s="6">
-        <f>IF(COUNT(AD52:AD53)=2,(AD52/AD53-1)*100,"")</f>
+        <f>IF(COUNT(AD52:AD53)=2,ROUND((AD52/AD53-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY52" s="6">
-        <f>IF(COUNT(AI52:AI53)=2,(AI52/AI53-1)*100,"")</f>
+        <f>IF(COUNT(AI52:AI53)=2,ROUND((AI52/AI53-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ52" s="6">
-        <f>IF(COUNT(AN52:AN53)=2,(AN52/AN53-1)*100,"")</f>
+        <f>IF(COUNT(AN52:AN53)=2,ROUND((AN52/AN53-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA52" s="6">
-        <f>IF(COUNT(AS52:AS53)=2,(AS52/AS53-1)*100,"")</f>
+        <f>IF(COUNT(AS52:AS53)=2,ROUND((AS52/AS53-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB52" s="5" t="n">
         <v>22.22</v>
       </c>
       <c r="BC52" s="6">
-        <f>IF(COUNT(BB52:BB53)=2,(BB52/BB53-1)*100,"")</f>
+        <f>IF(COUNT(BB52:BB53)=2,ROUND((BB52/BB53-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD52" s="6" t="n">
@@ -11579,11 +11579,11 @@
         <v>178.67</v>
       </c>
       <c r="D53" s="6">
-        <f>IF(COUNT(B53:B54)=2,(B53/B54-1)*100,"")</f>
+        <f>IF(COUNT(B53:B54)=2,ROUND((B53/B54-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E53" s="6">
-        <f>IF(COUNT(C53:C54)=2,(C53/C54-1)*100,"")</f>
+        <f>IF(COUNT(C53:C54)=2,ROUND((C53/C54-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F53" s="5" t="n">
@@ -11707,42 +11707,42 @@
         <v>111.1907</v>
       </c>
       <c r="AT53" s="6">
-        <f>IF(COUNT(J53:J54)=2,(J53/J54-1)*100,"")</f>
+        <f>IF(COUNT(J53:J54)=2,ROUND((J53/J54-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU53" s="6">
-        <f>IF(COUNT(O53:O54)=2,(O53/O54-1)*100,"")</f>
+        <f>IF(COUNT(O53:O54)=2,ROUND((O53/O54-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV53" s="6">
-        <f>IF(COUNT(T53:T54)=2,(T53/T54-1)*100,"")</f>
+        <f>IF(COUNT(T53:T54)=2,ROUND((T53/T54-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW53" s="6">
-        <f>IF(COUNT(Y53:Y54)=2,(Y53/Y54-1)*100,"")</f>
+        <f>IF(COUNT(Y53:Y54)=2,ROUND((Y53/Y54-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX53" s="6">
-        <f>IF(COUNT(AD53:AD54)=2,(AD53/AD54-1)*100,"")</f>
+        <f>IF(COUNT(AD53:AD54)=2,ROUND((AD53/AD54-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY53" s="6">
-        <f>IF(COUNT(AI53:AI54)=2,(AI53/AI54-1)*100,"")</f>
+        <f>IF(COUNT(AI53:AI54)=2,ROUND((AI53/AI54-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ53" s="6">
-        <f>IF(COUNT(AN53:AN54)=2,(AN53/AN54-1)*100,"")</f>
+        <f>IF(COUNT(AN53:AN54)=2,ROUND((AN53/AN54-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA53" s="6">
-        <f>IF(COUNT(AS53:AS54)=2,(AS53/AS54-1)*100,"")</f>
+        <f>IF(COUNT(AS53:AS54)=2,ROUND((AS53/AS54-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB53" s="5" t="n">
         <v>19.87</v>
       </c>
       <c r="BC53" s="6">
-        <f>IF(COUNT(BB53:BB54)=2,(BB53/BB54-1)*100,"")</f>
+        <f>IF(COUNT(BB53:BB54)=2,ROUND((BB53/BB54-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD53" s="6" t="n">
@@ -11794,11 +11794,11 @@
         <v>179.65</v>
       </c>
       <c r="D54" s="6">
-        <f>IF(COUNT(B54:B55)=2,(B54/B55-1)*100,"")</f>
+        <f>IF(COUNT(B54:B55)=2,ROUND((B54/B55-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E54" s="6">
-        <f>IF(COUNT(C54:C55)=2,(C54/C55-1)*100,"")</f>
+        <f>IF(COUNT(C54:C55)=2,ROUND((C54/C55-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F54" s="5" t="n">
@@ -11922,42 +11922,42 @@
         <v>110.8017</v>
       </c>
       <c r="AT54" s="6">
-        <f>IF(COUNT(J54:J55)=2,(J54/J55-1)*100,"")</f>
+        <f>IF(COUNT(J54:J55)=2,ROUND((J54/J55-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU54" s="6">
-        <f>IF(COUNT(O54:O55)=2,(O54/O55-1)*100,"")</f>
+        <f>IF(COUNT(O54:O55)=2,ROUND((O54/O55-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV54" s="6">
-        <f>IF(COUNT(T54:T55)=2,(T54/T55-1)*100,"")</f>
+        <f>IF(COUNT(T54:T55)=2,ROUND((T54/T55-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW54" s="6">
-        <f>IF(COUNT(Y54:Y55)=2,(Y54/Y55-1)*100,"")</f>
+        <f>IF(COUNT(Y54:Y55)=2,ROUND((Y54/Y55-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX54" s="6">
-        <f>IF(COUNT(AD54:AD55)=2,(AD54/AD55-1)*100,"")</f>
+        <f>IF(COUNT(AD54:AD55)=2,ROUND((AD54/AD55-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY54" s="6">
-        <f>IF(COUNT(AI54:AI55)=2,(AI54/AI55-1)*100,"")</f>
+        <f>IF(COUNT(AI54:AI55)=2,ROUND((AI54/AI55-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ54" s="6">
-        <f>IF(COUNT(AN54:AN55)=2,(AN54/AN55-1)*100,"")</f>
+        <f>IF(COUNT(AN54:AN55)=2,ROUND((AN54/AN55-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA54" s="6">
-        <f>IF(COUNT(AS54:AS55)=2,(AS54/AS55-1)*100,"")</f>
+        <f>IF(COUNT(AS54:AS55)=2,ROUND((AS54/AS55-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB54" s="5" t="n">
         <v>18.92</v>
       </c>
       <c r="BC54" s="6">
-        <f>IF(COUNT(BB54:BB55)=2,(BB54/BB55-1)*100,"")</f>
+        <f>IF(COUNT(BB54:BB55)=2,ROUND((BB54/BB55-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD54" s="6" t="n">
@@ -12009,11 +12009,11 @@
         <v>178.71</v>
       </c>
       <c r="D55" s="6">
-        <f>IF(COUNT(B55:B56)=2,(B55/B56-1)*100,"")</f>
+        <f>IF(COUNT(B55:B56)=2,ROUND((B55/B56-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E55" s="6">
-        <f>IF(COUNT(C55:C56)=2,(C55/C56-1)*100,"")</f>
+        <f>IF(COUNT(C55:C56)=2,ROUND((C55/C56-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F55" s="5" t="n">
@@ -12137,42 +12137,42 @@
         <v>111.3802</v>
       </c>
       <c r="AT55" s="6">
-        <f>IF(COUNT(J55:J56)=2,(J55/J56-1)*100,"")</f>
+        <f>IF(COUNT(J55:J56)=2,ROUND((J55/J56-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU55" s="6">
-        <f>IF(COUNT(O55:O56)=2,(O55/O56-1)*100,"")</f>
+        <f>IF(COUNT(O55:O56)=2,ROUND((O55/O56-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV55" s="6">
-        <f>IF(COUNT(T55:T56)=2,(T55/T56-1)*100,"")</f>
+        <f>IF(COUNT(T55:T56)=2,ROUND((T55/T56-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW55" s="6">
-        <f>IF(COUNT(Y55:Y56)=2,(Y55/Y56-1)*100,"")</f>
+        <f>IF(COUNT(Y55:Y56)=2,ROUND((Y55/Y56-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX55" s="6">
-        <f>IF(COUNT(AD55:AD56)=2,(AD55/AD56-1)*100,"")</f>
+        <f>IF(COUNT(AD55:AD56)=2,ROUND((AD55/AD56-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY55" s="6">
-        <f>IF(COUNT(AI55:AI56)=2,(AI55/AI56-1)*100,"")</f>
+        <f>IF(COUNT(AI55:AI56)=2,ROUND((AI55/AI56-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ55" s="6">
-        <f>IF(COUNT(AN55:AN56)=2,(AN55/AN56-1)*100,"")</f>
+        <f>IF(COUNT(AN55:AN56)=2,ROUND((AN55/AN56-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA55" s="6">
-        <f>IF(COUNT(AS55:AS56)=2,(AS55/AS56-1)*100,"")</f>
+        <f>IF(COUNT(AS55:AS56)=2,ROUND((AS55/AS56-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB55" s="5" t="n">
         <v>21.51</v>
       </c>
       <c r="BC55" s="6">
-        <f>IF(COUNT(BB55:BB56)=2,(BB55/BB56-1)*100,"")</f>
+        <f>IF(COUNT(BB55:BB56)=2,ROUND((BB55/BB56-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD55" s="6" t="n">
@@ -12224,11 +12224,11 @@
         <v>188.65</v>
       </c>
       <c r="D56" s="6">
-        <f>IF(COUNT(B56:B57)=2,(B56/B57-1)*100,"")</f>
+        <f>IF(COUNT(B56:B57)=2,ROUND((B56/B57-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E56" s="6">
-        <f>IF(COUNT(C56:C57)=2,(C56/C57-1)*100,"")</f>
+        <f>IF(COUNT(C56:C57)=2,ROUND((C56/C57-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F56" s="5" t="n">
@@ -12352,42 +12352,42 @@
         <v>112.8165</v>
       </c>
       <c r="AT56" s="6">
-        <f>IF(COUNT(J56:J57)=2,(J56/J57-1)*100,"")</f>
+        <f>IF(COUNT(J56:J57)=2,ROUND((J56/J57-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU56" s="6">
-        <f>IF(COUNT(O56:O57)=2,(O56/O57-1)*100,"")</f>
+        <f>IF(COUNT(O56:O57)=2,ROUND((O56/O57-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV56" s="6">
-        <f>IF(COUNT(T56:T57)=2,(T56/T57-1)*100,"")</f>
+        <f>IF(COUNT(T56:T57)=2,ROUND((T56/T57-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW56" s="6">
-        <f>IF(COUNT(Y56:Y57)=2,(Y56/Y57-1)*100,"")</f>
+        <f>IF(COUNT(Y56:Y57)=2,ROUND((Y56/Y57-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX56" s="6">
-        <f>IF(COUNT(AD56:AD57)=2,(AD56/AD57-1)*100,"")</f>
+        <f>IF(COUNT(AD56:AD57)=2,ROUND((AD56/AD57-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY56" s="6">
-        <f>IF(COUNT(AI56:AI57)=2,(AI56/AI57-1)*100,"")</f>
+        <f>IF(COUNT(AI56:AI57)=2,ROUND((AI56/AI57-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ56" s="6">
-        <f>IF(COUNT(AN56:AN57)=2,(AN56/AN57-1)*100,"")</f>
+        <f>IF(COUNT(AN56:AN57)=2,ROUND((AN56/AN57-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA56" s="6">
-        <f>IF(COUNT(AS56:AS57)=2,(AS56/AS57-1)*100,"")</f>
+        <f>IF(COUNT(AS56:AS57)=2,ROUND((AS56/AS57-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB56" s="5" t="n">
         <v>15.4</v>
       </c>
       <c r="BC56" s="6">
-        <f>IF(COUNT(BB56:BB57)=2,(BB56/BB57-1)*100,"")</f>
+        <f>IF(COUNT(BB56:BB57)=2,ROUND((BB56/BB57-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD56" s="6" t="n">
@@ -12439,11 +12439,11 @@
         <v>187.13</v>
       </c>
       <c r="D57" s="6">
-        <f>IF(COUNT(B57:B58)=2,(B57/B58-1)*100,"")</f>
+        <f>IF(COUNT(B57:B58)=2,ROUND((B57/B58-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E57" s="6">
-        <f>IF(COUNT(C57:C58)=2,(C57/C58-1)*100,"")</f>
+        <f>IF(COUNT(C57:C58)=2,ROUND((C57/C58-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F57" s="5" t="n">
@@ -12567,42 +12567,42 @@
         <v>111.7892</v>
       </c>
       <c r="AT57" s="6">
-        <f>IF(COUNT(J57:J58)=2,(J57/J58-1)*100,"")</f>
+        <f>IF(COUNT(J57:J58)=2,ROUND((J57/J58-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU57" s="6">
-        <f>IF(COUNT(O57:O58)=2,(O57/O58-1)*100,"")</f>
+        <f>IF(COUNT(O57:O58)=2,ROUND((O57/O58-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV57" s="6">
-        <f>IF(COUNT(T57:T58)=2,(T57/T58-1)*100,"")</f>
+        <f>IF(COUNT(T57:T58)=2,ROUND((T57/T58-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW57" s="6">
-        <f>IF(COUNT(Y57:Y58)=2,(Y57/Y58-1)*100,"")</f>
+        <f>IF(COUNT(Y57:Y58)=2,ROUND((Y57/Y58-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX57" s="6">
-        <f>IF(COUNT(AD57:AD58)=2,(AD57/AD58-1)*100,"")</f>
+        <f>IF(COUNT(AD57:AD58)=2,ROUND((AD57/AD58-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY57" s="6">
-        <f>IF(COUNT(AI57:AI58)=2,(AI57/AI58-1)*100,"")</f>
+        <f>IF(COUNT(AI57:AI58)=2,ROUND((AI57/AI58-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ57" s="6">
-        <f>IF(COUNT(AN57:AN58)=2,(AN57/AN58-1)*100,"")</f>
+        <f>IF(COUNT(AN57:AN58)=2,ROUND((AN57/AN58-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA57" s="6">
-        <f>IF(COUNT(AS57:AS58)=2,(AS57/AS58-1)*100,"")</f>
+        <f>IF(COUNT(AS57:AS58)=2,ROUND((AS57/AS58-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB57" s="5" t="n">
         <v>16.06</v>
       </c>
       <c r="BC57" s="6">
-        <f>IF(COUNT(BB57:BB58)=2,(BB57/BB58-1)*100,"")</f>
+        <f>IF(COUNT(BB57:BB58)=2,ROUND((BB57/BB58-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD57" s="6" t="n">
@@ -12654,11 +12654,11 @@
         <v>189.9</v>
       </c>
       <c r="D58" s="6">
-        <f>IF(COUNT(B58:B59)=2,(B58/B59-1)*100,"")</f>
+        <f>IF(COUNT(B58:B59)=2,ROUND((B58/B59-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E58" s="6">
-        <f>IF(COUNT(C58:C59)=2,(C58/C59-1)*100,"")</f>
+        <f>IF(COUNT(C58:C59)=2,ROUND((C58/C59-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F58" s="5" t="n">
@@ -12782,42 +12782,42 @@
         <v>113.2753</v>
       </c>
       <c r="AT58" s="6">
-        <f>IF(COUNT(J58:J59)=2,(J58/J59-1)*100,"")</f>
+        <f>IF(COUNT(J58:J59)=2,ROUND((J58/J59-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU58" s="6">
-        <f>IF(COUNT(O58:O59)=2,(O58/O59-1)*100,"")</f>
+        <f>IF(COUNT(O58:O59)=2,ROUND((O58/O59-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV58" s="6">
-        <f>IF(COUNT(T58:T59)=2,(T58/T59-1)*100,"")</f>
+        <f>IF(COUNT(T58:T59)=2,ROUND((T58/T59-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW58" s="6">
-        <f>IF(COUNT(Y58:Y59)=2,(Y58/Y59-1)*100,"")</f>
+        <f>IF(COUNT(Y58:Y59)=2,ROUND((Y58/Y59-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX58" s="6">
-        <f>IF(COUNT(AD58:AD59)=2,(AD58/AD59-1)*100,"")</f>
+        <f>IF(COUNT(AD58:AD59)=2,ROUND((AD58/AD59-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY58" s="6">
-        <f>IF(COUNT(AI58:AI59)=2,(AI58/AI59-1)*100,"")</f>
+        <f>IF(COUNT(AI58:AI59)=2,ROUND((AI58/AI59-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ58" s="6">
-        <f>IF(COUNT(AN58:AN59)=2,(AN58/AN59-1)*100,"")</f>
+        <f>IF(COUNT(AN58:AN59)=2,ROUND((AN58/AN59-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA58" s="6">
-        <f>IF(COUNT(AS58:AS59)=2,(AS58/AS59-1)*100,"")</f>
+        <f>IF(COUNT(AS58:AS59)=2,ROUND((AS58/AS59-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB58" s="5" t="n">
         <v>15.77</v>
       </c>
       <c r="BC58" s="6">
-        <f>IF(COUNT(BB58:BB59)=2,(BB58/BB59-1)*100,"")</f>
+        <f>IF(COUNT(BB58:BB59)=2,ROUND((BB58/BB59-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD58" s="6" t="n">
@@ -12869,11 +12869,11 @@
         <v>189.42</v>
       </c>
       <c r="D59" s="6">
-        <f>IF(COUNT(B59:B60)=2,(B59/B60-1)*100,"")</f>
+        <f>IF(COUNT(B59:B60)=2,ROUND((B59/B60-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E59" s="6">
-        <f>IF(COUNT(C59:C60)=2,(C59/C60-1)*100,"")</f>
+        <f>IF(COUNT(C59:C60)=2,ROUND((C59/C60-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F59" s="5" t="n">
@@ -12997,42 +12997,42 @@
         <v>115.31</v>
       </c>
       <c r="AT59" s="6">
-        <f>IF(COUNT(J59:J60)=2,(J59/J60-1)*100,"")</f>
+        <f>IF(COUNT(J59:J60)=2,ROUND((J59/J60-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU59" s="6">
-        <f>IF(COUNT(O59:O60)=2,(O59/O60-1)*100,"")</f>
+        <f>IF(COUNT(O59:O60)=2,ROUND((O59/O60-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV59" s="6">
-        <f>IF(COUNT(T59:T60)=2,(T59/T60-1)*100,"")</f>
+        <f>IF(COUNT(T59:T60)=2,ROUND((T59/T60-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW59" s="6">
-        <f>IF(COUNT(Y59:Y60)=2,(Y59/Y60-1)*100,"")</f>
+        <f>IF(COUNT(Y59:Y60)=2,ROUND((Y59/Y60-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX59" s="6">
-        <f>IF(COUNT(AD59:AD60)=2,(AD59/AD60-1)*100,"")</f>
+        <f>IF(COUNT(AD59:AD60)=2,ROUND((AD59/AD60-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY59" s="6">
-        <f>IF(COUNT(AI59:AI60)=2,(AI59/AI60-1)*100,"")</f>
+        <f>IF(COUNT(AI59:AI60)=2,ROUND((AI59/AI60-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ59" s="6">
-        <f>IF(COUNT(AN59:AN60)=2,(AN59/AN60-1)*100,"")</f>
+        <f>IF(COUNT(AN59:AN60)=2,ROUND((AN59/AN60-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA59" s="6">
-        <f>IF(COUNT(AS59:AS60)=2,(AS59/AS60-1)*100,"")</f>
+        <f>IF(COUNT(AS59:AS60)=2,ROUND((AS59/AS60-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB59" s="5" t="n">
         <v>16.05</v>
       </c>
       <c r="BC59" s="6">
-        <f>IF(COUNT(BB59:BB60)=2,(BB59/BB60-1)*100,"")</f>
+        <f>IF(COUNT(BB59:BB60)=2,ROUND((BB59/BB60-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD59" s="6" t="n">
@@ -13084,11 +13084,11 @@
         <v>188.5</v>
       </c>
       <c r="D60" s="6">
-        <f>IF(COUNT(B60:B61)=2,(B60/B61-1)*100,"")</f>
+        <f>IF(COUNT(B60:B61)=2,ROUND((B60/B61-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E60" s="6">
-        <f>IF(COUNT(C60:C61)=2,(C60/C61-1)*100,"")</f>
+        <f>IF(COUNT(C60:C61)=2,ROUND((C60/C61-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F60" s="5" t="n">
@@ -13212,42 +13212,42 @@
         <v>115.3898</v>
       </c>
       <c r="AT60" s="6">
-        <f>IF(COUNT(J60:J61)=2,(J60/J61-1)*100,"")</f>
+        <f>IF(COUNT(J60:J61)=2,ROUND((J60/J61-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU60" s="6">
-        <f>IF(COUNT(O60:O61)=2,(O60/O61-1)*100,"")</f>
+        <f>IF(COUNT(O60:O61)=2,ROUND((O60/O61-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV60" s="6">
-        <f>IF(COUNT(T60:T61)=2,(T60/T61-1)*100,"")</f>
+        <f>IF(COUNT(T60:T61)=2,ROUND((T60/T61-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW60" s="6">
-        <f>IF(COUNT(Y60:Y61)=2,(Y60/Y61-1)*100,"")</f>
+        <f>IF(COUNT(Y60:Y61)=2,ROUND((Y60/Y61-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX60" s="6">
-        <f>IF(COUNT(AD60:AD61)=2,(AD60/AD61-1)*100,"")</f>
+        <f>IF(COUNT(AD60:AD61)=2,ROUND((AD60/AD61-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY60" s="6">
-        <f>IF(COUNT(AI60:AI61)=2,(AI60/AI61-1)*100,"")</f>
+        <f>IF(COUNT(AI60:AI61)=2,ROUND((AI60/AI61-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ60" s="6">
-        <f>IF(COUNT(AN60:AN61)=2,(AN60/AN61-1)*100,"")</f>
+        <f>IF(COUNT(AN60:AN61)=2,ROUND((AN60/AN61-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA60" s="6">
-        <f>IF(COUNT(AS60:AS61)=2,(AS60/AS61-1)*100,"")</f>
+        <f>IF(COUNT(AS60:AS61)=2,ROUND((AS60/AS61-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB60" s="5" t="n">
         <v>15.32</v>
       </c>
       <c r="BC60" s="6">
-        <f>IF(COUNT(BB60:BB61)=2,(BB60/BB61-1)*100,"")</f>
+        <f>IF(COUNT(BB60:BB61)=2,ROUND((BB60/BB61-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD60" s="6" t="n">
@@ -13299,11 +13299,11 @@
         <v>187.68</v>
       </c>
       <c r="D61" s="6">
-        <f>IF(COUNT(B61:B62)=2,(B61/B62-1)*100,"")</f>
+        <f>IF(COUNT(B61:B62)=2,ROUND((B61/B62-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E61" s="6">
-        <f>IF(COUNT(C61:C62)=2,(C61/C62-1)*100,"")</f>
+        <f>IF(COUNT(C61:C62)=2,ROUND((C61/C62-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F61" s="5" t="n">
@@ -13427,42 +13427,42 @@
         <v>116.3673</v>
       </c>
       <c r="AT61" s="6">
-        <f>IF(COUNT(J61:J62)=2,(J61/J62-1)*100,"")</f>
+        <f>IF(COUNT(J61:J62)=2,ROUND((J61/J62-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU61" s="6">
-        <f>IF(COUNT(O61:O62)=2,(O61/O62-1)*100,"")</f>
+        <f>IF(COUNT(O61:O62)=2,ROUND((O61/O62-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV61" s="6">
-        <f>IF(COUNT(T61:T62)=2,(T61/T62-1)*100,"")</f>
+        <f>IF(COUNT(T61:T62)=2,ROUND((T61/T62-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW61" s="6">
-        <f>IF(COUNT(Y61:Y62)=2,(Y61/Y62-1)*100,"")</f>
+        <f>IF(COUNT(Y61:Y62)=2,ROUND((Y61/Y62-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX61" s="6">
-        <f>IF(COUNT(AD61:AD62)=2,(AD61/AD62-1)*100,"")</f>
+        <f>IF(COUNT(AD61:AD62)=2,ROUND((AD61/AD62-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY61" s="6">
-        <f>IF(COUNT(AI61:AI62)=2,(AI61/AI62-1)*100,"")</f>
+        <f>IF(COUNT(AI61:AI62)=2,ROUND((AI61/AI62-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ61" s="6">
-        <f>IF(COUNT(AN61:AN62)=2,(AN61/AN62-1)*100,"")</f>
+        <f>IF(COUNT(AN61:AN62)=2,ROUND((AN61/AN62-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA61" s="6">
-        <f>IF(COUNT(AS61:AS62)=2,(AS61/AS62-1)*100,"")</f>
+        <f>IF(COUNT(AS61:AS62)=2,ROUND((AS61/AS62-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB61" s="5" t="n">
         <v>15.74</v>
       </c>
       <c r="BC61" s="6">
-        <f>IF(COUNT(BB61:BB62)=2,(BB61/BB62-1)*100,"")</f>
+        <f>IF(COUNT(BB61:BB62)=2,ROUND((BB61/BB62-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD61" s="6" t="n">
@@ -13514,11 +13514,11 @@
         <v>185.59</v>
       </c>
       <c r="D62" s="6">
-        <f>IF(COUNT(B62:B63)=2,(B62/B63-1)*100,"")</f>
+        <f>IF(COUNT(B62:B63)=2,ROUND((B62/B63-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E62" s="6">
-        <f>IF(COUNT(C62:C63)=2,(C62/C63-1)*100,"")</f>
+        <f>IF(COUNT(C62:C63)=2,ROUND((C62/C63-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F62" s="5" t="n">
@@ -13642,42 +13642,42 @@
         <v>115.9583</v>
       </c>
       <c r="AT62" s="6">
-        <f>IF(COUNT(J62:J63)=2,(J62/J63-1)*100,"")</f>
+        <f>IF(COUNT(J62:J63)=2,ROUND((J62/J63-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU62" s="6">
-        <f>IF(COUNT(O62:O63)=2,(O62/O63-1)*100,"")</f>
+        <f>IF(COUNT(O62:O63)=2,ROUND((O62/O63-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV62" s="6">
-        <f>IF(COUNT(T62:T63)=2,(T62/T63-1)*100,"")</f>
+        <f>IF(COUNT(T62:T63)=2,ROUND((T62/T63-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW62" s="6">
-        <f>IF(COUNT(Y62:Y63)=2,(Y62/Y63-1)*100,"")</f>
+        <f>IF(COUNT(Y62:Y63)=2,ROUND((Y62/Y63-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX62" s="6">
-        <f>IF(COUNT(AD62:AD63)=2,(AD62/AD63-1)*100,"")</f>
+        <f>IF(COUNT(AD62:AD63)=2,ROUND((AD62/AD63-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY62" s="6">
-        <f>IF(COUNT(AI62:AI63)=2,(AI62/AI63-1)*100,"")</f>
+        <f>IF(COUNT(AI62:AI63)=2,ROUND((AI62/AI63-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ62" s="6">
-        <f>IF(COUNT(AN62:AN63)=2,(AN62/AN63-1)*100,"")</f>
+        <f>IF(COUNT(AN62:AN63)=2,ROUND((AN62/AN63-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA62" s="6">
-        <f>IF(COUNT(AS62:AS63)=2,(AS62/AS63-1)*100,"")</f>
+        <f>IF(COUNT(AS62:AS63)=2,ROUND((AS62/AS63-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB62" s="5" t="n">
         <v>16.29</v>
       </c>
       <c r="BC62" s="6">
-        <f>IF(COUNT(BB62:BB63)=2,(BB62/BB63-1)*100,"")</f>
+        <f>IF(COUNT(BB62:BB63)=2,ROUND((BB62/BB63-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD62" s="6" t="n">
@@ -13729,11 +13729,11 @@
         <v>185.57</v>
       </c>
       <c r="D63" s="6">
-        <f>IF(COUNT(B63:B64)=2,(B63/B64-1)*100,"")</f>
+        <f>IF(COUNT(B63:B64)=2,ROUND((B63/B64-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E63" s="6">
-        <f>IF(COUNT(C63:C64)=2,(C63/C64-1)*100,"")</f>
+        <f>IF(COUNT(C63:C64)=2,ROUND((C63/C64-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F63" s="5" t="n">
@@ -13857,42 +13857,42 @@
         <v>115.2502</v>
       </c>
       <c r="AT63" s="6">
-        <f>IF(COUNT(J63:J64)=2,(J63/J64-1)*100,"")</f>
+        <f>IF(COUNT(J63:J64)=2,ROUND((J63/J64-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU63" s="6">
-        <f>IF(COUNT(O63:O64)=2,(O63/O64-1)*100,"")</f>
+        <f>IF(COUNT(O63:O64)=2,ROUND((O63/O64-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV63" s="6">
-        <f>IF(COUNT(T63:T64)=2,(T63/T64-1)*100,"")</f>
+        <f>IF(COUNT(T63:T64)=2,ROUND((T63/T64-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW63" s="6">
-        <f>IF(COUNT(Y63:Y64)=2,(Y63/Y64-1)*100,"")</f>
+        <f>IF(COUNT(Y63:Y64)=2,ROUND((Y63/Y64-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX63" s="6">
-        <f>IF(COUNT(AD63:AD64)=2,(AD63/AD64-1)*100,"")</f>
+        <f>IF(COUNT(AD63:AD64)=2,ROUND((AD63/AD64-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY63" s="6">
-        <f>IF(COUNT(AI63:AI64)=2,(AI63/AI64-1)*100,"")</f>
+        <f>IF(COUNT(AI63:AI64)=2,ROUND((AI63/AI64-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ63" s="6">
-        <f>IF(COUNT(AN63:AN64)=2,(AN63/AN64-1)*100,"")</f>
+        <f>IF(COUNT(AN63:AN64)=2,ROUND((AN63/AN64-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA63" s="6">
-        <f>IF(COUNT(AS63:AS64)=2,(AS63/AS64-1)*100,"")</f>
+        <f>IF(COUNT(AS63:AS64)=2,ROUND((AS63/AS64-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB63" s="5" t="n">
         <v>17.01</v>
       </c>
       <c r="BC63" s="6">
-        <f>IF(COUNT(BB63:BB64)=2,(BB63/BB64-1)*100,"")</f>
+        <f>IF(COUNT(BB63:BB64)=2,ROUND((BB63/BB64-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD63" s="6" t="n">
@@ -13944,11 +13944,11 @@
         <v>183.39</v>
       </c>
       <c r="D64" s="6">
-        <f>IF(COUNT(B64:B65)=2,(B64/B65-1)*100,"")</f>
+        <f>IF(COUNT(B64:B65)=2,ROUND((B64/B65-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E64" s="6">
-        <f>IF(COUNT(C64:C65)=2,(C64/C65-1)*100,"")</f>
+        <f>IF(COUNT(C64:C65)=2,ROUND((C64/C65-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F64" s="5" t="n">
@@ -14072,42 +14072,42 @@
         <v>115.1604</v>
       </c>
       <c r="AT64" s="6">
-        <f>IF(COUNT(J64:J65)=2,(J64/J65-1)*100,"")</f>
+        <f>IF(COUNT(J64:J65)=2,ROUND((J64/J65-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU64" s="6">
-        <f>IF(COUNT(O64:O65)=2,(O64/O65-1)*100,"")</f>
+        <f>IF(COUNT(O64:O65)=2,ROUND((O64/O65-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV64" s="6">
-        <f>IF(COUNT(T64:T65)=2,(T64/T65-1)*100,"")</f>
+        <f>IF(COUNT(T64:T65)=2,ROUND((T64/T65-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW64" s="6">
-        <f>IF(COUNT(Y64:Y65)=2,(Y64/Y65-1)*100,"")</f>
+        <f>IF(COUNT(Y64:Y65)=2,ROUND((Y64/Y65-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX64" s="6">
-        <f>IF(COUNT(AD64:AD65)=2,(AD64/AD65-1)*100,"")</f>
+        <f>IF(COUNT(AD64:AD65)=2,ROUND((AD64/AD65-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY64" s="6">
-        <f>IF(COUNT(AI64:AI65)=2,(AI64/AI65-1)*100,"")</f>
+        <f>IF(COUNT(AI64:AI65)=2,ROUND((AI64/AI65-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ64" s="6">
-        <f>IF(COUNT(AN64:AN65)=2,(AN64/AN65-1)*100,"")</f>
+        <f>IF(COUNT(AN64:AN65)=2,ROUND((AN64/AN65-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA64" s="6">
-        <f>IF(COUNT(AS64:AS65)=2,(AS64/AS65-1)*100,"")</f>
+        <f>IF(COUNT(AS64:AS65)=2,ROUND((AS64/AS65-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB64" s="5" t="n">
         <v>16.7</v>
       </c>
       <c r="BC64" s="6">
-        <f>IF(COUNT(BB64:BB65)=2,(BB64/BB65-1)*100,"")</f>
+        <f>IF(COUNT(BB64:BB65)=2,ROUND((BB64/BB65-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD64" s="6" t="n">
@@ -14159,11 +14159,11 @@
         <v>182.04</v>
       </c>
       <c r="D65" s="6">
-        <f>IF(COUNT(B65:B66)=2,(B65/B66-1)*100,"")</f>
+        <f>IF(COUNT(B65:B66)=2,ROUND((B65/B66-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E65" s="6">
-        <f>IF(COUNT(C65:C66)=2,(C65/C66-1)*100,"")</f>
+        <f>IF(COUNT(C65:C66)=2,ROUND((C65/C66-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F65" s="5" t="n">
@@ -14287,42 +14287,42 @@
         <v>115.7987</v>
       </c>
       <c r="AT65" s="6">
-        <f>IF(COUNT(J65:J66)=2,(J65/J66-1)*100,"")</f>
+        <f>IF(COUNT(J65:J66)=2,ROUND((J65/J66-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU65" s="6">
-        <f>IF(COUNT(O65:O66)=2,(O65/O66-1)*100,"")</f>
+        <f>IF(COUNT(O65:O66)=2,ROUND((O65/O66-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV65" s="6">
-        <f>IF(COUNT(T65:T66)=2,(T65/T66-1)*100,"")</f>
+        <f>IF(COUNT(T65:T66)=2,ROUND((T65/T66-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW65" s="6">
-        <f>IF(COUNT(Y65:Y66)=2,(Y65/Y66-1)*100,"")</f>
+        <f>IF(COUNT(Y65:Y66)=2,ROUND((Y65/Y66-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX65" s="6">
-        <f>IF(COUNT(AD65:AD66)=2,(AD65/AD66-1)*100,"")</f>
+        <f>IF(COUNT(AD65:AD66)=2,ROUND((AD65/AD66-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY65" s="6">
-        <f>IF(COUNT(AI65:AI66)=2,(AI65/AI66-1)*100,"")</f>
+        <f>IF(COUNT(AI65:AI66)=2,ROUND((AI65/AI66-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ65" s="6">
-        <f>IF(COUNT(AN65:AN66)=2,(AN65/AN66-1)*100,"")</f>
+        <f>IF(COUNT(AN65:AN66)=2,ROUND((AN65/AN66-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA65" s="6">
-        <f>IF(COUNT(AS65:AS66)=2,(AS65/AS66-1)*100,"")</f>
+        <f>IF(COUNT(AS65:AS66)=2,ROUND((AS65/AS66-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB65" s="5" t="n">
         <v>16.76</v>
       </c>
       <c r="BC65" s="6">
-        <f>IF(COUNT(BB65:BB66)=2,(BB65/BB66-1)*100,"")</f>
+        <f>IF(COUNT(BB65:BB66)=2,ROUND((BB65/BB66-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD65" s="6" t="n">
@@ -14374,11 +14374,11 @@
         <v>181.4</v>
       </c>
       <c r="D66" s="6">
-        <f>IF(COUNT(B66:B67)=2,(B66/B67-1)*100,"")</f>
+        <f>IF(COUNT(B66:B67)=2,ROUND((B66/B67-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E66" s="6">
-        <f>IF(COUNT(C66:C67)=2,(C66/C67-1)*100,"")</f>
+        <f>IF(COUNT(C66:C67)=2,ROUND((C66/C67-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F66" s="5" t="n">
@@ -14502,42 +14502,42 @@
         <v>115.7987</v>
       </c>
       <c r="AT66" s="6">
-        <f>IF(COUNT(J66:J67)=2,(J66/J67-1)*100,"")</f>
+        <f>IF(COUNT(J66:J67)=2,ROUND((J66/J67-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU66" s="6">
-        <f>IF(COUNT(O66:O67)=2,(O66/O67-1)*100,"")</f>
+        <f>IF(COUNT(O66:O67)=2,ROUND((O66/O67-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV66" s="6">
-        <f>IF(COUNT(T66:T67)=2,(T66/T67-1)*100,"")</f>
+        <f>IF(COUNT(T66:T67)=2,ROUND((T66/T67-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW66" s="6">
-        <f>IF(COUNT(Y66:Y67)=2,(Y66/Y67-1)*100,"")</f>
+        <f>IF(COUNT(Y66:Y67)=2,ROUND((Y66/Y67-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX66" s="6">
-        <f>IF(COUNT(AD66:AD67)=2,(AD66/AD67-1)*100,"")</f>
+        <f>IF(COUNT(AD66:AD67)=2,ROUND((AD66/AD67-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY66" s="6">
-        <f>IF(COUNT(AI66:AI67)=2,(AI66/AI67-1)*100,"")</f>
+        <f>IF(COUNT(AI66:AI67)=2,ROUND((AI66/AI67-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ66" s="6">
-        <f>IF(COUNT(AN66:AN67)=2,(AN66/AN67-1)*100,"")</f>
+        <f>IF(COUNT(AN66:AN67)=2,ROUND((AN66/AN67-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA66" s="6">
-        <f>IF(COUNT(AS66:AS67)=2,(AS66/AS67-1)*100,"")</f>
+        <f>IF(COUNT(AS66:AS67)=2,ROUND((AS66/AS67-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB66" s="5" t="n">
         <v>17.44</v>
       </c>
       <c r="BC66" s="6">
-        <f>IF(COUNT(BB66:BB67)=2,(BB66/BB67-1)*100,"")</f>
+        <f>IF(COUNT(BB66:BB67)=2,ROUND((BB66/BB67-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD66" s="6" t="n">
@@ -14589,11 +14589,11 @@
         <v>177.64</v>
       </c>
       <c r="D67" s="6">
-        <f>IF(COUNT(B67:B68)=2,(B67/B68-1)*100,"")</f>
+        <f>IF(COUNT(B67:B68)=2,ROUND((B67/B68-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E67" s="6">
-        <f>IF(COUNT(C67:C68)=2,(C67/C68-1)*100,"")</f>
+        <f>IF(COUNT(C67:C68)=2,ROUND((C67/C68-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F67" s="5" t="n">
@@ -14717,42 +14717,42 @@
         <v>115.5494</v>
       </c>
       <c r="AT67" s="6">
-        <f>IF(COUNT(J67:J68)=2,(J67/J68-1)*100,"")</f>
+        <f>IF(COUNT(J67:J68)=2,ROUND((J67/J68-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU67" s="6">
-        <f>IF(COUNT(O67:O68)=2,(O67/O68-1)*100,"")</f>
+        <f>IF(COUNT(O67:O68)=2,ROUND((O67/O68-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV67" s="6">
-        <f>IF(COUNT(T67:T68)=2,(T67/T68-1)*100,"")</f>
+        <f>IF(COUNT(T67:T68)=2,ROUND((T67/T68-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW67" s="6">
-        <f>IF(COUNT(Y67:Y68)=2,(Y67/Y68-1)*100,"")</f>
+        <f>IF(COUNT(Y67:Y68)=2,ROUND((Y67/Y68-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX67" s="6">
-        <f>IF(COUNT(AD67:AD68)=2,(AD67/AD68-1)*100,"")</f>
+        <f>IF(COUNT(AD67:AD68)=2,ROUND((AD67/AD68-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY67" s="6">
-        <f>IF(COUNT(AI67:AI68)=2,(AI67/AI68-1)*100,"")</f>
+        <f>IF(COUNT(AI67:AI68)=2,ROUND((AI67/AI68-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ67" s="6">
-        <f>IF(COUNT(AN67:AN68)=2,(AN67/AN68-1)*100,"")</f>
+        <f>IF(COUNT(AN67:AN68)=2,ROUND((AN67/AN68-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA67" s="6">
-        <f>IF(COUNT(AS67:AS68)=2,(AS67/AS68-1)*100,"")</f>
+        <f>IF(COUNT(AS67:AS68)=2,ROUND((AS67/AS68-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB67" s="5" t="n">
         <v>18.06</v>
       </c>
       <c r="BC67" s="6">
-        <f>IF(COUNT(BB67:BB68)=2,(BB67/BB68-1)*100,"")</f>
+        <f>IF(COUNT(BB67:BB68)=2,ROUND((BB67/BB68-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD67" s="6" t="n">
@@ -14804,11 +14804,11 @@
         <v>180.04</v>
       </c>
       <c r="D68" s="6">
-        <f>IF(COUNT(B68:B69)=2,(B68/B69-1)*100,"")</f>
+        <f>IF(COUNT(B68:B69)=2,ROUND((B68/B69-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E68" s="6">
-        <f>IF(COUNT(C68:C69)=2,(C68/C69-1)*100,"")</f>
+        <f>IF(COUNT(C68:C69)=2,ROUND((C68/C69-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F68" s="5" t="n">
@@ -14932,42 +14932,42 @@
         <v>116.6765</v>
       </c>
       <c r="AT68" s="6">
-        <f>IF(COUNT(J68:J69)=2,(J68/J69-1)*100,"")</f>
+        <f>IF(COUNT(J68:J69)=2,ROUND((J68/J69-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU68" s="6">
-        <f>IF(COUNT(O68:O69)=2,(O68/O69-1)*100,"")</f>
+        <f>IF(COUNT(O68:O69)=2,ROUND((O68/O69-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV68" s="6">
-        <f>IF(COUNT(T68:T69)=2,(T68/T69-1)*100,"")</f>
+        <f>IF(COUNT(T68:T69)=2,ROUND((T68/T69-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW68" s="6">
-        <f>IF(COUNT(Y68:Y69)=2,(Y68/Y69-1)*100,"")</f>
+        <f>IF(COUNT(Y68:Y69)=2,ROUND((Y68/Y69-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX68" s="6">
-        <f>IF(COUNT(AD68:AD69)=2,(AD68/AD69-1)*100,"")</f>
+        <f>IF(COUNT(AD68:AD69)=2,ROUND((AD68/AD69-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY68" s="6">
-        <f>IF(COUNT(AI68:AI69)=2,(AI68/AI69-1)*100,"")</f>
+        <f>IF(COUNT(AI68:AI69)=2,ROUND((AI68/AI69-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ68" s="6">
-        <f>IF(COUNT(AN68:AN69)=2,(AN68/AN69-1)*100,"")</f>
+        <f>IF(COUNT(AN68:AN69)=2,ROUND((AN68/AN69-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA68" s="6">
-        <f>IF(COUNT(AS68:AS69)=2,(AS68/AS69-1)*100,"")</f>
+        <f>IF(COUNT(AS68:AS69)=2,ROUND((AS68/AS69-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB68" s="5" t="n">
         <v>17.82</v>
       </c>
       <c r="BC68" s="6">
-        <f>IF(COUNT(BB68:BB69)=2,(BB68/BB69-1)*100,"")</f>
+        <f>IF(COUNT(BB68:BB69)=2,ROUND((BB68/BB69-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD68" s="6" t="n">
@@ -15019,11 +15019,11 @@
         <v>180.37</v>
       </c>
       <c r="D69" s="6">
-        <f>IF(COUNT(B69:B70)=2,(B69/B70-1)*100,"")</f>
+        <f>IF(COUNT(B69:B70)=2,ROUND((B69/B70-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E69" s="6">
-        <f>IF(COUNT(C69:C70)=2,(C69/C70-1)*100,"")</f>
+        <f>IF(COUNT(C69:C70)=2,ROUND((C69/C70-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F69" s="5" t="n">
@@ -15147,42 +15147,42 @@
         <v>115.7788</v>
       </c>
       <c r="AT69" s="6">
-        <f>IF(COUNT(J69:J70)=2,(J69/J70-1)*100,"")</f>
+        <f>IF(COUNT(J69:J70)=2,ROUND((J69/J70-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU69" s="6">
-        <f>IF(COUNT(O69:O70)=2,(O69/O70-1)*100,"")</f>
+        <f>IF(COUNT(O69:O70)=2,ROUND((O69/O70-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV69" s="6">
-        <f>IF(COUNT(T69:T70)=2,(T69/T70-1)*100,"")</f>
+        <f>IF(COUNT(T69:T70)=2,ROUND((T69/T70-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW69" s="6">
-        <f>IF(COUNT(Y69:Y70)=2,(Y69/Y70-1)*100,"")</f>
+        <f>IF(COUNT(Y69:Y70)=2,ROUND((Y69/Y70-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX69" s="6">
-        <f>IF(COUNT(AD69:AD70)=2,(AD69/AD70-1)*100,"")</f>
+        <f>IF(COUNT(AD69:AD70)=2,ROUND((AD69/AD70-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY69" s="6">
-        <f>IF(COUNT(AI69:AI70)=2,(AI69/AI70-1)*100,"")</f>
+        <f>IF(COUNT(AI69:AI70)=2,ROUND((AI69/AI70-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ69" s="6">
-        <f>IF(COUNT(AN69:AN70)=2,(AN69/AN70-1)*100,"")</f>
+        <f>IF(COUNT(AN69:AN70)=2,ROUND((AN69/AN70-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA69" s="6">
-        <f>IF(COUNT(AS69:AS70)=2,(AS69/AS70-1)*100,"")</f>
+        <f>IF(COUNT(AS69:AS70)=2,ROUND((AS69/AS70-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB69" s="5" t="n">
         <v>18.43</v>
       </c>
       <c r="BC69" s="6">
-        <f>IF(COUNT(BB69:BB70)=2,(BB69/BB70-1)*100,"")</f>
+        <f>IF(COUNT(BB69:BB70)=2,ROUND((BB69/BB70-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD69" s="6" t="n">
@@ -15234,11 +15234,11 @@
         <v>184.9</v>
       </c>
       <c r="D70" s="6">
-        <f>IF(COUNT(B70:B71)=2,(B70/B71-1)*100,"")</f>
+        <f>IF(COUNT(B70:B71)=2,ROUND((B70/B71-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E70" s="6">
-        <f>IF(COUNT(C70:C71)=2,(C70/C71-1)*100,"")</f>
+        <f>IF(COUNT(C70:C71)=2,ROUND((C70/C71-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F70" s="5" t="n">
@@ -15362,42 +15362,42 @@
         <v>116.8061</v>
       </c>
       <c r="AT70" s="6">
-        <f>IF(COUNT(J70:J71)=2,(J70/J71-1)*100,"")</f>
+        <f>IF(COUNT(J70:J71)=2,ROUND((J70/J71-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU70" s="6">
-        <f>IF(COUNT(O70:O71)=2,(O70/O71-1)*100,"")</f>
+        <f>IF(COUNT(O70:O71)=2,ROUND((O70/O71-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV70" s="6">
-        <f>IF(COUNT(T70:T71)=2,(T70/T71-1)*100,"")</f>
+        <f>IF(COUNT(T70:T71)=2,ROUND((T70/T71-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW70" s="6">
-        <f>IF(COUNT(Y70:Y71)=2,(Y70/Y71-1)*100,"")</f>
+        <f>IF(COUNT(Y70:Y71)=2,ROUND((Y70/Y71-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX70" s="6">
-        <f>IF(COUNT(AD70:AD71)=2,(AD70/AD71-1)*100,"")</f>
+        <f>IF(COUNT(AD70:AD71)=2,ROUND((AD70/AD71-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY70" s="6">
-        <f>IF(COUNT(AI70:AI71)=2,(AI70/AI71-1)*100,"")</f>
+        <f>IF(COUNT(AI70:AI71)=2,ROUND((AI70/AI71-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ70" s="6">
-        <f>IF(COUNT(AN70:AN71)=2,(AN70/AN71-1)*100,"")</f>
+        <f>IF(COUNT(AN70:AN71)=2,ROUND((AN70/AN71-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA70" s="6">
-        <f>IF(COUNT(AS70:AS71)=2,(AS70/AS71-1)*100,"")</f>
+        <f>IF(COUNT(AS70:AS71)=2,ROUND((AS70/AS71-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB70" s="5" t="n">
         <v>17.26</v>
       </c>
       <c r="BC70" s="6">
-        <f>IF(COUNT(BB70:BB71)=2,(BB70/BB71-1)*100,"")</f>
+        <f>IF(COUNT(BB70:BB71)=2,ROUND((BB70/BB71-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD70" s="6" t="n">
@@ -15449,11 +15449,11 @@
         <v>182.13</v>
       </c>
       <c r="D71" s="6">
-        <f>IF(COUNT(B71:B72)=2,(B71/B72-1)*100,"")</f>
+        <f>IF(COUNT(B71:B72)=2,ROUND((B71/B72-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E71" s="6">
-        <f>IF(COUNT(C71:C72)=2,(C71/C72-1)*100,"")</f>
+        <f>IF(COUNT(C71:C72)=2,ROUND((C71/C72-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F71" s="5" t="n">
@@ -15577,42 +15577,42 @@
         <v>116.457</v>
       </c>
       <c r="AT71" s="6">
-        <f>IF(COUNT(J71:J72)=2,(J71/J72-1)*100,"")</f>
+        <f>IF(COUNT(J71:J72)=2,ROUND((J71/J72-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU71" s="6">
-        <f>IF(COUNT(O71:O72)=2,(O71/O72-1)*100,"")</f>
+        <f>IF(COUNT(O71:O72)=2,ROUND((O71/O72-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV71" s="6">
-        <f>IF(COUNT(T71:T72)=2,(T71/T72-1)*100,"")</f>
+        <f>IF(COUNT(T71:T72)=2,ROUND((T71/T72-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW71" s="6">
-        <f>IF(COUNT(Y71:Y72)=2,(Y71/Y72-1)*100,"")</f>
+        <f>IF(COUNT(Y71:Y72)=2,ROUND((Y71/Y72-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX71" s="6">
-        <f>IF(COUNT(AD71:AD72)=2,(AD71/AD72-1)*100,"")</f>
+        <f>IF(COUNT(AD71:AD72)=2,ROUND((AD71/AD72-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY71" s="6">
-        <f>IF(COUNT(AI71:AI72)=2,(AI71/AI72-1)*100,"")</f>
+        <f>IF(COUNT(AI71:AI72)=2,ROUND((AI71/AI72-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ71" s="6">
-        <f>IF(COUNT(AN71:AN72)=2,(AN71/AN72-1)*100,"")</f>
+        <f>IF(COUNT(AN71:AN72)=2,ROUND((AN71/AN72-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA71" s="6">
-        <f>IF(COUNT(AS71:AS72)=2,(AS71/AS72-1)*100,"")</f>
+        <f>IF(COUNT(AS71:AS72)=2,ROUND((AS71/AS72-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB71" s="5" t="n">
         <v>17.87</v>
       </c>
       <c r="BC71" s="6">
-        <f>IF(COUNT(BB71:BB72)=2,(BB71/BB72-1)*100,"")</f>
+        <f>IF(COUNT(BB71:BB72)=2,ROUND((BB71/BB72-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD71" s="6" t="n">
@@ -15664,11 +15664,11 @@
         <v>180.05</v>
       </c>
       <c r="D72" s="6">
-        <f>IF(COUNT(B72:B73)=2,(B72/B73-1)*100,"")</f>
+        <f>IF(COUNT(B72:B73)=2,ROUND((B72/B73-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E72" s="6">
-        <f>IF(COUNT(C72:C73)=2,(C72/C73-1)*100,"")</f>
+        <f>IF(COUNT(C72:C73)=2,ROUND((C72/C73-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F72" s="5" t="n">
@@ -15792,42 +15792,42 @@
         <v>115.5594</v>
       </c>
       <c r="AT72" s="6">
-        <f>IF(COUNT(J72:J73)=2,(J72/J73-1)*100,"")</f>
+        <f>IF(COUNT(J72:J73)=2,ROUND((J72/J73-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU72" s="6">
-        <f>IF(COUNT(O72:O73)=2,(O72/O73-1)*100,"")</f>
+        <f>IF(COUNT(O72:O73)=2,ROUND((O72/O73-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV72" s="6">
-        <f>IF(COUNT(T72:T73)=2,(T72/T73-1)*100,"")</f>
+        <f>IF(COUNT(T72:T73)=2,ROUND((T72/T73-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW72" s="6">
-        <f>IF(COUNT(Y72:Y73)=2,(Y72/Y73-1)*100,"")</f>
+        <f>IF(COUNT(Y72:Y73)=2,ROUND((Y72/Y73-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX72" s="6">
-        <f>IF(COUNT(AD72:AD73)=2,(AD72/AD73-1)*100,"")</f>
+        <f>IF(COUNT(AD72:AD73)=2,ROUND((AD72/AD73-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY72" s="6">
-        <f>IF(COUNT(AI72:AI73)=2,(AI72/AI73-1)*100,"")</f>
+        <f>IF(COUNT(AI72:AI73)=2,ROUND((AI72/AI73-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ72" s="6">
-        <f>IF(COUNT(AN72:AN73)=2,(AN72/AN73-1)*100,"")</f>
+        <f>IF(COUNT(AN72:AN73)=2,ROUND((AN72/AN73-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA72" s="6">
-        <f>IF(COUNT(AS72:AS73)=2,(AS72/AS73-1)*100,"")</f>
+        <f>IF(COUNT(AS72:AS73)=2,ROUND((AS72/AS73-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB72" s="5" t="n">
         <v>17.99</v>
       </c>
       <c r="BC72" s="6">
-        <f>IF(COUNT(BB72:BB73)=2,(BB72/BB73-1)*100,"")</f>
+        <f>IF(COUNT(BB72:BB73)=2,ROUND((BB72/BB73-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD72" s="6" t="n">
@@ -15879,11 +15879,11 @@
         <v>180.64</v>
       </c>
       <c r="D73" s="6">
-        <f>IF(COUNT(B73:B74)=2,(B73/B74-1)*100,"")</f>
+        <f>IF(COUNT(B73:B74)=2,ROUND((B73/B74-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="E73" s="6">
-        <f>IF(COUNT(C73:C74)=2,(C73/C74-1)*100,"")</f>
+        <f>IF(COUNT(C73:C74)=2,ROUND((C73/C74-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="F73" s="5" t="n">
@@ -16007,42 +16007,42 @@
         <v>115.2801</v>
       </c>
       <c r="AT73" s="6">
-        <f>IF(COUNT(J73:J74)=2,(J73/J74-1)*100,"")</f>
+        <f>IF(COUNT(J73:J74)=2,ROUND((J73/J74-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AU73" s="6">
-        <f>IF(COUNT(O73:O74)=2,(O73/O74-1)*100,"")</f>
+        <f>IF(COUNT(O73:O74)=2,ROUND((O73/O74-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AV73" s="6">
-        <f>IF(COUNT(T73:T74)=2,(T73/T74-1)*100,"")</f>
+        <f>IF(COUNT(T73:T74)=2,ROUND((T73/T74-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW73" s="6">
-        <f>IF(COUNT(Y73:Y74)=2,(Y73/Y74-1)*100,"")</f>
+        <f>IF(COUNT(Y73:Y74)=2,ROUND((Y73/Y74-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AX73" s="6">
-        <f>IF(COUNT(AD73:AD74)=2,(AD73/AD74-1)*100,"")</f>
+        <f>IF(COUNT(AD73:AD74)=2,ROUND((AD73/AD74-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AY73" s="6">
-        <f>IF(COUNT(AI73:AI74)=2,(AI73/AI74-1)*100,"")</f>
+        <f>IF(COUNT(AI73:AI74)=2,ROUND((AI73/AI74-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AZ73" s="6">
-        <f>IF(COUNT(AN73:AN74)=2,(AN73/AN74-1)*100,"")</f>
+        <f>IF(COUNT(AN73:AN74)=2,ROUND((AN73/AN74-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BA73" s="6">
-        <f>IF(COUNT(AS73:AS74)=2,(AS73/AS74-1)*100,"")</f>
+        <f>IF(COUNT(AS73:AS74)=2,ROUND((AS73/AS74-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BB73" s="5" t="n">
         <v>18.38</v>
       </c>
       <c r="BC73" s="6">
-        <f>IF(COUNT(BB73:BB74)=2,(BB73/BB74-1)*100,"")</f>
+        <f>IF(COUNT(BB73:BB74)=2,ROUND((BB73/BB74-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BD73" s="6" t="n">

--- a/04_结果/示例审批/两基金_m30新版式示例_公式说明版.xlsx
+++ b/04_结果/示例审批/两基金_m30新版式示例_公式说明版.xlsx
@@ -557,7 +557,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   表内按区块排列：基金区、每支ETF、ETF区结束后均用空白列分隔；外部 VIX→回报。</t>
+          <t xml:space="preserve">   表内按区块排列：基金区、每支ETF、ETF区、VIX区结束后均用空白列分隔。</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,15 @@
         <f>BQ3/(BQ3+BQ4)</f>
         <v/>
       </c>
-      <c r="BR2" s="3" t="n"/>
-      <c r="BS2" s="3">
-        <f>BS3/(BS3+BS4)</f>
-        <v/>
-      </c>
-      <c r="BT2" s="3" t="n"/>
+      <c r="BR2" s="3">
+        <f>BR3/(BR3+BR4)</f>
+        <v/>
+      </c>
+      <c r="BS2" s="3" t="n"/>
+      <c r="BT2" s="3">
+        <f>BT3/(BT3+BT4)</f>
+        <v/>
+      </c>
       <c r="BU2" s="3">
         <f>BU3/(BU3+BU4)</f>
         <v/>
@@ -1002,10 +1005,7 @@
         <f>BV3/(BV3+BV4)</f>
         <v/>
       </c>
-      <c r="BW2" s="3">
-        <f>BW3/(BW3+BW4)</f>
-        <v/>
-      </c>
+      <c r="BW2" s="3" t="n"/>
       <c r="BX2" s="3">
         <f>BX3/(BX3+BX4)</f>
         <v/>
@@ -1290,12 +1290,15 @@
         <f>COUNTIF(BQ16:BQ75,"&gt;0")</f>
         <v/>
       </c>
-      <c r="BR3" s="3" t="n"/>
-      <c r="BS3" s="3">
-        <f>COUNTIF(BS16:BS75,"&gt;0")</f>
-        <v/>
-      </c>
-      <c r="BT3" s="3" t="n"/>
+      <c r="BR3" s="3">
+        <f>COUNTIF(BR16:BR75,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="BS3" s="3" t="n"/>
+      <c r="BT3" s="3">
+        <f>COUNTIF(BT16:BT75,"&gt;0")</f>
+        <v/>
+      </c>
       <c r="BU3" s="3">
         <f>COUNTIF(BU16:BU75,"&gt;0")</f>
         <v/>
@@ -1304,10 +1307,7 @@
         <f>COUNTIF(BV16:BV75,"&gt;0")</f>
         <v/>
       </c>
-      <c r="BW3" s="3">
-        <f>COUNTIF(BW16:BW75,"&gt;0")</f>
-        <v/>
-      </c>
+      <c r="BW3" s="3" t="n"/>
       <c r="BX3" s="3">
         <f>COUNTIF(BX16:BX75,"&gt;0")</f>
         <v/>
@@ -1592,12 +1592,15 @@
         <f>COUNTIF(BQ16:BQ75,"&lt;0")</f>
         <v/>
       </c>
-      <c r="BR4" s="3" t="n"/>
-      <c r="BS4" s="3">
-        <f>COUNTIF(BS16:BS75,"&lt;0")</f>
-        <v/>
-      </c>
-      <c r="BT4" s="3" t="n"/>
+      <c r="BR4" s="3">
+        <f>COUNTIF(BR16:BR75,"&lt;0")</f>
+        <v/>
+      </c>
+      <c r="BS4" s="3" t="n"/>
+      <c r="BT4" s="3">
+        <f>COUNTIF(BT16:BT75,"&lt;0")</f>
+        <v/>
+      </c>
       <c r="BU4" s="3">
         <f>COUNTIF(BU16:BU75,"&lt;0")</f>
         <v/>
@@ -1606,10 +1609,7 @@
         <f>COUNTIF(BV16:BV75,"&lt;0")</f>
         <v/>
       </c>
-      <c r="BW4" s="3">
-        <f>COUNTIF(BW16:BW75,"&lt;0")</f>
-        <v/>
-      </c>
+      <c r="BW4" s="3" t="n"/>
       <c r="BX4" s="3">
         <f>COUNTIF(BX16:BX75,"&lt;0")</f>
         <v/>
@@ -1894,12 +1894,15 @@
         <f>AVERAGE(BQ16:BQ75)</f>
         <v/>
       </c>
-      <c r="BR5" s="3" t="n"/>
-      <c r="BS5" s="3">
-        <f>AVERAGE(BS16:BS75)</f>
-        <v/>
-      </c>
-      <c r="BT5" s="3" t="n"/>
+      <c r="BR5" s="3">
+        <f>AVERAGE(BR16:BR75)</f>
+        <v/>
+      </c>
+      <c r="BS5" s="3" t="n"/>
+      <c r="BT5" s="3">
+        <f>AVERAGE(BT16:BT75)</f>
+        <v/>
+      </c>
       <c r="BU5" s="3">
         <f>AVERAGE(BU16:BU75)</f>
         <v/>
@@ -1908,10 +1911,7 @@
         <f>AVERAGE(BV16:BV75)</f>
         <v/>
       </c>
-      <c r="BW5" s="3">
-        <f>AVERAGE(BW16:BW75)</f>
-        <v/>
-      </c>
+      <c r="BW5" s="3" t="n"/>
       <c r="BX5" s="3">
         <f>AVERAGE(BX16:BX75)</f>
         <v/>
@@ -2196,12 +2196,15 @@
         <f>MAX(BQ16:BQ75)</f>
         <v/>
       </c>
-      <c r="BR6" s="3" t="n"/>
-      <c r="BS6" s="3">
-        <f>MAX(BS16:BS75)</f>
-        <v/>
-      </c>
-      <c r="BT6" s="3" t="n"/>
+      <c r="BR6" s="3">
+        <f>MAX(BR16:BR75)</f>
+        <v/>
+      </c>
+      <c r="BS6" s="3" t="n"/>
+      <c r="BT6" s="3">
+        <f>MAX(BT16:BT75)</f>
+        <v/>
+      </c>
       <c r="BU6" s="3">
         <f>MAX(BU16:BU75)</f>
         <v/>
@@ -2210,10 +2213,7 @@
         <f>MAX(BV16:BV75)</f>
         <v/>
       </c>
-      <c r="BW6" s="3">
-        <f>MAX(BW16:BW75)</f>
-        <v/>
-      </c>
+      <c r="BW6" s="3" t="n"/>
       <c r="BX6" s="3">
         <f>MAX(BX16:BX75)</f>
         <v/>
@@ -2498,12 +2498,15 @@
         <f>MIN(BQ16:BQ75)</f>
         <v/>
       </c>
-      <c r="BR7" s="3" t="n"/>
-      <c r="BS7" s="3">
-        <f>MIN(BS16:BS75)</f>
-        <v/>
-      </c>
-      <c r="BT7" s="3" t="n"/>
+      <c r="BR7" s="3">
+        <f>MIN(BR16:BR75)</f>
+        <v/>
+      </c>
+      <c r="BS7" s="3" t="n"/>
+      <c r="BT7" s="3">
+        <f>MIN(BT16:BT75)</f>
+        <v/>
+      </c>
       <c r="BU7" s="3">
         <f>MIN(BU16:BU75)</f>
         <v/>
@@ -2512,10 +2515,7 @@
         <f>MIN(BV16:BV75)</f>
         <v/>
       </c>
-      <c r="BW7" s="3">
-        <f>MIN(BW16:BW75)</f>
-        <v/>
-      </c>
+      <c r="BW7" s="3" t="n"/>
       <c r="BX7" s="3">
         <f>MIN(BX16:BX75)</f>
         <v/>
@@ -2800,12 +2800,15 @@
         <f>COUNT(BQ16:BQ75)</f>
         <v/>
       </c>
-      <c r="BR8" s="3" t="n"/>
-      <c r="BS8" s="3">
-        <f>COUNT(BS16:BS75)</f>
-        <v/>
-      </c>
-      <c r="BT8" s="3" t="n"/>
+      <c r="BR8" s="3">
+        <f>COUNT(BR16:BR75)</f>
+        <v/>
+      </c>
+      <c r="BS8" s="3" t="n"/>
+      <c r="BT8" s="3">
+        <f>COUNT(BT16:BT75)</f>
+        <v/>
+      </c>
       <c r="BU8" s="3">
         <f>COUNT(BU16:BU75)</f>
         <v/>
@@ -2814,10 +2817,7 @@
         <f>COUNT(BV16:BV75)</f>
         <v/>
       </c>
-      <c r="BW8" s="3">
-        <f>COUNT(BW16:BW75)</f>
-        <v/>
-      </c>
+      <c r="BW8" s="3" t="n"/>
       <c r="BX8" s="3">
         <f>COUNT(BX16:BX75)</f>
         <v/>
@@ -3102,12 +3102,15 @@
         <f>STDEV(BQ16:BQ75)</f>
         <v/>
       </c>
-      <c r="BR9" s="3" t="n"/>
-      <c r="BS9" s="3">
-        <f>STDEV(BS16:BS75)</f>
-        <v/>
-      </c>
-      <c r="BT9" s="3" t="n"/>
+      <c r="BR9" s="3">
+        <f>STDEV(BR16:BR75)</f>
+        <v/>
+      </c>
+      <c r="BS9" s="3" t="n"/>
+      <c r="BT9" s="3">
+        <f>STDEV(BT16:BT75)</f>
+        <v/>
+      </c>
       <c r="BU9" s="3">
         <f>STDEV(BU16:BU75)</f>
         <v/>
@@ -3116,10 +3119,7 @@
         <f>STDEV(BV16:BV75)</f>
         <v/>
       </c>
-      <c r="BW9" s="3">
-        <f>STDEV(BW16:BW75)</f>
-        <v/>
-      </c>
+      <c r="BW9" s="3" t="n"/>
       <c r="BX9" s="3">
         <f>STDEV(BX16:BX75)</f>
         <v/>
@@ -3404,12 +3404,15 @@
         <f>SUM(BQ16:BQ75)</f>
         <v/>
       </c>
-      <c r="BR10" s="3" t="n"/>
-      <c r="BS10" s="3">
-        <f>SUM(BS16:BS75)</f>
-        <v/>
-      </c>
-      <c r="BT10" s="3" t="n"/>
+      <c r="BR10" s="3">
+        <f>SUM(BR16:BR75)</f>
+        <v/>
+      </c>
+      <c r="BS10" s="3" t="n"/>
+      <c r="BT10" s="3">
+        <f>SUM(BT16:BT75)</f>
+        <v/>
+      </c>
       <c r="BU10" s="3">
         <f>SUM(BU16:BU75)</f>
         <v/>
@@ -3418,10 +3421,7 @@
         <f>SUM(BV16:BV75)</f>
         <v/>
       </c>
-      <c r="BW10" s="3">
-        <f>SUM(BW16:BW75)</f>
-        <v/>
-      </c>
+      <c r="BW10" s="3" t="n"/>
       <c r="BX10" s="3">
         <f>SUM(BX16:BX75)</f>
         <v/>
@@ -3932,28 +3932,28 @@
           <t>GDX回报</t>
         </is>
       </c>
-      <c r="BR15" s="4" t="inlineStr"/>
-      <c r="BS15" s="4" t="inlineStr">
+      <c r="BR15" s="4" t="inlineStr">
         <is>
           <t>XLC回报</t>
         </is>
       </c>
-      <c r="BT15" s="4" t="inlineStr"/>
-      <c r="BU15" s="4" t="inlineStr">
+      <c r="BS15" s="4" t="inlineStr"/>
+      <c r="BT15" s="4" t="inlineStr">
         <is>
           <t>VIX_Close</t>
         </is>
       </c>
-      <c r="BV15" s="4" t="inlineStr">
+      <c r="BU15" s="4" t="inlineStr">
         <is>
           <t>VIX回报</t>
         </is>
       </c>
-      <c r="BW15" s="4" t="inlineStr">
+      <c r="BV15" s="4" t="inlineStr">
         <is>
           <t>VIX_Chg%</t>
         </is>
       </c>
+      <c r="BW15" s="4" t="inlineStr"/>
       <c r="BX15" s="4" t="inlineStr">
         <is>
           <t>VIX&gt;0 且 该基金当日回报&lt;=-2%，买基金第二天</t>
@@ -4196,22 +4196,22 @@
         <f>IF(COUNT(BA16:BA17)=2,ROUND((BA16/BA17-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR16" s="5" t="inlineStr"/>
-      <c r="BS16" s="6">
+      <c r="BR16" s="6">
         <f>IF(COUNT(BH16:BH17)=2,ROUND((BH16/BH17-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT16" s="5" t="inlineStr"/>
-      <c r="BU16" s="5" t="n">
+      <c r="BS16" s="5" t="inlineStr"/>
+      <c r="BT16" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="BV16" s="6">
-        <f>IF(COUNT(BU16:BU17)=2,ROUND((BU16/BU17-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW16" s="6" t="n">
+      <c r="BU16" s="6">
+        <f>IF(COUNT(BT16:BT17)=2,ROUND((BT16/BT17-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV16" s="6" t="n">
         <v>4.0353</v>
       </c>
+      <c r="BW16" s="5" t="inlineStr"/>
       <c r="BX16" s="6" t="inlineStr"/>
       <c r="BY16" s="6" t="inlineStr"/>
       <c r="BZ16" s="6" t="inlineStr"/>
@@ -4428,24 +4428,24 @@
         <f>IF(COUNT(BA17:BA18)=2,ROUND((BA17/BA18-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR17" s="5" t="inlineStr"/>
-      <c r="BS17" s="6">
+      <c r="BR17" s="6">
         <f>IF(COUNT(BH17:BH18)=2,ROUND((BH17/BH18-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT17" s="5" t="inlineStr"/>
-      <c r="BU17" s="5" t="n">
+      <c r="BS17" s="5" t="inlineStr"/>
+      <c r="BT17" s="5" t="n">
         <v>15.86</v>
       </c>
-      <c r="BV17" s="6">
-        <f>IF(COUNT(BU17:BU18)=2,ROUND((BU17/BU18-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW17" s="6" t="n">
+      <c r="BU17" s="6">
+        <f>IF(COUNT(BT17:BT18)=2,ROUND((BT17/BT18-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV17" s="6" t="n">
         <v>-0.8129999999999999</v>
       </c>
+      <c r="BW17" s="5" t="inlineStr"/>
       <c r="BX17" s="6">
-        <f>IF(AND(BW17&gt;$BX$12,D17&lt;=$BX$13),D16,"")</f>
+        <f>IF(AND(BV17&gt;$BX$12,D17&lt;=$BX$13),D16,"")</f>
         <v/>
       </c>
       <c r="BY17" s="6">
@@ -4461,7 +4461,7 @@
         <v/>
       </c>
       <c r="CB17" s="6">
-        <f>IF(AND(BQ17&gt;$CB$12,BS17&lt;$CB$13),E16,"")</f>
+        <f>IF(AND(BQ17&gt;$CB$12,BR17&lt;$CB$13),E16,"")</f>
         <v/>
       </c>
       <c r="CC17" s="6">
@@ -4678,24 +4678,24 @@
         <f>IF(COUNT(BA18:BA19)=2,ROUND((BA18/BA19-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR18" s="5" t="inlineStr"/>
-      <c r="BS18" s="6">
+      <c r="BR18" s="6">
         <f>IF(COUNT(BH18:BH19)=2,ROUND((BH18/BH19-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT18" s="5" t="inlineStr"/>
-      <c r="BU18" s="5" t="n">
+      <c r="BS18" s="5" t="inlineStr"/>
+      <c r="BT18" s="5" t="n">
         <v>15.99</v>
       </c>
-      <c r="BV18" s="6">
-        <f>IF(COUNT(BU18:BU19)=2,ROUND((BU18/BU19-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW18" s="6" t="n">
+      <c r="BU18" s="6">
+        <f>IF(COUNT(BT18:BT19)=2,ROUND((BT18/BT19-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV18" s="6" t="n">
         <v>-6.4365</v>
       </c>
+      <c r="BW18" s="5" t="inlineStr"/>
       <c r="BX18" s="6">
-        <f>IF(AND(BW18&gt;$BX$12,D18&lt;=$BX$13),D17,"")</f>
+        <f>IF(AND(BV18&gt;$BX$12,D18&lt;=$BX$13),D17,"")</f>
         <v/>
       </c>
       <c r="BY18" s="6">
@@ -4711,7 +4711,7 @@
         <v/>
       </c>
       <c r="CB18" s="6">
-        <f>IF(AND(BQ18&gt;$CB$12,BS18&lt;$CB$13),E17,"")</f>
+        <f>IF(AND(BQ18&gt;$CB$12,BR18&lt;$CB$13),E17,"")</f>
         <v/>
       </c>
       <c r="CC18" s="6">
@@ -4928,24 +4928,24 @@
         <f>IF(COUNT(BA19:BA20)=2,ROUND((BA19/BA20-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR19" s="5" t="inlineStr"/>
-      <c r="BS19" s="6">
+      <c r="BR19" s="6">
         <f>IF(COUNT(BH19:BH20)=2,ROUND((BH19/BH20-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT19" s="5" t="inlineStr"/>
-      <c r="BU19" s="5" t="n">
+      <c r="BS19" s="5" t="inlineStr"/>
+      <c r="BT19" s="5" t="n">
         <v>17.09</v>
       </c>
-      <c r="BV19" s="6">
-        <f>IF(COUNT(BU19:BU20)=2,ROUND((BU19/BU20-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW19" s="6" t="n">
+      <c r="BU19" s="6">
+        <f>IF(COUNT(BT19:BT20)=2,ROUND((BT19/BT20-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV19" s="6" t="n">
         <v>-17.2798</v>
       </c>
+      <c r="BW19" s="5" t="inlineStr"/>
       <c r="BX19" s="6">
-        <f>IF(AND(BW19&gt;$BX$12,D19&lt;=$BX$13),D18,"")</f>
+        <f>IF(AND(BV19&gt;$BX$12,D19&lt;=$BX$13),D18,"")</f>
         <v/>
       </c>
       <c r="BY19" s="6">
@@ -4961,7 +4961,7 @@
         <v/>
       </c>
       <c r="CB19" s="6">
-        <f>IF(AND(BQ19&gt;$CB$12,BS19&lt;$CB$13),E18,"")</f>
+        <f>IF(AND(BQ19&gt;$CB$12,BR19&lt;$CB$13),E18,"")</f>
         <v/>
       </c>
       <c r="CC19" s="6">
@@ -5178,24 +5178,24 @@
         <f>IF(COUNT(BA20:BA21)=2,ROUND((BA20/BA21-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR20" s="5" t="inlineStr"/>
-      <c r="BS20" s="6">
+      <c r="BR20" s="6">
         <f>IF(COUNT(BH20:BH21)=2,ROUND((BH20/BH21-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT20" s="5" t="inlineStr"/>
-      <c r="BU20" s="5" t="n">
+      <c r="BS20" s="5" t="inlineStr"/>
+      <c r="BT20" s="5" t="n">
         <v>20.66</v>
       </c>
-      <c r="BV20" s="6">
-        <f>IF(COUNT(BU20:BU21)=2,ROUND((BU20/BU21-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW20" s="6" t="n">
+      <c r="BU20" s="6">
+        <f>IF(COUNT(BT20:BT21)=2,ROUND((BT20/BT21-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV20" s="6" t="n">
         <v>13.4541</v>
       </c>
+      <c r="BW20" s="5" t="inlineStr"/>
       <c r="BX20" s="6">
-        <f>IF(AND(BW20&gt;$BX$12,D20&lt;=$BX$13),D19,"")</f>
+        <f>IF(AND(BV20&gt;$BX$12,D20&lt;=$BX$13),D19,"")</f>
         <v/>
       </c>
       <c r="BY20" s="6">
@@ -5211,7 +5211,7 @@
         <v/>
       </c>
       <c r="CB20" s="6">
-        <f>IF(AND(BQ20&gt;$CB$12,BS20&lt;$CB$13),E19,"")</f>
+        <f>IF(AND(BQ20&gt;$CB$12,BR20&lt;$CB$13),E19,"")</f>
         <v/>
       </c>
       <c r="CC20" s="6">
@@ -5428,24 +5428,24 @@
         <f>IF(COUNT(BA21:BA22)=2,ROUND((BA21/BA22-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR21" s="5" t="inlineStr"/>
-      <c r="BS21" s="6">
+      <c r="BR21" s="6">
         <f>IF(COUNT(BH21:BH22)=2,ROUND((BH21/BH22-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT21" s="5" t="inlineStr"/>
-      <c r="BU21" s="5" t="n">
+      <c r="BS21" s="5" t="inlineStr"/>
+      <c r="BT21" s="5" t="n">
         <v>18.21</v>
       </c>
-      <c r="BV21" s="6">
-        <f>IF(COUNT(BU21:BU22)=2,ROUND((BU21/BU22-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW21" s="6" t="n">
+      <c r="BU21" s="6">
+        <f>IF(COUNT(BT21:BT22)=2,ROUND((BT21/BT22-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV21" s="6" t="n">
         <v>-2.4638</v>
       </c>
+      <c r="BW21" s="5" t="inlineStr"/>
       <c r="BX21" s="6">
-        <f>IF(AND(BW21&gt;$BX$12,D21&lt;=$BX$13),D20,"")</f>
+        <f>IF(AND(BV21&gt;$BX$12,D21&lt;=$BX$13),D20,"")</f>
         <v/>
       </c>
       <c r="BY21" s="6">
@@ -5461,7 +5461,7 @@
         <v/>
       </c>
       <c r="CB21" s="6">
-        <f>IF(AND(BQ21&gt;$CB$12,BS21&lt;$CB$13),E20,"")</f>
+        <f>IF(AND(BQ21&gt;$CB$12,BR21&lt;$CB$13),E20,"")</f>
         <v/>
       </c>
       <c r="CC21" s="6">
@@ -5678,24 +5678,24 @@
         <f>IF(COUNT(BA22:BA23)=2,ROUND((BA22/BA23-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR22" s="5" t="inlineStr"/>
-      <c r="BS22" s="6">
+      <c r="BR22" s="6">
         <f>IF(COUNT(BH22:BH23)=2,ROUND((BH22/BH23-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT22" s="5" t="inlineStr"/>
-      <c r="BU22" s="5" t="n">
+      <c r="BS22" s="5" t="inlineStr"/>
+      <c r="BT22" s="5" t="n">
         <v>18.67</v>
       </c>
-      <c r="BV22" s="6">
-        <f>IF(COUNT(BU22:BU23)=2,ROUND((BU22/BU23-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW22" s="6" t="n">
+      <c r="BU22" s="6">
+        <f>IF(COUNT(BT22:BT23)=2,ROUND((BT22/BT23-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV22" s="6" t="n">
         <v>0.4844</v>
       </c>
+      <c r="BW22" s="5" t="inlineStr"/>
       <c r="BX22" s="6">
-        <f>IF(AND(BW22&gt;$BX$12,D22&lt;=$BX$13),D21,"")</f>
+        <f>IF(AND(BV22&gt;$BX$12,D22&lt;=$BX$13),D21,"")</f>
         <v/>
       </c>
       <c r="BY22" s="6">
@@ -5711,7 +5711,7 @@
         <v/>
       </c>
       <c r="CB22" s="6">
-        <f>IF(AND(BQ22&gt;$CB$12,BS22&lt;$CB$13),E21,"")</f>
+        <f>IF(AND(BQ22&gt;$CB$12,BR22&lt;$CB$13),E21,"")</f>
         <v/>
       </c>
       <c r="CC22" s="6">
@@ -5928,24 +5928,24 @@
         <f>IF(COUNT(BA23:BA24)=2,ROUND((BA23/BA24-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR23" s="5" t="inlineStr"/>
-      <c r="BS23" s="6">
+      <c r="BR23" s="6">
         <f>IF(COUNT(BH23:BH24)=2,ROUND((BH23/BH24-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT23" s="5" t="inlineStr"/>
-      <c r="BU23" s="5" t="n">
+      <c r="BS23" s="5" t="inlineStr"/>
+      <c r="BT23" s="5" t="n">
         <v>18.58</v>
       </c>
-      <c r="BV23" s="6">
-        <f>IF(COUNT(BU23:BU24)=2,ROUND((BU23/BU24-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW23" s="6" t="n">
+      <c r="BU23" s="6">
+        <f>IF(COUNT(BT23:BT24)=2,ROUND((BT23/BT24-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV23" s="6" t="n">
         <v>-0.6417</v>
       </c>
+      <c r="BW23" s="5" t="inlineStr"/>
       <c r="BX23" s="6">
-        <f>IF(AND(BW23&gt;$BX$12,D23&lt;=$BX$13),D22,"")</f>
+        <f>IF(AND(BV23&gt;$BX$12,D23&lt;=$BX$13),D22,"")</f>
         <v/>
       </c>
       <c r="BY23" s="6">
@@ -5961,7 +5961,7 @@
         <v/>
       </c>
       <c r="CB23" s="6">
-        <f>IF(AND(BQ23&gt;$CB$12,BS23&lt;$CB$13),E22,"")</f>
+        <f>IF(AND(BQ23&gt;$CB$12,BR23&lt;$CB$13),E22,"")</f>
         <v/>
       </c>
       <c r="CC23" s="6">
@@ -6178,24 +6178,24 @@
         <f>IF(COUNT(BA24:BA25)=2,ROUND((BA24/BA25-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR24" s="5" t="inlineStr"/>
-      <c r="BS24" s="6">
+      <c r="BR24" s="6">
         <f>IF(COUNT(BH24:BH25)=2,ROUND((BH24/BH25-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT24" s="5" t="inlineStr"/>
-      <c r="BU24" s="5" t="n">
+      <c r="BS24" s="5" t="inlineStr"/>
+      <c r="BT24" s="5" t="n">
         <v>18.7</v>
       </c>
-      <c r="BV24" s="6">
-        <f>IF(COUNT(BU24:BU25)=2,ROUND((BU24/BU25-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW24" s="6" t="n">
+      <c r="BU24" s="6">
+        <f>IF(COUNT(BT24:BT25)=2,ROUND((BT24/BT25-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV24" s="6" t="n">
         <v>12.3798</v>
       </c>
+      <c r="BW24" s="5" t="inlineStr"/>
       <c r="BX24" s="6">
-        <f>IF(AND(BW24&gt;$BX$12,D24&lt;=$BX$13),D23,"")</f>
+        <f>IF(AND(BV24&gt;$BX$12,D24&lt;=$BX$13),D23,"")</f>
         <v/>
       </c>
       <c r="BY24" s="6">
@@ -6211,7 +6211,7 @@
         <v/>
       </c>
       <c r="CB24" s="6">
-        <f>IF(AND(BQ24&gt;$CB$12,BS24&lt;$CB$13),E23,"")</f>
+        <f>IF(AND(BQ24&gt;$CB$12,BR24&lt;$CB$13),E23,"")</f>
         <v/>
       </c>
       <c r="CC24" s="6">
@@ -6428,24 +6428,24 @@
         <f>IF(COUNT(BA25:BA26)=2,ROUND((BA25/BA26-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR25" s="5" t="inlineStr"/>
-      <c r="BS25" s="6">
+      <c r="BR25" s="6">
         <f>IF(COUNT(BH25:BH26)=2,ROUND((BH25/BH26-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT25" s="5" t="inlineStr"/>
-      <c r="BU25" s="5" t="n">
+      <c r="BS25" s="5" t="inlineStr"/>
+      <c r="BT25" s="5" t="n">
         <v>16.64</v>
       </c>
-      <c r="BV25" s="6">
-        <f>IF(COUNT(BU25:BU26)=2,ROUND((BU25/BU26-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW25" s="6" t="n">
+      <c r="BU25" s="6">
+        <f>IF(COUNT(BT25:BT26)=2,ROUND((BT25/BT26-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV25" s="6" t="n">
         <v>-2.4047</v>
       </c>
+      <c r="BW25" s="5" t="inlineStr"/>
       <c r="BX25" s="6">
-        <f>IF(AND(BW25&gt;$BX$12,D25&lt;=$BX$13),D24,"")</f>
+        <f>IF(AND(BV25&gt;$BX$12,D25&lt;=$BX$13),D24,"")</f>
         <v/>
       </c>
       <c r="BY25" s="6">
@@ -6461,7 +6461,7 @@
         <v/>
       </c>
       <c r="CB25" s="6">
-        <f>IF(AND(BQ25&gt;$CB$12,BS25&lt;$CB$13),E24,"")</f>
+        <f>IF(AND(BQ25&gt;$CB$12,BR25&lt;$CB$13),E24,"")</f>
         <v/>
       </c>
       <c r="CC25" s="6">
@@ -6678,24 +6678,24 @@
         <f>IF(COUNT(BA26:BA27)=2,ROUND((BA26/BA27-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR26" s="5" t="inlineStr"/>
-      <c r="BS26" s="6">
+      <c r="BR26" s="6">
         <f>IF(COUNT(BH26:BH27)=2,ROUND((BH26/BH27-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT26" s="5" t="inlineStr"/>
-      <c r="BU26" s="5" t="n">
+      <c r="BS26" s="5" t="inlineStr"/>
+      <c r="BT26" s="5" t="n">
         <v>17.05</v>
       </c>
-      <c r="BV26" s="6">
-        <f>IF(COUNT(BU26:BU27)=2,ROUND((BU26/BU27-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW26" s="6" t="n">
+      <c r="BU26" s="6">
+        <f>IF(COUNT(BT26:BT27)=2,ROUND((BT26/BT27-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV26" s="6" t="n">
         <v>-8.5791</v>
       </c>
+      <c r="BW26" s="5" t="inlineStr"/>
       <c r="BX26" s="6">
-        <f>IF(AND(BW26&gt;$BX$12,D26&lt;=$BX$13),D25,"")</f>
+        <f>IF(AND(BV26&gt;$BX$12,D26&lt;=$BX$13),D25,"")</f>
         <v/>
       </c>
       <c r="BY26" s="6">
@@ -6711,7 +6711,7 @@
         <v/>
       </c>
       <c r="CB26" s="6">
-        <f>IF(AND(BQ26&gt;$CB$12,BS26&lt;$CB$13),E25,"")</f>
+        <f>IF(AND(BQ26&gt;$CB$12,BR26&lt;$CB$13),E25,"")</f>
         <v/>
       </c>
       <c r="CC26" s="6">
@@ -6928,24 +6928,24 @@
         <f>IF(COUNT(BA27:BA28)=2,ROUND((BA27/BA28-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR27" s="5" t="inlineStr"/>
-      <c r="BS27" s="6">
+      <c r="BR27" s="6">
         <f>IF(COUNT(BH27:BH28)=2,ROUND((BH27/BH28-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT27" s="5" t="inlineStr"/>
-      <c r="BU27" s="5" t="n">
+      <c r="BS27" s="5" t="inlineStr"/>
+      <c r="BT27" s="5" t="n">
         <v>18.65</v>
       </c>
-      <c r="BV27" s="6">
-        <f>IF(COUNT(BU27:BU28)=2,ROUND((BU27/BU28-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW27" s="6" t="n">
+      <c r="BU27" s="6">
+        <f>IF(COUNT(BT27:BT28)=2,ROUND((BT27/BT28-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV27" s="6" t="n">
         <v>-0.6393</v>
       </c>
+      <c r="BW27" s="5" t="inlineStr"/>
       <c r="BX27" s="6">
-        <f>IF(AND(BW27&gt;$BX$12,D27&lt;=$BX$13),D26,"")</f>
+        <f>IF(AND(BV27&gt;$BX$12,D27&lt;=$BX$13),D26,"")</f>
         <v/>
       </c>
       <c r="BY27" s="6">
@@ -6961,7 +6961,7 @@
         <v/>
       </c>
       <c r="CB27" s="6">
-        <f>IF(AND(BQ27&gt;$CB$12,BS27&lt;$CB$13),E26,"")</f>
+        <f>IF(AND(BQ27&gt;$CB$12,BR27&lt;$CB$13),E26,"")</f>
         <v/>
       </c>
       <c r="CC27" s="6">
@@ -7178,24 +7178,24 @@
         <f>IF(COUNT(BA28:BA29)=2,ROUND((BA28/BA29-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR28" s="5" t="inlineStr"/>
-      <c r="BS28" s="6">
+      <c r="BR28" s="6">
         <f>IF(COUNT(BH28:BH29)=2,ROUND((BH28/BH29-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT28" s="5" t="inlineStr"/>
-      <c r="BU28" s="5" t="n">
+      <c r="BS28" s="5" t="inlineStr"/>
+      <c r="BT28" s="5" t="n">
         <v>18.77</v>
       </c>
-      <c r="BV28" s="6">
-        <f>IF(COUNT(BU28:BU29)=2,ROUND((BU28/BU29-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW28" s="6" t="n">
+      <c r="BU28" s="6">
+        <f>IF(COUNT(BT28:BT29)=2,ROUND((BT28/BT29-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV28" s="6" t="n">
         <v>12.1937</v>
       </c>
+      <c r="BW28" s="5" t="inlineStr"/>
       <c r="BX28" s="6">
-        <f>IF(AND(BW28&gt;$BX$12,D28&lt;=$BX$13),D27,"")</f>
+        <f>IF(AND(BV28&gt;$BX$12,D28&lt;=$BX$13),D27,"")</f>
         <v/>
       </c>
       <c r="BY28" s="6">
@@ -7211,7 +7211,7 @@
         <v/>
       </c>
       <c r="CB28" s="6">
-        <f>IF(AND(BQ28&gt;$CB$12,BS28&lt;$CB$13),E27,"")</f>
+        <f>IF(AND(BQ28&gt;$CB$12,BR28&lt;$CB$13),E27,"")</f>
         <v/>
       </c>
       <c r="CC28" s="6">
@@ -7428,24 +7428,24 @@
         <f>IF(COUNT(BA29:BA30)=2,ROUND((BA29/BA30-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR29" s="5" t="inlineStr"/>
-      <c r="BS29" s="6">
+      <c r="BR29" s="6">
         <f>IF(COUNT(BH29:BH30)=2,ROUND((BH29/BH30-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT29" s="5" t="inlineStr"/>
-      <c r="BU29" s="5" t="n">
+      <c r="BS29" s="5" t="inlineStr"/>
+      <c r="BT29" s="5" t="n">
         <v>16.73</v>
       </c>
-      <c r="BV29" s="6">
-        <f>IF(COUNT(BU29:BU30)=2,ROUND((BU29/BU30-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW29" s="6" t="n">
+      <c r="BU29" s="6">
+        <f>IF(COUNT(BT29:BT30)=2,ROUND((BT29/BT30-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV29" s="6" t="n">
         <v>6.7645</v>
       </c>
+      <c r="BW29" s="5" t="inlineStr"/>
       <c r="BX29" s="6">
-        <f>IF(AND(BW29&gt;$BX$12,D29&lt;=$BX$13),D28,"")</f>
+        <f>IF(AND(BV29&gt;$BX$12,D29&lt;=$BX$13),D28,"")</f>
         <v/>
       </c>
       <c r="BY29" s="6">
@@ -7461,7 +7461,7 @@
         <v/>
       </c>
       <c r="CB29" s="6">
-        <f>IF(AND(BQ29&gt;$CB$12,BS29&lt;$CB$13),E28,"")</f>
+        <f>IF(AND(BQ29&gt;$CB$12,BR29&lt;$CB$13),E28,"")</f>
         <v/>
       </c>
       <c r="CC29" s="6">
@@ -7678,24 +7678,24 @@
         <f>IF(COUNT(BA30:BA31)=2,ROUND((BA30/BA31-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR30" s="5" t="inlineStr"/>
-      <c r="BS30" s="6">
+      <c r="BR30" s="6">
         <f>IF(COUNT(BH30:BH31)=2,ROUND((BH30/BH31-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT30" s="5" t="inlineStr"/>
-      <c r="BU30" s="5" t="n">
+      <c r="BS30" s="5" t="inlineStr"/>
+      <c r="BT30" s="5" t="n">
         <v>15.67</v>
       </c>
-      <c r="BV30" s="6">
-        <f>IF(COUNT(BU30:BU31)=2,ROUND((BU30/BU31-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW30" s="6" t="n">
+      <c r="BU30" s="6">
+        <f>IF(COUNT(BT30:BT31)=2,ROUND((BT30/BT31-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV30" s="6" t="n">
         <v>-5.0303</v>
       </c>
+      <c r="BW30" s="5" t="inlineStr"/>
       <c r="BX30" s="6">
-        <f>IF(AND(BW30&gt;$BX$12,D30&lt;=$BX$13),D29,"")</f>
+        <f>IF(AND(BV30&gt;$BX$12,D30&lt;=$BX$13),D29,"")</f>
         <v/>
       </c>
       <c r="BY30" s="6">
@@ -7711,7 +7711,7 @@
         <v/>
       </c>
       <c r="CB30" s="6">
-        <f>IF(AND(BQ30&gt;$CB$12,BS30&lt;$CB$13),E29,"")</f>
+        <f>IF(AND(BQ30&gt;$CB$12,BR30&lt;$CB$13),E29,"")</f>
         <v/>
       </c>
       <c r="CC30" s="6">
@@ -7928,24 +7928,24 @@
         <f>IF(COUNT(BA31:BA32)=2,ROUND((BA31/BA32-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR31" s="5" t="inlineStr"/>
-      <c r="BS31" s="6">
+      <c r="BR31" s="6">
         <f>IF(COUNT(BH31:BH32)=2,ROUND((BH31/BH32-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT31" s="5" t="inlineStr"/>
-      <c r="BU31" s="5" t="n">
+      <c r="BS31" s="5" t="inlineStr"/>
+      <c r="BT31" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="BV31" s="6">
-        <f>IF(COUNT(BU31:BU32)=2,ROUND((BU31/BU32-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW31" s="6" t="n">
+      <c r="BU31" s="6">
+        <f>IF(COUNT(BT31:BT32)=2,ROUND((BT31/BT32-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV31" s="6" t="n">
         <v>-3.8462</v>
       </c>
+      <c r="BW31" s="5" t="inlineStr"/>
       <c r="BX31" s="6">
-        <f>IF(AND(BW31&gt;$BX$12,D31&lt;=$BX$13),D30,"")</f>
+        <f>IF(AND(BV31&gt;$BX$12,D31&lt;=$BX$13),D30,"")</f>
         <v/>
       </c>
       <c r="BY31" s="6">
@@ -7961,7 +7961,7 @@
         <v/>
       </c>
       <c r="CB31" s="6">
-        <f>IF(AND(BQ31&gt;$CB$12,BS31&lt;$CB$13),E30,"")</f>
+        <f>IF(AND(BQ31&gt;$CB$12,BR31&lt;$CB$13),E30,"")</f>
         <v/>
       </c>
       <c r="CC31" s="6">
@@ -8178,24 +8178,24 @@
         <f>IF(COUNT(BA32:BA33)=2,ROUND((BA32/BA33-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR32" s="5" t="inlineStr"/>
-      <c r="BS32" s="6">
+      <c r="BR32" s="6">
         <f>IF(COUNT(BH32:BH33)=2,ROUND((BH32/BH33-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT32" s="5" t="inlineStr"/>
-      <c r="BU32" s="5" t="n">
+      <c r="BS32" s="5" t="inlineStr"/>
+      <c r="BT32" s="5" t="n">
         <v>17.16</v>
       </c>
-      <c r="BV32" s="6">
-        <f>IF(COUNT(BU32:BU33)=2,ROUND((BU32/BU33-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW32" s="6" t="n">
+      <c r="BU32" s="6">
+        <f>IF(COUNT(BT32:BT33)=2,ROUND((BT32/BT33-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV32" s="6" t="n">
         <v>14.1717</v>
       </c>
+      <c r="BW32" s="5" t="inlineStr"/>
       <c r="BX32" s="6">
-        <f>IF(AND(BW32&gt;$BX$12,D32&lt;=$BX$13),D31,"")</f>
+        <f>IF(AND(BV32&gt;$BX$12,D32&lt;=$BX$13),D31,"")</f>
         <v/>
       </c>
       <c r="BY32" s="6">
@@ -8211,7 +8211,7 @@
         <v/>
       </c>
       <c r="CB32" s="6">
-        <f>IF(AND(BQ32&gt;$CB$12,BS32&lt;$CB$13),E31,"")</f>
+        <f>IF(AND(BQ32&gt;$CB$12,BR32&lt;$CB$13),E31,"")</f>
         <v/>
       </c>
       <c r="CC32" s="6">
@@ -8428,24 +8428,24 @@
         <f>IF(COUNT(BA33:BA34)=2,ROUND((BA33/BA34-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR33" s="5" t="inlineStr"/>
-      <c r="BS33" s="6">
+      <c r="BR33" s="6">
         <f>IF(COUNT(BH33:BH34)=2,ROUND((BH33/BH34-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT33" s="5" t="inlineStr"/>
-      <c r="BU33" s="5" t="n">
+      <c r="BS33" s="5" t="inlineStr"/>
+      <c r="BT33" s="5" t="n">
         <v>15.03</v>
       </c>
-      <c r="BV33" s="6">
-        <f>IF(COUNT(BU33:BU34)=2,ROUND((BU33/BU34-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW33" s="6" t="n">
+      <c r="BU33" s="6">
+        <f>IF(COUNT(BT33:BT34)=2,ROUND((BT33/BT34-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV33" s="6" t="n">
         <v>-5.1136</v>
       </c>
+      <c r="BW33" s="5" t="inlineStr"/>
       <c r="BX33" s="6">
-        <f>IF(AND(BW33&gt;$BX$12,D33&lt;=$BX$13),D32,"")</f>
+        <f>IF(AND(BV33&gt;$BX$12,D33&lt;=$BX$13),D32,"")</f>
         <v/>
       </c>
       <c r="BY33" s="6">
@@ -8461,7 +8461,7 @@
         <v/>
       </c>
       <c r="CB33" s="6">
-        <f>IF(AND(BQ33&gt;$CB$12,BS33&lt;$CB$13),E32,"")</f>
+        <f>IF(AND(BQ33&gt;$CB$12,BR33&lt;$CB$13),E32,"")</f>
         <v/>
       </c>
       <c r="CC33" s="6">
@@ -8678,24 +8678,24 @@
         <f>IF(COUNT(BA34:BA35)=2,ROUND((BA34/BA35-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR34" s="5" t="inlineStr"/>
-      <c r="BS34" s="6">
+      <c r="BR34" s="6">
         <f>IF(COUNT(BH34:BH35)=2,ROUND((BH34/BH35-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT34" s="5" t="inlineStr"/>
-      <c r="BU34" s="5" t="n">
+      <c r="BS34" s="5" t="inlineStr"/>
+      <c r="BT34" s="5" t="n">
         <v>15.84</v>
       </c>
-      <c r="BV34" s="6">
-        <f>IF(COUNT(BU34:BU35)=2,ROUND((BU34/BU35-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW34" s="6" t="n">
+      <c r="BU34" s="6">
+        <f>IF(COUNT(BT34:BT35)=2,ROUND((BT34/BT35-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV34" s="6" t="n">
         <v>-6.2722</v>
       </c>
+      <c r="BW34" s="5" t="inlineStr"/>
       <c r="BX34" s="6">
-        <f>IF(AND(BW34&gt;$BX$12,D34&lt;=$BX$13),D33,"")</f>
+        <f>IF(AND(BV34&gt;$BX$12,D34&lt;=$BX$13),D33,"")</f>
         <v/>
       </c>
       <c r="BY34" s="6">
@@ -8711,7 +8711,7 @@
         <v/>
       </c>
       <c r="CB34" s="6">
-        <f>IF(AND(BQ34&gt;$CB$12,BS34&lt;$CB$13),E33,"")</f>
+        <f>IF(AND(BQ34&gt;$CB$12,BR34&lt;$CB$13),E33,"")</f>
         <v/>
       </c>
       <c r="CC34" s="6">
@@ -8928,24 +8928,24 @@
         <f>IF(COUNT(BA35:BA36)=2,ROUND((BA35/BA36-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR35" s="5" t="inlineStr"/>
-      <c r="BS35" s="6">
+      <c r="BR35" s="6">
         <f>IF(COUNT(BH35:BH36)=2,ROUND((BH35/BH36-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT35" s="5" t="inlineStr"/>
-      <c r="BU35" s="5" t="n">
+      <c r="BS35" s="5" t="inlineStr"/>
+      <c r="BT35" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="BV35" s="6">
-        <f>IF(COUNT(BU35:BU36)=2,ROUND((BU35/BU36-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW35" s="6" t="n">
+      <c r="BU35" s="6">
+        <f>IF(COUNT(BT35:BT36)=2,ROUND((BT35/BT36-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV35" s="6" t="n">
         <v>4.7737</v>
       </c>
+      <c r="BW35" s="5" t="inlineStr"/>
       <c r="BX35" s="6">
-        <f>IF(AND(BW35&gt;$BX$12,D35&lt;=$BX$13),D34,"")</f>
+        <f>IF(AND(BV35&gt;$BX$12,D35&lt;=$BX$13),D34,"")</f>
         <v/>
       </c>
       <c r="BY35" s="6">
@@ -8961,7 +8961,7 @@
         <v/>
       </c>
       <c r="CB35" s="6">
-        <f>IF(AND(BQ35&gt;$CB$12,BS35&lt;$CB$13),E34,"")</f>
+        <f>IF(AND(BQ35&gt;$CB$12,BR35&lt;$CB$13),E34,"")</f>
         <v/>
       </c>
       <c r="CC35" s="6">
@@ -9178,24 +9178,24 @@
         <f>IF(COUNT(BA36:BA37)=2,ROUND((BA36/BA37-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR36" s="5" t="inlineStr"/>
-      <c r="BS36" s="6">
+      <c r="BR36" s="6">
         <f>IF(COUNT(BH36:BH37)=2,ROUND((BH36/BH37-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT36" s="5" t="inlineStr"/>
-      <c r="BU36" s="5" t="n">
+      <c r="BS36" s="5" t="inlineStr"/>
+      <c r="BT36" s="5" t="n">
         <v>16.13</v>
       </c>
-      <c r="BV36" s="6">
-        <f>IF(COUNT(BU36:BU37)=2,ROUND((BU36/BU37-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW36" s="6" t="n">
+      <c r="BU36" s="6">
+        <f>IF(COUNT(BT36:BT37)=2,ROUND((BT36/BT37-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV36" s="6" t="n">
         <v>3.5967</v>
       </c>
+      <c r="BW36" s="5" t="inlineStr"/>
       <c r="BX36" s="6">
-        <f>IF(AND(BW36&gt;$BX$12,D36&lt;=$BX$13),D35,"")</f>
+        <f>IF(AND(BV36&gt;$BX$12,D36&lt;=$BX$13),D35,"")</f>
         <v/>
       </c>
       <c r="BY36" s="6">
@@ -9211,7 +9211,7 @@
         <v/>
       </c>
       <c r="CB36" s="6">
-        <f>IF(AND(BQ36&gt;$CB$12,BS36&lt;$CB$13),E35,"")</f>
+        <f>IF(AND(BQ36&gt;$CB$12,BR36&lt;$CB$13),E35,"")</f>
         <v/>
       </c>
       <c r="CC36" s="6">
@@ -9428,24 +9428,24 @@
         <f>IF(COUNT(BA37:BA38)=2,ROUND((BA37/BA38-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR37" s="5" t="inlineStr"/>
-      <c r="BS37" s="6">
+      <c r="BR37" s="6">
         <f>IF(COUNT(BH37:BH38)=2,ROUND((BH37/BH38-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT37" s="5" t="inlineStr"/>
-      <c r="BU37" s="5" t="n">
+      <c r="BS37" s="5" t="inlineStr"/>
+      <c r="BT37" s="5" t="n">
         <v>15.57</v>
       </c>
-      <c r="BV37" s="6">
-        <f>IF(COUNT(BU37:BU38)=2,ROUND((BU37/BU38-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW37" s="6" t="n">
+      <c r="BU37" s="6">
+        <f>IF(COUNT(BT37:BT38)=2,ROUND((BT37/BT38-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV37" s="6" t="n">
         <v>-3.5913</v>
       </c>
+      <c r="BW37" s="5" t="inlineStr"/>
       <c r="BX37" s="6">
-        <f>IF(AND(BW37&gt;$BX$12,D37&lt;=$BX$13),D36,"")</f>
+        <f>IF(AND(BV37&gt;$BX$12,D37&lt;=$BX$13),D36,"")</f>
         <v/>
       </c>
       <c r="BY37" s="6">
@@ -9461,7 +9461,7 @@
         <v/>
       </c>
       <c r="CB37" s="6">
-        <f>IF(AND(BQ37&gt;$CB$12,BS37&lt;$CB$13),E36,"")</f>
+        <f>IF(AND(BQ37&gt;$CB$12,BR37&lt;$CB$13),E36,"")</f>
         <v/>
       </c>
       <c r="CC37" s="6">
@@ -9678,24 +9678,24 @@
         <f>IF(COUNT(BA38:BA39)=2,ROUND((BA38/BA39-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR38" s="5" t="inlineStr"/>
-      <c r="BS38" s="6">
+      <c r="BR38" s="6">
         <f>IF(COUNT(BH38:BH39)=2,ROUND((BH38/BH39-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT38" s="5" t="inlineStr"/>
-      <c r="BU38" s="5" t="n">
+      <c r="BS38" s="5" t="inlineStr"/>
+      <c r="BT38" s="5" t="n">
         <v>16.15</v>
       </c>
-      <c r="BV38" s="6">
-        <f>IF(COUNT(BU38:BU39)=2,ROUND((BU38/BU39-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW38" s="6" t="n">
+      <c r="BU38" s="6">
+        <f>IF(COUNT(BT38:BT39)=2,ROUND((BT38/BT39-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV38" s="6" t="n">
         <v>-2.6522</v>
       </c>
+      <c r="BW38" s="5" t="inlineStr"/>
       <c r="BX38" s="6">
-        <f>IF(AND(BW38&gt;$BX$12,D38&lt;=$BX$13),D37,"")</f>
+        <f>IF(AND(BV38&gt;$BX$12,D38&lt;=$BX$13),D37,"")</f>
         <v/>
       </c>
       <c r="BY38" s="6">
@@ -9711,7 +9711,7 @@
         <v/>
       </c>
       <c r="CB38" s="6">
-        <f>IF(AND(BQ38&gt;$CB$12,BS38&lt;$CB$13),E37,"")</f>
+        <f>IF(AND(BQ38&gt;$CB$12,BR38&lt;$CB$13),E37,"")</f>
         <v/>
       </c>
       <c r="CC38" s="6">
@@ -9928,24 +9928,24 @@
         <f>IF(COUNT(BA39:BA40)=2,ROUND((BA39/BA40-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR39" s="5" t="inlineStr"/>
-      <c r="BS39" s="6">
+      <c r="BR39" s="6">
         <f>IF(COUNT(BH39:BH40)=2,ROUND((BH39/BH40-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT39" s="5" t="inlineStr"/>
-      <c r="BU39" s="5" t="n">
+      <c r="BS39" s="5" t="inlineStr"/>
+      <c r="BT39" s="5" t="n">
         <v>16.59</v>
       </c>
-      <c r="BV39" s="6">
-        <f>IF(COUNT(BU39:BU40)=2,ROUND((BU39/BU40-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW39" s="6" t="n">
+      <c r="BU39" s="6">
+        <f>IF(COUNT(BT39:BT40)=2,ROUND((BT39/BT40-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV39" s="6" t="n">
         <v>0.8511</v>
       </c>
+      <c r="BW39" s="5" t="inlineStr"/>
       <c r="BX39" s="6">
-        <f>IF(AND(BW39&gt;$BX$12,D39&lt;=$BX$13),D38,"")</f>
+        <f>IF(AND(BV39&gt;$BX$12,D39&lt;=$BX$13),D38,"")</f>
         <v/>
       </c>
       <c r="BY39" s="6">
@@ -9961,7 +9961,7 @@
         <v/>
       </c>
       <c r="CB39" s="6">
-        <f>IF(AND(BQ39&gt;$CB$12,BS39&lt;$CB$13),E38,"")</f>
+        <f>IF(AND(BQ39&gt;$CB$12,BR39&lt;$CB$13),E38,"")</f>
         <v/>
       </c>
       <c r="CC39" s="6">
@@ -10178,24 +10178,24 @@
         <f>IF(COUNT(BA40:BA41)=2,ROUND((BA40/BA41-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR40" s="5" t="inlineStr"/>
-      <c r="BS40" s="6">
+      <c r="BR40" s="6">
         <f>IF(COUNT(BH40:BH41)=2,ROUND((BH40/BH41-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT40" s="5" t="inlineStr"/>
-      <c r="BU40" s="5" t="n">
+      <c r="BS40" s="5" t="inlineStr"/>
+      <c r="BT40" s="5" t="n">
         <v>16.45</v>
       </c>
-      <c r="BV40" s="6">
-        <f>IF(COUNT(BU40:BU41)=2,ROUND((BU40/BU41-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW40" s="6" t="n">
+      <c r="BU40" s="6">
+        <f>IF(COUNT(BT40:BT41)=2,ROUND((BT40/BT41-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV40" s="6" t="n">
         <v>-6.7989</v>
       </c>
+      <c r="BW40" s="5" t="inlineStr"/>
       <c r="BX40" s="6">
-        <f>IF(AND(BW40&gt;$BX$12,D40&lt;=$BX$13),D39,"")</f>
+        <f>IF(AND(BV40&gt;$BX$12,D40&lt;=$BX$13),D39,"")</f>
         <v/>
       </c>
       <c r="BY40" s="6">
@@ -10211,7 +10211,7 @@
         <v/>
       </c>
       <c r="CB40" s="6">
-        <f>IF(AND(BQ40&gt;$CB$12,BS40&lt;$CB$13),E39,"")</f>
+        <f>IF(AND(BQ40&gt;$CB$12,BR40&lt;$CB$13),E39,"")</f>
         <v/>
       </c>
       <c r="CC40" s="6">
@@ -10428,24 +10428,24 @@
         <f>IF(COUNT(BA41:BA42)=2,ROUND((BA41/BA42-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR41" s="5" t="inlineStr"/>
-      <c r="BS41" s="6">
+      <c r="BR41" s="6">
         <f>IF(COUNT(BH41:BH42)=2,ROUND((BH41/BH42-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT41" s="5" t="inlineStr"/>
-      <c r="BU41" s="5" t="n">
+      <c r="BS41" s="5" t="inlineStr"/>
+      <c r="BT41" s="5" t="n">
         <v>17.65</v>
       </c>
-      <c r="BV41" s="6">
-        <f>IF(COUNT(BU41:BU42)=2,ROUND((BU41/BU42-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW41" s="6" t="n">
+      <c r="BU41" s="6">
+        <f>IF(COUNT(BT41:BT42)=2,ROUND((BT41/BT42-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV41" s="6" t="n">
         <v>-4.1282</v>
       </c>
+      <c r="BW41" s="5" t="inlineStr"/>
       <c r="BX41" s="6">
-        <f>IF(AND(BW41&gt;$BX$12,D41&lt;=$BX$13),D40,"")</f>
+        <f>IF(AND(BV41&gt;$BX$12,D41&lt;=$BX$13),D40,"")</f>
         <v/>
       </c>
       <c r="BY41" s="6">
@@ -10461,7 +10461,7 @@
         <v/>
       </c>
       <c r="CB41" s="6">
-        <f>IF(AND(BQ41&gt;$CB$12,BS41&lt;$CB$13),E40,"")</f>
+        <f>IF(AND(BQ41&gt;$CB$12,BR41&lt;$CB$13),E40,"")</f>
         <v/>
       </c>
       <c r="CC41" s="6">
@@ -10678,24 +10678,24 @@
         <f>IF(COUNT(BA42:BA43)=2,ROUND((BA42/BA43-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR42" s="5" t="inlineStr"/>
-      <c r="BS42" s="6">
+      <c r="BR42" s="6">
         <f>IF(COUNT(BH42:BH43)=2,ROUND((BH42/BH43-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT42" s="5" t="inlineStr"/>
-      <c r="BU42" s="5" t="n">
+      <c r="BS42" s="5" t="inlineStr"/>
+      <c r="BT42" s="5" t="n">
         <v>18.41</v>
       </c>
-      <c r="BV42" s="6">
-        <f>IF(COUNT(BU42:BU43)=2,ROUND((BU42/BU43-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW42" s="6" t="n">
+      <c r="BU42" s="6">
+        <f>IF(COUNT(BT42:BT43)=2,ROUND((BT42/BT43-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV42" s="6" t="n">
         <v>-2.541</v>
       </c>
+      <c r="BW42" s="5" t="inlineStr"/>
       <c r="BX42" s="6">
-        <f>IF(AND(BW42&gt;$BX$12,D42&lt;=$BX$13),D41,"")</f>
+        <f>IF(AND(BV42&gt;$BX$12,D42&lt;=$BX$13),D41,"")</f>
         <v/>
       </c>
       <c r="BY42" s="6">
@@ -10711,7 +10711,7 @@
         <v/>
       </c>
       <c r="CB42" s="6">
-        <f>IF(AND(BQ42&gt;$CB$12,BS42&lt;$CB$13),E41,"")</f>
+        <f>IF(AND(BQ42&gt;$CB$12,BR42&lt;$CB$13),E41,"")</f>
         <v/>
       </c>
       <c r="CC42" s="6">
@@ -10928,24 +10928,24 @@
         <f>IF(COUNT(BA43:BA44)=2,ROUND((BA43/BA44-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR43" s="5" t="inlineStr"/>
-      <c r="BS43" s="6">
+      <c r="BR43" s="6">
         <f>IF(COUNT(BH43:BH44)=2,ROUND((BH43/BH44-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT43" s="5" t="inlineStr"/>
-      <c r="BU43" s="5" t="n">
+      <c r="BS43" s="5" t="inlineStr"/>
+      <c r="BT43" s="5" t="n">
         <v>18.89</v>
       </c>
-      <c r="BV43" s="6">
-        <f>IF(COUNT(BU43:BU44)=2,ROUND((BU43/BU44-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW43" s="6" t="n">
+      <c r="BU43" s="6">
+        <f>IF(COUNT(BT43:BT44)=2,ROUND((BT43/BT44-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV43" s="6" t="n">
         <v>1.3956</v>
       </c>
+      <c r="BW43" s="5" t="inlineStr"/>
       <c r="BX43" s="6">
-        <f>IF(AND(BW43&gt;$BX$12,D43&lt;=$BX$13),D42,"")</f>
+        <f>IF(AND(BV43&gt;$BX$12,D43&lt;=$BX$13),D42,"")</f>
         <v/>
       </c>
       <c r="BY43" s="6">
@@ -10961,7 +10961,7 @@
         <v/>
       </c>
       <c r="CB43" s="6">
-        <f>IF(AND(BQ43&gt;$CB$12,BS43&lt;$CB$13),E42,"")</f>
+        <f>IF(AND(BQ43&gt;$CB$12,BR43&lt;$CB$13),E42,"")</f>
         <v/>
       </c>
       <c r="CC43" s="6">
@@ -11178,24 +11178,24 @@
         <f>IF(COUNT(BA44:BA45)=2,ROUND((BA44/BA45-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR44" s="5" t="inlineStr"/>
-      <c r="BS44" s="6">
+      <c r="BR44" s="6">
         <f>IF(COUNT(BH44:BH45)=2,ROUND((BH44/BH45-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT44" s="5" t="inlineStr"/>
-      <c r="BU44" s="5" t="n">
+      <c r="BS44" s="5" t="inlineStr"/>
+      <c r="BT44" s="5" t="n">
         <v>18.63</v>
       </c>
-      <c r="BV44" s="6">
-        <f>IF(COUNT(BU44:BU45)=2,ROUND((BU44/BU45-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW44" s="6" t="n">
+      <c r="BU44" s="6">
+        <f>IF(COUNT(BT44:BT45)=2,ROUND((BT44/BT45-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV44" s="6" t="n">
         <v>-4.4125</v>
       </c>
+      <c r="BW44" s="5" t="inlineStr"/>
       <c r="BX44" s="6">
-        <f>IF(AND(BW44&gt;$BX$12,D44&lt;=$BX$13),D43,"")</f>
+        <f>IF(AND(BV44&gt;$BX$12,D44&lt;=$BX$13),D43,"")</f>
         <v/>
       </c>
       <c r="BY44" s="6">
@@ -11211,7 +11211,7 @@
         <v/>
       </c>
       <c r="CB44" s="6">
-        <f>IF(AND(BQ44&gt;$CB$12,BS44&lt;$CB$13),E43,"")</f>
+        <f>IF(AND(BQ44&gt;$CB$12,BR44&lt;$CB$13),E43,"")</f>
         <v/>
       </c>
       <c r="CC44" s="6">
@@ -11428,24 +11428,24 @@
         <f>IF(COUNT(BA45:BA46)=2,ROUND((BA45/BA46-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR45" s="5" t="inlineStr"/>
-      <c r="BS45" s="6">
+      <c r="BR45" s="6">
         <f>IF(COUNT(BH45:BH46)=2,ROUND((BH45/BH46-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT45" s="5" t="inlineStr"/>
-      <c r="BU45" s="5" t="n">
+      <c r="BS45" s="5" t="inlineStr"/>
+      <c r="BT45" s="5" t="n">
         <v>19.49</v>
       </c>
-      <c r="BV45" s="6">
-        <f>IF(COUNT(BU45:BU46)=2,ROUND((BU45/BU46-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW45" s="6" t="n">
+      <c r="BU45" s="6">
+        <f>IF(COUNT(BT45:BT46)=2,ROUND((BT45/BT46-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV45" s="6" t="n">
         <v>12.7894</v>
       </c>
+      <c r="BW45" s="5" t="inlineStr"/>
       <c r="BX45" s="6">
-        <f>IF(AND(BW45&gt;$BX$12,D45&lt;=$BX$13),D44,"")</f>
+        <f>IF(AND(BV45&gt;$BX$12,D45&lt;=$BX$13),D44,"")</f>
         <v/>
       </c>
       <c r="BY45" s="6">
@@ -11461,7 +11461,7 @@
         <v/>
       </c>
       <c r="CB45" s="6">
-        <f>IF(AND(BQ45&gt;$CB$12,BS45&lt;$CB$13),E44,"")</f>
+        <f>IF(AND(BQ45&gt;$CB$12,BR45&lt;$CB$13),E44,"")</f>
         <v/>
       </c>
       <c r="CC45" s="6">
@@ -11678,24 +11678,24 @@
         <f>IF(COUNT(BA46:BA47)=2,ROUND((BA46/BA47-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR46" s="5" t="inlineStr"/>
-      <c r="BS46" s="6">
+      <c r="BR46" s="6">
         <f>IF(COUNT(BH46:BH47)=2,ROUND((BH46/BH47-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT46" s="5" t="inlineStr"/>
-      <c r="BU46" s="5" t="n">
+      <c r="BS46" s="5" t="inlineStr"/>
+      <c r="BT46" s="5" t="n">
         <v>17.28</v>
       </c>
-      <c r="BV46" s="6">
-        <f>IF(COUNT(BU46:BU47)=2,ROUND((BU46/BU47-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW46" s="6" t="n">
+      <c r="BU46" s="6">
+        <f>IF(COUNT(BT46:BT47)=2,ROUND((BT46/BT47-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV46" s="6" t="n">
         <v>5.3659</v>
       </c>
+      <c r="BW46" s="5" t="inlineStr"/>
       <c r="BX46" s="6">
-        <f>IF(AND(BW46&gt;$BX$12,D46&lt;=$BX$13),D45,"")</f>
+        <f>IF(AND(BV46&gt;$BX$12,D46&lt;=$BX$13),D45,"")</f>
         <v/>
       </c>
       <c r="BY46" s="6">
@@ -11711,7 +11711,7 @@
         <v/>
       </c>
       <c r="CB46" s="6">
-        <f>IF(AND(BQ46&gt;$CB$12,BS46&lt;$CB$13),E45,"")</f>
+        <f>IF(AND(BQ46&gt;$CB$12,BR46&lt;$CB$13),E45,"")</f>
         <v/>
       </c>
       <c r="CC46" s="6">
@@ -11928,24 +11928,24 @@
         <f>IF(COUNT(BA47:BA48)=2,ROUND((BA47/BA48-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR47" s="5" t="inlineStr"/>
-      <c r="BS47" s="6">
+      <c r="BR47" s="6">
         <f>IF(COUNT(BH47:BH48)=2,ROUND((BH47/BH48-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT47" s="5" t="inlineStr"/>
-      <c r="BU47" s="5" t="n">
+      <c r="BS47" s="5" t="inlineStr"/>
+      <c r="BT47" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="BV47" s="6">
-        <f>IF(COUNT(BU47:BU48)=2,ROUND((BU47/BU48-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW47" s="6" t="n">
+      <c r="BU47" s="6">
+        <f>IF(COUNT(BT47:BT48)=2,ROUND((BT47/BT48-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV47" s="6" t="n">
         <v>-11.0629</v>
       </c>
+      <c r="BW47" s="5" t="inlineStr"/>
       <c r="BX47" s="6">
-        <f>IF(AND(BW47&gt;$BX$12,D47&lt;=$BX$13),D46,"")</f>
+        <f>IF(AND(BV47&gt;$BX$12,D47&lt;=$BX$13),D46,"")</f>
         <v/>
       </c>
       <c r="BY47" s="6">
@@ -11961,7 +11961,7 @@
         <v/>
       </c>
       <c r="CB47" s="6">
-        <f>IF(AND(BQ47&gt;$CB$12,BS47&lt;$CB$13),E46,"")</f>
+        <f>IF(AND(BQ47&gt;$CB$12,BR47&lt;$CB$13),E46,"")</f>
         <v/>
       </c>
       <c r="CC47" s="6">
@@ -12178,24 +12178,24 @@
         <f>IF(COUNT(BA48:BA49)=2,ROUND((BA48/BA49-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR48" s="5" t="inlineStr"/>
-      <c r="BS48" s="6">
+      <c r="BR48" s="6">
         <f>IF(COUNT(BH48:BH49)=2,ROUND((BH48/BH49-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT48" s="5" t="inlineStr"/>
-      <c r="BU48" s="5" t="n">
+      <c r="BS48" s="5" t="inlineStr"/>
+      <c r="BT48" s="5" t="n">
         <v>18.44</v>
       </c>
-      <c r="BV48" s="6">
-        <f>IF(COUNT(BU48:BU49)=2,ROUND((BU48/BU49-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW48" s="6" t="n">
+      <c r="BU48" s="6">
+        <f>IF(COUNT(BT48:BT49)=2,ROUND((BT48/BT49-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV48" s="6" t="n">
         <v>12.3705</v>
       </c>
+      <c r="BW48" s="5" t="inlineStr"/>
       <c r="BX48" s="6">
-        <f>IF(AND(BW48&gt;$BX$12,D48&lt;=$BX$13),D47,"")</f>
+        <f>IF(AND(BV48&gt;$BX$12,D48&lt;=$BX$13),D47,"")</f>
         <v/>
       </c>
       <c r="BY48" s="6">
@@ -12211,7 +12211,7 @@
         <v/>
       </c>
       <c r="CB48" s="6">
-        <f>IF(AND(BQ48&gt;$CB$12,BS48&lt;$CB$13),E47,"")</f>
+        <f>IF(AND(BQ48&gt;$CB$12,BR48&lt;$CB$13),E47,"")</f>
         <v/>
       </c>
       <c r="CC48" s="6">
@@ -12428,24 +12428,24 @@
         <f>IF(COUNT(BA49:BA50)=2,ROUND((BA49/BA50-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR49" s="5" t="inlineStr"/>
-      <c r="BS49" s="6">
+      <c r="BR49" s="6">
         <f>IF(COUNT(BH49:BH50)=2,ROUND((BH49/BH50-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT49" s="5" t="inlineStr"/>
-      <c r="BU49" s="5" t="n">
+      <c r="BS49" s="5" t="inlineStr"/>
+      <c r="BT49" s="5" t="n">
         <v>16.41</v>
       </c>
-      <c r="BV49" s="6">
-        <f>IF(COUNT(BU49:BU50)=2,ROUND((BU49/BU50-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW49" s="6" t="n">
+      <c r="BU49" s="6">
+        <f>IF(COUNT(BT49:BT50)=2,ROUND((BT49/BT50-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV49" s="6" t="n">
         <v>1.2963</v>
       </c>
+      <c r="BW49" s="5" t="inlineStr"/>
       <c r="BX49" s="6">
-        <f>IF(AND(BW49&gt;$BX$12,D49&lt;=$BX$13),D48,"")</f>
+        <f>IF(AND(BV49&gt;$BX$12,D49&lt;=$BX$13),D48,"")</f>
         <v/>
       </c>
       <c r="BY49" s="6">
@@ -12461,7 +12461,7 @@
         <v/>
       </c>
       <c r="CB49" s="6">
-        <f>IF(AND(BQ49&gt;$CB$12,BS49&lt;$CB$13),E48,"")</f>
+        <f>IF(AND(BQ49&gt;$CB$12,BR49&lt;$CB$13),E48,"")</f>
         <v/>
       </c>
       <c r="CC49" s="6">
@@ -12678,24 +12678,24 @@
         <f>IF(COUNT(BA50:BA51)=2,ROUND((BA50/BA51-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR50" s="5" t="inlineStr"/>
-      <c r="BS50" s="6">
+      <c r="BR50" s="6">
         <f>IF(COUNT(BH50:BH51)=2,ROUND((BH50/BH51-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT50" s="5" t="inlineStr"/>
-      <c r="BU50" s="5" t="n">
+      <c r="BS50" s="5" t="inlineStr"/>
+      <c r="BT50" s="5" t="n">
         <v>16.2</v>
       </c>
-      <c r="BV50" s="6">
-        <f>IF(COUNT(BU50:BU51)=2,ROUND((BU50/BU51-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW50" s="6" t="n">
+      <c r="BU50" s="6">
+        <f>IF(COUNT(BT50:BT51)=2,ROUND((BT50/BT51-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV50" s="6" t="n">
         <v>-8.371</v>
       </c>
+      <c r="BW50" s="5" t="inlineStr"/>
       <c r="BX50" s="6">
-        <f>IF(AND(BW50&gt;$BX$12,D50&lt;=$BX$13),D49,"")</f>
+        <f>IF(AND(BV50&gt;$BX$12,D50&lt;=$BX$13),D49,"")</f>
         <v/>
       </c>
       <c r="BY50" s="6">
@@ -12711,7 +12711,7 @@
         <v/>
       </c>
       <c r="CB50" s="6">
-        <f>IF(AND(BQ50&gt;$CB$12,BS50&lt;$CB$13),E49,"")</f>
+        <f>IF(AND(BQ50&gt;$CB$12,BR50&lt;$CB$13),E49,"")</f>
         <v/>
       </c>
       <c r="CC50" s="6">
@@ -12928,24 +12928,24 @@
         <f>IF(COUNT(BA51:BA52)=2,ROUND((BA51/BA52-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR51" s="5" t="inlineStr"/>
-      <c r="BS51" s="6">
+      <c r="BR51" s="6">
         <f>IF(COUNT(BH51:BH52)=2,ROUND((BH51/BH52-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT51" s="5" t="inlineStr"/>
-      <c r="BU51" s="5" t="n">
+      <c r="BS51" s="5" t="inlineStr"/>
+      <c r="BT51" s="5" t="n">
         <v>17.68</v>
       </c>
-      <c r="BV51" s="6">
-        <f>IF(COUNT(BU51:BU52)=2,ROUND((BU51/BU52-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW51" s="6" t="n">
+      <c r="BU51" s="6">
+        <f>IF(COUNT(BT51:BT52)=2,ROUND((BT51/BT52-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV51" s="6" t="n">
         <v>-9.0535</v>
       </c>
+      <c r="BW51" s="5" t="inlineStr"/>
       <c r="BX51" s="6">
-        <f>IF(AND(BW51&gt;$BX$12,D51&lt;=$BX$13),D50,"")</f>
+        <f>IF(AND(BV51&gt;$BX$12,D51&lt;=$BX$13),D50,"")</f>
         <v/>
       </c>
       <c r="BY51" s="6">
@@ -12961,7 +12961,7 @@
         <v/>
       </c>
       <c r="CB51" s="6">
-        <f>IF(AND(BQ51&gt;$CB$12,BS51&lt;$CB$13),E50,"")</f>
+        <f>IF(AND(BQ51&gt;$CB$12,BR51&lt;$CB$13),E50,"")</f>
         <v/>
       </c>
       <c r="CC51" s="6">
@@ -13178,24 +13178,24 @@
         <f>IF(COUNT(BA52:BA53)=2,ROUND((BA52/BA53-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR52" s="5" t="inlineStr"/>
-      <c r="BS52" s="6">
+      <c r="BR52" s="6">
         <f>IF(COUNT(BH52:BH53)=2,ROUND((BH52/BH53-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT52" s="5" t="inlineStr"/>
-      <c r="BU52" s="5" t="n">
+      <c r="BS52" s="5" t="inlineStr"/>
+      <c r="BT52" s="5" t="n">
         <v>19.44</v>
       </c>
-      <c r="BV52" s="6">
-        <f>IF(COUNT(BU52:BU53)=2,ROUND((BU52/BU53-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW52" s="6" t="n">
+      <c r="BU52" s="6">
+        <f>IF(COUNT(BT52:BT53)=2,ROUND((BT52/BT53-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV52" s="6" t="n">
         <v>-12.5113</v>
       </c>
+      <c r="BW52" s="5" t="inlineStr"/>
       <c r="BX52" s="6">
-        <f>IF(AND(BW52&gt;$BX$12,D52&lt;=$BX$13),D51,"")</f>
+        <f>IF(AND(BV52&gt;$BX$12,D52&lt;=$BX$13),D51,"")</f>
         <v/>
       </c>
       <c r="BY52" s="6">
@@ -13211,7 +13211,7 @@
         <v/>
       </c>
       <c r="CB52" s="6">
-        <f>IF(AND(BQ52&gt;$CB$12,BS52&lt;$CB$13),E51,"")</f>
+        <f>IF(AND(BQ52&gt;$CB$12,BR52&lt;$CB$13),E51,"")</f>
         <v/>
       </c>
       <c r="CC52" s="6">
@@ -13428,24 +13428,24 @@
         <f>IF(COUNT(BA53:BA54)=2,ROUND((BA53/BA54-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR53" s="5" t="inlineStr"/>
-      <c r="BS53" s="6">
+      <c r="BR53" s="6">
         <f>IF(COUNT(BH53:BH54)=2,ROUND((BH53/BH54-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT53" s="5" t="inlineStr"/>
-      <c r="BU53" s="5" t="n">
+      <c r="BS53" s="5" t="inlineStr"/>
+      <c r="BT53" s="5" t="n">
         <v>22.22</v>
       </c>
-      <c r="BV53" s="6">
-        <f>IF(COUNT(BU53:BU54)=2,ROUND((BU53/BU54-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW53" s="6" t="n">
+      <c r="BU53" s="6">
+        <f>IF(COUNT(BT53:BT54)=2,ROUND((BT53/BT54-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV53" s="6" t="n">
         <v>11.8269</v>
       </c>
+      <c r="BW53" s="5" t="inlineStr"/>
       <c r="BX53" s="6">
-        <f>IF(AND(BW53&gt;$BX$12,D53&lt;=$BX$13),D52,"")</f>
+        <f>IF(AND(BV53&gt;$BX$12,D53&lt;=$BX$13),D52,"")</f>
         <v/>
       </c>
       <c r="BY53" s="6">
@@ -13461,7 +13461,7 @@
         <v/>
       </c>
       <c r="CB53" s="6">
-        <f>IF(AND(BQ53&gt;$CB$12,BS53&lt;$CB$13),E52,"")</f>
+        <f>IF(AND(BQ53&gt;$CB$12,BR53&lt;$CB$13),E52,"")</f>
         <v/>
       </c>
       <c r="CC53" s="6">
@@ -13678,24 +13678,24 @@
         <f>IF(COUNT(BA54:BA55)=2,ROUND((BA54/BA55-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR54" s="5" t="inlineStr"/>
-      <c r="BS54" s="6">
+      <c r="BR54" s="6">
         <f>IF(COUNT(BH54:BH55)=2,ROUND((BH54/BH55-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT54" s="5" t="inlineStr"/>
-      <c r="BU54" s="5" t="n">
+      <c r="BS54" s="5" t="inlineStr"/>
+      <c r="BT54" s="5" t="n">
         <v>19.87</v>
       </c>
-      <c r="BV54" s="6">
-        <f>IF(COUNT(BU54:BU55)=2,ROUND((BU54/BU55-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW54" s="6" t="n">
+      <c r="BU54" s="6">
+        <f>IF(COUNT(BT54:BT55)=2,ROUND((BT54/BT55-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV54" s="6" t="n">
         <v>5.0211</v>
       </c>
+      <c r="BW54" s="5" t="inlineStr"/>
       <c r="BX54" s="6">
-        <f>IF(AND(BW54&gt;$BX$12,D54&lt;=$BX$13),D53,"")</f>
+        <f>IF(AND(BV54&gt;$BX$12,D54&lt;=$BX$13),D53,"")</f>
         <v/>
       </c>
       <c r="BY54" s="6">
@@ -13711,7 +13711,7 @@
         <v/>
       </c>
       <c r="CB54" s="6">
-        <f>IF(AND(BQ54&gt;$CB$12,BS54&lt;$CB$13),E53,"")</f>
+        <f>IF(AND(BQ54&gt;$CB$12,BR54&lt;$CB$13),E53,"")</f>
         <v/>
       </c>
       <c r="CC54" s="6">
@@ -13928,24 +13928,24 @@
         <f>IF(COUNT(BA55:BA56)=2,ROUND((BA55/BA56-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR55" s="5" t="inlineStr"/>
-      <c r="BS55" s="6">
+      <c r="BR55" s="6">
         <f>IF(COUNT(BH55:BH56)=2,ROUND((BH55/BH56-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT55" s="5" t="inlineStr"/>
-      <c r="BU55" s="5" t="n">
+      <c r="BS55" s="5" t="inlineStr"/>
+      <c r="BT55" s="5" t="n">
         <v>18.92</v>
       </c>
-      <c r="BV55" s="6">
-        <f>IF(COUNT(BU55:BU56)=2,ROUND((BU55/BU56-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW55" s="6" t="n">
+      <c r="BU55" s="6">
+        <f>IF(COUNT(BT55:BT56)=2,ROUND((BT55/BT56-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV55" s="6" t="n">
         <v>-12.0409</v>
       </c>
+      <c r="BW55" s="5" t="inlineStr"/>
       <c r="BX55" s="6">
-        <f>IF(AND(BW55&gt;$BX$12,D55&lt;=$BX$13),D54,"")</f>
+        <f>IF(AND(BV55&gt;$BX$12,D55&lt;=$BX$13),D54,"")</f>
         <v/>
       </c>
       <c r="BY55" s="6">
@@ -13961,7 +13961,7 @@
         <v/>
       </c>
       <c r="CB55" s="6">
-        <f>IF(AND(BQ55&gt;$CB$12,BS55&lt;$CB$13),E54,"")</f>
+        <f>IF(AND(BQ55&gt;$CB$12,BR55&lt;$CB$13),E54,"")</f>
         <v/>
       </c>
       <c r="CC55" s="6">
@@ -14178,24 +14178,24 @@
         <f>IF(COUNT(BA56:BA57)=2,ROUND((BA56/BA57-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR56" s="5" t="inlineStr"/>
-      <c r="BS56" s="6">
+      <c r="BR56" s="6">
         <f>IF(COUNT(BH56:BH57)=2,ROUND((BH56/BH57-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT56" s="5" t="inlineStr"/>
-      <c r="BU56" s="5" t="n">
+      <c r="BS56" s="5" t="inlineStr"/>
+      <c r="BT56" s="5" t="n">
         <v>21.51</v>
       </c>
-      <c r="BV56" s="6">
-        <f>IF(COUNT(BU56:BU57)=2,ROUND((BU56/BU57-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW56" s="6" t="n">
+      <c r="BU56" s="6">
+        <f>IF(COUNT(BT56:BT57)=2,ROUND((BT56/BT57-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV56" s="6" t="n">
         <v>39.6753</v>
       </c>
+      <c r="BW56" s="5" t="inlineStr"/>
       <c r="BX56" s="6">
-        <f>IF(AND(BW56&gt;$BX$12,D56&lt;=$BX$13),D55,"")</f>
+        <f>IF(AND(BV56&gt;$BX$12,D56&lt;=$BX$13),D55,"")</f>
         <v/>
       </c>
       <c r="BY56" s="6">
@@ -14211,7 +14211,7 @@
         <v/>
       </c>
       <c r="CB56" s="6">
-        <f>IF(AND(BQ56&gt;$CB$12,BS56&lt;$CB$13),E55,"")</f>
+        <f>IF(AND(BQ56&gt;$CB$12,BR56&lt;$CB$13),E55,"")</f>
         <v/>
       </c>
       <c r="CC56" s="6">
@@ -14428,24 +14428,24 @@
         <f>IF(COUNT(BA57:BA58)=2,ROUND((BA57/BA58-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR57" s="5" t="inlineStr"/>
-      <c r="BS57" s="6">
+      <c r="BR57" s="6">
         <f>IF(COUNT(BH57:BH58)=2,ROUND((BH57/BH58-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT57" s="5" t="inlineStr"/>
-      <c r="BU57" s="5" t="n">
+      <c r="BS57" s="5" t="inlineStr"/>
+      <c r="BT57" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="BV57" s="6">
-        <f>IF(COUNT(BU57:BU58)=2,ROUND((BU57/BU58-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW57" s="6" t="n">
+      <c r="BU57" s="6">
+        <f>IF(COUNT(BT57:BT58)=2,ROUND((BT57/BT58-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV57" s="6" t="n">
         <v>-4.1096</v>
       </c>
+      <c r="BW57" s="5" t="inlineStr"/>
       <c r="BX57" s="6">
-        <f>IF(AND(BW57&gt;$BX$12,D57&lt;=$BX$13),D56,"")</f>
+        <f>IF(AND(BV57&gt;$BX$12,D57&lt;=$BX$13),D56,"")</f>
         <v/>
       </c>
       <c r="BY57" s="6">
@@ -14461,7 +14461,7 @@
         <v/>
       </c>
       <c r="CB57" s="6">
-        <f>IF(AND(BQ57&gt;$CB$12,BS57&lt;$CB$13),E56,"")</f>
+        <f>IF(AND(BQ57&gt;$CB$12,BR57&lt;$CB$13),E56,"")</f>
         <v/>
       </c>
       <c r="CC57" s="6">
@@ -14678,24 +14678,24 @@
         <f>IF(COUNT(BA58:BA59)=2,ROUND((BA58/BA59-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR58" s="5" t="inlineStr"/>
-      <c r="BS58" s="6">
+      <c r="BR58" s="6">
         <f>IF(COUNT(BH58:BH59)=2,ROUND((BH58/BH59-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT58" s="5" t="inlineStr"/>
-      <c r="BU58" s="5" t="n">
+      <c r="BS58" s="5" t="inlineStr"/>
+      <c r="BT58" s="5" t="n">
         <v>16.06</v>
       </c>
-      <c r="BV58" s="6">
-        <f>IF(COUNT(BU58:BU59)=2,ROUND((BU58/BU59-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW58" s="6" t="n">
+      <c r="BU58" s="6">
+        <f>IF(COUNT(BT58:BT59)=2,ROUND((BT58/BT59-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV58" s="6" t="n">
         <v>1.8389</v>
       </c>
+      <c r="BW58" s="5" t="inlineStr"/>
       <c r="BX58" s="6">
-        <f>IF(AND(BW58&gt;$BX$12,D58&lt;=$BX$13),D57,"")</f>
+        <f>IF(AND(BV58&gt;$BX$12,D58&lt;=$BX$13),D57,"")</f>
         <v/>
       </c>
       <c r="BY58" s="6">
@@ -14711,7 +14711,7 @@
         <v/>
       </c>
       <c r="CB58" s="6">
-        <f>IF(AND(BQ58&gt;$CB$12,BS58&lt;$CB$13),E57,"")</f>
+        <f>IF(AND(BQ58&gt;$CB$12,BR58&lt;$CB$13),E57,"")</f>
         <v/>
       </c>
       <c r="CC58" s="6">
@@ -14928,24 +14928,24 @@
         <f>IF(COUNT(BA59:BA60)=2,ROUND((BA59/BA60-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR59" s="5" t="inlineStr"/>
-      <c r="BS59" s="6">
+      <c r="BR59" s="6">
         <f>IF(COUNT(BH59:BH60)=2,ROUND((BH59/BH60-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT59" s="5" t="inlineStr"/>
-      <c r="BU59" s="5" t="n">
+      <c r="BS59" s="5" t="inlineStr"/>
+      <c r="BT59" s="5" t="n">
         <v>15.77</v>
       </c>
-      <c r="BV59" s="6">
-        <f>IF(COUNT(BU59:BU60)=2,ROUND((BU59/BU60-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW59" s="6" t="n">
+      <c r="BU59" s="6">
+        <f>IF(COUNT(BT59:BT60)=2,ROUND((BT59/BT60-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV59" s="6" t="n">
         <v>-1.7445</v>
       </c>
+      <c r="BW59" s="5" t="inlineStr"/>
       <c r="BX59" s="6">
-        <f>IF(AND(BW59&gt;$BX$12,D59&lt;=$BX$13),D58,"")</f>
+        <f>IF(AND(BV59&gt;$BX$12,D59&lt;=$BX$13),D58,"")</f>
         <v/>
       </c>
       <c r="BY59" s="6">
@@ -14961,7 +14961,7 @@
         <v/>
       </c>
       <c r="CB59" s="6">
-        <f>IF(AND(BQ59&gt;$CB$12,BS59&lt;$CB$13),E58,"")</f>
+        <f>IF(AND(BQ59&gt;$CB$12,BR59&lt;$CB$13),E58,"")</f>
         <v/>
       </c>
       <c r="CC59" s="6">
@@ -15178,24 +15178,24 @@
         <f>IF(COUNT(BA60:BA61)=2,ROUND((BA60/BA61-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR60" s="5" t="inlineStr"/>
-      <c r="BS60" s="6">
+      <c r="BR60" s="6">
         <f>IF(COUNT(BH60:BH61)=2,ROUND((BH60/BH61-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT60" s="5" t="inlineStr"/>
-      <c r="BU60" s="5" t="n">
+      <c r="BS60" s="5" t="inlineStr"/>
+      <c r="BT60" s="5" t="n">
         <v>16.05</v>
       </c>
-      <c r="BV60" s="6">
-        <f>IF(COUNT(BU60:BU61)=2,ROUND((BU60/BU61-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW60" s="6" t="n">
+      <c r="BU60" s="6">
+        <f>IF(COUNT(BT60:BT61)=2,ROUND((BT60/BT61-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV60" s="6" t="n">
         <v>4.765</v>
       </c>
+      <c r="BW60" s="5" t="inlineStr"/>
       <c r="BX60" s="6">
-        <f>IF(AND(BW60&gt;$BX$12,D60&lt;=$BX$13),D59,"")</f>
+        <f>IF(AND(BV60&gt;$BX$12,D60&lt;=$BX$13),D59,"")</f>
         <v/>
       </c>
       <c r="BY60" s="6">
@@ -15211,7 +15211,7 @@
         <v/>
       </c>
       <c r="CB60" s="6">
-        <f>IF(AND(BQ60&gt;$CB$12,BS60&lt;$CB$13),E59,"")</f>
+        <f>IF(AND(BQ60&gt;$CB$12,BR60&lt;$CB$13),E59,"")</f>
         <v/>
       </c>
       <c r="CC60" s="6">
@@ -15428,24 +15428,24 @@
         <f>IF(COUNT(BA61:BA62)=2,ROUND((BA61/BA62-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR61" s="5" t="inlineStr"/>
-      <c r="BS61" s="6">
+      <c r="BR61" s="6">
         <f>IF(COUNT(BH61:BH62)=2,ROUND((BH61/BH62-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT61" s="5" t="inlineStr"/>
-      <c r="BU61" s="5" t="n">
+      <c r="BS61" s="5" t="inlineStr"/>
+      <c r="BT61" s="5" t="n">
         <v>15.32</v>
       </c>
-      <c r="BV61" s="6">
-        <f>IF(COUNT(BU61:BU62)=2,ROUND((BU61/BU62-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW61" s="6" t="n">
+      <c r="BU61" s="6">
+        <f>IF(COUNT(BT61:BT62)=2,ROUND((BT61/BT62-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV61" s="6" t="n">
         <v>-2.6684</v>
       </c>
+      <c r="BW61" s="5" t="inlineStr"/>
       <c r="BX61" s="6">
-        <f>IF(AND(BW61&gt;$BX$12,D61&lt;=$BX$13),D60,"")</f>
+        <f>IF(AND(BV61&gt;$BX$12,D61&lt;=$BX$13),D60,"")</f>
         <v/>
       </c>
       <c r="BY61" s="6">
@@ -15461,7 +15461,7 @@
         <v/>
       </c>
       <c r="CB61" s="6">
-        <f>IF(AND(BQ61&gt;$CB$12,BS61&lt;$CB$13),E60,"")</f>
+        <f>IF(AND(BQ61&gt;$CB$12,BR61&lt;$CB$13),E60,"")</f>
         <v/>
       </c>
       <c r="CC61" s="6">
@@ -15678,24 +15678,24 @@
         <f>IF(COUNT(BA62:BA63)=2,ROUND((BA62/BA63-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR62" s="5" t="inlineStr"/>
-      <c r="BS62" s="6">
+      <c r="BR62" s="6">
         <f>IF(COUNT(BH62:BH63)=2,ROUND((BH62/BH63-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT62" s="5" t="inlineStr"/>
-      <c r="BU62" s="5" t="n">
+      <c r="BS62" s="5" t="inlineStr"/>
+      <c r="BT62" s="5" t="n">
         <v>15.74</v>
       </c>
-      <c r="BV62" s="6">
-        <f>IF(COUNT(BU62:BU63)=2,ROUND((BU62/BU63-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW62" s="6" t="n">
+      <c r="BU62" s="6">
+        <f>IF(COUNT(BT62:BT63)=2,ROUND((BT62/BT63-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV62" s="6" t="n">
         <v>-3.3763</v>
       </c>
+      <c r="BW62" s="5" t="inlineStr"/>
       <c r="BX62" s="6">
-        <f>IF(AND(BW62&gt;$BX$12,D62&lt;=$BX$13),D61,"")</f>
+        <f>IF(AND(BV62&gt;$BX$12,D62&lt;=$BX$13),D61,"")</f>
         <v/>
       </c>
       <c r="BY62" s="6">
@@ -15711,7 +15711,7 @@
         <v/>
       </c>
       <c r="CB62" s="6">
-        <f>IF(AND(BQ62&gt;$CB$12,BS62&lt;$CB$13),E61,"")</f>
+        <f>IF(AND(BQ62&gt;$CB$12,BR62&lt;$CB$13),E61,"")</f>
         <v/>
       </c>
       <c r="CC62" s="6">
@@ -15928,24 +15928,24 @@
         <f>IF(COUNT(BA63:BA64)=2,ROUND((BA63/BA64-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR63" s="5" t="inlineStr"/>
-      <c r="BS63" s="6">
+      <c r="BR63" s="6">
         <f>IF(COUNT(BH63:BH64)=2,ROUND((BH63/BH64-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT63" s="5" t="inlineStr"/>
-      <c r="BU63" s="5" t="n">
+      <c r="BS63" s="5" t="inlineStr"/>
+      <c r="BT63" s="5" t="n">
         <v>16.29</v>
       </c>
-      <c r="BV63" s="6">
-        <f>IF(COUNT(BU63:BU64)=2,ROUND((BU63/BU64-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW63" s="6" t="n">
+      <c r="BU63" s="6">
+        <f>IF(COUNT(BT63:BT64)=2,ROUND((BT63/BT64-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV63" s="6" t="n">
         <v>-4.2328</v>
       </c>
+      <c r="BW63" s="5" t="inlineStr"/>
       <c r="BX63" s="6">
-        <f>IF(AND(BW63&gt;$BX$12,D63&lt;=$BX$13),D62,"")</f>
+        <f>IF(AND(BV63&gt;$BX$12,D63&lt;=$BX$13),D62,"")</f>
         <v/>
       </c>
       <c r="BY63" s="6">
@@ -15961,7 +15961,7 @@
         <v/>
       </c>
       <c r="CB63" s="6">
-        <f>IF(AND(BQ63&gt;$CB$12,BS63&lt;$CB$13),E62,"")</f>
+        <f>IF(AND(BQ63&gt;$CB$12,BR63&lt;$CB$13),E62,"")</f>
         <v/>
       </c>
       <c r="CC63" s="6">
@@ -16178,24 +16178,24 @@
         <f>IF(COUNT(BA64:BA65)=2,ROUND((BA64/BA65-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR64" s="5" t="inlineStr"/>
-      <c r="BS64" s="6">
+      <c r="BR64" s="6">
         <f>IF(COUNT(BH64:BH65)=2,ROUND((BH64/BH65-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT64" s="5" t="inlineStr"/>
-      <c r="BU64" s="5" t="n">
+      <c r="BS64" s="5" t="inlineStr"/>
+      <c r="BT64" s="5" t="n">
         <v>17.01</v>
       </c>
-      <c r="BV64" s="6">
-        <f>IF(COUNT(BU64:BU65)=2,ROUND((BU64/BU65-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW64" s="6" t="n">
+      <c r="BU64" s="6">
+        <f>IF(COUNT(BT64:BT65)=2,ROUND((BT64/BT65-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV64" s="6" t="n">
         <v>1.8563</v>
       </c>
+      <c r="BW64" s="5" t="inlineStr"/>
       <c r="BX64" s="6">
-        <f>IF(AND(BW64&gt;$BX$12,D64&lt;=$BX$13),D63,"")</f>
+        <f>IF(AND(BV64&gt;$BX$12,D64&lt;=$BX$13),D63,"")</f>
         <v/>
       </c>
       <c r="BY64" s="6">
@@ -16211,7 +16211,7 @@
         <v/>
       </c>
       <c r="CB64" s="6">
-        <f>IF(AND(BQ64&gt;$CB$12,BS64&lt;$CB$13),E63,"")</f>
+        <f>IF(AND(BQ64&gt;$CB$12,BR64&lt;$CB$13),E63,"")</f>
         <v/>
       </c>
       <c r="CC64" s="6">
@@ -16428,24 +16428,24 @@
         <f>IF(COUNT(BA65:BA66)=2,ROUND((BA65/BA66-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR65" s="5" t="inlineStr"/>
-      <c r="BS65" s="6">
+      <c r="BR65" s="6">
         <f>IF(COUNT(BH65:BH66)=2,ROUND((BH65/BH66-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT65" s="5" t="inlineStr"/>
-      <c r="BU65" s="5" t="n">
+      <c r="BS65" s="5" t="inlineStr"/>
+      <c r="BT65" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="BV65" s="6">
-        <f>IF(COUNT(BU65:BU66)=2,ROUND((BU65/BU66-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW65" s="6" t="n">
+      <c r="BU65" s="6">
+        <f>IF(COUNT(BT65:BT66)=2,ROUND((BT65/BT66-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV65" s="6" t="n">
         <v>-0.358</v>
       </c>
+      <c r="BW65" s="5" t="inlineStr"/>
       <c r="BX65" s="6">
-        <f>IF(AND(BW65&gt;$BX$12,D65&lt;=$BX$13),D64,"")</f>
+        <f>IF(AND(BV65&gt;$BX$12,D65&lt;=$BX$13),D64,"")</f>
         <v/>
       </c>
       <c r="BY65" s="6">
@@ -16461,7 +16461,7 @@
         <v/>
       </c>
       <c r="CB65" s="6">
-        <f>IF(AND(BQ65&gt;$CB$12,BS65&lt;$CB$13),E64,"")</f>
+        <f>IF(AND(BQ65&gt;$CB$12,BR65&lt;$CB$13),E64,"")</f>
         <v/>
       </c>
       <c r="CC65" s="6">
@@ -16678,24 +16678,24 @@
         <f>IF(COUNT(BA66:BA67)=2,ROUND((BA66/BA67-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR66" s="5" t="inlineStr"/>
-      <c r="BS66" s="6">
+      <c r="BR66" s="6">
         <f>IF(COUNT(BH66:BH67)=2,ROUND((BH66/BH67-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT66" s="5" t="inlineStr"/>
-      <c r="BU66" s="5" t="n">
+      <c r="BS66" s="5" t="inlineStr"/>
+      <c r="BT66" s="5" t="n">
         <v>16.76</v>
       </c>
-      <c r="BV66" s="6">
-        <f>IF(COUNT(BU66:BU67)=2,ROUND((BU66/BU67-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW66" s="6" t="n">
+      <c r="BU66" s="6">
+        <f>IF(COUNT(BT66:BT67)=2,ROUND((BT66/BT67-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV66" s="6" t="n">
         <v>-3.8991</v>
       </c>
+      <c r="BW66" s="5" t="inlineStr"/>
       <c r="BX66" s="6">
-        <f>IF(AND(BW66&gt;$BX$12,D66&lt;=$BX$13),D65,"")</f>
+        <f>IF(AND(BV66&gt;$BX$12,D66&lt;=$BX$13),D65,"")</f>
         <v/>
       </c>
       <c r="BY66" s="6">
@@ -16711,7 +16711,7 @@
         <v/>
       </c>
       <c r="CB66" s="6">
-        <f>IF(AND(BQ66&gt;$CB$12,BS66&lt;$CB$13),E65,"")</f>
+        <f>IF(AND(BQ66&gt;$CB$12,BR66&lt;$CB$13),E65,"")</f>
         <v/>
       </c>
       <c r="CC66" s="6">
@@ -16928,24 +16928,24 @@
         <f>IF(COUNT(BA67:BA68)=2,ROUND((BA67/BA68-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR67" s="5" t="inlineStr"/>
-      <c r="BS67" s="6">
+      <c r="BR67" s="6">
         <f>IF(COUNT(BH67:BH68)=2,ROUND((BH67/BH68-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT67" s="5" t="inlineStr"/>
-      <c r="BU67" s="5" t="n">
+      <c r="BS67" s="5" t="inlineStr"/>
+      <c r="BT67" s="5" t="n">
         <v>17.44</v>
       </c>
-      <c r="BV67" s="6">
-        <f>IF(COUNT(BU67:BU68)=2,ROUND((BU67/BU68-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW67" s="6" t="n">
+      <c r="BU67" s="6">
+        <f>IF(COUNT(BT67:BT68)=2,ROUND((BT67/BT68-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV67" s="6" t="n">
         <v>-3.433</v>
       </c>
+      <c r="BW67" s="5" t="inlineStr"/>
       <c r="BX67" s="6">
-        <f>IF(AND(BW67&gt;$BX$12,D67&lt;=$BX$13),D66,"")</f>
+        <f>IF(AND(BV67&gt;$BX$12,D67&lt;=$BX$13),D66,"")</f>
         <v/>
       </c>
       <c r="BY67" s="6">
@@ -16961,7 +16961,7 @@
         <v/>
       </c>
       <c r="CB67" s="6">
-        <f>IF(AND(BQ67&gt;$CB$12,BS67&lt;$CB$13),E66,"")</f>
+        <f>IF(AND(BQ67&gt;$CB$12,BR67&lt;$CB$13),E66,"")</f>
         <v/>
       </c>
       <c r="CC67" s="6">
@@ -17178,24 +17178,24 @@
         <f>IF(COUNT(BA68:BA69)=2,ROUND((BA68/BA69-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR68" s="5" t="inlineStr"/>
-      <c r="BS68" s="6">
+      <c r="BR68" s="6">
         <f>IF(COUNT(BH68:BH69)=2,ROUND((BH68/BH69-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT68" s="5" t="inlineStr"/>
-      <c r="BU68" s="5" t="n">
+      <c r="BS68" s="5" t="inlineStr"/>
+      <c r="BT68" s="5" t="n">
         <v>18.06</v>
       </c>
-      <c r="BV68" s="6">
-        <f>IF(COUNT(BU68:BU69)=2,ROUND((BU68/BU69-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW68" s="6" t="n">
+      <c r="BU68" s="6">
+        <f>IF(COUNT(BT68:BT69)=2,ROUND((BT68/BT69-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV68" s="6" t="n">
         <v>1.3468</v>
       </c>
+      <c r="BW68" s="5" t="inlineStr"/>
       <c r="BX68" s="6">
-        <f>IF(AND(BW68&gt;$BX$12,D68&lt;=$BX$13),D67,"")</f>
+        <f>IF(AND(BV68&gt;$BX$12,D68&lt;=$BX$13),D67,"")</f>
         <v/>
       </c>
       <c r="BY68" s="6">
@@ -17211,7 +17211,7 @@
         <v/>
       </c>
       <c r="CB68" s="6">
-        <f>IF(AND(BQ68&gt;$CB$12,BS68&lt;$CB$13),E67,"")</f>
+        <f>IF(AND(BQ68&gt;$CB$12,BR68&lt;$CB$13),E67,"")</f>
         <v/>
       </c>
       <c r="CC68" s="6">
@@ -17428,24 +17428,24 @@
         <f>IF(COUNT(BA69:BA70)=2,ROUND((BA69/BA70-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR69" s="5" t="inlineStr"/>
-      <c r="BS69" s="6">
+      <c r="BR69" s="6">
         <f>IF(COUNT(BH69:BH70)=2,ROUND((BH69/BH70-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT69" s="5" t="inlineStr"/>
-      <c r="BU69" s="5" t="n">
+      <c r="BS69" s="5" t="inlineStr"/>
+      <c r="BT69" s="5" t="n">
         <v>17.82</v>
       </c>
-      <c r="BV69" s="6">
-        <f>IF(COUNT(BU69:BU70)=2,ROUND((BU69/BU70-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW69" s="6" t="n">
+      <c r="BU69" s="6">
+        <f>IF(COUNT(BT69:BT70)=2,ROUND((BT69/BT70-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV69" s="6" t="n">
         <v>-3.3098</v>
       </c>
+      <c r="BW69" s="5" t="inlineStr"/>
       <c r="BX69" s="6">
-        <f>IF(AND(BW69&gt;$BX$12,D69&lt;=$BX$13),D68,"")</f>
+        <f>IF(AND(BV69&gt;$BX$12,D69&lt;=$BX$13),D68,"")</f>
         <v/>
       </c>
       <c r="BY69" s="6">
@@ -17461,7 +17461,7 @@
         <v/>
       </c>
       <c r="CB69" s="6">
-        <f>IF(AND(BQ69&gt;$CB$12,BS69&lt;$CB$13),E68,"")</f>
+        <f>IF(AND(BQ69&gt;$CB$12,BR69&lt;$CB$13),E68,"")</f>
         <v/>
       </c>
       <c r="CC69" s="6">
@@ -17678,24 +17678,24 @@
         <f>IF(COUNT(BA70:BA71)=2,ROUND((BA70/BA71-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR70" s="5" t="inlineStr"/>
-      <c r="BS70" s="6">
+      <c r="BR70" s="6">
         <f>IF(COUNT(BH70:BH71)=2,ROUND((BH70/BH71-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT70" s="5" t="inlineStr"/>
-      <c r="BU70" s="5" t="n">
+      <c r="BS70" s="5" t="inlineStr"/>
+      <c r="BT70" s="5" t="n">
         <v>18.43</v>
       </c>
-      <c r="BV70" s="6">
-        <f>IF(COUNT(BU70:BU71)=2,ROUND((BU70/BU71-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW70" s="6" t="n">
+      <c r="BU70" s="6">
+        <f>IF(COUNT(BT70:BT71)=2,ROUND((BT70/BT71-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV70" s="6" t="n">
         <v>6.7787</v>
       </c>
+      <c r="BW70" s="5" t="inlineStr"/>
       <c r="BX70" s="6">
-        <f>IF(AND(BW70&gt;$BX$12,D70&lt;=$BX$13),D69,"")</f>
+        <f>IF(AND(BV70&gt;$BX$12,D70&lt;=$BX$13),D69,"")</f>
         <v/>
       </c>
       <c r="BY70" s="6">
@@ -17711,7 +17711,7 @@
         <v/>
       </c>
       <c r="CB70" s="6">
-        <f>IF(AND(BQ70&gt;$CB$12,BS70&lt;$CB$13),E69,"")</f>
+        <f>IF(AND(BQ70&gt;$CB$12,BR70&lt;$CB$13),E69,"")</f>
         <v/>
       </c>
       <c r="CC70" s="6">
@@ -17928,24 +17928,24 @@
         <f>IF(COUNT(BA71:BA72)=2,ROUND((BA71/BA72-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR71" s="5" t="inlineStr"/>
-      <c r="BS71" s="6">
+      <c r="BR71" s="6">
         <f>IF(COUNT(BH71:BH72)=2,ROUND((BH71/BH72-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT71" s="5" t="inlineStr"/>
-      <c r="BU71" s="5" t="n">
+      <c r="BS71" s="5" t="inlineStr"/>
+      <c r="BT71" s="5" t="n">
         <v>17.26</v>
       </c>
-      <c r="BV71" s="6">
-        <f>IF(COUNT(BU71:BU72)=2,ROUND((BU71/BU72-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW71" s="6" t="n">
+      <c r="BU71" s="6">
+        <f>IF(COUNT(BT71:BT72)=2,ROUND((BT71/BT72-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV71" s="6" t="n">
         <v>-3.4135</v>
       </c>
+      <c r="BW71" s="5" t="inlineStr"/>
       <c r="BX71" s="6">
-        <f>IF(AND(BW71&gt;$BX$12,D71&lt;=$BX$13),D70,"")</f>
+        <f>IF(AND(BV71&gt;$BX$12,D71&lt;=$BX$13),D70,"")</f>
         <v/>
       </c>
       <c r="BY71" s="6">
@@ -17961,7 +17961,7 @@
         <v/>
       </c>
       <c r="CB71" s="6">
-        <f>IF(AND(BQ71&gt;$CB$12,BS71&lt;$CB$13),E70,"")</f>
+        <f>IF(AND(BQ71&gt;$CB$12,BR71&lt;$CB$13),E70,"")</f>
         <v/>
       </c>
       <c r="CC71" s="6">
@@ -18178,24 +18178,24 @@
         <f>IF(COUNT(BA72:BA73)=2,ROUND((BA72/BA73-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR72" s="5" t="inlineStr"/>
-      <c r="BS72" s="6">
+      <c r="BR72" s="6">
         <f>IF(COUNT(BH72:BH73)=2,ROUND((BH72/BH73-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT72" s="5" t="inlineStr"/>
-      <c r="BU72" s="5" t="n">
+      <c r="BS72" s="5" t="inlineStr"/>
+      <c r="BT72" s="5" t="n">
         <v>17.87</v>
       </c>
-      <c r="BV72" s="6">
-        <f>IF(COUNT(BU72:BU73)=2,ROUND((BU72/BU73-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW72" s="6" t="n">
+      <c r="BU72" s="6">
+        <f>IF(COUNT(BT72:BT73)=2,ROUND((BT72/BT73-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV72" s="6" t="n">
         <v>-0.667</v>
       </c>
+      <c r="BW72" s="5" t="inlineStr"/>
       <c r="BX72" s="6">
-        <f>IF(AND(BW72&gt;$BX$12,D72&lt;=$BX$13),D71,"")</f>
+        <f>IF(AND(BV72&gt;$BX$12,D72&lt;=$BX$13),D71,"")</f>
         <v/>
       </c>
       <c r="BY72" s="6">
@@ -18211,7 +18211,7 @@
         <v/>
       </c>
       <c r="CB72" s="6">
-        <f>IF(AND(BQ72&gt;$CB$12,BS72&lt;$CB$13),E71,"")</f>
+        <f>IF(AND(BQ72&gt;$CB$12,BR72&lt;$CB$13),E71,"")</f>
         <v/>
       </c>
       <c r="CC72" s="6">
@@ -18428,24 +18428,24 @@
         <f>IF(COUNT(BA73:BA74)=2,ROUND((BA73/BA74-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR73" s="5" t="inlineStr"/>
-      <c r="BS73" s="6">
+      <c r="BR73" s="6">
         <f>IF(COUNT(BH73:BH74)=2,ROUND((BH73/BH74-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT73" s="5" t="inlineStr"/>
-      <c r="BU73" s="5" t="n">
+      <c r="BS73" s="5" t="inlineStr"/>
+      <c r="BT73" s="5" t="n">
         <v>17.99</v>
       </c>
-      <c r="BV73" s="6">
-        <f>IF(COUNT(BU73:BU74)=2,ROUND((BU73/BU74-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW73" s="6" t="n">
+      <c r="BU73" s="6">
+        <f>IF(COUNT(BT73:BT74)=2,ROUND((BT73/BT74-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV73" s="6" t="n">
         <v>-2.1219</v>
       </c>
+      <c r="BW73" s="5" t="inlineStr"/>
       <c r="BX73" s="6">
-        <f>IF(AND(BW73&gt;$BX$12,D73&lt;=$BX$13),D72,"")</f>
+        <f>IF(AND(BV73&gt;$BX$12,D73&lt;=$BX$13),D72,"")</f>
         <v/>
       </c>
       <c r="BY73" s="6">
@@ -18461,7 +18461,7 @@
         <v/>
       </c>
       <c r="CB73" s="6">
-        <f>IF(AND(BQ73&gt;$CB$12,BS73&lt;$CB$13),E72,"")</f>
+        <f>IF(AND(BQ73&gt;$CB$12,BR73&lt;$CB$13),E72,"")</f>
         <v/>
       </c>
       <c r="CC73" s="6">
@@ -18678,24 +18678,24 @@
         <f>IF(COUNT(BA74:BA75)=2,ROUND((BA74/BA75-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BR74" s="5" t="inlineStr"/>
-      <c r="BS74" s="6">
+      <c r="BR74" s="6">
         <f>IF(COUNT(BH74:BH75)=2,ROUND((BH74/BH75-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="BT74" s="5" t="inlineStr"/>
-      <c r="BU74" s="5" t="n">
+      <c r="BS74" s="5" t="inlineStr"/>
+      <c r="BT74" s="5" t="n">
         <v>18.38</v>
       </c>
-      <c r="BV74" s="6">
-        <f>IF(COUNT(BU74:BU75)=2,ROUND((BU74/BU75-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BW74" s="6" t="n">
+      <c r="BU74" s="6">
+        <f>IF(COUNT(BT74:BT75)=2,ROUND((BT74/BT75-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="BV74" s="6" t="n">
         <v>6.9226</v>
       </c>
+      <c r="BW74" s="5" t="inlineStr"/>
       <c r="BX74" s="6">
-        <f>IF(AND(BW74&gt;$BX$12,D74&lt;=$BX$13),D73,"")</f>
+        <f>IF(AND(BV74&gt;$BX$12,D74&lt;=$BX$13),D73,"")</f>
         <v/>
       </c>
       <c r="BY74" s="6">
@@ -18711,7 +18711,7 @@
         <v/>
       </c>
       <c r="CB74" s="6">
-        <f>IF(AND(BQ74&gt;$CB$12,BS74&lt;$CB$13),E73,"")</f>
+        <f>IF(AND(BQ74&gt;$CB$12,BR74&lt;$CB$13),E73,"")</f>
         <v/>
       </c>
       <c r="CC74" s="6">
@@ -18901,18 +18901,18 @@
       <c r="BO75" s="6" t="inlineStr"/>
       <c r="BP75" s="6" t="inlineStr"/>
       <c r="BQ75" s="6" t="inlineStr"/>
-      <c r="BR75" s="5" t="inlineStr"/>
-      <c r="BS75" s="6" t="inlineStr"/>
-      <c r="BT75" s="5" t="inlineStr"/>
-      <c r="BU75" s="5" t="n">
+      <c r="BR75" s="6" t="inlineStr"/>
+      <c r="BS75" s="5" t="inlineStr"/>
+      <c r="BT75" s="5" t="n">
         <v>17.19</v>
       </c>
-      <c r="BV75" s="6" t="inlineStr"/>
-      <c r="BW75" s="6" t="n">
+      <c r="BU75" s="6" t="inlineStr"/>
+      <c r="BV75" s="6" t="n">
         <v>0.644</v>
       </c>
+      <c r="BW75" s="5" t="inlineStr"/>
       <c r="BX75" s="6">
-        <f>IF(AND(BW75&gt;$BX$12,D75&lt;=$BX$13),D74,"")</f>
+        <f>IF(AND(BV75&gt;$BX$12,D75&lt;=$BX$13),D74,"")</f>
         <v/>
       </c>
       <c r="BY75" s="6">
@@ -18928,7 +18928,7 @@
         <v/>
       </c>
       <c r="CB75" s="6">
-        <f>IF(AND(BQ75&gt;$CB$12,BS75&lt;$CB$13),E74,"")</f>
+        <f>IF(AND(BQ75&gt;$CB$12,BR75&lt;$CB$13),E74,"")</f>
         <v/>
       </c>
       <c r="CC75" s="6">
